--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>310</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.303568532</v>
+        <v>1811.3036050799</v>
       </c>
       <c r="O6" t="n">
-        <v>561504.1062449201</v>
+        <v>561504.1175747691</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7465268817</v>
+        <v>3376.7465222073</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.929763423</v>
+        <v>2985043.925631254</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1234,10 +1234,10 @@
         <v>210</v>
       </c>
       <c r="N21" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371340839</v>
       </c>
       <c r="O21" t="n">
-        <v>824635.7984654789</v>
+        <v>824635.798157619</v>
       </c>
       <c r="P21" t="n">
         <v>4800</v>
@@ -1747,10 +1747,10 @@
         <v>16</v>
       </c>
       <c r="N34" t="n">
-        <v>12837.964266667</v>
+        <v>12837.964861111</v>
       </c>
       <c r="O34" t="n">
-        <v>205407.428266672</v>
+        <v>205407.437777776</v>
       </c>
       <c r="P34" t="n">
         <v>22900</v>
@@ -2001,10 +2001,10 @@
         <v>24</v>
       </c>
       <c r="N40" t="n">
-        <v>15711.966441948</v>
+        <v>15711.966415094</v>
       </c>
       <c r="O40" t="n">
-        <v>377087.194606752</v>
+        <v>377087.193962256</v>
       </c>
       <c r="P40" t="n">
         <v>28500</v>
@@ -2298,10 +2298,10 @@
         <v>53</v>
       </c>
       <c r="N47" t="n">
-        <v>141416.88438871</v>
+        <v>141416.8844164</v>
       </c>
       <c r="O47" t="n">
-        <v>7495094.872601629</v>
+        <v>7495094.874069199</v>
       </c>
       <c r="P47" t="n">
         <v>251900</v>
@@ -2340,10 +2340,10 @@
         <v>16</v>
       </c>
       <c r="N48" t="n">
-        <v>200072.19883562</v>
+        <v>200072.19889655</v>
       </c>
       <c r="O48" t="n">
-        <v>3201155.18136992</v>
+        <v>3201155.1823448</v>
       </c>
       <c r="P48" t="n">
         <v>312000</v>
@@ -2774,10 +2774,10 @@
         <v>14</v>
       </c>
       <c r="N58" t="n">
-        <v>28.165701357466</v>
+        <v>28.165681818182</v>
       </c>
       <c r="O58" t="n">
-        <v>394.319819004524</v>
+        <v>394.319545454548</v>
       </c>
       <c r="P58" t="n">
         <v>6800</v>
@@ -3508,10 +3508,10 @@
         <v>1871</v>
       </c>
       <c r="N75" t="n">
-        <v>1098.0517240829</v>
+        <v>1098.0519160318</v>
       </c>
       <c r="O75" t="n">
-        <v>2054454.775759106</v>
+        <v>2054455.134895498</v>
       </c>
       <c r="P75" t="n">
         <v>1500</v>
@@ -4579,10 +4579,10 @@
         <v>60</v>
       </c>
       <c r="N99" t="n">
-        <v>2033.5815122873</v>
+        <v>2033.5814772727</v>
       </c>
       <c r="O99" t="n">
-        <v>122014.890737238</v>
+        <v>122014.888636362</v>
       </c>
       <c r="P99" t="n">
         <v>4100</v>
@@ -4810,10 +4810,10 @@
         <v>3199</v>
       </c>
       <c r="N104" t="n">
-        <v>3158.8608104732</v>
+        <v>3158.8608123465</v>
       </c>
       <c r="O104" t="n">
-        <v>10105195.73270377</v>
+        <v>10105195.73869645</v>
       </c>
       <c r="P104" t="n">
         <v>5600</v>
@@ -4946,10 +4946,10 @@
         <v>211</v>
       </c>
       <c r="N107" t="n">
-        <v>3230.0679765396</v>
+        <v>3230.0679433681</v>
       </c>
       <c r="O107" t="n">
-        <v>681544.3430498556</v>
+        <v>681544.3360506691</v>
       </c>
       <c r="P107" t="n">
         <v>6200</v>
@@ -5630,10 +5630,10 @@
         <v>318</v>
       </c>
       <c r="N122" t="n">
-        <v>4890.9300453258</v>
+        <v>4890.9300453515</v>
       </c>
       <c r="O122" t="n">
-        <v>1555315.754413605</v>
+        <v>1555315.754421777</v>
       </c>
       <c r="P122" t="n">
         <v>8200</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -6080,19 +6080,19 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="N132" t="n">
         <v>2034.86</v>
       </c>
       <c r="O132" t="n">
-        <v>439529.76</v>
+        <v>297089.56</v>
       </c>
       <c r="P132" t="n">
         <v>3900</v>
       </c>
       <c r="Q132" t="n">
-        <v>842400</v>
+        <v>569400</v>
       </c>
     </row>
     <row r="133">
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -6126,19 +6126,19 @@
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="N133" t="n">
         <v>10716.34</v>
       </c>
       <c r="O133" t="n">
-        <v>450086.28</v>
+        <v>375071.9</v>
       </c>
       <c r="P133" t="n">
         <v>39000</v>
       </c>
       <c r="Q133" t="n">
-        <v>1638000</v>
+        <v>1365000</v>
       </c>
     </row>
     <row r="134">
@@ -6178,10 +6178,10 @@
         <v>288</v>
       </c>
       <c r="N134" t="n">
-        <v>3594.2542925089</v>
+        <v>3594.2542686567</v>
       </c>
       <c r="O134" t="n">
-        <v>1035145.236242563</v>
+        <v>1035145.22937313</v>
       </c>
       <c r="P134" t="n">
         <v>6500</v>
@@ -6268,10 +6268,10 @@
         <v>108</v>
       </c>
       <c r="N136" t="n">
-        <v>3240.850028169</v>
+        <v>3240.85002886</v>
       </c>
       <c r="O136" t="n">
-        <v>350011.803042252</v>
+        <v>350011.80311688</v>
       </c>
       <c r="P136" t="n">
         <v>5200</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -6403,19 +6403,19 @@
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="N139" t="n">
         <v>8154</v>
       </c>
       <c r="O139" t="n">
-        <v>3612222</v>
+        <v>3408372</v>
       </c>
       <c r="P139" t="n">
         <v>13500</v>
       </c>
       <c r="Q139" t="n">
-        <v>5980500</v>
+        <v>5643000</v>
       </c>
     </row>
     <row r="140">
@@ -7128,10 +7128,10 @@
         <v>42</v>
       </c>
       <c r="N155" t="n">
-        <v>4193.85</v>
+        <v>4242.3899305556</v>
       </c>
       <c r="O155" t="n">
-        <v>176141.7</v>
+        <v>178180.3770833352</v>
       </c>
       <c r="P155" t="n">
         <v>7500</v>
@@ -7177,10 +7177,10 @@
         <v>220</v>
       </c>
       <c r="N156" t="n">
-        <v>3041.6600119048</v>
+        <v>3041.6600119617</v>
       </c>
       <c r="O156" t="n">
-        <v>669165.202619056</v>
+        <v>669165.202631574</v>
       </c>
       <c r="P156" t="n">
         <v>5500</v>
@@ -7349,10 +7349,10 @@
         <v>883</v>
       </c>
       <c r="N160" t="n">
-        <v>6441.03</v>
+        <v>6470.8036363636</v>
       </c>
       <c r="O160" t="n">
-        <v>5687429.49</v>
+        <v>5713719.610909059</v>
       </c>
       <c r="P160" t="n">
         <v>10500</v>
@@ -7395,10 +7395,10 @@
         <v>558</v>
       </c>
       <c r="N161" t="n">
-        <v>1592.5679711276</v>
+        <v>1592.5679397781</v>
       </c>
       <c r="O161" t="n">
-        <v>888652.9278892009</v>
+        <v>888652.9103961798</v>
       </c>
       <c r="P161" t="n">
         <v>3900</v>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>4240</v>
+        <v>4080</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -8194,19 +8194,19 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>4240</v>
+        <v>4080</v>
       </c>
       <c r="N179" t="n">
         <v>1387.55</v>
       </c>
       <c r="O179" t="n">
-        <v>5883212</v>
+        <v>5661204</v>
       </c>
       <c r="P179" t="n">
         <v>2300</v>
       </c>
       <c r="Q179" t="n">
-        <v>9752000</v>
+        <v>9384000</v>
       </c>
     </row>
     <row r="180">
@@ -9186,10 +9186,10 @@
         <v>920</v>
       </c>
       <c r="N200" t="n">
-        <v>1630.9228220183</v>
+        <v>1630.9228476208</v>
       </c>
       <c r="O200" t="n">
-        <v>1500448.996256836</v>
+        <v>1500449.019811136</v>
       </c>
       <c r="P200" t="n">
         <v>2500</v>
@@ -9232,10 +9232,10 @@
         <v>5</v>
       </c>
       <c r="N201" t="n">
-        <v>1467.3289090909</v>
+        <v>1467.328030303</v>
       </c>
       <c r="O201" t="n">
-        <v>7336.6445454545</v>
+        <v>7336.640151515001</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9278,10 +9278,10 @@
         <v>512</v>
       </c>
       <c r="N202" t="n">
-        <v>1690.6051240876</v>
+        <v>1690.604715</v>
       </c>
       <c r="O202" t="n">
-        <v>865589.8235328512</v>
+        <v>865589.61408</v>
       </c>
       <c r="P202" t="n">
         <v>2900</v>
@@ -9324,10 +9324,10 @@
         <v>2406</v>
       </c>
       <c r="N203" t="n">
-        <v>1550.1927548066</v>
+        <v>1550.1927793589</v>
       </c>
       <c r="O203" t="n">
-        <v>3729763.76806468</v>
+        <v>3729763.827137514</v>
       </c>
       <c r="P203" t="n">
         <v>2500</v>
@@ -9370,10 +9370,10 @@
         <v>22</v>
       </c>
       <c r="N204" t="n">
-        <v>1579.391452381</v>
+        <v>1579.3914319809</v>
       </c>
       <c r="O204" t="n">
-        <v>34746.61195238199</v>
+        <v>34746.6115035798</v>
       </c>
       <c r="P204" t="n">
         <v>2900</v>
@@ -9416,10 +9416,10 @@
         <v>760</v>
       </c>
       <c r="N205" t="n">
-        <v>2403.5095333845</v>
+        <v>2403.5096714419</v>
       </c>
       <c r="O205" t="n">
-        <v>1826667.24537222</v>
+        <v>1826667.350295844</v>
       </c>
       <c r="P205" t="n">
         <v>3500</v>
@@ -9462,10 +9462,10 @@
         <v>208</v>
       </c>
       <c r="N206" t="n">
-        <v>2521.5499887387</v>
+        <v>2521.5498862344</v>
       </c>
       <c r="O206" t="n">
-        <v>524482.3976576496</v>
+        <v>524482.3763367552</v>
       </c>
       <c r="P206" t="n">
         <v>3900</v>
@@ -11179,10 +11179,10 @@
         <v>159</v>
       </c>
       <c r="N245" t="n">
-        <v>2680.7397012195</v>
+        <v>2680.739700672</v>
       </c>
       <c r="O245" t="n">
-        <v>426237.6124939005</v>
+        <v>426237.6124068479</v>
       </c>
       <c r="P245" t="n">
         <v>4900</v>
@@ -11491,10 +11491,10 @@
         <v>900</v>
       </c>
       <c r="N252" t="n">
-        <v>998.76124730022</v>
+        <v>998.76125748503</v>
       </c>
       <c r="O252" t="n">
-        <v>898885.122570198</v>
+        <v>898885.131736527</v>
       </c>
       <c r="P252" t="n">
         <v>1600</v>
@@ -11586,10 +11586,10 @@
         <v>125</v>
       </c>
       <c r="N254" t="n">
-        <v>4285.1951158107</v>
+        <v>4285.1951469098</v>
       </c>
       <c r="O254" t="n">
-        <v>535649.3894763376</v>
+        <v>535649.393363725</v>
       </c>
       <c r="P254" t="n">
         <v>6900</v>
@@ -11932,10 +11932,10 @@
         <v>32</v>
       </c>
       <c r="N262" t="n">
-        <v>11562.038549223</v>
+        <v>11562.038545455</v>
       </c>
       <c r="O262" t="n">
-        <v>369985.233575136</v>
+        <v>369985.23345456</v>
       </c>
       <c r="P262" t="n">
         <v>18500</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12420,19 +12420,19 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="N273" t="n">
         <v>5431.12</v>
       </c>
       <c r="O273" t="n">
-        <v>260693.76</v>
+        <v>206382.56</v>
       </c>
       <c r="P273" t="n">
         <v>8900</v>
       </c>
       <c r="Q273" t="n">
-        <v>427200</v>
+        <v>338200</v>
       </c>
     </row>
     <row r="274">
@@ -12469,10 +12469,10 @@
         <v>653</v>
       </c>
       <c r="N274" t="n">
-        <v>1560.9979018405</v>
+        <v>1560.9980701754</v>
       </c>
       <c r="O274" t="n">
-        <v>1019331.629901846</v>
+        <v>1019331.739824536</v>
       </c>
       <c r="P274" t="n">
         <v>2900</v>
@@ -12607,10 +12607,10 @@
         <v>188</v>
       </c>
       <c r="N277" t="n">
-        <v>7969.9501638124</v>
+        <v>7969.9501643017</v>
       </c>
       <c r="O277" t="n">
-        <v>1498350.630796731</v>
+        <v>1498350.63088872</v>
       </c>
       <c r="P277" t="n">
         <v>12900</v>
@@ -13448,10 +13448,10 @@
         <v>122</v>
       </c>
       <c r="N295" t="n">
-        <v>3113.8900218818</v>
+        <v>3113.890023175</v>
       </c>
       <c r="O295" t="n">
-        <v>379894.5826695796</v>
+        <v>379894.58282735</v>
       </c>
       <c r="P295" t="n">
         <v>5000</v>
@@ -13816,10 +13816,10 @@
         <v>81</v>
       </c>
       <c r="N303" t="n">
-        <v>5218.1704503582</v>
+        <v>5234.4433367983</v>
       </c>
       <c r="O303" t="n">
-        <v>422671.8064790142</v>
+        <v>423989.9102806623</v>
       </c>
       <c r="P303" t="n">
         <v>8500</v>
@@ -13862,10 +13862,10 @@
         <v>1</v>
       </c>
       <c r="N304" t="n">
-        <v>1595.0095763657</v>
+        <v>1595.0095696489</v>
       </c>
       <c r="O304" t="n">
-        <v>1595.0095763657</v>
+        <v>1595.0095696489</v>
       </c>
       <c r="P304" t="n">
         <v>2600</v>
@@ -13908,10 +13908,10 @@
         <v>123</v>
       </c>
       <c r="N305" t="n">
-        <v>3610.6500218579</v>
+        <v>3610.6500224972</v>
       </c>
       <c r="O305" t="n">
-        <v>444109.9526885217</v>
+        <v>444109.9527671556</v>
       </c>
       <c r="P305" t="n">
         <v>5800</v>
@@ -14371,10 +14371,10 @@
         <v>192</v>
       </c>
       <c r="N315" t="n">
-        <v>1664.3622356902</v>
+        <v>1664.362204192</v>
       </c>
       <c r="O315" t="n">
-        <v>319557.5492525184</v>
+        <v>319557.543204864</v>
       </c>
       <c r="P315" t="n">
         <v>2900</v>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14555,19 +14555,19 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N319" t="n">
         <v>34546</v>
       </c>
       <c r="O319" t="n">
-        <v>241822</v>
+        <v>207276</v>
       </c>
       <c r="P319" t="n">
         <v>57900</v>
       </c>
       <c r="Q319" t="n">
-        <v>405300</v>
+        <v>347400</v>
       </c>
     </row>
     <row r="320">
@@ -14696,10 +14696,10 @@
         <v>824</v>
       </c>
       <c r="N322" t="n">
-        <v>1778.4724932172</v>
+        <v>1778.4724989266</v>
       </c>
       <c r="O322" t="n">
-        <v>1465461.334410973</v>
+        <v>1465461.339115518</v>
       </c>
       <c r="P322" t="n">
         <v>4900</v>
@@ -16812,7 +16812,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16821,19 +16821,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N368" t="n">
         <v>5858</v>
       </c>
       <c r="O368" t="n">
-        <v>199172</v>
+        <v>193314</v>
       </c>
       <c r="P368" t="n">
         <v>9500</v>
       </c>
       <c r="Q368" t="n">
-        <v>323000</v>
+        <v>313500</v>
       </c>
     </row>
     <row r="369">
@@ -16870,10 +16870,10 @@
         <v>53</v>
       </c>
       <c r="N369" t="n">
-        <v>2252.2960775371</v>
+        <v>2252.2960914286</v>
       </c>
       <c r="O369" t="n">
-        <v>119371.6921094663</v>
+        <v>119371.6928457158</v>
       </c>
       <c r="P369" t="n">
         <v>3900</v>
@@ -17196,10 +17196,10 @@
         <v>324</v>
       </c>
       <c r="N376" t="n">
-        <v>2328.1187653599</v>
+        <v>2328.11876101</v>
       </c>
       <c r="O376" t="n">
-        <v>754310.4799766076</v>
+        <v>754310.4785672401</v>
       </c>
       <c r="P376" t="n">
         <v>4500</v>
@@ -17552,7 +17552,7 @@
         </is>
       </c>
       <c r="J384" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="K384" t="n">
         <v>0</v>
@@ -17561,19 +17561,19 @@
         <v>0</v>
       </c>
       <c r="M384" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="N384" t="n">
         <v>4544</v>
       </c>
       <c r="O384" t="n">
-        <v>263552</v>
+        <v>13632</v>
       </c>
       <c r="P384" t="n">
         <v>7900</v>
       </c>
       <c r="Q384" t="n">
-        <v>458200</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="385">
@@ -17840,10 +17840,10 @@
         <v>173</v>
       </c>
       <c r="N390" t="n">
-        <v>4907.8218731563</v>
+        <v>4907.821884273</v>
       </c>
       <c r="O390" t="n">
-        <v>849053.1840560399</v>
+        <v>849053.185979229</v>
       </c>
       <c r="P390" t="n">
         <v>8200</v>
@@ -18070,10 +18070,10 @@
         <v>289</v>
       </c>
       <c r="N395" t="n">
-        <v>3903.7357803468</v>
+        <v>3903.7358031838</v>
       </c>
       <c r="O395" t="n">
-        <v>1128179.640520225</v>
+        <v>1128179.647120118</v>
       </c>
       <c r="P395" t="n">
         <v>7500</v>
@@ -18341,10 +18341,10 @@
         <v>48</v>
       </c>
       <c r="N401" t="n">
-        <v>5869.1728472222</v>
+        <v>5869.1728258706</v>
       </c>
       <c r="O401" t="n">
-        <v>281720.2966666656</v>
+        <v>281720.2956417888</v>
       </c>
       <c r="P401" t="n">
         <v>9500</v>
@@ -19215,10 +19215,10 @@
         <v>292</v>
       </c>
       <c r="N420" t="n">
-        <v>17075.989526424</v>
+        <v>17075.98952512</v>
       </c>
       <c r="O420" t="n">
-        <v>4986188.941715808</v>
+        <v>4986188.94133504</v>
       </c>
       <c r="P420" t="n">
         <v>27500</v>
@@ -20409,10 +20409,10 @@
         <v>1320</v>
       </c>
       <c r="N446" t="n">
-        <v>1516.0388206553</v>
+        <v>1516.0388192979</v>
       </c>
       <c r="O446" t="n">
-        <v>2001171.243264996</v>
+        <v>2001171.241473228</v>
       </c>
       <c r="P446" t="n">
         <v>2300</v>
@@ -20501,10 +20501,10 @@
         <v>136</v>
       </c>
       <c r="N448" t="n">
-        <v>4248.6103213611</v>
+        <v>4248.611257732</v>
       </c>
       <c r="O448" t="n">
-        <v>577811.0037051097</v>
+        <v>577811.131051552</v>
       </c>
       <c r="P448" t="n">
         <v>5900</v>
@@ -20547,10 +20547,10 @@
         <v>240</v>
       </c>
       <c r="N449" t="n">
-        <v>2458.5136716147</v>
+        <v>2458.5136620146</v>
       </c>
       <c r="O449" t="n">
-        <v>590043.2811875279</v>
+        <v>590043.278883504</v>
       </c>
       <c r="P449" t="n">
         <v>3500</v>
@@ -20639,10 +20639,10 @@
         <v>288</v>
       </c>
       <c r="N451" t="n">
-        <v>2079.3843686869</v>
+        <v>2079.3843256997</v>
       </c>
       <c r="O451" t="n">
-        <v>598862.6981818272</v>
+        <v>598862.6858015136</v>
       </c>
       <c r="P451" t="n">
         <v>2900</v>
@@ -20685,10 +20685,10 @@
         <v>264</v>
       </c>
       <c r="N452" t="n">
-        <v>1803.0147280335</v>
+        <v>1803.0147949081</v>
       </c>
       <c r="O452" t="n">
-        <v>475995.888200844</v>
+        <v>475995.9058557384</v>
       </c>
       <c r="P452" t="n">
         <v>2500</v>
@@ -20731,10 +20731,10 @@
         <v>240</v>
       </c>
       <c r="N453" t="n">
-        <v>3306.595599022</v>
+        <v>3306.5955223881</v>
       </c>
       <c r="O453" t="n">
-        <v>793582.94376528</v>
+        <v>793582.925373144</v>
       </c>
       <c r="P453" t="n">
         <v>4900</v>
@@ -20777,10 +20777,10 @@
         <v>192</v>
       </c>
       <c r="N454" t="n">
-        <v>2122.1642044444</v>
+        <v>2122.1641906742</v>
       </c>
       <c r="O454" t="n">
-        <v>407455.5272533249</v>
+        <v>407455.5246094464</v>
       </c>
       <c r="P454" t="n">
         <v>2900</v>
@@ -20823,10 +20823,10 @@
         <v>240</v>
       </c>
       <c r="N455" t="n">
-        <v>2108.7892625995</v>
+        <v>2108.7893319081</v>
       </c>
       <c r="O455" t="n">
-        <v>506109.42302388</v>
+        <v>506109.439657944</v>
       </c>
       <c r="P455" t="n">
         <v>2900</v>
@@ -20869,10 +20869,10 @@
         <v>288</v>
       </c>
       <c r="N456" t="n">
-        <v>2056.0840859599</v>
+        <v>2056.0840312319</v>
       </c>
       <c r="O456" t="n">
-        <v>592152.2167564513</v>
+        <v>592152.2009947873</v>
       </c>
       <c r="P456" t="n">
         <v>2900</v>
@@ -20915,10 +20915,10 @@
         <v>216</v>
       </c>
       <c r="N457" t="n">
-        <v>3224.5675687104</v>
+        <v>3224.5675847458</v>
       </c>
       <c r="O457" t="n">
-        <v>696506.5948414464</v>
+        <v>696506.5983050928</v>
       </c>
       <c r="P457" t="n">
         <v>4500</v>
@@ -20961,10 +20961,10 @@
         <v>384</v>
       </c>
       <c r="N458" t="n">
-        <v>1655.9315593531</v>
+        <v>1655.9315412844</v>
       </c>
       <c r="O458" t="n">
-        <v>635877.7187915904</v>
+        <v>635877.7118532097</v>
       </c>
       <c r="P458" t="n">
         <v>2500</v>
@@ -21191,10 +21191,10 @@
         <v>480</v>
       </c>
       <c r="N463" t="n">
-        <v>1592.2740100137</v>
+        <v>1592.274090065</v>
       </c>
       <c r="O463" t="n">
-        <v>764291.524806576</v>
+        <v>764291.5632312001</v>
       </c>
       <c r="P463" t="n">
         <v>2500</v>
@@ -21322,10 +21322,10 @@
         <v>168</v>
       </c>
       <c r="N466" t="n">
-        <v>2311.9281444759</v>
+        <v>2311.9280428571</v>
       </c>
       <c r="O466" t="n">
-        <v>388403.9282719512</v>
+        <v>388403.9111999928</v>
       </c>
       <c r="P466" t="n">
         <v>3500</v>
@@ -21368,10 +21368,10 @@
         <v>84</v>
       </c>
       <c r="N467" t="n">
-        <v>1906.1878571429</v>
+        <v>1906.1877678571</v>
       </c>
       <c r="O467" t="n">
-        <v>160119.7800000036</v>
+        <v>160119.7724999964</v>
       </c>
       <c r="P467" t="n">
         <v>2900</v>
@@ -21414,10 +21414,10 @@
         <v>216</v>
       </c>
       <c r="N468" t="n">
-        <v>3033.7328518519</v>
+        <v>3033.7328200371</v>
       </c>
       <c r="O468" t="n">
-        <v>655286.2960000103</v>
+        <v>655286.2891280135</v>
       </c>
       <c r="P468" t="n">
         <v>4500</v>
@@ -21460,10 +21460,10 @@
         <v>456</v>
       </c>
       <c r="N469" t="n">
-        <v>2060.1610697674</v>
+        <v>2060.1609859155</v>
       </c>
       <c r="O469" t="n">
-        <v>939433.4478139344</v>
+        <v>939433.4095774681</v>
       </c>
       <c r="P469" t="n">
         <v>2900</v>
@@ -21506,10 +21506,10 @@
         <v>120</v>
       </c>
       <c r="N470" t="n">
-        <v>1668.6124489796</v>
+        <v>1668.6125935484</v>
       </c>
       <c r="O470" t="n">
-        <v>200233.493877552</v>
+        <v>200233.511225808</v>
       </c>
       <c r="P470" t="n">
         <v>2500</v>
@@ -21552,10 +21552,10 @@
         <v>192</v>
       </c>
       <c r="N471" t="n">
-        <v>2546.9861569689</v>
+        <v>2546.986027972</v>
       </c>
       <c r="O471" t="n">
-        <v>489021.3421380288</v>
+        <v>489021.317370624</v>
       </c>
       <c r="P471" t="n">
         <v>3900</v>
@@ -21598,10 +21598,10 @@
         <v>900</v>
       </c>
       <c r="N472" t="n">
-        <v>1259.2741948888</v>
+        <v>1259.2742318172</v>
       </c>
       <c r="O472" t="n">
-        <v>1133346.77539992</v>
+        <v>1133346.80863548</v>
       </c>
       <c r="P472" t="n">
         <v>1900</v>
@@ -21731,10 +21731,10 @@
         <v>192</v>
       </c>
       <c r="N475" t="n">
-        <v>2556.7442028986</v>
+        <v>2556.7442542787</v>
       </c>
       <c r="O475" t="n">
-        <v>490894.8869565312</v>
+        <v>490894.8968215104</v>
       </c>
       <c r="P475" t="n">
         <v>3900</v>
@@ -21821,10 +21821,10 @@
         <v>660</v>
       </c>
       <c r="N477" t="n">
-        <v>692.1519887834301</v>
+        <v>692.151995671</v>
       </c>
       <c r="O477" t="n">
-        <v>456820.3125970638</v>
+        <v>456820.31714286</v>
       </c>
       <c r="P477" t="n">
         <v>1200</v>
@@ -22281,10 +22281,10 @@
         <v>248</v>
       </c>
       <c r="N487" t="n">
-        <v>2857.22</v>
+        <v>2861.1357880311</v>
       </c>
       <c r="O487" t="n">
-        <v>708590.5599999999</v>
+        <v>709561.6754317129</v>
       </c>
       <c r="P487" t="n">
         <v>4900</v>
@@ -22518,10 +22518,10 @@
         <v>360</v>
       </c>
       <c r="N492" t="n">
-        <v>1530.4499206664</v>
+        <v>1530.4499206349</v>
       </c>
       <c r="O492" t="n">
-        <v>550961.971439904</v>
+        <v>550961.9714285641</v>
       </c>
       <c r="P492" t="n">
         <v>2600</v>
@@ -22875,7 +22875,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -22884,19 +22884,19 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="N500" t="n">
         <v>2357.74</v>
       </c>
       <c r="O500" t="n">
-        <v>198050.16</v>
+        <v>103740.56</v>
       </c>
       <c r="P500" t="n">
         <v>3000</v>
       </c>
       <c r="Q500" t="n">
-        <v>252000</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="501">
@@ -22977,10 +22977,10 @@
         <v>306</v>
       </c>
       <c r="N502" t="n">
-        <v>1690.8700087222</v>
+        <v>1690.8700087336</v>
       </c>
       <c r="O502" t="n">
-        <v>517406.2226689932</v>
+        <v>517406.2226724816</v>
       </c>
       <c r="P502" t="n">
         <v>3000</v>
@@ -23261,10 +23261,10 @@
         <v>9193</v>
       </c>
       <c r="N508" t="n">
-        <v>345.55838654429</v>
+        <v>345.55838640256</v>
       </c>
       <c r="O508" t="n">
-        <v>3176718.247501658</v>
+        <v>3176718.246198734</v>
       </c>
       <c r="P508" t="n">
         <v>600</v>
@@ -23864,10 +23864,10 @@
         <v>1325</v>
       </c>
       <c r="N521" t="n">
-        <v>517.28707627294</v>
+        <v>517.28716412902</v>
       </c>
       <c r="O521" t="n">
-        <v>685405.3760616455</v>
+        <v>685405.4924709515</v>
       </c>
       <c r="P521" t="n">
         <v>900</v>
@@ -24287,10 +24287,10 @@
         <v>1009</v>
       </c>
       <c r="N530" t="n">
-        <v>3110.8438819661</v>
+        <v>3110.8436976288</v>
       </c>
       <c r="O530" t="n">
-        <v>3138841.476903795</v>
+        <v>3138841.290907459</v>
       </c>
       <c r="P530" t="n">
         <v>4500</v>
@@ -24738,10 +24738,10 @@
         <v>20666</v>
       </c>
       <c r="N540" t="n">
-        <v>703.79553851454</v>
+        <v>703.79553051727</v>
       </c>
       <c r="O540" t="n">
-        <v>14544638.59894148</v>
+        <v>14544638.4336699</v>
       </c>
       <c r="P540" t="n">
         <v>900</v>
@@ -24775,7 +24775,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24784,19 +24784,19 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N541" t="n">
-        <v>3182.2510791367</v>
+        <v>3182.2510752688</v>
       </c>
       <c r="O541" t="n">
-        <v>213210.8223021589</v>
+        <v>175023.809139784</v>
       </c>
       <c r="P541" t="n">
         <v>6900</v>
       </c>
       <c r="Q541" t="n">
-        <v>462300</v>
+        <v>379500</v>
       </c>
     </row>
     <row r="542">
@@ -24879,10 +24879,10 @@
         <v>102</v>
       </c>
       <c r="N543" t="n">
-        <v>2501.3856451613</v>
+        <v>2501.3856275304</v>
       </c>
       <c r="O543" t="n">
-        <v>255141.3358064526</v>
+        <v>255141.3340081008</v>
       </c>
       <c r="P543" t="n">
         <v>4100</v>
@@ -25245,10 +25245,10 @@
         <v>47</v>
       </c>
       <c r="N551" t="n">
-        <v>1595.5196456996</v>
+        <v>1595.5195815035</v>
       </c>
       <c r="O551" t="n">
-        <v>74989.42334788119</v>
+        <v>74989.42033066449</v>
       </c>
       <c r="P551" t="n">
         <v>2500</v>
@@ -25862,7 +25862,7 @@
         </is>
       </c>
       <c r="J564" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K564" t="n">
         <v>0</v>
@@ -25871,19 +25871,19 @@
         <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N564" t="n">
         <v>28615.2</v>
       </c>
       <c r="O564" t="n">
-        <v>1602451.2</v>
+        <v>1459375.2</v>
       </c>
       <c r="P564" t="n">
         <v>36500</v>
       </c>
       <c r="Q564" t="n">
-        <v>2044000</v>
+        <v>1861500</v>
       </c>
     </row>
     <row r="565">
@@ -26015,10 +26015,10 @@
         <v>18</v>
       </c>
       <c r="N567" t="n">
-        <v>11866.99440678</v>
+        <v>11866.994561404</v>
       </c>
       <c r="O567" t="n">
-        <v>213605.89932204</v>
+        <v>213605.902105272</v>
       </c>
       <c r="P567" t="n">
         <v>55000</v>
@@ -29455,10 +29455,10 @@
         <v>1135</v>
       </c>
       <c r="N639" t="n">
-        <v>7046.9398310097</v>
+        <v>7046.9398308668</v>
       </c>
       <c r="O639" t="n">
-        <v>7998276.70819601</v>
+        <v>7998276.708033818</v>
       </c>
       <c r="P639" t="n">
         <v>9900</v>
@@ -30856,10 +30856,10 @@
         <v>190</v>
       </c>
       <c r="N670" t="n">
-        <v>2523.3377672076</v>
+        <v>2523.3377665827</v>
       </c>
       <c r="O670" t="n">
-        <v>479434.175769444</v>
+        <v>479434.175650713</v>
       </c>
       <c r="P670" t="n">
         <v>2800</v>
@@ -31216,10 +31216,10 @@
         <v>93</v>
       </c>
       <c r="N678" t="n">
-        <v>4985.4042105263</v>
+        <v>4985.4043478261</v>
       </c>
       <c r="O678" t="n">
-        <v>463642.5915789459</v>
+        <v>463642.6043478273</v>
       </c>
       <c r="P678" t="n">
         <v>7900</v>
@@ -31267,10 +31267,10 @@
         <v>19</v>
       </c>
       <c r="N679" t="n">
-        <v>1547.8820987654</v>
+        <v>1547.8821518987</v>
       </c>
       <c r="O679" t="n">
-        <v>29409.7598765426</v>
+        <v>29409.7608860753</v>
       </c>
       <c r="P679" t="n">
         <v>5500</v>
@@ -31318,10 +31318,10 @@
         <v>310</v>
       </c>
       <c r="N680" t="n">
-        <v>1757.3204971319</v>
+        <v>1757.320503876</v>
       </c>
       <c r="O680" t="n">
-        <v>544769.354110889</v>
+        <v>544769.35620156</v>
       </c>
       <c r="P680" t="n">
         <v>2000</v>
@@ -32289,10 +32289,10 @@
         <v>200</v>
       </c>
       <c r="N701" t="n">
-        <v>1319.3608426966</v>
+        <v>1319.3608695652</v>
       </c>
       <c r="O701" t="n">
-        <v>263872.16853932</v>
+        <v>263872.17391304</v>
       </c>
       <c r="P701" t="n">
         <v>3500</v>
@@ -32437,10 +32437,10 @@
         <v>18</v>
       </c>
       <c r="N704" t="n">
-        <v>2432.1338016529</v>
+        <v>2432.1338655462</v>
       </c>
       <c r="O704" t="n">
-        <v>43778.4084297522</v>
+        <v>43778.4095798316</v>
       </c>
       <c r="P704" t="n">
         <v>4500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -7128,10 +7128,10 @@
         <v>42</v>
       </c>
       <c r="N155" t="n">
-        <v>4242.3899305556</v>
+        <v>4193.85</v>
       </c>
       <c r="O155" t="n">
-        <v>178180.3770833352</v>
+        <v>176141.7</v>
       </c>
       <c r="P155" t="n">
         <v>7500</v>
@@ -7349,10 +7349,10 @@
         <v>883</v>
       </c>
       <c r="N160" t="n">
-        <v>6470.8036363636</v>
+        <v>6441.03</v>
       </c>
       <c r="O160" t="n">
-        <v>5713719.610909059</v>
+        <v>5687429.49</v>
       </c>
       <c r="P160" t="n">
         <v>10500</v>
@@ -13816,10 +13816,10 @@
         <v>81</v>
       </c>
       <c r="N303" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O303" t="n">
-        <v>423989.9102806623</v>
+        <v>422671.8070478205</v>
       </c>
       <c r="P303" t="n">
         <v>8500</v>
@@ -22281,10 +22281,10 @@
         <v>248</v>
       </c>
       <c r="N487" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O487" t="n">
-        <v>709561.6754317129</v>
+        <v>708590.5599999999</v>
       </c>
       <c r="P487" t="n">
         <v>4900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -675,10 +675,10 @@
         <v>51</v>
       </c>
       <c r="N7" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O7" t="n">
-        <v>1388523.012552294</v>
+        <v>1377000</v>
       </c>
       <c r="P7" t="n">
         <v>30000</v>
@@ -831,10 +831,10 @@
         <v>55</v>
       </c>
       <c r="N11" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O11" t="n">
-        <v>318144.3046460195</v>
+        <v>316742.7878318605</v>
       </c>
       <c r="P11" t="n">
         <v>16900</v>
@@ -1354,10 +1354,10 @@
         <v>92</v>
       </c>
       <c r="N24" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="O24" t="n">
-        <v>222779.6235294096</v>
+        <v>221996.1082352952</v>
       </c>
       <c r="P24" t="n">
         <v>4700</v>
@@ -1393,10 +1393,10 @@
         <v>102</v>
       </c>
       <c r="N25" t="n">
-        <v>2487.0572046589</v>
+        <v>2474.7042429285</v>
       </c>
       <c r="O25" t="n">
-        <v>253679.8348752078</v>
+        <v>252419.832778707</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -1627,10 +1627,10 @@
         <v>35</v>
       </c>
       <c r="N31" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O31" t="n">
-        <v>752875.657468865</v>
+        <v>746679.1499999999</v>
       </c>
       <c r="P31" t="n">
         <v>30000</v>
@@ -2001,10 +2001,10 @@
         <v>24</v>
       </c>
       <c r="N40" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O40" t="n">
-        <v>380033.185312512</v>
+        <v>377087.190937512</v>
       </c>
       <c r="P40" t="n">
         <v>28500</v>
@@ -2636,10 +2636,10 @@
         <v>39</v>
       </c>
       <c r="N55" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O55" t="n">
-        <v>1062077.58620691</v>
+        <v>1053000</v>
       </c>
       <c r="P55" t="n">
         <v>20000</v>
@@ -3066,10 +3066,10 @@
         <v>42</v>
       </c>
       <c r="N65" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O65" t="n">
-        <v>108229.9111111092</v>
+        <v>107660.28</v>
       </c>
       <c r="P65" t="n">
         <v>4700</v>
@@ -3872,10 +3872,10 @@
         <v>22</v>
       </c>
       <c r="N83" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O83" t="n">
-        <v>299741.17977012</v>
+        <v>299053.7</v>
       </c>
       <c r="P83" t="n">
         <v>25500</v>
@@ -5858,10 +5858,10 @@
         <v>326</v>
       </c>
       <c r="N127" t="n">
-        <v>2289.4664730119</v>
+        <v>2267.0481788216</v>
       </c>
       <c r="O127" t="n">
-        <v>746366.0702018794</v>
+        <v>739057.7062958415</v>
       </c>
       <c r="P127" t="n">
         <v>3900</v>
@@ -6360,10 +6360,10 @@
         <v>123</v>
       </c>
       <c r="N138" t="n">
-        <v>4898.3218562874</v>
+        <v>4891</v>
       </c>
       <c r="O138" t="n">
-        <v>602493.5883233502</v>
+        <v>601593</v>
       </c>
       <c r="P138" t="n">
         <v>8200</v>
@@ -9544,10 +9544,10 @@
         <v>11</v>
       </c>
       <c r="N208" t="n">
-        <v>11658.147712418</v>
+        <v>11507.72</v>
       </c>
       <c r="O208" t="n">
-        <v>128239.624836598</v>
+        <v>126584.92</v>
       </c>
       <c r="P208" t="n">
         <v>25800</v>
@@ -9994,10 +9994,10 @@
         <v>5</v>
       </c>
       <c r="N218" t="n">
-        <v>19900</v>
+        <v>15920</v>
       </c>
       <c r="O218" t="n">
-        <v>99500</v>
+        <v>79600</v>
       </c>
       <c r="P218" t="n">
         <v>19900</v>
@@ -10173,10 +10173,10 @@
         <v>36</v>
       </c>
       <c r="N222" t="n">
-        <v>9301.333333333299</v>
+        <v>8720</v>
       </c>
       <c r="O222" t="n">
-        <v>334847.9999999988</v>
+        <v>313920</v>
       </c>
       <c r="P222" t="n">
         <v>10900</v>
@@ -10756,10 +10756,10 @@
         <v>2</v>
       </c>
       <c r="N235" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="O235" t="n">
-        <v>9016.2511210762</v>
+        <v>8976</v>
       </c>
       <c r="P235" t="n">
         <v>6200</v>
@@ -10797,10 +10797,10 @@
         <v>94</v>
       </c>
       <c r="N236" t="n">
-        <v>2613.7446197991</v>
+        <v>2610</v>
       </c>
       <c r="O236" t="n">
-        <v>245691.9942611154</v>
+        <v>245340</v>
       </c>
       <c r="P236" t="n">
         <v>3200</v>
@@ -11978,10 +11978,10 @@
         <v>22</v>
       </c>
       <c r="N263" t="n">
-        <v>13805.304244604</v>
+        <v>13513.64294964</v>
       </c>
       <c r="O263" t="n">
-        <v>303716.693381288</v>
+        <v>297300.14489208</v>
       </c>
       <c r="P263" t="n">
         <v>21900</v>
@@ -12423,10 +12423,10 @@
         <v>38</v>
       </c>
       <c r="N273" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O273" t="n">
-        <v>207238.9191701262</v>
+        <v>206382.56</v>
       </c>
       <c r="P273" t="n">
         <v>8900</v>
@@ -12561,10 +12561,10 @@
         <v>32</v>
       </c>
       <c r="N276" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O276" t="n">
-        <v>871263.111111104</v>
+        <v>859328</v>
       </c>
       <c r="P276" t="n">
         <v>43900</v>
@@ -13074,10 +13074,10 @@
         <v>35</v>
       </c>
       <c r="N287" t="n">
-        <v>7408.8065217391</v>
+        <v>5875.95</v>
       </c>
       <c r="O287" t="n">
-        <v>259308.2282608685</v>
+        <v>205658.25</v>
       </c>
       <c r="P287" t="n">
         <v>5900</v>
@@ -13448,10 +13448,10 @@
         <v>122</v>
       </c>
       <c r="N295" t="n">
-        <v>3117.5970357143</v>
+        <v>3113.8900238095</v>
       </c>
       <c r="O295" t="n">
-        <v>380346.8383571446</v>
+        <v>379894.582904759</v>
       </c>
       <c r="P295" t="n">
         <v>5000</v>
@@ -13678,10 +13678,10 @@
         <v>5</v>
       </c>
       <c r="N300" t="n">
-        <v>9099.032608695699</v>
+        <v>8878.450000000001</v>
       </c>
       <c r="O300" t="n">
-        <v>45495.1630434785</v>
+        <v>44392.25</v>
       </c>
       <c r="P300" t="n">
         <v>14100</v>
@@ -13724,10 +13724,10 @@
         <v>144</v>
       </c>
       <c r="N301" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O301" t="n">
-        <v>359816.0882637312</v>
+        <v>359421.12</v>
       </c>
       <c r="P301" t="n">
         <v>4100</v>
@@ -14141,10 +14141,10 @@
         <v>77</v>
       </c>
       <c r="N310" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O310" t="n">
-        <v>305684.3946287131</v>
+        <v>305306.54</v>
       </c>
       <c r="P310" t="n">
         <v>6500</v>
@@ -14187,10 +14187,10 @@
         <v>36</v>
       </c>
       <c r="N311" t="n">
-        <v>5844.4237327189</v>
+        <v>5791.05</v>
       </c>
       <c r="O311" t="n">
-        <v>210399.2543778804</v>
+        <v>208477.8</v>
       </c>
       <c r="P311" t="n">
         <v>9300</v>
@@ -14466,10 +14466,10 @@
         <v>19</v>
       </c>
       <c r="N317" t="n">
-        <v>44124.685714286</v>
+        <v>42899</v>
       </c>
       <c r="O317" t="n">
-        <v>838369.0285714341</v>
+        <v>815081</v>
       </c>
       <c r="P317" t="n">
         <v>70900</v>
@@ -14834,10 +14834,10 @@
         <v>151</v>
       </c>
       <c r="N325" t="n">
-        <v>22795.894912427</v>
+        <v>22739</v>
       </c>
       <c r="O325" t="n">
-        <v>3442180.131776477</v>
+        <v>3433589</v>
       </c>
       <c r="P325" t="n">
         <v>36900</v>
@@ -14926,10 +14926,10 @@
         <v>143</v>
       </c>
       <c r="N327" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O327" t="n">
-        <v>2301162.467844526</v>
+        <v>2296294</v>
       </c>
       <c r="P327" t="n">
         <v>25900</v>
@@ -16594,10 +16594,10 @@
         <v>8</v>
       </c>
       <c r="N363" t="n">
-        <v>9704.4375</v>
+        <v>8508</v>
       </c>
       <c r="O363" t="n">
-        <v>77635.5</v>
+        <v>68064</v>
       </c>
       <c r="P363" t="n">
         <v>14500</v>
@@ -17014,10 +17014,10 @@
         <v>4</v>
       </c>
       <c r="N372" t="n">
-        <v>9368.9914285714</v>
+        <v>7715.64</v>
       </c>
       <c r="O372" t="n">
-        <v>37475.9657142856</v>
+        <v>30862.56</v>
       </c>
       <c r="P372" t="n">
         <v>9900</v>
@@ -17196,10 +17196,10 @@
         <v>119</v>
       </c>
       <c r="N376" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O376" t="n">
-        <v>2588061.296213862</v>
+        <v>2579444</v>
       </c>
       <c r="P376" t="n">
         <v>34900</v>
@@ -17702,10 +17702,10 @@
         <v>20</v>
       </c>
       <c r="N387" t="n">
-        <v>18473.630136986</v>
+        <v>17981</v>
       </c>
       <c r="O387" t="n">
-        <v>369472.60273972</v>
+        <v>359620</v>
       </c>
       <c r="P387" t="n">
         <v>29900</v>
@@ -18525,10 +18525,10 @@
         <v>18</v>
       </c>
       <c r="N405" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O405" t="n">
-        <v>493603.2</v>
+        <v>489348</v>
       </c>
       <c r="P405" t="n">
         <v>43900</v>
@@ -18571,10 +18571,10 @@
         <v>157</v>
       </c>
       <c r="N406" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O406" t="n">
-        <v>612923.9095785514</v>
+        <v>611986</v>
       </c>
       <c r="P406" t="n">
         <v>6900</v>
@@ -18617,10 +18617,10 @@
         <v>151</v>
       </c>
       <c r="N407" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O407" t="n">
-        <v>2051404.464555066</v>
+        <v>2048315</v>
       </c>
       <c r="P407" t="n">
         <v>22500</v>
@@ -18847,10 +18847,10 @@
         <v>159</v>
       </c>
       <c r="N412" t="n">
-        <v>8836.1575342466</v>
+        <v>8806</v>
       </c>
       <c r="O412" t="n">
-        <v>1404949.04794521</v>
+        <v>1400154</v>
       </c>
       <c r="P412" t="n">
         <v>14900</v>
@@ -19673,10 +19673,10 @@
         <v>120</v>
       </c>
       <c r="N430" t="n">
-        <v>3647.235915493</v>
+        <v>3639.35</v>
       </c>
       <c r="O430" t="n">
-        <v>437668.30985916</v>
+        <v>436722</v>
       </c>
       <c r="P430" t="n">
         <v>7500</v>
@@ -19811,10 +19811,10 @@
         <v>15</v>
       </c>
       <c r="N433" t="n">
-        <v>10816.221634615</v>
+        <v>10713.21</v>
       </c>
       <c r="O433" t="n">
-        <v>162243.324519225</v>
+        <v>160698.15</v>
       </c>
       <c r="P433" t="n">
         <v>20900</v>
@@ -19995,10 +19995,10 @@
         <v>21</v>
       </c>
       <c r="N437" t="n">
-        <v>21937.5</v>
+        <v>21762</v>
       </c>
       <c r="O437" t="n">
-        <v>460687.5</v>
+        <v>457002</v>
       </c>
       <c r="P437" t="n">
         <v>35900</v>
@@ -25202,10 +25202,10 @@
         <v>7</v>
       </c>
       <c r="N550" t="n">
-        <v>8330.0435897436</v>
+        <v>7923.7</v>
       </c>
       <c r="O550" t="n">
-        <v>58310.3051282052</v>
+        <v>55465.9</v>
       </c>
       <c r="P550" t="n">
         <v>16600</v>
@@ -25689,10 +25689,10 @@
         <v>35</v>
       </c>
       <c r="N560" t="n">
-        <v>2870.9917808219</v>
+        <v>2832.1946575342</v>
       </c>
       <c r="O560" t="n">
-        <v>100484.7123287665</v>
+        <v>99126.813013697</v>
       </c>
       <c r="P560" t="n">
         <v>12900</v>
@@ -25782,10 +25782,10 @@
         <v>51</v>
       </c>
       <c r="N562" t="n">
-        <v>29585.206779661</v>
+        <v>28615.2</v>
       </c>
       <c r="O562" t="n">
-        <v>1508845.545762711</v>
+        <v>1459375.2</v>
       </c>
       <c r="P562" t="n">
         <v>36500</v>
@@ -25831,10 +25831,10 @@
         <v>11</v>
       </c>
       <c r="N563" t="n">
-        <v>18030.611052632</v>
+        <v>16313.41</v>
       </c>
       <c r="O563" t="n">
-        <v>198336.721578952</v>
+        <v>179447.51</v>
       </c>
       <c r="P563" t="n">
         <v>33500</v>
@@ -25972,10 +25972,10 @@
         <v>62</v>
       </c>
       <c r="N566" t="n">
-        <v>10459.349677419</v>
+        <v>10348.08</v>
       </c>
       <c r="O566" t="n">
-        <v>648479.679999978</v>
+        <v>641580.96</v>
       </c>
       <c r="P566" t="n">
         <v>16900</v>
@@ -26021,10 +26021,10 @@
         <v>40</v>
       </c>
       <c r="N567" t="n">
-        <v>10806.564102564</v>
+        <v>10536.4</v>
       </c>
       <c r="O567" t="n">
-        <v>432262.56410256</v>
+        <v>421456</v>
       </c>
       <c r="P567" t="n">
         <v>16900</v>
@@ -26119,10 +26119,10 @@
         <v>5</v>
       </c>
       <c r="N569" t="n">
-        <v>10649.1</v>
+        <v>9874.620000000001</v>
       </c>
       <c r="O569" t="n">
-        <v>53245.5</v>
+        <v>49373.10000000001</v>
       </c>
       <c r="P569" t="n">
         <v>14700</v>
@@ -26508,10 +26508,10 @@
         <v>25</v>
       </c>
       <c r="N577" t="n">
-        <v>10020.157196262</v>
+        <v>9746.8801869159</v>
       </c>
       <c r="O577" t="n">
-        <v>250503.92990655</v>
+        <v>243672.0046728975</v>
       </c>
       <c r="P577" t="n">
         <v>18500</v>
@@ -26995,10 +26995,10 @@
         <v>66</v>
       </c>
       <c r="N587" t="n">
-        <v>4388.3371764706</v>
+        <v>4337.31</v>
       </c>
       <c r="O587" t="n">
-        <v>289630.2536470596</v>
+        <v>286262.46</v>
       </c>
       <c r="P587" t="n">
         <v>12900</v>
@@ -27319,10 +27319,10 @@
         <v>162</v>
       </c>
       <c r="N594" t="n">
-        <v>4360.6660810811</v>
+        <v>4190.77</v>
       </c>
       <c r="O594" t="n">
-        <v>706427.9051351382</v>
+        <v>678904.7400000001</v>
       </c>
       <c r="P594" t="n">
         <v>5900</v>
@@ -27896,10 +27896,10 @@
         <v>35</v>
       </c>
       <c r="N606" t="n">
-        <v>6053.1143</v>
+        <v>5876.81</v>
       </c>
       <c r="O606" t="n">
-        <v>211859.0005</v>
+        <v>205688.35</v>
       </c>
       <c r="P606" t="n">
         <v>22900</v>
@@ -28179,10 +28179,10 @@
         <v>9</v>
       </c>
       <c r="N612" t="n">
-        <v>7984.35</v>
+        <v>7258.5</v>
       </c>
       <c r="O612" t="n">
-        <v>71859.15000000001</v>
+        <v>65326.5</v>
       </c>
       <c r="P612" t="n">
         <v>17500</v>
@@ -28271,10 +28271,10 @@
         <v>18</v>
       </c>
       <c r="N614" t="n">
-        <v>10018.344827586</v>
+        <v>9372</v>
       </c>
       <c r="O614" t="n">
-        <v>180330.206896548</v>
+        <v>168696</v>
       </c>
       <c r="P614" t="n">
         <v>17900</v>
@@ -29409,10 +29409,10 @@
         <v>1</v>
       </c>
       <c r="N638" t="n">
-        <v>17438.2184</v>
+        <v>16146.4984</v>
       </c>
       <c r="O638" t="n">
-        <v>17438.2184</v>
+        <v>16146.4984</v>
       </c>
       <c r="P638" t="n">
         <v>26900</v>
@@ -30988,10 +30988,10 @@
         <v>358</v>
       </c>
       <c r="N673" t="n">
-        <v>23008.657146402</v>
+        <v>22951.705012407</v>
       </c>
       <c r="O673" t="n">
-        <v>8237099.258411917</v>
+        <v>8216710.394441706</v>
       </c>
       <c r="P673" t="n">
         <v>37900</v>
@@ -31821,10 +31821,10 @@
         <v>37</v>
       </c>
       <c r="N691" t="n">
-        <v>449.18534246575</v>
+        <v>415.07</v>
       </c>
       <c r="O691" t="n">
-        <v>16619.85767123275</v>
+        <v>15357.59</v>
       </c>
       <c r="P691" t="n">
         <v>2900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>238</v>
       </c>
       <c r="N6" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O6" t="n">
-        <v>432207.1162348856</v>
+        <v>431090.3043177948</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -2852,10 +2852,10 @@
         <v>128</v>
       </c>
       <c r="N60" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O60" t="n">
-        <v>495657.4050258176</v>
+        <v>494805.76</v>
       </c>
       <c r="P60" t="n">
         <v>5500</v>
@@ -2898,10 +2898,10 @@
         <v>48</v>
       </c>
       <c r="N61" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O61" t="n">
-        <v>124318.0535483856</v>
+        <v>123488.16</v>
       </c>
       <c r="P61" t="n">
         <v>4700</v>
@@ -2944,10 +2944,10 @@
         <v>73</v>
       </c>
       <c r="N62" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O62" t="n">
-        <v>189613.4175796163</v>
+        <v>187621.68</v>
       </c>
       <c r="P62" t="n">
         <v>4700</v>
@@ -3066,10 +3066,10 @@
         <v>42</v>
       </c>
       <c r="N65" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O65" t="n">
-        <v>109103.4472922268</v>
+        <v>107660.28</v>
       </c>
       <c r="P65" t="n">
         <v>4700</v>
@@ -3328,10 +3328,10 @@
         <v>135</v>
       </c>
       <c r="N71" t="n">
-        <v>3489.6196317829</v>
+        <v>3456.13</v>
       </c>
       <c r="O71" t="n">
-        <v>471098.6502906915</v>
+        <v>466577.55</v>
       </c>
       <c r="P71" t="n">
         <v>5700</v>
@@ -4441,10 +4441,10 @@
         <v>816</v>
       </c>
       <c r="N96" t="n">
-        <v>2588.3559055118</v>
+        <v>2582.2560787402</v>
       </c>
       <c r="O96" t="n">
-        <v>2112098.418897629</v>
+        <v>2107120.960252003</v>
       </c>
       <c r="P96" t="n">
         <v>4500</v>
@@ -5223,10 +5223,10 @@
         <v>298</v>
       </c>
       <c r="N113" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O113" t="n">
-        <v>2246510.96710124</v>
+        <v>2237202.22</v>
       </c>
       <c r="P113" t="n">
         <v>13500</v>
@@ -5272,10 +5272,10 @@
         <v>55</v>
       </c>
       <c r="N114" t="n">
-        <v>8907.908396946599</v>
+        <v>8796</v>
       </c>
       <c r="O114" t="n">
-        <v>489934.961832063</v>
+        <v>483780</v>
       </c>
       <c r="P114" t="n">
         <v>14900</v>
@@ -5451,10 +5451,10 @@
         <v>593</v>
       </c>
       <c r="N118" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O118" t="n">
-        <v>2254426.932166427</v>
+        <v>2250856.034181184</v>
       </c>
       <c r="P118" t="n">
         <v>6200</v>
@@ -5497,10 +5497,10 @@
         <v>266</v>
       </c>
       <c r="N119" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O119" t="n">
-        <v>982948.9390119181</v>
+        <v>979944</v>
       </c>
       <c r="P119" t="n">
         <v>6200</v>
@@ -5771,10 +5771,10 @@
         <v>20</v>
       </c>
       <c r="N125" t="n">
-        <v>1213.150338295</v>
+        <v>1203.38</v>
       </c>
       <c r="O125" t="n">
-        <v>24263.0067659</v>
+        <v>24067.6</v>
       </c>
       <c r="P125" t="n">
         <v>1900</v>
@@ -5904,10 +5904,10 @@
         <v>326</v>
       </c>
       <c r="N128" t="n">
-        <v>2286.8353823774</v>
+        <v>2267.048162926</v>
       </c>
       <c r="O128" t="n">
-        <v>745508.3346550324</v>
+        <v>739057.701113876</v>
       </c>
       <c r="P128" t="n">
         <v>3900</v>
@@ -6088,10 +6088,10 @@
         <v>281</v>
       </c>
       <c r="N132" t="n">
-        <v>8687.96003996</v>
+        <v>8662</v>
       </c>
       <c r="O132" t="n">
-        <v>2441316.77122876</v>
+        <v>2434022</v>
       </c>
       <c r="P132" t="n">
         <v>14200</v>
@@ -6452,10 +6452,10 @@
         <v>418</v>
       </c>
       <c r="N140" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O140" t="n">
-        <v>3431717.013698633</v>
+        <v>3408372</v>
       </c>
       <c r="P140" t="n">
         <v>13500</v>
@@ -7395,10 +7395,10 @@
         <v>883</v>
       </c>
       <c r="N161" t="n">
-        <v>6493.1840890688</v>
+        <v>6441.03</v>
       </c>
       <c r="O161" t="n">
-        <v>5733481.55064775</v>
+        <v>5687429.49</v>
       </c>
       <c r="P161" t="n">
         <v>10500</v>
@@ -7569,10 +7569,10 @@
         <v>759</v>
       </c>
       <c r="N165" t="n">
-        <v>3660.708</v>
+        <v>3655.96</v>
       </c>
       <c r="O165" t="n">
-        <v>2778477.372</v>
+        <v>2774873.64</v>
       </c>
       <c r="P165" t="n">
         <v>5500</v>
@@ -7931,10 +7931,10 @@
         <v>450</v>
       </c>
       <c r="N173" t="n">
-        <v>1535.9702761427</v>
+        <v>1532.6290291403</v>
       </c>
       <c r="O173" t="n">
-        <v>691186.624264215</v>
+        <v>689683.0631131349</v>
       </c>
       <c r="P173" t="n">
         <v>1200</v>
@@ -8856,10 +8856,10 @@
         <v>33</v>
       </c>
       <c r="N193" t="n">
-        <v>9795.0468</v>
+        <v>9678.9</v>
       </c>
       <c r="O193" t="n">
-        <v>323236.5444</v>
+        <v>319403.7</v>
       </c>
       <c r="P193" t="n">
         <v>15500</v>
@@ -9804,10 +9804,10 @@
         <v>609</v>
       </c>
       <c r="N214" t="n">
-        <v>1303.6380504587</v>
+        <v>1301.3994036697</v>
       </c>
       <c r="O214" t="n">
-        <v>793915.5727293483</v>
+        <v>792552.2368348473</v>
       </c>
       <c r="P214" t="n">
         <v>2000</v>
@@ -10802,10 +10802,10 @@
         <v>2</v>
       </c>
       <c r="N236" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="O236" t="n">
-        <v>9101.831775701001</v>
+        <v>8976</v>
       </c>
       <c r="P236" t="n">
         <v>6200</v>
@@ -10843,10 +10843,10 @@
         <v>94</v>
       </c>
       <c r="N237" t="n">
-        <v>2621.3808139535</v>
+        <v>2610</v>
       </c>
       <c r="O237" t="n">
-        <v>246409.796511629</v>
+        <v>245340</v>
       </c>
       <c r="P237" t="n">
         <v>3200</v>
@@ -10925,10 +10925,10 @@
         <v>263</v>
       </c>
       <c r="N239" t="n">
-        <v>1979.2819843342</v>
+        <v>1969</v>
       </c>
       <c r="O239" t="n">
-        <v>520551.1618798946</v>
+        <v>517847</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
@@ -10966,10 +10966,10 @@
         <v>34</v>
       </c>
       <c r="N240" t="n">
-        <v>2040.34375</v>
+        <v>1958.73</v>
       </c>
       <c r="O240" t="n">
-        <v>69371.6875</v>
+        <v>66596.82000000001</v>
       </c>
       <c r="P240" t="n">
         <v>3400</v>
@@ -11007,10 +11007,10 @@
         <v>148</v>
       </c>
       <c r="N241" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O241" t="n">
-        <v>1305204.584351694</v>
+        <v>1301583.04</v>
       </c>
       <c r="P241" t="n">
         <v>14500</v>
@@ -11978,10 +11978,10 @@
         <v>32</v>
       </c>
       <c r="N263" t="n">
-        <v>11652.839895288</v>
+        <v>11562.038534031</v>
       </c>
       <c r="O263" t="n">
-        <v>372890.876649216</v>
+        <v>369985.233088992</v>
       </c>
       <c r="P263" t="n">
         <v>18500</v>
@@ -12157,10 +12157,10 @@
         <v>26</v>
       </c>
       <c r="N267" t="n">
-        <v>22817.681329923</v>
+        <v>22730.48</v>
       </c>
       <c r="O267" t="n">
-        <v>593259.714577998</v>
+        <v>590992.48</v>
       </c>
       <c r="P267" t="n">
         <v>36900</v>
@@ -14000,10 +14000,10 @@
         <v>187</v>
       </c>
       <c r="N307" t="n">
-        <v>5220.5451448041</v>
+        <v>5194</v>
       </c>
       <c r="O307" t="n">
-        <v>976241.9420783668</v>
+        <v>971278</v>
       </c>
       <c r="P307" t="n">
         <v>9000</v>
@@ -15159,10 +15159,10 @@
         <v>74</v>
       </c>
       <c r="N332" t="n">
-        <v>11682.094594595</v>
+        <v>11450</v>
       </c>
       <c r="O332" t="n">
-        <v>864475.00000003</v>
+        <v>847300</v>
       </c>
       <c r="P332" t="n">
         <v>18300</v>
@@ -15251,10 +15251,10 @@
         <v>97</v>
       </c>
       <c r="N334" t="n">
-        <v>6365.625</v>
+        <v>6300</v>
       </c>
       <c r="O334" t="n">
-        <v>617465.625</v>
+        <v>611100</v>
       </c>
       <c r="P334" t="n">
         <v>10200</v>
@@ -15343,10 +15343,10 @@
         <v>56</v>
       </c>
       <c r="N336" t="n">
-        <v>7371.3029315961</v>
+        <v>7230</v>
       </c>
       <c r="O336" t="n">
-        <v>412792.9641693816</v>
+        <v>404880</v>
       </c>
       <c r="P336" t="n">
         <v>11600</v>
@@ -15389,10 +15389,10 @@
         <v>66</v>
       </c>
       <c r="N337" t="n">
-        <v>5291.8727915194</v>
+        <v>5200</v>
       </c>
       <c r="O337" t="n">
-        <v>349263.6042402804</v>
+        <v>343200</v>
       </c>
       <c r="P337" t="n">
         <v>8500</v>
@@ -15435,10 +15435,10 @@
         <v>62</v>
       </c>
       <c r="N338" t="n">
-        <v>1420.3389830508</v>
+        <v>1400</v>
       </c>
       <c r="O338" t="n">
-        <v>88061.01694914959</v>
+        <v>86800</v>
       </c>
       <c r="P338" t="n">
         <v>2300</v>
@@ -15481,10 +15481,10 @@
         <v>48</v>
       </c>
       <c r="N339" t="n">
-        <v>6085.1063829787</v>
+        <v>6000</v>
       </c>
       <c r="O339" t="n">
-        <v>292085.1063829776</v>
+        <v>288000</v>
       </c>
       <c r="P339" t="n">
         <v>10000</v>
@@ -15573,10 +15573,10 @@
         <v>131</v>
       </c>
       <c r="N341" t="n">
-        <v>1243.273381295</v>
+        <v>1230</v>
       </c>
       <c r="O341" t="n">
-        <v>162868.812949645</v>
+        <v>161130</v>
       </c>
       <c r="P341" t="n">
         <v>2000</v>
@@ -15711,10 +15711,10 @@
         <v>96</v>
       </c>
       <c r="N344" t="n">
-        <v>1441.9626168224</v>
+        <v>1390</v>
       </c>
       <c r="O344" t="n">
-        <v>138428.4112149504</v>
+        <v>133440</v>
       </c>
       <c r="P344" t="n">
         <v>2300</v>
@@ -15757,10 +15757,10 @@
         <v>67</v>
       </c>
       <c r="N345" t="n">
-        <v>1944.3046357616</v>
+        <v>1870</v>
       </c>
       <c r="O345" t="n">
-        <v>130268.4105960272</v>
+        <v>125290</v>
       </c>
       <c r="P345" t="n">
         <v>3000</v>
@@ -15803,10 +15803,10 @@
         <v>48</v>
       </c>
       <c r="N346" t="n">
-        <v>2110.9815037594</v>
+        <v>2019.86</v>
       </c>
       <c r="O346" t="n">
-        <v>101327.1121804512</v>
+        <v>96953.28</v>
       </c>
       <c r="P346" t="n">
         <v>3300</v>
@@ -15849,10 +15849,10 @@
         <v>90</v>
       </c>
       <c r="N347" t="n">
-        <v>539.28902627512</v>
+        <v>520</v>
       </c>
       <c r="O347" t="n">
-        <v>48536.01236476081</v>
+        <v>46800</v>
       </c>
       <c r="P347" t="n">
         <v>850</v>
@@ -15895,10 +15895,10 @@
         <v>17</v>
       </c>
       <c r="N348" t="n">
-        <v>2318.1974248927</v>
+        <v>2260</v>
       </c>
       <c r="O348" t="n">
-        <v>39409.3562231759</v>
+        <v>38420</v>
       </c>
       <c r="P348" t="n">
         <v>3800</v>
@@ -15990,10 +15990,10 @@
         <v>86</v>
       </c>
       <c r="N350" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="O350" t="n">
-        <v>161032.4705882358</v>
+        <v>158240</v>
       </c>
       <c r="P350" t="n">
         <v>3000</v>
@@ -16082,10 +16082,10 @@
         <v>79</v>
       </c>
       <c r="N352" t="n">
-        <v>2878.4650112867</v>
+        <v>2840</v>
       </c>
       <c r="O352" t="n">
-        <v>227398.7358916493</v>
+        <v>224360</v>
       </c>
       <c r="P352" t="n">
         <v>4600</v>
@@ -16272,10 +16272,10 @@
         <v>72</v>
       </c>
       <c r="N356" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O356" t="n">
-        <v>998207.068965552</v>
+        <v>985464</v>
       </c>
       <c r="P356" t="n">
         <v>21900</v>
@@ -16824,10 +16824,10 @@
         <v>23</v>
       </c>
       <c r="N368" t="n">
-        <v>6112.6956521739</v>
+        <v>5858</v>
       </c>
       <c r="O368" t="n">
-        <v>140591.9999999997</v>
+        <v>134734</v>
       </c>
       <c r="P368" t="n">
         <v>9500</v>
@@ -17472,10 +17472,10 @@
         <v>141</v>
       </c>
       <c r="N382" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O382" t="n">
-        <v>1275410.844339626</v>
+        <v>1269423</v>
       </c>
       <c r="P382" t="n">
         <v>14900</v>
@@ -18295,10 +18295,10 @@
         <v>17</v>
       </c>
       <c r="N400" t="n">
-        <v>10095.669565217</v>
+        <v>9839</v>
       </c>
       <c r="O400" t="n">
-        <v>171626.382608689</v>
+        <v>167263</v>
       </c>
       <c r="P400" t="n">
         <v>16900</v>
@@ -20547,10 +20547,10 @@
         <v>192</v>
       </c>
       <c r="N449" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O449" t="n">
-        <v>344968.8928752192</v>
+        <v>340049.526509952</v>
       </c>
       <c r="P449" t="n">
         <v>2500</v>
@@ -20593,10 +20593,10 @@
         <v>264</v>
       </c>
       <c r="N450" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O450" t="n">
-        <v>553223.9552331624</v>
+        <v>548957.4348186456</v>
       </c>
       <c r="P450" t="n">
         <v>2900</v>
@@ -20639,10 +20639,10 @@
         <v>264</v>
       </c>
       <c r="N451" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O451" t="n">
-        <v>482715.8804470464</v>
+        <v>475995.9561176424</v>
       </c>
       <c r="P451" t="n">
         <v>2500</v>
@@ -20731,10 +20731,10 @@
         <v>192</v>
       </c>
       <c r="N453" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O453" t="n">
-        <v>410396.5509293184</v>
+        <v>407455.5105202944</v>
       </c>
       <c r="P453" t="n">
         <v>2900</v>
@@ -20869,10 +20869,10 @@
         <v>216</v>
       </c>
       <c r="N456" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O456" t="n">
-        <v>707616.1894904713</v>
+        <v>696506.6730704472</v>
       </c>
       <c r="P456" t="n">
         <v>4500</v>
@@ -21230,10 +21230,10 @@
         <v>8</v>
       </c>
       <c r="N464" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O464" t="n">
-        <v>43316.613</v>
+        <v>42781.84</v>
       </c>
       <c r="P464" t="n">
         <v>9500</v>
@@ -21598,10 +21598,10 @@
         <v>47</v>
       </c>
       <c r="N472" t="n">
-        <v>3051.52</v>
+        <v>2980</v>
       </c>
       <c r="O472" t="n">
-        <v>143421.44</v>
+        <v>140060</v>
       </c>
       <c r="P472" t="n">
         <v>4800</v>
@@ -22700,10 +22700,10 @@
         <v>450</v>
       </c>
       <c r="N496" t="n">
-        <v>577.72789151821</v>
+        <v>574.67194894975</v>
       </c>
       <c r="O496" t="n">
-        <v>259977.5511831945</v>
+        <v>258602.3770273875</v>
       </c>
       <c r="P496" t="n">
         <v>800</v>
@@ -23078,10 +23078,10 @@
         <v>3</v>
       </c>
       <c r="N504" t="n">
-        <v>2483.1635416667</v>
+        <v>2270.3210416667</v>
       </c>
       <c r="O504" t="n">
-        <v>7449.4906250001</v>
+        <v>6810.963125000099</v>
       </c>
       <c r="P504" t="n">
         <v>3900</v>
@@ -23450,10 +23450,10 @@
         <v>118</v>
       </c>
       <c r="N512" t="n">
-        <v>1815.5064655172</v>
+        <v>1684.79</v>
       </c>
       <c r="O512" t="n">
-        <v>214229.7629310296</v>
+        <v>198805.22</v>
       </c>
       <c r="P512" t="n">
         <v>2900</v>
@@ -23494,10 +23494,10 @@
         <v>15</v>
       </c>
       <c r="N513" t="n">
-        <v>6349.5722627737</v>
+        <v>6213.51</v>
       </c>
       <c r="O513" t="n">
-        <v>95243.5839416055</v>
+        <v>93202.65000000001</v>
       </c>
       <c r="P513" t="n">
         <v>10300</v>
@@ -24419,10 +24419,10 @@
         <v>236</v>
       </c>
       <c r="N533" t="n">
-        <v>2047.4600343643</v>
+        <v>2030.02</v>
       </c>
       <c r="O533" t="n">
-        <v>483200.5681099748</v>
+        <v>479084.72</v>
       </c>
       <c r="P533" t="n">
         <v>3600</v>
@@ -24692,10 +24692,10 @@
         <v>20378</v>
       </c>
       <c r="N539" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O539" t="n">
-        <v>14349738.36108323</v>
+        <v>14341943.77608344</v>
       </c>
       <c r="P539" t="n">
         <v>900</v>
@@ -24741,10 +24741,10 @@
         <v>55</v>
       </c>
       <c r="N540" t="n">
-        <v>3216.9665454545</v>
+        <v>3182.2510909091</v>
       </c>
       <c r="O540" t="n">
-        <v>176933.1599999975</v>
+        <v>175023.8100000005</v>
       </c>
       <c r="P540" t="n">
         <v>6900</v>
@@ -25106,10 +25106,10 @@
         <v>30</v>
       </c>
       <c r="N548" t="n">
-        <v>3674.9932848233</v>
+        <v>3629.7161122661</v>
       </c>
       <c r="O548" t="n">
-        <v>110249.798544699</v>
+        <v>108891.483367983</v>
       </c>
       <c r="P548" t="n">
         <v>4900</v>
@@ -29169,10 +29169,10 @@
         <v>682</v>
       </c>
       <c r="N633" t="n">
-        <v>713.93197013211</v>
+        <v>711.48</v>
       </c>
       <c r="O633" t="n">
-        <v>486901.603630099</v>
+        <v>485229.36</v>
       </c>
       <c r="P633" t="n">
         <v>2500</v>
@@ -30029,10 +30029,10 @@
         <v>14</v>
       </c>
       <c r="N651" t="n">
-        <v>2851.4129341317</v>
+        <v>2752.52</v>
       </c>
       <c r="O651" t="n">
-        <v>39919.7810778438</v>
+        <v>38535.28</v>
       </c>
       <c r="P651" t="n">
         <v>4500</v>
@@ -30377,10 +30377,10 @@
         <v>90</v>
       </c>
       <c r="N659" t="n">
-        <v>2496.9418200728</v>
+        <v>2489.1752678107</v>
       </c>
       <c r="O659" t="n">
-        <v>224724.763806552</v>
+        <v>224025.774102963</v>
       </c>
       <c r="P659" t="n">
         <v>3000</v>
@@ -30544,10 +30544,10 @@
         <v>861</v>
       </c>
       <c r="N663" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O663" t="n">
-        <v>2748893.298916325</v>
+        <v>2739615.9</v>
       </c>
       <c r="P663" t="n">
         <v>5100</v>
@@ -30629,10 +30629,10 @@
         <v>450</v>
       </c>
       <c r="N665" t="n">
-        <v>1803.5408695029</v>
+        <v>1794.2879773671</v>
       </c>
       <c r="O665" t="n">
-        <v>811593.391276305</v>
+        <v>807429.589815195</v>
       </c>
       <c r="P665" t="n">
         <v>1600</v>
@@ -30673,10 +30673,10 @@
         <v>44</v>
       </c>
       <c r="N666" t="n">
-        <v>3081.4280769231</v>
+        <v>2830.2251183432</v>
       </c>
       <c r="O666" t="n">
-        <v>135582.8353846164</v>
+        <v>124529.9052071008</v>
       </c>
       <c r="P666" t="n">
         <v>2400</v>
@@ -30761,10 +30761,10 @@
         <v>190</v>
       </c>
       <c r="N668" t="n">
-        <v>2540.4017582418</v>
+        <v>2523.3377514793</v>
       </c>
       <c r="O668" t="n">
-        <v>482676.334065942</v>
+        <v>479434.172781067</v>
       </c>
       <c r="P668" t="n">
         <v>2800</v>
@@ -31080,10 +31080,10 @@
         <v>172</v>
       </c>
       <c r="N675" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O675" t="n">
-        <v>121624.9547289162</v>
+        <v>121350.8180722887</v>
       </c>
       <c r="P675" t="n">
         <v>1500</v>
@@ -32342,10 +32342,10 @@
         <v>686</v>
       </c>
       <c r="N702" t="n">
-        <v>229.9076771366</v>
+        <v>227.41596785975</v>
       </c>
       <c r="O702" t="n">
-        <v>157716.6665157076</v>
+        <v>156007.3539517885</v>
       </c>
       <c r="P702" t="n">
         <v>1200</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -630,22 +630,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M6" t="n">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3037996546</v>
+        <v>1811.3039621792</v>
       </c>
       <c r="O6" t="n">
-        <v>431090.3043177948</v>
+        <v>322412.1052678976</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
       </c>
       <c r="Q6" t="n">
-        <v>618800</v>
+        <v>462800</v>
       </c>
     </row>
     <row r="7">
@@ -1234,10 +1234,10 @@
         <v>210</v>
       </c>
       <c r="N21" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O21" t="n">
-        <v>824635.797849465</v>
+        <v>824635.7972321911</v>
       </c>
       <c r="P21" t="n">
         <v>4800</v>
@@ -1354,10 +1354,10 @@
         <v>92</v>
       </c>
       <c r="N24" t="n">
-        <v>2413.0011764706</v>
+        <v>2413.0010330579</v>
       </c>
       <c r="O24" t="n">
-        <v>221996.1082352952</v>
+        <v>221996.0950413268</v>
       </c>
       <c r="P24" t="n">
         <v>4700</v>
@@ -1432,10 +1432,10 @@
         <v>48</v>
       </c>
       <c r="N26" t="n">
-        <v>12793.680086207</v>
+        <v>12793.68008658</v>
       </c>
       <c r="O26" t="n">
-        <v>614096.6441379359</v>
+        <v>614096.6441558399</v>
       </c>
       <c r="P26" t="n">
         <v>24000</v>
@@ -1471,10 +1471,10 @@
         <v>120</v>
       </c>
       <c r="N27" t="n">
-        <v>3716.330188383</v>
+        <v>3716.3301889764</v>
       </c>
       <c r="O27" t="n">
-        <v>445959.62260596</v>
+        <v>445959.6226771681</v>
       </c>
       <c r="P27" t="n">
         <v>9500</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N35" t="n">
         <v>10580</v>
       </c>
       <c r="O35" t="n">
-        <v>105800</v>
+        <v>84640</v>
       </c>
       <c r="P35" t="n">
         <v>17900</v>
       </c>
       <c r="Q35" t="n">
-        <v>179000</v>
+        <v>143200</v>
       </c>
     </row>
     <row r="36">
@@ -1836,10 +1836,10 @@
         <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>10994.352244898</v>
+        <v>10994.353043478</v>
       </c>
       <c r="O36" t="n">
-        <v>65966.113469388</v>
+        <v>65966.11826086801</v>
       </c>
       <c r="P36" t="n">
         <v>16900</v>
@@ -1872,22 +1872,22 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M37" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>17085.64</v>
+        <v>17085.59</v>
       </c>
       <c r="O37" t="n">
-        <v>375884.08</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>29200</v>
       </c>
       <c r="Q37" t="n">
-        <v>642400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1953,22 +1953,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M39" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>36762.36</v>
       </c>
       <c r="O39" t="n">
-        <v>772009.5600000001</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>57100</v>
       </c>
       <c r="Q39" t="n">
-        <v>1199100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1995,22 +1995,22 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N40" t="n">
-        <v>15711.966215139</v>
+        <v>15711.9662</v>
       </c>
       <c r="O40" t="n">
-        <v>377087.189163336</v>
+        <v>282815.3916</v>
       </c>
       <c r="P40" t="n">
         <v>28500</v>
       </c>
       <c r="Q40" t="n">
-        <v>684000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="41">
@@ -2251,10 +2251,10 @@
         <v>8</v>
       </c>
       <c r="N46" t="n">
-        <v>56906.800422535</v>
+        <v>56906.800571429</v>
       </c>
       <c r="O46" t="n">
-        <v>455254.40338028</v>
+        <v>455254.404571432</v>
       </c>
       <c r="P46" t="n">
         <v>95900</v>
@@ -2292,22 +2292,22 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M47" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N47" t="n">
-        <v>141416.88447284</v>
+        <v>141416.88453074</v>
       </c>
       <c r="O47" t="n">
-        <v>7495094.87706052</v>
+        <v>6505176.68841404</v>
       </c>
       <c r="P47" t="n">
         <v>251900</v>
       </c>
       <c r="Q47" t="n">
-        <v>13350700</v>
+        <v>11587400</v>
       </c>
     </row>
     <row r="48">
@@ -2381,22 +2381,22 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N49" t="n">
-        <v>344599.17881356</v>
+        <v>344599.1787931</v>
       </c>
       <c r="O49" t="n">
-        <v>4824388.50338984</v>
+        <v>4479789.3243103</v>
       </c>
       <c r="P49" t="n">
         <v>532900</v>
       </c>
       <c r="Q49" t="n">
-        <v>7460600</v>
+        <v>6927700</v>
       </c>
     </row>
     <row r="50">
@@ -2774,10 +2774,10 @@
         <v>14</v>
       </c>
       <c r="N58" t="n">
-        <v>28.165681818182</v>
+        <v>28.165642201835</v>
       </c>
       <c r="O58" t="n">
-        <v>394.319545454548</v>
+        <v>394.31899082569</v>
       </c>
       <c r="P58" t="n">
         <v>6800</v>
@@ -3156,10 +3156,10 @@
         <v>41</v>
       </c>
       <c r="N67" t="n">
-        <v>732.63410958904</v>
+        <v>732.63413793103</v>
       </c>
       <c r="O67" t="n">
-        <v>30037.99849315064</v>
+        <v>30037.99965517223</v>
       </c>
       <c r="P67" t="n">
         <v>6200</v>
@@ -3246,10 +3246,10 @@
         <v>228</v>
       </c>
       <c r="N69" t="n">
-        <v>4937.3101595359</v>
+        <v>4937.3101601164</v>
       </c>
       <c r="O69" t="n">
-        <v>1125706.716374185</v>
+        <v>1125706.716506539</v>
       </c>
       <c r="P69" t="n">
         <v>7500</v>
@@ -3508,10 +3508,10 @@
         <v>1727</v>
       </c>
       <c r="N75" t="n">
-        <v>1098.0527732407</v>
+        <v>1098.0529624405</v>
       </c>
       <c r="O75" t="n">
-        <v>1896337.139386689</v>
+        <v>1896337.466134744</v>
       </c>
       <c r="P75" t="n">
         <v>1500</v>
@@ -4441,10 +4441,10 @@
         <v>816</v>
       </c>
       <c r="N96" t="n">
-        <v>2582.2560787402</v>
+        <v>2582.2560663507</v>
       </c>
       <c r="O96" t="n">
-        <v>2107120.960252003</v>
+        <v>2107120.950142171</v>
       </c>
       <c r="P96" t="n">
         <v>4500</v>
@@ -4625,10 +4625,10 @@
         <v>60</v>
       </c>
       <c r="N100" t="n">
-        <v>2033.5763768116</v>
+        <v>2033.5756109726</v>
       </c>
       <c r="O100" t="n">
-        <v>122014.582608696</v>
+        <v>122014.536658356</v>
       </c>
       <c r="P100" t="n">
         <v>4100</v>
@@ -5676,10 +5676,10 @@
         <v>318</v>
       </c>
       <c r="N123" t="n">
-        <v>4890.930045977</v>
+        <v>4890.9300460299</v>
       </c>
       <c r="O123" t="n">
-        <v>1555315.754620686</v>
+        <v>1555315.754637508</v>
       </c>
       <c r="P123" t="n">
         <v>8200</v>
@@ -5904,10 +5904,10 @@
         <v>326</v>
       </c>
       <c r="N128" t="n">
-        <v>2267.048162926</v>
+        <v>2267.0481598668</v>
       </c>
       <c r="O128" t="n">
-        <v>739057.701113876</v>
+        <v>739057.7001165767</v>
       </c>
       <c r="P128" t="n">
         <v>3900</v>
@@ -6169,22 +6169,22 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M134" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N134" t="n">
         <v>10716.34</v>
       </c>
       <c r="O134" t="n">
-        <v>246475.82</v>
+        <v>117879.74</v>
       </c>
       <c r="P134" t="n">
         <v>39000</v>
       </c>
       <c r="Q134" t="n">
-        <v>897000</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="135">
@@ -6224,10 +6224,10 @@
         <v>288</v>
       </c>
       <c r="N135" t="n">
-        <v>3594.2542480527</v>
+        <v>3594.2542307692</v>
       </c>
       <c r="O135" t="n">
-        <v>1035145.223439178</v>
+        <v>1035145.21846153</v>
       </c>
       <c r="P135" t="n">
         <v>6500</v>
@@ -6314,10 +6314,10 @@
         <v>108</v>
       </c>
       <c r="N137" t="n">
-        <v>3240.8500291545</v>
+        <v>3240.8500293255</v>
       </c>
       <c r="O137" t="n">
-        <v>350011.803148686</v>
+        <v>350011.803167154</v>
       </c>
       <c r="P137" t="n">
         <v>5200</v>
@@ -7223,10 +7223,10 @@
         <v>220</v>
       </c>
       <c r="N157" t="n">
-        <v>3041.6600123457</v>
+        <v>3041.6600124378</v>
       </c>
       <c r="O157" t="n">
-        <v>669165.202716054</v>
+        <v>669165.202736316</v>
       </c>
       <c r="P157" t="n">
         <v>5500</v>
@@ -7351,10 +7351,10 @@
         <v>1945</v>
       </c>
       <c r="N160" t="n">
-        <v>4372.2107862617</v>
+        <v>4372.2107863175</v>
       </c>
       <c r="O160" t="n">
-        <v>8503949.979279008</v>
+        <v>8503949.979387537</v>
       </c>
       <c r="P160" t="n">
         <v>7500</v>
@@ -7441,10 +7441,10 @@
         <v>558</v>
       </c>
       <c r="N162" t="n">
-        <v>1592.5677691978</v>
+        <v>1592.5677332171</v>
       </c>
       <c r="O162" t="n">
-        <v>888652.8152123725</v>
+        <v>888652.7951351418</v>
       </c>
       <c r="P162" t="n">
         <v>3900</v>
@@ -7931,10 +7931,10 @@
         <v>450</v>
       </c>
       <c r="N173" t="n">
-        <v>1532.6290291403</v>
+        <v>1532.629028858</v>
       </c>
       <c r="O173" t="n">
-        <v>689683.0631131349</v>
+        <v>689683.0629861001</v>
       </c>
       <c r="P173" t="n">
         <v>1200</v>
@@ -8431,10 +8431,10 @@
         <v>71</v>
       </c>
       <c r="N184" t="n">
-        <v>2021.7211191336</v>
+        <v>2021.7211218335</v>
       </c>
       <c r="O184" t="n">
-        <v>143542.1994584856</v>
+        <v>143542.1996501785</v>
       </c>
       <c r="P184" t="n">
         <v>2400</v>
@@ -9232,10 +9232,10 @@
         <v>872</v>
       </c>
       <c r="N201" t="n">
-        <v>1630.9229788882</v>
+        <v>1630.9230192383</v>
       </c>
       <c r="O201" t="n">
-        <v>1422164.83759051</v>
+        <v>1422164.872775797</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9324,10 +9324,10 @@
         <v>416</v>
       </c>
       <c r="N203" t="n">
-        <v>1690.6043069815</v>
+        <v>1690.603799682</v>
       </c>
       <c r="O203" t="n">
-        <v>703291.391704304</v>
+        <v>703291.180667712</v>
       </c>
       <c r="P203" t="n">
         <v>2900</v>
@@ -9370,10 +9370,10 @@
         <v>2238</v>
       </c>
       <c r="N204" t="n">
-        <v>1550.1929105882</v>
+        <v>1550.19293615</v>
       </c>
       <c r="O204" t="n">
-        <v>3469331.733896391</v>
+        <v>3469331.7911037</v>
       </c>
       <c r="P204" t="n">
         <v>2500</v>
@@ -9416,10 +9416,10 @@
         <v>22</v>
       </c>
       <c r="N205" t="n">
-        <v>1579.3913493976</v>
+        <v>1579.3910696517</v>
       </c>
       <c r="O205" t="n">
-        <v>34746.6096867472</v>
+        <v>34746.6035323374</v>
       </c>
       <c r="P205" t="n">
         <v>2900</v>
@@ -9462,10 +9462,10 @@
         <v>454</v>
       </c>
       <c r="N206" t="n">
-        <v>2403.5099727039</v>
+        <v>2403.5100306848</v>
       </c>
       <c r="O206" t="n">
-        <v>1091193.527607571</v>
+        <v>1091193.553930899</v>
       </c>
       <c r="P206" t="n">
         <v>3500</v>
@@ -9508,10 +9508,10 @@
         <v>80</v>
       </c>
       <c r="N207" t="n">
-        <v>2521.5483026316</v>
+        <v>2521.5479047619</v>
       </c>
       <c r="O207" t="n">
-        <v>201723.864210528</v>
+        <v>201723.832380952</v>
       </c>
       <c r="P207" t="n">
         <v>3900</v>
@@ -11225,10 +11225,10 @@
         <v>159</v>
       </c>
       <c r="N246" t="n">
-        <v>2680.739700489</v>
+        <v>2680.7396999388</v>
       </c>
       <c r="O246" t="n">
-        <v>426237.612377751</v>
+        <v>426237.6122902692</v>
       </c>
       <c r="P246" t="n">
         <v>4900</v>
@@ -11271,10 +11271,10 @@
         <v>10</v>
       </c>
       <c r="N247" t="n">
-        <v>11431.604880952</v>
+        <v>11431.604819277</v>
       </c>
       <c r="O247" t="n">
-        <v>114316.04880952</v>
+        <v>114316.04819277</v>
       </c>
       <c r="P247" t="n">
         <v>48900</v>
@@ -11491,10 +11491,10 @@
         <v>12</v>
       </c>
       <c r="N252" t="n">
-        <v>3731.0243234323</v>
+        <v>3731.0243377483</v>
       </c>
       <c r="O252" t="n">
-        <v>44772.2918811876</v>
+        <v>44772.2920529796</v>
       </c>
       <c r="P252" t="n">
         <v>5200</v>
@@ -11632,10 +11632,10 @@
         <v>125</v>
       </c>
       <c r="N255" t="n">
-        <v>4285.1952263374</v>
+        <v>4285.1952479339</v>
       </c>
       <c r="O255" t="n">
-        <v>535649.4032921749</v>
+        <v>535649.4059917375</v>
       </c>
       <c r="P255" t="n">
         <v>6900</v>
@@ -12024,10 +12024,10 @@
         <v>22</v>
       </c>
       <c r="N264" t="n">
-        <v>13513.64294964</v>
+        <v>13513.642971014</v>
       </c>
       <c r="O264" t="n">
-        <v>297300.14489208</v>
+        <v>297300.145362308</v>
       </c>
       <c r="P264" t="n">
         <v>21900</v>
@@ -12249,10 +12249,10 @@
         <v>94</v>
       </c>
       <c r="N269" t="n">
-        <v>27123.765259259</v>
+        <v>27123.765250464</v>
       </c>
       <c r="O269" t="n">
-        <v>2549633.934370346</v>
+        <v>2549633.933543616</v>
       </c>
       <c r="P269" t="n">
         <v>44500</v>
@@ -12509,22 +12509,22 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M275" t="n">
-        <v>653</v>
+        <v>629</v>
       </c>
       <c r="N275" t="n">
-        <v>1560.9985110132</v>
+        <v>1560.9988178914</v>
       </c>
       <c r="O275" t="n">
-        <v>1019332.02769162</v>
+        <v>981868.2564536906</v>
       </c>
       <c r="P275" t="n">
         <v>2900</v>
       </c>
       <c r="Q275" t="n">
-        <v>1893700</v>
+        <v>1824100</v>
       </c>
     </row>
     <row r="276">
@@ -12653,10 +12653,10 @@
         <v>188</v>
       </c>
       <c r="N278" t="n">
-        <v>7969.9501643017</v>
+        <v>7969.950164794</v>
       </c>
       <c r="O278" t="n">
-        <v>1498350.63088872</v>
+        <v>1498350.630981272</v>
       </c>
       <c r="P278" t="n">
         <v>12900</v>
@@ -12838,10 +12838,10 @@
         <v>306</v>
       </c>
       <c r="N282" t="n">
-        <v>548.14728797763</v>
+        <v>548.14728291317</v>
       </c>
       <c r="O282" t="n">
-        <v>167733.0701211548</v>
+        <v>167733.06857143</v>
       </c>
       <c r="P282" t="n">
         <v>2000</v>
@@ -13494,10 +13494,10 @@
         <v>122</v>
       </c>
       <c r="N296" t="n">
-        <v>3113.8900239521</v>
+        <v>3113.8900249066</v>
       </c>
       <c r="O296" t="n">
-        <v>379894.5829221562</v>
+        <v>379894.5830386052</v>
       </c>
       <c r="P296" t="n">
         <v>5000</v>
@@ -13862,10 +13862,10 @@
         <v>81</v>
       </c>
       <c r="N304" t="n">
-        <v>5218.1704756757</v>
+        <v>5218.1704867257</v>
       </c>
       <c r="O304" t="n">
-        <v>422671.8085297317</v>
+        <v>422671.8094247817</v>
       </c>
       <c r="P304" t="n">
         <v>8500</v>
@@ -13908,10 +13908,10 @@
         <v>1</v>
       </c>
       <c r="N305" t="n">
-        <v>1595.0095090439</v>
+        <v>1595.0094973545</v>
       </c>
       <c r="O305" t="n">
-        <v>1595.0095090439</v>
+        <v>1595.0094973545</v>
       </c>
       <c r="P305" t="n">
         <v>2600</v>
@@ -13954,10 +13954,10 @@
         <v>123</v>
       </c>
       <c r="N306" t="n">
-        <v>3610.6500232019</v>
+        <v>3610.6500236967</v>
       </c>
       <c r="O306" t="n">
-        <v>444109.9528538337</v>
+        <v>444109.9529146941</v>
       </c>
       <c r="P306" t="n">
         <v>5800</v>
@@ -14417,10 +14417,10 @@
         <v>48</v>
       </c>
       <c r="N316" t="n">
-        <v>1664.3613046757</v>
+        <v>1664.3609992194</v>
       </c>
       <c r="O316" t="n">
-        <v>79889.3426244336</v>
+        <v>79889.3279625312</v>
       </c>
       <c r="P316" t="n">
         <v>2900</v>
@@ -14696,10 +14696,10 @@
         <v>824</v>
       </c>
       <c r="N322" t="n">
-        <v>1778.4725093418</v>
+        <v>1778.4725198441</v>
       </c>
       <c r="O322" t="n">
-        <v>1465461.347697643</v>
+        <v>1465461.356351538</v>
       </c>
       <c r="P322" t="n">
         <v>4900</v>
@@ -17196,10 +17196,10 @@
         <v>324</v>
       </c>
       <c r="N376" t="n">
-        <v>2328.1187536917</v>
+        <v>2328.1187525865</v>
       </c>
       <c r="O376" t="n">
-        <v>754310.4761961108</v>
+        <v>754310.4758380259</v>
       </c>
       <c r="P376" t="n">
         <v>4500</v>
@@ -17840,10 +17840,10 @@
         <v>165</v>
       </c>
       <c r="N390" t="n">
-        <v>4907.821904048</v>
+        <v>4907.8219155354</v>
       </c>
       <c r="O390" t="n">
-        <v>809790.61416792</v>
+        <v>809790.616063341</v>
       </c>
       <c r="P390" t="n">
         <v>8200</v>
@@ -18070,10 +18070,10 @@
         <v>289</v>
       </c>
       <c r="N395" t="n">
-        <v>3903.7358605664</v>
+        <v>3903.7358951965</v>
       </c>
       <c r="O395" t="n">
-        <v>1128179.66370369</v>
+        <v>1128179.673711789</v>
       </c>
       <c r="P395" t="n">
         <v>7500</v>
@@ -18341,10 +18341,10 @@
         <v>48</v>
       </c>
       <c r="N401" t="n">
-        <v>5869.1727610442</v>
+        <v>5869.1727464789</v>
       </c>
       <c r="O401" t="n">
-        <v>281720.2925301216</v>
+        <v>281720.2918309872</v>
       </c>
       <c r="P401" t="n">
         <v>9500</v>
@@ -20363,10 +20363,10 @@
         <v>1320</v>
       </c>
       <c r="N445" t="n">
-        <v>1516.0388166875</v>
+        <v>1516.0388137227</v>
       </c>
       <c r="O445" t="n">
-        <v>2001171.2380275</v>
+        <v>2001171.234113964</v>
       </c>
       <c r="P445" t="n">
         <v>2300</v>
@@ -20449,22 +20449,22 @@
         <v>0</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M447" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="N447" t="n">
-        <v>4248.6136842105</v>
+        <v>4248.6172239748</v>
       </c>
       <c r="O447" t="n">
-        <v>373878.004210524</v>
+        <v>33988.9377917984</v>
       </c>
       <c r="P447" t="n">
         <v>5900</v>
       </c>
       <c r="Q447" t="n">
-        <v>519200</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="448">
@@ -20501,10 +20501,10 @@
         <v>120</v>
       </c>
       <c r="N448" t="n">
-        <v>2458.5134637046</v>
+        <v>2458.5134514107</v>
       </c>
       <c r="O448" t="n">
-        <v>295021.615644552</v>
+        <v>295021.614169284</v>
       </c>
       <c r="P448" t="n">
         <v>3500</v>
@@ -20639,10 +20639,10 @@
         <v>264</v>
       </c>
       <c r="N451" t="n">
-        <v>1803.0149852941</v>
+        <v>1803.0149867608</v>
       </c>
       <c r="O451" t="n">
-        <v>475995.9561176424</v>
+        <v>475995.9565048512</v>
       </c>
       <c r="P451" t="n">
         <v>2500</v>
@@ -20777,10 +20777,10 @@
         <v>216</v>
       </c>
       <c r="N454" t="n">
-        <v>2108.7897270195</v>
+        <v>2108.7897651007</v>
       </c>
       <c r="O454" t="n">
-        <v>455498.581036212</v>
+        <v>455498.5892617512</v>
       </c>
       <c r="P454" t="n">
         <v>2900</v>
@@ -20817,22 +20817,22 @@
         <v>0</v>
       </c>
       <c r="L455" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M455" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="N455" t="n">
-        <v>2056.0839525344</v>
+        <v>2056.0838952972</v>
       </c>
       <c r="O455" t="n">
-        <v>493460.148608256</v>
+        <v>296076.0809227968</v>
       </c>
       <c r="P455" t="n">
         <v>2900</v>
       </c>
       <c r="Q455" t="n">
-        <v>696000</v>
+        <v>417600</v>
       </c>
     </row>
     <row r="456">
@@ -20869,10 +20869,10 @@
         <v>216</v>
       </c>
       <c r="N456" t="n">
-        <v>3224.5679308817</v>
+        <v>3224.5679626335</v>
       </c>
       <c r="O456" t="n">
-        <v>696506.6730704472</v>
+        <v>696506.6799288359</v>
       </c>
       <c r="P456" t="n">
         <v>4500</v>
@@ -20915,10 +20915,10 @@
         <v>360</v>
       </c>
       <c r="N457" t="n">
-        <v>1655.9314259144</v>
+        <v>1655.93135625</v>
       </c>
       <c r="O457" t="n">
-        <v>596135.313329184</v>
+        <v>596135.28825</v>
       </c>
       <c r="P457" t="n">
         <v>2500</v>
@@ -21145,10 +21145,10 @@
         <v>432</v>
       </c>
       <c r="N462" t="n">
-        <v>1592.2745718734</v>
+        <v>1592.2746762208</v>
       </c>
       <c r="O462" t="n">
-        <v>687862.6150493087</v>
+        <v>687862.6601273856</v>
       </c>
       <c r="P462" t="n">
         <v>2500</v>
@@ -21276,10 +21276,10 @@
         <v>132</v>
       </c>
       <c r="N465" t="n">
-        <v>2311.9273755656</v>
+        <v>2311.9269828927</v>
       </c>
       <c r="O465" t="n">
-        <v>305174.4135746592</v>
+        <v>305174.3617418364</v>
       </c>
       <c r="P465" t="n">
         <v>3500</v>
@@ -21322,10 +21322,10 @@
         <v>48</v>
       </c>
       <c r="N466" t="n">
-        <v>1906.1870703125</v>
+        <v>1906.1869325153</v>
       </c>
       <c r="O466" t="n">
-        <v>91496.979375</v>
+        <v>91496.9727607344</v>
       </c>
       <c r="P466" t="n">
         <v>2900</v>
@@ -21362,22 +21362,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M467" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="N467" t="n">
-        <v>3033.7322944551</v>
+        <v>3033.7319844358</v>
       </c>
       <c r="O467" t="n">
-        <v>655286.1756023016</v>
+        <v>364047.838132296</v>
       </c>
       <c r="P467" t="n">
         <v>4500</v>
       </c>
       <c r="Q467" t="n">
-        <v>972000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="468">
@@ -21414,10 +21414,10 @@
         <v>408</v>
       </c>
       <c r="N468" t="n">
-        <v>2060.1608716323</v>
+        <v>2060.160798722</v>
       </c>
       <c r="O468" t="n">
-        <v>840545.6356259783</v>
+        <v>840545.6058785759</v>
       </c>
       <c r="P468" t="n">
         <v>2900</v>
@@ -21460,10 +21460,10 @@
         <v>72</v>
       </c>
       <c r="N469" t="n">
-        <v>1668.6141040462</v>
+        <v>1668.6155910543</v>
       </c>
       <c r="O469" t="n">
-        <v>120140.2154913264</v>
+        <v>120140.3225559096</v>
       </c>
       <c r="P469" t="n">
         <v>2500</v>
@@ -21506,10 +21506,10 @@
         <v>72</v>
       </c>
       <c r="N470" t="n">
-        <v>2546.9853442623</v>
+        <v>2546.9852428811</v>
       </c>
       <c r="O470" t="n">
-        <v>183382.9447868856</v>
+        <v>183382.9374874392</v>
       </c>
       <c r="P470" t="n">
         <v>3900</v>
@@ -21552,10 +21552,10 @@
         <v>900</v>
       </c>
       <c r="N471" t="n">
-        <v>1259.274396777</v>
+        <v>1259.2744102228</v>
       </c>
       <c r="O471" t="n">
-        <v>1133346.9570993</v>
+        <v>1133346.96920052</v>
       </c>
       <c r="P471" t="n">
         <v>1900</v>
@@ -21639,10 +21639,10 @@
         <v>97</v>
       </c>
       <c r="N473" t="n">
-        <v>2842.2738221529</v>
+        <v>2842.2737931034</v>
       </c>
       <c r="O473" t="n">
-        <v>275700.5607488313</v>
+        <v>275700.5579310298</v>
       </c>
       <c r="P473" t="n">
         <v>4900</v>
@@ -21685,10 +21685,10 @@
         <v>72</v>
       </c>
       <c r="N474" t="n">
-        <v>2556.7443828715</v>
+        <v>2556.7444501279</v>
       </c>
       <c r="O474" t="n">
-        <v>184085.595566748</v>
+        <v>184085.6004092088</v>
       </c>
       <c r="P474" t="n">
         <v>3900</v>
@@ -21775,10 +21775,10 @@
         <v>660</v>
       </c>
       <c r="N476" t="n">
-        <v>692.1520380194499</v>
+        <v>692.15204525288</v>
       </c>
       <c r="O476" t="n">
-        <v>456820.3450928369</v>
+        <v>456820.3498669008</v>
       </c>
       <c r="P476" t="n">
         <v>1200</v>
@@ -22330,10 +22330,10 @@
         <v>46</v>
       </c>
       <c r="N488" t="n">
-        <v>3026.5146116505</v>
+        <v>3026.514679803</v>
       </c>
       <c r="O488" t="n">
-        <v>139219.672135923</v>
+        <v>139219.675270938</v>
       </c>
       <c r="P488" t="n">
         <v>7000</v>
@@ -23078,10 +23078,10 @@
         <v>3</v>
       </c>
       <c r="N504" t="n">
-        <v>2270.3210416667</v>
+        <v>2270.3210752688</v>
       </c>
       <c r="O504" t="n">
-        <v>6810.963125000099</v>
+        <v>6810.9632258064</v>
       </c>
       <c r="P504" t="n">
         <v>3900</v>
@@ -23264,10 +23264,10 @@
         <v>140</v>
       </c>
       <c r="N508" t="n">
-        <v>3907.5003187251</v>
+        <v>3907.5003212851</v>
       </c>
       <c r="O508" t="n">
-        <v>547050.044621514</v>
+        <v>547050.044979914</v>
       </c>
       <c r="P508" t="n">
         <v>3900</v>
@@ -23584,10 +23584,10 @@
         <v>149</v>
       </c>
       <c r="N515" t="n">
-        <v>1283.6542902208</v>
+        <v>1283.6540655738</v>
       </c>
       <c r="O515" t="n">
-        <v>191264.4892428992</v>
+        <v>191264.4557704962</v>
       </c>
       <c r="P515" t="n">
         <v>1900</v>
@@ -23818,10 +23818,10 @@
         <v>1037</v>
       </c>
       <c r="N520" t="n">
-        <v>517.28747614462</v>
+        <v>517.28760395334</v>
       </c>
       <c r="O520" t="n">
-        <v>536427.112761971</v>
+        <v>536427.2452996136</v>
       </c>
       <c r="P520" t="n">
         <v>900</v>
@@ -24241,10 +24241,10 @@
         <v>757</v>
       </c>
       <c r="N529" t="n">
-        <v>3110.8433414956</v>
+        <v>3110.843282022</v>
       </c>
       <c r="O529" t="n">
-        <v>2354908.409512169</v>
+        <v>2354908.364490654</v>
       </c>
       <c r="P529" t="n">
         <v>4500</v>
@@ -24692,10 +24692,10 @@
         <v>20378</v>
       </c>
       <c r="N539" t="n">
-        <v>703.79545471015</v>
+        <v>703.79543678174</v>
       </c>
       <c r="O539" t="n">
-        <v>14341943.77608344</v>
+        <v>14341943.4107383</v>
       </c>
       <c r="P539" t="n">
         <v>900</v>
@@ -24833,10 +24833,10 @@
         <v>102</v>
       </c>
       <c r="N542" t="n">
-        <v>2501.3854811715</v>
+        <v>2501.3854621849</v>
       </c>
       <c r="O542" t="n">
-        <v>255141.319079493</v>
+        <v>255141.3171428598</v>
       </c>
       <c r="P542" t="n">
         <v>4100</v>
@@ -25106,10 +25106,10 @@
         <v>30</v>
       </c>
       <c r="N548" t="n">
-        <v>3629.7161122661</v>
+        <v>3629.7161041667</v>
       </c>
       <c r="O548" t="n">
-        <v>108891.483367983</v>
+        <v>108891.483125001</v>
       </c>
       <c r="P548" t="n">
         <v>4900</v>
@@ -25199,10 +25199,10 @@
         <v>47</v>
       </c>
       <c r="N550" t="n">
-        <v>1595.51921946</v>
+        <v>1595.5191410878</v>
       </c>
       <c r="O550" t="n">
-        <v>74989.40331461999</v>
+        <v>74989.39963112661</v>
       </c>
       <c r="P550" t="n">
         <v>2500</v>
@@ -26456,10 +26456,10 @@
         <v>24</v>
       </c>
       <c r="N576" t="n">
-        <v>23475.658235294</v>
+        <v>23475.658181818</v>
       </c>
       <c r="O576" t="n">
-        <v>563415.7976470559</v>
+        <v>563415.796363632</v>
       </c>
       <c r="P576" t="n">
         <v>31900</v>
@@ -26845,10 +26845,10 @@
         <v>169</v>
       </c>
       <c r="N584" t="n">
-        <v>875.6901492537301</v>
+        <v>875.69015037594</v>
       </c>
       <c r="O584" t="n">
-        <v>147991.6352238804</v>
+        <v>147991.6354135339</v>
       </c>
       <c r="P584" t="n">
         <v>4500</v>
@@ -27172,10 +27172,10 @@
         <v>312</v>
       </c>
       <c r="N591" t="n">
-        <v>3414.5660866203</v>
+        <v>3414.5660805577</v>
       </c>
       <c r="O591" t="n">
-        <v>1065344.619025534</v>
+        <v>1065344.617134002</v>
       </c>
       <c r="P591" t="n">
         <v>3500</v>
@@ -29360,10 +29360,10 @@
         <v>1135</v>
       </c>
       <c r="N637" t="n">
-        <v>7046.9398305803</v>
+        <v>7046.9398302567</v>
       </c>
       <c r="O637" t="n">
-        <v>7998276.70770864</v>
+        <v>7998276.707341354</v>
       </c>
       <c r="P637" t="n">
         <v>9900</v>
@@ -29550,10 +29550,10 @@
         <v>648</v>
       </c>
       <c r="N641" t="n">
-        <v>665.32324616023</v>
+        <v>665.32330236486</v>
       </c>
       <c r="O641" t="n">
-        <v>431129.4635118291</v>
+        <v>431129.4999324292</v>
       </c>
       <c r="P641" t="n">
         <v>2900</v>
@@ -29890,10 +29890,10 @@
         <v>61</v>
       </c>
       <c r="N648" t="n">
-        <v>540.40245098039</v>
+        <v>540.4025</v>
       </c>
       <c r="O648" t="n">
-        <v>32964.54950980379</v>
+        <v>32964.55250000001</v>
       </c>
       <c r="P648" t="n">
         <v>2500</v>
@@ -30585,10 +30585,10 @@
         <v>4</v>
       </c>
       <c r="N664" t="n">
-        <v>1213.6821153846</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O664" t="n">
-        <v>4854.7284615384</v>
+        <v>4854.728477842</v>
       </c>
       <c r="P664" t="n">
         <v>1500</v>
@@ -30761,10 +30761,10 @@
         <v>190</v>
       </c>
       <c r="N668" t="n">
-        <v>2523.3377514793</v>
+        <v>2523.3377476715</v>
       </c>
       <c r="O668" t="n">
-        <v>479434.172781067</v>
+        <v>479434.172057585</v>
       </c>
       <c r="P668" t="n">
         <v>2800</v>
@@ -31034,10 +31034,10 @@
         <v>358</v>
       </c>
       <c r="N674" t="n">
-        <v>22951.705012407</v>
+        <v>22951.704981273</v>
       </c>
       <c r="O674" t="n">
-        <v>8216710.394441706</v>
+        <v>8216710.383295734</v>
       </c>
       <c r="P674" t="n">
         <v>37900</v>
@@ -31121,10 +31121,10 @@
         <v>93</v>
       </c>
       <c r="N676" t="n">
-        <v>4985.4045627376</v>
+        <v>4985.4046332046</v>
       </c>
       <c r="O676" t="n">
-        <v>463642.6243345968</v>
+        <v>463642.6308880278</v>
       </c>
       <c r="P676" t="n">
         <v>7900</v>
@@ -31172,10 +31172,10 @@
         <v>19</v>
       </c>
       <c r="N677" t="n">
-        <v>1547.8822666667</v>
+        <v>1547.8823611111</v>
       </c>
       <c r="O677" t="n">
-        <v>29409.7630666673</v>
+        <v>29409.7648611109</v>
       </c>
       <c r="P677" t="n">
         <v>5500</v>
@@ -31223,10 +31223,10 @@
         <v>310</v>
       </c>
       <c r="N678" t="n">
-        <v>1757.320515873</v>
+        <v>1757.3205179283</v>
       </c>
       <c r="O678" t="n">
-        <v>544769.35992063</v>
+        <v>544769.360557773</v>
       </c>
       <c r="P678" t="n">
         <v>2000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>178</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3039621792</v>
+        <v>1811.3040256176</v>
       </c>
       <c r="O6" t="n">
-        <v>322412.1052678976</v>
+        <v>322412.1165599328</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7465175202</v>
+        <v>3376.746511879</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.921487857</v>
+        <v>2985043.916501036</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1393,10 +1393,10 @@
         <v>102</v>
       </c>
       <c r="N25" t="n">
-        <v>2474.7042429285</v>
+        <v>2474.7042140468</v>
       </c>
       <c r="O25" t="n">
-        <v>252419.832778707</v>
+        <v>252419.8298327736</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -1878,10 +1878,10 @@
         <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>16486.410204082</v>
+        <v>16486.41</v>
       </c>
       <c r="O37" t="n">
-        <v>395673.844897968</v>
+        <v>395673.84</v>
       </c>
       <c r="P37" t="n">
         <v>30500</v>
@@ -1920,10 +1920,10 @@
         <v>18</v>
       </c>
       <c r="N38" t="n">
-        <v>15711.9662</v>
+        <v>15711.966184739</v>
       </c>
       <c r="O38" t="n">
-        <v>282815.3916</v>
+        <v>282815.391325302</v>
       </c>
       <c r="P38" t="n">
         <v>28500</v>
@@ -1967,10 +1967,10 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>13712.849787234</v>
+        <v>13712.847027027</v>
       </c>
       <c r="O39" t="n">
-        <v>13712.849787234</v>
+        <v>13712.847027027</v>
       </c>
       <c r="P39" t="n">
         <v>22600</v>
@@ -2259,10 +2259,10 @@
         <v>16</v>
       </c>
       <c r="N46" t="n">
-        <v>200072.19914894</v>
+        <v>200072.19977273</v>
       </c>
       <c r="O46" t="n">
-        <v>3201155.18638304</v>
+        <v>3201155.19636368</v>
       </c>
       <c r="P46" t="n">
         <v>312000</v>
@@ -2422,22 +2422,22 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>15780</v>
       </c>
       <c r="O50" t="n">
-        <v>110460</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>21900</v>
       </c>
       <c r="Q50" t="n">
-        <v>153300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3427,10 +3427,10 @@
         <v>1727</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0529624405</v>
+        <v>1098.053336357</v>
       </c>
       <c r="O73" t="n">
-        <v>1896337.466134744</v>
+        <v>1896338.111888539</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4354,22 +4354,22 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M94" t="n">
-        <v>816</v>
+        <v>771</v>
       </c>
       <c r="N94" t="n">
-        <v>2582.2560663507</v>
+        <v>2582.256064019</v>
       </c>
       <c r="O94" t="n">
-        <v>2107120.950142171</v>
+        <v>1990919.425358649</v>
       </c>
       <c r="P94" t="n">
         <v>4500</v>
       </c>
       <c r="Q94" t="n">
-        <v>3672000</v>
+        <v>3469500</v>
       </c>
     </row>
     <row r="95">
@@ -4544,10 +4544,10 @@
         <v>60</v>
       </c>
       <c r="N98" t="n">
-        <v>2033.5756109726</v>
+        <v>2033.574464752</v>
       </c>
       <c r="O98" t="n">
-        <v>122014.536658356</v>
+        <v>122014.46788512</v>
       </c>
       <c r="P98" t="n">
         <v>4100</v>
@@ -5050,10 +5050,10 @@
         <v>259</v>
       </c>
       <c r="N109" t="n">
-        <v>2694.8235120643</v>
+        <v>2694.8234975369</v>
       </c>
       <c r="O109" t="n">
-        <v>697959.2896246536</v>
+        <v>697959.2858620571</v>
       </c>
       <c r="P109" t="n">
         <v>4900</v>
@@ -6088,22 +6088,22 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M132" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N132" t="n">
         <v>10716.34</v>
       </c>
       <c r="O132" t="n">
-        <v>117879.74</v>
+        <v>53581.7</v>
       </c>
       <c r="P132" t="n">
         <v>39000</v>
       </c>
       <c r="Q132" t="n">
-        <v>429000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="133">
@@ -6233,10 +6233,10 @@
         <v>108</v>
       </c>
       <c r="N135" t="n">
-        <v>3240.8500293255</v>
+        <v>3240.8500293686</v>
       </c>
       <c r="O135" t="n">
-        <v>350011.803167154</v>
+        <v>350011.8031718088</v>
       </c>
       <c r="P135" t="n">
         <v>5200</v>
@@ -6417,10 +6417,10 @@
         <v>308</v>
       </c>
       <c r="N139" t="n">
-        <v>14822.378867925</v>
+        <v>14822.378867257</v>
       </c>
       <c r="O139" t="n">
-        <v>4565292.6913209</v>
+        <v>4565292.691115156</v>
       </c>
       <c r="P139" t="n">
         <v>24900</v>
@@ -7142,10 +7142,10 @@
         <v>220</v>
       </c>
       <c r="N155" t="n">
-        <v>3041.6600124378</v>
+        <v>3041.6600124456</v>
       </c>
       <c r="O155" t="n">
-        <v>669165.202736316</v>
+        <v>669165.202738032</v>
       </c>
       <c r="P155" t="n">
         <v>5500</v>
@@ -7360,10 +7360,10 @@
         <v>558</v>
       </c>
       <c r="N160" t="n">
-        <v>1592.5677332171</v>
+        <v>1592.567707231</v>
       </c>
       <c r="O160" t="n">
-        <v>888652.7951351418</v>
+        <v>888652.780634898</v>
       </c>
       <c r="P160" t="n">
         <v>3900</v>
@@ -8628,22 +8628,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M188" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="N188" t="n">
         <v>3761.6</v>
       </c>
       <c r="O188" t="n">
-        <v>421299.2</v>
+        <v>376160</v>
       </c>
       <c r="P188" t="n">
         <v>6900</v>
       </c>
       <c r="Q188" t="n">
-        <v>772800</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="189">
@@ -9050,22 +9050,22 @@
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M197" t="n">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="N197" t="n">
         <v>3751</v>
       </c>
       <c r="O197" t="n">
-        <v>2055548</v>
+        <v>2018038</v>
       </c>
       <c r="P197" t="n">
         <v>6400</v>
       </c>
       <c r="Q197" t="n">
-        <v>3507200</v>
+        <v>3443200</v>
       </c>
     </row>
     <row r="198">
@@ -9151,10 +9151,10 @@
         <v>872</v>
       </c>
       <c r="N199" t="n">
-        <v>1630.9230192383</v>
+        <v>1630.9230407276</v>
       </c>
       <c r="O199" t="n">
-        <v>1422164.872775797</v>
+        <v>1422164.891514467</v>
       </c>
       <c r="P199" t="n">
         <v>2500</v>
@@ -9243,10 +9243,10 @@
         <v>416</v>
       </c>
       <c r="N201" t="n">
-        <v>1690.603799682</v>
+        <v>1690.6035821697</v>
       </c>
       <c r="O201" t="n">
-        <v>703291.180667712</v>
+        <v>703291.0901825952</v>
       </c>
       <c r="P201" t="n">
         <v>2900</v>
@@ -9289,10 +9289,10 @@
         <v>2238</v>
       </c>
       <c r="N202" t="n">
-        <v>1550.19293615</v>
+        <v>1550.1929579149</v>
       </c>
       <c r="O202" t="n">
-        <v>3469331.7911037</v>
+        <v>3469331.839813546</v>
       </c>
       <c r="P202" t="n">
         <v>2500</v>
@@ -9381,10 +9381,10 @@
         <v>454</v>
       </c>
       <c r="N204" t="n">
-        <v>2403.5100306848</v>
+        <v>2403.5100778841</v>
       </c>
       <c r="O204" t="n">
-        <v>1091193.553930899</v>
+        <v>1091193.575359382</v>
       </c>
       <c r="P204" t="n">
         <v>3500</v>
@@ -9427,10 +9427,10 @@
         <v>80</v>
       </c>
       <c r="N205" t="n">
-        <v>2521.5479047619</v>
+        <v>2521.5475490196</v>
       </c>
       <c r="O205" t="n">
-        <v>201723.832380952</v>
+        <v>201723.803921568</v>
       </c>
       <c r="P205" t="n">
         <v>3900</v>
@@ -9468,10 +9468,10 @@
         <v>77</v>
       </c>
       <c r="N206" t="n">
-        <v>1232.8083690987</v>
+        <v>1232.8081659389</v>
       </c>
       <c r="O206" t="n">
-        <v>94926.24442059991</v>
+        <v>94926.2287772953</v>
       </c>
       <c r="P206" t="n">
         <v>2400</v>
@@ -10132,22 +10132,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M221" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N221" t="n">
         <v>8720</v>
       </c>
       <c r="O221" t="n">
-        <v>313920</v>
+        <v>270320</v>
       </c>
       <c r="P221" t="n">
         <v>10900</v>
       </c>
       <c r="Q221" t="n">
-        <v>392400</v>
+        <v>337900</v>
       </c>
     </row>
     <row r="222">
@@ -11810,10 +11810,10 @@
         <v>567</v>
       </c>
       <c r="N259" t="n">
-        <v>4605.2146231618</v>
+        <v>4605.2146487985</v>
       </c>
       <c r="O259" t="n">
-        <v>2611156.691332741</v>
+        <v>2611156.705868749</v>
       </c>
       <c r="P259" t="n">
         <v>7600</v>
@@ -12434,10 +12434,10 @@
         <v>629</v>
       </c>
       <c r="N273" t="n">
-        <v>1560.9988178914</v>
+        <v>1560.9988868445</v>
       </c>
       <c r="O273" t="n">
-        <v>981868.2564536906</v>
+        <v>981868.2998251906</v>
       </c>
       <c r="P273" t="n">
         <v>2900</v>
@@ -13413,10 +13413,10 @@
         <v>122</v>
       </c>
       <c r="N294" t="n">
-        <v>3113.8900249066</v>
+        <v>3113.8900261438</v>
       </c>
       <c r="O294" t="n">
-        <v>379894.5830386052</v>
+        <v>379894.5831895436</v>
       </c>
       <c r="P294" t="n">
         <v>5000</v>
@@ -13781,10 +13781,10 @@
         <v>81</v>
       </c>
       <c r="N302" t="n">
-        <v>5218.1704867257</v>
+        <v>5218.170490524</v>
       </c>
       <c r="O302" t="n">
-        <v>422671.8094247817</v>
+        <v>422671.809732444</v>
       </c>
       <c r="P302" t="n">
         <v>8500</v>
@@ -13827,10 +13827,10 @@
         <v>1</v>
       </c>
       <c r="N303" t="n">
-        <v>1595.0094973545</v>
+        <v>1595.0094864865</v>
       </c>
       <c r="O303" t="n">
-        <v>1595.0094973545</v>
+        <v>1595.0094864865</v>
       </c>
       <c r="P303" t="n">
         <v>2600</v>
@@ -13873,10 +13873,10 @@
         <v>123</v>
       </c>
       <c r="N304" t="n">
-        <v>3610.6500236967</v>
+        <v>3610.6500238379</v>
       </c>
       <c r="O304" t="n">
-        <v>444109.9529146941</v>
+        <v>444109.9529320617</v>
       </c>
       <c r="P304" t="n">
         <v>5800</v>
@@ -14336,10 +14336,10 @@
         <v>48</v>
       </c>
       <c r="N314" t="n">
-        <v>1664.3609992194</v>
+        <v>1664.360841938</v>
       </c>
       <c r="O314" t="n">
-        <v>79889.3279625312</v>
+        <v>79889.320413024</v>
       </c>
       <c r="P314" t="n">
         <v>2900</v>
@@ -14569,10 +14569,10 @@
         <v>14</v>
       </c>
       <c r="N319" t="n">
-        <v>23521.624852941</v>
+        <v>23521.624776119</v>
       </c>
       <c r="O319" t="n">
-        <v>329302.747941174</v>
+        <v>329302.746865666</v>
       </c>
       <c r="P319" t="n">
         <v>39000</v>
@@ -14615,10 +14615,10 @@
         <v>824</v>
       </c>
       <c r="N320" t="n">
-        <v>1778.4725198441</v>
+        <v>1778.4725231214</v>
       </c>
       <c r="O320" t="n">
-        <v>1465461.356351538</v>
+        <v>1465461.359052034</v>
       </c>
       <c r="P320" t="n">
         <v>4900</v>
@@ -15026,22 +15026,22 @@
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M329" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N329" t="n">
         <v>5148</v>
       </c>
       <c r="O329" t="n">
-        <v>97812</v>
+        <v>77220</v>
       </c>
       <c r="P329" t="n">
         <v>8600</v>
       </c>
       <c r="Q329" t="n">
-        <v>163400</v>
+        <v>129000</v>
       </c>
     </row>
     <row r="330">
@@ -16507,22 +16507,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M361" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="N361" t="n">
         <v>3424</v>
       </c>
       <c r="O361" t="n">
-        <v>277344</v>
+        <v>243104</v>
       </c>
       <c r="P361" t="n">
         <v>5900</v>
       </c>
       <c r="Q361" t="n">
-        <v>477900</v>
+        <v>418900</v>
       </c>
     </row>
     <row r="362">
@@ -16553,22 +16553,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M362" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N362" t="n">
         <v>8508</v>
       </c>
       <c r="O362" t="n">
-        <v>68064</v>
+        <v>0</v>
       </c>
       <c r="P362" t="n">
         <v>14500</v>
       </c>
       <c r="Q362" t="n">
-        <v>116000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -16789,10 +16789,10 @@
         <v>53</v>
       </c>
       <c r="N367" t="n">
-        <v>2252.2963076923</v>
+        <v>2252.2963603819</v>
       </c>
       <c r="O367" t="n">
-        <v>119371.7043076919</v>
+        <v>119371.7071002407</v>
       </c>
       <c r="P367" t="n">
         <v>3900</v>
@@ -17621,10 +17621,10 @@
         <v>26</v>
       </c>
       <c r="N385" t="n">
-        <v>16285.911097561</v>
+        <v>16285.911111111</v>
       </c>
       <c r="O385" t="n">
-        <v>423433.688536586</v>
+        <v>423433.688888886</v>
       </c>
       <c r="P385" t="n">
         <v>29900</v>
@@ -17759,10 +17759,10 @@
         <v>165</v>
       </c>
       <c r="N388" t="n">
-        <v>4907.8219155354</v>
+        <v>4907.8219300912</v>
       </c>
       <c r="O388" t="n">
-        <v>809790.616063341</v>
+        <v>809790.6184650479</v>
       </c>
       <c r="P388" t="n">
         <v>8200</v>
@@ -17989,10 +17989,10 @@
         <v>289</v>
       </c>
       <c r="N393" t="n">
-        <v>3903.7358951965</v>
+        <v>3903.7359183673</v>
       </c>
       <c r="O393" t="n">
-        <v>1128179.673711789</v>
+        <v>1128179.68040815</v>
       </c>
       <c r="P393" t="n">
         <v>7500</v>
@@ -19088,10 +19088,10 @@
         <v>292</v>
       </c>
       <c r="N417" t="n">
-        <v>17075.98952512</v>
+        <v>17075.989524793</v>
       </c>
       <c r="O417" t="n">
-        <v>4986188.94133504</v>
+        <v>4986188.941239556</v>
       </c>
       <c r="P417" t="n">
         <v>27500</v>
@@ -20046,22 +20046,22 @@
         <v>0</v>
       </c>
       <c r="L438" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M438" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N438" t="n">
         <v>15472</v>
       </c>
       <c r="O438" t="n">
-        <v>278496</v>
+        <v>247552</v>
       </c>
       <c r="P438" t="n">
         <v>25900</v>
       </c>
       <c r="Q438" t="n">
-        <v>466200</v>
+        <v>414400</v>
       </c>
     </row>
     <row r="439">
@@ -20282,10 +20282,10 @@
         <v>1320</v>
       </c>
       <c r="N443" t="n">
-        <v>1516.0388137227</v>
+        <v>1516.0388131508</v>
       </c>
       <c r="O443" t="n">
-        <v>2001171.234113964</v>
+        <v>2001171.233359056</v>
       </c>
       <c r="P443" t="n">
         <v>2300</v>
@@ -20374,10 +20374,10 @@
         <v>8</v>
       </c>
       <c r="N445" t="n">
-        <v>4248.6172239748</v>
+        <v>4248.6195698925</v>
       </c>
       <c r="O445" t="n">
-        <v>33988.9377917984</v>
+        <v>33988.95655914</v>
       </c>
       <c r="P445" t="n">
         <v>5900</v>
@@ -20466,10 +20466,10 @@
         <v>192</v>
       </c>
       <c r="N447" t="n">
-        <v>1771.091283906</v>
+        <v>1771.0912628399</v>
       </c>
       <c r="O447" t="n">
-        <v>340049.526509952</v>
+        <v>340049.5224652608</v>
       </c>
       <c r="P447" t="n">
         <v>2500</v>
@@ -20512,10 +20512,10 @@
         <v>264</v>
       </c>
       <c r="N448" t="n">
-        <v>2079.3842227979</v>
+        <v>2079.3842209265</v>
       </c>
       <c r="O448" t="n">
-        <v>548957.4348186456</v>
+        <v>548957.434324596</v>
       </c>
       <c r="P448" t="n">
         <v>2900</v>
@@ -20558,10 +20558,10 @@
         <v>264</v>
       </c>
       <c r="N449" t="n">
-        <v>1803.0149867608</v>
+        <v>1803.0149882284</v>
       </c>
       <c r="O449" t="n">
-        <v>475995.9565048512</v>
+        <v>475995.9568922976</v>
       </c>
       <c r="P449" t="n">
         <v>2500</v>
@@ -20604,10 +20604,10 @@
         <v>216</v>
       </c>
       <c r="N450" t="n">
-        <v>3306.5954602774</v>
+        <v>3306.5954545455</v>
       </c>
       <c r="O450" t="n">
-        <v>714224.6194199184</v>
+        <v>714224.6181818281</v>
       </c>
       <c r="P450" t="n">
         <v>4900</v>
@@ -20650,10 +20650,10 @@
         <v>192</v>
       </c>
       <c r="N451" t="n">
-        <v>2122.1641172932</v>
+        <v>2122.1641155235</v>
       </c>
       <c r="O451" t="n">
-        <v>407455.5105202944</v>
+        <v>407455.510180512</v>
       </c>
       <c r="P451" t="n">
         <v>2900</v>
@@ -20696,10 +20696,10 @@
         <v>216</v>
       </c>
       <c r="N452" t="n">
-        <v>2108.7897651007</v>
+        <v>2108.7897869955</v>
       </c>
       <c r="O452" t="n">
-        <v>455498.5892617512</v>
+        <v>455498.593991028</v>
       </c>
       <c r="P452" t="n">
         <v>2900</v>
@@ -20742,10 +20742,10 @@
         <v>144</v>
       </c>
       <c r="N453" t="n">
-        <v>2056.0838952972</v>
+        <v>2056.0838880663</v>
       </c>
       <c r="O453" t="n">
-        <v>296076.0809227968</v>
+        <v>296076.0798815472</v>
       </c>
       <c r="P453" t="n">
         <v>2900</v>
@@ -20834,10 +20834,10 @@
         <v>360</v>
       </c>
       <c r="N455" t="n">
-        <v>1655.93135625</v>
+        <v>1655.931342723</v>
       </c>
       <c r="O455" t="n">
-        <v>596135.28825</v>
+        <v>596135.28338028</v>
       </c>
       <c r="P455" t="n">
         <v>2500</v>
@@ -21064,10 +21064,10 @@
         <v>432</v>
       </c>
       <c r="N460" t="n">
-        <v>1592.2746762208</v>
+        <v>1592.2747647377</v>
       </c>
       <c r="O460" t="n">
-        <v>687862.6601273856</v>
+        <v>687862.6983666865</v>
       </c>
       <c r="P460" t="n">
         <v>2500</v>
@@ -21195,10 +21195,10 @@
         <v>132</v>
       </c>
       <c r="N463" t="n">
-        <v>2311.9269828927</v>
+        <v>2311.9267563291</v>
       </c>
       <c r="O463" t="n">
-        <v>305174.3617418364</v>
+        <v>305174.3318354412</v>
       </c>
       <c r="P463" t="n">
         <v>3500</v>
@@ -21241,10 +21241,10 @@
         <v>48</v>
       </c>
       <c r="N464" t="n">
-        <v>1906.1869325153</v>
+        <v>1906.1867602592</v>
       </c>
       <c r="O464" t="n">
-        <v>91496.9727607344</v>
+        <v>91496.96449244159</v>
       </c>
       <c r="P464" t="n">
         <v>2900</v>
@@ -21287,10 +21287,10 @@
         <v>120</v>
       </c>
       <c r="N465" t="n">
-        <v>3033.7319844358</v>
+        <v>3033.7318786693</v>
       </c>
       <c r="O465" t="n">
-        <v>364047.838132296</v>
+        <v>364047.825440316</v>
       </c>
       <c r="P465" t="n">
         <v>4500</v>
@@ -21333,10 +21333,10 @@
         <v>408</v>
       </c>
       <c r="N466" t="n">
-        <v>2060.160798722</v>
+        <v>2060.160784</v>
       </c>
       <c r="O466" t="n">
-        <v>840545.6058785759</v>
+        <v>840545.599872</v>
       </c>
       <c r="P466" t="n">
         <v>2900</v>
@@ -21379,10 +21379,10 @@
         <v>72</v>
       </c>
       <c r="N467" t="n">
-        <v>1668.6155910543</v>
+        <v>1668.6157419355</v>
       </c>
       <c r="O467" t="n">
-        <v>120140.3225559096</v>
+        <v>120140.333419356</v>
       </c>
       <c r="P467" t="n">
         <v>2500</v>
@@ -21425,10 +21425,10 @@
         <v>72</v>
       </c>
       <c r="N468" t="n">
-        <v>2546.9852428811</v>
+        <v>2546.9851864407</v>
       </c>
       <c r="O468" t="n">
-        <v>183382.9374874392</v>
+        <v>183382.9334237304</v>
       </c>
       <c r="P468" t="n">
         <v>3900</v>
@@ -21471,10 +21471,10 @@
         <v>900</v>
       </c>
       <c r="N469" t="n">
-        <v>1259.2744102228</v>
+        <v>1259.2744140796</v>
       </c>
       <c r="O469" t="n">
-        <v>1133346.96920052</v>
+        <v>1133346.97267164</v>
       </c>
       <c r="P469" t="n">
         <v>1900</v>
@@ -21604,10 +21604,10 @@
         <v>72</v>
       </c>
       <c r="N472" t="n">
-        <v>2556.7444501279</v>
+        <v>2556.7446648794</v>
       </c>
       <c r="O472" t="n">
-        <v>184085.6004092088</v>
+        <v>184085.6158713168</v>
       </c>
       <c r="P472" t="n">
         <v>3900</v>
@@ -21694,10 +21694,10 @@
         <v>660</v>
       </c>
       <c r="N474" t="n">
-        <v>692.15204525288</v>
+        <v>692.15205253785</v>
       </c>
       <c r="O474" t="n">
-        <v>456820.3498669008</v>
+        <v>456820.354674981</v>
       </c>
       <c r="P474" t="n">
         <v>1200</v>
@@ -21835,10 +21835,10 @@
         <v>2800</v>
       </c>
       <c r="N477" t="n">
-        <v>1185.3195720165</v>
+        <v>1185.3195716639</v>
       </c>
       <c r="O477" t="n">
-        <v>3318894.8016462</v>
+        <v>3318894.80065892</v>
       </c>
       <c r="P477" t="n">
         <v>1900</v>
@@ -22249,10 +22249,10 @@
         <v>46</v>
       </c>
       <c r="N486" t="n">
-        <v>3026.514679803</v>
+        <v>3026.5146568627</v>
       </c>
       <c r="O486" t="n">
-        <v>139219.675270938</v>
+        <v>139219.6742156842</v>
       </c>
       <c r="P486" t="n">
         <v>7000</v>
@@ -22477,22 +22477,22 @@
         <v>0</v>
       </c>
       <c r="L491" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M491" t="n">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="N491" t="n">
         <v>3629.36</v>
       </c>
       <c r="O491" t="n">
-        <v>1067031.84</v>
+        <v>1023479.52</v>
       </c>
       <c r="P491" t="n">
         <v>3900</v>
       </c>
       <c r="Q491" t="n">
-        <v>1146600</v>
+        <v>1099800</v>
       </c>
     </row>
     <row r="492">
@@ -22850,10 +22850,10 @@
         <v>306</v>
       </c>
       <c r="N499" t="n">
-        <v>1690.8700088067</v>
+        <v>1690.8700088574</v>
       </c>
       <c r="O499" t="n">
-        <v>517406.2226948502</v>
+        <v>517406.2227103644</v>
       </c>
       <c r="P499" t="n">
         <v>3000</v>
@@ -23737,10 +23737,10 @@
         <v>1037</v>
       </c>
       <c r="N518" t="n">
-        <v>517.28760395334</v>
+        <v>517.28764753291</v>
       </c>
       <c r="O518" t="n">
-        <v>536427.2452996136</v>
+        <v>536427.2904916276</v>
       </c>
       <c r="P518" t="n">
         <v>900</v>
@@ -24160,10 +24160,10 @@
         <v>757</v>
       </c>
       <c r="N527" t="n">
-        <v>3110.843282022</v>
+        <v>3110.8431677619</v>
       </c>
       <c r="O527" t="n">
-        <v>2354908.364490654</v>
+        <v>2354908.277995758</v>
       </c>
       <c r="P527" t="n">
         <v>4500</v>
@@ -24332,22 +24332,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M531" t="n">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="N531" t="n">
         <v>2030.02</v>
       </c>
       <c r="O531" t="n">
-        <v>479084.72</v>
+        <v>416154.1</v>
       </c>
       <c r="P531" t="n">
         <v>3600</v>
       </c>
       <c r="Q531" t="n">
-        <v>849600</v>
+        <v>738000</v>
       </c>
     </row>
     <row r="532">
@@ -24611,10 +24611,10 @@
         <v>20378</v>
       </c>
       <c r="N537" t="n">
-        <v>703.79543678174</v>
+        <v>703.79542528945</v>
       </c>
       <c r="O537" t="n">
-        <v>14341943.4107383</v>
+        <v>14341943.17654841</v>
       </c>
       <c r="P537" t="n">
         <v>900</v>
@@ -24660,10 +24660,10 @@
         <v>55</v>
       </c>
       <c r="N538" t="n">
-        <v>3182.2510909091</v>
+        <v>3182.2510928962</v>
       </c>
       <c r="O538" t="n">
-        <v>175023.8100000005</v>
+        <v>175023.810109291</v>
       </c>
       <c r="P538" t="n">
         <v>6900</v>
@@ -24746,22 +24746,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M540" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="N540" t="n">
-        <v>2501.3854621849</v>
+        <v>2501.385443038</v>
       </c>
       <c r="O540" t="n">
-        <v>255141.3171428598</v>
+        <v>225124.68987342</v>
       </c>
       <c r="P540" t="n">
         <v>4100</v>
       </c>
       <c r="Q540" t="n">
-        <v>418200</v>
+        <v>369000</v>
       </c>
     </row>
     <row r="541">
@@ -25118,10 +25118,10 @@
         <v>47</v>
       </c>
       <c r="N548" t="n">
-        <v>1595.5191410878</v>
+        <v>1595.5191323094</v>
       </c>
       <c r="O548" t="n">
-        <v>74989.39963112661</v>
+        <v>74989.3992185418</v>
       </c>
       <c r="P548" t="n">
         <v>2500</v>
@@ -25507,10 +25507,10 @@
         <v>168</v>
       </c>
       <c r="N556" t="n">
-        <v>2098.4047922438</v>
+        <v>2098.4048459384</v>
       </c>
       <c r="O556" t="n">
-        <v>352532.0050969584</v>
+        <v>352532.0141176512</v>
       </c>
       <c r="P556" t="n">
         <v>9500</v>
@@ -25550,22 +25550,22 @@
         <v>0</v>
       </c>
       <c r="L557" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M557" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N557" t="n">
         <v>16301</v>
       </c>
       <c r="O557" t="n">
-        <v>97806</v>
+        <v>0</v>
       </c>
       <c r="P557" t="n">
         <v>22500</v>
       </c>
       <c r="Q557" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
@@ -26323,22 +26323,22 @@
         <v>0</v>
       </c>
       <c r="L573" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M573" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N573" t="n">
         <v>7230.04</v>
       </c>
       <c r="O573" t="n">
-        <v>238591.32</v>
+        <v>224131.24</v>
       </c>
       <c r="P573" t="n">
         <v>15900</v>
       </c>
       <c r="Q573" t="n">
-        <v>524700</v>
+        <v>492900</v>
       </c>
     </row>
     <row r="574">
@@ -26375,10 +26375,10 @@
         <v>24</v>
       </c>
       <c r="N574" t="n">
-        <v>23475.658181818</v>
+        <v>23475.658125</v>
       </c>
       <c r="O574" t="n">
-        <v>563415.796363632</v>
+        <v>563415.795</v>
       </c>
       <c r="P574" t="n">
         <v>31900</v>
@@ -26473,10 +26473,10 @@
         <v>25</v>
       </c>
       <c r="N576" t="n">
-        <v>9746.8801869159</v>
+        <v>9746.880188679201</v>
       </c>
       <c r="O576" t="n">
-        <v>243672.0046728975</v>
+        <v>243672.00471698</v>
       </c>
       <c r="P576" t="n">
         <v>18500</v>
@@ -26712,22 +26712,22 @@
         <v>0</v>
       </c>
       <c r="L581" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M581" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N581" t="n">
         <v>2992.5684269663</v>
       </c>
       <c r="O581" t="n">
-        <v>122695.3055056183</v>
+        <v>110725.0317977531</v>
       </c>
       <c r="P581" t="n">
         <v>6000</v>
       </c>
       <c r="Q581" t="n">
-        <v>246000</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="582">
@@ -26758,22 +26758,22 @@
         <v>0</v>
       </c>
       <c r="L582" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M582" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N582" t="n">
-        <v>875.69015037594</v>
+        <v>875.69015686275</v>
       </c>
       <c r="O582" t="n">
-        <v>147991.6354135339</v>
+        <v>144488.8758823538</v>
       </c>
       <c r="P582" t="n">
         <v>4500</v>
       </c>
       <c r="Q582" t="n">
-        <v>760500</v>
+        <v>742500</v>
       </c>
     </row>
     <row r="583">
@@ -26807,22 +26807,22 @@
         <v>0</v>
       </c>
       <c r="L583" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M583" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N583" t="n">
         <v>5430.86</v>
       </c>
       <c r="O583" t="n">
-        <v>124909.78</v>
+        <v>92324.62</v>
       </c>
       <c r="P583" t="n">
         <v>13900</v>
       </c>
       <c r="Q583" t="n">
-        <v>319700</v>
+        <v>236300</v>
       </c>
     </row>
     <row r="584">
@@ -26905,22 +26905,22 @@
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M585" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="N585" t="n">
         <v>4568.55</v>
       </c>
       <c r="O585" t="n">
-        <v>402032.4</v>
+        <v>338072.7</v>
       </c>
       <c r="P585" t="n">
         <v>6900</v>
       </c>
       <c r="Q585" t="n">
-        <v>607200</v>
+        <v>510600</v>
       </c>
     </row>
     <row r="586">
@@ -28190,10 +28190,10 @@
         <v>15</v>
       </c>
       <c r="N612" t="n">
-        <v>14751.8203125</v>
+        <v>14751.82031746</v>
       </c>
       <c r="O612" t="n">
-        <v>221277.3046875</v>
+        <v>221277.3047619</v>
       </c>
       <c r="P612" t="n">
         <v>37100</v>
@@ -28898,10 +28898,10 @@
         <v>4</v>
       </c>
       <c r="N627" t="n">
-        <v>14327.781428571</v>
+        <v>14327.781538462</v>
       </c>
       <c r="O627" t="n">
-        <v>57311.125714284</v>
+        <v>57311.126153848</v>
       </c>
       <c r="P627" t="n">
         <v>29900</v>
@@ -29469,10 +29469,10 @@
         <v>648</v>
       </c>
       <c r="N639" t="n">
-        <v>665.32330236486</v>
+        <v>665.3233262441501</v>
       </c>
       <c r="O639" t="n">
-        <v>431129.4999324292</v>
+        <v>431129.5154062092</v>
       </c>
       <c r="P639" t="n">
         <v>2900</v>
@@ -30953,10 +30953,10 @@
         <v>358</v>
       </c>
       <c r="N672" t="n">
-        <v>22951.704981273</v>
+        <v>22951.704968711</v>
       </c>
       <c r="O672" t="n">
-        <v>8216710.383295734</v>
+        <v>8216710.378798539</v>
       </c>
       <c r="P672" t="n">
         <v>37900</v>
@@ -31085,22 +31085,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M675" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N675" t="n">
-        <v>1547.8823611111</v>
+        <v>1547.8824285714</v>
       </c>
       <c r="O675" t="n">
-        <v>29409.7648611109</v>
+        <v>12383.0594285712</v>
       </c>
       <c r="P675" t="n">
         <v>5500</v>
       </c>
       <c r="Q675" t="n">
-        <v>104500</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="676">
@@ -31280,10 +31280,10 @@
         <v>4600</v>
       </c>
       <c r="N679" t="n">
-        <v>220.00867896778</v>
+        <v>220.00852554547</v>
       </c>
       <c r="O679" t="n">
-        <v>1012039.923251788</v>
+        <v>1012039.217509162</v>
       </c>
       <c r="P679" t="n">
         <v>260</v>
@@ -31550,22 +31550,22 @@
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M685" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N685" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O685" t="n">
-        <v>262121.13</v>
+        <v>213580.18</v>
       </c>
       <c r="P685" t="n">
         <v>10200</v>
       </c>
       <c r="Q685" t="n">
-        <v>275400</v>
+        <v>224400</v>
       </c>
     </row>
     <row r="686">
@@ -31642,22 +31642,22 @@
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M687" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="N687" t="n">
         <v>1952.41</v>
       </c>
       <c r="O687" t="n">
-        <v>378767.54</v>
+        <v>359243.44</v>
       </c>
       <c r="P687" t="n">
         <v>2700</v>
       </c>
       <c r="Q687" t="n">
-        <v>523800</v>
+        <v>496800</v>
       </c>
     </row>
     <row r="688">
@@ -31780,22 +31780,22 @@
         <v>0</v>
       </c>
       <c r="L690" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M690" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N690" t="n">
         <v>415.07</v>
       </c>
       <c r="O690" t="n">
-        <v>15357.59</v>
+        <v>12867.17</v>
       </c>
       <c r="P690" t="n">
         <v>2900</v>
       </c>
       <c r="Q690" t="n">
-        <v>107300</v>
+        <v>89900</v>
       </c>
     </row>
     <row r="691">
@@ -32067,10 +32067,10 @@
         <v>200</v>
       </c>
       <c r="N696" t="n">
-        <v>1319.3608695652</v>
+        <v>1319.360872093</v>
       </c>
       <c r="O696" t="n">
-        <v>263872.17391304</v>
+        <v>263872.1744186</v>
       </c>
       <c r="P696" t="n">
         <v>3500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -556,10 +556,10 @@
         <v>322</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27043.062200957</v>
       </c>
       <c r="O4" t="n">
-        <v>8694000</v>
+        <v>8707866.028708154</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -589,22 +589,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N5" t="n">
         <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>2997000</v>
+        <v>2943000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2220000</v>
+        <v>2180000</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M6" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3040256176</v>
+        <v>1811.3041548631</v>
       </c>
       <c r="O6" t="n">
-        <v>322412.1165599328</v>
+        <v>266261.7107648757</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
       </c>
       <c r="Q6" t="n">
-        <v>462800</v>
+        <v>382200</v>
       </c>
     </row>
     <row r="7">
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.746511879</v>
+        <v>3376.7465109371</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.916501036</v>
+        <v>2985043.915668396</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -995,10 +995,10 @@
         <v>156</v>
       </c>
       <c r="N15" t="n">
-        <v>27000</v>
+        <v>27064.133016627</v>
       </c>
       <c r="O15" t="n">
-        <v>4212000</v>
+        <v>4222004.750593812</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
@@ -1234,10 +1234,10 @@
         <v>210</v>
       </c>
       <c r="N21" t="n">
-        <v>3926.8371296771</v>
+        <v>3926.8371267317</v>
       </c>
       <c r="O21" t="n">
-        <v>824635.7972321911</v>
+        <v>824635.796613657</v>
       </c>
       <c r="P21" t="n">
         <v>4800</v>
@@ -1471,10 +1471,10 @@
         <v>120</v>
       </c>
       <c r="N27" t="n">
-        <v>3716.3301889764</v>
+        <v>3716.3301892744</v>
       </c>
       <c r="O27" t="n">
-        <v>445959.6226771681</v>
+        <v>445959.622712928</v>
       </c>
       <c r="P27" t="n">
         <v>9500</v>
@@ -1582,22 +1582,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N30" t="n">
         <v>27000</v>
       </c>
       <c r="O30" t="n">
-        <v>2727000</v>
+        <v>2673000</v>
       </c>
       <c r="P30" t="n">
         <v>30000</v>
       </c>
       <c r="Q30" t="n">
-        <v>3030000</v>
+        <v>2970000</v>
       </c>
     </row>
     <row r="31">
@@ -1627,10 +1627,10 @@
         <v>35</v>
       </c>
       <c r="N31" t="n">
-        <v>21333.69</v>
+        <v>21423.327352941</v>
       </c>
       <c r="O31" t="n">
-        <v>746679.1499999999</v>
+        <v>749816.457352935</v>
       </c>
       <c r="P31" t="n">
         <v>30000</v>
@@ -1747,10 +1747,10 @@
         <v>16</v>
       </c>
       <c r="N34" t="n">
-        <v>12837.964861111</v>
+        <v>12837.965507246</v>
       </c>
       <c r="O34" t="n">
-        <v>205407.437777776</v>
+        <v>205407.448115936</v>
       </c>
       <c r="P34" t="n">
         <v>22900</v>
@@ -1836,10 +1836,10 @@
         <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>10994.353043478</v>
+        <v>10994.353483146</v>
       </c>
       <c r="O36" t="n">
-        <v>65966.11826086801</v>
+        <v>65966.120898876</v>
       </c>
       <c r="P36" t="n">
         <v>16900</v>
@@ -1878,10 +1878,10 @@
         <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>16486.41</v>
+        <v>16486.409489051</v>
       </c>
       <c r="O37" t="n">
-        <v>395673.84</v>
+        <v>395673.8277372239</v>
       </c>
       <c r="P37" t="n">
         <v>30500</v>
@@ -1920,10 +1920,10 @@
         <v>18</v>
       </c>
       <c r="N38" t="n">
-        <v>15711.966184739</v>
+        <v>15711.966106557</v>
       </c>
       <c r="O38" t="n">
-        <v>282815.391325302</v>
+        <v>282815.389918026</v>
       </c>
       <c r="P38" t="n">
         <v>28500</v>
@@ -1967,10 +1967,10 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>13712.847027027</v>
+        <v>13712.845882353</v>
       </c>
       <c r="O39" t="n">
-        <v>13712.847027027</v>
+        <v>13712.845882353</v>
       </c>
       <c r="P39" t="n">
         <v>22600</v>
@@ -2123,10 +2123,10 @@
         <v>19</v>
       </c>
       <c r="N43" t="n">
-        <v>14708.815789474</v>
+        <v>14708.815744681</v>
       </c>
       <c r="O43" t="n">
-        <v>279467.500000006</v>
+        <v>279467.499148939</v>
       </c>
       <c r="P43" t="n">
         <v>16900</v>
@@ -2253,22 +2253,22 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M46" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N46" t="n">
         <v>200072.19977273</v>
       </c>
       <c r="O46" t="n">
-        <v>3201155.19636368</v>
+        <v>1400505.39840911</v>
       </c>
       <c r="P46" t="n">
         <v>312000</v>
       </c>
       <c r="Q46" t="n">
-        <v>4992000</v>
+        <v>2184000</v>
       </c>
     </row>
     <row r="47">
@@ -2306,10 +2306,10 @@
         <v>13</v>
       </c>
       <c r="N47" t="n">
-        <v>344599.1787931</v>
+        <v>344599.17865385</v>
       </c>
       <c r="O47" t="n">
-        <v>4479789.3243103</v>
+        <v>4479789.32250005</v>
       </c>
       <c r="P47" t="n">
         <v>532900</v>
@@ -2565,10 +2565,10 @@
         <v>144</v>
       </c>
       <c r="N53" t="n">
-        <v>580.36602666667</v>
+        <v>580.36600536193</v>
       </c>
       <c r="O53" t="n">
-        <v>83572.70784000048</v>
+        <v>83572.70477211791</v>
       </c>
       <c r="P53" t="n">
         <v>6800</v>
@@ -2611,10 +2611,10 @@
         <v>98</v>
       </c>
       <c r="N54" t="n">
-        <v>538.40029962547</v>
+        <v>538.40033834586</v>
       </c>
       <c r="O54" t="n">
-        <v>52763.22936329606</v>
+        <v>52763.23315789428</v>
       </c>
       <c r="P54" t="n">
         <v>6800</v>
@@ -2657,10 +2657,10 @@
         <v>14</v>
       </c>
       <c r="N55" t="n">
-        <v>28.165642201835</v>
+        <v>28.165601851852</v>
       </c>
       <c r="O55" t="n">
-        <v>394.31899082569</v>
+        <v>394.318425925928</v>
       </c>
       <c r="P55" t="n">
         <v>6800</v>
@@ -3129,10 +3129,10 @@
         <v>228</v>
       </c>
       <c r="N66" t="n">
-        <v>4937.3101601164</v>
+        <v>4937.3101603499</v>
       </c>
       <c r="O66" t="n">
-        <v>1125706.716506539</v>
+        <v>1125706.716559777</v>
       </c>
       <c r="P66" t="n">
         <v>7500</v>
@@ -3391,10 +3391,10 @@
         <v>1727</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.053336357</v>
+        <v>1098.0535004591</v>
       </c>
       <c r="O72" t="n">
-        <v>1896338.111888539</v>
+        <v>1896338.395292866</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -3796,10 +3796,10 @@
         <v>61</v>
       </c>
       <c r="N81" t="n">
-        <v>17207.41</v>
+        <v>17261.351724138</v>
       </c>
       <c r="O81" t="n">
-        <v>1049652.01</v>
+        <v>1052942.455172418</v>
       </c>
       <c r="P81" t="n">
         <v>20000</v>
@@ -4060,10 +4060,10 @@
         <v>363</v>
       </c>
       <c r="N87" t="n">
-        <v>2804.33</v>
+        <v>2808.0329005282</v>
       </c>
       <c r="O87" t="n">
-        <v>1017971.79</v>
+        <v>1019315.942891737</v>
       </c>
       <c r="P87" t="n">
         <v>4900</v>
@@ -4324,10 +4324,10 @@
         <v>771</v>
       </c>
       <c r="N93" t="n">
-        <v>2582.256064019</v>
+        <v>2582.2560562265</v>
       </c>
       <c r="O93" t="n">
-        <v>1990919.425358649</v>
+        <v>1990919.419350631</v>
       </c>
       <c r="P93" t="n">
         <v>4500</v>
@@ -4502,22 +4502,22 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M97" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2033.574464752</v>
+        <v>2033.573495935</v>
       </c>
       <c r="O97" t="n">
-        <v>122014.46788512</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
         <v>4100</v>
       </c>
       <c r="Q97" t="n">
-        <v>246000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4739,10 +4739,10 @@
         <v>3199</v>
       </c>
       <c r="N102" t="n">
-        <v>3158.8608137572</v>
+        <v>3158.860813875</v>
       </c>
       <c r="O102" t="n">
-        <v>10105195.74320928</v>
+        <v>10105195.74358612</v>
       </c>
       <c r="P102" t="n">
         <v>5600</v>
@@ -4785,10 +4785,10 @@
         <v>80</v>
       </c>
       <c r="N103" t="n">
-        <v>3841.6246911197</v>
+        <v>3841.6247184466</v>
       </c>
       <c r="O103" t="n">
-        <v>307329.975289576</v>
+        <v>307329.977475728</v>
       </c>
       <c r="P103" t="n">
         <v>6900</v>
@@ -4869,22 +4869,22 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M105" t="n">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="N105" t="n">
-        <v>3230.0677597403</v>
+        <v>3230.067752443</v>
       </c>
       <c r="O105" t="n">
-        <v>642783.4841883198</v>
+        <v>581412.19543974</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
       </c>
       <c r="Q105" t="n">
-        <v>1233800</v>
+        <v>1116000</v>
       </c>
     </row>
     <row r="106">
@@ -5014,10 +5014,10 @@
         <v>259</v>
       </c>
       <c r="N108" t="n">
-        <v>2694.8234975369</v>
+        <v>2694.8234682861</v>
       </c>
       <c r="O108" t="n">
-        <v>697959.2858620571</v>
+        <v>697959.2782860999</v>
       </c>
       <c r="P108" t="n">
         <v>4900</v>
@@ -5247,10 +5247,10 @@
         <v>391</v>
       </c>
       <c r="N113" t="n">
-        <v>6507</v>
+        <v>6511.2612966601</v>
       </c>
       <c r="O113" t="n">
-        <v>2544237</v>
+        <v>2545903.166994099</v>
       </c>
       <c r="P113" t="n">
         <v>9900</v>
@@ -5334,10 +5334,10 @@
         <v>593</v>
       </c>
       <c r="N115" t="n">
-        <v>3795.7100070509</v>
+        <v>3795.7100070547</v>
       </c>
       <c r="O115" t="n">
-        <v>2250856.034181184</v>
+        <v>2250856.034183437</v>
       </c>
       <c r="P115" t="n">
         <v>6200</v>
@@ -5559,10 +5559,10 @@
         <v>318</v>
       </c>
       <c r="N120" t="n">
-        <v>4890.9300460299</v>
+        <v>4890.9300461095</v>
       </c>
       <c r="O120" t="n">
-        <v>1555315.754637508</v>
+        <v>1555315.754662821</v>
       </c>
       <c r="P120" t="n">
         <v>8200</v>
@@ -5648,22 +5648,22 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M122" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
         <v>1203.38</v>
       </c>
       <c r="O122" t="n">
-        <v>24067.6</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
         <v>1900</v>
       </c>
       <c r="Q122" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5879,10 +5879,10 @@
         <v>967</v>
       </c>
       <c r="N127" t="n">
-        <v>5667.94</v>
+        <v>5672.995244381</v>
       </c>
       <c r="O127" t="n">
-        <v>5480897.98</v>
+        <v>5485786.401316427</v>
       </c>
       <c r="P127" t="n">
         <v>9500</v>
@@ -5971,10 +5971,10 @@
         <v>281</v>
       </c>
       <c r="N129" t="n">
-        <v>8662</v>
+        <v>8688.0641925777</v>
       </c>
       <c r="O129" t="n">
-        <v>2434022</v>
+        <v>2441346.038114334</v>
       </c>
       <c r="P129" t="n">
         <v>14200</v>
@@ -6107,10 +6107,10 @@
         <v>288</v>
       </c>
       <c r="N132" t="n">
-        <v>3594.2542307692</v>
+        <v>3594.254188862</v>
       </c>
       <c r="O132" t="n">
-        <v>1035145.21846153</v>
+        <v>1035145.206392256</v>
       </c>
       <c r="P132" t="n">
         <v>6500</v>
@@ -6150,22 +6150,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M133" t="n">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="N133" t="n">
         <v>489.88</v>
       </c>
       <c r="O133" t="n">
-        <v>90627.8</v>
+        <v>8327.959999999999</v>
       </c>
       <c r="P133" t="n">
         <v>700</v>
       </c>
       <c r="Q133" t="n">
-        <v>129500</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="134">
@@ -6197,10 +6197,10 @@
         <v>108</v>
       </c>
       <c r="N134" t="n">
-        <v>3240.8500293686</v>
+        <v>3259.9983308715</v>
       </c>
       <c r="O134" t="n">
-        <v>350011.8031718088</v>
+        <v>352079.819734122</v>
       </c>
       <c r="P134" t="n">
         <v>5200</v>
@@ -6698,10 +6698,10 @@
         <v>708</v>
       </c>
       <c r="N145" t="n">
-        <v>2665.4</v>
+        <v>2670.3450834879</v>
       </c>
       <c r="O145" t="n">
-        <v>1887103.2</v>
+        <v>1890604.319109433</v>
       </c>
       <c r="P145" t="n">
         <v>20900</v>
@@ -6790,10 +6790,10 @@
         <v>43</v>
       </c>
       <c r="N147" t="n">
-        <v>12267.651212121</v>
+        <v>12267.650842105</v>
       </c>
       <c r="O147" t="n">
-        <v>527509.002121203</v>
+        <v>527508.986210515</v>
       </c>
       <c r="P147" t="n">
         <v>19900</v>
@@ -7106,10 +7106,10 @@
         <v>220</v>
       </c>
       <c r="N154" t="n">
-        <v>3041.6600124456</v>
+        <v>3041.6600125549</v>
       </c>
       <c r="O154" t="n">
-        <v>669165.202738032</v>
+        <v>669165.2027620779</v>
       </c>
       <c r="P154" t="n">
         <v>5500</v>
@@ -7234,10 +7234,10 @@
         <v>1945</v>
       </c>
       <c r="N157" t="n">
-        <v>4372.2107863175</v>
+        <v>4372.2107866525</v>
       </c>
       <c r="O157" t="n">
-        <v>8503949.979387537</v>
+        <v>8503949.980039112</v>
       </c>
       <c r="P157" t="n">
         <v>7500</v>
@@ -7272,22 +7272,22 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M158" t="n">
-        <v>883</v>
+        <v>863</v>
       </c>
       <c r="N158" t="n">
         <v>6441.03</v>
       </c>
       <c r="O158" t="n">
-        <v>5687429.49</v>
+        <v>5558608.89</v>
       </c>
       <c r="P158" t="n">
         <v>10500</v>
       </c>
       <c r="Q158" t="n">
-        <v>9271500</v>
+        <v>9061500</v>
       </c>
     </row>
     <row r="159">
@@ -7318,22 +7318,22 @@
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M159" t="n">
-        <v>558</v>
+        <v>498</v>
       </c>
       <c r="N159" t="n">
-        <v>1592.567707231</v>
+        <v>1592.5676712942</v>
       </c>
       <c r="O159" t="n">
-        <v>888652.780634898</v>
+        <v>793098.7003045116</v>
       </c>
       <c r="P159" t="n">
         <v>3900</v>
       </c>
       <c r="Q159" t="n">
-        <v>2176200</v>
+        <v>1942200</v>
       </c>
     </row>
     <row r="160">
@@ -8401,22 +8401,22 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M183" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="N183" t="n">
         <v>16897</v>
       </c>
       <c r="O183" t="n">
-        <v>1892464</v>
+        <v>1774185</v>
       </c>
       <c r="P183" t="n">
         <v>27900</v>
       </c>
       <c r="Q183" t="n">
-        <v>3124800</v>
+        <v>2929500</v>
       </c>
     </row>
     <row r="184">
@@ -9014,22 +9014,22 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M196" t="n">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="N196" t="n">
         <v>3751</v>
       </c>
       <c r="O196" t="n">
-        <v>2018038</v>
+        <v>2003034</v>
       </c>
       <c r="P196" t="n">
         <v>6400</v>
       </c>
       <c r="Q196" t="n">
-        <v>3443200</v>
+        <v>3417600</v>
       </c>
     </row>
     <row r="197">
@@ -9109,22 +9109,22 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M198" t="n">
-        <v>872</v>
+        <v>824</v>
       </c>
       <c r="N198" t="n">
-        <v>1630.9230407276</v>
+        <v>1630.9230521929</v>
       </c>
       <c r="O198" t="n">
-        <v>1422164.891514467</v>
+        <v>1343880.59500695</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
       </c>
       <c r="Q198" t="n">
-        <v>2180000</v>
+        <v>2060000</v>
       </c>
     </row>
     <row r="199">
@@ -9201,22 +9201,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M200" t="n">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="N200" t="n">
-        <v>1690.6035821697</v>
+        <v>1690.6034846029</v>
       </c>
       <c r="O200" t="n">
-        <v>703291.0901825952</v>
+        <v>649191.7380875136</v>
       </c>
       <c r="P200" t="n">
         <v>2900</v>
       </c>
       <c r="Q200" t="n">
-        <v>1206400</v>
+        <v>1113600</v>
       </c>
     </row>
     <row r="201">
@@ -9247,22 +9247,22 @@
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M201" t="n">
-        <v>2238</v>
+        <v>2118</v>
       </c>
       <c r="N201" t="n">
-        <v>1550.1929579149</v>
+        <v>1550.1930031561</v>
       </c>
       <c r="O201" t="n">
-        <v>3469331.839813546</v>
+        <v>3283308.78068462</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
       </c>
       <c r="Q201" t="n">
-        <v>5595000</v>
+        <v>5295000</v>
       </c>
     </row>
     <row r="202">
@@ -9299,10 +9299,10 @@
         <v>22</v>
       </c>
       <c r="N202" t="n">
-        <v>1579.3910696517</v>
+        <v>1579.3910473815</v>
       </c>
       <c r="O202" t="n">
-        <v>34746.6035323374</v>
+        <v>34746.603042393</v>
       </c>
       <c r="P202" t="n">
         <v>2900</v>
@@ -9345,10 +9345,10 @@
         <v>454</v>
       </c>
       <c r="N203" t="n">
-        <v>2403.5100778841</v>
+        <v>2403.5101337902</v>
       </c>
       <c r="O203" t="n">
-        <v>1091193.575359382</v>
+        <v>1091193.600740751</v>
       </c>
       <c r="P203" t="n">
         <v>3500</v>
@@ -9391,10 +9391,10 @@
         <v>80</v>
       </c>
       <c r="N204" t="n">
-        <v>2521.5475490196</v>
+        <v>2521.5468491124</v>
       </c>
       <c r="O204" t="n">
-        <v>201723.803921568</v>
+        <v>201723.747928992</v>
       </c>
       <c r="P204" t="n">
         <v>3900</v>
@@ -9508,22 +9508,22 @@
         <v>0</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M207" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
         <v>18598</v>
       </c>
       <c r="O207" t="n">
-        <v>55794</v>
+        <v>0</v>
       </c>
       <c r="P207" t="n">
         <v>21900</v>
       </c>
       <c r="Q207" t="n">
-        <v>65700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -10004,22 +10004,22 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M218" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="N218" t="n">
         <v>7028</v>
       </c>
       <c r="O218" t="n">
-        <v>794164</v>
+        <v>709828</v>
       </c>
       <c r="P218" t="n">
         <v>15900</v>
       </c>
       <c r="Q218" t="n">
-        <v>1796700</v>
+        <v>1605900</v>
       </c>
     </row>
     <row r="219">
@@ -10096,22 +10096,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M220" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N220" t="n">
         <v>8720</v>
       </c>
       <c r="O220" t="n">
-        <v>270320</v>
+        <v>252880</v>
       </c>
       <c r="P220" t="n">
         <v>10900</v>
       </c>
       <c r="Q220" t="n">
-        <v>337900</v>
+        <v>316100</v>
       </c>
     </row>
     <row r="221">
@@ -10644,10 +10644,10 @@
         <v>19</v>
       </c>
       <c r="N232" t="n">
-        <v>7537.4721014493</v>
+        <v>7537.4721167883</v>
       </c>
       <c r="O232" t="n">
-        <v>143211.9699275367</v>
+        <v>143211.9702189777</v>
       </c>
       <c r="P232" t="n">
         <v>8900</v>
@@ -10685,10 +10685,10 @@
         <v>2</v>
       </c>
       <c r="N233" t="n">
-        <v>4488</v>
+        <v>4530.3396226415</v>
       </c>
       <c r="O233" t="n">
-        <v>8976</v>
+        <v>9060.679245283</v>
       </c>
       <c r="P233" t="n">
         <v>6200</v>
@@ -11235,22 +11235,22 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M246" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="N246" t="n">
         <v>5674</v>
       </c>
       <c r="O246" t="n">
-        <v>317744</v>
+        <v>249656</v>
       </c>
       <c r="P246" t="n">
         <v>8600</v>
       </c>
       <c r="Q246" t="n">
-        <v>481600</v>
+        <v>378400</v>
       </c>
     </row>
     <row r="247">
@@ -11420,10 +11420,10 @@
         <v>900</v>
       </c>
       <c r="N250" t="n">
-        <v>998.76125816993</v>
+        <v>998.76125988546</v>
       </c>
       <c r="O250" t="n">
-        <v>898885.132352937</v>
+        <v>898885.1338969141</v>
       </c>
       <c r="P250" t="n">
         <v>1600</v>
@@ -11815,10 +11815,10 @@
         <v>921</v>
       </c>
       <c r="N259" t="n">
-        <v>3591.13</v>
+        <v>3592.9712903777</v>
       </c>
       <c r="O259" t="n">
-        <v>3307430.73</v>
+        <v>3309126.558437862</v>
       </c>
       <c r="P259" t="n">
         <v>6300</v>
@@ -11861,10 +11861,10 @@
         <v>32</v>
       </c>
       <c r="N260" t="n">
-        <v>11562.038534031</v>
+        <v>11562.038530184</v>
       </c>
       <c r="O260" t="n">
-        <v>369985.233088992</v>
+        <v>369985.232965888</v>
       </c>
       <c r="P260" t="n">
         <v>18500</v>
@@ -11942,22 +11942,22 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M262" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
         <v>15700</v>
       </c>
       <c r="O262" t="n">
-        <v>94200</v>
+        <v>0</v>
       </c>
       <c r="P262" t="n">
         <v>29900</v>
       </c>
       <c r="Q262" t="n">
-        <v>179400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -12080,22 +12080,22 @@
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M265" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N265" t="n">
         <v>29631.46</v>
       </c>
       <c r="O265" t="n">
-        <v>207420.22</v>
+        <v>148157.3</v>
       </c>
       <c r="P265" t="n">
         <v>65500</v>
       </c>
       <c r="Q265" t="n">
-        <v>458500</v>
+        <v>327500</v>
       </c>
     </row>
     <row r="266">
@@ -12213,22 +12213,22 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M268" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="N268" t="n">
         <v>16974.69</v>
       </c>
       <c r="O268" t="n">
-        <v>1120329.54</v>
+        <v>916633.2599999999</v>
       </c>
       <c r="P268" t="n">
         <v>26900</v>
       </c>
       <c r="Q268" t="n">
-        <v>1775400</v>
+        <v>1452600</v>
       </c>
     </row>
     <row r="269">
@@ -12260,10 +12260,10 @@
         <v>1330</v>
       </c>
       <c r="N269" t="n">
-        <v>4100.45</v>
+        <v>4107.7418494369</v>
       </c>
       <c r="O269" t="n">
-        <v>5453598.5</v>
+        <v>5463296.659751077</v>
       </c>
       <c r="P269" t="n">
         <v>26900</v>
@@ -12392,22 +12392,22 @@
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M272" t="n">
-        <v>629</v>
+        <v>599</v>
       </c>
       <c r="N272" t="n">
-        <v>1560.9988868445</v>
+        <v>1560.9989986027</v>
       </c>
       <c r="O272" t="n">
-        <v>981868.2998251906</v>
+        <v>935038.4001630173</v>
       </c>
       <c r="P272" t="n">
         <v>2900</v>
       </c>
       <c r="Q272" t="n">
-        <v>1824100</v>
+        <v>1737100</v>
       </c>
     </row>
     <row r="273">
@@ -12666,22 +12666,22 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M278" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N278" t="n">
         <v>10900</v>
       </c>
       <c r="O278" t="n">
-        <v>261600</v>
+        <v>174400</v>
       </c>
       <c r="P278" t="n">
         <v>18900</v>
       </c>
       <c r="Q278" t="n">
-        <v>453600</v>
+        <v>302400</v>
       </c>
     </row>
     <row r="279">
@@ -12816,10 +12816,10 @@
         <v>26</v>
       </c>
       <c r="N281" t="n">
-        <v>12981.59</v>
+        <v>13028.454945848</v>
       </c>
       <c r="O281" t="n">
-        <v>337521.34</v>
+        <v>338739.828592048</v>
       </c>
       <c r="P281" t="n">
         <v>21900</v>
@@ -13092,22 +13092,22 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M287" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
         <v>20504</v>
       </c>
       <c r="O287" t="n">
-        <v>102520</v>
+        <v>0</v>
       </c>
       <c r="P287" t="n">
         <v>32900</v>
       </c>
       <c r="Q287" t="n">
-        <v>164500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -13141,22 +13141,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M288" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N288" t="n">
         <v>8562.18</v>
       </c>
       <c r="O288" t="n">
-        <v>128432.7</v>
+        <v>119870.52</v>
       </c>
       <c r="P288" t="n">
         <v>9900</v>
       </c>
       <c r="Q288" t="n">
-        <v>148500</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="289">
@@ -13745,10 +13745,10 @@
         <v>81</v>
       </c>
       <c r="N301" t="n">
-        <v>5218.170490524</v>
+        <v>5218.1704988662</v>
       </c>
       <c r="O301" t="n">
-        <v>422671.809732444</v>
+        <v>422671.8104081622</v>
       </c>
       <c r="P301" t="n">
         <v>8500</v>
@@ -13791,10 +13791,10 @@
         <v>1</v>
       </c>
       <c r="N302" t="n">
-        <v>1595.0094864865</v>
+        <v>1595.0094843962</v>
       </c>
       <c r="O302" t="n">
-        <v>1595.0094864865</v>
+        <v>1595.0094843962</v>
       </c>
       <c r="P302" t="n">
         <v>2600</v>
@@ -13837,10 +13837,10 @@
         <v>123</v>
       </c>
       <c r="N303" t="n">
-        <v>3610.6500238379</v>
+        <v>3610.6500238663</v>
       </c>
       <c r="O303" t="n">
-        <v>444109.9529320617</v>
+        <v>444109.9529355549</v>
       </c>
       <c r="P303" t="n">
         <v>5800</v>
@@ -14300,10 +14300,10 @@
         <v>48</v>
       </c>
       <c r="N313" t="n">
-        <v>1664.360841938</v>
+        <v>1664.3605954323</v>
       </c>
       <c r="O313" t="n">
-        <v>79889.320413024</v>
+        <v>79889.3085807504</v>
       </c>
       <c r="P313" t="n">
         <v>2900</v>
@@ -14435,22 +14435,22 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N316" t="n">
         <v>34546</v>
       </c>
       <c r="O316" t="n">
-        <v>103638</v>
+        <v>69092</v>
       </c>
       <c r="P316" t="n">
         <v>57900</v>
       </c>
       <c r="Q316" t="n">
-        <v>173700</v>
+        <v>115800</v>
       </c>
     </row>
     <row r="317">
@@ -14527,22 +14527,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N318" t="n">
         <v>23521.624776119</v>
       </c>
       <c r="O318" t="n">
-        <v>329302.746865666</v>
+        <v>305781.122089547</v>
       </c>
       <c r="P318" t="n">
         <v>39000</v>
       </c>
       <c r="Q318" t="n">
-        <v>546000</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="319">
@@ -14579,10 +14579,10 @@
         <v>824</v>
       </c>
       <c r="N319" t="n">
-        <v>1778.4725231214</v>
+        <v>1778.4725400058</v>
       </c>
       <c r="O319" t="n">
-        <v>1465461.359052034</v>
+        <v>1465461.372964779</v>
       </c>
       <c r="P319" t="n">
         <v>4900</v>
@@ -14619,22 +14619,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M320" t="n">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="N320" t="n">
         <v>1548</v>
       </c>
       <c r="O320" t="n">
-        <v>1126944</v>
+        <v>1114560</v>
       </c>
       <c r="P320" t="n">
         <v>3900</v>
       </c>
       <c r="Q320" t="n">
-        <v>2839200</v>
+        <v>2808000</v>
       </c>
     </row>
     <row r="321">
@@ -14665,22 +14665,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M321" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="N321" t="n">
         <v>2325</v>
       </c>
       <c r="O321" t="n">
-        <v>511500</v>
+        <v>455700</v>
       </c>
       <c r="P321" t="n">
         <v>4900</v>
       </c>
       <c r="Q321" t="n">
-        <v>1078000</v>
+        <v>960400</v>
       </c>
     </row>
     <row r="322">
@@ -14711,22 +14711,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M322" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N322" t="n">
         <v>10571</v>
       </c>
       <c r="O322" t="n">
-        <v>306559</v>
+        <v>264275</v>
       </c>
       <c r="P322" t="n">
         <v>18900</v>
       </c>
       <c r="Q322" t="n">
-        <v>548100</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="323">
@@ -14855,10 +14855,10 @@
         <v>143</v>
       </c>
       <c r="N325" t="n">
-        <v>16058</v>
+        <v>16069.364472753</v>
       </c>
       <c r="O325" t="n">
-        <v>2296294</v>
+        <v>2297919.119603679</v>
       </c>
       <c r="P325" t="n">
         <v>25900</v>
@@ -16563,22 +16563,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N362" t="n">
         <v>10411</v>
       </c>
       <c r="O362" t="n">
-        <v>166576</v>
+        <v>156165</v>
       </c>
       <c r="P362" t="n">
         <v>16900</v>
       </c>
       <c r="Q362" t="n">
-        <v>270400</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="363">
@@ -16655,22 +16655,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M364" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N364" t="n">
         <v>5858</v>
       </c>
       <c r="O364" t="n">
-        <v>134734</v>
+        <v>123018</v>
       </c>
       <c r="P364" t="n">
         <v>9500</v>
       </c>
       <c r="Q364" t="n">
-        <v>218500</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="365">
@@ -17355,10 +17355,10 @@
         <v>172</v>
       </c>
       <c r="N379" t="n">
-        <v>9178</v>
+        <v>9197.9305103149</v>
       </c>
       <c r="O379" t="n">
-        <v>1578616</v>
+        <v>1582044.047774163</v>
       </c>
       <c r="P379" t="n">
         <v>14900</v>
@@ -17493,10 +17493,10 @@
         <v>52</v>
       </c>
       <c r="N382" t="n">
-        <v>13922</v>
+        <v>13973.183823529</v>
       </c>
       <c r="O382" t="n">
-        <v>723944</v>
+        <v>726605.558823508</v>
       </c>
       <c r="P382" t="n">
         <v>22900</v>
@@ -17539,10 +17539,10 @@
         <v>26</v>
       </c>
       <c r="N383" t="n">
-        <v>16285.911111111</v>
+        <v>16489.485</v>
       </c>
       <c r="O383" t="n">
-        <v>423433.688888886</v>
+        <v>428726.61</v>
       </c>
       <c r="P383" t="n">
         <v>29900</v>
@@ -17677,10 +17677,10 @@
         <v>165</v>
       </c>
       <c r="N386" t="n">
-        <v>4907.8219300912</v>
+        <v>4907.8219330289</v>
       </c>
       <c r="O386" t="n">
-        <v>809790.6184650479</v>
+        <v>809790.6189497686</v>
       </c>
       <c r="P386" t="n">
         <v>8200</v>
@@ -17809,22 +17809,22 @@
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M389" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N389" t="n">
-        <v>76839</v>
+        <v>77344.519736842</v>
       </c>
       <c r="O389" t="n">
-        <v>768390</v>
+        <v>618756.157894736</v>
       </c>
       <c r="P389" t="n">
         <v>122900</v>
       </c>
       <c r="Q389" t="n">
-        <v>1229000</v>
+        <v>983200</v>
       </c>
     </row>
     <row r="390">
@@ -17855,22 +17855,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M390" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N390" t="n">
         <v>52443</v>
       </c>
       <c r="O390" t="n">
-        <v>1835505</v>
+        <v>1730619</v>
       </c>
       <c r="P390" t="n">
         <v>83900</v>
       </c>
       <c r="Q390" t="n">
-        <v>2936500</v>
+        <v>2768700</v>
       </c>
     </row>
     <row r="391">
@@ -17907,10 +17907,10 @@
         <v>289</v>
       </c>
       <c r="N391" t="n">
-        <v>3903.7359183673</v>
+        <v>3903.7359649123</v>
       </c>
       <c r="O391" t="n">
-        <v>1128179.68040815</v>
+        <v>1128179.693859655</v>
       </c>
       <c r="P391" t="n">
         <v>7500</v>
@@ -17994,10 +17994,10 @@
         <v>18</v>
       </c>
       <c r="N393" t="n">
-        <v>12113</v>
+        <v>12928.298076923</v>
       </c>
       <c r="O393" t="n">
-        <v>218034</v>
+        <v>232709.365384614</v>
       </c>
       <c r="P393" t="n">
         <v>19900</v>
@@ -18914,10 +18914,10 @@
         <v>54</v>
       </c>
       <c r="N413" t="n">
-        <v>17992</v>
+        <v>18015.037131882</v>
       </c>
       <c r="O413" t="n">
-        <v>971568</v>
+        <v>972812.0051216279</v>
       </c>
       <c r="P413" t="n">
         <v>28900</v>
@@ -19006,10 +19006,10 @@
         <v>292</v>
       </c>
       <c r="N415" t="n">
-        <v>17075.989524793</v>
+        <v>17075.989524138</v>
       </c>
       <c r="O415" t="n">
-        <v>4986188.941239556</v>
+        <v>4986188.941048296</v>
       </c>
       <c r="P415" t="n">
         <v>27500</v>
@@ -19504,22 +19504,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M426" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N426" t="n">
-        <v>8700</v>
+        <v>8709.5604395604</v>
       </c>
       <c r="O426" t="n">
-        <v>469800</v>
+        <v>444187.5824175804</v>
       </c>
       <c r="P426" t="n">
         <v>14900</v>
       </c>
       <c r="Q426" t="n">
-        <v>804600</v>
+        <v>759900</v>
       </c>
     </row>
     <row r="427">
@@ -19872,22 +19872,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M434" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N434" t="n">
         <v>21762</v>
       </c>
       <c r="O434" t="n">
-        <v>457002</v>
+        <v>413478</v>
       </c>
       <c r="P434" t="n">
         <v>35900</v>
       </c>
       <c r="Q434" t="n">
-        <v>753900</v>
+        <v>682100</v>
       </c>
     </row>
     <row r="435">
@@ -19964,22 +19964,22 @@
         <v>0</v>
       </c>
       <c r="L436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M436" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N436" t="n">
         <v>15472</v>
       </c>
       <c r="O436" t="n">
-        <v>247552</v>
+        <v>216608</v>
       </c>
       <c r="P436" t="n">
         <v>25900</v>
       </c>
       <c r="Q436" t="n">
-        <v>414400</v>
+        <v>362600</v>
       </c>
     </row>
     <row r="437">
@@ -20200,10 +20200,10 @@
         <v>1320</v>
       </c>
       <c r="N441" t="n">
-        <v>1516.0388131508</v>
+        <v>1516.0388129219</v>
       </c>
       <c r="O441" t="n">
-        <v>2001171.233359056</v>
+        <v>2001171.233056908</v>
       </c>
       <c r="P441" t="n">
         <v>2300</v>
@@ -20292,10 +20292,10 @@
         <v>8</v>
       </c>
       <c r="N443" t="n">
-        <v>4248.6195698925</v>
+        <v>4248.6196402878</v>
       </c>
       <c r="O443" t="n">
-        <v>33988.95655914</v>
+        <v>33988.9571223024</v>
       </c>
       <c r="P443" t="n">
         <v>5900</v>
@@ -20338,10 +20338,10 @@
         <v>120</v>
       </c>
       <c r="N444" t="n">
-        <v>2458.5134514107</v>
+        <v>2458.5134452463</v>
       </c>
       <c r="O444" t="n">
-        <v>295021.614169284</v>
+        <v>295021.613429556</v>
       </c>
       <c r="P444" t="n">
         <v>3500</v>
@@ -20430,10 +20430,10 @@
         <v>264</v>
       </c>
       <c r="N446" t="n">
-        <v>2079.3842209265</v>
+        <v>2079.3842077922</v>
       </c>
       <c r="O446" t="n">
-        <v>548957.434324596</v>
+        <v>548957.4308571408</v>
       </c>
       <c r="P446" t="n">
         <v>2900</v>
@@ -20470,22 +20470,22 @@
         <v>0</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M447" t="n">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="N447" t="n">
         <v>1803.0149882284</v>
       </c>
       <c r="O447" t="n">
-        <v>475995.9568922976</v>
+        <v>346178.8777398528</v>
       </c>
       <c r="P447" t="n">
         <v>2500</v>
       </c>
       <c r="Q447" t="n">
-        <v>660000</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="448">
@@ -20522,10 +20522,10 @@
         <v>216</v>
       </c>
       <c r="N448" t="n">
-        <v>3306.5954545455</v>
+        <v>3306.595443038</v>
       </c>
       <c r="O448" t="n">
-        <v>714224.6181818281</v>
+        <v>714224.6156962081</v>
       </c>
       <c r="P448" t="n">
         <v>4900</v>
@@ -20568,10 +20568,10 @@
         <v>192</v>
       </c>
       <c r="N449" t="n">
-        <v>2122.1641155235</v>
+        <v>2122.1641066586</v>
       </c>
       <c r="O449" t="n">
-        <v>407455.510180512</v>
+        <v>407455.5084784512</v>
       </c>
       <c r="P449" t="n">
         <v>2900</v>
@@ -20614,10 +20614,10 @@
         <v>216</v>
       </c>
       <c r="N450" t="n">
-        <v>2108.7897869955</v>
+        <v>2108.7898867497</v>
       </c>
       <c r="O450" t="n">
-        <v>455498.593991028</v>
+        <v>455498.6155379352</v>
       </c>
       <c r="P450" t="n">
         <v>2900</v>
@@ -20660,10 +20660,10 @@
         <v>144</v>
       </c>
       <c r="N451" t="n">
-        <v>2056.0838880663</v>
+        <v>2056.692917654</v>
       </c>
       <c r="O451" t="n">
-        <v>296076.0798815472</v>
+        <v>296163.780142176</v>
       </c>
       <c r="P451" t="n">
         <v>2900</v>
@@ -20706,10 +20706,10 @@
         <v>216</v>
       </c>
       <c r="N452" t="n">
-        <v>3224.5679626335</v>
+        <v>3224.5679768271</v>
       </c>
       <c r="O452" t="n">
-        <v>696506.6799288359</v>
+        <v>696506.6829946537</v>
       </c>
       <c r="P452" t="n">
         <v>4500</v>
@@ -20752,10 +20752,10 @@
         <v>360</v>
       </c>
       <c r="N453" t="n">
-        <v>1655.931342723</v>
+        <v>1655.9313291536</v>
       </c>
       <c r="O453" t="n">
-        <v>596135.28338028</v>
+        <v>596135.278495296</v>
       </c>
       <c r="P453" t="n">
         <v>2500</v>
@@ -20976,22 +20976,22 @@
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M458" t="n">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="N458" t="n">
-        <v>1592.2747647377</v>
+        <v>1592.2748727876</v>
       </c>
       <c r="O458" t="n">
-        <v>687862.6983666865</v>
+        <v>636909.94911504</v>
       </c>
       <c r="P458" t="n">
         <v>2500</v>
       </c>
       <c r="Q458" t="n">
-        <v>1080000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="459">
@@ -21107,22 +21107,22 @@
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M461" t="n">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="N461" t="n">
-        <v>2311.9267563291</v>
+        <v>2311.9264781906</v>
       </c>
       <c r="O461" t="n">
-        <v>305174.3318354412</v>
+        <v>27743.1177382872</v>
       </c>
       <c r="P461" t="n">
         <v>3500</v>
       </c>
       <c r="Q461" t="n">
-        <v>462000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="462">
@@ -21159,10 +21159,10 @@
         <v>48</v>
       </c>
       <c r="N462" t="n">
-        <v>1906.1867602592</v>
+        <v>1906.1867105263</v>
       </c>
       <c r="O462" t="n">
-        <v>91496.96449244159</v>
+        <v>91496.9621052624</v>
       </c>
       <c r="P462" t="n">
         <v>2900</v>
@@ -21205,10 +21205,10 @@
         <v>120</v>
       </c>
       <c r="N463" t="n">
-        <v>3033.7318786693</v>
+        <v>3033.7312929293</v>
       </c>
       <c r="O463" t="n">
-        <v>364047.825440316</v>
+        <v>364047.755151516</v>
       </c>
       <c r="P463" t="n">
         <v>4500</v>
@@ -21251,10 +21251,10 @@
         <v>408</v>
       </c>
       <c r="N464" t="n">
-        <v>2060.160784</v>
+        <v>2060.1607096774</v>
       </c>
       <c r="O464" t="n">
-        <v>840545.599872</v>
+        <v>840545.5695483793</v>
       </c>
       <c r="P464" t="n">
         <v>2900</v>
@@ -21297,10 +21297,10 @@
         <v>72</v>
       </c>
       <c r="N465" t="n">
-        <v>1668.6157419355</v>
+        <v>1668.6158441558</v>
       </c>
       <c r="O465" t="n">
-        <v>120140.333419356</v>
+        <v>120140.3407792176</v>
       </c>
       <c r="P465" t="n">
         <v>2500</v>
@@ -21343,10 +21343,10 @@
         <v>72</v>
       </c>
       <c r="N466" t="n">
-        <v>2546.9851864407</v>
+        <v>2546.9851535836</v>
       </c>
       <c r="O466" t="n">
-        <v>183382.9334237304</v>
+        <v>183382.9310580192</v>
       </c>
       <c r="P466" t="n">
         <v>3900</v>
@@ -21383,22 +21383,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M467" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="N467" t="n">
-        <v>1259.2744140796</v>
+        <v>1259.2744160105</v>
       </c>
       <c r="O467" t="n">
-        <v>1133346.97267164</v>
+        <v>1007419.5328084</v>
       </c>
       <c r="P467" t="n">
         <v>1900</v>
       </c>
       <c r="Q467" t="n">
-        <v>1710000</v>
+        <v>1520000</v>
       </c>
     </row>
     <row r="468">
@@ -21476,10 +21476,10 @@
         <v>97</v>
       </c>
       <c r="N469" t="n">
-        <v>2842.2737931034</v>
+        <v>2842.2737735849</v>
       </c>
       <c r="O469" t="n">
-        <v>275700.5579310298</v>
+        <v>275700.5560377353</v>
       </c>
       <c r="P469" t="n">
         <v>4900</v>
@@ -21522,10 +21522,10 @@
         <v>72</v>
       </c>
       <c r="N470" t="n">
-        <v>2556.7446648794</v>
+        <v>2556.7449856734</v>
       </c>
       <c r="O470" t="n">
-        <v>184085.6158713168</v>
+        <v>184085.6389684848</v>
       </c>
       <c r="P470" t="n">
         <v>3900</v>
@@ -21655,22 +21655,22 @@
         <v>0</v>
       </c>
       <c r="L473" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M473" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N473" t="n">
         <v>18491</v>
       </c>
       <c r="O473" t="n">
-        <v>1719663</v>
+        <v>1608717</v>
       </c>
       <c r="P473" t="n">
         <v>13500</v>
       </c>
       <c r="Q473" t="n">
-        <v>1255500</v>
+        <v>1174500</v>
       </c>
     </row>
     <row r="474">
@@ -22115,22 +22115,22 @@
         <v>0</v>
       </c>
       <c r="L483" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M483" t="n">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="N483" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O483" t="n">
-        <v>8193968.079999999</v>
+        <v>8167131.939999999</v>
       </c>
       <c r="P483" t="n">
         <v>14900</v>
       </c>
       <c r="Q483" t="n">
-        <v>13648400</v>
+        <v>13603700</v>
       </c>
     </row>
     <row r="484">
@@ -22309,10 +22309,10 @@
         <v>360</v>
       </c>
       <c r="N487" t="n">
-        <v>1530.4499204455</v>
+        <v>1530.4499204138</v>
       </c>
       <c r="O487" t="n">
-        <v>550961.9713603801</v>
+        <v>550961.971348968</v>
       </c>
       <c r="P487" t="n">
         <v>2600</v>
@@ -22678,10 +22678,10 @@
         <v>20</v>
       </c>
       <c r="N495" t="n">
-        <v>2357.74</v>
+        <v>2458.0693617021</v>
       </c>
       <c r="O495" t="n">
-        <v>47154.8</v>
+        <v>49161.38723404201</v>
       </c>
       <c r="P495" t="n">
         <v>3000</v>
@@ -22768,10 +22768,10 @@
         <v>306</v>
       </c>
       <c r="N497" t="n">
-        <v>1690.8700088574</v>
+        <v>1690.8700089286</v>
       </c>
       <c r="O497" t="n">
-        <v>517406.2227103644</v>
+        <v>517406.2227321516</v>
       </c>
       <c r="P497" t="n">
         <v>3000</v>
@@ -22915,10 +22915,10 @@
         <v>3</v>
       </c>
       <c r="N500" t="n">
-        <v>2270.3210752688</v>
+        <v>2270.3211494253</v>
       </c>
       <c r="O500" t="n">
-        <v>6810.9632258064</v>
+        <v>6810.9634482759</v>
       </c>
       <c r="P500" t="n">
         <v>3900</v>
@@ -23649,22 +23649,22 @@
         <v>0</v>
       </c>
       <c r="L516" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M516" t="n">
-        <v>1037</v>
+        <v>749</v>
       </c>
       <c r="N516" t="n">
-        <v>517.28764753291</v>
+        <v>517.28774146762</v>
       </c>
       <c r="O516" t="n">
-        <v>536427.2904916276</v>
+        <v>387448.5183592474</v>
       </c>
       <c r="P516" t="n">
         <v>900</v>
       </c>
       <c r="Q516" t="n">
-        <v>933300</v>
+        <v>674100</v>
       </c>
     </row>
     <row r="517">
@@ -24078,10 +24078,10 @@
         <v>757</v>
       </c>
       <c r="N525" t="n">
-        <v>3110.8431677619</v>
+        <v>3110.8430699863</v>
       </c>
       <c r="O525" t="n">
-        <v>2354908.277995758</v>
+        <v>2354908.203979629</v>
       </c>
       <c r="P525" t="n">
         <v>4500</v>
@@ -24250,22 +24250,22 @@
         <v>0</v>
       </c>
       <c r="L529" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M529" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="N529" t="n">
         <v>2030.02</v>
       </c>
       <c r="O529" t="n">
-        <v>416154.1</v>
+        <v>385703.8</v>
       </c>
       <c r="P529" t="n">
         <v>3600</v>
       </c>
       <c r="Q529" t="n">
-        <v>738000</v>
+        <v>684000</v>
       </c>
     </row>
     <row r="530">
@@ -24296,22 +24296,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M530" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N530" t="n">
         <v>7120</v>
       </c>
       <c r="O530" t="n">
-        <v>113920</v>
+        <v>92560</v>
       </c>
       <c r="P530" t="n">
         <v>8900</v>
       </c>
       <c r="Q530" t="n">
-        <v>142400</v>
+        <v>115700</v>
       </c>
     </row>
     <row r="531">
@@ -24523,22 +24523,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M535" t="n">
-        <v>20378</v>
+        <v>20090</v>
       </c>
       <c r="N535" t="n">
-        <v>703.79542528945</v>
+        <v>703.79541200942</v>
       </c>
       <c r="O535" t="n">
-        <v>14341943.17654841</v>
+        <v>14139249.82726925</v>
       </c>
       <c r="P535" t="n">
         <v>900</v>
       </c>
       <c r="Q535" t="n">
-        <v>18340200</v>
+        <v>18081000</v>
       </c>
     </row>
     <row r="536">
@@ -24578,10 +24578,10 @@
         <v>55</v>
       </c>
       <c r="N536" t="n">
-        <v>3182.2510928962</v>
+        <v>3182.2511009174</v>
       </c>
       <c r="O536" t="n">
-        <v>175023.810109291</v>
+        <v>175023.810550457</v>
       </c>
       <c r="P536" t="n">
         <v>6900</v>
@@ -25425,10 +25425,10 @@
         <v>168</v>
       </c>
       <c r="N554" t="n">
-        <v>2098.4048459384</v>
+        <v>2098.4048595506</v>
       </c>
       <c r="O554" t="n">
-        <v>352532.0141176512</v>
+        <v>352532.0164045008</v>
       </c>
       <c r="P554" t="n">
         <v>9500</v>
@@ -25517,22 +25517,22 @@
         <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M556" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N556" t="n">
         <v>2832.1946575342</v>
       </c>
       <c r="O556" t="n">
-        <v>99126.813013697</v>
+        <v>93462.4236986286</v>
       </c>
       <c r="P556" t="n">
         <v>12900</v>
       </c>
       <c r="Q556" t="n">
-        <v>451500</v>
+        <v>425700</v>
       </c>
     </row>
     <row r="557">
@@ -26385,22 +26385,22 @@
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M574" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N574" t="n">
         <v>10296.29</v>
       </c>
       <c r="O574" t="n">
-        <v>195629.51</v>
+        <v>175036.93</v>
       </c>
       <c r="P574" t="n">
         <v>16900</v>
       </c>
       <c r="Q574" t="n">
-        <v>321100</v>
+        <v>287300</v>
       </c>
     </row>
     <row r="575">
@@ -26581,22 +26581,22 @@
         <v>0</v>
       </c>
       <c r="L578" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M578" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N578" t="n">
-        <v>2992.5684269663</v>
+        <v>2992.5687209302</v>
       </c>
       <c r="O578" t="n">
-        <v>110725.0317977531</v>
+        <v>104739.905232557</v>
       </c>
       <c r="P578" t="n">
         <v>6000</v>
       </c>
       <c r="Q578" t="n">
-        <v>222000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="579">
@@ -27003,22 +27003,22 @@
         <v>0</v>
       </c>
       <c r="L587" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M587" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N587" t="n">
         <v>3067.0905341246</v>
       </c>
       <c r="O587" t="n">
-        <v>349648.3208902044</v>
+        <v>343514.1398219552</v>
       </c>
       <c r="P587" t="n">
         <v>7200</v>
       </c>
       <c r="Q587" t="n">
-        <v>820800</v>
+        <v>806400</v>
       </c>
     </row>
     <row r="588">
@@ -27868,22 +27868,22 @@
         <v>0</v>
       </c>
       <c r="L605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M605" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N605" t="n">
         <v>10737.526727273</v>
       </c>
       <c r="O605" t="n">
-        <v>268438.168181825</v>
+        <v>257700.641454552</v>
       </c>
       <c r="P605" t="n">
         <v>18900</v>
       </c>
       <c r="Q605" t="n">
-        <v>472500</v>
+        <v>453600</v>
       </c>
     </row>
     <row r="606">
@@ -28761,22 +28761,22 @@
         <v>0</v>
       </c>
       <c r="L624" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M624" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N624" t="n">
         <v>14327.781538462</v>
       </c>
       <c r="O624" t="n">
-        <v>57311.126153848</v>
+        <v>0</v>
       </c>
       <c r="P624" t="n">
         <v>29900</v>
       </c>
       <c r="Q624" t="n">
-        <v>119600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="625">
@@ -29338,10 +29338,10 @@
         <v>648</v>
       </c>
       <c r="N636" t="n">
-        <v>665.3233262441501</v>
+        <v>665.32333760137</v>
       </c>
       <c r="O636" t="n">
-        <v>431129.5154062092</v>
+        <v>431129.5227656877</v>
       </c>
       <c r="P636" t="n">
         <v>2900</v>
@@ -29776,10 +29776,10 @@
         <v>153</v>
       </c>
       <c r="N645" t="n">
-        <v>315.02675450763</v>
+        <v>315.02678272981</v>
       </c>
       <c r="O645" t="n">
-        <v>48199.09343966739</v>
+        <v>48199.09775766093</v>
       </c>
       <c r="P645" t="n">
         <v>2200</v>
@@ -30326,22 +30326,22 @@
         <v>0</v>
       </c>
       <c r="L658" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M658" t="n">
-        <v>861</v>
+        <v>831</v>
       </c>
       <c r="N658" t="n">
         <v>3181.9</v>
       </c>
       <c r="O658" t="n">
-        <v>2739615.9</v>
+        <v>2644158.9</v>
       </c>
       <c r="P658" t="n">
         <v>5100</v>
       </c>
       <c r="Q658" t="n">
-        <v>4391100</v>
+        <v>4238100</v>
       </c>
     </row>
     <row r="659">
@@ -30909,10 +30909,10 @@
         <v>93</v>
       </c>
       <c r="N671" t="n">
-        <v>4985.4046332046</v>
+        <v>5004.7279069767</v>
       </c>
       <c r="O671" t="n">
-        <v>463642.6308880278</v>
+        <v>465439.6953488331</v>
       </c>
       <c r="P671" t="n">
         <v>7900</v>
@@ -31011,10 +31011,10 @@
         <v>310</v>
       </c>
       <c r="N673" t="n">
-        <v>1757.3205179283</v>
+        <v>1757.3205295316</v>
       </c>
       <c r="O673" t="n">
-        <v>544769.360557773</v>
+        <v>544769.364154796</v>
       </c>
       <c r="P673" t="n">
         <v>2000</v>
@@ -31149,10 +31149,10 @@
         <v>4600</v>
       </c>
       <c r="N676" t="n">
-        <v>220.00852554547</v>
+        <v>220.00820587826</v>
       </c>
       <c r="O676" t="n">
-        <v>1012039.217509162</v>
+        <v>1012037.747039996</v>
       </c>
       <c r="P676" t="n">
         <v>260</v>
@@ -31419,22 +31419,22 @@
         <v>0</v>
       </c>
       <c r="L682" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M682" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N682" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O682" t="n">
-        <v>213580.18</v>
+        <v>194163.8</v>
       </c>
       <c r="P682" t="n">
         <v>10200</v>
       </c>
       <c r="Q682" t="n">
-        <v>224400</v>
+        <v>204000</v>
       </c>
     </row>
     <row r="683">
@@ -31936,10 +31936,10 @@
         <v>200</v>
       </c>
       <c r="N693" t="n">
-        <v>1319.360872093</v>
+        <v>1319.3608797654</v>
       </c>
       <c r="O693" t="n">
-        <v>263872.1744186</v>
+        <v>263872.17595308</v>
       </c>
       <c r="P693" t="n">
         <v>3500</v>
@@ -32084,10 +32084,10 @@
         <v>18</v>
       </c>
       <c r="N696" t="n">
-        <v>2432.1340350877</v>
+        <v>2432.1341071429</v>
       </c>
       <c r="O696" t="n">
-        <v>43778.4126315786</v>
+        <v>43778.4139285722</v>
       </c>
       <c r="P696" t="n">
         <v>4500</v>
@@ -32216,22 +32216,22 @@
         <v>0</v>
       </c>
       <c r="L699" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M699" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="N699" t="n">
         <v>2058.92</v>
       </c>
       <c r="O699" t="n">
-        <v>391194.8</v>
+        <v>366487.76</v>
       </c>
       <c r="P699" t="n">
         <v>2500</v>
       </c>
       <c r="Q699" t="n">
-        <v>475000</v>
+        <v>445000</v>
       </c>
     </row>
     <row r="700">
@@ -32262,22 +32262,22 @@
         <v>0</v>
       </c>
       <c r="L700" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M700" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="N700" t="n">
         <v>3306.0098310139</v>
       </c>
       <c r="O700" t="n">
-        <v>429781.278031807</v>
+        <v>380191.1305665985</v>
       </c>
       <c r="P700" t="n">
         <v>4200</v>
       </c>
       <c r="Q700" t="n">
-        <v>546000</v>
+        <v>483000</v>
       </c>
     </row>
     <row r="701">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>147</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3041548631</v>
+        <v>1811.3043052838</v>
       </c>
       <c r="O6" t="n">
-        <v>266261.7107648757</v>
+        <v>266261.7328767186</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7465109371</v>
+        <v>3376.7465014893</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.915668396</v>
+        <v>2985043.907316541</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1354,10 +1354,10 @@
         <v>92</v>
       </c>
       <c r="N24" t="n">
-        <v>2413.0010330579</v>
+        <v>2413.001059322</v>
       </c>
       <c r="O24" t="n">
-        <v>221996.0950413268</v>
+        <v>221996.097457624</v>
       </c>
       <c r="P24" t="n">
         <v>4700</v>
@@ -1705,10 +1705,10 @@
         <v>23</v>
       </c>
       <c r="N33" t="n">
-        <v>14857.623171806</v>
+        <v>14857.623185841</v>
       </c>
       <c r="O33" t="n">
-        <v>341725.332951538</v>
+        <v>341725.333274343</v>
       </c>
       <c r="P33" t="n">
         <v>34900</v>
@@ -1920,10 +1920,10 @@
         <v>18</v>
       </c>
       <c r="N38" t="n">
-        <v>15711.966106557</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O38" t="n">
-        <v>282815.389918026</v>
+        <v>282815.389045638</v>
       </c>
       <c r="P38" t="n">
         <v>28500</v>
@@ -2170,10 +2170,10 @@
         <v>8</v>
       </c>
       <c r="N44" t="n">
-        <v>56906.800571429</v>
+        <v>56906.801935484</v>
       </c>
       <c r="O44" t="n">
-        <v>455254.404571432</v>
+        <v>455254.415483872</v>
       </c>
       <c r="P44" t="n">
         <v>95900</v>
@@ -2217,10 +2217,10 @@
         <v>46</v>
       </c>
       <c r="N45" t="n">
-        <v>141416.88453074</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O45" t="n">
-        <v>6505176.68841404</v>
+        <v>6505176.689090701</v>
       </c>
       <c r="P45" t="n">
         <v>251900</v>
@@ -2611,10 +2611,10 @@
         <v>98</v>
       </c>
       <c r="N54" t="n">
-        <v>538.40033834586</v>
+        <v>542.47912878788</v>
       </c>
       <c r="O54" t="n">
-        <v>52763.23315789428</v>
+        <v>53162.95462121224</v>
       </c>
       <c r="P54" t="n">
         <v>6800</v>
@@ -2657,10 +2657,10 @@
         <v>14</v>
       </c>
       <c r="N55" t="n">
-        <v>28.165601851852</v>
+        <v>28.165539906103</v>
       </c>
       <c r="O55" t="n">
-        <v>394.318425925928</v>
+        <v>394.317558685442</v>
       </c>
       <c r="P55" t="n">
         <v>6800</v>
@@ -3129,10 +3129,10 @@
         <v>228</v>
       </c>
       <c r="N66" t="n">
-        <v>4937.3101603499</v>
+        <v>4937.3101608187</v>
       </c>
       <c r="O66" t="n">
-        <v>1125706.716559777</v>
+        <v>1125706.716666664</v>
       </c>
       <c r="P66" t="n">
         <v>7500</v>
@@ -3391,10 +3391,10 @@
         <v>1727</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0535004591</v>
+        <v>1098.0541801698</v>
       </c>
       <c r="O72" t="n">
-        <v>1896338.395292866</v>
+        <v>1896339.569153245</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -3431,22 +3431,22 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N73" t="n">
         <v>6295.2</v>
       </c>
       <c r="O73" t="n">
-        <v>371416.8</v>
+        <v>358826.4</v>
       </c>
       <c r="P73" t="n">
         <v>10500</v>
       </c>
       <c r="Q73" t="n">
-        <v>619500</v>
+        <v>598500</v>
       </c>
     </row>
     <row r="74">
@@ -3749,22 +3749,22 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M80" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
         <v>13593.35</v>
       </c>
       <c r="O80" t="n">
-        <v>299053.7</v>
+        <v>13593.35</v>
       </c>
       <c r="P80" t="n">
         <v>25500</v>
       </c>
       <c r="Q80" t="n">
-        <v>561000</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="81">
@@ -4324,10 +4324,10 @@
         <v>771</v>
       </c>
       <c r="N93" t="n">
-        <v>2582.2560562265</v>
+        <v>2582.2560231583</v>
       </c>
       <c r="O93" t="n">
-        <v>1990919.419350631</v>
+        <v>1990919.39385505</v>
       </c>
       <c r="P93" t="n">
         <v>4500</v>
@@ -4462,10 +4462,10 @@
         <v>720</v>
       </c>
       <c r="N96" t="n">
-        <v>5216.8959875629</v>
+        <v>5216.8959762435</v>
       </c>
       <c r="O96" t="n">
-        <v>3756165.111045288</v>
+        <v>3756165.10289532</v>
       </c>
       <c r="P96" t="n">
         <v>8500</v>
@@ -4693,10 +4693,10 @@
         <v>3199</v>
       </c>
       <c r="N101" t="n">
-        <v>3158.860813875</v>
+        <v>3158.8608143857</v>
       </c>
       <c r="O101" t="n">
-        <v>10105195.74358612</v>
+        <v>10105195.74521985</v>
       </c>
       <c r="P101" t="n">
         <v>5600</v>
@@ -4968,10 +4968,10 @@
         <v>259</v>
       </c>
       <c r="N107" t="n">
-        <v>2694.8234682861</v>
+        <v>2694.8234624043</v>
       </c>
       <c r="O107" t="n">
-        <v>697959.2782860999</v>
+        <v>697959.2767627137</v>
       </c>
       <c r="P107" t="n">
         <v>4900</v>
@@ -5513,10 +5513,10 @@
         <v>318</v>
       </c>
       <c r="N119" t="n">
-        <v>4890.9300461095</v>
+        <v>4890.9300462963</v>
       </c>
       <c r="O119" t="n">
-        <v>1555315.754662821</v>
+        <v>1555315.754722223</v>
       </c>
       <c r="P119" t="n">
         <v>8200</v>
@@ -5553,22 +5553,22 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M120" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N120" t="n">
         <v>5613.75</v>
       </c>
       <c r="O120" t="n">
-        <v>566988.75</v>
+        <v>550147.5</v>
       </c>
       <c r="P120" t="n">
         <v>7900</v>
       </c>
       <c r="Q120" t="n">
-        <v>797900</v>
+        <v>774200</v>
       </c>
     </row>
     <row r="121">
@@ -5954,25 +5954,25 @@
         <v>5</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M129" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N129" t="n">
         <v>10716.34</v>
       </c>
       <c r="O129" t="n">
-        <v>53581.7</v>
+        <v>535817</v>
       </c>
       <c r="P129" t="n">
         <v>39000</v>
       </c>
       <c r="Q129" t="n">
-        <v>195000</v>
+        <v>1950000</v>
       </c>
     </row>
     <row r="130">
@@ -6012,10 +6012,10 @@
         <v>288</v>
       </c>
       <c r="N130" t="n">
-        <v>3594.254188862</v>
+        <v>3594.2541747573</v>
       </c>
       <c r="O130" t="n">
-        <v>1035145.206392256</v>
+        <v>1035145.202330102</v>
       </c>
       <c r="P130" t="n">
         <v>6500</v>
@@ -6055,22 +6055,22 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M131" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
         <v>489.88</v>
       </c>
       <c r="O131" t="n">
-        <v>8327.959999999999</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
         <v>700</v>
       </c>
       <c r="Q131" t="n">
-        <v>11900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -6234,22 +6234,22 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M135" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N135" t="n">
         <v>8154</v>
       </c>
       <c r="O135" t="n">
-        <v>3408372</v>
+        <v>3383910</v>
       </c>
       <c r="P135" t="n">
         <v>13500</v>
       </c>
       <c r="Q135" t="n">
-        <v>5643000</v>
+        <v>5602500</v>
       </c>
     </row>
     <row r="136">
@@ -6286,10 +6286,10 @@
         <v>308</v>
       </c>
       <c r="N136" t="n">
-        <v>14822.378867257</v>
+        <v>14822.378864577</v>
       </c>
       <c r="O136" t="n">
-        <v>4565292.691115156</v>
+        <v>4565292.690289716</v>
       </c>
       <c r="P136" t="n">
         <v>24900</v>
@@ -6373,22 +6373,22 @@
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M138" t="n">
-        <v>1986</v>
+        <v>1890</v>
       </c>
       <c r="N138" t="n">
         <v>2090.85</v>
       </c>
       <c r="O138" t="n">
-        <v>4152428.1</v>
+        <v>3951706.5</v>
       </c>
       <c r="P138" t="n">
         <v>2900</v>
       </c>
       <c r="Q138" t="n">
-        <v>5759400</v>
+        <v>5481000</v>
       </c>
     </row>
     <row r="139">
@@ -6695,10 +6695,10 @@
         <v>43</v>
       </c>
       <c r="N145" t="n">
-        <v>12267.650842105</v>
+        <v>12267.650645161</v>
       </c>
       <c r="O145" t="n">
-        <v>527508.986210515</v>
+        <v>527508.9777419231</v>
       </c>
       <c r="P145" t="n">
         <v>19900</v>
@@ -6956,22 +6956,22 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M151" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="N151" t="n">
         <v>4193.85</v>
       </c>
       <c r="O151" t="n">
-        <v>176141.7</v>
+        <v>134203.2</v>
       </c>
       <c r="P151" t="n">
         <v>7500</v>
       </c>
       <c r="Q151" t="n">
-        <v>315000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="152">
@@ -7005,22 +7005,22 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M152" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="N152" t="n">
-        <v>3041.6600125549</v>
+        <v>3041.6600125945</v>
       </c>
       <c r="O152" t="n">
-        <v>669165.2027620779</v>
+        <v>638748.602644845</v>
       </c>
       <c r="P152" t="n">
         <v>5500</v>
       </c>
       <c r="Q152" t="n">
-        <v>1210000</v>
+        <v>1155000</v>
       </c>
     </row>
     <row r="153">
@@ -7139,10 +7139,10 @@
         <v>1945</v>
       </c>
       <c r="N155" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="O155" t="n">
-        <v>8503949.980039112</v>
+        <v>8503949.980582351</v>
       </c>
       <c r="P155" t="n">
         <v>7500</v>
@@ -7229,10 +7229,10 @@
         <v>498</v>
       </c>
       <c r="N157" t="n">
-        <v>1592.5676712942</v>
+        <v>1592.5675881262</v>
       </c>
       <c r="O157" t="n">
-        <v>793098.7003045116</v>
+        <v>793098.6588868476</v>
       </c>
       <c r="P157" t="n">
         <v>3900</v>
@@ -7623,22 +7623,22 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M166" t="n">
-        <v>1678</v>
+        <v>1666</v>
       </c>
       <c r="N166" t="n">
         <v>4648.6</v>
       </c>
       <c r="O166" t="n">
-        <v>7800350.800000001</v>
+        <v>7744567.600000001</v>
       </c>
       <c r="P166" t="n">
         <v>8900</v>
       </c>
       <c r="Q166" t="n">
-        <v>14934200</v>
+        <v>14827400</v>
       </c>
     </row>
     <row r="167">
@@ -7855,10 +7855,10 @@
         <v>2752</v>
       </c>
       <c r="N171" t="n">
-        <v>17472.91</v>
+        <v>17476.031091396</v>
       </c>
       <c r="O171" t="n">
-        <v>48085448.32</v>
+        <v>48094037.56352179</v>
       </c>
       <c r="P171" t="n">
         <v>2900</v>
@@ -8356,10 +8356,10 @@
         <v>82</v>
       </c>
       <c r="N182" t="n">
-        <v>8341.030000000001</v>
+        <v>8367.5094603175</v>
       </c>
       <c r="O182" t="n">
-        <v>683964.4600000001</v>
+        <v>686135.775746035</v>
       </c>
       <c r="P182" t="n">
         <v>13900</v>
@@ -8548,22 +8548,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M186" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="N186" t="n">
         <v>11921.4</v>
       </c>
       <c r="O186" t="n">
-        <v>1692838.8</v>
+        <v>1573624.8</v>
       </c>
       <c r="P186" t="n">
         <v>19900</v>
       </c>
       <c r="Q186" t="n">
-        <v>2825800</v>
+        <v>2626800</v>
       </c>
     </row>
     <row r="187">
@@ -8884,10 +8884,10 @@
         <v>1238</v>
       </c>
       <c r="N193" t="n">
-        <v>1151.3923550423</v>
+        <v>1151.3923553227</v>
       </c>
       <c r="O193" t="n">
-        <v>1425423.735542367</v>
+        <v>1425423.735889503</v>
       </c>
       <c r="P193" t="n">
         <v>1500</v>
@@ -8968,22 +8968,22 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N195" t="n">
         <v>9903</v>
       </c>
       <c r="O195" t="n">
-        <v>2020212</v>
+        <v>2010309</v>
       </c>
       <c r="P195" t="n">
         <v>15900</v>
       </c>
       <c r="Q195" t="n">
-        <v>3243600</v>
+        <v>3227700</v>
       </c>
     </row>
     <row r="196">
@@ -9020,10 +9020,10 @@
         <v>824</v>
       </c>
       <c r="N196" t="n">
-        <v>1630.9230521929</v>
+        <v>1630.9231064431</v>
       </c>
       <c r="O196" t="n">
-        <v>1343880.59500695</v>
+        <v>1343880.639709115</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9112,10 +9112,10 @@
         <v>384</v>
       </c>
       <c r="N198" t="n">
-        <v>1690.6034846029</v>
+        <v>1690.6033768352</v>
       </c>
       <c r="O198" t="n">
-        <v>649191.7380875136</v>
+        <v>649191.6967047168</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9158,10 +9158,10 @@
         <v>2118</v>
       </c>
       <c r="N199" t="n">
-        <v>1550.1930031561</v>
+        <v>1550.1930735465</v>
       </c>
       <c r="O199" t="n">
-        <v>3283308.78068462</v>
+        <v>3283308.929771487</v>
       </c>
       <c r="P199" t="n">
         <v>2500</v>
@@ -9250,10 +9250,10 @@
         <v>454</v>
       </c>
       <c r="N201" t="n">
-        <v>2403.5101337902</v>
+        <v>2403.5102087442</v>
       </c>
       <c r="O201" t="n">
-        <v>1091193.600740751</v>
+        <v>1091193.634769867</v>
       </c>
       <c r="P201" t="n">
         <v>3500</v>
@@ -9296,10 +9296,10 @@
         <v>80</v>
       </c>
       <c r="N202" t="n">
-        <v>2521.5468491124</v>
+        <v>2521.5455211726</v>
       </c>
       <c r="O202" t="n">
-        <v>201723.747928992</v>
+        <v>201723.641693808</v>
       </c>
       <c r="P202" t="n">
         <v>3900</v>
@@ -9331,22 +9331,22 @@
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M203" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="N203" t="n">
         <v>1232.8081659389</v>
       </c>
       <c r="O203" t="n">
-        <v>94926.2287772953</v>
+        <v>80132.5307860285</v>
       </c>
       <c r="P203" t="n">
         <v>2400</v>
       </c>
       <c r="Q203" t="n">
-        <v>184800</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="204">
@@ -10508,10 +10508,10 @@
         <v>19</v>
       </c>
       <c r="N229" t="n">
-        <v>7537.4721167883</v>
+        <v>7537.4721481481</v>
       </c>
       <c r="O229" t="n">
-        <v>143211.9702189777</v>
+        <v>143211.9708148139</v>
       </c>
       <c r="P229" t="n">
         <v>8900</v>
@@ -10794,22 +10794,22 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M236" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="N236" t="n">
         <v>2567</v>
       </c>
       <c r="O236" t="n">
-        <v>277236</v>
+        <v>215628</v>
       </c>
       <c r="P236" t="n">
         <v>4500</v>
       </c>
       <c r="Q236" t="n">
-        <v>486000</v>
+        <v>378000</v>
       </c>
     </row>
     <row r="237">
@@ -11324,22 +11324,22 @@
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M248" t="n">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="N248" t="n">
         <v>3877.89</v>
       </c>
       <c r="O248" t="n">
-        <v>2776569.24</v>
+        <v>2730034.56</v>
       </c>
       <c r="P248" t="n">
         <v>6500</v>
       </c>
       <c r="Q248" t="n">
-        <v>4654000</v>
+        <v>4576000</v>
       </c>
     </row>
     <row r="249">
@@ -11379,10 +11379,10 @@
         <v>125</v>
       </c>
       <c r="N249" t="n">
-        <v>4285.1952479339</v>
+        <v>4285.1952751817</v>
       </c>
       <c r="O249" t="n">
-        <v>535649.4059917375</v>
+        <v>535649.4093977124</v>
       </c>
       <c r="P249" t="n">
         <v>6900</v>
@@ -11632,22 +11632,22 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M255" t="n">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="N255" t="n">
-        <v>4605.2146487985</v>
+        <v>4605.2146574074</v>
       </c>
       <c r="O255" t="n">
-        <v>2611156.705868749</v>
+        <v>2592735.852120366</v>
       </c>
       <c r="P255" t="n">
         <v>7600</v>
       </c>
       <c r="Q255" t="n">
-        <v>4309200</v>
+        <v>4278800</v>
       </c>
     </row>
     <row r="256">
@@ -11765,22 +11765,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M258" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N258" t="n">
         <v>13513.642971014</v>
       </c>
       <c r="O258" t="n">
-        <v>297300.145362308</v>
+        <v>256759.216449266</v>
       </c>
       <c r="P258" t="n">
         <v>21900</v>
       </c>
       <c r="Q258" t="n">
-        <v>481800</v>
+        <v>416100</v>
       </c>
     </row>
     <row r="259">
@@ -11955,10 +11955,10 @@
         <v>94</v>
       </c>
       <c r="N262" t="n">
-        <v>27123.765250464</v>
+        <v>27123.765241636</v>
       </c>
       <c r="O262" t="n">
-        <v>2549633.933543616</v>
+        <v>2549633.932713784</v>
       </c>
       <c r="P262" t="n">
         <v>44500</v>
@@ -12129,10 +12129,10 @@
         <v>72</v>
       </c>
       <c r="N266" t="n">
-        <v>8332.779624999999</v>
+        <v>8332.7796240601</v>
       </c>
       <c r="O266" t="n">
-        <v>599960.1329999999</v>
+        <v>599960.1329323272</v>
       </c>
       <c r="P266" t="n">
         <v>14900</v>
@@ -12221,10 +12221,10 @@
         <v>599</v>
       </c>
       <c r="N268" t="n">
-        <v>1560.9989986027</v>
+        <v>1560.9991607397</v>
       </c>
       <c r="O268" t="n">
-        <v>935038.4001630173</v>
+        <v>935038.4972830804</v>
       </c>
       <c r="P268" t="n">
         <v>2900</v>
@@ -12359,10 +12359,10 @@
         <v>188</v>
       </c>
       <c r="N271" t="n">
-        <v>7969.950164794</v>
+        <v>7969.9501649175</v>
       </c>
       <c r="O271" t="n">
-        <v>1498350.630981272</v>
+        <v>1498350.63100449</v>
       </c>
       <c r="P271" t="n">
         <v>12900</v>
@@ -12918,22 +12918,22 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M283" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N283" t="n">
         <v>8562.18</v>
       </c>
       <c r="O283" t="n">
-        <v>119870.52</v>
+        <v>85621.8</v>
       </c>
       <c r="P283" t="n">
         <v>9900</v>
       </c>
       <c r="Q283" t="n">
-        <v>138600</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="284">
@@ -13522,10 +13522,10 @@
         <v>81</v>
       </c>
       <c r="N296" t="n">
-        <v>5218.1704988662</v>
+        <v>5218.1705022831</v>
       </c>
       <c r="O296" t="n">
-        <v>422671.8104081622</v>
+        <v>422671.8106849311</v>
       </c>
       <c r="P296" t="n">
         <v>8500</v>
@@ -13568,10 +13568,10 @@
         <v>1</v>
       </c>
       <c r="N297" t="n">
-        <v>1595.0094843962</v>
+        <v>1595.0094808743</v>
       </c>
       <c r="O297" t="n">
-        <v>1595.0094843962</v>
+        <v>1595.0094808743</v>
       </c>
       <c r="P297" t="n">
         <v>2600</v>
@@ -14077,10 +14077,10 @@
         <v>48</v>
       </c>
       <c r="N308" t="n">
-        <v>1664.3605954323</v>
+        <v>1664.360187234</v>
       </c>
       <c r="O308" t="n">
-        <v>79889.3085807504</v>
+        <v>79889.28898723199</v>
       </c>
       <c r="P308" t="n">
         <v>2900</v>
@@ -14356,10 +14356,10 @@
         <v>824</v>
       </c>
       <c r="N314" t="n">
-        <v>1778.4725400058</v>
+        <v>1778.4725489051</v>
       </c>
       <c r="O314" t="n">
-        <v>1465461.372964779</v>
+        <v>1465461.380297802</v>
       </c>
       <c r="P314" t="n">
         <v>4900</v>
@@ -16024,10 +16024,10 @@
         <v>96</v>
       </c>
       <c r="N350" t="n">
-        <v>8293</v>
+        <v>8329.056521739099</v>
       </c>
       <c r="O350" t="n">
-        <v>796128</v>
+        <v>799589.4260869536</v>
       </c>
       <c r="P350" t="n">
         <v>13500</v>
@@ -16294,22 +16294,22 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M356" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="N356" t="n">
         <v>8858.16</v>
       </c>
       <c r="O356" t="n">
-        <v>3826725.12</v>
+        <v>3791292.48</v>
       </c>
       <c r="P356" t="n">
         <v>15500</v>
       </c>
       <c r="Q356" t="n">
-        <v>6696000</v>
+        <v>6634000</v>
       </c>
     </row>
     <row r="357">
@@ -16386,22 +16386,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M358" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N358" t="n">
-        <v>17644.653166667</v>
+        <v>17644.653275862</v>
       </c>
       <c r="O358" t="n">
-        <v>194091.184833337</v>
+        <v>158801.879482758</v>
       </c>
       <c r="P358" t="n">
         <v>28200</v>
       </c>
       <c r="Q358" t="n">
-        <v>310200</v>
+        <v>253800</v>
       </c>
     </row>
     <row r="359">
@@ -16478,22 +16478,22 @@
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M360" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="N360" t="n">
-        <v>2252.2963603819</v>
+        <v>2252.2964527845</v>
       </c>
       <c r="O360" t="n">
-        <v>119371.7071002407</v>
+        <v>65316.5971307505</v>
       </c>
       <c r="P360" t="n">
         <v>3900</v>
       </c>
       <c r="Q360" t="n">
-        <v>206700</v>
+        <v>113100</v>
       </c>
     </row>
     <row r="361">
@@ -16810,10 +16810,10 @@
         <v>324</v>
       </c>
       <c r="N367" t="n">
-        <v>2328.1187525865</v>
+        <v>2328.1187507401</v>
       </c>
       <c r="O367" t="n">
-        <v>754310.4758380259</v>
+        <v>754310.4752397924</v>
       </c>
       <c r="P367" t="n">
         <v>4500</v>
@@ -17264,22 +17264,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M377" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N377" t="n">
         <v>13922</v>
       </c>
       <c r="O377" t="n">
-        <v>723944</v>
+        <v>640412</v>
       </c>
       <c r="P377" t="n">
         <v>22900</v>
       </c>
       <c r="Q377" t="n">
-        <v>1190800</v>
+        <v>1053400</v>
       </c>
     </row>
     <row r="378">
@@ -17684,10 +17684,10 @@
         <v>289</v>
       </c>
       <c r="N386" t="n">
-        <v>3903.7359649123</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O386" t="n">
-        <v>1128179.693859655</v>
+        <v>1128179.748461552</v>
       </c>
       <c r="P386" t="n">
         <v>7500</v>
@@ -17903,22 +17903,22 @@
         <v>0</v>
       </c>
       <c r="L391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M391" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N391" t="n">
         <v>9839</v>
       </c>
       <c r="O391" t="n">
-        <v>167263</v>
+        <v>147585</v>
       </c>
       <c r="P391" t="n">
         <v>16900</v>
       </c>
       <c r="Q391" t="n">
-        <v>287300</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="392">
@@ -17995,22 +17995,22 @@
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M393" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="N393" t="n">
         <v>6849.2</v>
       </c>
       <c r="O393" t="n">
-        <v>2808172</v>
+        <v>2739680</v>
       </c>
       <c r="P393" t="n">
         <v>11500</v>
       </c>
       <c r="Q393" t="n">
-        <v>4715000</v>
+        <v>4600000</v>
       </c>
     </row>
     <row r="394">
@@ -18133,22 +18133,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M396" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="N396" t="n">
         <v>6645</v>
       </c>
       <c r="O396" t="n">
-        <v>372120</v>
+        <v>292380</v>
       </c>
       <c r="P396" t="n">
         <v>10900</v>
       </c>
       <c r="Q396" t="n">
-        <v>610400</v>
+        <v>479600</v>
       </c>
     </row>
     <row r="397">
@@ -18783,10 +18783,10 @@
         <v>292</v>
       </c>
       <c r="N410" t="n">
-        <v>17075.989524138</v>
+        <v>17075.98952381</v>
       </c>
       <c r="O410" t="n">
-        <v>4986188.941048296</v>
+        <v>4986188.94095252</v>
       </c>
       <c r="P410" t="n">
         <v>27500</v>
@@ -19051,22 +19051,22 @@
         <v>0</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M416" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="N416" t="n">
         <v>10755</v>
       </c>
       <c r="O416" t="n">
-        <v>1946655</v>
+        <v>1817595</v>
       </c>
       <c r="P416" t="n">
         <v>17900</v>
       </c>
       <c r="Q416" t="n">
-        <v>3239900</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="417">
@@ -19511,22 +19511,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M426" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="N426" t="n">
         <v>10817</v>
       </c>
       <c r="O426" t="n">
-        <v>389412</v>
+        <v>346144</v>
       </c>
       <c r="P426" t="n">
         <v>17900</v>
       </c>
       <c r="Q426" t="n">
-        <v>644400</v>
+        <v>572800</v>
       </c>
     </row>
     <row r="427">
@@ -20069,10 +20069,10 @@
         <v>8</v>
       </c>
       <c r="N438" t="n">
-        <v>4248.6196402878</v>
+        <v>4248.6214117647</v>
       </c>
       <c r="O438" t="n">
-        <v>33988.9571223024</v>
+        <v>33988.9712941176</v>
       </c>
       <c r="P438" t="n">
         <v>5900</v>
@@ -20115,10 +20115,10 @@
         <v>120</v>
       </c>
       <c r="N439" t="n">
-        <v>2458.5134452463</v>
+        <v>2458.5134204724</v>
       </c>
       <c r="O439" t="n">
-        <v>295021.613429556</v>
+        <v>295021.610456688</v>
       </c>
       <c r="P439" t="n">
         <v>3500</v>
@@ -20207,10 +20207,10 @@
         <v>264</v>
       </c>
       <c r="N441" t="n">
-        <v>2079.3842077922</v>
+        <v>2079.384205911</v>
       </c>
       <c r="O441" t="n">
-        <v>548957.4308571408</v>
+        <v>548957.4303605041</v>
       </c>
       <c r="P441" t="n">
         <v>2900</v>
@@ -20253,10 +20253,10 @@
         <v>192</v>
       </c>
       <c r="N442" t="n">
-        <v>1803.0149882284</v>
+        <v>1803.0150073855</v>
       </c>
       <c r="O442" t="n">
-        <v>346178.8777398528</v>
+        <v>346178.881418016</v>
       </c>
       <c r="P442" t="n">
         <v>2500</v>
@@ -20299,10 +20299,10 @@
         <v>216</v>
       </c>
       <c r="N443" t="n">
-        <v>3306.595443038</v>
+        <v>3306.5954372624</v>
       </c>
       <c r="O443" t="n">
-        <v>714224.6156962081</v>
+        <v>714224.6144486784</v>
       </c>
       <c r="P443" t="n">
         <v>4900</v>
@@ -20345,10 +20345,10 @@
         <v>192</v>
       </c>
       <c r="N444" t="n">
-        <v>2122.1641066586</v>
+        <v>2122.1640959855</v>
       </c>
       <c r="O444" t="n">
-        <v>407455.5084784512</v>
+        <v>407455.506429216</v>
       </c>
       <c r="P444" t="n">
         <v>2900</v>
@@ -20391,10 +20391,10 @@
         <v>216</v>
       </c>
       <c r="N445" t="n">
-        <v>2108.7898867497</v>
+        <v>2108.7899091941</v>
       </c>
       <c r="O445" t="n">
-        <v>455498.6155379352</v>
+        <v>455498.6203859256</v>
       </c>
       <c r="P445" t="n">
         <v>2900</v>
@@ -20437,10 +20437,10 @@
         <v>144</v>
       </c>
       <c r="N446" t="n">
-        <v>2056.0838862559</v>
+        <v>2056.083871734</v>
       </c>
       <c r="O446" t="n">
-        <v>296076.0796208496</v>
+        <v>296076.077529696</v>
       </c>
       <c r="P446" t="n">
         <v>2900</v>
@@ -20483,10 +20483,10 @@
         <v>216</v>
       </c>
       <c r="N447" t="n">
-        <v>3224.5679768271</v>
+        <v>3224.5680666967</v>
       </c>
       <c r="O447" t="n">
-        <v>696506.6829946537</v>
+        <v>696506.7024064872</v>
       </c>
       <c r="P447" t="n">
         <v>4500</v>
@@ -20529,10 +20529,10 @@
         <v>360</v>
       </c>
       <c r="N448" t="n">
-        <v>1655.9313291536</v>
+        <v>1655.9312964128</v>
       </c>
       <c r="O448" t="n">
-        <v>596135.278495296</v>
+        <v>596135.266708608</v>
       </c>
       <c r="P448" t="n">
         <v>2500</v>
@@ -20759,10 +20759,10 @@
         <v>400</v>
       </c>
       <c r="N453" t="n">
-        <v>1592.2748727876</v>
+        <v>1592.2752659892</v>
       </c>
       <c r="O453" t="n">
-        <v>636909.94911504</v>
+        <v>636910.10639568</v>
       </c>
       <c r="P453" t="n">
         <v>2500</v>
@@ -20844,10 +20844,10 @@
         <v>8</v>
       </c>
       <c r="N455" t="n">
-        <v>5347.73</v>
+        <v>5370.4862978723</v>
       </c>
       <c r="O455" t="n">
-        <v>42781.84</v>
+        <v>42963.8903829784</v>
       </c>
       <c r="P455" t="n">
         <v>9500</v>
@@ -20890,10 +20890,10 @@
         <v>12</v>
       </c>
       <c r="N456" t="n">
-        <v>2311.9264781906</v>
+        <v>2311.9257410562</v>
       </c>
       <c r="O456" t="n">
-        <v>27743.1177382872</v>
+        <v>27743.1088926744</v>
       </c>
       <c r="P456" t="n">
         <v>3500</v>
@@ -20936,10 +20936,10 @@
         <v>48</v>
       </c>
       <c r="N457" t="n">
-        <v>1906.1867105263</v>
+        <v>1906.1864705882</v>
       </c>
       <c r="O457" t="n">
-        <v>91496.9621052624</v>
+        <v>91496.95058823361</v>
       </c>
       <c r="P457" t="n">
         <v>2900</v>
@@ -20982,10 +20982,10 @@
         <v>120</v>
       </c>
       <c r="N458" t="n">
-        <v>3033.7312929293</v>
+        <v>3033.7307083333</v>
       </c>
       <c r="O458" t="n">
-        <v>364047.755151516</v>
+        <v>364047.684999996</v>
       </c>
       <c r="P458" t="n">
         <v>4500</v>
@@ -21028,10 +21028,10 @@
         <v>408</v>
       </c>
       <c r="N459" t="n">
-        <v>2060.1607096774</v>
+        <v>2060.1606493506</v>
       </c>
       <c r="O459" t="n">
-        <v>840545.5695483793</v>
+        <v>840545.5449350448</v>
       </c>
       <c r="P459" t="n">
         <v>2900</v>
@@ -21074,10 +21074,10 @@
         <v>72</v>
       </c>
       <c r="N460" t="n">
-        <v>1668.6158441558</v>
+        <v>1668.6165143824</v>
       </c>
       <c r="O460" t="n">
-        <v>120140.3407792176</v>
+        <v>120140.3890355328</v>
       </c>
       <c r="P460" t="n">
         <v>2500</v>
@@ -21166,10 +21166,10 @@
         <v>800</v>
       </c>
       <c r="N462" t="n">
-        <v>1259.2744160105</v>
+        <v>1259.2744247206</v>
       </c>
       <c r="O462" t="n">
-        <v>1007419.5328084</v>
+        <v>1007419.53977648</v>
       </c>
       <c r="P462" t="n">
         <v>1900</v>
@@ -21299,10 +21299,10 @@
         <v>72</v>
       </c>
       <c r="N465" t="n">
-        <v>2556.7449856734</v>
+        <v>2556.7450581395</v>
       </c>
       <c r="O465" t="n">
-        <v>184085.6389684848</v>
+        <v>184085.644186044</v>
       </c>
       <c r="P465" t="n">
         <v>3900</v>
@@ -21389,10 +21389,10 @@
         <v>660</v>
       </c>
       <c r="N467" t="n">
-        <v>692.15205253785</v>
+        <v>692.15206356312</v>
       </c>
       <c r="O467" t="n">
-        <v>456820.354674981</v>
+        <v>456820.3619516592</v>
       </c>
       <c r="P467" t="n">
         <v>1200</v>
@@ -21944,10 +21944,10 @@
         <v>46</v>
       </c>
       <c r="N479" t="n">
-        <v>3026.5146568627</v>
+        <v>3026.514679803</v>
       </c>
       <c r="O479" t="n">
-        <v>139219.6742156842</v>
+        <v>139219.675270938</v>
       </c>
       <c r="P479" t="n">
         <v>7000</v>
@@ -22878,10 +22878,10 @@
         <v>140</v>
       </c>
       <c r="N499" t="n">
-        <v>3907.5003212851</v>
+        <v>3907.5003292181</v>
       </c>
       <c r="O499" t="n">
-        <v>547050.044979914</v>
+        <v>547050.046090534</v>
       </c>
       <c r="P499" t="n">
         <v>3900</v>
@@ -23432,10 +23432,10 @@
         <v>749</v>
       </c>
       <c r="N511" t="n">
-        <v>517.28774146762</v>
+        <v>517.2878865955601</v>
       </c>
       <c r="O511" t="n">
-        <v>387448.5183592474</v>
+        <v>387448.6270600745</v>
       </c>
       <c r="P511" t="n">
         <v>900</v>
@@ -23855,10 +23855,10 @@
         <v>757</v>
       </c>
       <c r="N520" t="n">
-        <v>3110.8430699863</v>
+        <v>3110.8429819337</v>
       </c>
       <c r="O520" t="n">
-        <v>2354908.203979629</v>
+        <v>2354908.137323811</v>
       </c>
       <c r="P520" t="n">
         <v>4500</v>
@@ -24306,10 +24306,10 @@
         <v>20090</v>
       </c>
       <c r="N530" t="n">
-        <v>703.79541200942</v>
+        <v>703.79538564105</v>
       </c>
       <c r="O530" t="n">
-        <v>14139249.82726925</v>
+        <v>14139249.29752869</v>
       </c>
       <c r="P530" t="n">
         <v>900</v>
@@ -24447,10 +24447,10 @@
         <v>90</v>
       </c>
       <c r="N533" t="n">
-        <v>2501.385443038</v>
+        <v>2501.3854237288</v>
       </c>
       <c r="O533" t="n">
-        <v>225124.68987342</v>
+        <v>225124.688135592</v>
       </c>
       <c r="P533" t="n">
         <v>4100</v>
@@ -24813,10 +24813,10 @@
         <v>47</v>
       </c>
       <c r="N541" t="n">
-        <v>1595.5191323094</v>
+        <v>1595.5190941049</v>
       </c>
       <c r="O541" t="n">
-        <v>74989.3992185418</v>
+        <v>74989.3974229303</v>
       </c>
       <c r="P541" t="n">
         <v>2500</v>
@@ -25202,10 +25202,10 @@
         <v>168</v>
       </c>
       <c r="N549" t="n">
-        <v>2098.4048595506</v>
+        <v>2098.4049008499</v>
       </c>
       <c r="O549" t="n">
-        <v>352532.0164045008</v>
+        <v>352532.0233427832</v>
       </c>
       <c r="P549" t="n">
         <v>9500</v>
@@ -25300,10 +25300,10 @@
         <v>33</v>
       </c>
       <c r="N551" t="n">
-        <v>2832.1946575342</v>
+        <v>2832.1948571429</v>
       </c>
       <c r="O551" t="n">
-        <v>93462.4236986286</v>
+        <v>93462.4302857157</v>
       </c>
       <c r="P551" t="n">
         <v>12900</v>
@@ -26021,10 +26021,10 @@
         <v>24</v>
       </c>
       <c r="N566" t="n">
-        <v>23475.658125</v>
+        <v>23475.658064516</v>
       </c>
       <c r="O566" t="n">
-        <v>563415.795</v>
+        <v>563415.793548384</v>
       </c>
       <c r="P566" t="n">
         <v>31900</v>
@@ -26410,10 +26410,10 @@
         <v>165</v>
       </c>
       <c r="N574" t="n">
-        <v>875.69015686275</v>
+        <v>875.69016</v>
       </c>
       <c r="O574" t="n">
-        <v>144488.8758823538</v>
+        <v>144488.8764</v>
       </c>
       <c r="P574" t="n">
         <v>4500</v>
@@ -26502,22 +26502,22 @@
         <v>0</v>
       </c>
       <c r="L576" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M576" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N576" t="n">
         <v>6989.34</v>
       </c>
       <c r="O576" t="n">
-        <v>663987.3</v>
+        <v>629040.6</v>
       </c>
       <c r="P576" t="n">
         <v>10900</v>
       </c>
       <c r="Q576" t="n">
-        <v>1035500</v>
+        <v>981000</v>
       </c>
     </row>
     <row r="577">
@@ -26551,22 +26551,22 @@
         <v>0</v>
       </c>
       <c r="L577" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M577" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="N577" t="n">
         <v>4568.55</v>
       </c>
       <c r="O577" t="n">
-        <v>338072.7</v>
+        <v>301524.3</v>
       </c>
       <c r="P577" t="n">
         <v>6900</v>
       </c>
       <c r="Q577" t="n">
-        <v>510600</v>
+        <v>455400</v>
       </c>
     </row>
     <row r="578">
@@ -26786,10 +26786,10 @@
         <v>112</v>
       </c>
       <c r="N582" t="n">
-        <v>3067.0905341246</v>
+        <v>3067.0905389222</v>
       </c>
       <c r="O582" t="n">
-        <v>343514.1398219552</v>
+        <v>343514.1403592864</v>
       </c>
       <c r="P582" t="n">
         <v>7200</v>
@@ -26930,10 +26930,10 @@
         <v>162</v>
       </c>
       <c r="N585" t="n">
-        <v>4190.77</v>
+        <v>4205.0243197279</v>
       </c>
       <c r="O585" t="n">
-        <v>678904.7400000001</v>
+        <v>681213.9397959197</v>
       </c>
       <c r="P585" t="n">
         <v>5900</v>
@@ -26979,10 +26979,10 @@
         <v>341</v>
       </c>
       <c r="N586" t="n">
-        <v>3499.72</v>
+        <v>3508.0033609467</v>
       </c>
       <c r="O586" t="n">
-        <v>1193404.52</v>
+        <v>1196229.146082825</v>
       </c>
       <c r="P586" t="n">
         <v>6900</v>
@@ -27651,10 +27651,10 @@
         <v>24</v>
       </c>
       <c r="N600" t="n">
-        <v>10737.526727273</v>
+        <v>10737.526666667</v>
       </c>
       <c r="O600" t="n">
-        <v>257700.641454552</v>
+        <v>257700.640000008</v>
       </c>
       <c r="P600" t="n">
         <v>18900</v>
@@ -28827,10 +28827,10 @@
         <v>340</v>
       </c>
       <c r="N625" t="n">
-        <v>1934.77</v>
+        <v>1942.8822431866</v>
       </c>
       <c r="O625" t="n">
-        <v>657821.8</v>
+        <v>660579.9626834439</v>
       </c>
       <c r="P625" t="n">
         <v>8900</v>
@@ -28870,22 +28870,22 @@
         <v>0</v>
       </c>
       <c r="L626" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M626" t="n">
-        <v>1135</v>
+        <v>1105</v>
       </c>
       <c r="N626" t="n">
-        <v>7046.9398302567</v>
+        <v>7046.9398299681</v>
       </c>
       <c r="O626" t="n">
-        <v>7998276.707341354</v>
+        <v>7786868.51211475</v>
       </c>
       <c r="P626" t="n">
         <v>9900</v>
       </c>
       <c r="Q626" t="n">
-        <v>11236500</v>
+        <v>10939500</v>
       </c>
     </row>
     <row r="627">
@@ -29066,10 +29066,10 @@
         <v>648</v>
       </c>
       <c r="N630" t="n">
-        <v>665.32333760137</v>
+        <v>665.32334188034</v>
       </c>
       <c r="O630" t="n">
-        <v>431129.5227656877</v>
+        <v>431129.5255384603</v>
       </c>
       <c r="P630" t="n">
         <v>2900</v>
@@ -29164,10 +29164,10 @@
         <v>720</v>
       </c>
       <c r="N632" t="n">
-        <v>641.78</v>
+        <v>642.25894029851</v>
       </c>
       <c r="O632" t="n">
-        <v>462081.6</v>
+        <v>462426.4370149272</v>
       </c>
       <c r="P632" t="n">
         <v>2500</v>
@@ -29256,22 +29256,22 @@
         <v>0</v>
       </c>
       <c r="L634" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M634" t="n">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="N634" t="n">
         <v>4581.84</v>
       </c>
       <c r="O634" t="n">
-        <v>531493.4400000001</v>
+        <v>421529.28</v>
       </c>
       <c r="P634" t="n">
         <v>7900</v>
       </c>
       <c r="Q634" t="n">
-        <v>916400</v>
+        <v>726800</v>
       </c>
     </row>
     <row r="635">
@@ -29406,10 +29406,10 @@
         <v>61</v>
       </c>
       <c r="N637" t="n">
-        <v>540.4025</v>
+        <v>540.40252525253</v>
       </c>
       <c r="O637" t="n">
-        <v>32964.55250000001</v>
+        <v>32964.55404040433</v>
       </c>
       <c r="P637" t="n">
         <v>2500</v>
@@ -29504,10 +29504,10 @@
         <v>153</v>
       </c>
       <c r="N639" t="n">
-        <v>315.02678272981</v>
+        <v>315.02679218968</v>
       </c>
       <c r="O639" t="n">
-        <v>48199.09775766093</v>
+        <v>48199.09920502104</v>
       </c>
       <c r="P639" t="n">
         <v>2200</v>
@@ -29805,10 +29805,10 @@
         <v>30</v>
       </c>
       <c r="N646" t="n">
-        <v>5577.2680821918</v>
+        <v>5577.2680778032</v>
       </c>
       <c r="O646" t="n">
-        <v>167318.042465754</v>
+        <v>167318.042334096</v>
       </c>
       <c r="P646" t="n">
         <v>6500</v>
@@ -30010,22 +30010,22 @@
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="M651" t="n">
-        <v>1562</v>
+        <v>1346</v>
       </c>
       <c r="N651" t="n">
         <v>1176.57</v>
       </c>
       <c r="O651" t="n">
-        <v>1837802.34</v>
+        <v>1583663.22</v>
       </c>
       <c r="P651" t="n">
         <v>1900</v>
       </c>
       <c r="Q651" t="n">
-        <v>2967800</v>
+        <v>2557400</v>
       </c>
     </row>
     <row r="652">
@@ -30101,10 +30101,10 @@
         <v>4</v>
       </c>
       <c r="N653" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821442495</v>
       </c>
       <c r="O653" t="n">
-        <v>4854.728477842</v>
+        <v>4854.728576998</v>
       </c>
       <c r="P653" t="n">
         <v>1500</v>
@@ -30145,10 +30145,10 @@
         <v>450</v>
       </c>
       <c r="N654" t="n">
-        <v>1794.2879773671</v>
+        <v>1794.2879767875</v>
       </c>
       <c r="O654" t="n">
-        <v>807429.589815195</v>
+        <v>807429.5895543749</v>
       </c>
       <c r="P654" t="n">
         <v>1600</v>
@@ -30544,22 +30544,22 @@
         <v>0</v>
       </c>
       <c r="L663" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M663" t="n">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="N663" t="n">
         <v>22951.704968711</v>
       </c>
       <c r="O663" t="n">
-        <v>8216710.378798539</v>
+        <v>8079000.148986273</v>
       </c>
       <c r="P663" t="n">
         <v>37900</v>
       </c>
       <c r="Q663" t="n">
-        <v>13568200</v>
+        <v>13340800</v>
       </c>
     </row>
     <row r="664">
@@ -30739,10 +30739,10 @@
         <v>310</v>
       </c>
       <c r="N667" t="n">
-        <v>1757.3205295316</v>
+        <v>1757.3205360825</v>
       </c>
       <c r="O667" t="n">
-        <v>544769.364154796</v>
+        <v>544769.366185575</v>
       </c>
       <c r="P667" t="n">
         <v>2000</v>
@@ -30871,22 +30871,22 @@
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M670" t="n">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="N670" t="n">
         <v>220.00820587826</v>
       </c>
       <c r="O670" t="n">
-        <v>1012037.747039996</v>
+        <v>968036.1058643439</v>
       </c>
       <c r="P670" t="n">
         <v>260</v>
       </c>
       <c r="Q670" t="n">
-        <v>1196000</v>
+        <v>1144000</v>
       </c>
     </row>
     <row r="671">
@@ -31101,22 +31101,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M675" t="n">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="N675" t="n">
         <v>1952.66</v>
       </c>
       <c r="O675" t="n">
-        <v>781064</v>
+        <v>757632.0800000001</v>
       </c>
       <c r="P675" t="n">
         <v>3500</v>
       </c>
       <c r="Q675" t="n">
-        <v>1400000</v>
+        <v>1358000</v>
       </c>
     </row>
     <row r="676">
@@ -31291,10 +31291,10 @@
         <v>11</v>
       </c>
       <c r="N679" t="n">
-        <v>9855.0382758621</v>
+        <v>9855.0381481481</v>
       </c>
       <c r="O679" t="n">
-        <v>108405.4210344831</v>
+        <v>108405.4196296291</v>
       </c>
       <c r="P679" t="n">
         <v>15500</v>
@@ -31858,10 +31858,10 @@
         <v>686</v>
       </c>
       <c r="N691" t="n">
-        <v>227.41596785975</v>
+        <v>227.41597222222</v>
       </c>
       <c r="O691" t="n">
-        <v>156007.3539517885</v>
+        <v>156007.3569444429</v>
       </c>
       <c r="P691" t="n">
         <v>1200</v>
@@ -31996,10 +31996,10 @@
         <v>115</v>
       </c>
       <c r="N694" t="n">
-        <v>3306.0098310139</v>
+        <v>3306.00983</v>
       </c>
       <c r="O694" t="n">
-        <v>380191.1305665985</v>
+        <v>380191.13045</v>
       </c>
       <c r="P694" t="n">
         <v>4200</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -630,22 +630,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M6" t="n">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3043052838</v>
+        <v>1811.3044243338</v>
       </c>
       <c r="O6" t="n">
-        <v>266261.7328767186</v>
+        <v>157583.4849170406</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
       </c>
       <c r="Q6" t="n">
-        <v>382200</v>
+        <v>226200</v>
       </c>
     </row>
     <row r="7">
@@ -1234,10 +1234,10 @@
         <v>210</v>
       </c>
       <c r="N21" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O21" t="n">
-        <v>824635.796613657</v>
+        <v>824635.795993842</v>
       </c>
       <c r="P21" t="n">
         <v>4800</v>
@@ -1276,10 +1276,10 @@
         <v>24</v>
       </c>
       <c r="N22" t="n">
-        <v>11491.09631068</v>
+        <v>11955.383030303</v>
       </c>
       <c r="O22" t="n">
-        <v>275786.31145632</v>
+        <v>286929.192727272</v>
       </c>
       <c r="P22" t="n">
         <v>23000</v>
@@ -1747,10 +1747,10 @@
         <v>16</v>
       </c>
       <c r="N34" t="n">
-        <v>12837.965507246</v>
+        <v>12837.966461538</v>
       </c>
       <c r="O34" t="n">
-        <v>205407.448115936</v>
+        <v>205407.463384608</v>
       </c>
       <c r="P34" t="n">
         <v>22900</v>
@@ -1836,10 +1836,10 @@
         <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>10994.353483146</v>
+        <v>10994.353793103</v>
       </c>
       <c r="O36" t="n">
-        <v>65966.120898876</v>
+        <v>65966.122758618</v>
       </c>
       <c r="P36" t="n">
         <v>16900</v>
@@ -1878,10 +1878,10 @@
         <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>16486.409489051</v>
+        <v>16486.409172932</v>
       </c>
       <c r="O37" t="n">
-        <v>395673.8277372239</v>
+        <v>395673.820150368</v>
       </c>
       <c r="P37" t="n">
         <v>30500</v>
@@ -2259,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>200072.19977273</v>
+        <v>200072.19992308</v>
       </c>
       <c r="O46" t="n">
-        <v>1400505.39840911</v>
+        <v>1400505.39946156</v>
       </c>
       <c r="P46" t="n">
         <v>312000</v>
@@ -2306,10 +2306,10 @@
         <v>13</v>
       </c>
       <c r="N47" t="n">
-        <v>344599.17865385</v>
+        <v>344599.17862745</v>
       </c>
       <c r="O47" t="n">
-        <v>4479789.32250005</v>
+        <v>4479789.32215685</v>
       </c>
       <c r="P47" t="n">
         <v>532900</v>
@@ -2431,10 +2431,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="n">
-        <v>20961.76</v>
+        <v>21291.002303665</v>
       </c>
       <c r="O50" t="n">
-        <v>628852.7999999999</v>
+        <v>638730.0691099501</v>
       </c>
       <c r="P50" t="n">
         <v>38300</v>
@@ -3341,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M71" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N71" t="n">
         <v>14233.54</v>
       </c>
       <c r="O71" t="n">
-        <v>1708024.8</v>
+        <v>1651090.64</v>
       </c>
       <c r="P71" t="n">
         <v>10000</v>
       </c>
       <c r="Q71" t="n">
-        <v>1200000</v>
+        <v>1160000</v>
       </c>
     </row>
     <row r="72">
@@ -3391,10 +3391,10 @@
         <v>1727</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0541801698</v>
+        <v>1098.0548595108</v>
       </c>
       <c r="O72" t="n">
-        <v>1896339.569153245</v>
+        <v>1896340.742375152</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -3790,22 +3790,22 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N81" t="n">
         <v>17207.41</v>
       </c>
       <c r="O81" t="n">
-        <v>1049652.01</v>
+        <v>1015237.19</v>
       </c>
       <c r="P81" t="n">
         <v>20000</v>
       </c>
       <c r="Q81" t="n">
-        <v>1220000</v>
+        <v>1180000</v>
       </c>
     </row>
     <row r="82">
@@ -4008,22 +4008,22 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M86" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N86" t="n">
         <v>8119.38</v>
       </c>
       <c r="O86" t="n">
-        <v>113671.32</v>
+        <v>40596.9</v>
       </c>
       <c r="P86" t="n">
         <v>10700</v>
       </c>
       <c r="Q86" t="n">
-        <v>149800</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="87">
@@ -4462,10 +4462,10 @@
         <v>720</v>
       </c>
       <c r="N96" t="n">
-        <v>5216.8959762435</v>
+        <v>5216.8959678619</v>
       </c>
       <c r="O96" t="n">
-        <v>3756165.10289532</v>
+        <v>3756165.096860568</v>
       </c>
       <c r="P96" t="n">
         <v>8500</v>
@@ -4693,10 +4693,10 @@
         <v>3199</v>
       </c>
       <c r="N101" t="n">
-        <v>3158.8608143857</v>
+        <v>3158.8608147003</v>
       </c>
       <c r="O101" t="n">
-        <v>10105195.74521985</v>
+        <v>10105195.74622626</v>
       </c>
       <c r="P101" t="n">
         <v>5600</v>
@@ -4968,10 +4968,10 @@
         <v>259</v>
       </c>
       <c r="N107" t="n">
-        <v>2694.8234624043</v>
+        <v>2694.8234565119</v>
       </c>
       <c r="O107" t="n">
-        <v>697959.2767627137</v>
+        <v>697959.2752365822</v>
       </c>
       <c r="P107" t="n">
         <v>4900</v>
@@ -5288,10 +5288,10 @@
         <v>593</v>
       </c>
       <c r="N114" t="n">
-        <v>3795.7100070547</v>
+        <v>3795.7100070621</v>
       </c>
       <c r="O114" t="n">
-        <v>2250856.034183437</v>
+        <v>2250856.034187825</v>
       </c>
       <c r="P114" t="n">
         <v>6200</v>
@@ -5513,10 +5513,10 @@
         <v>318</v>
       </c>
       <c r="N119" t="n">
-        <v>4890.9300462963</v>
+        <v>4890.9300463499</v>
       </c>
       <c r="O119" t="n">
-        <v>1555315.754722223</v>
+        <v>1555315.754739268</v>
       </c>
       <c r="P119" t="n">
         <v>8200</v>
@@ -5957,22 +5957,22 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M129" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N129" t="n">
         <v>10716.34</v>
       </c>
       <c r="O129" t="n">
-        <v>535817</v>
+        <v>439369.94</v>
       </c>
       <c r="P129" t="n">
         <v>39000</v>
       </c>
       <c r="Q129" t="n">
-        <v>1950000</v>
+        <v>1599000</v>
       </c>
     </row>
     <row r="130">
@@ -6012,10 +6012,10 @@
         <v>288</v>
       </c>
       <c r="N130" t="n">
-        <v>3594.2541747573</v>
+        <v>3594.25414277</v>
       </c>
       <c r="O130" t="n">
-        <v>1035145.202330102</v>
+        <v>1035145.19311776</v>
       </c>
       <c r="P130" t="n">
         <v>6500</v>
@@ -6053,10 +6053,10 @@
         <v>108</v>
       </c>
       <c r="N131" t="n">
-        <v>3240.8500295421</v>
+        <v>3240.850029985</v>
       </c>
       <c r="O131" t="n">
-        <v>350011.8031905468</v>
+        <v>350011.80323838</v>
       </c>
       <c r="P131" t="n">
         <v>5200</v>
@@ -6093,22 +6093,22 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N132" t="n">
         <v>7120</v>
       </c>
       <c r="O132" t="n">
-        <v>206480</v>
+        <v>199360</v>
       </c>
       <c r="P132" t="n">
         <v>8900</v>
       </c>
       <c r="Q132" t="n">
-        <v>258100</v>
+        <v>249200</v>
       </c>
     </row>
     <row r="133">
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M135" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="N135" t="n">
-        <v>14822.378864577</v>
+        <v>14822.378863905</v>
       </c>
       <c r="O135" t="n">
-        <v>4565292.690289716</v>
+        <v>4520825.553491025</v>
       </c>
       <c r="P135" t="n">
         <v>24900</v>
       </c>
       <c r="Q135" t="n">
-        <v>7669200</v>
+        <v>7594500</v>
       </c>
     </row>
     <row r="136">
@@ -7090,10 +7090,10 @@
         <v>1945</v>
       </c>
       <c r="N154" t="n">
-        <v>4372.2107869318</v>
+        <v>4372.2107876031</v>
       </c>
       <c r="O154" t="n">
-        <v>8503949.980582351</v>
+        <v>8503949.981888028</v>
       </c>
       <c r="P154" t="n">
         <v>7500</v>
@@ -7180,10 +7180,10 @@
         <v>498</v>
       </c>
       <c r="N156" t="n">
-        <v>1592.5675881262</v>
+        <v>1592.567520267</v>
       </c>
       <c r="O156" t="n">
-        <v>793098.6588868476</v>
+        <v>793098.625092966</v>
       </c>
       <c r="P156" t="n">
         <v>3900</v>
@@ -7670,10 +7670,10 @@
         <v>450</v>
       </c>
       <c r="N167" t="n">
-        <v>1532.629028858</v>
+        <v>1532.6290284343</v>
       </c>
       <c r="O167" t="n">
-        <v>689683.0629861001</v>
+        <v>689683.062795435</v>
       </c>
       <c r="P167" t="n">
         <v>1200</v>
@@ -7932,22 +7932,22 @@
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N173" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O173" t="n">
-        <v>1412146.5</v>
+        <v>1402732.19</v>
       </c>
       <c r="P173" t="n">
         <v>16900</v>
       </c>
       <c r="Q173" t="n">
-        <v>2535000</v>
+        <v>2518100</v>
       </c>
     </row>
     <row r="174">
@@ -8263,10 +8263,10 @@
         <v>105</v>
       </c>
       <c r="N180" t="n">
-        <v>16897</v>
+        <v>17010.976391231</v>
       </c>
       <c r="O180" t="n">
-        <v>1774185</v>
+        <v>1786152.521079255</v>
       </c>
       <c r="P180" t="n">
         <v>27900</v>
@@ -8301,22 +8301,22 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M181" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N181" t="n">
         <v>8341.030000000001</v>
       </c>
       <c r="O181" t="n">
-        <v>683964.4600000001</v>
+        <v>658941.37</v>
       </c>
       <c r="P181" t="n">
         <v>13900</v>
       </c>
       <c r="Q181" t="n">
-        <v>1139800</v>
+        <v>1098100</v>
       </c>
     </row>
     <row r="182">
@@ -8971,10 +8971,10 @@
         <v>824</v>
       </c>
       <c r="N195" t="n">
-        <v>1630.9231064431</v>
+        <v>1630.923147125</v>
       </c>
       <c r="O195" t="n">
-        <v>1343880.639709115</v>
+        <v>1343880.673231</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9017,10 +9017,10 @@
         <v>5</v>
       </c>
       <c r="N196" t="n">
-        <v>1467.3275193798</v>
+        <v>1467.327254902</v>
       </c>
       <c r="O196" t="n">
-        <v>7336.637596899</v>
+        <v>7336.63627451</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9063,10 +9063,10 @@
         <v>384</v>
       </c>
       <c r="N197" t="n">
-        <v>1690.6033768352</v>
+        <v>1690.6028354857</v>
       </c>
       <c r="O197" t="n">
-        <v>649191.6967047168</v>
+        <v>649191.4888265089</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9109,10 +9109,10 @@
         <v>2118</v>
       </c>
       <c r="N198" t="n">
-        <v>1550.1930735465</v>
+        <v>1550.1931350849</v>
       </c>
       <c r="O198" t="n">
-        <v>3283308.929771487</v>
+        <v>3283309.060109818</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
@@ -9201,10 +9201,10 @@
         <v>454</v>
       </c>
       <c r="N200" t="n">
-        <v>2403.5102087442</v>
+        <v>2403.5103430475</v>
       </c>
       <c r="O200" t="n">
-        <v>1091193.634769867</v>
+        <v>1091193.695743565</v>
       </c>
       <c r="P200" t="n">
         <v>3500</v>
@@ -9247,10 +9247,10 @@
         <v>80</v>
       </c>
       <c r="N201" t="n">
-        <v>2521.5455211726</v>
+        <v>2521.5446987952</v>
       </c>
       <c r="O201" t="n">
-        <v>201723.641693808</v>
+        <v>201723.575903616</v>
       </c>
       <c r="P201" t="n">
         <v>3900</v>
@@ -9288,10 +9288,10 @@
         <v>65</v>
       </c>
       <c r="N202" t="n">
-        <v>1232.8081659389</v>
+        <v>1232.8080088496</v>
       </c>
       <c r="O202" t="n">
-        <v>80132.5307860285</v>
+        <v>80132.520575224</v>
       </c>
       <c r="P202" t="n">
         <v>2400</v>
@@ -9819,22 +9819,22 @@
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M214" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="N214" t="n">
         <v>7028</v>
       </c>
       <c r="O214" t="n">
-        <v>709828</v>
+        <v>639548</v>
       </c>
       <c r="P214" t="n">
         <v>15900</v>
       </c>
       <c r="Q214" t="n">
-        <v>1605900</v>
+        <v>1446900</v>
       </c>
     </row>
     <row r="215">
@@ -10235,22 +10235,22 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M223" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N223" t="n">
         <v>11095.52</v>
       </c>
       <c r="O223" t="n">
-        <v>510393.92</v>
+        <v>466011.84</v>
       </c>
       <c r="P223" t="n">
         <v>10900</v>
       </c>
       <c r="Q223" t="n">
-        <v>501400</v>
+        <v>457800</v>
       </c>
     </row>
     <row r="224">
@@ -10459,10 +10459,10 @@
         <v>19</v>
       </c>
       <c r="N228" t="n">
-        <v>7537.4721481481</v>
+        <v>7537.4721641791</v>
       </c>
       <c r="O228" t="n">
-        <v>143211.9708148139</v>
+        <v>143211.9711194029</v>
       </c>
       <c r="P228" t="n">
         <v>8900</v>
@@ -11676,10 +11676,10 @@
         <v>32</v>
       </c>
       <c r="N256" t="n">
-        <v>11562.038530184</v>
+        <v>11562.038526316</v>
       </c>
       <c r="O256" t="n">
-        <v>369985.232965888</v>
+        <v>369985.232842112</v>
       </c>
       <c r="P256" t="n">
         <v>18500</v>
@@ -11722,10 +11722,10 @@
         <v>19</v>
       </c>
       <c r="N257" t="n">
-        <v>13513.642971014</v>
+        <v>13513.642992701</v>
       </c>
       <c r="O257" t="n">
-        <v>256759.216449266</v>
+        <v>256759.216861319</v>
       </c>
       <c r="P257" t="n">
         <v>21900</v>
@@ -11808,22 +11808,22 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M259" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N259" t="n">
         <v>22730.48</v>
       </c>
       <c r="O259" t="n">
-        <v>590992.48</v>
+        <v>500070.56</v>
       </c>
       <c r="P259" t="n">
         <v>36900</v>
       </c>
       <c r="Q259" t="n">
-        <v>959400</v>
+        <v>811800</v>
       </c>
     </row>
     <row r="260">
@@ -11906,10 +11906,10 @@
         <v>94</v>
       </c>
       <c r="N261" t="n">
-        <v>27123.765241636</v>
+        <v>27123.765232775</v>
       </c>
       <c r="O261" t="n">
-        <v>2549633.932713784</v>
+        <v>2549633.93188085</v>
       </c>
       <c r="P261" t="n">
         <v>44500</v>
@@ -12126,10 +12126,10 @@
         <v>38</v>
       </c>
       <c r="N266" t="n">
-        <v>5431.12</v>
+        <v>5465.2779874214</v>
       </c>
       <c r="O266" t="n">
-        <v>206382.56</v>
+        <v>207680.5635220132</v>
       </c>
       <c r="P266" t="n">
         <v>8900</v>
@@ -12172,10 +12172,10 @@
         <v>599</v>
       </c>
       <c r="N267" t="n">
-        <v>1560.9991607397</v>
+        <v>1560.999261745</v>
       </c>
       <c r="O267" t="n">
-        <v>935038.4972830804</v>
+        <v>935038.557785255</v>
       </c>
       <c r="P267" t="n">
         <v>2900</v>
@@ -12310,10 +12310,10 @@
         <v>188</v>
       </c>
       <c r="N270" t="n">
-        <v>7969.9501649175</v>
+        <v>7987.9139894816</v>
       </c>
       <c r="O270" t="n">
-        <v>1498350.63100449</v>
+        <v>1501727.830022541</v>
       </c>
       <c r="P270" t="n">
         <v>12900</v>
@@ -12538,22 +12538,22 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="N275" t="n">
         <v>5147.61</v>
       </c>
       <c r="O275" t="n">
-        <v>6892649.789999999</v>
+        <v>6887502.18</v>
       </c>
       <c r="P275" t="n">
         <v>5900</v>
       </c>
       <c r="Q275" t="n">
-        <v>7900100</v>
+        <v>7894200</v>
       </c>
     </row>
     <row r="276">
@@ -12630,22 +12630,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M277" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N277" t="n">
         <v>8720</v>
       </c>
       <c r="O277" t="n">
-        <v>959200</v>
+        <v>924320</v>
       </c>
       <c r="P277" t="n">
         <v>10900</v>
       </c>
       <c r="Q277" t="n">
-        <v>1199000</v>
+        <v>1155400</v>
       </c>
     </row>
     <row r="278">
@@ -12820,22 +12820,22 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M281" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N281" t="n">
         <v>5470.94</v>
       </c>
       <c r="O281" t="n">
-        <v>273547</v>
+        <v>246192.3</v>
       </c>
       <c r="P281" t="n">
         <v>6900</v>
       </c>
       <c r="Q281" t="n">
-        <v>345000</v>
+        <v>310500</v>
       </c>
     </row>
     <row r="282">
@@ -13053,22 +13053,22 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M286" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
         <v>2634.61</v>
       </c>
       <c r="O286" t="n">
-        <v>86942.13</v>
+        <v>0</v>
       </c>
       <c r="P286" t="n">
         <v>4200</v>
       </c>
       <c r="Q286" t="n">
-        <v>138600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -13105,10 +13105,10 @@
         <v>122</v>
       </c>
       <c r="N287" t="n">
-        <v>3113.8900261438</v>
+        <v>3113.8900262812</v>
       </c>
       <c r="O287" t="n">
-        <v>379894.5831895436</v>
+        <v>379894.5832063064</v>
       </c>
       <c r="P287" t="n">
         <v>5000</v>
@@ -13473,10 +13473,10 @@
         <v>81</v>
       </c>
       <c r="N295" t="n">
-        <v>5218.1705022831</v>
+        <v>5218.1705134189</v>
       </c>
       <c r="O295" t="n">
-        <v>422671.8106849311</v>
+        <v>422671.8115869309</v>
       </c>
       <c r="P295" t="n">
         <v>8500</v>
@@ -13519,10 +13519,10 @@
         <v>1</v>
       </c>
       <c r="N296" t="n">
-        <v>1595.0094808743</v>
+        <v>1595.0094571429</v>
       </c>
       <c r="O296" t="n">
-        <v>1595.0094808743</v>
+        <v>1595.0094571429</v>
       </c>
       <c r="P296" t="n">
         <v>2600</v>
@@ -13565,10 +13565,10 @@
         <v>123</v>
       </c>
       <c r="N297" t="n">
-        <v>3610.6500238663</v>
+        <v>3610.6500248756</v>
       </c>
       <c r="O297" t="n">
-        <v>444109.9529355549</v>
+        <v>444109.9530596988</v>
       </c>
       <c r="P297" t="n">
         <v>5800</v>
@@ -13700,22 +13700,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M300" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N300" t="n">
         <v>3920</v>
       </c>
       <c r="O300" t="n">
-        <v>1912960</v>
+        <v>1901200</v>
       </c>
       <c r="P300" t="n">
         <v>4900</v>
       </c>
       <c r="Q300" t="n">
-        <v>2391200</v>
+        <v>2376500</v>
       </c>
     </row>
     <row r="301">
@@ -13930,22 +13930,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M305" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N305" t="n">
         <v>10977.27</v>
       </c>
       <c r="O305" t="n">
-        <v>812317.98</v>
+        <v>746454.36</v>
       </c>
       <c r="P305" t="n">
         <v>17900</v>
       </c>
       <c r="Q305" t="n">
-        <v>1324600</v>
+        <v>1217200</v>
       </c>
     </row>
     <row r="306">
@@ -14028,10 +14028,10 @@
         <v>48</v>
       </c>
       <c r="N307" t="n">
-        <v>1664.360187234</v>
+        <v>1664.359264432</v>
       </c>
       <c r="O307" t="n">
-        <v>79889.28898723199</v>
+        <v>79889.244692736</v>
       </c>
       <c r="P307" t="n">
         <v>2900</v>
@@ -14261,10 +14261,10 @@
         <v>13</v>
       </c>
       <c r="N312" t="n">
-        <v>23521.624776119</v>
+        <v>23878.013030303</v>
       </c>
       <c r="O312" t="n">
-        <v>305781.122089547</v>
+        <v>310414.169393939</v>
       </c>
       <c r="P312" t="n">
         <v>39000</v>
@@ -14307,10 +14307,10 @@
         <v>824</v>
       </c>
       <c r="N313" t="n">
-        <v>1778.4725489051</v>
+        <v>1786.8332290289</v>
       </c>
       <c r="O313" t="n">
-        <v>1465461.380297802</v>
+        <v>1472350.580719813</v>
       </c>
       <c r="P313" t="n">
         <v>4900</v>
@@ -14347,22 +14347,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M314" t="n">
-        <v>720</v>
+        <v>688</v>
       </c>
       <c r="N314" t="n">
         <v>1548</v>
       </c>
       <c r="O314" t="n">
-        <v>1114560</v>
+        <v>1065024</v>
       </c>
       <c r="P314" t="n">
         <v>3900</v>
       </c>
       <c r="Q314" t="n">
-        <v>2808000</v>
+        <v>2683200</v>
       </c>
     </row>
     <row r="315">
@@ -15788,10 +15788,10 @@
         <v>66</v>
       </c>
       <c r="N345" t="n">
-        <v>4917</v>
+        <v>5030.2949308756</v>
       </c>
       <c r="O345" t="n">
-        <v>324522</v>
+        <v>331999.4654377896</v>
       </c>
       <c r="P345" t="n">
         <v>8600</v>
@@ -15975,10 +15975,10 @@
         <v>96</v>
       </c>
       <c r="N349" t="n">
-        <v>8293</v>
+        <v>8329.2139737991</v>
       </c>
       <c r="O349" t="n">
-        <v>796128</v>
+        <v>799604.5414847136</v>
       </c>
       <c r="P349" t="n">
         <v>13500</v>
@@ -16021,10 +16021,10 @@
         <v>102</v>
       </c>
       <c r="N350" t="n">
-        <v>7713</v>
+        <v>7735.3565217391</v>
       </c>
       <c r="O350" t="n">
-        <v>786726</v>
+        <v>789006.3652173881</v>
       </c>
       <c r="P350" t="n">
         <v>12500</v>
@@ -16343,10 +16343,10 @@
         <v>9</v>
       </c>
       <c r="N357" t="n">
-        <v>17644.653275862</v>
+        <v>17644.653166667</v>
       </c>
       <c r="O357" t="n">
-        <v>158801.879482758</v>
+        <v>158801.878500003</v>
       </c>
       <c r="P357" t="n">
         <v>28200</v>
@@ -16383,22 +16383,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M358" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N358" t="n">
         <v>5858</v>
       </c>
       <c r="O358" t="n">
-        <v>123018</v>
+        <v>99586</v>
       </c>
       <c r="P358" t="n">
         <v>9500</v>
       </c>
       <c r="Q358" t="n">
-        <v>199500</v>
+        <v>161500</v>
       </c>
     </row>
     <row r="359">
@@ -16761,10 +16761,10 @@
         <v>324</v>
       </c>
       <c r="N366" t="n">
-        <v>2328.1187507401</v>
+        <v>2328.1187488882</v>
       </c>
       <c r="O366" t="n">
-        <v>754310.4752397924</v>
+        <v>754310.4746397769</v>
       </c>
       <c r="P366" t="n">
         <v>4500</v>
@@ -17307,22 +17307,22 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M378" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N378" t="n">
         <v>17981</v>
       </c>
       <c r="O378" t="n">
-        <v>359620</v>
+        <v>305677</v>
       </c>
       <c r="P378" t="n">
         <v>29900</v>
       </c>
       <c r="Q378" t="n">
-        <v>598000</v>
+        <v>508300</v>
       </c>
     </row>
     <row r="379">
@@ -17405,10 +17405,10 @@
         <v>165</v>
       </c>
       <c r="N380" t="n">
-        <v>4907.8219330289</v>
+        <v>4907.821941896</v>
       </c>
       <c r="O380" t="n">
-        <v>809790.6189497686</v>
+        <v>809790.6204128399</v>
       </c>
       <c r="P380" t="n">
         <v>8200</v>
@@ -17451,10 +17451,10 @@
         <v>30</v>
       </c>
       <c r="N381" t="n">
-        <v>6414</v>
+        <v>6426.7641791045</v>
       </c>
       <c r="O381" t="n">
-        <v>192420</v>
+        <v>192802.925373135</v>
       </c>
       <c r="P381" t="n">
         <v>10900</v>
@@ -17635,10 +17635,10 @@
         <v>289</v>
       </c>
       <c r="N385" t="n">
-        <v>3903.7361538462</v>
+        <v>3903.7361658031</v>
       </c>
       <c r="O385" t="n">
-        <v>1128179.748461552</v>
+        <v>1128179.751917096</v>
       </c>
       <c r="P385" t="n">
         <v>7500</v>
@@ -17854,22 +17854,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M390" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N390" t="n">
         <v>9839</v>
       </c>
       <c r="O390" t="n">
-        <v>147585</v>
+        <v>49195</v>
       </c>
       <c r="P390" t="n">
         <v>16900</v>
       </c>
       <c r="Q390" t="n">
-        <v>253500</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="391">
@@ -18038,22 +18038,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M394" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="N394" t="n">
-        <v>5772</v>
+        <v>5789.4673839946</v>
       </c>
       <c r="O394" t="n">
-        <v>259740</v>
+        <v>156315.6193678542</v>
       </c>
       <c r="P394" t="n">
         <v>9900</v>
       </c>
       <c r="Q394" t="n">
-        <v>445500</v>
+        <v>267300</v>
       </c>
     </row>
     <row r="395">
@@ -18090,10 +18090,10 @@
         <v>44</v>
       </c>
       <c r="N395" t="n">
-        <v>6645</v>
+        <v>6663.0865541644</v>
       </c>
       <c r="O395" t="n">
-        <v>292380</v>
+        <v>293175.8083832336</v>
       </c>
       <c r="P395" t="n">
         <v>10900</v>
@@ -18130,22 +18130,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M396" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N396" t="n">
         <v>27186</v>
       </c>
       <c r="O396" t="n">
-        <v>489348</v>
+        <v>380604</v>
       </c>
       <c r="P396" t="n">
         <v>43900</v>
       </c>
       <c r="Q396" t="n">
-        <v>790200</v>
+        <v>614600</v>
       </c>
     </row>
     <row r="397">
@@ -18182,10 +18182,10 @@
         <v>157</v>
       </c>
       <c r="N397" t="n">
-        <v>3898</v>
+        <v>3913.1437451437</v>
       </c>
       <c r="O397" t="n">
-        <v>611986</v>
+        <v>614363.5679875609</v>
       </c>
       <c r="P397" t="n">
         <v>6900</v>
@@ -18406,22 +18406,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M402" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="N402" t="n">
         <v>16086</v>
       </c>
       <c r="O402" t="n">
-        <v>450408</v>
+        <v>369978</v>
       </c>
       <c r="P402" t="n">
         <v>25900</v>
       </c>
       <c r="Q402" t="n">
-        <v>725200</v>
+        <v>595700</v>
       </c>
     </row>
     <row r="403">
@@ -18498,22 +18498,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M404" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N404" t="n">
         <v>23439</v>
       </c>
       <c r="O404" t="n">
-        <v>468780</v>
+        <v>375024</v>
       </c>
       <c r="P404" t="n">
         <v>37900</v>
       </c>
       <c r="Q404" t="n">
-        <v>758000</v>
+        <v>606400</v>
       </c>
     </row>
     <row r="405">
@@ -19100,10 +19100,10 @@
         <v>12</v>
       </c>
       <c r="N417" t="n">
-        <v>27254</v>
+        <v>27323.703324808</v>
       </c>
       <c r="O417" t="n">
-        <v>327048</v>
+        <v>327884.439897696</v>
       </c>
       <c r="P417" t="n">
         <v>43900</v>
@@ -19278,22 +19278,22 @@
         <v>0</v>
       </c>
       <c r="L421" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M421" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N421" t="n">
-        <v>3639.35</v>
+        <v>3659.324478595</v>
       </c>
       <c r="O421" t="n">
-        <v>436722</v>
+        <v>420822.315038425</v>
       </c>
       <c r="P421" t="n">
         <v>7500</v>
       </c>
       <c r="Q421" t="n">
-        <v>900000</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="422">
@@ -19324,22 +19324,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M422" t="n">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="N422" t="n">
         <v>1326</v>
       </c>
       <c r="O422" t="n">
-        <v>3159858</v>
+        <v>3157206</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
       </c>
       <c r="Q422" t="n">
-        <v>5957500</v>
+        <v>5952500</v>
       </c>
     </row>
     <row r="423">
@@ -19376,10 +19376,10 @@
         <v>36</v>
       </c>
       <c r="N423" t="n">
-        <v>5640</v>
+        <v>5732.1568627451</v>
       </c>
       <c r="O423" t="n">
-        <v>203040</v>
+        <v>206357.6470588236</v>
       </c>
       <c r="P423" t="n">
         <v>9900</v>
@@ -19416,22 +19416,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M424" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N424" t="n">
         <v>10713.21</v>
       </c>
       <c r="O424" t="n">
-        <v>160698.15</v>
+        <v>74992.47</v>
       </c>
       <c r="P424" t="n">
         <v>20900</v>
       </c>
       <c r="Q424" t="n">
-        <v>313500</v>
+        <v>146300</v>
       </c>
     </row>
     <row r="425">
@@ -19652,10 +19652,10 @@
         <v>1126</v>
       </c>
       <c r="N429" t="n">
-        <v>3821</v>
+        <v>3828.7583756345</v>
       </c>
       <c r="O429" t="n">
-        <v>4302446</v>
+        <v>4311181.930964448</v>
       </c>
       <c r="P429" t="n">
         <v>5900</v>
@@ -19928,10 +19928,10 @@
         <v>1320</v>
       </c>
       <c r="N435" t="n">
-        <v>1516.0388129219</v>
+        <v>1517.7951815022</v>
       </c>
       <c r="O435" t="n">
-        <v>2001171.233056908</v>
+        <v>2003489.639582904</v>
       </c>
       <c r="P435" t="n">
         <v>2300</v>
@@ -20020,10 +20020,10 @@
         <v>8</v>
       </c>
       <c r="N437" t="n">
-        <v>4248.6214117647</v>
+        <v>4248.6224691358</v>
       </c>
       <c r="O437" t="n">
-        <v>33988.9712941176</v>
+        <v>33988.9797530864</v>
       </c>
       <c r="P437" t="n">
         <v>5900</v>
@@ -20066,10 +20066,10 @@
         <v>120</v>
       </c>
       <c r="N438" t="n">
-        <v>2458.5134204724</v>
+        <v>2458.5134059343</v>
       </c>
       <c r="O438" t="n">
-        <v>295021.610456688</v>
+        <v>295021.608712116</v>
       </c>
       <c r="P438" t="n">
         <v>3500</v>
@@ -20112,10 +20112,10 @@
         <v>192</v>
       </c>
       <c r="N439" t="n">
-        <v>1771.0912628399</v>
+        <v>1771.0911342735</v>
       </c>
       <c r="O439" t="n">
-        <v>340049.5224652608</v>
+        <v>340049.497780512</v>
       </c>
       <c r="P439" t="n">
         <v>2500</v>
@@ -20158,10 +20158,10 @@
         <v>264</v>
       </c>
       <c r="N440" t="n">
-        <v>2079.384205911</v>
+        <v>2079.3842021449</v>
       </c>
       <c r="O440" t="n">
-        <v>548957.4303605041</v>
+        <v>548957.4293662535</v>
       </c>
       <c r="P440" t="n">
         <v>2900</v>
@@ -20204,10 +20204,10 @@
         <v>192</v>
       </c>
       <c r="N441" t="n">
-        <v>1803.0150073855</v>
+        <v>1803.0151441578</v>
       </c>
       <c r="O441" t="n">
-        <v>346178.881418016</v>
+        <v>346178.9076782976</v>
       </c>
       <c r="P441" t="n">
         <v>2500</v>
@@ -20250,10 +20250,10 @@
         <v>216</v>
       </c>
       <c r="N442" t="n">
-        <v>3306.5954372624</v>
+        <v>3306.5953548387</v>
       </c>
       <c r="O442" t="n">
-        <v>714224.6144486784</v>
+        <v>714224.5966451592</v>
       </c>
       <c r="P442" t="n">
         <v>4900</v>
@@ -20296,10 +20296,10 @@
         <v>192</v>
       </c>
       <c r="N443" t="n">
-        <v>2122.1640959855</v>
+        <v>2126.0638621746</v>
       </c>
       <c r="O443" t="n">
-        <v>407455.506429216</v>
+        <v>408204.2615375232</v>
       </c>
       <c r="P443" t="n">
         <v>2900</v>
@@ -20342,10 +20342,10 @@
         <v>216</v>
       </c>
       <c r="N444" t="n">
-        <v>2108.7899091941</v>
+        <v>2108.7899828473</v>
       </c>
       <c r="O444" t="n">
-        <v>455498.6203859256</v>
+        <v>455498.6362950168</v>
       </c>
       <c r="P444" t="n">
         <v>2900</v>
@@ -20388,10 +20388,10 @@
         <v>144</v>
       </c>
       <c r="N445" t="n">
-        <v>2056.083871734</v>
+        <v>2059.7554464286</v>
       </c>
       <c r="O445" t="n">
-        <v>296076.077529696</v>
+        <v>296604.7842857184</v>
       </c>
       <c r="P445" t="n">
         <v>2900</v>
@@ -20434,10 +20434,10 @@
         <v>216</v>
       </c>
       <c r="N446" t="n">
-        <v>3224.5680666967</v>
+        <v>3224.5682755432</v>
       </c>
       <c r="O446" t="n">
-        <v>696506.7024064872</v>
+        <v>696506.7475173312</v>
       </c>
       <c r="P446" t="n">
         <v>4500</v>
@@ -20480,10 +20480,10 @@
         <v>360</v>
       </c>
       <c r="N447" t="n">
-        <v>1655.9312964128</v>
+        <v>1657.5320592975</v>
       </c>
       <c r="O447" t="n">
-        <v>596135.266708608</v>
+        <v>596711.5413470999</v>
       </c>
       <c r="P447" t="n">
         <v>2500</v>
@@ -20710,10 +20710,10 @@
         <v>400</v>
       </c>
       <c r="N452" t="n">
-        <v>1592.2752659892</v>
+        <v>1592.2754925187</v>
       </c>
       <c r="O452" t="n">
-        <v>636910.10639568</v>
+        <v>636910.1970074801</v>
       </c>
       <c r="P452" t="n">
         <v>2500</v>
@@ -20795,10 +20795,10 @@
         <v>8</v>
       </c>
       <c r="N454" t="n">
-        <v>5347.73</v>
+        <v>5393.6332618026</v>
       </c>
       <c r="O454" t="n">
-        <v>42781.84</v>
+        <v>43149.0660944208</v>
       </c>
       <c r="P454" t="n">
         <v>9500</v>
@@ -20841,10 +20841,10 @@
         <v>12</v>
       </c>
       <c r="N455" t="n">
-        <v>2311.9257410562</v>
+        <v>2311.9248916968</v>
       </c>
       <c r="O455" t="n">
-        <v>27743.1088926744</v>
+        <v>27743.0987003616</v>
       </c>
       <c r="P455" t="n">
         <v>3500</v>
@@ -20887,10 +20887,10 @@
         <v>48</v>
       </c>
       <c r="N456" t="n">
-        <v>1906.1864705882</v>
+        <v>1906.1862686567</v>
       </c>
       <c r="O456" t="n">
-        <v>91496.95058823361</v>
+        <v>91496.94089552159</v>
       </c>
       <c r="P456" t="n">
         <v>2900</v>
@@ -20933,10 +20933,10 @@
         <v>120</v>
       </c>
       <c r="N457" t="n">
-        <v>3033.7307083333</v>
+        <v>3033.7296483516</v>
       </c>
       <c r="O457" t="n">
-        <v>364047.684999996</v>
+        <v>364047.5578021921</v>
       </c>
       <c r="P457" t="n">
         <v>4500</v>
@@ -20979,10 +20979,10 @@
         <v>408</v>
       </c>
       <c r="N458" t="n">
-        <v>2060.1606493506</v>
+        <v>2060.1606035889</v>
       </c>
       <c r="O458" t="n">
-        <v>840545.5449350448</v>
+        <v>840545.5262642711</v>
       </c>
       <c r="P458" t="n">
         <v>2900</v>
@@ -21025,10 +21025,10 @@
         <v>72</v>
       </c>
       <c r="N459" t="n">
-        <v>1668.6165143824</v>
+        <v>1668.6186615679</v>
       </c>
       <c r="O459" t="n">
-        <v>120140.3890355328</v>
+        <v>120140.5436328888</v>
       </c>
       <c r="P459" t="n">
         <v>2500</v>
@@ -21071,10 +21071,10 @@
         <v>72</v>
       </c>
       <c r="N460" t="n">
-        <v>2546.9851535836</v>
+        <v>2546.9851286449</v>
       </c>
       <c r="O460" t="n">
-        <v>183382.9310580192</v>
+        <v>183382.9292624328</v>
       </c>
       <c r="P460" t="n">
         <v>3900</v>
@@ -21117,10 +21117,10 @@
         <v>800</v>
       </c>
       <c r="N461" t="n">
-        <v>1259.2744247206</v>
+        <v>1259.2744276316</v>
       </c>
       <c r="O461" t="n">
-        <v>1007419.53977648</v>
+        <v>1007419.54210528</v>
       </c>
       <c r="P461" t="n">
         <v>1900</v>
@@ -21204,10 +21204,10 @@
         <v>97</v>
       </c>
       <c r="N463" t="n">
-        <v>2842.2737735849</v>
+        <v>2851.2399369085</v>
       </c>
       <c r="O463" t="n">
-        <v>275700.5560377353</v>
+        <v>276570.2738801245</v>
       </c>
       <c r="P463" t="n">
         <v>4900</v>
@@ -21250,10 +21250,10 @@
         <v>72</v>
       </c>
       <c r="N464" t="n">
-        <v>2556.7450581395</v>
+        <v>2556.7452252252</v>
       </c>
       <c r="O464" t="n">
-        <v>184085.644186044</v>
+        <v>184085.6562162144</v>
       </c>
       <c r="P464" t="n">
         <v>3900</v>
@@ -21296,10 +21296,10 @@
         <v>10080</v>
       </c>
       <c r="N465" t="n">
-        <v>1801</v>
+        <v>1803.2544202785</v>
       </c>
       <c r="O465" t="n">
-        <v>18154080</v>
+        <v>18176804.55640728</v>
       </c>
       <c r="P465" t="n">
         <v>2900</v>
@@ -21334,22 +21334,22 @@
         <v>0</v>
       </c>
       <c r="L466" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M466" t="n">
-        <v>660</v>
+        <v>540</v>
       </c>
       <c r="N466" t="n">
-        <v>692.15206356312</v>
+        <v>692.15208975521</v>
       </c>
       <c r="O466" t="n">
-        <v>456820.3619516592</v>
+        <v>373762.1284678134</v>
       </c>
       <c r="P466" t="n">
         <v>1200</v>
       </c>
       <c r="Q466" t="n">
-        <v>792000</v>
+        <v>648000</v>
       </c>
     </row>
     <row r="467">
@@ -21609,22 +21609,22 @@
         <v>0</v>
       </c>
       <c r="L472" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M472" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="N472" t="n">
         <v>15423.36</v>
       </c>
       <c r="O472" t="n">
-        <v>863708.16</v>
+        <v>771168</v>
       </c>
       <c r="P472" t="n">
         <v>24900</v>
       </c>
       <c r="Q472" t="n">
-        <v>1394400</v>
+        <v>1245000</v>
       </c>
     </row>
     <row r="473">
@@ -21800,10 +21800,10 @@
         <v>248</v>
       </c>
       <c r="N476" t="n">
-        <v>2857.22</v>
+        <v>2865.3179310345</v>
       </c>
       <c r="O476" t="n">
-        <v>708590.5599999999</v>
+        <v>710598.846896556</v>
       </c>
       <c r="P476" t="n">
         <v>4900</v>
@@ -21849,10 +21849,10 @@
         <v>913</v>
       </c>
       <c r="N477" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O477" t="n">
-        <v>8167131.939999999</v>
+        <v>8169514.764781954</v>
       </c>
       <c r="P477" t="n">
         <v>14900</v>
@@ -22037,10 +22037,10 @@
         <v>360</v>
       </c>
       <c r="N481" t="n">
-        <v>1530.4499204138</v>
+        <v>1530.4499206034</v>
       </c>
       <c r="O481" t="n">
-        <v>550961.971348968</v>
+        <v>550961.971417224</v>
       </c>
       <c r="P481" t="n">
         <v>2600</v>
@@ -22496,10 +22496,10 @@
         <v>306</v>
       </c>
       <c r="N491" t="n">
-        <v>1690.8700089286</v>
+        <v>1690.8700089526</v>
       </c>
       <c r="O491" t="n">
-        <v>517406.2227321516</v>
+        <v>517406.2227394956</v>
       </c>
       <c r="P491" t="n">
         <v>3000</v>
@@ -22588,22 +22588,22 @@
         <v>0</v>
       </c>
       <c r="L493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M493" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N493" t="n">
         <v>6090.22</v>
       </c>
       <c r="O493" t="n">
-        <v>371503.42</v>
+        <v>365413.2</v>
       </c>
       <c r="P493" t="n">
         <v>8500</v>
       </c>
       <c r="Q493" t="n">
-        <v>518500</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="494">
@@ -23053,22 +23053,22 @@
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M503" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N503" t="n">
         <v>6213.51</v>
       </c>
       <c r="O503" t="n">
-        <v>93202.65000000001</v>
+        <v>0</v>
       </c>
       <c r="P503" t="n">
         <v>10300</v>
       </c>
       <c r="Q503" t="n">
-        <v>154500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504">
@@ -23383,10 +23383,10 @@
         <v>749</v>
       </c>
       <c r="N510" t="n">
-        <v>517.2878865955601</v>
+        <v>523.15541944326</v>
       </c>
       <c r="O510" t="n">
-        <v>387448.6270600745</v>
+        <v>391843.4091630018</v>
       </c>
       <c r="P510" t="n">
         <v>900</v>
@@ -23806,10 +23806,10 @@
         <v>757</v>
       </c>
       <c r="N519" t="n">
-        <v>3110.8429819337</v>
+        <v>3110.8429525518</v>
       </c>
       <c r="O519" t="n">
-        <v>2354908.137323811</v>
+        <v>2354908.115081713</v>
       </c>
       <c r="P519" t="n">
         <v>4500</v>
@@ -24257,10 +24257,10 @@
         <v>20090</v>
       </c>
       <c r="N529" t="n">
-        <v>703.79538564105</v>
+        <v>703.79534416571</v>
       </c>
       <c r="O529" t="n">
-        <v>14139249.29752869</v>
+        <v>14139248.46428912</v>
       </c>
       <c r="P529" t="n">
         <v>900</v>
@@ -24764,10 +24764,10 @@
         <v>47</v>
       </c>
       <c r="N540" t="n">
-        <v>1595.5190941049</v>
+        <v>1595.5190882035</v>
       </c>
       <c r="O540" t="n">
-        <v>74989.3974229303</v>
+        <v>74989.39714556449</v>
       </c>
       <c r="P540" t="n">
         <v>2500</v>
@@ -25387,22 +25387,22 @@
         <v>0</v>
       </c>
       <c r="L553" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M553" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N553" t="n">
         <v>16313.41</v>
       </c>
       <c r="O553" t="n">
-        <v>179447.51</v>
+        <v>163134.1</v>
       </c>
       <c r="P553" t="n">
         <v>33500</v>
       </c>
       <c r="Q553" t="n">
-        <v>368500</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="554">
@@ -25724,22 +25724,22 @@
         <v>0</v>
       </c>
       <c r="L560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M560" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N560" t="n">
         <v>12837.03</v>
       </c>
       <c r="O560" t="n">
-        <v>256740.6</v>
+        <v>243903.57</v>
       </c>
       <c r="P560" t="n">
         <v>15500</v>
       </c>
       <c r="Q560" t="n">
-        <v>310000</v>
+        <v>294500</v>
       </c>
     </row>
     <row r="561">
@@ -25871,22 +25871,22 @@
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M563" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N563" t="n">
         <v>10084.09</v>
       </c>
       <c r="O563" t="n">
-        <v>191597.71</v>
+        <v>131093.17</v>
       </c>
       <c r="P563" t="n">
         <v>17900</v>
       </c>
       <c r="Q563" t="n">
-        <v>340100</v>
+        <v>232700</v>
       </c>
     </row>
     <row r="564">
@@ -25920,22 +25920,22 @@
         <v>0</v>
       </c>
       <c r="L564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M564" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N564" t="n">
         <v>7230.04</v>
       </c>
       <c r="O564" t="n">
-        <v>224131.24</v>
+        <v>216901.2</v>
       </c>
       <c r="P564" t="n">
         <v>15900</v>
       </c>
       <c r="Q564" t="n">
-        <v>492900</v>
+        <v>477000</v>
       </c>
     </row>
     <row r="565">
@@ -26064,22 +26064,22 @@
         <v>0</v>
       </c>
       <c r="L567" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M567" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N567" t="n">
         <v>9746.880188679201</v>
       </c>
       <c r="O567" t="n">
-        <v>243672.00471698</v>
+        <v>185190.7235849048</v>
       </c>
       <c r="P567" t="n">
         <v>18500</v>
       </c>
       <c r="Q567" t="n">
-        <v>462500</v>
+        <v>351500</v>
       </c>
     </row>
     <row r="568">
@@ -26162,22 +26162,22 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M569" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N569" t="n">
         <v>2672.89</v>
       </c>
       <c r="O569" t="n">
-        <v>943530.1699999999</v>
+        <v>938184.3899999999</v>
       </c>
       <c r="P569" t="n">
         <v>10200</v>
       </c>
       <c r="Q569" t="n">
-        <v>3600600</v>
+        <v>3580200</v>
       </c>
     </row>
     <row r="570">
@@ -26211,22 +26211,22 @@
         <v>0</v>
       </c>
       <c r="L570" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M570" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N570" t="n">
         <v>4795.69</v>
       </c>
       <c r="O570" t="n">
-        <v>1194126.81</v>
+        <v>1184535.43</v>
       </c>
       <c r="P570" t="n">
         <v>10200</v>
       </c>
       <c r="Q570" t="n">
-        <v>2539800</v>
+        <v>2519400</v>
       </c>
     </row>
     <row r="571">
@@ -26315,10 +26315,10 @@
         <v>35</v>
       </c>
       <c r="N572" t="n">
-        <v>2992.5687209302</v>
+        <v>2992.5688235294</v>
       </c>
       <c r="O572" t="n">
-        <v>104739.905232557</v>
+        <v>104739.908823529</v>
       </c>
       <c r="P572" t="n">
         <v>6000</v>
@@ -26930,10 +26930,10 @@
         <v>341</v>
       </c>
       <c r="N585" t="n">
-        <v>3499.72</v>
+        <v>3516.3655172414</v>
       </c>
       <c r="O585" t="n">
-        <v>1193404.52</v>
+        <v>1199080.641379318</v>
       </c>
       <c r="P585" t="n">
         <v>6900</v>
@@ -26979,10 +26979,10 @@
         <v>323</v>
       </c>
       <c r="N586" t="n">
-        <v>5347.88</v>
+        <v>5377.3043741403</v>
       </c>
       <c r="O586" t="n">
-        <v>1727365.24</v>
+        <v>1736869.312847317</v>
       </c>
       <c r="P586" t="n">
         <v>7900</v>
@@ -27028,10 +27028,10 @@
         <v>292</v>
       </c>
       <c r="N587" t="n">
-        <v>4578.04</v>
+        <v>4597.9229098806</v>
       </c>
       <c r="O587" t="n">
-        <v>1336787.68</v>
+        <v>1342593.489685135</v>
       </c>
       <c r="P587" t="n">
         <v>7500</v>
@@ -27602,10 +27602,10 @@
         <v>24</v>
       </c>
       <c r="N599" t="n">
-        <v>10737.526666667</v>
+        <v>11369.145882353</v>
       </c>
       <c r="O599" t="n">
-        <v>257700.640000008</v>
+        <v>272859.501176472</v>
       </c>
       <c r="P599" t="n">
         <v>18900</v>
@@ -29017,10 +29017,10 @@
         <v>648</v>
       </c>
       <c r="N629" t="n">
-        <v>665.32334188034</v>
+        <v>665.32342381786</v>
       </c>
       <c r="O629" t="n">
-        <v>431129.5255384603</v>
+        <v>431129.5786339733</v>
       </c>
       <c r="P629" t="n">
         <v>2900</v>
@@ -30011,10 +30011,10 @@
         <v>831</v>
       </c>
       <c r="N651" t="n">
-        <v>3181.9</v>
+        <v>3209.0377398721</v>
       </c>
       <c r="O651" t="n">
-        <v>2644158.9</v>
+        <v>2666710.361833715</v>
       </c>
       <c r="P651" t="n">
         <v>5100</v>
@@ -30052,10 +30052,10 @@
         <v>4</v>
       </c>
       <c r="N652" t="n">
-        <v>1213.6821442495</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O652" t="n">
-        <v>4854.728576998</v>
+        <v>4854.728477842</v>
       </c>
       <c r="P652" t="n">
         <v>1500</v>
@@ -30096,10 +30096,10 @@
         <v>450</v>
       </c>
       <c r="N653" t="n">
-        <v>1794.2879767875</v>
+        <v>1794.2879750466</v>
       </c>
       <c r="O653" t="n">
-        <v>807429.5895543749</v>
+        <v>807429.58877097</v>
       </c>
       <c r="P653" t="n">
         <v>1600</v>
@@ -30684,22 +30684,22 @@
         <v>0</v>
       </c>
       <c r="L666" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M666" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="N666" t="n">
         <v>1757.3205360825</v>
       </c>
       <c r="O666" t="n">
-        <v>544769.366185575</v>
+        <v>537740.084041245</v>
       </c>
       <c r="P666" t="n">
         <v>2000</v>
       </c>
       <c r="Q666" t="n">
-        <v>620000</v>
+        <v>612000</v>
       </c>
     </row>
     <row r="667">
@@ -30730,22 +30730,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M667" t="n">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N667" t="n">
         <v>1561.33</v>
       </c>
       <c r="O667" t="n">
-        <v>551149.49</v>
+        <v>541781.51</v>
       </c>
       <c r="P667" t="n">
         <v>2000</v>
       </c>
       <c r="Q667" t="n">
-        <v>706000</v>
+        <v>694000</v>
       </c>
     </row>
     <row r="668">
@@ -30828,10 +30828,10 @@
         <v>4400</v>
       </c>
       <c r="N669" t="n">
-        <v>220.00820587826</v>
+        <v>220.00803927108</v>
       </c>
       <c r="O669" t="n">
-        <v>968036.1058643439</v>
+        <v>968035.372792752</v>
       </c>
       <c r="P669" t="n">
         <v>260</v>
@@ -31098,22 +31098,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M675" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N675" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O675" t="n">
-        <v>194163.8</v>
+        <v>184455.61</v>
       </c>
       <c r="P675" t="n">
         <v>10200</v>
       </c>
       <c r="Q675" t="n">
-        <v>204000</v>
+        <v>193800</v>
       </c>
     </row>
     <row r="676">
@@ -31190,22 +31190,22 @@
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M677" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="N677" t="n">
         <v>1952.41</v>
       </c>
       <c r="O677" t="n">
-        <v>359243.44</v>
+        <v>353386.21</v>
       </c>
       <c r="P677" t="n">
         <v>2700</v>
       </c>
       <c r="Q677" t="n">
-        <v>496800</v>
+        <v>488700</v>
       </c>
     </row>
     <row r="678">
@@ -31472,10 +31472,10 @@
         <v>12</v>
       </c>
       <c r="N683" t="n">
-        <v>1129.14</v>
+        <v>1151.172</v>
       </c>
       <c r="O683" t="n">
-        <v>13549.68</v>
+        <v>13814.064</v>
       </c>
       <c r="P683" t="n">
         <v>6900</v>
@@ -31512,22 +31512,22 @@
         <v>0</v>
       </c>
       <c r="L684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M684" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N684" t="n">
         <v>11433.53</v>
       </c>
       <c r="O684" t="n">
-        <v>137202.36</v>
+        <v>125768.83</v>
       </c>
       <c r="P684" t="n">
         <v>15000</v>
       </c>
       <c r="Q684" t="n">
-        <v>180000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="685">
@@ -31763,10 +31763,10 @@
         <v>18</v>
       </c>
       <c r="N689" t="n">
-        <v>2432.1341071429</v>
+        <v>2432.1345098039</v>
       </c>
       <c r="O689" t="n">
-        <v>43778.4139285722</v>
+        <v>43778.4211764702</v>
       </c>
       <c r="P689" t="n">
         <v>4500</v>
@@ -31947,10 +31947,10 @@
         <v>115</v>
       </c>
       <c r="N693" t="n">
-        <v>3306.00983</v>
+        <v>3306.0098310139</v>
       </c>
       <c r="O693" t="n">
-        <v>380191.13045</v>
+        <v>380191.1305665985</v>
       </c>
       <c r="P693" t="n">
         <v>4200</v>
@@ -32177,10 +32177,10 @@
         <v>10</v>
       </c>
       <c r="N698" t="n">
-        <v>3732.8784810127</v>
+        <v>3732.8777027027</v>
       </c>
       <c r="O698" t="n">
-        <v>37328.784810127</v>
+        <v>37328.777027027</v>
       </c>
       <c r="P698" t="n">
         <v>4500</v>
@@ -32217,22 +32217,22 @@
         <v>0</v>
       </c>
       <c r="L699" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M699" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N699" t="n">
         <v>24780.39</v>
       </c>
       <c r="O699" t="n">
-        <v>247803.9</v>
+        <v>0</v>
       </c>
       <c r="P699" t="n">
         <v>31500</v>
       </c>
       <c r="Q699" t="n">
-        <v>315000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="700">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>87</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3044243338</v>
+        <v>1811.3044829343</v>
       </c>
       <c r="O6" t="n">
-        <v>157583.4849170406</v>
+        <v>157583.4900152841</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7465014893</v>
+        <v>3376.746498645</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.907316541</v>
+        <v>2985043.90480218</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1354,10 +1354,10 @@
         <v>92</v>
       </c>
       <c r="N24" t="n">
-        <v>2413.001059322</v>
+        <v>2413.0010615711</v>
       </c>
       <c r="O24" t="n">
-        <v>221996.097457624</v>
+        <v>221996.0976645412</v>
       </c>
       <c r="P24" t="n">
         <v>4700</v>
@@ -1393,10 +1393,10 @@
         <v>102</v>
       </c>
       <c r="N25" t="n">
-        <v>2474.7042140468</v>
+        <v>2474.7042043551</v>
       </c>
       <c r="O25" t="n">
-        <v>252419.8298327736</v>
+        <v>252419.8288442202</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -2259,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>200072.19992308</v>
+        <v>200072.2</v>
       </c>
       <c r="O46" t="n">
-        <v>1400505.39946156</v>
+        <v>1400505.4</v>
       </c>
       <c r="P46" t="n">
         <v>312000</v>
@@ -3129,10 +3129,10 @@
         <v>228</v>
       </c>
       <c r="N66" t="n">
-        <v>4937.3101608187</v>
+        <v>4937.3101611722</v>
       </c>
       <c r="O66" t="n">
-        <v>1125706.716666664</v>
+        <v>1125706.716747262</v>
       </c>
       <c r="P66" t="n">
         <v>7500</v>
@@ -3385,22 +3385,22 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M72" t="n">
-        <v>1727</v>
+        <v>1583</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0548595108</v>
+        <v>1098.0555939754</v>
       </c>
       <c r="O72" t="n">
-        <v>1896340.742375152</v>
+        <v>1738222.005263058</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
       </c>
       <c r="Q72" t="n">
-        <v>2590500</v>
+        <v>2374500</v>
       </c>
     </row>
     <row r="73">
@@ -4324,10 +4324,10 @@
         <v>771</v>
       </c>
       <c r="N93" t="n">
-        <v>2582.2560231583</v>
+        <v>2582.2560112135</v>
       </c>
       <c r="O93" t="n">
-        <v>1990919.39385505</v>
+        <v>1990919.384645609</v>
       </c>
       <c r="P93" t="n">
         <v>4500</v>
@@ -4462,10 +4462,10 @@
         <v>720</v>
       </c>
       <c r="N96" t="n">
-        <v>5216.8959678619</v>
+        <v>5216.8959654608</v>
       </c>
       <c r="O96" t="n">
-        <v>3756165.096860568</v>
+        <v>3756165.095131776</v>
       </c>
       <c r="P96" t="n">
         <v>8500</v>
@@ -4693,10 +4693,10 @@
         <v>3199</v>
       </c>
       <c r="N101" t="n">
-        <v>3158.8608147003</v>
+        <v>3158.860814779</v>
       </c>
       <c r="O101" t="n">
-        <v>10105195.74622626</v>
+        <v>10105195.74647802</v>
       </c>
       <c r="P101" t="n">
         <v>5600</v>
@@ -4739,10 +4739,10 @@
         <v>80</v>
       </c>
       <c r="N102" t="n">
-        <v>3841.6247184466</v>
+        <v>3841.6247414634</v>
       </c>
       <c r="O102" t="n">
-        <v>307329.977475728</v>
+        <v>307329.979317072</v>
       </c>
       <c r="P102" t="n">
         <v>6900</v>
@@ -4829,10 +4829,10 @@
         <v>180</v>
       </c>
       <c r="N104" t="n">
-        <v>3230.067752443</v>
+        <v>3230.0677414075</v>
       </c>
       <c r="O104" t="n">
-        <v>581412.19543974</v>
+        <v>581412.19345335</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -5513,10 +5513,10 @@
         <v>318</v>
       </c>
       <c r="N119" t="n">
-        <v>4890.9300463499</v>
+        <v>4890.9300464306</v>
       </c>
       <c r="O119" t="n">
-        <v>1555315.754739268</v>
+        <v>1555315.754764931</v>
       </c>
       <c r="P119" t="n">
         <v>8200</v>
@@ -5957,22 +5957,22 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M129" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N129" t="n">
         <v>10716.34</v>
       </c>
       <c r="O129" t="n">
-        <v>439369.94</v>
+        <v>375071.9</v>
       </c>
       <c r="P129" t="n">
         <v>39000</v>
       </c>
       <c r="Q129" t="n">
-        <v>1599000</v>
+        <v>1365000</v>
       </c>
     </row>
     <row r="130">
@@ -6012,10 +6012,10 @@
         <v>288</v>
       </c>
       <c r="N130" t="n">
-        <v>3594.25414277</v>
+        <v>3594.2541391941</v>
       </c>
       <c r="O130" t="n">
-        <v>1035145.19311776</v>
+        <v>1035145.192087901</v>
       </c>
       <c r="P130" t="n">
         <v>6500</v>
@@ -6053,10 +6053,10 @@
         <v>108</v>
       </c>
       <c r="N131" t="n">
-        <v>3240.850029985</v>
+        <v>3240.8500301659</v>
       </c>
       <c r="O131" t="n">
-        <v>350011.80323838</v>
+        <v>350011.8032579172</v>
       </c>
       <c r="P131" t="n">
         <v>5200</v>
@@ -6237,10 +6237,10 @@
         <v>305</v>
       </c>
       <c r="N135" t="n">
-        <v>14822.378863905</v>
+        <v>14822.378862559</v>
       </c>
       <c r="O135" t="n">
-        <v>4520825.553491025</v>
+        <v>4520825.553080495</v>
       </c>
       <c r="P135" t="n">
         <v>24900</v>
@@ -6646,10 +6646,10 @@
         <v>43</v>
       </c>
       <c r="N144" t="n">
-        <v>12267.650645161</v>
+        <v>12267.65043956</v>
       </c>
       <c r="O144" t="n">
-        <v>527508.9777419231</v>
+        <v>527508.96890108</v>
       </c>
       <c r="P144" t="n">
         <v>19900</v>
@@ -6962,10 +6962,10 @@
         <v>210</v>
       </c>
       <c r="N151" t="n">
-        <v>3041.6600125945</v>
+        <v>3041.6600126502</v>
       </c>
       <c r="O151" t="n">
-        <v>638748.602644845</v>
+        <v>638748.602656542</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -7090,10 +7090,10 @@
         <v>1945</v>
       </c>
       <c r="N154" t="n">
-        <v>4372.2107876031</v>
+        <v>4372.2107877711</v>
       </c>
       <c r="O154" t="n">
-        <v>8503949.981888028</v>
+        <v>8503949.982214788</v>
       </c>
       <c r="P154" t="n">
         <v>7500</v>
@@ -7174,22 +7174,22 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M156" t="n">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="N156" t="n">
-        <v>1592.567520267</v>
+        <v>1592.5674522293</v>
       </c>
       <c r="O156" t="n">
-        <v>793098.625092966</v>
+        <v>764432.377070064</v>
       </c>
       <c r="P156" t="n">
         <v>3900</v>
       </c>
       <c r="Q156" t="n">
-        <v>1942200</v>
+        <v>1872000</v>
       </c>
     </row>
     <row r="157">
@@ -8170,10 +8170,10 @@
         <v>71</v>
       </c>
       <c r="N178" t="n">
-        <v>2021.7211218335</v>
+        <v>2021.7211225106</v>
       </c>
       <c r="O178" t="n">
-        <v>143542.1996501785</v>
+        <v>143542.1996982526</v>
       </c>
       <c r="P178" t="n">
         <v>2400</v>
@@ -8971,10 +8971,10 @@
         <v>824</v>
       </c>
       <c r="N195" t="n">
-        <v>1630.923147125</v>
+        <v>1630.9231587595</v>
       </c>
       <c r="O195" t="n">
-        <v>1343880.673231</v>
+        <v>1343880.682817828</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9063,10 +9063,10 @@
         <v>384</v>
       </c>
       <c r="N197" t="n">
-        <v>1690.6028354857</v>
+        <v>1690.6026503973</v>
       </c>
       <c r="O197" t="n">
-        <v>649191.4888265089</v>
+        <v>649191.4177525633</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9109,10 +9109,10 @@
         <v>2118</v>
       </c>
       <c r="N198" t="n">
-        <v>1550.1931350849</v>
+        <v>1550.1931558806</v>
       </c>
       <c r="O198" t="n">
-        <v>3283309.060109818</v>
+        <v>3283309.104155111</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
@@ -9155,10 +9155,10 @@
         <v>22</v>
       </c>
       <c r="N199" t="n">
-        <v>1579.3910473815</v>
+        <v>1579.391025</v>
       </c>
       <c r="O199" t="n">
-        <v>34746.603042393</v>
+        <v>34746.60255</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
@@ -9201,10 +9201,10 @@
         <v>454</v>
       </c>
       <c r="N200" t="n">
-        <v>2403.5103430475</v>
+        <v>2403.5103724115</v>
       </c>
       <c r="O200" t="n">
-        <v>1091193.695743565</v>
+        <v>1091193.709074821</v>
       </c>
       <c r="P200" t="n">
         <v>3500</v>
@@ -9247,10 +9247,10 @@
         <v>80</v>
       </c>
       <c r="N201" t="n">
-        <v>2521.5446987952</v>
+        <v>2521.5439240506</v>
       </c>
       <c r="O201" t="n">
-        <v>201723.575903616</v>
+        <v>201723.513924048</v>
       </c>
       <c r="P201" t="n">
         <v>3900</v>
@@ -10459,10 +10459,10 @@
         <v>19</v>
       </c>
       <c r="N228" t="n">
-        <v>7537.4721641791</v>
+        <v>7537.4721804511</v>
       </c>
       <c r="O228" t="n">
-        <v>143211.9711194029</v>
+        <v>143211.9714285709</v>
       </c>
       <c r="P228" t="n">
         <v>8900</v>
@@ -12172,10 +12172,10 @@
         <v>599</v>
       </c>
       <c r="N267" t="n">
-        <v>1560.999261745</v>
+        <v>1560.9993877551</v>
       </c>
       <c r="O267" t="n">
-        <v>935038.557785255</v>
+        <v>935038.633265305</v>
       </c>
       <c r="P267" t="n">
         <v>2900</v>
@@ -12495,10 +12495,10 @@
         <v>306</v>
       </c>
       <c r="N274" t="n">
-        <v>548.14728291317</v>
+        <v>548.14725212465</v>
       </c>
       <c r="O274" t="n">
-        <v>167733.06857143</v>
+        <v>167733.0591501429</v>
       </c>
       <c r="P274" t="n">
         <v>2000</v>
@@ -13427,10 +13427,10 @@
         <v>81</v>
       </c>
       <c r="N294" t="n">
-        <v>5218.1705134189</v>
+        <v>5218.1705164319</v>
       </c>
       <c r="O294" t="n">
-        <v>422671.8115869309</v>
+        <v>422671.8118309839</v>
       </c>
       <c r="P294" t="n">
         <v>8500</v>
@@ -13473,10 +13473,10 @@
         <v>1</v>
       </c>
       <c r="N295" t="n">
-        <v>1595.0094571429</v>
+        <v>1595.0094492754</v>
       </c>
       <c r="O295" t="n">
-        <v>1595.0094571429</v>
+        <v>1595.0094492754</v>
       </c>
       <c r="P295" t="n">
         <v>2600</v>
@@ -13884,22 +13884,22 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M304" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N304" t="n">
         <v>10977.27</v>
       </c>
       <c r="O304" t="n">
-        <v>746454.36</v>
+        <v>702545.28</v>
       </c>
       <c r="P304" t="n">
         <v>17900</v>
       </c>
       <c r="Q304" t="n">
-        <v>1217200</v>
+        <v>1145600</v>
       </c>
     </row>
     <row r="305">
@@ -13982,10 +13982,10 @@
         <v>48</v>
       </c>
       <c r="N306" t="n">
-        <v>1664.359264432</v>
+        <v>1664.3592041199</v>
       </c>
       <c r="O306" t="n">
-        <v>79889.244692736</v>
+        <v>79889.2417977552</v>
       </c>
       <c r="P306" t="n">
         <v>2900</v>
@@ -14215,10 +14215,10 @@
         <v>13</v>
       </c>
       <c r="N311" t="n">
-        <v>23521.62469697</v>
+        <v>23521.62453125</v>
       </c>
       <c r="O311" t="n">
-        <v>305781.12106061</v>
+        <v>305781.11890625</v>
       </c>
       <c r="P311" t="n">
         <v>39000</v>
@@ -14261,10 +14261,10 @@
         <v>824</v>
       </c>
       <c r="N312" t="n">
-        <v>1778.4725650066</v>
+        <v>1778.4725680247</v>
       </c>
       <c r="O312" t="n">
-        <v>1465461.393565438</v>
+        <v>1465461.396052353</v>
       </c>
       <c r="P312" t="n">
         <v>4900</v>
@@ -16389,10 +16389,10 @@
         <v>29</v>
       </c>
       <c r="N358" t="n">
-        <v>2252.2964527845</v>
+        <v>2252.2965479115</v>
       </c>
       <c r="O358" t="n">
-        <v>65316.5971307505</v>
+        <v>65316.5998894335</v>
       </c>
       <c r="P358" t="n">
         <v>3900</v>
@@ -17359,10 +17359,10 @@
         <v>165</v>
       </c>
       <c r="N379" t="n">
-        <v>4907.821941896</v>
+        <v>4907.8219448698</v>
       </c>
       <c r="O379" t="n">
-        <v>809790.6204128399</v>
+        <v>809790.620903517</v>
       </c>
       <c r="P379" t="n">
         <v>8200</v>
@@ -17589,10 +17589,10 @@
         <v>289</v>
       </c>
       <c r="N384" t="n">
-        <v>3903.7361658031</v>
+        <v>3903.7362017804</v>
       </c>
       <c r="O384" t="n">
-        <v>1128179.751917096</v>
+        <v>1128179.762314535</v>
       </c>
       <c r="P384" t="n">
         <v>7500</v>
@@ -19370,22 +19370,22 @@
         <v>0</v>
       </c>
       <c r="L423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N423" t="n">
         <v>10713.21</v>
       </c>
       <c r="O423" t="n">
-        <v>74992.47</v>
+        <v>64279.25999999999</v>
       </c>
       <c r="P423" t="n">
         <v>20900</v>
       </c>
       <c r="Q423" t="n">
-        <v>146300</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="424">
@@ -19882,10 +19882,10 @@
         <v>1320</v>
       </c>
       <c r="N434" t="n">
-        <v>1516.0388115466</v>
+        <v>1516.0388110875</v>
       </c>
       <c r="O434" t="n">
-        <v>2001171.231241512</v>
+        <v>2001171.2306355</v>
       </c>
       <c r="P434" t="n">
         <v>2300</v>
@@ -19974,10 +19974,10 @@
         <v>8</v>
       </c>
       <c r="N436" t="n">
-        <v>4248.6224691358</v>
+        <v>4248.6238427948</v>
       </c>
       <c r="O436" t="n">
-        <v>33988.9797530864</v>
+        <v>33988.9907423584</v>
       </c>
       <c r="P436" t="n">
         <v>5900</v>
@@ -20020,10 +20020,10 @@
         <v>120</v>
       </c>
       <c r="N437" t="n">
-        <v>2458.5134059343</v>
+        <v>2458.5133829585</v>
       </c>
       <c r="O437" t="n">
-        <v>295021.608712116</v>
+        <v>295021.60595502</v>
       </c>
       <c r="P437" t="n">
         <v>3500</v>
@@ -20112,10 +20112,10 @@
         <v>264</v>
       </c>
       <c r="N439" t="n">
-        <v>2079.3842021449</v>
+        <v>2079.3841889251</v>
       </c>
       <c r="O439" t="n">
-        <v>548957.4293662535</v>
+        <v>548957.4258762264</v>
       </c>
       <c r="P439" t="n">
         <v>2900</v>
@@ -20158,10 +20158,10 @@
         <v>192</v>
       </c>
       <c r="N440" t="n">
-        <v>1803.0151441578</v>
+        <v>1803.0151566778</v>
       </c>
       <c r="O440" t="n">
-        <v>346178.9076782976</v>
+        <v>346178.9100821376</v>
       </c>
       <c r="P440" t="n">
         <v>2500</v>
@@ -20204,10 +20204,10 @@
         <v>216</v>
       </c>
       <c r="N441" t="n">
-        <v>3306.5953548387</v>
+        <v>3306.5953488372</v>
       </c>
       <c r="O441" t="n">
-        <v>714224.5966451592</v>
+        <v>714224.5953488352</v>
       </c>
       <c r="P441" t="n">
         <v>4900</v>
@@ -20250,10 +20250,10 @@
         <v>192</v>
       </c>
       <c r="N442" t="n">
-        <v>2122.1640091884</v>
+        <v>2122.1640073529</v>
       </c>
       <c r="O442" t="n">
-        <v>407455.4897641728</v>
+        <v>407455.4894117569</v>
       </c>
       <c r="P442" t="n">
         <v>2900</v>
@@ -20296,10 +20296,10 @@
         <v>216</v>
       </c>
       <c r="N443" t="n">
-        <v>2108.7899828473</v>
+        <v>2108.7899885584</v>
       </c>
       <c r="O443" t="n">
-        <v>455498.6362950168</v>
+        <v>455498.6375286144</v>
       </c>
       <c r="P443" t="n">
         <v>2900</v>
@@ -20342,10 +20342,10 @@
         <v>144</v>
       </c>
       <c r="N444" t="n">
-        <v>2056.0838571429</v>
+        <v>2056.0838222089</v>
       </c>
       <c r="O444" t="n">
-        <v>296076.0754285776</v>
+        <v>296076.0703980816</v>
       </c>
       <c r="P444" t="n">
         <v>2900</v>
@@ -20388,10 +20388,10 @@
         <v>216</v>
       </c>
       <c r="N445" t="n">
-        <v>3224.5682755432</v>
+        <v>3224.568287037</v>
       </c>
       <c r="O445" t="n">
-        <v>696506.7475173312</v>
+        <v>696506.7499999921</v>
       </c>
       <c r="P445" t="n">
         <v>4500</v>
@@ -20434,10 +20434,10 @@
         <v>360</v>
       </c>
       <c r="N446" t="n">
-        <v>1655.9310860458</v>
+        <v>1655.931057226</v>
       </c>
       <c r="O446" t="n">
-        <v>596135.1909764879</v>
+        <v>596135.1806013599</v>
       </c>
       <c r="P446" t="n">
         <v>2500</v>
@@ -20664,10 +20664,10 @@
         <v>400</v>
       </c>
       <c r="N451" t="n">
-        <v>1592.2754925187</v>
+        <v>1592.2755269762</v>
       </c>
       <c r="O451" t="n">
-        <v>636910.1970074801</v>
+        <v>636910.2107904799</v>
       </c>
       <c r="P451" t="n">
         <v>2500</v>
@@ -20795,10 +20795,10 @@
         <v>12</v>
       </c>
       <c r="N454" t="n">
-        <v>2311.9248916968</v>
+        <v>2311.9247818182</v>
       </c>
       <c r="O454" t="n">
-        <v>27743.0987003616</v>
+        <v>27743.0973818184</v>
       </c>
       <c r="P454" t="n">
         <v>3500</v>
@@ -20841,10 +20841,10 @@
         <v>48</v>
       </c>
       <c r="N455" t="n">
-        <v>1906.1862686567</v>
+        <v>1906.18625</v>
       </c>
       <c r="O455" t="n">
-        <v>91496.94089552159</v>
+        <v>91496.94</v>
       </c>
       <c r="P455" t="n">
         <v>2900</v>
@@ -20887,10 +20887,10 @@
         <v>120</v>
       </c>
       <c r="N456" t="n">
-        <v>3033.7296483516</v>
+        <v>3033.7290022676</v>
       </c>
       <c r="O456" t="n">
-        <v>364047.5578021921</v>
+        <v>364047.480272112</v>
       </c>
       <c r="P456" t="n">
         <v>4500</v>
@@ -20933,10 +20933,10 @@
         <v>408</v>
       </c>
       <c r="N457" t="n">
-        <v>2060.1606035889</v>
+        <v>2060.160557377</v>
       </c>
       <c r="O457" t="n">
-        <v>840545.5262642711</v>
+        <v>840545.5074098159</v>
       </c>
       <c r="P457" t="n">
         <v>2900</v>
@@ -20979,10 +20979,10 @@
         <v>72</v>
       </c>
       <c r="N458" t="n">
-        <v>1668.6186615679</v>
+        <v>1668.6190998043</v>
       </c>
       <c r="O458" t="n">
-        <v>120140.5436328888</v>
+        <v>120140.5751859096</v>
       </c>
       <c r="P458" t="n">
         <v>2500</v>
@@ -21025,10 +21025,10 @@
         <v>72</v>
       </c>
       <c r="N459" t="n">
-        <v>2546.9851286449</v>
+        <v>2546.9850949914</v>
       </c>
       <c r="O459" t="n">
-        <v>183382.9292624328</v>
+        <v>183382.9268393808</v>
       </c>
       <c r="P459" t="n">
         <v>3900</v>
@@ -21071,10 +21071,10 @@
         <v>800</v>
       </c>
       <c r="N460" t="n">
-        <v>1259.2744276316</v>
+        <v>1259.2744422442</v>
       </c>
       <c r="O460" t="n">
-        <v>1007419.54210528</v>
+        <v>1007419.55379536</v>
       </c>
       <c r="P460" t="n">
         <v>1900</v>
@@ -22734,10 +22734,10 @@
         <v>9193</v>
       </c>
       <c r="N496" t="n">
-        <v>345.55838640256</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O496" t="n">
-        <v>3176718.246198734</v>
+        <v>3176718.245547226</v>
       </c>
       <c r="P496" t="n">
         <v>600</v>
@@ -23059,10 +23059,10 @@
         <v>149</v>
       </c>
       <c r="N503" t="n">
-        <v>1283.6540655738</v>
+        <v>1283.653986711</v>
       </c>
       <c r="O503" t="n">
-        <v>191264.4557704962</v>
+        <v>191264.444019939</v>
       </c>
       <c r="P503" t="n">
         <v>1900</v>
@@ -23293,10 +23293,10 @@
         <v>749</v>
       </c>
       <c r="N508" t="n">
-        <v>517.28807221513</v>
+        <v>517.28815469086</v>
       </c>
       <c r="O508" t="n">
-        <v>387448.7660891323</v>
+        <v>387448.8278634541</v>
       </c>
       <c r="P508" t="n">
         <v>900</v>
@@ -23716,10 +23716,10 @@
         <v>757</v>
       </c>
       <c r="N517" t="n">
-        <v>3110.8429525518</v>
+        <v>3110.8427709611</v>
       </c>
       <c r="O517" t="n">
-        <v>2354908.115081713</v>
+        <v>2354907.977617553</v>
       </c>
       <c r="P517" t="n">
         <v>4500</v>
@@ -24167,10 +24167,10 @@
         <v>20090</v>
       </c>
       <c r="N527" t="n">
-        <v>703.79534416571</v>
+        <v>703.79533220158</v>
       </c>
       <c r="O527" t="n">
-        <v>14139248.46428912</v>
+        <v>14139248.22392974</v>
       </c>
       <c r="P527" t="n">
         <v>900</v>
@@ -24308,10 +24308,10 @@
         <v>90</v>
       </c>
       <c r="N530" t="n">
-        <v>2501.3854237288</v>
+        <v>2501.3852212389</v>
       </c>
       <c r="O530" t="n">
-        <v>225124.688135592</v>
+        <v>225124.669911501</v>
       </c>
       <c r="P530" t="n">
         <v>4100</v>
@@ -24674,10 +24674,10 @@
         <v>47</v>
       </c>
       <c r="N538" t="n">
-        <v>1595.5190882035</v>
+        <v>1595.5155551576</v>
       </c>
       <c r="O538" t="n">
-        <v>74989.39714556449</v>
+        <v>74989.23109240719</v>
       </c>
       <c r="P538" t="n">
         <v>2500</v>
@@ -25063,10 +25063,10 @@
         <v>168</v>
       </c>
       <c r="N546" t="n">
-        <v>2098.4049008499</v>
+        <v>2098.4049147727</v>
       </c>
       <c r="O546" t="n">
-        <v>352532.0233427832</v>
+        <v>352532.0256818136</v>
       </c>
       <c r="P546" t="n">
         <v>9500</v>
@@ -25395,10 +25395,10 @@
         <v>18</v>
       </c>
       <c r="N553" t="n">
-        <v>11866.994561404</v>
+        <v>11866.994642857</v>
       </c>
       <c r="O553" t="n">
-        <v>213605.902105272</v>
+        <v>213605.903571426</v>
       </c>
       <c r="P553" t="n">
         <v>55000</v>
@@ -26598,10 +26598,10 @@
         <v>312</v>
       </c>
       <c r="N578" t="n">
-        <v>3414.5660805577</v>
+        <v>3414.5660775194</v>
       </c>
       <c r="O578" t="n">
-        <v>1065344.617134002</v>
+        <v>1065344.616186053</v>
       </c>
       <c r="P578" t="n">
         <v>3500</v>
@@ -27278,10 +27278,10 @@
         <v>17</v>
       </c>
       <c r="N592" t="n">
-        <v>4697.3811111111</v>
+        <v>4697.3811428571</v>
       </c>
       <c r="O592" t="n">
-        <v>79855.4788888887</v>
+        <v>79855.4794285707</v>
       </c>
       <c r="P592" t="n">
         <v>10900</v>
@@ -28737,10 +28737,10 @@
         <v>1105</v>
       </c>
       <c r="N623" t="n">
-        <v>7046.9398299681</v>
+        <v>7046.939829932</v>
       </c>
       <c r="O623" t="n">
-        <v>7786868.51211475</v>
+        <v>7786868.51207486</v>
       </c>
       <c r="P623" t="n">
         <v>9900</v>
@@ -28927,10 +28927,10 @@
         <v>648</v>
       </c>
       <c r="N627" t="n">
-        <v>665.32342381786</v>
+        <v>665.32343283582</v>
       </c>
       <c r="O627" t="n">
-        <v>431129.5786339733</v>
+        <v>431129.5844776114</v>
       </c>
       <c r="P627" t="n">
         <v>2900</v>
@@ -29267,10 +29267,10 @@
         <v>61</v>
       </c>
       <c r="N634" t="n">
-        <v>540.40252525253</v>
+        <v>540.40111607143</v>
       </c>
       <c r="O634" t="n">
-        <v>32964.55404040433</v>
+        <v>32964.46808035723</v>
       </c>
       <c r="P634" t="n">
         <v>2500</v>
@@ -29666,10 +29666,10 @@
         <v>30</v>
       </c>
       <c r="N643" t="n">
-        <v>5577.2680778032</v>
+        <v>5577.2680733945</v>
       </c>
       <c r="O643" t="n">
-        <v>167318.042334096</v>
+        <v>167318.042201835</v>
       </c>
       <c r="P643" t="n">
         <v>6500</v>
@@ -30138,10 +30138,10 @@
         <v>190</v>
       </c>
       <c r="N654" t="n">
-        <v>2523.3377476715</v>
+        <v>2523.3377470356</v>
       </c>
       <c r="O654" t="n">
-        <v>479434.172057585</v>
+        <v>479434.171936764</v>
       </c>
       <c r="P654" t="n">
         <v>2800</v>
@@ -30549,10 +30549,10 @@
         <v>8</v>
       </c>
       <c r="N663" t="n">
-        <v>1547.8824285714</v>
+        <v>1547.8824637681</v>
       </c>
       <c r="O663" t="n">
-        <v>12383.0594285712</v>
+        <v>12383.0597101448</v>
       </c>
       <c r="P663" t="n">
         <v>5500</v>
@@ -30732,22 +30732,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M667" t="n">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="N667" t="n">
-        <v>220.00803927108</v>
+        <v>220.00769152493</v>
       </c>
       <c r="O667" t="n">
-        <v>968035.372792752</v>
+        <v>924032.304404706</v>
       </c>
       <c r="P667" t="n">
         <v>260</v>
       </c>
       <c r="Q667" t="n">
-        <v>1144000</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="668">
@@ -30830,10 +30830,10 @@
         <v>82</v>
       </c>
       <c r="N669" t="n">
-        <v>13493.858313253</v>
+        <v>13493.858308157</v>
       </c>
       <c r="O669" t="n">
-        <v>1106496.381686746</v>
+        <v>1106496.381268874</v>
       </c>
       <c r="P669" t="n">
         <v>16900</v>
@@ -31525,10 +31525,10 @@
         <v>200</v>
       </c>
       <c r="N684" t="n">
-        <v>1319.3608797654</v>
+        <v>1319.3608823529</v>
       </c>
       <c r="O684" t="n">
-        <v>263872.17595308</v>
+        <v>263872.17647058</v>
       </c>
       <c r="P684" t="n">
         <v>3500</v>
@@ -31673,10 +31673,10 @@
         <v>18</v>
       </c>
       <c r="N687" t="n">
-        <v>2432.1345098039</v>
+        <v>2432.1345544554</v>
       </c>
       <c r="O687" t="n">
-        <v>43778.4211764702</v>
+        <v>43778.4219801972</v>
       </c>
       <c r="P687" t="n">
         <v>4500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>1727</v>
+        <v>1583</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>1583</v>
@@ -5951,13 +5951,13 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
         <v>35</v>
@@ -7168,13 +7168,13 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
         <v>480</v>
@@ -13878,13 +13878,13 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M304" t="n">
         <v>64</v>
@@ -19364,13 +19364,13 @@
         </is>
       </c>
       <c r="J423" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K423" t="n">
         <v>0</v>
       </c>
       <c r="L423" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M423" t="n">
         <v>6</v>
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="K667" t="n">
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M667" t="n">
         <v>4200</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>87</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3044829343</v>
+        <v>1811.3047800109</v>
       </c>
       <c r="O6" t="n">
-        <v>157583.4900152841</v>
+        <v>157583.5158609483</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.90480218</v>
+        <v>2985043.903963176</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1354,10 +1354,10 @@
         <v>92</v>
       </c>
       <c r="N24" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="O24" t="n">
-        <v>221996.0976645412</v>
+        <v>221996.0977683356</v>
       </c>
       <c r="P24" t="n">
         <v>4700</v>
@@ -1393,10 +1393,10 @@
         <v>102</v>
       </c>
       <c r="N25" t="n">
-        <v>2474.7042043551</v>
+        <v>2474.7041652614</v>
       </c>
       <c r="O25" t="n">
-        <v>252419.8288442202</v>
+        <v>252419.8248566628</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -1705,10 +1705,10 @@
         <v>23</v>
       </c>
       <c r="N33" t="n">
-        <v>14857.623185841</v>
+        <v>14857.6232</v>
       </c>
       <c r="O33" t="n">
-        <v>341725.333274343</v>
+        <v>341725.3336</v>
       </c>
       <c r="P33" t="n">
         <v>34900</v>
@@ -2123,10 +2123,10 @@
         <v>19</v>
       </c>
       <c r="N43" t="n">
-        <v>14708.815744681</v>
+        <v>14708.815698925</v>
       </c>
       <c r="O43" t="n">
-        <v>279467.499148939</v>
+        <v>279467.498279575</v>
       </c>
       <c r="P43" t="n">
         <v>16900</v>
@@ -2259,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O46" t="n">
-        <v>1400505.4</v>
+        <v>1400505.40054684</v>
       </c>
       <c r="P46" t="n">
         <v>312000</v>
@@ -3039,10 +3039,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>732.63413793103</v>
+        <v>732.63415224913</v>
       </c>
       <c r="O64" t="n">
-        <v>30037.99965517223</v>
+        <v>30038.00024221433</v>
       </c>
       <c r="P64" t="n">
         <v>6200</v>
@@ -3129,10 +3129,10 @@
         <v>228</v>
       </c>
       <c r="N66" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O66" t="n">
-        <v>1125706.716747262</v>
+        <v>1125706.716774188</v>
       </c>
       <c r="P66" t="n">
         <v>7500</v>
@@ -3385,22 +3385,22 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M72" t="n">
-        <v>1583</v>
+        <v>1295</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0555939754</v>
+        <v>1098.055952691</v>
       </c>
       <c r="O72" t="n">
-        <v>1738222.005263058</v>
+        <v>1421982.458734845</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
       </c>
       <c r="Q72" t="n">
-        <v>2374500</v>
+        <v>1942500</v>
       </c>
     </row>
     <row r="73">
@@ -4324,10 +4324,10 @@
         <v>771</v>
       </c>
       <c r="N93" t="n">
-        <v>2582.2560112135</v>
+        <v>2582.2559895309</v>
       </c>
       <c r="O93" t="n">
-        <v>1990919.384645609</v>
+        <v>1990919.367928324</v>
       </c>
       <c r="P93" t="n">
         <v>4500</v>
@@ -4364,22 +4364,22 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M94" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>8138.14</v>
       </c>
       <c r="O94" t="n">
-        <v>154624.66</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
         <v>13500</v>
       </c>
       <c r="Q94" t="n">
-        <v>256500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4462,10 +4462,10 @@
         <v>720</v>
       </c>
       <c r="N96" t="n">
-        <v>5216.8959654608</v>
+        <v>5216.8959618537</v>
       </c>
       <c r="O96" t="n">
-        <v>3756165.095131776</v>
+        <v>3756165.092534664</v>
       </c>
       <c r="P96" t="n">
         <v>8500</v>
@@ -4693,10 +4693,10 @@
         <v>3199</v>
       </c>
       <c r="N101" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O101" t="n">
-        <v>10105195.74647802</v>
+        <v>10105195.74862007</v>
       </c>
       <c r="P101" t="n">
         <v>5600</v>
@@ -4829,10 +4829,10 @@
         <v>180</v>
       </c>
       <c r="N104" t="n">
-        <v>3230.0677414075</v>
+        <v>3230.0677302632</v>
       </c>
       <c r="O104" t="n">
-        <v>581412.19345335</v>
+        <v>581412.1914473759</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -4968,10 +4968,10 @@
         <v>259</v>
       </c>
       <c r="N107" t="n">
-        <v>2694.8234565119</v>
+        <v>2694.8234059946</v>
       </c>
       <c r="O107" t="n">
-        <v>697959.2752365822</v>
+        <v>697959.2621526014</v>
       </c>
       <c r="P107" t="n">
         <v>4900</v>
@@ -5288,10 +5288,10 @@
         <v>593</v>
       </c>
       <c r="N114" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O114" t="n">
-        <v>2250856.034187825</v>
+        <v>2250856.03419079</v>
       </c>
       <c r="P114" t="n">
         <v>6200</v>
@@ -5507,22 +5507,22 @@
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M119" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="N119" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O119" t="n">
-        <v>1555315.754764931</v>
+        <v>1540642.964676763</v>
       </c>
       <c r="P119" t="n">
         <v>8200</v>
       </c>
       <c r="Q119" t="n">
-        <v>2607600</v>
+        <v>2583000</v>
       </c>
     </row>
     <row r="120">
@@ -5686,22 +5686,22 @@
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N123" t="n">
-        <v>2267.0481598668</v>
+        <v>2267.0481583333</v>
       </c>
       <c r="O123" t="n">
-        <v>739057.7001165767</v>
+        <v>734523.6032999891</v>
       </c>
       <c r="P123" t="n">
         <v>3900</v>
       </c>
       <c r="Q123" t="n">
-        <v>1271400</v>
+        <v>1263600</v>
       </c>
     </row>
     <row r="124">
@@ -5957,22 +5957,22 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M129" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N129" t="n">
         <v>10716.34</v>
       </c>
       <c r="O129" t="n">
-        <v>375071.9</v>
+        <v>353639.22</v>
       </c>
       <c r="P129" t="n">
         <v>39000</v>
       </c>
       <c r="Q129" t="n">
-        <v>1365000</v>
+        <v>1287000</v>
       </c>
     </row>
     <row r="130">
@@ -6012,10 +6012,10 @@
         <v>288</v>
       </c>
       <c r="N130" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O130" t="n">
-        <v>1035145.192087901</v>
+        <v>1035145.187955936</v>
       </c>
       <c r="P130" t="n">
         <v>6500</v>
@@ -6053,10 +6053,10 @@
         <v>108</v>
       </c>
       <c r="N131" t="n">
-        <v>3240.8500301659</v>
+        <v>3240.8500302572</v>
       </c>
       <c r="O131" t="n">
-        <v>350011.8032579172</v>
+        <v>350011.8032677776</v>
       </c>
       <c r="P131" t="n">
         <v>5200</v>
@@ -6237,10 +6237,10 @@
         <v>305</v>
       </c>
       <c r="N135" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O135" t="n">
-        <v>4520825.553080495</v>
+        <v>4520825.552874925</v>
       </c>
       <c r="P135" t="n">
         <v>24900</v>
@@ -6962,10 +6962,10 @@
         <v>210</v>
       </c>
       <c r="N151" t="n">
-        <v>3041.6600126502</v>
+        <v>3041.6600127551</v>
       </c>
       <c r="O151" t="n">
-        <v>638748.602656542</v>
+        <v>638748.602678571</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -7180,10 +7180,10 @@
         <v>480</v>
       </c>
       <c r="N156" t="n">
-        <v>1592.5674522293</v>
+        <v>1592.5674</v>
       </c>
       <c r="O156" t="n">
-        <v>764432.377070064</v>
+        <v>764432.352</v>
       </c>
       <c r="P156" t="n">
         <v>3900</v>
@@ -8120,22 +8120,22 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M177" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N177" t="n">
         <v>4635.49</v>
       </c>
       <c r="O177" t="n">
-        <v>991994.86</v>
+        <v>978088.3899999999</v>
       </c>
       <c r="P177" t="n">
         <v>7500</v>
       </c>
       <c r="Q177" t="n">
-        <v>1605000</v>
+        <v>1582500</v>
       </c>
     </row>
     <row r="178">
@@ -8499,22 +8499,22 @@
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M185" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N185" t="n">
         <v>11921.4</v>
       </c>
       <c r="O185" t="n">
-        <v>1573624.8</v>
+        <v>1525939.2</v>
       </c>
       <c r="P185" t="n">
         <v>19900</v>
       </c>
       <c r="Q185" t="n">
-        <v>2626800</v>
+        <v>2547200</v>
       </c>
     </row>
     <row r="186">
@@ -8971,10 +8971,10 @@
         <v>824</v>
       </c>
       <c r="N195" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O195" t="n">
-        <v>1343880.682817828</v>
+        <v>1343880.694631763</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9017,10 +9017,10 @@
         <v>5</v>
       </c>
       <c r="N196" t="n">
-        <v>1467.327254902</v>
+        <v>1467.3264227642</v>
       </c>
       <c r="O196" t="n">
-        <v>7336.63627451</v>
+        <v>7336.632113821001</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9063,10 +9063,10 @@
         <v>384</v>
       </c>
       <c r="N197" t="n">
-        <v>1690.6026503973</v>
+        <v>1690.6023498845</v>
       </c>
       <c r="O197" t="n">
-        <v>649191.4177525633</v>
+        <v>649191.302355648</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9109,10 +9109,10 @@
         <v>2118</v>
       </c>
       <c r="N198" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O198" t="n">
-        <v>3283309.104155111</v>
+        <v>3283309.163220624</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
@@ -9155,10 +9155,10 @@
         <v>22</v>
       </c>
       <c r="N199" t="n">
-        <v>1579.391025</v>
+        <v>1579.3909343434</v>
       </c>
       <c r="O199" t="n">
-        <v>34746.60255</v>
+        <v>34746.6005555548</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
@@ -9201,10 +9201,10 @@
         <v>454</v>
       </c>
       <c r="N200" t="n">
-        <v>2403.5103724115</v>
+        <v>2403.5104597508</v>
       </c>
       <c r="O200" t="n">
-        <v>1091193.709074821</v>
+        <v>1091193.748726863</v>
       </c>
       <c r="P200" t="n">
         <v>3500</v>
@@ -9247,10 +9247,10 @@
         <v>80</v>
       </c>
       <c r="N201" t="n">
-        <v>2521.5439240506</v>
+        <v>2521.5426705653</v>
       </c>
       <c r="O201" t="n">
-        <v>201723.513924048</v>
+        <v>201723.413645224</v>
       </c>
       <c r="P201" t="n">
         <v>3900</v>
@@ -11235,10 +11235,10 @@
         <v>900</v>
       </c>
       <c r="N246" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O246" t="n">
-        <v>898885.1338969141</v>
+        <v>898885.134825327</v>
       </c>
       <c r="P246" t="n">
         <v>1600</v>
@@ -11330,10 +11330,10 @@
         <v>125</v>
       </c>
       <c r="N248" t="n">
-        <v>4285.1952751817</v>
+        <v>4285.1952806653</v>
       </c>
       <c r="O248" t="n">
-        <v>535649.4093977124</v>
+        <v>535649.4100831625</v>
       </c>
       <c r="P248" t="n">
         <v>6900</v>
@@ -11987,22 +11987,22 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M263" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N263" t="n">
         <v>16974.69</v>
       </c>
       <c r="O263" t="n">
-        <v>916633.2599999999</v>
+        <v>882683.8799999999</v>
       </c>
       <c r="P263" t="n">
         <v>26900</v>
       </c>
       <c r="Q263" t="n">
-        <v>1452600</v>
+        <v>1398800</v>
       </c>
     </row>
     <row r="264">
@@ -12172,10 +12172,10 @@
         <v>599</v>
       </c>
       <c r="N267" t="n">
-        <v>1560.9993877551</v>
+        <v>1560.9994428152</v>
       </c>
       <c r="O267" t="n">
-        <v>935038.633265305</v>
+        <v>935038.6662463048</v>
       </c>
       <c r="P267" t="n">
         <v>2900</v>
@@ -12495,10 +12495,10 @@
         <v>306</v>
       </c>
       <c r="N274" t="n">
-        <v>548.14725212465</v>
+        <v>548.14724692526</v>
       </c>
       <c r="O274" t="n">
-        <v>167733.0591501429</v>
+        <v>167733.0575591295</v>
       </c>
       <c r="P274" t="n">
         <v>2000</v>
@@ -12771,22 +12771,22 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M280" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N280" t="n">
         <v>5875.95</v>
       </c>
       <c r="O280" t="n">
-        <v>205658.25</v>
+        <v>158650.65</v>
       </c>
       <c r="P280" t="n">
         <v>5900</v>
       </c>
       <c r="Q280" t="n">
-        <v>206500</v>
+        <v>159300</v>
       </c>
     </row>
     <row r="281">
@@ -12869,22 +12869,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M282" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N282" t="n">
         <v>8562.18</v>
       </c>
       <c r="O282" t="n">
-        <v>85621.8</v>
+        <v>59935.26</v>
       </c>
       <c r="P282" t="n">
         <v>9900</v>
       </c>
       <c r="Q282" t="n">
-        <v>99000</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="283">
@@ -13427,10 +13427,10 @@
         <v>81</v>
       </c>
       <c r="N294" t="n">
-        <v>5218.1705164319</v>
+        <v>5218.170521327</v>
       </c>
       <c r="O294" t="n">
-        <v>422671.8118309839</v>
+        <v>422671.812227487</v>
       </c>
       <c r="P294" t="n">
         <v>8500</v>
@@ -13473,10 +13473,10 @@
         <v>1</v>
       </c>
       <c r="N295" t="n">
-        <v>1595.0094492754</v>
+        <v>1595.0094476744</v>
       </c>
       <c r="O295" t="n">
-        <v>1595.0094492754</v>
+        <v>1595.0094476744</v>
       </c>
       <c r="P295" t="n">
         <v>2600</v>
@@ -13519,10 +13519,10 @@
         <v>123</v>
       </c>
       <c r="N296" t="n">
-        <v>3610.6500248756</v>
+        <v>3610.6500249688</v>
       </c>
       <c r="O296" t="n">
-        <v>444109.9530596988</v>
+        <v>444109.9530711624</v>
       </c>
       <c r="P296" t="n">
         <v>5800</v>
@@ -13982,10 +13982,10 @@
         <v>48</v>
       </c>
       <c r="N306" t="n">
-        <v>1664.3592041199</v>
+        <v>1664.3590294957</v>
       </c>
       <c r="O306" t="n">
-        <v>79889.2417977552</v>
+        <v>79889.2334157936</v>
       </c>
       <c r="P306" t="n">
         <v>2900</v>
@@ -16383,22 +16383,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M358" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N358" t="n">
-        <v>2252.2965479115</v>
+        <v>2252.2965559656</v>
       </c>
       <c r="O358" t="n">
-        <v>65316.5998894335</v>
+        <v>11261.482779828</v>
       </c>
       <c r="P358" t="n">
         <v>3900</v>
       </c>
       <c r="Q358" t="n">
-        <v>113100</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="359">
@@ -16847,22 +16847,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N368" t="n">
         <v>32332</v>
       </c>
       <c r="O368" t="n">
-        <v>226324</v>
+        <v>193992</v>
       </c>
       <c r="P368" t="n">
         <v>55900</v>
       </c>
       <c r="Q368" t="n">
-        <v>391300</v>
+        <v>335400</v>
       </c>
     </row>
     <row r="369">
@@ -17353,22 +17353,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M379" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="N379" t="n">
-        <v>4907.8219448698</v>
+        <v>4907.8219751166</v>
       </c>
       <c r="O379" t="n">
-        <v>809790.620903517</v>
+        <v>731265.4742923734</v>
       </c>
       <c r="P379" t="n">
         <v>8200</v>
       </c>
       <c r="Q379" t="n">
-        <v>1353000</v>
+        <v>1221800</v>
       </c>
     </row>
     <row r="380">
@@ -18222,22 +18222,22 @@
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M398" t="n">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="N398" t="n">
         <v>7635</v>
       </c>
       <c r="O398" t="n">
-        <v>4061820</v>
+        <v>4038915</v>
       </c>
       <c r="P398" t="n">
         <v>13900</v>
       </c>
       <c r="Q398" t="n">
-        <v>7394800</v>
+        <v>7353100</v>
       </c>
     </row>
     <row r="399">
@@ -19882,10 +19882,10 @@
         <v>1320</v>
       </c>
       <c r="N434" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O434" t="n">
-        <v>2001171.2306355</v>
+        <v>2001171.229573824</v>
       </c>
       <c r="P434" t="n">
         <v>2300</v>
@@ -19974,10 +19974,10 @@
         <v>8</v>
       </c>
       <c r="N436" t="n">
-        <v>4248.6238427948</v>
+        <v>4248.635</v>
       </c>
       <c r="O436" t="n">
-        <v>33988.9907423584</v>
+        <v>33989.08</v>
       </c>
       <c r="P436" t="n">
         <v>5900</v>
@@ -20020,10 +20020,10 @@
         <v>120</v>
       </c>
       <c r="N437" t="n">
-        <v>2458.5133829585</v>
+        <v>2458.5133724619</v>
       </c>
       <c r="O437" t="n">
-        <v>295021.60595502</v>
+        <v>295021.604695428</v>
       </c>
       <c r="P437" t="n">
         <v>3500</v>
@@ -20066,10 +20066,10 @@
         <v>192</v>
       </c>
       <c r="N438" t="n">
-        <v>1771.0911342735</v>
+        <v>1771.0911179361</v>
       </c>
       <c r="O438" t="n">
-        <v>340049.497780512</v>
+        <v>340049.4946437312</v>
       </c>
       <c r="P438" t="n">
         <v>2500</v>
@@ -20112,10 +20112,10 @@
         <v>264</v>
       </c>
       <c r="N439" t="n">
-        <v>2079.3841889251</v>
+        <v>2079.3841813438</v>
       </c>
       <c r="O439" t="n">
-        <v>548957.4258762264</v>
+        <v>548957.4238747632</v>
       </c>
       <c r="P439" t="n">
         <v>2900</v>
@@ -20158,10 +20158,10 @@
         <v>192</v>
       </c>
       <c r="N440" t="n">
-        <v>1803.0151566778</v>
+        <v>1803.0151724138</v>
       </c>
       <c r="O440" t="n">
-        <v>346178.9100821376</v>
+        <v>346178.9131034496</v>
       </c>
       <c r="P440" t="n">
         <v>2500</v>
@@ -20250,10 +20250,10 @@
         <v>192</v>
       </c>
       <c r="N442" t="n">
-        <v>2122.1640073529</v>
+        <v>2122.1640036787</v>
       </c>
       <c r="O442" t="n">
-        <v>407455.4894117569</v>
+        <v>407455.4887063104</v>
       </c>
       <c r="P442" t="n">
         <v>2900</v>
@@ -20296,10 +20296,10 @@
         <v>216</v>
       </c>
       <c r="N443" t="n">
-        <v>2108.7899885584</v>
+        <v>2108.7900518135</v>
       </c>
       <c r="O443" t="n">
-        <v>455498.6375286144</v>
+        <v>455498.651191716</v>
       </c>
       <c r="P443" t="n">
         <v>2900</v>
@@ -20342,10 +20342,10 @@
         <v>144</v>
       </c>
       <c r="N444" t="n">
-        <v>2056.0838222089</v>
+        <v>2056.0837188071</v>
       </c>
       <c r="O444" t="n">
-        <v>296076.0703980816</v>
+        <v>296076.0555082224</v>
       </c>
       <c r="P444" t="n">
         <v>2900</v>
@@ -20388,10 +20388,10 @@
         <v>216</v>
       </c>
       <c r="N445" t="n">
-        <v>3224.568287037</v>
+        <v>3224.5683024119</v>
       </c>
       <c r="O445" t="n">
-        <v>696506.7499999921</v>
+        <v>696506.7533209703</v>
       </c>
       <c r="P445" t="n">
         <v>4500</v>
@@ -20434,10 +20434,10 @@
         <v>360</v>
       </c>
       <c r="N446" t="n">
-        <v>1655.931057226</v>
+        <v>1655.9310223953</v>
       </c>
       <c r="O446" t="n">
-        <v>596135.1806013599</v>
+        <v>596135.168062308</v>
       </c>
       <c r="P446" t="n">
         <v>2500</v>
@@ -20664,10 +20664,10 @@
         <v>400</v>
       </c>
       <c r="N451" t="n">
-        <v>1592.2755269762</v>
+        <v>1592.2756948933</v>
       </c>
       <c r="O451" t="n">
-        <v>636910.2107904799</v>
+        <v>636910.27795732</v>
       </c>
       <c r="P451" t="n">
         <v>2500</v>
@@ -20795,10 +20795,10 @@
         <v>12</v>
       </c>
       <c r="N454" t="n">
-        <v>2311.9247818182</v>
+        <v>2311.9246983547</v>
       </c>
       <c r="O454" t="n">
-        <v>27743.0973818184</v>
+        <v>27743.0963802564</v>
       </c>
       <c r="P454" t="n">
         <v>3500</v>
@@ -20887,10 +20887,10 @@
         <v>120</v>
       </c>
       <c r="N456" t="n">
-        <v>3033.7290022676</v>
+        <v>3033.7273039216</v>
       </c>
       <c r="O456" t="n">
-        <v>364047.480272112</v>
+        <v>364047.276470592</v>
       </c>
       <c r="P456" t="n">
         <v>4500</v>
@@ -20933,10 +20933,10 @@
         <v>408</v>
       </c>
       <c r="N457" t="n">
-        <v>2060.160557377</v>
+        <v>2060.1604635762</v>
       </c>
       <c r="O457" t="n">
-        <v>840545.5074098159</v>
+        <v>840545.4691390896</v>
       </c>
       <c r="P457" t="n">
         <v>2900</v>
@@ -20979,10 +20979,10 @@
         <v>72</v>
       </c>
       <c r="N458" t="n">
-        <v>1668.6190998043</v>
+        <v>1668.6199591002</v>
       </c>
       <c r="O458" t="n">
-        <v>120140.5751859096</v>
+        <v>120140.6370552144</v>
       </c>
       <c r="P458" t="n">
         <v>2500</v>
@@ -21025,10 +21025,10 @@
         <v>72</v>
       </c>
       <c r="N459" t="n">
-        <v>2546.9850949914</v>
+        <v>2546.985</v>
       </c>
       <c r="O459" t="n">
-        <v>183382.9268393808</v>
+        <v>183382.92</v>
       </c>
       <c r="P459" t="n">
         <v>3900</v>
@@ -21071,10 +21071,10 @@
         <v>800</v>
       </c>
       <c r="N460" t="n">
-        <v>1259.2744422442</v>
+        <v>1259.2744638514</v>
       </c>
       <c r="O460" t="n">
-        <v>1007419.55379536</v>
+        <v>1007419.57108112</v>
       </c>
       <c r="P460" t="n">
         <v>1900</v>
@@ -21204,10 +21204,10 @@
         <v>72</v>
       </c>
       <c r="N463" t="n">
-        <v>2556.7452252252</v>
+        <v>2556.7453211009</v>
       </c>
       <c r="O463" t="n">
-        <v>184085.6562162144</v>
+        <v>184085.6631192648</v>
       </c>
       <c r="P463" t="n">
         <v>3900</v>
@@ -21294,10 +21294,10 @@
         <v>540</v>
       </c>
       <c r="N465" t="n">
-        <v>692.15208975521</v>
+        <v>692.15209736124</v>
       </c>
       <c r="O465" t="n">
-        <v>373762.1284678134</v>
+        <v>373762.1325750696</v>
       </c>
       <c r="P465" t="n">
         <v>1200</v>
@@ -22077,22 +22077,22 @@
         <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M482" t="n">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="N482" t="n">
         <v>3629.36</v>
       </c>
       <c r="O482" t="n">
-        <v>1023479.52</v>
+        <v>987185.92</v>
       </c>
       <c r="P482" t="n">
         <v>3900</v>
       </c>
       <c r="Q482" t="n">
-        <v>1099800</v>
+        <v>1060800</v>
       </c>
     </row>
     <row r="483">
@@ -22450,10 +22450,10 @@
         <v>306</v>
       </c>
       <c r="N490" t="n">
-        <v>1690.8700089526</v>
+        <v>1690.8700089606</v>
       </c>
       <c r="O490" t="n">
-        <v>517406.2227394956</v>
+        <v>517406.2227419436</v>
       </c>
       <c r="P490" t="n">
         <v>3000</v>
@@ -23195,10 +23195,10 @@
         <v>52</v>
       </c>
       <c r="N506" t="n">
-        <v>4032.3968542199</v>
+        <v>4032.3968461538</v>
       </c>
       <c r="O506" t="n">
-        <v>209684.6364194348</v>
+        <v>209684.6359999976</v>
       </c>
       <c r="P506" t="n">
         <v>4200</v>
@@ -23293,10 +23293,10 @@
         <v>749</v>
       </c>
       <c r="N508" t="n">
-        <v>517.28815469086</v>
+        <v>517.28824762181</v>
       </c>
       <c r="O508" t="n">
-        <v>387448.8278634541</v>
+        <v>387448.8974687357</v>
       </c>
       <c r="P508" t="n">
         <v>900</v>
@@ -23667,10 +23667,10 @@
         <v>33</v>
       </c>
       <c r="N516" t="n">
-        <v>3259.1342205323</v>
+        <v>3259.1342528736</v>
       </c>
       <c r="O516" t="n">
-        <v>107551.4292775659</v>
+        <v>107551.4303448288</v>
       </c>
       <c r="P516" t="n">
         <v>3600</v>
@@ -23716,10 +23716,10 @@
         <v>757</v>
       </c>
       <c r="N517" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O517" t="n">
-        <v>2354907.977617553</v>
+        <v>2354907.918799107</v>
       </c>
       <c r="P517" t="n">
         <v>4500</v>
@@ -24167,10 +24167,10 @@
         <v>20090</v>
       </c>
       <c r="N527" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O527" t="n">
-        <v>14139248.22392974</v>
+        <v>14139247.98233182</v>
       </c>
       <c r="P527" t="n">
         <v>900</v>
@@ -24308,10 +24308,10 @@
         <v>90</v>
       </c>
       <c r="N530" t="n">
-        <v>2501.3852212389</v>
+        <v>2501.3851351351</v>
       </c>
       <c r="O530" t="n">
-        <v>225124.669911501</v>
+        <v>225124.662162159</v>
       </c>
       <c r="P530" t="n">
         <v>4100</v>
@@ -24674,10 +24674,10 @@
         <v>47</v>
       </c>
       <c r="N538" t="n">
-        <v>1595.5155551576</v>
+        <v>1595.5155292429</v>
       </c>
       <c r="O538" t="n">
-        <v>74989.23109240719</v>
+        <v>74989.2298744163</v>
       </c>
       <c r="P538" t="n">
         <v>2500</v>
@@ -25585,22 +25585,22 @@
         <v>0</v>
       </c>
       <c r="L557" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M557" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N557" t="n">
         <v>9874.620000000001</v>
       </c>
       <c r="O557" t="n">
-        <v>49373.10000000001</v>
+        <v>0</v>
       </c>
       <c r="P557" t="n">
         <v>14700</v>
       </c>
       <c r="Q557" t="n">
-        <v>73500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
@@ -26412,22 +26412,22 @@
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M574" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N574" t="n">
         <v>4568.55</v>
       </c>
       <c r="O574" t="n">
-        <v>301524.3</v>
+        <v>292387.2</v>
       </c>
       <c r="P574" t="n">
         <v>6900</v>
       </c>
       <c r="Q574" t="n">
-        <v>455400</v>
+        <v>441600</v>
       </c>
     </row>
     <row r="575">
@@ -26647,10 +26647,10 @@
         <v>112</v>
       </c>
       <c r="N579" t="n">
-        <v>3067.0905389222</v>
+        <v>3067.0905454545</v>
       </c>
       <c r="O579" t="n">
-        <v>343514.1403592864</v>
+        <v>343514.141090904</v>
       </c>
       <c r="P579" t="n">
         <v>7200</v>
@@ -27512,10 +27512,10 @@
         <v>24</v>
       </c>
       <c r="N597" t="n">
-        <v>10737.526470588</v>
+        <v>10737.5264</v>
       </c>
       <c r="O597" t="n">
-        <v>257700.635294112</v>
+        <v>257700.6336</v>
       </c>
       <c r="P597" t="n">
         <v>18900</v>
@@ -28737,10 +28737,10 @@
         <v>1105</v>
       </c>
       <c r="N623" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O623" t="n">
-        <v>7786868.51207486</v>
+        <v>7786868.51203486</v>
       </c>
       <c r="P623" t="n">
         <v>9900</v>
@@ -28927,10 +28927,10 @@
         <v>648</v>
       </c>
       <c r="N627" t="n">
-        <v>665.32343283582</v>
+        <v>665.3234571176</v>
       </c>
       <c r="O627" t="n">
-        <v>431129.5844776114</v>
+        <v>431129.6002122048</v>
       </c>
       <c r="P627" t="n">
         <v>2900</v>
@@ -30050,10 +30050,10 @@
         <v>44</v>
       </c>
       <c r="N652" t="n">
-        <v>2830.2251183432</v>
+        <v>2830.2251488095</v>
       </c>
       <c r="O652" t="n">
-        <v>124529.9052071008</v>
+        <v>124529.906547618</v>
       </c>
       <c r="P652" t="n">
         <v>2400</v>
@@ -30094,10 +30094,10 @@
         <v>28</v>
       </c>
       <c r="N653" t="n">
-        <v>15219.155340909</v>
+        <v>15219.155287356</v>
       </c>
       <c r="O653" t="n">
-        <v>426136.349545452</v>
+        <v>426136.348045968</v>
       </c>
       <c r="P653" t="n">
         <v>16000</v>
@@ -30225,22 +30225,22 @@
         <v>0</v>
       </c>
       <c r="L656" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M656" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N656" t="n">
-        <v>8922.214777777799</v>
+        <v>8922.214942528701</v>
       </c>
       <c r="O656" t="n">
-        <v>517488.4571111124</v>
+        <v>481799.6068965498</v>
       </c>
       <c r="P656" t="n">
         <v>8200</v>
       </c>
       <c r="Q656" t="n">
-        <v>475600</v>
+        <v>442800</v>
       </c>
     </row>
     <row r="657">
@@ -30498,10 +30498,10 @@
         <v>93</v>
       </c>
       <c r="N662" t="n">
-        <v>4985.4046511628</v>
+        <v>4985.4047058824</v>
       </c>
       <c r="O662" t="n">
-        <v>463642.6325581404</v>
+        <v>463642.6376470632</v>
       </c>
       <c r="P662" t="n">
         <v>7900</v>
@@ -30600,10 +30600,10 @@
         <v>306</v>
       </c>
       <c r="N664" t="n">
-        <v>1757.3205360825</v>
+        <v>1757.3205416667</v>
       </c>
       <c r="O664" t="n">
-        <v>537740.084041245</v>
+        <v>537740.0857500102</v>
       </c>
       <c r="P664" t="n">
         <v>2000</v>
@@ -30738,10 +30738,10 @@
         <v>4200</v>
       </c>
       <c r="N667" t="n">
-        <v>220.00769152493</v>
+        <v>220.00713026296</v>
       </c>
       <c r="O667" t="n">
-        <v>924032.304404706</v>
+        <v>924029.947104432</v>
       </c>
       <c r="P667" t="n">
         <v>260</v>
@@ -31673,10 +31673,10 @@
         <v>18</v>
       </c>
       <c r="N687" t="n">
-        <v>2432.1345544554</v>
+        <v>2432.1346</v>
       </c>
       <c r="O687" t="n">
-        <v>43778.4219801972</v>
+        <v>43778.4228</v>
       </c>
       <c r="P687" t="n">
         <v>4500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -550,22 +550,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N4" t="n">
         <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>8694000</v>
+        <v>8640000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6440000</v>
+        <v>6400000</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M6" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3047800109</v>
+        <v>1811.3053012048</v>
       </c>
       <c r="O6" t="n">
-        <v>157583.5158609483</v>
+        <v>1811.3053012048</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
       </c>
       <c r="Q6" t="n">
-        <v>226200</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="7">
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464976959</v>
+        <v>3376.7464891304</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.903963176</v>
+        <v>2985043.896391273</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1234,10 +1234,10 @@
         <v>210</v>
       </c>
       <c r="N21" t="n">
-        <v>3926.8371237802</v>
+        <v>3926.8371059432</v>
       </c>
       <c r="O21" t="n">
-        <v>824635.795993842</v>
+        <v>824635.792248072</v>
       </c>
       <c r="P21" t="n">
         <v>4800</v>
@@ -1354,10 +1354,10 @@
         <v>92</v>
       </c>
       <c r="N24" t="n">
-        <v>2413.0010626993</v>
+        <v>2413.0010683761</v>
       </c>
       <c r="O24" t="n">
-        <v>221996.0977683356</v>
+        <v>221996.0982906012</v>
       </c>
       <c r="P24" t="n">
         <v>4700</v>
@@ -1471,10 +1471,10 @@
         <v>120</v>
       </c>
       <c r="N27" t="n">
-        <v>3716.3301892744</v>
+        <v>3716.3301923077</v>
       </c>
       <c r="O27" t="n">
-        <v>445959.622712928</v>
+        <v>445959.623076924</v>
       </c>
       <c r="P27" t="n">
         <v>9500</v>
@@ -1878,10 +1878,10 @@
         <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>16486.409172932</v>
+        <v>16486.409090909</v>
       </c>
       <c r="O37" t="n">
-        <v>395673.820150368</v>
+        <v>395673.818181816</v>
       </c>
       <c r="P37" t="n">
         <v>30500</v>
@@ -2259,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>200072.20007812</v>
+        <v>200072.20015748</v>
       </c>
       <c r="O46" t="n">
-        <v>1400505.40054684</v>
+        <v>1400505.40110236</v>
       </c>
       <c r="P46" t="n">
         <v>312000</v>
@@ -2347,22 +2347,22 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N48" t="n">
         <v>27000</v>
       </c>
       <c r="O48" t="n">
-        <v>2268000</v>
+        <v>2214000</v>
       </c>
       <c r="P48" t="n">
         <v>20000</v>
       </c>
       <c r="Q48" t="n">
-        <v>1680000</v>
+        <v>1640000</v>
       </c>
     </row>
     <row r="49">
@@ -3391,10 +3391,10 @@
         <v>1295</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.055952691</v>
+        <v>1098.0561100153</v>
       </c>
       <c r="O72" t="n">
-        <v>1421982.458734845</v>
+        <v>1421982.662469813</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -4324,10 +4324,10 @@
         <v>771</v>
       </c>
       <c r="N93" t="n">
-        <v>2582.2559895309</v>
+        <v>2582.2559749444</v>
       </c>
       <c r="O93" t="n">
-        <v>1990919.367928324</v>
+        <v>1990919.356682132</v>
       </c>
       <c r="P93" t="n">
         <v>4500</v>
@@ -4416,10 +4416,10 @@
         <v>720</v>
       </c>
       <c r="N95" t="n">
-        <v>5216.8959618537</v>
+        <v>5216.8962134973</v>
       </c>
       <c r="O95" t="n">
-        <v>3756165.092534664</v>
+        <v>3756165.273718056</v>
       </c>
       <c r="P95" t="n">
         <v>8500</v>
@@ -4647,10 +4647,10 @@
         <v>3199</v>
       </c>
       <c r="N100" t="n">
-        <v>3158.8608154486</v>
+        <v>3158.8608230874</v>
       </c>
       <c r="O100" t="n">
-        <v>10105195.74862007</v>
+        <v>10105195.77305659</v>
       </c>
       <c r="P100" t="n">
         <v>5600</v>
@@ -4783,10 +4783,10 @@
         <v>180</v>
       </c>
       <c r="N103" t="n">
-        <v>3230.0677302632</v>
+        <v>3230.0675874126</v>
       </c>
       <c r="O103" t="n">
-        <v>581412.1914473759</v>
+        <v>581412.165734268</v>
       </c>
       <c r="P103" t="n">
         <v>6200</v>
@@ -4922,10 +4922,10 @@
         <v>259</v>
       </c>
       <c r="N106" t="n">
-        <v>2694.8234059946</v>
+        <v>2694.8233333333</v>
       </c>
       <c r="O106" t="n">
-        <v>697959.2621526014</v>
+        <v>697959.2433333247</v>
       </c>
       <c r="P106" t="n">
         <v>4900</v>
@@ -5242,10 +5242,10 @@
         <v>593</v>
       </c>
       <c r="N113" t="n">
-        <v>3795.7100070671</v>
+        <v>3795.7100070822</v>
       </c>
       <c r="O113" t="n">
-        <v>2250856.03419079</v>
+        <v>2250856.034199744</v>
       </c>
       <c r="P113" t="n">
         <v>6200</v>
@@ -5467,10 +5467,10 @@
         <v>315</v>
       </c>
       <c r="N118" t="n">
-        <v>4890.9300465929</v>
+        <v>4890.9300467563</v>
       </c>
       <c r="O118" t="n">
-        <v>1540642.964676763</v>
+        <v>1540642.964728234</v>
       </c>
       <c r="P118" t="n">
         <v>8200</v>
@@ -5507,22 +5507,22 @@
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M119" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="N119" t="n">
         <v>5613.75</v>
       </c>
       <c r="O119" t="n">
-        <v>550147.5</v>
+        <v>376121.25</v>
       </c>
       <c r="P119" t="n">
         <v>7900</v>
       </c>
       <c r="Q119" t="n">
-        <v>774200</v>
+        <v>529300</v>
       </c>
     </row>
     <row r="120">
@@ -5911,22 +5911,22 @@
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N128" t="n">
         <v>10716.34</v>
       </c>
       <c r="O128" t="n">
-        <v>353639.22</v>
+        <v>342922.88</v>
       </c>
       <c r="P128" t="n">
         <v>39000</v>
       </c>
       <c r="Q128" t="n">
-        <v>1287000</v>
+        <v>1248000</v>
       </c>
     </row>
     <row r="129">
@@ -5966,10 +5966,10 @@
         <v>288</v>
       </c>
       <c r="N129" t="n">
-        <v>3594.254124847</v>
+        <v>3594.2541140405</v>
       </c>
       <c r="O129" t="n">
-        <v>1035145.187955936</v>
+        <v>1035145.184843664</v>
       </c>
       <c r="P129" t="n">
         <v>6500</v>
@@ -6007,10 +6007,10 @@
         <v>108</v>
       </c>
       <c r="N130" t="n">
-        <v>3240.8500302572</v>
+        <v>3240.8500303951</v>
       </c>
       <c r="O130" t="n">
-        <v>350011.8032677776</v>
+        <v>350011.8032826708</v>
       </c>
       <c r="P130" t="n">
         <v>5200</v>
@@ -6916,10 +6916,10 @@
         <v>210</v>
       </c>
       <c r="N150" t="n">
-        <v>3041.6600127551</v>
+        <v>3041.6600128617</v>
       </c>
       <c r="O150" t="n">
-        <v>638748.602678571</v>
+        <v>638748.602700957</v>
       </c>
       <c r="P150" t="n">
         <v>5500</v>
@@ -7044,10 +7044,10 @@
         <v>1945</v>
       </c>
       <c r="N153" t="n">
-        <v>4372.2107877711</v>
+        <v>4372.2107879391</v>
       </c>
       <c r="O153" t="n">
-        <v>8503949.982214788</v>
+        <v>8503949.982541548</v>
       </c>
       <c r="P153" t="n">
         <v>7500</v>
@@ -7134,10 +7134,10 @@
         <v>480</v>
       </c>
       <c r="N155" t="n">
-        <v>1592.5674</v>
+        <v>1592.5673455845</v>
       </c>
       <c r="O155" t="n">
-        <v>764432.352</v>
+        <v>764432.32588056</v>
       </c>
       <c r="P155" t="n">
         <v>3900</v>
@@ -7343,22 +7343,22 @@
         <v>0</v>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M160" t="n">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="N160" t="n">
         <v>4717</v>
       </c>
       <c r="O160" t="n">
-        <v>1235854</v>
+        <v>1094344</v>
       </c>
       <c r="P160" t="n">
         <v>7900</v>
       </c>
       <c r="Q160" t="n">
-        <v>2069800</v>
+        <v>1832800</v>
       </c>
     </row>
     <row r="161">
@@ -8074,22 +8074,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M176" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="N176" t="n">
         <v>4635.49</v>
       </c>
       <c r="O176" t="n">
-        <v>978088.3899999999</v>
+        <v>922462.51</v>
       </c>
       <c r="P176" t="n">
         <v>7500</v>
       </c>
       <c r="Q176" t="n">
-        <v>1582500</v>
+        <v>1492500</v>
       </c>
     </row>
     <row r="177">
@@ -8402,22 +8402,22 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M183" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="N183" t="n">
         <v>3761.6</v>
       </c>
       <c r="O183" t="n">
-        <v>376160</v>
+        <v>331020.8</v>
       </c>
       <c r="P183" t="n">
         <v>6900</v>
       </c>
       <c r="Q183" t="n">
-        <v>690000</v>
+        <v>607200</v>
       </c>
     </row>
     <row r="184">
@@ -8919,22 +8919,22 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M194" t="n">
-        <v>824</v>
+        <v>776</v>
       </c>
       <c r="N194" t="n">
-        <v>1630.9231730968</v>
+        <v>1630.9233118002</v>
       </c>
       <c r="O194" t="n">
-        <v>1343880.694631763</v>
+        <v>1265596.489956955</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
       </c>
       <c r="Q194" t="n">
-        <v>2060000</v>
+        <v>1940000</v>
       </c>
     </row>
     <row r="195">
@@ -9011,22 +9011,22 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M196" t="n">
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="N196" t="n">
-        <v>1690.6023498845</v>
+        <v>1690.6006518987</v>
       </c>
       <c r="O196" t="n">
-        <v>649191.302355648</v>
+        <v>486892.9877468256</v>
       </c>
       <c r="P196" t="n">
         <v>2900</v>
       </c>
       <c r="Q196" t="n">
-        <v>1113600</v>
+        <v>835200</v>
       </c>
     </row>
     <row r="197">
@@ -9057,22 +9057,22 @@
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M197" t="n">
-        <v>2118</v>
+        <v>2022</v>
       </c>
       <c r="N197" t="n">
-        <v>1550.193183768</v>
+        <v>1550.1933219945</v>
       </c>
       <c r="O197" t="n">
-        <v>3283309.163220624</v>
+        <v>3134490.897072879</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
       </c>
       <c r="Q197" t="n">
-        <v>5295000</v>
+        <v>5055000</v>
       </c>
     </row>
     <row r="198">
@@ -9109,10 +9109,10 @@
         <v>22</v>
       </c>
       <c r="N198" t="n">
-        <v>1579.3909343434</v>
+        <v>1579.3908883249</v>
       </c>
       <c r="O198" t="n">
-        <v>34746.6005555548</v>
+        <v>34746.5995431478</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9149,22 +9149,22 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M199" t="n">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="N199" t="n">
-        <v>2403.5104597508</v>
+        <v>2403.5107961064</v>
       </c>
       <c r="O199" t="n">
-        <v>1091193.748726863</v>
+        <v>1004667.512772475</v>
       </c>
       <c r="P199" t="n">
         <v>3500</v>
       </c>
       <c r="Q199" t="n">
-        <v>1589000</v>
+        <v>1463000</v>
       </c>
     </row>
     <row r="200">
@@ -9195,22 +9195,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M200" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>2521.5426705653</v>
+        <v>2521.5415942029</v>
       </c>
       <c r="O200" t="n">
-        <v>201723.413645224</v>
+        <v>0</v>
       </c>
       <c r="P200" t="n">
         <v>3900</v>
       </c>
       <c r="Q200" t="n">
-        <v>312000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -11143,10 +11143,10 @@
         <v>12</v>
       </c>
       <c r="N244" t="n">
-        <v>3731.0243377483</v>
+        <v>3731.0243521595</v>
       </c>
       <c r="O244" t="n">
-        <v>44772.2920529796</v>
+        <v>44772.292225914</v>
       </c>
       <c r="P244" t="n">
         <v>5200</v>
@@ -11284,10 +11284,10 @@
         <v>125</v>
       </c>
       <c r="N247" t="n">
-        <v>4285.1952806653</v>
+        <v>4285.1953699789</v>
       </c>
       <c r="O247" t="n">
-        <v>535649.4100831625</v>
+        <v>535649.4212473625</v>
       </c>
       <c r="P247" t="n">
         <v>6900</v>
@@ -12126,10 +12126,10 @@
         <v>599</v>
       </c>
       <c r="N266" t="n">
-        <v>1560.9994428152</v>
+        <v>1560.9995548961</v>
       </c>
       <c r="O266" t="n">
-        <v>935038.6662463048</v>
+        <v>935038.7333827639</v>
       </c>
       <c r="P266" t="n">
         <v>2900</v>
@@ -12449,10 +12449,10 @@
         <v>306</v>
       </c>
       <c r="N273" t="n">
-        <v>548.14724692526</v>
+        <v>548.14724170616</v>
       </c>
       <c r="O273" t="n">
-        <v>167733.0575591295</v>
+        <v>167733.055962085</v>
       </c>
       <c r="P273" t="n">
         <v>2000</v>
@@ -13013,10 +13013,10 @@
         <v>122</v>
       </c>
       <c r="N285" t="n">
-        <v>3113.8900262812</v>
+        <v>3113.8900265957</v>
       </c>
       <c r="O285" t="n">
-        <v>379894.5832063064</v>
+        <v>379894.5832446754</v>
       </c>
       <c r="P285" t="n">
         <v>5000</v>
@@ -13099,22 +13099,22 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M287" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
         <v>4690.64</v>
       </c>
       <c r="O287" t="n">
-        <v>117266</v>
+        <v>0</v>
       </c>
       <c r="P287" t="n">
         <v>7500</v>
       </c>
       <c r="Q287" t="n">
-        <v>187500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -13329,22 +13329,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M292" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="N292" t="n">
         <v>3254.49</v>
       </c>
       <c r="O292" t="n">
-        <v>263613.69</v>
+        <v>198523.89</v>
       </c>
       <c r="P292" t="n">
         <v>5200</v>
       </c>
       <c r="Q292" t="n">
-        <v>421200</v>
+        <v>317200</v>
       </c>
     </row>
     <row r="293">
@@ -13381,10 +13381,10 @@
         <v>81</v>
       </c>
       <c r="N293" t="n">
-        <v>5218.170521327</v>
+        <v>5218.1705238095</v>
       </c>
       <c r="O293" t="n">
-        <v>422671.812227487</v>
+        <v>422671.8124285695</v>
       </c>
       <c r="P293" t="n">
         <v>8500</v>
@@ -13427,10 +13427,10 @@
         <v>1</v>
       </c>
       <c r="N294" t="n">
-        <v>1595.0094476744</v>
+        <v>1595.0094378698</v>
       </c>
       <c r="O294" t="n">
-        <v>1595.0094476744</v>
+        <v>1595.0094378698</v>
       </c>
       <c r="P294" t="n">
         <v>2600</v>
@@ -13473,10 +13473,10 @@
         <v>123</v>
       </c>
       <c r="N295" t="n">
-        <v>3610.6500249688</v>
+        <v>3610.6500252207</v>
       </c>
       <c r="O295" t="n">
-        <v>444109.9530711624</v>
+        <v>444109.9531021461</v>
       </c>
       <c r="P295" t="n">
         <v>5800</v>
@@ -13700,22 +13700,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M300" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="N300" t="n">
         <v>3965.02</v>
       </c>
       <c r="O300" t="n">
-        <v>305306.54</v>
+        <v>146705.74</v>
       </c>
       <c r="P300" t="n">
         <v>6500</v>
       </c>
       <c r="Q300" t="n">
-        <v>500500</v>
+        <v>240500</v>
       </c>
     </row>
     <row r="301">
@@ -13930,22 +13930,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M305" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N305" t="n">
-        <v>1664.3590294957</v>
+        <v>1664.3585273632</v>
       </c>
       <c r="O305" t="n">
-        <v>79889.2334157936</v>
+        <v>0</v>
       </c>
       <c r="P305" t="n">
         <v>2900</v>
       </c>
       <c r="Q305" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -14215,10 +14215,10 @@
         <v>824</v>
       </c>
       <c r="N311" t="n">
-        <v>1778.4725680247</v>
+        <v>1778.4725740823</v>
       </c>
       <c r="O311" t="n">
-        <v>1465461.396052353</v>
+        <v>1465461.401043815</v>
       </c>
       <c r="P311" t="n">
         <v>4900</v>
@@ -15457,22 +15457,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M338" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N338" t="n">
         <v>40438.3</v>
       </c>
       <c r="O338" t="n">
-        <v>121314.9</v>
+        <v>0</v>
       </c>
       <c r="P338" t="n">
         <v>49900</v>
       </c>
       <c r="Q338" t="n">
-        <v>149700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -16015,22 +16015,22 @@
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M350" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N350" t="n">
         <v>12709</v>
       </c>
       <c r="O350" t="n">
-        <v>76254</v>
+        <v>0</v>
       </c>
       <c r="P350" t="n">
         <v>20500</v>
       </c>
       <c r="Q350" t="n">
-        <v>123000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -17313,10 +17313,10 @@
         <v>149</v>
       </c>
       <c r="N378" t="n">
-        <v>4907.8219751166</v>
+        <v>4907.8219812793</v>
       </c>
       <c r="O378" t="n">
-        <v>731265.4742923734</v>
+        <v>731265.4752106158</v>
       </c>
       <c r="P378" t="n">
         <v>8200</v>
@@ -19048,22 +19048,22 @@
         <v>0</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M416" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N416" t="n">
         <v>29835</v>
       </c>
       <c r="O416" t="n">
-        <v>208845</v>
+        <v>59670</v>
       </c>
       <c r="P416" t="n">
         <v>47900</v>
       </c>
       <c r="Q416" t="n">
-        <v>335300</v>
+        <v>95800</v>
       </c>
     </row>
     <row r="417">
@@ -19836,10 +19836,10 @@
         <v>1320</v>
       </c>
       <c r="N433" t="n">
-        <v>1516.0388102832</v>
+        <v>1516.0388052024</v>
       </c>
       <c r="O433" t="n">
-        <v>2001171.229573824</v>
+        <v>2001171.222867168</v>
       </c>
       <c r="P433" t="n">
         <v>2300</v>
@@ -19928,10 +19928,10 @@
         <v>8</v>
       </c>
       <c r="N435" t="n">
-        <v>4248.635</v>
+        <v>4248.6401470588</v>
       </c>
       <c r="O435" t="n">
-        <v>33989.08</v>
+        <v>33989.1211764704</v>
       </c>
       <c r="P435" t="n">
         <v>5900</v>
@@ -20020,10 +20020,10 @@
         <v>192</v>
       </c>
       <c r="N437" t="n">
-        <v>1771.0911179361</v>
+        <v>1771.0908132147</v>
       </c>
       <c r="O437" t="n">
-        <v>340049.4946437312</v>
+        <v>340049.4361372224</v>
       </c>
       <c r="P437" t="n">
         <v>2500</v>
@@ -20066,10 +20066,10 @@
         <v>264</v>
       </c>
       <c r="N438" t="n">
-        <v>2079.3841813438</v>
+        <v>2079.3841354372</v>
       </c>
       <c r="O438" t="n">
-        <v>548957.4238747632</v>
+        <v>548957.4117554207</v>
       </c>
       <c r="P438" t="n">
         <v>2900</v>
@@ -20112,10 +20112,10 @@
         <v>192</v>
       </c>
       <c r="N439" t="n">
-        <v>1803.0151724138</v>
+        <v>1803.0152234206</v>
       </c>
       <c r="O439" t="n">
-        <v>346178.9131034496</v>
+        <v>346178.9228967552</v>
       </c>
       <c r="P439" t="n">
         <v>2500</v>
@@ -20158,10 +20158,10 @@
         <v>216</v>
       </c>
       <c r="N440" t="n">
-        <v>3306.5953488372</v>
+        <v>3306.5953246753</v>
       </c>
       <c r="O440" t="n">
-        <v>714224.5953488352</v>
+        <v>714224.5901298649</v>
       </c>
       <c r="P440" t="n">
         <v>4900</v>
@@ -20204,10 +20204,10 @@
         <v>192</v>
       </c>
       <c r="N441" t="n">
-        <v>2122.1640036787</v>
+        <v>2122.164</v>
       </c>
       <c r="O441" t="n">
-        <v>407455.4887063104</v>
+        <v>407455.488</v>
       </c>
       <c r="P441" t="n">
         <v>2900</v>
@@ -20250,10 +20250,10 @@
         <v>216</v>
       </c>
       <c r="N442" t="n">
-        <v>2108.7900518135</v>
+        <v>2108.7900692042</v>
       </c>
       <c r="O442" t="n">
-        <v>455498.651191716</v>
+        <v>455498.6549481072</v>
       </c>
       <c r="P442" t="n">
         <v>2900</v>
@@ -20296,10 +20296,10 @@
         <v>144</v>
       </c>
       <c r="N443" t="n">
-        <v>2056.0837188071</v>
+        <v>2056.0837111517</v>
       </c>
       <c r="O443" t="n">
-        <v>296076.0555082224</v>
+        <v>296076.0544058448</v>
       </c>
       <c r="P443" t="n">
         <v>2900</v>
@@ -20388,10 +20388,10 @@
         <v>360</v>
       </c>
       <c r="N445" t="n">
-        <v>1655.9310223953</v>
+        <v>1655.9309931618</v>
       </c>
       <c r="O445" t="n">
-        <v>596135.168062308</v>
+        <v>596135.157538248</v>
       </c>
       <c r="P445" t="n">
         <v>2500</v>
@@ -20612,22 +20612,22 @@
         <v>0</v>
       </c>
       <c r="L450" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M450" t="n">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="N450" t="n">
-        <v>1592.2756948933</v>
+        <v>1592.27610957</v>
       </c>
       <c r="O450" t="n">
-        <v>636910.27795732</v>
+        <v>611434.02607488</v>
       </c>
       <c r="P450" t="n">
         <v>2500</v>
       </c>
       <c r="Q450" t="n">
-        <v>1000000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="451">
@@ -20743,22 +20743,22 @@
         <v>0</v>
       </c>
       <c r="L453" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M453" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N453" t="n">
-        <v>2311.9246983547</v>
+        <v>2311.9221535181</v>
       </c>
       <c r="O453" t="n">
-        <v>27743.0963802564</v>
+        <v>0</v>
       </c>
       <c r="P453" t="n">
         <v>3500</v>
       </c>
       <c r="Q453" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -20789,22 +20789,22 @@
         <v>0</v>
       </c>
       <c r="L454" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M454" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N454" t="n">
-        <v>1906.18625</v>
+        <v>1906.1853846154</v>
       </c>
       <c r="O454" t="n">
-        <v>91496.94</v>
+        <v>0</v>
       </c>
       <c r="P454" t="n">
         <v>2900</v>
       </c>
       <c r="Q454" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -20835,22 +20835,22 @@
         <v>0</v>
       </c>
       <c r="L455" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M455" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="N455" t="n">
-        <v>3033.7273039216</v>
+        <v>3033.7269651741</v>
       </c>
       <c r="O455" t="n">
-        <v>364047.276470592</v>
+        <v>0</v>
       </c>
       <c r="P455" t="n">
         <v>4500</v>
       </c>
       <c r="Q455" t="n">
-        <v>540000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -20927,22 +20927,22 @@
         <v>0</v>
       </c>
       <c r="L457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M457" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="N457" t="n">
-        <v>1668.6199591002</v>
+        <v>1668.6236893204</v>
       </c>
       <c r="O457" t="n">
-        <v>120140.6370552144</v>
+        <v>40046.9685436896</v>
       </c>
       <c r="P457" t="n">
         <v>2500</v>
       </c>
       <c r="Q457" t="n">
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="458">
@@ -20973,22 +20973,22 @@
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M458" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="N458" t="n">
-        <v>2546.985</v>
+        <v>2546.9846915888</v>
       </c>
       <c r="O458" t="n">
-        <v>183382.92</v>
+        <v>61127.6325981312</v>
       </c>
       <c r="P458" t="n">
         <v>3900</v>
       </c>
       <c r="Q458" t="n">
-        <v>280800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="459">
@@ -21158,10 +21158,10 @@
         <v>72</v>
       </c>
       <c r="N462" t="n">
-        <v>2556.7453211009</v>
+        <v>2556.7455948553</v>
       </c>
       <c r="O462" t="n">
-        <v>184085.6631192648</v>
+        <v>184085.6828295816</v>
       </c>
       <c r="P462" t="n">
         <v>3900</v>
@@ -21248,10 +21248,10 @@
         <v>540</v>
       </c>
       <c r="N464" t="n">
-        <v>692.15209736124</v>
+        <v>692.15211662075</v>
       </c>
       <c r="O464" t="n">
-        <v>373762.1325750696</v>
+        <v>373762.142975205</v>
       </c>
       <c r="P464" t="n">
         <v>1200</v>
@@ -21803,10 +21803,10 @@
         <v>46</v>
       </c>
       <c r="N476" t="n">
-        <v>3026.514679803</v>
+        <v>3026.5149222798</v>
       </c>
       <c r="O476" t="n">
-        <v>139219.675270938</v>
+        <v>139219.6864248708</v>
       </c>
       <c r="P476" t="n">
         <v>7000</v>
@@ -21945,10 +21945,10 @@
         <v>360</v>
       </c>
       <c r="N479" t="n">
-        <v>1530.4499206034</v>
+        <v>1530.4499195171</v>
       </c>
       <c r="O479" t="n">
-        <v>550961.971417224</v>
+        <v>550961.971026156</v>
       </c>
       <c r="P479" t="n">
         <v>2600</v>
@@ -22404,10 +22404,10 @@
         <v>306</v>
       </c>
       <c r="N489" t="n">
-        <v>1690.8700089606</v>
+        <v>1690.8700089847</v>
       </c>
       <c r="O489" t="n">
-        <v>517406.2227419436</v>
+        <v>517406.2227493182</v>
       </c>
       <c r="P489" t="n">
         <v>3000</v>
@@ -22551,10 +22551,10 @@
         <v>3</v>
       </c>
       <c r="N492" t="n">
-        <v>2270.3211494253</v>
+        <v>2270.3211627907</v>
       </c>
       <c r="O492" t="n">
-        <v>6810.9634482759</v>
+        <v>6810.963488372099</v>
       </c>
       <c r="P492" t="n">
         <v>3900</v>
@@ -23241,22 +23241,22 @@
         <v>0</v>
       </c>
       <c r="L507" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M507" t="n">
-        <v>749</v>
+        <v>461</v>
       </c>
       <c r="N507" t="n">
-        <v>517.28824762181</v>
+        <v>517.28836312001</v>
       </c>
       <c r="O507" t="n">
-        <v>387448.8974687357</v>
+        <v>238469.9353983246</v>
       </c>
       <c r="P507" t="n">
         <v>900</v>
       </c>
       <c r="Q507" t="n">
-        <v>674100</v>
+        <v>414900</v>
       </c>
     </row>
     <row r="508">
@@ -23670,10 +23670,10 @@
         <v>757</v>
       </c>
       <c r="N516" t="n">
-        <v>3110.8426932617</v>
+        <v>3110.8426185007</v>
       </c>
       <c r="O516" t="n">
-        <v>2354907.918799107</v>
+        <v>2354907.86220503</v>
       </c>
       <c r="P516" t="n">
         <v>4500</v>
@@ -24121,10 +24121,10 @@
         <v>20090</v>
       </c>
       <c r="N526" t="n">
-        <v>703.7953201758</v>
+        <v>703.79529676406</v>
       </c>
       <c r="O526" t="n">
-        <v>14139247.98233182</v>
+        <v>14139247.51198997</v>
       </c>
       <c r="P526" t="n">
         <v>900</v>
@@ -24628,10 +24628,10 @@
         <v>47</v>
       </c>
       <c r="N537" t="n">
-        <v>1595.5155292429</v>
+        <v>1595.5153131828</v>
       </c>
       <c r="O537" t="n">
-        <v>74989.2298744163</v>
+        <v>74989.21971959159</v>
       </c>
       <c r="P537" t="n">
         <v>2500</v>
@@ -25017,10 +25017,10 @@
         <v>168</v>
       </c>
       <c r="N545" t="n">
-        <v>2098.4049147727</v>
+        <v>2098.4049570201</v>
       </c>
       <c r="O545" t="n">
-        <v>352532.0256818136</v>
+        <v>352532.0327793768</v>
       </c>
       <c r="P545" t="n">
         <v>9500</v>
@@ -25781,22 +25781,22 @@
         <v>0</v>
       </c>
       <c r="L561" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M561" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N561" t="n">
-        <v>23475.658064516</v>
+        <v>23475.658</v>
       </c>
       <c r="O561" t="n">
-        <v>563415.793548384</v>
+        <v>422561.844</v>
       </c>
       <c r="P561" t="n">
         <v>31900</v>
       </c>
       <c r="Q561" t="n">
-        <v>765600</v>
+        <v>574200</v>
       </c>
     </row>
     <row r="562">
@@ -26546,22 +26546,22 @@
         <v>0</v>
       </c>
       <c r="L577" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M577" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N577" t="n">
         <v>3067.0905454545</v>
       </c>
       <c r="O577" t="n">
-        <v>343514.141090904</v>
+        <v>325111.597818177</v>
       </c>
       <c r="P577" t="n">
         <v>7200</v>
       </c>
       <c r="Q577" t="n">
-        <v>806400</v>
+        <v>763200</v>
       </c>
     </row>
     <row r="578">
@@ -26932,22 +26932,22 @@
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M585" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N585" t="n">
         <v>10378.12</v>
       </c>
       <c r="O585" t="n">
-        <v>778359.0000000001</v>
+        <v>674577.8</v>
       </c>
       <c r="P585" t="n">
         <v>13500</v>
       </c>
       <c r="Q585" t="n">
-        <v>1012500</v>
+        <v>877500</v>
       </c>
     </row>
     <row r="586">
@@ -28642,10 +28642,10 @@
         <v>1105</v>
       </c>
       <c r="N621" t="n">
-        <v>7046.9398298958</v>
+        <v>7046.9398286204</v>
       </c>
       <c r="O621" t="n">
-        <v>7786868.51203486</v>
+        <v>7786868.510625541</v>
       </c>
       <c r="P621" t="n">
         <v>9900</v>
@@ -28682,22 +28682,22 @@
         <v>0</v>
       </c>
       <c r="L622" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M622" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="N622" t="n">
         <v>24338.47</v>
       </c>
       <c r="O622" t="n">
-        <v>3480401.21</v>
+        <v>3188339.57</v>
       </c>
       <c r="P622" t="n">
         <v>27900</v>
       </c>
       <c r="Q622" t="n">
-        <v>3989700</v>
+        <v>3654900</v>
       </c>
     </row>
     <row r="623">
@@ -28832,10 +28832,10 @@
         <v>648</v>
       </c>
       <c r="N625" t="n">
-        <v>665.3234571176</v>
+        <v>665.32347555556</v>
       </c>
       <c r="O625" t="n">
-        <v>431129.6002122048</v>
+        <v>431129.6121600029</v>
       </c>
       <c r="P625" t="n">
         <v>2900</v>
@@ -29571,10 +29571,10 @@
         <v>30</v>
       </c>
       <c r="N641" t="n">
-        <v>5577.2680733945</v>
+        <v>5577.2680465116</v>
       </c>
       <c r="O641" t="n">
-        <v>167318.042201835</v>
+        <v>167318.041395348</v>
       </c>
       <c r="P641" t="n">
         <v>6500</v>
@@ -29615,10 +29615,10 @@
         <v>40</v>
       </c>
       <c r="N642" t="n">
-        <v>6243.3530555556</v>
+        <v>6243.3531428571</v>
       </c>
       <c r="O642" t="n">
-        <v>249734.122222224</v>
+        <v>249734.125714284</v>
       </c>
       <c r="P642" t="n">
         <v>9900</v>
@@ -30130,22 +30130,22 @@
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M654" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N654" t="n">
         <v>8922.214942528701</v>
       </c>
       <c r="O654" t="n">
-        <v>481799.6068965498</v>
+        <v>428266.3172413777</v>
       </c>
       <c r="P654" t="n">
         <v>8200</v>
       </c>
       <c r="Q654" t="n">
-        <v>442800</v>
+        <v>393600</v>
       </c>
     </row>
     <row r="655">
@@ -30316,10 +30316,10 @@
         <v>352</v>
       </c>
       <c r="N658" t="n">
-        <v>22951.704968711</v>
+        <v>22951.704962406</v>
       </c>
       <c r="O658" t="n">
-        <v>8079000.148986273</v>
+        <v>8079000.146766911</v>
       </c>
       <c r="P658" t="n">
         <v>37900</v>
@@ -30403,10 +30403,10 @@
         <v>93</v>
       </c>
       <c r="N660" t="n">
-        <v>4985.4047058824</v>
+        <v>4985.4047808765</v>
       </c>
       <c r="O660" t="n">
-        <v>463642.6376470632</v>
+        <v>463642.6446215145</v>
       </c>
       <c r="P660" t="n">
         <v>7900</v>
@@ -30454,10 +30454,10 @@
         <v>8</v>
       </c>
       <c r="N661" t="n">
-        <v>1547.8824637681</v>
+        <v>1547.8825373134</v>
       </c>
       <c r="O661" t="n">
-        <v>12383.0597101448</v>
+        <v>12383.0602985072</v>
       </c>
       <c r="P661" t="n">
         <v>5500</v>
@@ -30643,10 +30643,10 @@
         <v>4200</v>
       </c>
       <c r="N665" t="n">
-        <v>220.00713026296</v>
+        <v>220.00693162525</v>
       </c>
       <c r="O665" t="n">
-        <v>924029.947104432</v>
+        <v>924029.1128260499</v>
       </c>
       <c r="P665" t="n">
         <v>260</v>
@@ -30913,22 +30913,22 @@
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M671" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N671" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O671" t="n">
-        <v>184455.61</v>
+        <v>155331.04</v>
       </c>
       <c r="P671" t="n">
         <v>10200</v>
       </c>
       <c r="Q671" t="n">
-        <v>193800</v>
+        <v>163200</v>
       </c>
     </row>
     <row r="672">
@@ -31097,22 +31097,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M675" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N675" t="n">
         <v>17986.24</v>
       </c>
       <c r="O675" t="n">
-        <v>1654734.08</v>
+        <v>1528830.4</v>
       </c>
       <c r="P675" t="n">
         <v>18500</v>
       </c>
       <c r="Q675" t="n">
-        <v>1702000</v>
+        <v>1572500</v>
       </c>
     </row>
     <row r="676">
@@ -31710,22 +31710,22 @@
         <v>0</v>
       </c>
       <c r="L688" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M688" t="n">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="N688" t="n">
         <v>2058.92</v>
       </c>
       <c r="O688" t="n">
-        <v>366487.76</v>
+        <v>325309.36</v>
       </c>
       <c r="P688" t="n">
         <v>2500</v>
       </c>
       <c r="Q688" t="n">
-        <v>445000</v>
+        <v>395000</v>
       </c>
     </row>
     <row r="689">
@@ -31756,22 +31756,22 @@
         <v>0</v>
       </c>
       <c r="L689" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M689" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="N689" t="n">
         <v>3306.0098310139</v>
       </c>
       <c r="O689" t="n">
-        <v>380191.1305665985</v>
+        <v>314070.9339463205</v>
       </c>
       <c r="P689" t="n">
         <v>4200</v>
       </c>
       <c r="Q689" t="n">
-        <v>483000</v>
+        <v>399000</v>
       </c>
     </row>
     <row r="690">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1471,10 +1471,10 @@
         <v>120</v>
       </c>
       <c r="N27" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O27" t="n">
-        <v>445959.623076924</v>
+        <v>445959.623225808</v>
       </c>
       <c r="P27" t="n">
         <v>9500</v>
@@ -2217,10 +2217,10 @@
         <v>46</v>
       </c>
       <c r="N45" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O45" t="n">
-        <v>6505176.689090701</v>
+        <v>6505176.68977196</v>
       </c>
       <c r="P45" t="n">
         <v>251900</v>
@@ -2565,10 +2565,10 @@
         <v>144</v>
       </c>
       <c r="N53" t="n">
-        <v>580.36600536193</v>
+        <v>580.36599462366</v>
       </c>
       <c r="O53" t="n">
-        <v>83572.70477211791</v>
+        <v>83572.70322580704</v>
       </c>
       <c r="P53" t="n">
         <v>6800</v>
@@ -2657,10 +2657,10 @@
         <v>14</v>
       </c>
       <c r="N55" t="n">
-        <v>28.165539906103</v>
+        <v>28.165518867925</v>
       </c>
       <c r="O55" t="n">
-        <v>394.317558685442</v>
+        <v>394.31726415095</v>
       </c>
       <c r="P55" t="n">
         <v>6800</v>
@@ -3391,10 +3391,10 @@
         <v>1295</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0561100153</v>
+        <v>1098.0566124294</v>
       </c>
       <c r="O72" t="n">
-        <v>1421982.662469813</v>
+        <v>1421983.313096073</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -4324,10 +4324,10 @@
         <v>771</v>
       </c>
       <c r="N93" t="n">
-        <v>2582.2559749444</v>
+        <v>2582.255965161</v>
       </c>
       <c r="O93" t="n">
-        <v>1990919.356682132</v>
+        <v>1990919.349139131</v>
       </c>
       <c r="P93" t="n">
         <v>4500</v>
@@ -4647,10 +4647,10 @@
         <v>3199</v>
       </c>
       <c r="N100" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O100" t="n">
-        <v>10105195.77305659</v>
+        <v>10105195.77485635</v>
       </c>
       <c r="P100" t="n">
         <v>5600</v>
@@ -4693,10 +4693,10 @@
         <v>80</v>
       </c>
       <c r="N101" t="n">
-        <v>3841.6247414634</v>
+        <v>3841.6247693817</v>
       </c>
       <c r="O101" t="n">
-        <v>307329.979317072</v>
+        <v>307329.981550536</v>
       </c>
       <c r="P101" t="n">
         <v>6900</v>
@@ -4783,10 +4783,10 @@
         <v>180</v>
       </c>
       <c r="N103" t="n">
-        <v>3230.0675874126</v>
+        <v>3230.0675313059</v>
       </c>
       <c r="O103" t="n">
-        <v>581412.165734268</v>
+        <v>581412.155635062</v>
       </c>
       <c r="P103" t="n">
         <v>6200</v>
@@ -4922,10 +4922,10 @@
         <v>259</v>
       </c>
       <c r="N106" t="n">
-        <v>2694.8233333333</v>
+        <v>2694.8232839963</v>
       </c>
       <c r="O106" t="n">
-        <v>697959.2433333247</v>
+        <v>697959.2305550417</v>
       </c>
       <c r="P106" t="n">
         <v>4900</v>
@@ -5242,10 +5242,10 @@
         <v>593</v>
       </c>
       <c r="N113" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O113" t="n">
-        <v>2250856.034199744</v>
+        <v>2250856.03420271</v>
       </c>
       <c r="P113" t="n">
         <v>6200</v>
@@ -5467,10 +5467,10 @@
         <v>315</v>
       </c>
       <c r="N118" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O118" t="n">
-        <v>1540642.964728234</v>
+        <v>1540642.964754096</v>
       </c>
       <c r="P118" t="n">
         <v>8200</v>
@@ -5911,22 +5911,22 @@
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M128" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N128" t="n">
         <v>10716.34</v>
       </c>
       <c r="O128" t="n">
-        <v>342922.88</v>
+        <v>214326.8</v>
       </c>
       <c r="P128" t="n">
         <v>39000</v>
       </c>
       <c r="Q128" t="n">
-        <v>1248000</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="129">
@@ -6007,10 +6007,10 @@
         <v>108</v>
       </c>
       <c r="N130" t="n">
-        <v>3240.8500303951</v>
+        <v>3240.8500305344</v>
       </c>
       <c r="O130" t="n">
-        <v>350011.8032826708</v>
+        <v>350011.8032977152</v>
       </c>
       <c r="P130" t="n">
         <v>5200</v>
@@ -6191,10 +6191,10 @@
         <v>305</v>
       </c>
       <c r="N134" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O134" t="n">
-        <v>4520825.552874925</v>
+        <v>4520825.55184311</v>
       </c>
       <c r="P134" t="n">
         <v>24900</v>
@@ -6278,22 +6278,22 @@
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M136" t="n">
-        <v>1890</v>
+        <v>1794</v>
       </c>
       <c r="N136" t="n">
         <v>2090.85</v>
       </c>
       <c r="O136" t="n">
-        <v>3951706.5</v>
+        <v>3750984.9</v>
       </c>
       <c r="P136" t="n">
         <v>2900</v>
       </c>
       <c r="Q136" t="n">
-        <v>5481000</v>
+        <v>5202600</v>
       </c>
     </row>
     <row r="137">
@@ -6916,10 +6916,10 @@
         <v>210</v>
       </c>
       <c r="N150" t="n">
-        <v>3041.6600128617</v>
+        <v>3041.660012945</v>
       </c>
       <c r="O150" t="n">
-        <v>638748.602700957</v>
+        <v>638748.60271845</v>
       </c>
       <c r="P150" t="n">
         <v>5500</v>
@@ -7134,10 +7134,10 @@
         <v>480</v>
       </c>
       <c r="N155" t="n">
-        <v>1592.5673455845</v>
+        <v>1592.5672645976</v>
       </c>
       <c r="O155" t="n">
-        <v>764432.32588056</v>
+        <v>764432.2870068479</v>
       </c>
       <c r="P155" t="n">
         <v>3900</v>
@@ -8124,10 +8124,10 @@
         <v>71</v>
       </c>
       <c r="N177" t="n">
-        <v>2021.7211225106</v>
+        <v>2021.7211231884</v>
       </c>
       <c r="O177" t="n">
-        <v>143542.1996982526</v>
+        <v>143542.1997463764</v>
       </c>
       <c r="P177" t="n">
         <v>2400</v>
@@ -8925,10 +8925,10 @@
         <v>776</v>
       </c>
       <c r="N194" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O194" t="n">
-        <v>1265596.489956955</v>
+        <v>1265596.510034713</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8971,10 +8971,10 @@
         <v>5</v>
       </c>
       <c r="N195" t="n">
-        <v>1467.3264227642</v>
+        <v>1467.3258333333</v>
       </c>
       <c r="O195" t="n">
-        <v>7336.632113821001</v>
+        <v>7336.629166666499</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9017,10 +9017,10 @@
         <v>288</v>
       </c>
       <c r="N196" t="n">
-        <v>1690.6006518987</v>
+        <v>1690.6000587084</v>
       </c>
       <c r="O196" t="n">
-        <v>486892.9877468256</v>
+        <v>486892.8169080192</v>
       </c>
       <c r="P196" t="n">
         <v>2900</v>
@@ -9063,10 +9063,10 @@
         <v>2022</v>
       </c>
       <c r="N197" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O197" t="n">
-        <v>3134490.897072879</v>
+        <v>3134490.963259814</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
@@ -9109,10 +9109,10 @@
         <v>22</v>
       </c>
       <c r="N198" t="n">
-        <v>1579.3908883249</v>
+        <v>1579.3908418367</v>
       </c>
       <c r="O198" t="n">
-        <v>34746.5995431478</v>
+        <v>34746.5985204074</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9155,10 +9155,10 @@
         <v>418</v>
       </c>
       <c r="N199" t="n">
-        <v>2403.5107961064</v>
+        <v>2403.5109560769</v>
       </c>
       <c r="O199" t="n">
-        <v>1004667.512772475</v>
+        <v>1004667.579640144</v>
       </c>
       <c r="P199" t="n">
         <v>3500</v>
@@ -9196,10 +9196,10 @@
         <v>65</v>
       </c>
       <c r="N200" t="n">
-        <v>1232.8080088496</v>
+        <v>1232.8076255708</v>
       </c>
       <c r="O200" t="n">
-        <v>80132.520575224</v>
+        <v>80132.495662102</v>
       </c>
       <c r="P200" t="n">
         <v>2400</v>
@@ -11584,10 +11584,10 @@
         <v>32</v>
       </c>
       <c r="N254" t="n">
-        <v>11562.038526316</v>
+        <v>11562.038522427</v>
       </c>
       <c r="O254" t="n">
-        <v>369985.232842112</v>
+        <v>369985.232717664</v>
       </c>
       <c r="P254" t="n">
         <v>18500</v>
@@ -12080,10 +12080,10 @@
         <v>599</v>
       </c>
       <c r="N265" t="n">
-        <v>1560.9995548961</v>
+        <v>1560.9996939288</v>
       </c>
       <c r="O265" t="n">
-        <v>935038.7333827639</v>
+        <v>935038.8166633513</v>
       </c>
       <c r="P265" t="n">
         <v>2900</v>
@@ -12967,10 +12967,10 @@
         <v>122</v>
       </c>
       <c r="N284" t="n">
-        <v>3113.8900265957</v>
+        <v>3113.890027137</v>
       </c>
       <c r="O284" t="n">
-        <v>379894.5832446754</v>
+        <v>379894.583310714</v>
       </c>
       <c r="P284" t="n">
         <v>5000</v>
@@ -13289,10 +13289,10 @@
         <v>81</v>
       </c>
       <c r="N291" t="n">
-        <v>5218.1705238095</v>
+        <v>5218.1705269461</v>
       </c>
       <c r="O291" t="n">
-        <v>422671.8124285695</v>
+        <v>422671.8126826341</v>
       </c>
       <c r="P291" t="n">
         <v>8500</v>
@@ -13335,10 +13335,10 @@
         <v>1</v>
       </c>
       <c r="N292" t="n">
-        <v>1595.0094378698</v>
+        <v>1595.0094189602</v>
       </c>
       <c r="O292" t="n">
-        <v>1595.0094378698</v>
+        <v>1595.0094189602</v>
       </c>
       <c r="P292" t="n">
         <v>2600</v>
@@ -13381,10 +13381,10 @@
         <v>123</v>
       </c>
       <c r="N293" t="n">
-        <v>3610.6500252207</v>
+        <v>3610.6500253807</v>
       </c>
       <c r="O293" t="n">
-        <v>444109.9531021461</v>
+        <v>444109.9531218261</v>
       </c>
       <c r="P293" t="n">
         <v>5800</v>
@@ -14031,10 +14031,10 @@
         <v>13</v>
       </c>
       <c r="N307" t="n">
-        <v>23521.62453125</v>
+        <v>23521.624354839</v>
       </c>
       <c r="O307" t="n">
-        <v>305781.11890625</v>
+        <v>305781.116612907</v>
       </c>
       <c r="P307" t="n">
         <v>39000</v>
@@ -14077,10 +14077,10 @@
         <v>824</v>
       </c>
       <c r="N308" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O308" t="n">
-        <v>1465461.401043815</v>
+        <v>1465461.406687391</v>
       </c>
       <c r="P308" t="n">
         <v>4900</v>
@@ -16436,10 +16436,10 @@
         <v>324</v>
       </c>
       <c r="N359" t="n">
-        <v>2328.1187488882</v>
+        <v>2328.118739546</v>
       </c>
       <c r="O359" t="n">
-        <v>754310.4746397769</v>
+        <v>754310.471612904</v>
       </c>
       <c r="P359" t="n">
         <v>4500</v>
@@ -17310,10 +17310,10 @@
         <v>289</v>
       </c>
       <c r="N378" t="n">
-        <v>3903.7362017804</v>
+        <v>3903.736812933</v>
       </c>
       <c r="O378" t="n">
-        <v>1128179.762314535</v>
+        <v>1128179.938937637</v>
       </c>
       <c r="P378" t="n">
         <v>7500</v>
@@ -17581,10 +17581,10 @@
         <v>48</v>
       </c>
       <c r="N384" t="n">
-        <v>5869.1727464789</v>
+        <v>5869.1727391742</v>
       </c>
       <c r="O384" t="n">
-        <v>281720.2918309872</v>
+        <v>281720.2914803616</v>
       </c>
       <c r="P384" t="n">
         <v>9500</v>
@@ -19695,10 +19695,10 @@
         <v>8</v>
       </c>
       <c r="N430" t="n">
-        <v>4248.6401470588</v>
+        <v>4248.6496363636</v>
       </c>
       <c r="O430" t="n">
-        <v>33989.1211764704</v>
+        <v>33989.1970909088</v>
       </c>
       <c r="P430" t="n">
         <v>5900</v>
@@ -19833,10 +19833,10 @@
         <v>264</v>
       </c>
       <c r="N433" t="n">
-        <v>2079.3841354372</v>
+        <v>2079.384121911</v>
       </c>
       <c r="O433" t="n">
-        <v>548957.4117554207</v>
+        <v>548957.408184504</v>
       </c>
       <c r="P433" t="n">
         <v>2900</v>
@@ -19879,10 +19879,10 @@
         <v>192</v>
       </c>
       <c r="N434" t="n">
-        <v>1803.0152234206</v>
+        <v>1803.0152282542</v>
       </c>
       <c r="O434" t="n">
-        <v>346178.9228967552</v>
+        <v>346178.9238248064</v>
       </c>
       <c r="P434" t="n">
         <v>2500</v>
@@ -19925,10 +19925,10 @@
         <v>216</v>
       </c>
       <c r="N435" t="n">
-        <v>3306.5953246753</v>
+        <v>3306.5952380952</v>
       </c>
       <c r="O435" t="n">
-        <v>714224.5901298649</v>
+        <v>714224.5714285632</v>
       </c>
       <c r="P435" t="n">
         <v>4900</v>
@@ -19971,10 +19971,10 @@
         <v>192</v>
       </c>
       <c r="N436" t="n">
-        <v>2122.164</v>
+        <v>2122.1639833897</v>
       </c>
       <c r="O436" t="n">
-        <v>407455.488</v>
+        <v>407455.4848108224</v>
       </c>
       <c r="P436" t="n">
         <v>2900</v>
@@ -20017,10 +20017,10 @@
         <v>216</v>
       </c>
       <c r="N437" t="n">
-        <v>2108.7900692042</v>
+        <v>2108.7902645503</v>
       </c>
       <c r="O437" t="n">
-        <v>455498.6549481072</v>
+        <v>455498.6971428648</v>
       </c>
       <c r="P437" t="n">
         <v>2900</v>
@@ -20063,10 +20063,10 @@
         <v>144</v>
       </c>
       <c r="N438" t="n">
-        <v>2056.0837111517</v>
+        <v>2056.0836725935</v>
       </c>
       <c r="O438" t="n">
-        <v>296076.0544058448</v>
+        <v>296076.048853464</v>
       </c>
       <c r="P438" t="n">
         <v>2900</v>
@@ -20385,10 +20385,10 @@
         <v>384</v>
       </c>
       <c r="N445" t="n">
-        <v>1592.27610957</v>
+        <v>1592.2763108883</v>
       </c>
       <c r="O445" t="n">
-        <v>611434.02607488</v>
+        <v>611434.1033811072</v>
       </c>
       <c r="P445" t="n">
         <v>2500</v>
@@ -20516,10 +20516,10 @@
         <v>408</v>
       </c>
       <c r="N448" t="n">
-        <v>2060.1604635762</v>
+        <v>2060.1603355705</v>
       </c>
       <c r="O448" t="n">
-        <v>840545.4691390896</v>
+        <v>840545.4169127641</v>
       </c>
       <c r="P448" t="n">
         <v>2900</v>
@@ -20562,10 +20562,10 @@
         <v>24</v>
       </c>
       <c r="N449" t="n">
-        <v>1668.6236893204</v>
+        <v>1668.6240987654</v>
       </c>
       <c r="O449" t="n">
-        <v>40046.9685436896</v>
+        <v>40046.9783703696</v>
       </c>
       <c r="P449" t="n">
         <v>2500</v>
@@ -20608,10 +20608,10 @@
         <v>24</v>
       </c>
       <c r="N450" t="n">
-        <v>2546.9846915888</v>
+        <v>2546.9846816479</v>
       </c>
       <c r="O450" t="n">
-        <v>61127.6325981312</v>
+        <v>61127.63235954959</v>
       </c>
       <c r="P450" t="n">
         <v>3900</v>
@@ -20654,10 +20654,10 @@
         <v>800</v>
       </c>
       <c r="N451" t="n">
-        <v>1259.2744638514</v>
+        <v>1259.2745016722</v>
       </c>
       <c r="O451" t="n">
-        <v>1007419.57108112</v>
+        <v>1007419.60133776</v>
       </c>
       <c r="P451" t="n">
         <v>1900</v>
@@ -20877,10 +20877,10 @@
         <v>540</v>
       </c>
       <c r="N456" t="n">
-        <v>692.15211662075</v>
+        <v>692.1521205151799</v>
       </c>
       <c r="O456" t="n">
-        <v>373762.142975205</v>
+        <v>373762.1450781972</v>
       </c>
       <c r="P456" t="n">
         <v>1200</v>
@@ -22033,10 +22033,10 @@
         <v>306</v>
       </c>
       <c r="N481" t="n">
-        <v>1690.8700089847</v>
+        <v>1690.870009009</v>
       </c>
       <c r="O481" t="n">
-        <v>517406.2227493182</v>
+        <v>517406.222756754</v>
       </c>
       <c r="P481" t="n">
         <v>3000</v>
@@ -22642,10 +22642,10 @@
         <v>149</v>
       </c>
       <c r="N494" t="n">
-        <v>1283.653986711</v>
+        <v>1283.6539464883</v>
       </c>
       <c r="O494" t="n">
-        <v>191264.444019939</v>
+        <v>191264.4380267567</v>
       </c>
       <c r="P494" t="n">
         <v>1900</v>
@@ -22876,10 +22876,10 @@
         <v>461</v>
       </c>
       <c r="N499" t="n">
-        <v>517.28836312001</v>
+        <v>517.2884408203601</v>
       </c>
       <c r="O499" t="n">
-        <v>238469.9353983246</v>
+        <v>238469.971218186</v>
       </c>
       <c r="P499" t="n">
         <v>900</v>
@@ -23299,10 +23299,10 @@
         <v>757</v>
       </c>
       <c r="N508" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O508" t="n">
-        <v>2354907.86220503</v>
+        <v>2354907.82106647</v>
       </c>
       <c r="P508" t="n">
         <v>4500</v>
@@ -23744,22 +23744,22 @@
         <v>0</v>
       </c>
       <c r="L518" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M518" t="n">
-        <v>20090</v>
+        <v>19802</v>
       </c>
       <c r="N518" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O518" t="n">
-        <v>14139247.51198997</v>
+        <v>13936553.9022762</v>
       </c>
       <c r="P518" t="n">
         <v>900</v>
       </c>
       <c r="Q518" t="n">
-        <v>18081000</v>
+        <v>17821800</v>
       </c>
     </row>
     <row r="519">
@@ -23891,10 +23891,10 @@
         <v>90</v>
       </c>
       <c r="N521" t="n">
-        <v>2501.3851351351</v>
+        <v>2501.3850684932</v>
       </c>
       <c r="O521" t="n">
-        <v>225124.662162159</v>
+        <v>225124.656164388</v>
       </c>
       <c r="P521" t="n">
         <v>4100</v>
@@ -24257,10 +24257,10 @@
         <v>47</v>
       </c>
       <c r="N529" t="n">
-        <v>1595.5153131828</v>
+        <v>1595.5151400147</v>
       </c>
       <c r="O529" t="n">
-        <v>74989.21971959159</v>
+        <v>74989.2115806909</v>
       </c>
       <c r="P529" t="n">
         <v>2500</v>
@@ -26812,10 +26812,10 @@
         <v>17</v>
       </c>
       <c r="N582" t="n">
-        <v>4697.3811428571</v>
+        <v>4697.38125</v>
       </c>
       <c r="O582" t="n">
-        <v>79855.4794285707</v>
+        <v>79855.48125000001</v>
       </c>
       <c r="P582" t="n">
         <v>10900</v>
@@ -27046,10 +27046,10 @@
         <v>24</v>
       </c>
       <c r="N587" t="n">
-        <v>10737.5264</v>
+        <v>10737.526326531</v>
       </c>
       <c r="O587" t="n">
-        <v>257700.6336</v>
+        <v>257700.631836744</v>
       </c>
       <c r="P587" t="n">
         <v>18900</v>
@@ -28461,10 +28461,10 @@
         <v>648</v>
       </c>
       <c r="N617" t="n">
-        <v>665.32347555556</v>
+        <v>665.32351302785</v>
       </c>
       <c r="O617" t="n">
-        <v>431129.6121600029</v>
+        <v>431129.6364420468</v>
       </c>
       <c r="P617" t="n">
         <v>2900</v>
@@ -28899,10 +28899,10 @@
         <v>153</v>
       </c>
       <c r="N626" t="n">
-        <v>315.02679218968</v>
+        <v>315.02685915493</v>
       </c>
       <c r="O626" t="n">
-        <v>48199.09920502104</v>
+        <v>48199.10945070429</v>
       </c>
       <c r="P626" t="n">
         <v>2200</v>
@@ -29765,10 +29765,10 @@
         <v>48</v>
       </c>
       <c r="N646" t="n">
-        <v>8922.214942528701</v>
+        <v>8922.215</v>
       </c>
       <c r="O646" t="n">
-        <v>428266.3172413777</v>
+        <v>428266.32</v>
       </c>
       <c r="P646" t="n">
         <v>8200</v>
@@ -29945,10 +29945,10 @@
         <v>352</v>
       </c>
       <c r="N650" t="n">
-        <v>22951.704962406</v>
+        <v>22951.704956085</v>
       </c>
       <c r="O650" t="n">
-        <v>8079000.146766911</v>
+        <v>8079000.144541919</v>
       </c>
       <c r="P650" t="n">
         <v>37900</v>
@@ -30032,10 +30032,10 @@
         <v>93</v>
       </c>
       <c r="N652" t="n">
-        <v>4985.4047808765</v>
+        <v>4985.4050632911</v>
       </c>
       <c r="O652" t="n">
-        <v>463642.6446215145</v>
+        <v>463642.6708860723</v>
       </c>
       <c r="P652" t="n">
         <v>7900</v>
@@ -30134,10 +30134,10 @@
         <v>306</v>
       </c>
       <c r="N654" t="n">
-        <v>1757.3205416667</v>
+        <v>1757.3205462185</v>
       </c>
       <c r="O654" t="n">
-        <v>537740.0857500102</v>
+        <v>537740.087142861</v>
       </c>
       <c r="P654" t="n">
         <v>2000</v>
@@ -30266,22 +30266,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M657" t="n">
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="N657" t="n">
-        <v>220.00693162525</v>
+        <v>220.00651536869</v>
       </c>
       <c r="O657" t="n">
-        <v>924029.1128260499</v>
+        <v>880026.0614747601</v>
       </c>
       <c r="P657" t="n">
         <v>260</v>
       </c>
       <c r="Q657" t="n">
-        <v>1092000</v>
+        <v>1040000</v>
       </c>
     </row>
     <row r="658">
@@ -31207,10 +31207,10 @@
         <v>18</v>
       </c>
       <c r="N677" t="n">
-        <v>2432.1346</v>
+        <v>2432.1346938776</v>
       </c>
       <c r="O677" t="n">
-        <v>43778.4228</v>
+        <v>43778.4244897968</v>
       </c>
       <c r="P677" t="n">
         <v>4500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -5905,13 +5905,13 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
         <v>20</v>
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>1890</v>
+        <v>1794</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
         <v>1794</v>
@@ -23738,13 +23738,13 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>20090</v>
+        <v>19802</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
       </c>
       <c r="L518" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="M518" t="n">
         <v>19802</v>
@@ -30260,13 +30260,13 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M657" t="n">
         <v>4000</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q695"/>
+  <dimension ref="A1:Q706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3053333333</v>
+        <v>1811.3054760423</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3053333333</v>
+        <v>1811.3054760423</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1705,10 +1705,10 @@
         <v>23</v>
       </c>
       <c r="N33" t="n">
-        <v>14857.6232</v>
+        <v>14857.623214286</v>
       </c>
       <c r="O33" t="n">
-        <v>341725.3336</v>
+        <v>341725.333928578</v>
       </c>
       <c r="P33" t="n">
         <v>34900</v>
@@ -1836,10 +1836,10 @@
         <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>10994.353793103</v>
+        <v>10994.359047619</v>
       </c>
       <c r="O36" t="n">
-        <v>65966.122758618</v>
+        <v>65966.154285714</v>
       </c>
       <c r="P36" t="n">
         <v>16900</v>
@@ -2170,10 +2170,10 @@
         <v>8</v>
       </c>
       <c r="N44" t="n">
-        <v>56906.801935484</v>
+        <v>56906.802333333</v>
       </c>
       <c r="O44" t="n">
-        <v>455254.415483872</v>
+        <v>455254.418666664</v>
       </c>
       <c r="P44" t="n">
         <v>95900</v>
@@ -2259,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>200072.20015748</v>
+        <v>200072.20040323</v>
       </c>
       <c r="O46" t="n">
-        <v>1400505.40110236</v>
+        <v>1400505.40282261</v>
       </c>
       <c r="P46" t="n">
         <v>312000</v>
@@ -3129,10 +3129,10 @@
         <v>228</v>
       </c>
       <c r="N66" t="n">
-        <v>4937.3101612903</v>
+        <v>4937.3101616458</v>
       </c>
       <c r="O66" t="n">
-        <v>1125706.716774188</v>
+        <v>1125706.716855242</v>
       </c>
       <c r="P66" t="n">
         <v>7500</v>
@@ -3391,10 +3391,10 @@
         <v>1295</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0566124294</v>
+        <v>1098.0571872808</v>
       </c>
       <c r="O72" t="n">
-        <v>1421983.313096073</v>
+        <v>1421984.057528636</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -4278,10 +4278,10 @@
         <v>1968</v>
       </c>
       <c r="N92" t="n">
-        <v>3247</v>
+        <v>3250.4653148346</v>
       </c>
       <c r="O92" t="n">
-        <v>6390096</v>
+        <v>6396915.739594493</v>
       </c>
       <c r="P92" t="n">
         <v>5200</v>
@@ -4324,10 +4324,10 @@
         <v>771</v>
       </c>
       <c r="N93" t="n">
-        <v>2582.255965161</v>
+        <v>2582.2559238797</v>
       </c>
       <c r="O93" t="n">
-        <v>1990919.349139131</v>
+        <v>1990919.317311249</v>
       </c>
       <c r="P93" t="n">
         <v>4500</v>
@@ -4364,22 +4364,22 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M94" t="n">
-        <v>1250</v>
+        <v>1235</v>
       </c>
       <c r="N94" t="n">
         <v>10600</v>
       </c>
       <c r="O94" t="n">
-        <v>13250000</v>
+        <v>13091000</v>
       </c>
       <c r="P94" t="n">
         <v>17200</v>
       </c>
       <c r="Q94" t="n">
-        <v>21500000</v>
+        <v>21242000</v>
       </c>
     </row>
     <row r="95">
@@ -4416,10 +4416,10 @@
         <v>720</v>
       </c>
       <c r="N95" t="n">
-        <v>5216.8962134973</v>
+        <v>5216.8961954233</v>
       </c>
       <c r="O95" t="n">
-        <v>3756165.273718056</v>
+        <v>3756165.260704776</v>
       </c>
       <c r="P95" t="n">
         <v>8500</v>
@@ -4647,10 +4647,10 @@
         <v>3199</v>
       </c>
       <c r="N100" t="n">
-        <v>3158.86082365</v>
+        <v>3158.860824576</v>
       </c>
       <c r="O100" t="n">
-        <v>10105195.77485635</v>
+        <v>10105195.77781862</v>
       </c>
       <c r="P100" t="n">
         <v>5600</v>
@@ -4693,10 +4693,10 @@
         <v>80</v>
       </c>
       <c r="N101" t="n">
-        <v>3841.6247693817</v>
+        <v>3841.6247787611</v>
       </c>
       <c r="O101" t="n">
-        <v>307329.981550536</v>
+        <v>307329.982300888</v>
       </c>
       <c r="P101" t="n">
         <v>6900</v>
@@ -4783,10 +4783,10 @@
         <v>180</v>
       </c>
       <c r="N103" t="n">
-        <v>3230.0675313059</v>
+        <v>3230.0675179856</v>
       </c>
       <c r="O103" t="n">
-        <v>581412.155635062</v>
+        <v>581412.1532374079</v>
       </c>
       <c r="P103" t="n">
         <v>6200</v>
@@ -4922,10 +4922,10 @@
         <v>259</v>
       </c>
       <c r="N106" t="n">
-        <v>2694.8232839963</v>
+        <v>2694.8232527881</v>
       </c>
       <c r="O106" t="n">
-        <v>697959.2305550417</v>
+        <v>697959.2224721179</v>
       </c>
       <c r="P106" t="n">
         <v>4900</v>
@@ -4962,22 +4962,22 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M107" t="n">
-        <v>7994</v>
+        <v>5994</v>
       </c>
       <c r="N107" t="n">
         <v>156.25</v>
       </c>
       <c r="O107" t="n">
-        <v>1249062.5</v>
+        <v>936562.5</v>
       </c>
       <c r="P107" t="n">
         <v>250</v>
       </c>
       <c r="Q107" t="n">
-        <v>1998500</v>
+        <v>1498500</v>
       </c>
     </row>
     <row r="108">
@@ -5008,22 +5008,22 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M108" t="n">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="N108" t="n">
         <v>7507.39</v>
       </c>
       <c r="O108" t="n">
-        <v>2237202.22</v>
+        <v>2177143.1</v>
       </c>
       <c r="P108" t="n">
         <v>13500</v>
       </c>
       <c r="Q108" t="n">
-        <v>4023000</v>
+        <v>3915000</v>
       </c>
     </row>
     <row r="109">
@@ -5057,22 +5057,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M109" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N109" t="n">
         <v>8796</v>
       </c>
       <c r="O109" t="n">
-        <v>483780</v>
+        <v>413412</v>
       </c>
       <c r="P109" t="n">
         <v>14900</v>
       </c>
       <c r="Q109" t="n">
-        <v>819500</v>
+        <v>700300</v>
       </c>
     </row>
     <row r="110">
@@ -5242,10 +5242,10 @@
         <v>593</v>
       </c>
       <c r="N113" t="n">
-        <v>3795.7100070872</v>
+        <v>3795.7100071023</v>
       </c>
       <c r="O113" t="n">
-        <v>2250856.03420271</v>
+        <v>2250856.034211664</v>
       </c>
       <c r="P113" t="n">
         <v>6200</v>
@@ -5467,10 +5467,10 @@
         <v>315</v>
       </c>
       <c r="N118" t="n">
-        <v>4890.9300468384</v>
+        <v>4890.9300473934</v>
       </c>
       <c r="O118" t="n">
-        <v>1540642.964754096</v>
+        <v>1540642.964928921</v>
       </c>
       <c r="P118" t="n">
         <v>8200</v>
@@ -5646,10 +5646,10 @@
         <v>324</v>
       </c>
       <c r="N122" t="n">
-        <v>2267.0481583333</v>
+        <v>2267.0481475272</v>
       </c>
       <c r="O122" t="n">
-        <v>734523.6032999891</v>
+        <v>734523.5997988128</v>
       </c>
       <c r="P122" t="n">
         <v>3900</v>
@@ -5911,22 +5911,22 @@
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M128" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N128" t="n">
         <v>10716.34</v>
       </c>
       <c r="O128" t="n">
-        <v>214326.8</v>
+        <v>150028.76</v>
       </c>
       <c r="P128" t="n">
         <v>39000</v>
       </c>
       <c r="Q128" t="n">
-        <v>780000</v>
+        <v>546000</v>
       </c>
     </row>
     <row r="129">
@@ -5966,10 +5966,10 @@
         <v>288</v>
       </c>
       <c r="N129" t="n">
-        <v>3594.2541140405</v>
+        <v>3594.2540923077</v>
       </c>
       <c r="O129" t="n">
-        <v>1035145.184843664</v>
+        <v>1035145.178584618</v>
       </c>
       <c r="P129" t="n">
         <v>6500</v>
@@ -6007,10 +6007,10 @@
         <v>108</v>
       </c>
       <c r="N130" t="n">
-        <v>3240.8500305344</v>
+        <v>3240.850030581</v>
       </c>
       <c r="O130" t="n">
-        <v>350011.8032977152</v>
+        <v>350011.803302748</v>
       </c>
       <c r="P130" t="n">
         <v>5200</v>
@@ -6191,10 +6191,10 @@
         <v>305</v>
       </c>
       <c r="N134" t="n">
-        <v>14822.378858502</v>
+        <v>14822.378857823</v>
       </c>
       <c r="O134" t="n">
-        <v>4520825.55184311</v>
+        <v>4520825.551636015</v>
       </c>
       <c r="P134" t="n">
         <v>24900</v>
@@ -7044,10 +7044,10 @@
         <v>1945</v>
       </c>
       <c r="N153" t="n">
-        <v>4372.2107879391</v>
+        <v>4372.210788556</v>
       </c>
       <c r="O153" t="n">
-        <v>8503949.982541548</v>
+        <v>8503949.983741419</v>
       </c>
       <c r="P153" t="n">
         <v>7500</v>
@@ -7082,22 +7082,22 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M154" t="n">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="N154" t="n">
         <v>6441.03</v>
       </c>
       <c r="O154" t="n">
-        <v>5558608.89</v>
+        <v>5429788.29</v>
       </c>
       <c r="P154" t="n">
         <v>10500</v>
       </c>
       <c r="Q154" t="n">
-        <v>9061500</v>
+        <v>8851500</v>
       </c>
     </row>
     <row r="155">
@@ -7134,10 +7134,10 @@
         <v>480</v>
       </c>
       <c r="N155" t="n">
-        <v>1592.5672645976</v>
+        <v>1592.5670868347</v>
       </c>
       <c r="O155" t="n">
-        <v>764432.2870068479</v>
+        <v>764432.2016806559</v>
       </c>
       <c r="P155" t="n">
         <v>3900</v>
@@ -8925,10 +8925,10 @@
         <v>776</v>
       </c>
       <c r="N194" t="n">
-        <v>1630.9233376736</v>
+        <v>1630.9233676374</v>
       </c>
       <c r="O194" t="n">
-        <v>1265596.510034713</v>
+        <v>1265596.533286622</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8971,10 +8971,10 @@
         <v>5</v>
       </c>
       <c r="N195" t="n">
-        <v>1467.3258333333</v>
+        <v>1467.3254237288</v>
       </c>
       <c r="O195" t="n">
-        <v>7336.629166666499</v>
+        <v>7336.627118644</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9017,10 +9017,10 @@
         <v>288</v>
       </c>
       <c r="N196" t="n">
-        <v>1690.6000587084</v>
+        <v>1690.5998749177</v>
       </c>
       <c r="O196" t="n">
-        <v>486892.8169080192</v>
+        <v>486892.7639762976</v>
       </c>
       <c r="P196" t="n">
         <v>2900</v>
@@ -9063,10 +9063,10 @@
         <v>2022</v>
       </c>
       <c r="N197" t="n">
-        <v>1550.1933547279</v>
+        <v>1550.1933908991</v>
       </c>
       <c r="O197" t="n">
-        <v>3134490.963259814</v>
+        <v>3134491.03639798</v>
       </c>
       <c r="P197" t="n">
         <v>2500</v>
@@ -9155,10 +9155,10 @@
         <v>418</v>
       </c>
       <c r="N199" t="n">
-        <v>2403.5109560769</v>
+        <v>2403.5111708633</v>
       </c>
       <c r="O199" t="n">
-        <v>1004667.579640144</v>
+        <v>1004667.669420859</v>
       </c>
       <c r="P199" t="n">
         <v>3500</v>
@@ -10367,10 +10367,10 @@
         <v>19</v>
       </c>
       <c r="N226" t="n">
-        <v>7537.4721804511</v>
+        <v>7537.4721969697</v>
       </c>
       <c r="O226" t="n">
-        <v>143211.9714285709</v>
+        <v>143211.9717424243</v>
       </c>
       <c r="P226" t="n">
         <v>8900</v>
@@ -10613,10 +10613,10 @@
         <v>148</v>
       </c>
       <c r="N232" t="n">
-        <v>8794.48</v>
+        <v>8799.395863611</v>
       </c>
       <c r="O232" t="n">
-        <v>1301583.04</v>
+        <v>1302310.587814428</v>
       </c>
       <c r="P232" t="n">
         <v>14500</v>
@@ -10877,10 +10877,10 @@
         <v>10</v>
       </c>
       <c r="N238" t="n">
-        <v>11431.604819277</v>
+        <v>11431.604756098</v>
       </c>
       <c r="O238" t="n">
-        <v>114316.04819277</v>
+        <v>114316.04756098</v>
       </c>
       <c r="P238" t="n">
         <v>48900</v>
@@ -11238,10 +11238,10 @@
         <v>125</v>
       </c>
       <c r="N246" t="n">
-        <v>4285.1953699789</v>
+        <v>4285.1953813559</v>
       </c>
       <c r="O246" t="n">
-        <v>535649.4212473625</v>
+        <v>535649.4226694875</v>
       </c>
       <c r="P246" t="n">
         <v>6900</v>
@@ -11988,10 +11988,10 @@
         <v>72</v>
       </c>
       <c r="N263" t="n">
-        <v>8332.7796240601</v>
+        <v>8332.779624999999</v>
       </c>
       <c r="O263" t="n">
-        <v>599960.1329323272</v>
+        <v>599960.1329999999</v>
       </c>
       <c r="P263" t="n">
         <v>14900</v>
@@ -12080,10 +12080,10 @@
         <v>599</v>
       </c>
       <c r="N265" t="n">
-        <v>1560.9996939288</v>
+        <v>1560.9997428139</v>
       </c>
       <c r="O265" t="n">
-        <v>935038.8166633513</v>
+        <v>935038.845945526</v>
       </c>
       <c r="P265" t="n">
         <v>2900</v>
@@ -12218,10 +12218,10 @@
         <v>188</v>
       </c>
       <c r="N268" t="n">
-        <v>7969.9501652893</v>
+        <v>7969.9501660377</v>
       </c>
       <c r="O268" t="n">
-        <v>1498350.631074388</v>
+        <v>1498350.631215088</v>
       </c>
       <c r="P268" t="n">
         <v>12900</v>
@@ -12823,22 +12823,22 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M281" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N281" t="n">
         <v>6000</v>
       </c>
       <c r="O281" t="n">
-        <v>402000</v>
+        <v>366000</v>
       </c>
       <c r="P281" t="n">
         <v>7500</v>
       </c>
       <c r="Q281" t="n">
-        <v>502500</v>
+        <v>457500</v>
       </c>
     </row>
     <row r="282">
@@ -13289,10 +13289,10 @@
         <v>81</v>
       </c>
       <c r="N291" t="n">
-        <v>5218.1705269461</v>
+        <v>5218.1705339806</v>
       </c>
       <c r="O291" t="n">
-        <v>422671.8126826341</v>
+        <v>422671.8132524286</v>
       </c>
       <c r="P291" t="n">
         <v>8500</v>
@@ -13335,10 +13335,10 @@
         <v>1</v>
       </c>
       <c r="N292" t="n">
-        <v>1595.0094189602</v>
+        <v>1595.0094144838</v>
       </c>
       <c r="O292" t="n">
-        <v>1595.0094189602</v>
+        <v>1595.0094144838</v>
       </c>
       <c r="P292" t="n">
         <v>2600</v>
@@ -13381,10 +13381,10 @@
         <v>123</v>
       </c>
       <c r="N293" t="n">
-        <v>3610.6500253807</v>
+        <v>3610.6500255754</v>
       </c>
       <c r="O293" t="n">
-        <v>444109.9531218261</v>
+        <v>444109.9531457742</v>
       </c>
       <c r="P293" t="n">
         <v>5800</v>
@@ -14031,10 +14031,10 @@
         <v>13</v>
       </c>
       <c r="N307" t="n">
-        <v>23521.624354839</v>
+        <v>23521.624262295</v>
       </c>
       <c r="O307" t="n">
-        <v>305781.116612907</v>
+        <v>305781.115409835</v>
       </c>
       <c r="P307" t="n">
         <v>39000</v>
@@ -14077,10 +14077,10 @@
         <v>824</v>
       </c>
       <c r="N308" t="n">
-        <v>1778.4725809313</v>
+        <v>1778.4725908889</v>
       </c>
       <c r="O308" t="n">
-        <v>1465461.406687391</v>
+        <v>1465461.414892453</v>
       </c>
       <c r="P308" t="n">
         <v>4900</v>
@@ -16110,10 +16110,10 @@
         <v>5</v>
       </c>
       <c r="N352" t="n">
-        <v>2252.2965559656</v>
+        <v>2252.2966541823</v>
       </c>
       <c r="O352" t="n">
-        <v>11261.482779828</v>
+        <v>11261.4832709115</v>
       </c>
       <c r="P352" t="n">
         <v>3900</v>
@@ -16436,10 +16436,10 @@
         <v>324</v>
       </c>
       <c r="N359" t="n">
-        <v>2328.118739546</v>
+        <v>2328.1187258454</v>
       </c>
       <c r="O359" t="n">
-        <v>754310.471612904</v>
+        <v>754310.4671739097</v>
       </c>
       <c r="P359" t="n">
         <v>4500</v>
@@ -16844,22 +16844,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M368" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="N368" t="n">
         <v>3196</v>
       </c>
       <c r="O368" t="n">
-        <v>306816</v>
+        <v>51136</v>
       </c>
       <c r="P368" t="n">
         <v>6400</v>
       </c>
       <c r="Q368" t="n">
-        <v>614400</v>
+        <v>102400</v>
       </c>
     </row>
     <row r="369">
@@ -17034,10 +17034,10 @@
         <v>153</v>
       </c>
       <c r="N372" t="n">
-        <v>3396.38</v>
+        <v>3418.6270305677</v>
       </c>
       <c r="O372" t="n">
-        <v>519646.14</v>
+        <v>523049.9356768581</v>
       </c>
       <c r="P372" t="n">
         <v>6500</v>
@@ -17080,10 +17080,10 @@
         <v>149</v>
       </c>
       <c r="N373" t="n">
-        <v>4907.8219812793</v>
+        <v>4907.8220190779</v>
       </c>
       <c r="O373" t="n">
-        <v>731265.4752106158</v>
+        <v>731265.4808426071</v>
       </c>
       <c r="P373" t="n">
         <v>8200</v>
@@ -17310,10 +17310,10 @@
         <v>289</v>
       </c>
       <c r="N378" t="n">
-        <v>3903.736812933</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O378" t="n">
-        <v>1128179.938937637</v>
+        <v>1128179.748461552</v>
       </c>
       <c r="P378" t="n">
         <v>7500</v>
@@ -17581,10 +17581,10 @@
         <v>48</v>
       </c>
       <c r="N384" t="n">
-        <v>5869.1727391742</v>
+        <v>5869.1727171717</v>
       </c>
       <c r="O384" t="n">
-        <v>281720.2914803616</v>
+        <v>281720.2904242416</v>
       </c>
       <c r="P384" t="n">
         <v>9500</v>
@@ -17719,10 +17719,10 @@
         <v>27</v>
       </c>
       <c r="N387" t="n">
-        <v>5772</v>
+        <v>5775.9026369168</v>
       </c>
       <c r="O387" t="n">
-        <v>155844</v>
+        <v>155949.3711967536</v>
       </c>
       <c r="P387" t="n">
         <v>9900</v>
@@ -17857,10 +17857,10 @@
         <v>157</v>
       </c>
       <c r="N390" t="n">
-        <v>3898</v>
+        <v>3904.1097178683</v>
       </c>
       <c r="O390" t="n">
-        <v>611986</v>
+        <v>612945.225705323</v>
       </c>
       <c r="P390" t="n">
         <v>6900</v>
@@ -19603,10 +19603,10 @@
         <v>1320</v>
       </c>
       <c r="N428" t="n">
-        <v>1516.0388052024</v>
+        <v>1516.0388047383</v>
       </c>
       <c r="O428" t="n">
-        <v>2001171.222867168</v>
+        <v>2001171.222254556</v>
       </c>
       <c r="P428" t="n">
         <v>2300</v>
@@ -19695,10 +19695,10 @@
         <v>8</v>
       </c>
       <c r="N430" t="n">
-        <v>4248.6496363636</v>
+        <v>4248.6505555556</v>
       </c>
       <c r="O430" t="n">
-        <v>33989.1970909088</v>
+        <v>33989.2044444448</v>
       </c>
       <c r="P430" t="n">
         <v>5900</v>
@@ -19741,10 +19741,10 @@
         <v>120</v>
       </c>
       <c r="N431" t="n">
-        <v>2458.5133724619</v>
+        <v>2458.5132807977</v>
       </c>
       <c r="O431" t="n">
-        <v>295021.604695428</v>
+        <v>295021.593695724</v>
       </c>
       <c r="P431" t="n">
         <v>3500</v>
@@ -19787,10 +19787,10 @@
         <v>192</v>
       </c>
       <c r="N432" t="n">
-        <v>1771.0908132147</v>
+        <v>1775.6031464968</v>
       </c>
       <c r="O432" t="n">
-        <v>340049.4361372224</v>
+        <v>340915.8041273856</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
@@ -19833,10 +19833,10 @@
         <v>264</v>
       </c>
       <c r="N433" t="n">
-        <v>2079.384121911</v>
+        <v>2079.3840612517</v>
       </c>
       <c r="O433" t="n">
-        <v>548957.408184504</v>
+        <v>548957.3921704488</v>
       </c>
       <c r="P433" t="n">
         <v>2900</v>
@@ -19873,22 +19873,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M434" t="n">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="N434" t="n">
-        <v>1803.0152282542</v>
+        <v>1803.015492547</v>
       </c>
       <c r="O434" t="n">
-        <v>346178.9238248064</v>
+        <v>129817.115463384</v>
       </c>
       <c r="P434" t="n">
         <v>2500</v>
       </c>
       <c r="Q434" t="n">
-        <v>480000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="435">
@@ -19971,10 +19971,10 @@
         <v>192</v>
       </c>
       <c r="N436" t="n">
-        <v>2122.1639833897</v>
+        <v>2122.163972265</v>
       </c>
       <c r="O436" t="n">
-        <v>407455.4848108224</v>
+        <v>407455.4826748801</v>
       </c>
       <c r="P436" t="n">
         <v>2900</v>
@@ -20011,22 +20011,22 @@
         <v>0</v>
       </c>
       <c r="L437" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M437" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="N437" t="n">
-        <v>2108.7902645503</v>
+        <v>2108.7909398496</v>
       </c>
       <c r="O437" t="n">
-        <v>455498.6971428648</v>
+        <v>253054.912781952</v>
       </c>
       <c r="P437" t="n">
         <v>2900</v>
       </c>
       <c r="Q437" t="n">
-        <v>626400</v>
+        <v>348000</v>
       </c>
     </row>
     <row r="438">
@@ -20063,10 +20063,10 @@
         <v>144</v>
       </c>
       <c r="N438" t="n">
-        <v>2056.0836725935</v>
+        <v>2056.0835600624</v>
       </c>
       <c r="O438" t="n">
-        <v>296076.048853464</v>
+        <v>296076.0326489856</v>
       </c>
       <c r="P438" t="n">
         <v>2900</v>
@@ -20109,10 +20109,10 @@
         <v>216</v>
       </c>
       <c r="N439" t="n">
-        <v>3224.5683024119</v>
+        <v>3224.5684753788</v>
       </c>
       <c r="O439" t="n">
-        <v>696506.7533209703</v>
+        <v>696506.7906818208</v>
       </c>
       <c r="P439" t="n">
         <v>4500</v>
@@ -20385,10 +20385,10 @@
         <v>384</v>
       </c>
       <c r="N445" t="n">
-        <v>1592.2763108883</v>
+        <v>1592.2766843703</v>
       </c>
       <c r="O445" t="n">
-        <v>611434.1033811072</v>
+        <v>611434.2467981952</v>
       </c>
       <c r="P445" t="n">
         <v>2500</v>
@@ -20562,10 +20562,10 @@
         <v>24</v>
       </c>
       <c r="N449" t="n">
-        <v>1668.6240987654</v>
+        <v>1668.6249616368</v>
       </c>
       <c r="O449" t="n">
-        <v>40046.9783703696</v>
+        <v>40046.9990792832</v>
       </c>
       <c r="P449" t="n">
         <v>2500</v>
@@ -20654,10 +20654,10 @@
         <v>800</v>
       </c>
       <c r="N451" t="n">
-        <v>1259.2745016722</v>
+        <v>1259.2745137492</v>
       </c>
       <c r="O451" t="n">
-        <v>1007419.60133776</v>
+        <v>1007419.61099936</v>
       </c>
       <c r="P451" t="n">
         <v>1900</v>
@@ -20787,10 +20787,10 @@
         <v>72</v>
       </c>
       <c r="N454" t="n">
-        <v>2556.7455948553</v>
+        <v>2556.745819398</v>
       </c>
       <c r="O454" t="n">
-        <v>184085.6828295816</v>
+        <v>184085.698996656</v>
       </c>
       <c r="P454" t="n">
         <v>3900</v>
@@ -21891,22 +21891,22 @@
         <v>0</v>
       </c>
       <c r="L478" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M478" t="n">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="N478" t="n">
         <v>7103.81</v>
       </c>
       <c r="O478" t="n">
-        <v>3793434.54</v>
+        <v>3594527.86</v>
       </c>
       <c r="P478" t="n">
         <v>8900</v>
       </c>
       <c r="Q478" t="n">
-        <v>4752600</v>
+        <v>4503400</v>
       </c>
     </row>
     <row r="479">
@@ -21943,10 +21943,10 @@
         <v>20</v>
       </c>
       <c r="N479" t="n">
-        <v>2357.74</v>
+        <v>2474.8947826087</v>
       </c>
       <c r="O479" t="n">
-        <v>47154.8</v>
+        <v>49497.895652174</v>
       </c>
       <c r="P479" t="n">
         <v>3000</v>
@@ -22033,10 +22033,10 @@
         <v>306</v>
       </c>
       <c r="N481" t="n">
-        <v>1690.870009009</v>
+        <v>1690.8700090131</v>
       </c>
       <c r="O481" t="n">
-        <v>517406.222756754</v>
+        <v>517406.2227580086</v>
       </c>
       <c r="P481" t="n">
         <v>3000</v>
@@ -22876,10 +22876,10 @@
         <v>461</v>
       </c>
       <c r="N499" t="n">
-        <v>517.2884408203601</v>
+        <v>517.28876931766</v>
       </c>
       <c r="O499" t="n">
-        <v>238469.971218186</v>
+        <v>238470.1226554413</v>
       </c>
       <c r="P499" t="n">
         <v>900</v>
@@ -23250,10 +23250,10 @@
         <v>33</v>
       </c>
       <c r="N507" t="n">
-        <v>3259.1342528736</v>
+        <v>3259.1342692308</v>
       </c>
       <c r="O507" t="n">
-        <v>107551.4303448288</v>
+        <v>107551.4308846164</v>
       </c>
       <c r="P507" t="n">
         <v>3600</v>
@@ -23299,10 +23299,10 @@
         <v>757</v>
       </c>
       <c r="N508" t="n">
-        <v>3110.8425641565</v>
+        <v>3110.8424546425</v>
       </c>
       <c r="O508" t="n">
-        <v>2354907.82106647</v>
+        <v>2354907.738164372</v>
       </c>
       <c r="P508" t="n">
         <v>4500</v>
@@ -23750,10 +23750,10 @@
         <v>19802</v>
       </c>
       <c r="N518" t="n">
-        <v>703.79526826968</v>
+        <v>703.7952483310401</v>
       </c>
       <c r="O518" t="n">
-        <v>13936553.9022762</v>
+        <v>13936553.50745125</v>
       </c>
       <c r="P518" t="n">
         <v>900</v>
@@ -23799,10 +23799,10 @@
         <v>55</v>
       </c>
       <c r="N519" t="n">
-        <v>3182.2511009174</v>
+        <v>3182.2511070111</v>
       </c>
       <c r="O519" t="n">
-        <v>175023.810550457</v>
+        <v>175023.8108856105</v>
       </c>
       <c r="P519" t="n">
         <v>6900</v>
@@ -23891,10 +23891,10 @@
         <v>90</v>
       </c>
       <c r="N521" t="n">
-        <v>2501.3850684932</v>
+        <v>2501.3850230415</v>
       </c>
       <c r="O521" t="n">
-        <v>225124.656164388</v>
+        <v>225124.652073735</v>
       </c>
       <c r="P521" t="n">
         <v>4100</v>
@@ -24257,10 +24257,10 @@
         <v>47</v>
       </c>
       <c r="N529" t="n">
-        <v>1595.5151400147</v>
+        <v>1595.5132932891</v>
       </c>
       <c r="O529" t="n">
-        <v>74989.2115806909</v>
+        <v>74989.12478458769</v>
       </c>
       <c r="P529" t="n">
         <v>2500</v>
@@ -24744,10 +24744,10 @@
         <v>33</v>
       </c>
       <c r="N539" t="n">
-        <v>2832.1948571429</v>
+        <v>2832.1949275362</v>
       </c>
       <c r="O539" t="n">
-        <v>93462.4302857157</v>
+        <v>93462.43260869459</v>
       </c>
       <c r="P539" t="n">
         <v>12900</v>
@@ -25514,10 +25514,10 @@
         <v>19</v>
       </c>
       <c r="N555" t="n">
-        <v>9746.880188679201</v>
+        <v>9746.8801904762</v>
       </c>
       <c r="O555" t="n">
-        <v>185190.7235849048</v>
+        <v>185190.7236190478</v>
       </c>
       <c r="P555" t="n">
         <v>18500</v>
@@ -25557,22 +25557,22 @@
         <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M556" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N556" t="n">
         <v>10296.29</v>
       </c>
       <c r="O556" t="n">
-        <v>175036.93</v>
+        <v>123555.48</v>
       </c>
       <c r="P556" t="n">
         <v>16900</v>
       </c>
       <c r="Q556" t="n">
-        <v>287300</v>
+        <v>202800</v>
       </c>
     </row>
     <row r="557">
@@ -25759,10 +25759,10 @@
         <v>35</v>
       </c>
       <c r="N560" t="n">
-        <v>2992.5688235294</v>
+        <v>2992.5689285714</v>
       </c>
       <c r="O560" t="n">
-        <v>104739.908823529</v>
+        <v>104739.912499999</v>
       </c>
       <c r="P560" t="n">
         <v>6000</v>
@@ -26175,22 +26175,22 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M569" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="N569" t="n">
-        <v>3067.0905454545</v>
+        <v>3067.0905844156</v>
       </c>
       <c r="O569" t="n">
-        <v>325111.597818177</v>
+        <v>306709.05844156</v>
       </c>
       <c r="P569" t="n">
         <v>7200</v>
       </c>
       <c r="Q569" t="n">
-        <v>763200</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="570">
@@ -28271,10 +28271,10 @@
         <v>1105</v>
       </c>
       <c r="N613" t="n">
-        <v>7046.9398286204</v>
+        <v>7046.9398281418</v>
       </c>
       <c r="O613" t="n">
-        <v>7786868.510625541</v>
+        <v>7786868.510096689</v>
       </c>
       <c r="P613" t="n">
         <v>9900</v>
@@ -28899,10 +28899,10 @@
         <v>153</v>
       </c>
       <c r="N626" t="n">
-        <v>315.02685915493</v>
+        <v>315.02694721826</v>
       </c>
       <c r="O626" t="n">
-        <v>48199.10945070429</v>
+        <v>48199.12292439378</v>
       </c>
       <c r="P626" t="n">
         <v>2200</v>
@@ -29449,22 +29449,22 @@
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M639" t="n">
-        <v>831</v>
+        <v>791</v>
       </c>
       <c r="N639" t="n">
         <v>3181.9</v>
       </c>
       <c r="O639" t="n">
-        <v>2644158.9</v>
+        <v>2516882.9</v>
       </c>
       <c r="P639" t="n">
         <v>5100</v>
       </c>
       <c r="Q639" t="n">
-        <v>4238100</v>
+        <v>4034100</v>
       </c>
     </row>
     <row r="640">
@@ -29540,10 +29540,10 @@
         <v>450</v>
       </c>
       <c r="N641" t="n">
-        <v>1794.2879750466</v>
+        <v>1794.2879721384</v>
       </c>
       <c r="O641" t="n">
-        <v>807429.58877097</v>
+        <v>807429.5874622799</v>
       </c>
       <c r="P641" t="n">
         <v>1600</v>
@@ -29945,10 +29945,10 @@
         <v>352</v>
       </c>
       <c r="N650" t="n">
-        <v>22951.704956085</v>
+        <v>22951.704917826</v>
       </c>
       <c r="O650" t="n">
-        <v>8079000.144541919</v>
+        <v>8079000.131074752</v>
       </c>
       <c r="P650" t="n">
         <v>37900</v>
@@ -30032,10 +30032,10 @@
         <v>93</v>
       </c>
       <c r="N652" t="n">
-        <v>4985.4050632911</v>
+        <v>4985.4051948052</v>
       </c>
       <c r="O652" t="n">
-        <v>463642.6708860723</v>
+        <v>463642.6831168836</v>
       </c>
       <c r="P652" t="n">
         <v>7900</v>
@@ -30134,10 +30134,10 @@
         <v>306</v>
       </c>
       <c r="N654" t="n">
-        <v>1757.3205462185</v>
+        <v>1775.9757537155</v>
       </c>
       <c r="O654" t="n">
-        <v>537740.087142861</v>
+        <v>543448.580636943</v>
       </c>
       <c r="P654" t="n">
         <v>2000</v>
@@ -30266,22 +30266,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M657" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="N657" t="n">
         <v>220.00651536869</v>
       </c>
       <c r="O657" t="n">
-        <v>880026.0614747601</v>
+        <v>814024.1068641531</v>
       </c>
       <c r="P657" t="n">
         <v>260</v>
       </c>
       <c r="Q657" t="n">
-        <v>1040000</v>
+        <v>962000</v>
       </c>
     </row>
     <row r="658">
@@ -30747,12 +30747,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>J-1314</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>PERRO CON GAFAS CAMINA J-1314</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -30766,39 +30766,39 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K668" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L668" t="n">
         <v>0</v>
       </c>
       <c r="M668" t="n">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="N668" t="n">
-        <v>415.07</v>
+        <v>6336</v>
       </c>
       <c r="O668" t="n">
-        <v>12867.17</v>
+        <v>912384</v>
       </c>
       <c r="P668" t="n">
-        <v>2900</v>
+        <v>7900</v>
       </c>
       <c r="Q668" t="n">
-        <v>89900</v>
+        <v>1137600</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -30812,44 +30812,44 @@
         </is>
       </c>
       <c r="J669" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K669" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="L669" t="n">
         <v>0</v>
       </c>
       <c r="M669" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="N669" t="n">
-        <v>46491.75</v>
+        <v>5280</v>
       </c>
       <c r="O669" t="n">
-        <v>2743013.25</v>
+        <v>781440</v>
       </c>
       <c r="P669" t="n">
-        <v>52900</v>
+        <v>6900</v>
       </c>
       <c r="Q669" t="n">
-        <v>3121100</v>
+        <v>1021200</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -30858,44 +30858,44 @@
         </is>
       </c>
       <c r="J670" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K670" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L670" t="n">
         <v>0</v>
       </c>
       <c r="M670" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="N670" t="n">
-        <v>910.85</v>
+        <v>5280</v>
       </c>
       <c r="O670" t="n">
-        <v>41899.1</v>
+        <v>792000</v>
       </c>
       <c r="P670" t="n">
-        <v>7900</v>
+        <v>6900</v>
       </c>
       <c r="Q670" t="n">
-        <v>363400</v>
+        <v>1035000</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>J-1320</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>CARRO TODO TERRENO J-1320</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -30904,44 +30904,44 @@
         </is>
       </c>
       <c r="J671" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K671" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L671" t="n">
         <v>0</v>
       </c>
       <c r="M671" t="n">
-        <v>12</v>
+        <v>288</v>
       </c>
       <c r="N671" t="n">
-        <v>1129.14</v>
+        <v>1584</v>
       </c>
       <c r="O671" t="n">
-        <v>13549.68</v>
+        <v>456192</v>
       </c>
       <c r="P671" t="n">
-        <v>6900</v>
+        <v>2000</v>
       </c>
       <c r="Q671" t="n">
-        <v>82800</v>
+        <v>576000</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>J-1323</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -30950,49 +30950,44 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K672" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="L672" t="n">
         <v>0</v>
       </c>
       <c r="M672" t="n">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="N672" t="n">
-        <v>11433.53</v>
+        <v>3872</v>
       </c>
       <c r="O672" t="n">
-        <v>125768.83</v>
+        <v>650496</v>
       </c>
       <c r="P672" t="n">
-        <v>15000</v>
+        <v>4900</v>
       </c>
       <c r="Q672" t="n">
-        <v>165000</v>
+        <v>823200</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>J-1328</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>CUATRIMOTO LUZ IMPULSO J-1328</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -31001,44 +30996,44 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K673" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L673" t="n">
         <v>0</v>
       </c>
       <c r="M673" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="N673" t="n">
-        <v>15452.21</v>
+        <v>6160</v>
       </c>
       <c r="O673" t="n">
-        <v>61808.84</v>
+        <v>517440</v>
       </c>
       <c r="P673" t="n">
-        <v>36500</v>
+        <v>7900</v>
       </c>
       <c r="Q673" t="n">
-        <v>146000</v>
+        <v>663600</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>J-1331</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -31047,49 +31042,44 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K674" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="L674" t="n">
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="N674" t="n">
-        <v>1319.3608823529</v>
+        <v>4400</v>
       </c>
       <c r="O674" t="n">
-        <v>263872.17647058</v>
+        <v>739200</v>
       </c>
       <c r="P674" t="n">
-        <v>3500</v>
+        <v>5900</v>
       </c>
       <c r="Q674" t="n">
-        <v>700000</v>
+        <v>991200</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>J-455</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>TABLETA MAGICA J-455</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -31098,44 +31088,44 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K675" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L675" t="n">
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="N675" t="n">
-        <v>751.45</v>
+        <v>3520</v>
       </c>
       <c r="O675" t="n">
-        <v>59364.55</v>
+        <v>704000</v>
       </c>
       <c r="P675" t="n">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="Q675" t="n">
-        <v>197500</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>J-687</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>BOLITRON OJO 3 COLORES J-687</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -31144,49 +31134,44 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="K676" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>143</v>
+        <v>576</v>
       </c>
       <c r="N676" t="n">
-        <v>571.87</v>
+        <v>2288</v>
       </c>
       <c r="O676" t="n">
-        <v>81777.41</v>
+        <v>1317888</v>
       </c>
       <c r="P676" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q676" t="n">
-        <v>357500</v>
+        <v>1670400</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -31195,44 +31180,44 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K677" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L677" t="n">
         <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="N677" t="n">
-        <v>2432.1346938776</v>
+        <v>4576</v>
       </c>
       <c r="O677" t="n">
-        <v>43778.4244897968</v>
+        <v>878592</v>
       </c>
       <c r="P677" t="n">
-        <v>4500</v>
+        <v>5900</v>
       </c>
       <c r="Q677" t="n">
-        <v>81000</v>
+        <v>1132800</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -31241,49 +31226,44 @@
         </is>
       </c>
       <c r="J678" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="K678" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="L678" t="n">
         <v>0</v>
       </c>
       <c r="M678" t="n">
-        <v>686</v>
+        <v>299</v>
       </c>
       <c r="N678" t="n">
-        <v>227.41597222222</v>
+        <v>5280</v>
       </c>
       <c r="O678" t="n">
-        <v>156007.3569444429</v>
+        <v>1578720</v>
       </c>
       <c r="P678" t="n">
-        <v>1200</v>
+        <v>6900</v>
       </c>
       <c r="Q678" t="n">
-        <v>823200</v>
+        <v>2063100</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -31292,7 +31272,7 @@
         </is>
       </c>
       <c r="J679" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K679" t="n">
         <v>0</v>
@@ -31301,39 +31281,44 @@
         <v>0</v>
       </c>
       <c r="M679" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="N679" t="n">
-        <v>9917.040000000001</v>
+        <v>415.07</v>
       </c>
       <c r="O679" t="n">
-        <v>218174.88</v>
+        <v>12867.17</v>
       </c>
       <c r="P679" t="n">
-        <v>15900</v>
+        <v>2900</v>
       </c>
       <c r="Q679" t="n">
-        <v>349800</v>
+        <v>89900</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>MT4004</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>COCINA CAJA MED MG20233</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J680" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="K680" t="n">
         <v>0</v>
@@ -31342,35 +31327,35 @@
         <v>0</v>
       </c>
       <c r="M680" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="N680" t="n">
-        <v>2058.92</v>
+        <v>46491.75</v>
       </c>
       <c r="O680" t="n">
-        <v>325309.36</v>
+        <v>2743013.25</v>
       </c>
       <c r="P680" t="n">
-        <v>2500</v>
+        <v>52900</v>
       </c>
       <c r="Q680" t="n">
-        <v>395000</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -31379,7 +31364,7 @@
         </is>
       </c>
       <c r="J681" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="K681" t="n">
         <v>0</v>
@@ -31388,35 +31373,35 @@
         <v>0</v>
       </c>
       <c r="M681" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="N681" t="n">
-        <v>3306.0098310139</v>
+        <v>910.85</v>
       </c>
       <c r="O681" t="n">
-        <v>314070.9339463205</v>
+        <v>41899.1</v>
       </c>
       <c r="P681" t="n">
-        <v>4200</v>
+        <v>7900</v>
       </c>
       <c r="Q681" t="n">
-        <v>399000</v>
+        <v>363400</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -31425,7 +31410,7 @@
         </is>
       </c>
       <c r="J682" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K682" t="n">
         <v>0</v>
@@ -31434,30 +31419,30 @@
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N682" t="n">
-        <v>7600</v>
+        <v>1129.14</v>
       </c>
       <c r="O682" t="n">
-        <v>364800</v>
+        <v>13549.68</v>
       </c>
       <c r="P682" t="n">
-        <v>9500</v>
+        <v>6900</v>
       </c>
       <c r="Q682" t="n">
-        <v>456000</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -31471,7 +31456,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -31480,35 +31465,40 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="N683" t="n">
-        <v>5520</v>
+        <v>11433.53</v>
       </c>
       <c r="O683" t="n">
-        <v>524400</v>
+        <v>125768.83</v>
       </c>
       <c r="P683" t="n">
-        <v>6900</v>
+        <v>15000</v>
       </c>
       <c r="Q683" t="n">
-        <v>655500</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>SEB09</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -31517,7 +31507,7 @@
         </is>
       </c>
       <c r="J684" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="K684" t="n">
         <v>0</v>
@@ -31526,35 +31516,35 @@
         <v>0</v>
       </c>
       <c r="M684" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="N684" t="n">
-        <v>1600</v>
+        <v>15452.21</v>
       </c>
       <c r="O684" t="n">
-        <v>132800</v>
+        <v>61808.84</v>
       </c>
       <c r="P684" t="n">
-        <v>2000</v>
+        <v>36500</v>
       </c>
       <c r="Q684" t="n">
-        <v>166000</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -31563,7 +31553,7 @@
         </is>
       </c>
       <c r="J685" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="K685" t="n">
         <v>0</v>
@@ -31572,35 +31562,40 @@
         <v>0</v>
       </c>
       <c r="M685" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="N685" t="n">
-        <v>4091.4</v>
+        <v>1319.3608823529</v>
       </c>
       <c r="O685" t="n">
-        <v>4091.4</v>
+        <v>263872.17647058</v>
       </c>
       <c r="P685" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="Q685" t="n">
-        <v>10000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>SLT027</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>JUGUETE  DRAGON   AB-02 / 082</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -31609,7 +31604,7 @@
         </is>
       </c>
       <c r="J686" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="K686" t="n">
         <v>0</v>
@@ -31618,35 +31613,35 @@
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="N686" t="n">
-        <v>3732.8777027027</v>
+        <v>751.45</v>
       </c>
       <c r="O686" t="n">
-        <v>37328.777027027</v>
+        <v>59364.55</v>
       </c>
       <c r="P686" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="Q686" t="n">
-        <v>45000</v>
+        <v>197500</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -31655,7 +31650,7 @@
         </is>
       </c>
       <c r="J687" t="n">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="K687" t="n">
         <v>0</v>
@@ -31664,35 +31659,40 @@
         <v>0</v>
       </c>
       <c r="M687" t="n">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="N687" t="n">
-        <v>3661.88</v>
+        <v>571.87</v>
       </c>
       <c r="O687" t="n">
-        <v>10985.64</v>
+        <v>81777.41</v>
       </c>
       <c r="P687" t="n">
-        <v>38900</v>
+        <v>2500</v>
       </c>
       <c r="Q687" t="n">
-        <v>116700</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -31701,7 +31701,7 @@
         </is>
       </c>
       <c r="J688" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K688" t="n">
         <v>0</v>
@@ -31710,35 +31710,35 @@
         <v>0</v>
       </c>
       <c r="M688" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N688" t="n">
-        <v>2797.08</v>
+        <v>2432.1346938776</v>
       </c>
       <c r="O688" t="n">
-        <v>13985.4</v>
+        <v>43778.4244897968</v>
       </c>
       <c r="P688" t="n">
-        <v>30900</v>
+        <v>4500</v>
       </c>
       <c r="Q688" t="n">
-        <v>154500</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -31747,7 +31747,7 @@
         </is>
       </c>
       <c r="J689" t="n">
-        <v>11</v>
+        <v>686</v>
       </c>
       <c r="K689" t="n">
         <v>0</v>
@@ -31756,35 +31756,40 @@
         <v>0</v>
       </c>
       <c r="M689" t="n">
-        <v>11</v>
+        <v>686</v>
       </c>
       <c r="N689" t="n">
-        <v>3462.255</v>
+        <v>229.09061119293</v>
       </c>
       <c r="O689" t="n">
-        <v>38084.805</v>
+        <v>157156.15927835</v>
       </c>
       <c r="P689" t="n">
-        <v>42000</v>
+        <v>1200</v>
       </c>
       <c r="Q689" t="n">
-        <v>462000</v>
+        <v>823200</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -31793,7 +31798,7 @@
         </is>
       </c>
       <c r="J690" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K690" t="n">
         <v>0</v>
@@ -31802,44 +31807,39 @@
         <v>0</v>
       </c>
       <c r="M690" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N690" t="n">
-        <v>24882.58</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O690" t="n">
-        <v>696712.24</v>
+        <v>218174.88</v>
       </c>
       <c r="P690" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q690" t="n">
-        <v>882000</v>
+        <v>349800</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>MT4004</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
-        </is>
-      </c>
-      <c r="E691" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J691" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="K691" t="n">
         <v>0</v>
@@ -31848,35 +31848,35 @@
         <v>0</v>
       </c>
       <c r="M691" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="N691" t="n">
-        <v>0.8</v>
+        <v>2058.92</v>
       </c>
       <c r="O691" t="n">
-        <v>15.2</v>
+        <v>325309.36</v>
       </c>
       <c r="P691" t="n">
-        <v>22900</v>
+        <v>2500</v>
       </c>
       <c r="Q691" t="n">
-        <v>435100</v>
+        <v>395000</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -31885,7 +31885,7 @@
         </is>
       </c>
       <c r="J692" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="K692" t="n">
         <v>0</v>
@@ -31894,35 +31894,35 @@
         <v>0</v>
       </c>
       <c r="M692" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="N692" t="n">
-        <v>5186.45</v>
+        <v>3306.0098306773</v>
       </c>
       <c r="O692" t="n">
-        <v>82983.2</v>
+        <v>314070.9339143435</v>
       </c>
       <c r="P692" t="n">
-        <v>7200</v>
+        <v>4200</v>
       </c>
       <c r="Q692" t="n">
-        <v>115200</v>
+        <v>399000</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>SEB010</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="J693" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="K693" t="n">
         <v>0</v>
@@ -31940,35 +31940,35 @@
         <v>0</v>
       </c>
       <c r="M693" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="N693" t="n">
-        <v>47796.1625</v>
+        <v>7600</v>
       </c>
       <c r="O693" t="n">
-        <v>95592.325</v>
+        <v>364800</v>
       </c>
       <c r="P693" t="n">
-        <v>54000</v>
+        <v>9500</v>
       </c>
       <c r="Q693" t="n">
-        <v>108000</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>TB115</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -31977,7 +31977,7 @@
         </is>
       </c>
       <c r="J694" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="K694" t="n">
         <v>0</v>
@@ -31986,64 +31986,570 @@
         <v>0</v>
       </c>
       <c r="M694" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="N694" t="n">
-        <v>8006.3731111111</v>
+        <v>5520</v>
       </c>
       <c r="O694" t="n">
-        <v>344274.0437777773</v>
+        <v>524400</v>
       </c>
       <c r="P694" t="n">
-        <v>10000</v>
+        <v>6900</v>
       </c>
       <c r="Q694" t="n">
-        <v>430000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
+          <t>SEB09</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J695" t="n">
+        <v>83</v>
+      </c>
+      <c r="K695" t="n">
+        <v>0</v>
+      </c>
+      <c r="L695" t="n">
+        <v>0</v>
+      </c>
+      <c r="M695" t="n">
+        <v>83</v>
+      </c>
+      <c r="N695" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O695" t="n">
+        <v>132800</v>
+      </c>
+      <c r="P695" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q695" t="n">
+        <v>166000</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>SEBQ04</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>TORRES DE ABACO SE1428</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J696" t="n">
+        <v>1</v>
+      </c>
+      <c r="K696" t="n">
+        <v>0</v>
+      </c>
+      <c r="L696" t="n">
+        <v>0</v>
+      </c>
+      <c r="M696" t="n">
+        <v>1</v>
+      </c>
+      <c r="N696" t="n">
+        <v>4091.4</v>
+      </c>
+      <c r="O696" t="n">
+        <v>4091.4</v>
+      </c>
+      <c r="P696" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q696" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>SLT027</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>JUGUETE  DRAGON   AB-02 / 082</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J697" t="n">
+        <v>10</v>
+      </c>
+      <c r="K697" t="n">
+        <v>0</v>
+      </c>
+      <c r="L697" t="n">
+        <v>0</v>
+      </c>
+      <c r="M697" t="n">
+        <v>10</v>
+      </c>
+      <c r="N697" t="n">
+        <v>3732.8773611111</v>
+      </c>
+      <c r="O697" t="n">
+        <v>37328.773611111</v>
+      </c>
+      <c r="P697" t="n">
+        <v>4500</v>
+      </c>
+      <c r="Q697" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>T040-LJ</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J698" t="n">
+        <v>3</v>
+      </c>
+      <c r="K698" t="n">
+        <v>0</v>
+      </c>
+      <c r="L698" t="n">
+        <v>0</v>
+      </c>
+      <c r="M698" t="n">
+        <v>3</v>
+      </c>
+      <c r="N698" t="n">
+        <v>3661.88</v>
+      </c>
+      <c r="O698" t="n">
+        <v>10985.64</v>
+      </c>
+      <c r="P698" t="n">
+        <v>38900</v>
+      </c>
+      <c r="Q698" t="n">
+        <v>116700</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>T041-LJ</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J699" t="n">
+        <v>5</v>
+      </c>
+      <c r="K699" t="n">
+        <v>0</v>
+      </c>
+      <c r="L699" t="n">
+        <v>0</v>
+      </c>
+      <c r="M699" t="n">
+        <v>5</v>
+      </c>
+      <c r="N699" t="n">
+        <v>2797.08</v>
+      </c>
+      <c r="O699" t="n">
+        <v>13985.4</v>
+      </c>
+      <c r="P699" t="n">
+        <v>30900</v>
+      </c>
+      <c r="Q699" t="n">
+        <v>154500</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>T048-LJ</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J700" t="n">
+        <v>11</v>
+      </c>
+      <c r="K700" t="n">
+        <v>0</v>
+      </c>
+      <c r="L700" t="n">
+        <v>0</v>
+      </c>
+      <c r="M700" t="n">
+        <v>11</v>
+      </c>
+      <c r="N700" t="n">
+        <v>3462.255</v>
+      </c>
+      <c r="O700" t="n">
+        <v>38084.805</v>
+      </c>
+      <c r="P700" t="n">
+        <v>42000</v>
+      </c>
+      <c r="Q700" t="n">
+        <v>462000</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>T062-LJ</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J701" t="n">
+        <v>28</v>
+      </c>
+      <c r="K701" t="n">
+        <v>0</v>
+      </c>
+      <c r="L701" t="n">
+        <v>0</v>
+      </c>
+      <c r="M701" t="n">
+        <v>28</v>
+      </c>
+      <c r="N701" t="n">
+        <v>24882.58</v>
+      </c>
+      <c r="O701" t="n">
+        <v>696712.24</v>
+      </c>
+      <c r="P701" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q701" t="n">
+        <v>882000</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>T119-LJ</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J702" t="n">
+        <v>19</v>
+      </c>
+      <c r="K702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L702" t="n">
+        <v>0</v>
+      </c>
+      <c r="M702" t="n">
+        <v>19</v>
+      </c>
+      <c r="N702" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O702" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="P702" t="n">
+        <v>22900</v>
+      </c>
+      <c r="Q702" t="n">
+        <v>435100</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>T166-LJ</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J703" t="n">
+        <v>16</v>
+      </c>
+      <c r="K703" t="n">
+        <v>0</v>
+      </c>
+      <c r="L703" t="n">
+        <v>0</v>
+      </c>
+      <c r="M703" t="n">
+        <v>16</v>
+      </c>
+      <c r="N703" t="n">
+        <v>5186.45</v>
+      </c>
+      <c r="O703" t="n">
+        <v>82983.2</v>
+      </c>
+      <c r="P703" t="n">
+        <v>7200</v>
+      </c>
+      <c r="Q703" t="n">
+        <v>115200</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>TB028</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J704" t="n">
+        <v>2</v>
+      </c>
+      <c r="K704" t="n">
+        <v>0</v>
+      </c>
+      <c r="L704" t="n">
+        <v>0</v>
+      </c>
+      <c r="M704" t="n">
+        <v>2</v>
+      </c>
+      <c r="N704" t="n">
+        <v>47796.1625</v>
+      </c>
+      <c r="O704" t="n">
+        <v>95592.325</v>
+      </c>
+      <c r="P704" t="n">
+        <v>54000</v>
+      </c>
+      <c r="Q704" t="n">
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>TB115</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J705" t="n">
+        <v>43</v>
+      </c>
+      <c r="K705" t="n">
+        <v>0</v>
+      </c>
+      <c r="L705" t="n">
+        <v>0</v>
+      </c>
+      <c r="M705" t="n">
+        <v>43</v>
+      </c>
+      <c r="N705" t="n">
+        <v>8006.3731111111</v>
+      </c>
+      <c r="O705" t="n">
+        <v>344274.0437777773</v>
+      </c>
+      <c r="P705" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q705" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
           <t>TB122</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
-      <c r="E695" t="inlineStr">
+      <c r="E706" t="inlineStr">
         <is>
           <t>PELUCHES</t>
         </is>
       </c>
-      <c r="I695" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J695" t="n">
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J706" t="n">
         <v>4</v>
       </c>
-      <c r="K695" t="n">
-        <v>0</v>
-      </c>
-      <c r="L695" t="n">
-        <v>0</v>
-      </c>
-      <c r="M695" t="n">
+      <c r="K706" t="n">
+        <v>0</v>
+      </c>
+      <c r="L706" t="n">
+        <v>0</v>
+      </c>
+      <c r="M706" t="n">
         <v>4</v>
       </c>
-      <c r="N695" t="n">
+      <c r="N706" t="n">
         <v>47920</v>
       </c>
-      <c r="O695" t="n">
+      <c r="O706" t="n">
         <v>191680</v>
       </c>
-      <c r="P695" t="n">
+      <c r="P706" t="n">
         <v>59900</v>
       </c>
-      <c r="Q695" t="n">
+      <c r="Q706" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4278,10 +4278,10 @@
         <v>1968</v>
       </c>
       <c r="N92" t="n">
-        <v>3250.4653148346</v>
+        <v>3247</v>
       </c>
       <c r="O92" t="n">
-        <v>6396915.739594493</v>
+        <v>6390096</v>
       </c>
       <c r="P92" t="n">
         <v>5200</v>
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>1250</v>
+        <v>1235</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>1235</v>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>7994</v>
+        <v>5994</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
         <v>5994</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
         <v>290</v>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
         <v>47</v>
@@ -5905,13 +5905,13 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
         <v>14</v>
@@ -7076,13 +7076,13 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>843</v>
@@ -10613,10 +10613,10 @@
         <v>148</v>
       </c>
       <c r="N232" t="n">
-        <v>8799.395863611</v>
+        <v>8794.48</v>
       </c>
       <c r="O232" t="n">
-        <v>1302310.587814428</v>
+        <v>1301583.04</v>
       </c>
       <c r="P232" t="n">
         <v>14500</v>
@@ -12817,13 +12817,13 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
         <v>61</v>
@@ -16838,13 +16838,13 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M368" t="n">
         <v>16</v>
@@ -17034,10 +17034,10 @@
         <v>153</v>
       </c>
       <c r="N372" t="n">
-        <v>3418.6270305677</v>
+        <v>3396.38</v>
       </c>
       <c r="O372" t="n">
-        <v>523049.9356768581</v>
+        <v>519646.14</v>
       </c>
       <c r="P372" t="n">
         <v>6500</v>
@@ -17719,10 +17719,10 @@
         <v>27</v>
       </c>
       <c r="N387" t="n">
-        <v>5775.9026369168</v>
+        <v>5772</v>
       </c>
       <c r="O387" t="n">
-        <v>155949.3711967536</v>
+        <v>155844</v>
       </c>
       <c r="P387" t="n">
         <v>9900</v>
@@ -17857,10 +17857,10 @@
         <v>157</v>
       </c>
       <c r="N390" t="n">
-        <v>3904.1097178683</v>
+        <v>3898</v>
       </c>
       <c r="O390" t="n">
-        <v>612945.225705323</v>
+        <v>611986</v>
       </c>
       <c r="P390" t="n">
         <v>6900</v>
@@ -19787,10 +19787,10 @@
         <v>192</v>
       </c>
       <c r="N432" t="n">
-        <v>1775.6031464968</v>
+        <v>1771.0907898089</v>
       </c>
       <c r="O432" t="n">
-        <v>340915.8041273856</v>
+        <v>340049.4316433088</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
@@ -19867,13 +19867,13 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M434" t="n">
         <v>72</v>
@@ -20005,13 +20005,13 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
       </c>
       <c r="L437" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M437" t="n">
         <v>120</v>
@@ -21885,13 +21885,13 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
       </c>
       <c r="L478" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M478" t="n">
         <v>506</v>
@@ -21943,10 +21943,10 @@
         <v>20</v>
       </c>
       <c r="N479" t="n">
-        <v>2474.8947826087</v>
+        <v>2357.74</v>
       </c>
       <c r="O479" t="n">
-        <v>49497.895652174</v>
+        <v>47154.8</v>
       </c>
       <c r="P479" t="n">
         <v>3000</v>
@@ -25551,13 +25551,13 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M556" t="n">
         <v>12</v>
@@ -26169,13 +26169,13 @@
         </is>
       </c>
       <c r="J569" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="K569" t="n">
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M569" t="n">
         <v>100</v>
@@ -29443,13 +29443,13 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>831</v>
+        <v>791</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M639" t="n">
         <v>791</v>
@@ -30134,10 +30134,10 @@
         <v>306</v>
       </c>
       <c r="N654" t="n">
-        <v>1775.9757537155</v>
+        <v>1757.320552017</v>
       </c>
       <c r="O654" t="n">
-        <v>543448.580636943</v>
+        <v>537740.088917202</v>
       </c>
       <c r="P654" t="n">
         <v>2000</v>
@@ -30260,13 +30260,13 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M657" t="n">
         <v>3700</v>
@@ -30766,10 +30766,10 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="K668" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="L668" t="n">
         <v>0</v>
@@ -30812,10 +30812,10 @@
         </is>
       </c>
       <c r="J669" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="K669" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="L669" t="n">
         <v>0</v>
@@ -30858,10 +30858,10 @@
         </is>
       </c>
       <c r="J670" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K670" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L670" t="n">
         <v>0</v>
@@ -30904,10 +30904,10 @@
         </is>
       </c>
       <c r="J671" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K671" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L671" t="n">
         <v>0</v>
@@ -30950,10 +30950,10 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K672" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="L672" t="n">
         <v>0</v>
@@ -30996,10 +30996,10 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K673" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L673" t="n">
         <v>0</v>
@@ -31042,10 +31042,10 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K674" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="L674" t="n">
         <v>0</v>
@@ -31088,10 +31088,10 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K675" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L675" t="n">
         <v>0</v>
@@ -31134,10 +31134,10 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="K676" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
@@ -31180,10 +31180,10 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="K677" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="L677" t="n">
         <v>0</v>
@@ -31226,10 +31226,10 @@
         </is>
       </c>
       <c r="J678" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="K678" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="L678" t="n">
         <v>0</v>
@@ -31759,10 +31759,10 @@
         <v>686</v>
       </c>
       <c r="N689" t="n">
-        <v>229.09061119293</v>
+        <v>227.41601620029</v>
       </c>
       <c r="O689" t="n">
-        <v>157156.15927835</v>
+        <v>156007.3871133989</v>
       </c>
       <c r="P689" t="n">
         <v>1200</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q692"/>
+  <dimension ref="A1:Q694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3058666667</v>
+        <v>1811.3059701493</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3058666667</v>
+        <v>1811.3059701493</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464891304</v>
+        <v>3376.7464843537</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.896391273</v>
+        <v>2985043.892168671</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -831,10 +831,10 @@
         <v>55</v>
       </c>
       <c r="N11" t="n">
-        <v>5758.9597787611</v>
+        <v>5758.9597782705</v>
       </c>
       <c r="O11" t="n">
-        <v>316742.7878318605</v>
+        <v>316742.7878048775</v>
       </c>
       <c r="P11" t="n">
         <v>16900</v>
@@ -1312,10 +1312,10 @@
         <v>92</v>
       </c>
       <c r="N23" t="n">
-        <v>2413.0010683761</v>
+        <v>2413.0010706638</v>
       </c>
       <c r="O23" t="n">
-        <v>221996.0982906012</v>
+        <v>221996.0985010696</v>
       </c>
       <c r="P23" t="n">
         <v>4700</v>
@@ -1705,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>12837.966461538</v>
+        <v>12837.967258065</v>
       </c>
       <c r="O33" t="n">
-        <v>51351.865846152</v>
+        <v>51351.86903226</v>
       </c>
       <c r="P33" t="n">
         <v>22900</v>
@@ -1794,10 +1794,10 @@
         <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>10994.360689655</v>
+        <v>10994.361428571</v>
       </c>
       <c r="O35" t="n">
-        <v>65966.16413793</v>
+        <v>65966.16857142599</v>
       </c>
       <c r="P35" t="n">
         <v>16900</v>
@@ -1878,10 +1878,10 @@
         <v>18</v>
       </c>
       <c r="N37" t="n">
-        <v>15711.966041667</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O37" t="n">
-        <v>282815.388750006</v>
+        <v>282815.388151254</v>
       </c>
       <c r="P37" t="n">
         <v>28500</v>
@@ -2128,10 +2128,10 @@
         <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>56906.802542373</v>
+        <v>56906.802982456</v>
       </c>
       <c r="O43" t="n">
-        <v>455254.420338984</v>
+        <v>455254.423859648</v>
       </c>
       <c r="P43" t="n">
         <v>95900</v>
@@ -2217,10 +2217,10 @@
         <v>7</v>
       </c>
       <c r="N45" t="n">
-        <v>200072.2004878</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O45" t="n">
-        <v>1400505.4034146</v>
+        <v>1400505.40401639</v>
       </c>
       <c r="P45" t="n">
         <v>312000</v>
@@ -3087,10 +3087,10 @@
         <v>228</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="O65" t="n">
-        <v>1125706.716855242</v>
+        <v>1125706.717018445</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3349,10 +3349,10 @@
         <v>1295</v>
       </c>
       <c r="N71" t="n">
-        <v>1098.0574483741</v>
+        <v>1098.0580436917</v>
       </c>
       <c r="O71" t="n">
-        <v>1421984.395644459</v>
+        <v>1421985.166580752</v>
       </c>
       <c r="P71" t="n">
         <v>1500</v>
@@ -4282,10 +4282,10 @@
         <v>771</v>
       </c>
       <c r="N92" t="n">
-        <v>2582.2558919365</v>
+        <v>2582.2558569052</v>
       </c>
       <c r="O92" t="n">
-        <v>1990919.292683042</v>
+        <v>1990919.265673909</v>
       </c>
       <c r="P92" t="n">
         <v>4500</v>
@@ -4374,10 +4374,10 @@
         <v>720</v>
       </c>
       <c r="N94" t="n">
-        <v>5216.8961798703</v>
+        <v>5216.8961652752</v>
       </c>
       <c r="O94" t="n">
-        <v>3756165.249506616</v>
+        <v>3756165.238998143</v>
       </c>
       <c r="P94" t="n">
         <v>8500</v>
@@ -4605,10 +4605,10 @@
         <v>3199</v>
       </c>
       <c r="N99" t="n">
-        <v>3158.8608246566</v>
+        <v>3158.8608249792</v>
       </c>
       <c r="O99" t="n">
-        <v>10105195.77807646</v>
+        <v>10105195.77910846</v>
       </c>
       <c r="P99" t="n">
         <v>5600</v>
@@ -4741,10 +4741,10 @@
         <v>180</v>
       </c>
       <c r="N102" t="n">
-        <v>3230.0674725275</v>
+        <v>3230.0674157303</v>
       </c>
       <c r="O102" t="n">
-        <v>581412.1450549499</v>
+        <v>581412.134831454</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4880,10 +4880,10 @@
         <v>259</v>
       </c>
       <c r="N105" t="n">
-        <v>2694.8232527881</v>
+        <v>2694.823243369</v>
       </c>
       <c r="O105" t="n">
-        <v>697959.2224721179</v>
+        <v>697959.220032571</v>
       </c>
       <c r="P105" t="n">
         <v>4900</v>
@@ -5425,10 +5425,10 @@
         <v>312</v>
       </c>
       <c r="N117" t="n">
-        <v>4890.9300476474</v>
+        <v>4890.9300481348</v>
       </c>
       <c r="O117" t="n">
-        <v>1525970.174865989</v>
+        <v>1525970.175018058</v>
       </c>
       <c r="P117" t="n">
         <v>8200</v>
@@ -5869,22 +5869,22 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M127" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N127" t="n">
         <v>10716.34</v>
       </c>
       <c r="O127" t="n">
-        <v>150028.76</v>
+        <v>85730.72</v>
       </c>
       <c r="P127" t="n">
         <v>39000</v>
       </c>
       <c r="Q127" t="n">
-        <v>546000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="128">
@@ -5924,10 +5924,10 @@
         <v>288</v>
       </c>
       <c r="N128" t="n">
-        <v>3594.25408867</v>
+        <v>3594.2540740741</v>
       </c>
       <c r="O128" t="n">
-        <v>1035145.17753696</v>
+        <v>1035145.173333341</v>
       </c>
       <c r="P128" t="n">
         <v>6500</v>
@@ -5965,10 +5965,10 @@
         <v>108</v>
       </c>
       <c r="N129" t="n">
-        <v>3240.8500313972</v>
+        <v>3240.8500314961</v>
       </c>
       <c r="O129" t="n">
-        <v>350011.8033908976</v>
+        <v>350011.8034015788</v>
       </c>
       <c r="P129" t="n">
         <v>5200</v>
@@ -6149,10 +6149,10 @@
         <v>305</v>
       </c>
       <c r="N133" t="n">
-        <v>14822.378855098</v>
+        <v>14822.378854415</v>
       </c>
       <c r="O133" t="n">
-        <v>4520825.55080489</v>
+        <v>4520825.550596574</v>
       </c>
       <c r="P133" t="n">
         <v>24900</v>
@@ -6874,10 +6874,10 @@
         <v>210</v>
       </c>
       <c r="N149" t="n">
-        <v>3041.6600129618</v>
+        <v>3041.6600129786</v>
       </c>
       <c r="O149" t="n">
-        <v>638748.602721978</v>
+        <v>638748.6027255061</v>
       </c>
       <c r="P149" t="n">
         <v>5500</v>
@@ -7002,10 +7002,10 @@
         <v>1945</v>
       </c>
       <c r="N152" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O152" t="n">
-        <v>8503949.983741419</v>
+        <v>8503949.983959649</v>
       </c>
       <c r="P152" t="n">
         <v>7500</v>
@@ -7092,10 +7092,10 @@
         <v>480</v>
       </c>
       <c r="N154" t="n">
-        <v>1592.5670028818</v>
+        <v>1592.5669608416</v>
       </c>
       <c r="O154" t="n">
-        <v>764432.161383264</v>
+        <v>764432.141203968</v>
       </c>
       <c r="P154" t="n">
         <v>3900</v>
@@ -7582,10 +7582,10 @@
         <v>450</v>
       </c>
       <c r="N165" t="n">
-        <v>1532.6290283636</v>
+        <v>1532.6290281516</v>
       </c>
       <c r="O165" t="n">
-        <v>689683.0627636199</v>
+        <v>689683.06266822</v>
       </c>
       <c r="P165" t="n">
         <v>1200</v>
@@ -8883,10 +8883,10 @@
         <v>776</v>
       </c>
       <c r="N193" t="n">
-        <v>1630.9234162594</v>
+        <v>1630.9234624043</v>
       </c>
       <c r="O193" t="n">
-        <v>1265596.571017294</v>
+        <v>1265596.606825737</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -8929,10 +8929,10 @@
         <v>5</v>
       </c>
       <c r="N194" t="n">
-        <v>1467.3247826087</v>
+        <v>1467.3243362832</v>
       </c>
       <c r="O194" t="n">
-        <v>7336.6239130435</v>
+        <v>7336.621681416</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8975,10 +8975,10 @@
         <v>288</v>
       </c>
       <c r="N195" t="n">
-        <v>1690.5995518395</v>
+        <v>1690.5992886179</v>
       </c>
       <c r="O195" t="n">
-        <v>486892.670929776</v>
+        <v>486892.5951219551</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9021,10 +9021,10 @@
         <v>2022</v>
       </c>
       <c r="N196" t="n">
-        <v>1550.1934418475</v>
+        <v>1550.1935205388</v>
       </c>
       <c r="O196" t="n">
-        <v>3134491.139415645</v>
+        <v>3134491.298529454</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9067,10 +9067,10 @@
         <v>22</v>
       </c>
       <c r="N197" t="n">
-        <v>1579.3908418367</v>
+        <v>1579.3907948718</v>
       </c>
       <c r="O197" t="n">
-        <v>34746.5985204074</v>
+        <v>34746.5974871796</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9113,10 +9113,10 @@
         <v>418</v>
       </c>
       <c r="N198" t="n">
-        <v>2403.5113112366</v>
+        <v>2403.5114869613</v>
       </c>
       <c r="O198" t="n">
-        <v>1004667.728096899</v>
+        <v>1004667.801549823</v>
       </c>
       <c r="P198" t="n">
         <v>3500</v>
@@ -10789,10 +10789,10 @@
         <v>159</v>
       </c>
       <c r="N236" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O236" t="n">
-        <v>426237.6122902692</v>
+        <v>426237.6122317572</v>
       </c>
       <c r="P236" t="n">
         <v>4900</v>
@@ -11196,10 +11196,10 @@
         <v>125</v>
       </c>
       <c r="N245" t="n">
-        <v>4285.1953927813</v>
+        <v>4285.1954215582</v>
       </c>
       <c r="O245" t="n">
-        <v>535649.4240976626</v>
+        <v>535649.427694775</v>
       </c>
       <c r="P245" t="n">
         <v>6900</v>
@@ -11455,10 +11455,10 @@
         <v>563</v>
       </c>
       <c r="N251" t="n">
-        <v>4605.2146617238</v>
+        <v>4605.2146660482</v>
       </c>
       <c r="O251" t="n">
-        <v>2592735.854550499</v>
+        <v>2592735.856985137</v>
       </c>
       <c r="P251" t="n">
         <v>7600</v>
@@ -11542,10 +11542,10 @@
         <v>32</v>
       </c>
       <c r="N253" t="n">
-        <v>11562.038522427</v>
+        <v>11562.038518519</v>
       </c>
       <c r="O253" t="n">
-        <v>369985.232717664</v>
+        <v>369985.232592608</v>
       </c>
       <c r="P253" t="n">
         <v>18500</v>
@@ -12038,10 +12038,10 @@
         <v>599</v>
       </c>
       <c r="N264" t="n">
-        <v>1561</v>
+        <v>1561.0000887728</v>
       </c>
       <c r="O264" t="n">
-        <v>935039</v>
+        <v>935039.0531749071</v>
       </c>
       <c r="P264" t="n">
         <v>2900</v>
@@ -12176,10 +12176,10 @@
         <v>188</v>
       </c>
       <c r="N267" t="n">
-        <v>7969.9501660377</v>
+        <v>7969.9501665405</v>
       </c>
       <c r="O267" t="n">
-        <v>1498350.631215088</v>
+        <v>1498350.631309614</v>
       </c>
       <c r="P267" t="n">
         <v>12900</v>
@@ -12925,10 +12925,10 @@
         <v>122</v>
       </c>
       <c r="N283" t="n">
-        <v>3113.8900273598</v>
+        <v>3113.8900274725</v>
       </c>
       <c r="O283" t="n">
-        <v>379894.5833378956</v>
+        <v>379894.583351645</v>
       </c>
       <c r="P283" t="n">
         <v>5000</v>
@@ -13247,10 +13247,10 @@
         <v>81</v>
       </c>
       <c r="N290" t="n">
-        <v>5218.1705346294</v>
+        <v>5218.1705412054</v>
       </c>
       <c r="O290" t="n">
-        <v>422671.8133049814</v>
+        <v>422671.8138376374</v>
       </c>
       <c r="P290" t="n">
         <v>8500</v>
@@ -13293,10 +13293,10 @@
         <v>1</v>
       </c>
       <c r="N291" t="n">
-        <v>1595.0094090202</v>
+        <v>1595.0093958665</v>
       </c>
       <c r="O291" t="n">
-        <v>1595.0094090202</v>
+        <v>1595.0093958665</v>
       </c>
       <c r="P291" t="n">
         <v>2600</v>
@@ -14035,10 +14035,10 @@
         <v>824</v>
       </c>
       <c r="N307" t="n">
-        <v>1778.4725974412</v>
+        <v>1778.4725978277</v>
       </c>
       <c r="O307" t="n">
-        <v>1465461.420291549</v>
+        <v>1465461.420610025</v>
       </c>
       <c r="P307" t="n">
         <v>4900</v>
@@ -15415,22 +15415,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M337" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N337" t="n">
         <v>7108.85</v>
       </c>
       <c r="O337" t="n">
-        <v>170612.4</v>
+        <v>0</v>
       </c>
       <c r="P337" t="n">
         <v>7900</v>
       </c>
       <c r="Q337" t="n">
-        <v>189600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -17038,10 +17038,10 @@
         <v>149</v>
       </c>
       <c r="N372" t="n">
-        <v>4907.8220483871</v>
+        <v>4907.8220583468</v>
       </c>
       <c r="O372" t="n">
-        <v>731265.485209678</v>
+        <v>731265.4866936732</v>
       </c>
       <c r="P372" t="n">
         <v>8200</v>
@@ -17268,10 +17268,10 @@
         <v>289</v>
       </c>
       <c r="N377" t="n">
-        <v>3903.7363106796</v>
+        <v>3903.7364457831</v>
       </c>
       <c r="O377" t="n">
-        <v>1128179.793786404</v>
+        <v>1128179.832831316</v>
       </c>
       <c r="P377" t="n">
         <v>7500</v>
@@ -17349,22 +17349,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M379" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N379" t="n">
         <v>12113</v>
       </c>
       <c r="O379" t="n">
-        <v>218034</v>
+        <v>0</v>
       </c>
       <c r="P379" t="n">
         <v>19900</v>
       </c>
       <c r="Q379" t="n">
-        <v>358200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -18321,10 +18321,10 @@
         <v>292</v>
       </c>
       <c r="N400" t="n">
-        <v>17075.98952381</v>
+        <v>17075.989523481</v>
       </c>
       <c r="O400" t="n">
-        <v>4986188.94095252</v>
+        <v>4986188.940856452</v>
       </c>
       <c r="P400" t="n">
         <v>27500</v>
@@ -19515,10 +19515,10 @@
         <v>1320</v>
       </c>
       <c r="N426" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O426" t="n">
-        <v>2001171.220106916</v>
+        <v>2001171.218415468</v>
       </c>
       <c r="P426" t="n">
         <v>2300</v>
@@ -19607,10 +19607,10 @@
         <v>8</v>
       </c>
       <c r="N428" t="n">
-        <v>4248.652</v>
+        <v>4248.6728</v>
       </c>
       <c r="O428" t="n">
-        <v>33989.216</v>
+        <v>33989.3824</v>
       </c>
       <c r="P428" t="n">
         <v>5900</v>
@@ -19653,10 +19653,10 @@
         <v>120</v>
       </c>
       <c r="N429" t="n">
-        <v>2458.5132807977</v>
+        <v>2458.5132504039</v>
       </c>
       <c r="O429" t="n">
-        <v>295021.593695724</v>
+        <v>295021.590048468</v>
       </c>
       <c r="P429" t="n">
         <v>3500</v>
@@ -19699,10 +19699,10 @@
         <v>192</v>
       </c>
       <c r="N430" t="n">
-        <v>1771.0906468305</v>
+        <v>1771.0905981795</v>
       </c>
       <c r="O430" t="n">
-        <v>340049.404191456</v>
+        <v>340049.394850464</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -19745,10 +19745,10 @@
         <v>264</v>
       </c>
       <c r="N431" t="n">
-        <v>2079.3840533333</v>
+        <v>2079.3840473807</v>
       </c>
       <c r="O431" t="n">
-        <v>548957.3900799912</v>
+        <v>548957.3885085048</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
@@ -19791,10 +19791,10 @@
         <v>72</v>
       </c>
       <c r="N432" t="n">
-        <v>1803.0155537353</v>
+        <v>1803.0155591997</v>
       </c>
       <c r="O432" t="n">
-        <v>129817.1198689416</v>
+        <v>129817.1202623784</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
@@ -19837,10 +19837,10 @@
         <v>216</v>
       </c>
       <c r="N433" t="n">
-        <v>3306.5952380952</v>
+        <v>3306.5951935915</v>
       </c>
       <c r="O433" t="n">
-        <v>714224.5714285632</v>
+        <v>714224.5618157641</v>
       </c>
       <c r="P433" t="n">
         <v>4900</v>
@@ -19883,10 +19883,10 @@
         <v>192</v>
       </c>
       <c r="N434" t="n">
-        <v>2122.1639235788</v>
+        <v>2122.1639198011</v>
       </c>
       <c r="O434" t="n">
-        <v>407455.4733271296</v>
+        <v>407455.4726018112</v>
       </c>
       <c r="P434" t="n">
         <v>2900</v>
@@ -19929,10 +19929,10 @@
         <v>120</v>
       </c>
       <c r="N435" t="n">
-        <v>2108.7910927573</v>
+        <v>2108.7914267016</v>
       </c>
       <c r="O435" t="n">
-        <v>253054.931130876</v>
+        <v>253054.971204192</v>
       </c>
       <c r="P435" t="n">
         <v>2900</v>
@@ -19975,10 +19975,10 @@
         <v>144</v>
       </c>
       <c r="N436" t="n">
-        <v>2056.0834704208</v>
+        <v>2056.0834183673</v>
       </c>
       <c r="O436" t="n">
-        <v>296076.0197405952</v>
+        <v>296076.0122448912</v>
       </c>
       <c r="P436" t="n">
         <v>2900</v>
@@ -20021,10 +20021,10 @@
         <v>216</v>
       </c>
       <c r="N437" t="n">
-        <v>3224.5685035629</v>
+        <v>3224.5685238095</v>
       </c>
       <c r="O437" t="n">
-        <v>696506.7967695864</v>
+        <v>696506.8011428521</v>
       </c>
       <c r="P437" t="n">
         <v>4500</v>
@@ -20067,10 +20067,10 @@
         <v>360</v>
       </c>
       <c r="N438" t="n">
-        <v>1655.9309755302</v>
+        <v>1655.9309666884</v>
       </c>
       <c r="O438" t="n">
-        <v>596135.151190872</v>
+        <v>596135.1480078241</v>
       </c>
       <c r="P438" t="n">
         <v>2500</v>
@@ -20297,10 +20297,10 @@
         <v>384</v>
       </c>
       <c r="N443" t="n">
-        <v>1592.276898982</v>
+        <v>1592.2773416667</v>
       </c>
       <c r="O443" t="n">
-        <v>611434.329209088</v>
+        <v>611434.4992000128</v>
       </c>
       <c r="P443" t="n">
         <v>2500</v>
@@ -20428,10 +20428,10 @@
         <v>408</v>
       </c>
       <c r="N446" t="n">
-        <v>2060.1603030303</v>
+        <v>2060.1601200686</v>
       </c>
       <c r="O446" t="n">
-        <v>840545.4036363624</v>
+        <v>840545.3289879888</v>
       </c>
       <c r="P446" t="n">
         <v>2900</v>
@@ -20474,10 +20474,10 @@
         <v>24</v>
       </c>
       <c r="N447" t="n">
-        <v>1668.6274157303</v>
+        <v>1668.628045977</v>
       </c>
       <c r="O447" t="n">
-        <v>40047.05797752721</v>
+        <v>40047.073103448</v>
       </c>
       <c r="P447" t="n">
         <v>2500</v>
@@ -20520,10 +20520,10 @@
         <v>24</v>
       </c>
       <c r="N448" t="n">
-        <v>2546.9846516008</v>
+        <v>2546.9843873518</v>
       </c>
       <c r="O448" t="n">
-        <v>61127.6316384192</v>
+        <v>61127.62529644319</v>
       </c>
       <c r="P448" t="n">
         <v>3900</v>
@@ -20566,10 +20566,10 @@
         <v>800</v>
       </c>
       <c r="N449" t="n">
-        <v>1259.2745137492</v>
+        <v>1259.2745258911</v>
       </c>
       <c r="O449" t="n">
-        <v>1007419.61099936</v>
+        <v>1007419.62071288</v>
       </c>
       <c r="P449" t="n">
         <v>1900</v>
@@ -20653,10 +20653,10 @@
         <v>97</v>
       </c>
       <c r="N451" t="n">
-        <v>2842.2737539432</v>
+        <v>2842.2737341772</v>
       </c>
       <c r="O451" t="n">
-        <v>275700.5541324904</v>
+        <v>275700.5522151884</v>
       </c>
       <c r="P451" t="n">
         <v>4900</v>
@@ -20699,10 +20699,10 @@
         <v>72</v>
       </c>
       <c r="N452" t="n">
-        <v>2556.745819398</v>
+        <v>2556.7459385666</v>
       </c>
       <c r="O452" t="n">
-        <v>184085.698996656</v>
+        <v>184085.7075767952</v>
       </c>
       <c r="P452" t="n">
         <v>3900</v>
@@ -20789,10 +20789,10 @@
         <v>540</v>
       </c>
       <c r="N454" t="n">
-        <v>692.15220363289</v>
+        <v>692.15222061657</v>
       </c>
       <c r="O454" t="n">
-        <v>373762.1899617606</v>
+        <v>373762.1991329478</v>
       </c>
       <c r="P454" t="n">
         <v>1200</v>
@@ -21104,22 +21104,22 @@
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M461" t="n">
-        <v>911</v>
+        <v>875</v>
       </c>
       <c r="N461" t="n">
         <v>1337.86</v>
       </c>
       <c r="O461" t="n">
-        <v>1218790.46</v>
+        <v>1170627.5</v>
       </c>
       <c r="P461" t="n">
         <v>3000</v>
       </c>
       <c r="Q461" t="n">
-        <v>2733000</v>
+        <v>2625000</v>
       </c>
     </row>
     <row r="462">
@@ -21945,10 +21945,10 @@
         <v>306</v>
       </c>
       <c r="N479" t="n">
-        <v>1690.870009058</v>
+        <v>1690.8700090909</v>
       </c>
       <c r="O479" t="n">
-        <v>517406.222771748</v>
+        <v>517406.2227818154</v>
       </c>
       <c r="P479" t="n">
         <v>3000</v>
@@ -22554,10 +22554,10 @@
         <v>149</v>
       </c>
       <c r="N492" t="n">
-        <v>1283.6539261745</v>
+        <v>1283.6538013699</v>
       </c>
       <c r="O492" t="n">
-        <v>191264.4350000005</v>
+        <v>191264.4164041151</v>
       </c>
       <c r="P492" t="n">
         <v>1900</v>
@@ -22788,10 +22788,10 @@
         <v>461</v>
       </c>
       <c r="N497" t="n">
-        <v>517.28896164542</v>
+        <v>517.28908220781</v>
       </c>
       <c r="O497" t="n">
-        <v>238470.2113185386</v>
+        <v>238470.2668978004</v>
       </c>
       <c r="P497" t="n">
         <v>900</v>
@@ -23211,10 +23211,10 @@
         <v>757</v>
       </c>
       <c r="N506" t="n">
-        <v>3110.8423302235</v>
+        <v>3110.842321894</v>
       </c>
       <c r="O506" t="n">
-        <v>2354907.643979189</v>
+        <v>2354907.637673758</v>
       </c>
       <c r="P506" t="n">
         <v>4500</v>
@@ -23662,10 +23662,10 @@
         <v>19802</v>
       </c>
       <c r="N516" t="n">
-        <v>703.79522697548</v>
+        <v>703.79521051815</v>
       </c>
       <c r="O516" t="n">
-        <v>13936553.08456845</v>
+        <v>13936552.75868041</v>
       </c>
       <c r="P516" t="n">
         <v>900</v>
@@ -23711,10 +23711,10 @@
         <v>55</v>
       </c>
       <c r="N517" t="n">
-        <v>3182.2511070111</v>
+        <v>3182.2511214953</v>
       </c>
       <c r="O517" t="n">
-        <v>175023.8108856105</v>
+        <v>175023.8116822415</v>
       </c>
       <c r="P517" t="n">
         <v>6900</v>
@@ -24169,10 +24169,10 @@
         <v>47</v>
       </c>
       <c r="N527" t="n">
-        <v>1595.5132863655</v>
+        <v>1595.513125523</v>
       </c>
       <c r="O527" t="n">
-        <v>74989.12445917851</v>
+        <v>74989.116899581</v>
       </c>
       <c r="P527" t="n">
         <v>2500</v>
@@ -28373,10 +28373,10 @@
         <v>648</v>
       </c>
       <c r="N615" t="n">
-        <v>665.32351302785</v>
+        <v>665.32352410996</v>
       </c>
       <c r="O615" t="n">
-        <v>431129.6364420468</v>
+        <v>431129.6436232541</v>
       </c>
       <c r="P615" t="n">
         <v>2900</v>
@@ -28811,10 +28811,10 @@
         <v>153</v>
       </c>
       <c r="N624" t="n">
-        <v>315.02694721826</v>
+        <v>315.02697707736</v>
       </c>
       <c r="O624" t="n">
-        <v>48199.12292439378</v>
+        <v>48199.12749283608</v>
       </c>
       <c r="P624" t="n">
         <v>2200</v>
@@ -29156,10 +29156,10 @@
         <v>40</v>
       </c>
       <c r="N632" t="n">
-        <v>6243.3531428571</v>
+        <v>6243.3531578947</v>
       </c>
       <c r="O632" t="n">
-        <v>249734.125714284</v>
+        <v>249734.126315788</v>
       </c>
       <c r="P632" t="n">
         <v>9900</v>
@@ -29241,10 +29241,10 @@
         <v>20</v>
       </c>
       <c r="N634" t="n">
-        <v>2129.8331598174</v>
+        <v>2129.8331627057</v>
       </c>
       <c r="O634" t="n">
-        <v>42596.663196348</v>
+        <v>42596.663254114</v>
       </c>
       <c r="P634" t="n">
         <v>2700</v>
@@ -29540,10 +29540,10 @@
         <v>28</v>
       </c>
       <c r="N641" t="n">
-        <v>15219.155232558</v>
+        <v>15219.155176471</v>
       </c>
       <c r="O641" t="n">
-        <v>426136.346511624</v>
+        <v>426136.344941188</v>
       </c>
       <c r="P641" t="n">
         <v>16000</v>
@@ -29857,10 +29857,10 @@
         <v>352</v>
       </c>
       <c r="N648" t="n">
-        <v>22951.704911392</v>
+        <v>22951.704904943</v>
       </c>
       <c r="O648" t="n">
-        <v>8079000.128809984</v>
+        <v>8079000.126539935</v>
       </c>
       <c r="P648" t="n">
         <v>37900</v>
@@ -29903,10 +29903,10 @@
         <v>172</v>
       </c>
       <c r="N649" t="n">
-        <v>705.52801204819</v>
+        <v>705.52800453515</v>
       </c>
       <c r="O649" t="n">
-        <v>121350.8180722887</v>
+        <v>121350.8167800458</v>
       </c>
       <c r="P649" t="n">
         <v>1500</v>
@@ -29944,10 +29944,10 @@
         <v>93</v>
       </c>
       <c r="N650" t="n">
-        <v>4985.4051948052</v>
+        <v>4985.4053097345</v>
       </c>
       <c r="O650" t="n">
-        <v>463642.6831168836</v>
+        <v>463642.6938053085</v>
       </c>
       <c r="P650" t="n">
         <v>7900</v>
@@ -30046,10 +30046,10 @@
         <v>306</v>
       </c>
       <c r="N652" t="n">
-        <v>1757.3205567452</v>
+        <v>1757.3205591398</v>
       </c>
       <c r="O652" t="n">
-        <v>537740.0903640313</v>
+        <v>537740.0910967789</v>
       </c>
       <c r="P652" t="n">
         <v>2000</v>
@@ -30184,10 +30184,10 @@
         <v>3700</v>
       </c>
       <c r="N655" t="n">
-        <v>220.00629713546</v>
+        <v>220.00534867624</v>
       </c>
       <c r="O655" t="n">
-        <v>814023.299401202</v>
+        <v>814019.790102088</v>
       </c>
       <c r="P655" t="n">
         <v>260</v>
@@ -30659,12 +30659,12 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -30678,39 +30678,39 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K666" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="N666" t="n">
-        <v>415.07</v>
+        <v>7480</v>
       </c>
       <c r="O666" t="n">
-        <v>12867.17</v>
+        <v>1077120</v>
       </c>
       <c r="P666" t="n">
-        <v>2900</v>
+        <v>9500</v>
       </c>
       <c r="Q666" t="n">
-        <v>89900</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -30724,44 +30724,44 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K667" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="L667" t="n">
         <v>0</v>
       </c>
       <c r="M667" t="n">
-        <v>59</v>
+        <v>480</v>
       </c>
       <c r="N667" t="n">
-        <v>46491.75</v>
+        <v>9240</v>
       </c>
       <c r="O667" t="n">
-        <v>2743013.25</v>
+        <v>4435200</v>
       </c>
       <c r="P667" t="n">
-        <v>52900</v>
+        <v>11500</v>
       </c>
       <c r="Q667" t="n">
-        <v>3121100</v>
+        <v>5520000</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -30770,7 +30770,7 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="K668" t="n">
         <v>0</v>
@@ -30779,35 +30779,35 @@
         <v>0</v>
       </c>
       <c r="M668" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N668" t="n">
-        <v>910.85</v>
+        <v>415.07</v>
       </c>
       <c r="O668" t="n">
-        <v>41899.1</v>
+        <v>12867.17</v>
       </c>
       <c r="P668" t="n">
-        <v>7900</v>
+        <v>2900</v>
       </c>
       <c r="Q668" t="n">
-        <v>363400</v>
+        <v>89900</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -30816,7 +30816,7 @@
         </is>
       </c>
       <c r="J669" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="K669" t="n">
         <v>0</v>
@@ -30825,30 +30825,30 @@
         <v>0</v>
       </c>
       <c r="M669" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="N669" t="n">
-        <v>1129.14</v>
+        <v>46491.75</v>
       </c>
       <c r="O669" t="n">
-        <v>13549.68</v>
+        <v>2743013.25</v>
       </c>
       <c r="P669" t="n">
-        <v>6900</v>
+        <v>52900</v>
       </c>
       <c r="Q669" t="n">
-        <v>82800</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -30862,49 +30862,44 @@
         </is>
       </c>
       <c r="J670" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="K670" t="n">
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M670" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="N670" t="n">
-        <v>11433.53</v>
+        <v>910.85</v>
       </c>
       <c r="O670" t="n">
-        <v>125768.83</v>
+        <v>32790.6</v>
       </c>
       <c r="P670" t="n">
-        <v>15000</v>
+        <v>7900</v>
       </c>
       <c r="Q670" t="n">
-        <v>165000</v>
+        <v>284400</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -30913,7 +30908,7 @@
         </is>
       </c>
       <c r="J671" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K671" t="n">
         <v>0</v>
@@ -30922,35 +30917,35 @@
         <v>0</v>
       </c>
       <c r="M671" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N671" t="n">
-        <v>15452.21</v>
+        <v>1129.14</v>
       </c>
       <c r="O671" t="n">
-        <v>61808.84</v>
+        <v>13549.68</v>
       </c>
       <c r="P671" t="n">
-        <v>36500</v>
+        <v>6900</v>
       </c>
       <c r="Q671" t="n">
-        <v>146000</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -30959,7 +30954,7 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
@@ -30968,40 +30963,40 @@
         <v>0</v>
       </c>
       <c r="M672" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="N672" t="n">
-        <v>1319.3608823529</v>
+        <v>11433.53</v>
       </c>
       <c r="O672" t="n">
-        <v>263872.17647058</v>
+        <v>125768.83</v>
       </c>
       <c r="P672" t="n">
-        <v>3500</v>
+        <v>15000</v>
       </c>
       <c r="Q672" t="n">
-        <v>700000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>MG33219</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>MG33219</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -31010,7 +31005,7 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="K673" t="n">
         <v>0</v>
@@ -31019,35 +31014,35 @@
         <v>0</v>
       </c>
       <c r="M673" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="N673" t="n">
-        <v>751.45</v>
+        <v>15452.21</v>
       </c>
       <c r="O673" t="n">
-        <v>50347.15</v>
+        <v>61808.84</v>
       </c>
       <c r="P673" t="n">
-        <v>2500</v>
+        <v>36500</v>
       </c>
       <c r="Q673" t="n">
-        <v>167500</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -31056,7 +31051,7 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
@@ -31065,35 +31060,40 @@
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="N674" t="n">
-        <v>571.87</v>
+        <v>1319.3608823529</v>
       </c>
       <c r="O674" t="n">
-        <v>81777.41</v>
+        <v>263872.17647058</v>
       </c>
       <c r="P674" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="Q674" t="n">
-        <v>357500</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -31102,7 +31102,7 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>686</v>
+        <v>67</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -31111,40 +31111,35 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>686</v>
+        <v>67</v>
       </c>
       <c r="N675" t="n">
-        <v>227.41601620029</v>
+        <v>751.45</v>
       </c>
       <c r="O675" t="n">
-        <v>156007.3871133989</v>
+        <v>50347.15</v>
       </c>
       <c r="P675" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="Q675" t="n">
-        <v>823200</v>
+        <v>167500</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -31153,7 +31148,7 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
@@ -31162,39 +31157,44 @@
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="N676" t="n">
-        <v>9917.040000000001</v>
+        <v>571.87</v>
       </c>
       <c r="O676" t="n">
-        <v>218174.88</v>
+        <v>81777.41</v>
       </c>
       <c r="P676" t="n">
-        <v>15900</v>
+        <v>2500</v>
       </c>
       <c r="Q676" t="n">
-        <v>349800</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>MT4004</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J677" t="n">
-        <v>158</v>
+        <v>686</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
@@ -31203,35 +31203,40 @@
         <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>158</v>
+        <v>686</v>
       </c>
       <c r="N677" t="n">
-        <v>2058.92</v>
+        <v>227.41601620029</v>
       </c>
       <c r="O677" t="n">
-        <v>325309.36</v>
+        <v>156007.3871133989</v>
       </c>
       <c r="P677" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="Q677" t="n">
-        <v>395000</v>
+        <v>823200</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -31240,7 +31245,7 @@
         </is>
       </c>
       <c r="J678" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="K678" t="n">
         <v>0</v>
@@ -31249,44 +31254,39 @@
         <v>0</v>
       </c>
       <c r="M678" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="N678" t="n">
-        <v>3306.0098306773</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O678" t="n">
-        <v>314070.9339143435</v>
+        <v>218174.88</v>
       </c>
       <c r="P678" t="n">
-        <v>4200</v>
+        <v>15900</v>
       </c>
       <c r="Q678" t="n">
-        <v>399000</v>
+        <v>349800</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>MT4004</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
-        </is>
-      </c>
-      <c r="E679" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J679" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="K679" t="n">
         <v>0</v>
@@ -31295,35 +31295,35 @@
         <v>0</v>
       </c>
       <c r="M679" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="N679" t="n">
-        <v>7600</v>
+        <v>2058.92</v>
       </c>
       <c r="O679" t="n">
-        <v>364800</v>
+        <v>325309.36</v>
       </c>
       <c r="P679" t="n">
-        <v>9500</v>
+        <v>2500</v>
       </c>
       <c r="Q679" t="n">
-        <v>456000</v>
+        <v>395000</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -31344,32 +31344,32 @@
         <v>95</v>
       </c>
       <c r="N680" t="n">
-        <v>5520</v>
+        <v>3306.00983</v>
       </c>
       <c r="O680" t="n">
-        <v>524400</v>
+        <v>314070.93385</v>
       </c>
       <c r="P680" t="n">
-        <v>6900</v>
+        <v>4200</v>
       </c>
       <c r="Q680" t="n">
-        <v>655500</v>
+        <v>399000</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>SEB09</t>
+          <t>SEB010</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="J681" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="K681" t="n">
         <v>0</v>
@@ -31387,30 +31387,30 @@
         <v>0</v>
       </c>
       <c r="M681" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="N681" t="n">
-        <v>1600</v>
+        <v>7600</v>
       </c>
       <c r="O681" t="n">
-        <v>132800</v>
+        <v>364800</v>
       </c>
       <c r="P681" t="n">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="Q681" t="n">
-        <v>166000</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -31424,7 +31424,7 @@
         </is>
       </c>
       <c r="J682" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="K682" t="n">
         <v>0</v>
@@ -31433,30 +31433,30 @@
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="N682" t="n">
-        <v>4091.4</v>
+        <v>5520</v>
       </c>
       <c r="O682" t="n">
-        <v>4091.4</v>
+        <v>524400</v>
       </c>
       <c r="P682" t="n">
-        <v>10000</v>
+        <v>6900</v>
       </c>
       <c r="Q682" t="n">
-        <v>10000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>SLT027</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>JUGUETE  DRAGON   AB-02 / 082</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -31470,7 +31470,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -31479,35 +31479,35 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="N683" t="n">
-        <v>3732.8773611111</v>
+        <v>1600</v>
       </c>
       <c r="O683" t="n">
-        <v>37328.773611111</v>
+        <v>132800</v>
       </c>
       <c r="P683" t="n">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="Q683" t="n">
-        <v>45000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -31516,7 +31516,7 @@
         </is>
       </c>
       <c r="J684" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K684" t="n">
         <v>0</v>
@@ -31525,35 +31525,35 @@
         <v>0</v>
       </c>
       <c r="M684" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N684" t="n">
-        <v>3661.88</v>
+        <v>4091.4</v>
       </c>
       <c r="O684" t="n">
-        <v>10985.64</v>
+        <v>4091.4</v>
       </c>
       <c r="P684" t="n">
-        <v>38900</v>
+        <v>10000</v>
       </c>
       <c r="Q684" t="n">
-        <v>116700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>SLT027</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>JUGUETE  DRAGON   AB-02 / 082</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -31562,7 +31562,7 @@
         </is>
       </c>
       <c r="J685" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K685" t="n">
         <v>0</v>
@@ -31571,30 +31571,30 @@
         <v>0</v>
       </c>
       <c r="M685" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N685" t="n">
-        <v>2797.08</v>
+        <v>3732.8773611111</v>
       </c>
       <c r="O685" t="n">
-        <v>13985.4</v>
+        <v>37328.773611111</v>
       </c>
       <c r="P685" t="n">
-        <v>30900</v>
+        <v>4500</v>
       </c>
       <c r="Q685" t="n">
-        <v>154500</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T040-LJ</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -31608,7 +31608,7 @@
         </is>
       </c>
       <c r="J686" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K686" t="n">
         <v>0</v>
@@ -31617,30 +31617,30 @@
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N686" t="n">
-        <v>3462.255</v>
+        <v>3661.88</v>
       </c>
       <c r="O686" t="n">
-        <v>38084.805</v>
+        <v>10985.64</v>
       </c>
       <c r="P686" t="n">
-        <v>42000</v>
+        <v>38900</v>
       </c>
       <c r="Q686" t="n">
-        <v>462000</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T041-LJ</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -31654,7 +31654,7 @@
         </is>
       </c>
       <c r="J687" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K687" t="n">
         <v>0</v>
@@ -31663,30 +31663,30 @@
         <v>0</v>
       </c>
       <c r="M687" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="N687" t="n">
-        <v>24882.58</v>
+        <v>2797.08</v>
       </c>
       <c r="O687" t="n">
-        <v>696712.24</v>
+        <v>13985.4</v>
       </c>
       <c r="P687" t="n">
-        <v>31500</v>
+        <v>30900</v>
       </c>
       <c r="Q687" t="n">
-        <v>882000</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -31700,7 +31700,7 @@
         </is>
       </c>
       <c r="J688" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K688" t="n">
         <v>0</v>
@@ -31709,35 +31709,35 @@
         <v>0</v>
       </c>
       <c r="M688" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N688" t="n">
-        <v>0.8</v>
+        <v>3462.255</v>
       </c>
       <c r="O688" t="n">
-        <v>15.2</v>
+        <v>38084.805</v>
       </c>
       <c r="P688" t="n">
-        <v>22900</v>
+        <v>42000</v>
       </c>
       <c r="Q688" t="n">
-        <v>435100</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -31746,7 +31746,7 @@
         </is>
       </c>
       <c r="J689" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K689" t="n">
         <v>0</v>
@@ -31755,35 +31755,35 @@
         <v>0</v>
       </c>
       <c r="M689" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N689" t="n">
-        <v>5186.45</v>
+        <v>24882.58</v>
       </c>
       <c r="O689" t="n">
-        <v>82983.2</v>
+        <v>696712.24</v>
       </c>
       <c r="P689" t="n">
-        <v>7200</v>
+        <v>31500</v>
       </c>
       <c r="Q689" t="n">
-        <v>115200</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>T119-LJ</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -31792,7 +31792,7 @@
         </is>
       </c>
       <c r="J690" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K690" t="n">
         <v>0</v>
@@ -31801,30 +31801,30 @@
         <v>0</v>
       </c>
       <c r="M690" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N690" t="n">
-        <v>47796.1625</v>
+        <v>0.8</v>
       </c>
       <c r="O690" t="n">
-        <v>95592.325</v>
+        <v>15.2</v>
       </c>
       <c r="P690" t="n">
-        <v>54000</v>
+        <v>22900</v>
       </c>
       <c r="Q690" t="n">
-        <v>108000</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>TB115</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -31838,7 +31838,7 @@
         </is>
       </c>
       <c r="J691" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K691" t="n">
         <v>0</v>
@@ -31847,64 +31847,156 @@
         <v>0</v>
       </c>
       <c r="M691" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="N691" t="n">
-        <v>8006.3731111111</v>
+        <v>5186.45</v>
       </c>
       <c r="O691" t="n">
-        <v>344274.0437777773</v>
+        <v>82983.2</v>
       </c>
       <c r="P691" t="n">
-        <v>10000</v>
+        <v>7200</v>
       </c>
       <c r="Q691" t="n">
-        <v>430000</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
+          <t>TB028</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J692" t="n">
+        <v>2</v>
+      </c>
+      <c r="K692" t="n">
+        <v>0</v>
+      </c>
+      <c r="L692" t="n">
+        <v>0</v>
+      </c>
+      <c r="M692" t="n">
+        <v>2</v>
+      </c>
+      <c r="N692" t="n">
+        <v>47796.1625</v>
+      </c>
+      <c r="O692" t="n">
+        <v>95592.325</v>
+      </c>
+      <c r="P692" t="n">
+        <v>54000</v>
+      </c>
+      <c r="Q692" t="n">
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>TB115</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J693" t="n">
+        <v>43</v>
+      </c>
+      <c r="K693" t="n">
+        <v>0</v>
+      </c>
+      <c r="L693" t="n">
+        <v>0</v>
+      </c>
+      <c r="M693" t="n">
+        <v>43</v>
+      </c>
+      <c r="N693" t="n">
+        <v>8006.3731111111</v>
+      </c>
+      <c r="O693" t="n">
+        <v>344274.0437777773</v>
+      </c>
+      <c r="P693" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q693" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
           <t>TB122</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
-      <c r="E692" t="inlineStr">
+      <c r="E694" t="inlineStr">
         <is>
           <t>PELUCHES</t>
         </is>
       </c>
-      <c r="I692" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J692" t="n">
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J694" t="n">
         <v>4</v>
       </c>
-      <c r="K692" t="n">
-        <v>0</v>
-      </c>
-      <c r="L692" t="n">
-        <v>0</v>
-      </c>
-      <c r="M692" t="n">
+      <c r="K694" t="n">
+        <v>0</v>
+      </c>
+      <c r="L694" t="n">
+        <v>0</v>
+      </c>
+      <c r="M694" t="n">
         <v>4</v>
       </c>
-      <c r="N692" t="n">
+      <c r="N694" t="n">
         <v>47920</v>
       </c>
-      <c r="O692" t="n">
+      <c r="O694" t="n">
         <v>191680</v>
       </c>
-      <c r="P692" t="n">
+      <c r="P694" t="n">
         <v>59900</v>
       </c>
-      <c r="Q692" t="n">
+      <c r="Q694" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3059701493</v>
+        <v>1811.3062015504</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3059701493</v>
+        <v>1811.3062015504</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464843537</v>
+        <v>3376.7464728365</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.892168671</v>
+        <v>2985043.881987466</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -831,10 +831,10 @@
         <v>55</v>
       </c>
       <c r="N11" t="n">
-        <v>5758.9597782705</v>
+        <v>5758.9597777778</v>
       </c>
       <c r="O11" t="n">
-        <v>316742.7878048775</v>
+        <v>316742.787777779</v>
       </c>
       <c r="P11" t="n">
         <v>16900</v>
@@ -1663,10 +1663,10 @@
         <v>23</v>
       </c>
       <c r="N32" t="n">
-        <v>14857.623214286</v>
+        <v>14857.623243243</v>
       </c>
       <c r="O32" t="n">
-        <v>341725.333928578</v>
+        <v>341725.334594589</v>
       </c>
       <c r="P32" t="n">
         <v>34900</v>
@@ -1836,10 +1836,10 @@
         <v>24</v>
       </c>
       <c r="N36" t="n">
-        <v>16486.408923077</v>
+        <v>16614.210542636</v>
       </c>
       <c r="O36" t="n">
-        <v>395673.814153848</v>
+        <v>398741.053023264</v>
       </c>
       <c r="P36" t="n">
         <v>30500</v>
@@ -1878,10 +1878,10 @@
         <v>18</v>
       </c>
       <c r="N37" t="n">
-        <v>15711.966008403</v>
+        <v>15711.965957447</v>
       </c>
       <c r="O37" t="n">
-        <v>282815.388151254</v>
+        <v>282815.387234046</v>
       </c>
       <c r="P37" t="n">
         <v>28500</v>
@@ -2128,10 +2128,10 @@
         <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>56906.802982456</v>
+        <v>56906.803962264</v>
       </c>
       <c r="O43" t="n">
-        <v>455254.423859648</v>
+        <v>455254.431698112</v>
       </c>
       <c r="P43" t="n">
         <v>95900</v>
@@ -3349,10 +3349,10 @@
         <v>1295</v>
       </c>
       <c r="N71" t="n">
-        <v>1098.0580436917</v>
+        <v>1098.0583408184</v>
       </c>
       <c r="O71" t="n">
-        <v>1421985.166580752</v>
+        <v>1421985.551359828</v>
       </c>
       <c r="P71" t="n">
         <v>1500</v>
@@ -3920,22 +3920,22 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M84" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="N84" t="n">
         <v>18694.410088692</v>
       </c>
       <c r="O84" t="n">
-        <v>1757274.548337048</v>
+        <v>1570330.447450128</v>
       </c>
       <c r="P84" t="n">
         <v>29900</v>
       </c>
       <c r="Q84" t="n">
-        <v>2810600</v>
+        <v>2511600</v>
       </c>
     </row>
     <row r="85">
@@ -4276,22 +4276,22 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M92" t="n">
-        <v>771</v>
+        <v>741</v>
       </c>
       <c r="N92" t="n">
-        <v>2582.2558569052</v>
+        <v>2582.2558256496</v>
       </c>
       <c r="O92" t="n">
-        <v>1990919.265673909</v>
+        <v>1913451.566806354</v>
       </c>
       <c r="P92" t="n">
         <v>4500</v>
       </c>
       <c r="Q92" t="n">
-        <v>3469500</v>
+        <v>3334500</v>
       </c>
     </row>
     <row r="93">
@@ -4374,10 +4374,10 @@
         <v>720</v>
       </c>
       <c r="N94" t="n">
-        <v>5216.8961652752</v>
+        <v>5216.8961603854</v>
       </c>
       <c r="O94" t="n">
-        <v>3756165.238998143</v>
+        <v>3756165.235477488</v>
       </c>
       <c r="P94" t="n">
         <v>8500</v>
@@ -4605,10 +4605,10 @@
         <v>3199</v>
       </c>
       <c r="N99" t="n">
-        <v>3158.8608249792</v>
+        <v>3158.860825504</v>
       </c>
       <c r="O99" t="n">
-        <v>10105195.77910846</v>
+        <v>10105195.78078729</v>
       </c>
       <c r="P99" t="n">
         <v>5600</v>
@@ -4651,10 +4651,10 @@
         <v>80</v>
       </c>
       <c r="N100" t="n">
-        <v>3841.6247787611</v>
+        <v>3841.6247928994</v>
       </c>
       <c r="O100" t="n">
-        <v>307329.982300888</v>
+        <v>307329.983431952</v>
       </c>
       <c r="P100" t="n">
         <v>6900</v>
@@ -4735,22 +4735,22 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M102" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="N102" t="n">
-        <v>3230.0674157303</v>
+        <v>3230.0673863636</v>
       </c>
       <c r="O102" t="n">
-        <v>581412.134831454</v>
+        <v>503890.5122727216</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
       </c>
       <c r="Q102" t="n">
-        <v>1116000</v>
+        <v>967200</v>
       </c>
     </row>
     <row r="103">
@@ -4880,10 +4880,10 @@
         <v>259</v>
       </c>
       <c r="N105" t="n">
-        <v>2694.823243369</v>
+        <v>2694.8232244517</v>
       </c>
       <c r="O105" t="n">
-        <v>697959.220032571</v>
+        <v>697959.2151329903</v>
       </c>
       <c r="P105" t="n">
         <v>4900</v>
@@ -5200,10 +5200,10 @@
         <v>593</v>
       </c>
       <c r="N112" t="n">
-        <v>3795.7100071073</v>
+        <v>3795.7100075415</v>
       </c>
       <c r="O112" t="n">
-        <v>2250856.034214629</v>
+        <v>2250856.03447211</v>
       </c>
       <c r="P112" t="n">
         <v>6200</v>
@@ -5425,10 +5425,10 @@
         <v>312</v>
       </c>
       <c r="N117" t="n">
-        <v>4890.9300481348</v>
+        <v>4914.5862998791</v>
       </c>
       <c r="O117" t="n">
-        <v>1525970.175018058</v>
+        <v>1533350.925562279</v>
       </c>
       <c r="P117" t="n">
         <v>8200</v>
@@ -5650,10 +5650,10 @@
         <v>614</v>
       </c>
       <c r="N122" t="n">
-        <v>7041</v>
+        <v>7095.9541463415</v>
       </c>
       <c r="O122" t="n">
-        <v>4323174</v>
+        <v>4356915.845853681</v>
       </c>
       <c r="P122" t="n">
         <v>11500</v>
@@ -5742,10 +5742,10 @@
         <v>246</v>
       </c>
       <c r="N124" t="n">
-        <v>8012</v>
+        <v>8088.1838351823</v>
       </c>
       <c r="O124" t="n">
-        <v>1970952</v>
+        <v>1989693.223454846</v>
       </c>
       <c r="P124" t="n">
         <v>13200</v>
@@ -5924,10 +5924,10 @@
         <v>288</v>
       </c>
       <c r="N128" t="n">
-        <v>3594.2540740741</v>
+        <v>3594.2540520446</v>
       </c>
       <c r="O128" t="n">
-        <v>1035145.173333341</v>
+        <v>1035145.166988845</v>
       </c>
       <c r="P128" t="n">
         <v>6500</v>
@@ -6057,10 +6057,10 @@
         <v>123</v>
       </c>
       <c r="N131" t="n">
-        <v>4891</v>
+        <v>4913.5912240185</v>
       </c>
       <c r="O131" t="n">
-        <v>601593</v>
+        <v>604371.7205542754</v>
       </c>
       <c r="P131" t="n">
         <v>8200</v>
@@ -6552,22 +6552,22 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M142" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="N142" t="n">
-        <v>12267.650113636</v>
+        <v>12267.649642857</v>
       </c>
       <c r="O142" t="n">
-        <v>502973.654659076</v>
+        <v>392564.788571424</v>
       </c>
       <c r="P142" t="n">
         <v>19900</v>
       </c>
       <c r="Q142" t="n">
-        <v>815900</v>
+        <v>636800</v>
       </c>
     </row>
     <row r="143">
@@ -7002,10 +7002,10 @@
         <v>1945</v>
       </c>
       <c r="N152" t="n">
-        <v>4372.2107886682</v>
+        <v>4374.7024319704</v>
       </c>
       <c r="O152" t="n">
-        <v>8503949.983959649</v>
+        <v>8508796.230182428</v>
       </c>
       <c r="P152" t="n">
         <v>7500</v>
@@ -7086,22 +7086,22 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M154" t="n">
-        <v>480</v>
+        <v>306</v>
       </c>
       <c r="N154" t="n">
-        <v>1592.5669608416</v>
+        <v>1592.5669555035</v>
       </c>
       <c r="O154" t="n">
-        <v>764432.141203968</v>
+        <v>487325.488384071</v>
       </c>
       <c r="P154" t="n">
         <v>3900</v>
       </c>
       <c r="Q154" t="n">
-        <v>1872000</v>
+        <v>1193400</v>
       </c>
     </row>
     <row r="155">
@@ -8032,22 +8032,22 @@
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M175" t="n">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="N175" t="n">
         <v>4635.49</v>
       </c>
       <c r="O175" t="n">
-        <v>922462.51</v>
+        <v>505268.41</v>
       </c>
       <c r="P175" t="n">
         <v>7500</v>
       </c>
       <c r="Q175" t="n">
-        <v>1492500</v>
+        <v>817500</v>
       </c>
     </row>
     <row r="176">
@@ -8360,22 +8360,22 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M182" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="N182" t="n">
-        <v>3761.6</v>
+        <v>3788.0590855803</v>
       </c>
       <c r="O182" t="n">
-        <v>319736</v>
+        <v>231071.6042203983</v>
       </c>
       <c r="P182" t="n">
         <v>6900</v>
       </c>
       <c r="Q182" t="n">
-        <v>586500</v>
+        <v>420900</v>
       </c>
     </row>
     <row r="183">
@@ -8877,22 +8877,22 @@
         <v>0</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M193" t="n">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="N193" t="n">
-        <v>1630.9234624043</v>
+        <v>1630.9234875283</v>
       </c>
       <c r="O193" t="n">
-        <v>1265596.606825737</v>
+        <v>1239501.850521508</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
       </c>
       <c r="Q193" t="n">
-        <v>1940000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="194">
@@ -8975,10 +8975,10 @@
         <v>288</v>
       </c>
       <c r="N195" t="n">
-        <v>1690.5992886179</v>
+        <v>1690.5983498584</v>
       </c>
       <c r="O195" t="n">
-        <v>486892.5951219551</v>
+        <v>486892.3247592192</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9015,22 +9015,22 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M196" t="n">
-        <v>2022</v>
+        <v>1942</v>
       </c>
       <c r="N196" t="n">
-        <v>1550.1935205388</v>
+        <v>1550.1935332762</v>
       </c>
       <c r="O196" t="n">
-        <v>3134491.298529454</v>
+        <v>3010475.841622381</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
       </c>
       <c r="Q196" t="n">
-        <v>5055000</v>
+        <v>4855000</v>
       </c>
     </row>
     <row r="197">
@@ -9067,10 +9067,10 @@
         <v>22</v>
       </c>
       <c r="N197" t="n">
-        <v>1579.3907948718</v>
+        <v>1579.3907235142</v>
       </c>
       <c r="O197" t="n">
-        <v>34746.5974871796</v>
+        <v>34746.5959173124</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9113,10 +9113,10 @@
         <v>418</v>
       </c>
       <c r="N198" t="n">
-        <v>2403.5114869613</v>
+        <v>2403.5115510508</v>
       </c>
       <c r="O198" t="n">
-        <v>1004667.801549823</v>
+        <v>1004667.828339234</v>
       </c>
       <c r="P198" t="n">
         <v>3500</v>
@@ -10284,10 +10284,10 @@
         <v>79</v>
       </c>
       <c r="N224" t="n">
-        <v>5162.2539766082</v>
+        <v>5162.2539411765</v>
       </c>
       <c r="O224" t="n">
-        <v>407818.0641520478</v>
+        <v>407818.0613529435</v>
       </c>
       <c r="P224" t="n">
         <v>8200</v>
@@ -11196,10 +11196,10 @@
         <v>125</v>
       </c>
       <c r="N245" t="n">
-        <v>4285.1954215582</v>
+        <v>4285.1954682454</v>
       </c>
       <c r="O245" t="n">
-        <v>535649.427694775</v>
+        <v>535649.433530675</v>
       </c>
       <c r="P245" t="n">
         <v>6900</v>
@@ -11455,10 +11455,10 @@
         <v>563</v>
       </c>
       <c r="N251" t="n">
-        <v>4605.2146660482</v>
+        <v>4657.0557317073</v>
       </c>
       <c r="O251" t="n">
-        <v>2592735.856985137</v>
+        <v>2621922.37695121</v>
       </c>
       <c r="P251" t="n">
         <v>7600</v>
@@ -11496,10 +11496,10 @@
         <v>921</v>
       </c>
       <c r="N252" t="n">
-        <v>3591.13</v>
+        <v>3598.612819934</v>
       </c>
       <c r="O252" t="n">
-        <v>3307430.73</v>
+        <v>3314322.407159214</v>
       </c>
       <c r="P252" t="n">
         <v>6300</v>
@@ -12038,10 +12038,10 @@
         <v>599</v>
       </c>
       <c r="N264" t="n">
-        <v>1561.0000887728</v>
+        <v>1561.000152391</v>
       </c>
       <c r="O264" t="n">
-        <v>935039.0531749071</v>
+        <v>935039.091282209</v>
       </c>
       <c r="P264" t="n">
         <v>2900</v>
@@ -12361,10 +12361,10 @@
         <v>306</v>
       </c>
       <c r="N271" t="n">
-        <v>548.14724170616</v>
+        <v>548.14722592946</v>
       </c>
       <c r="O271" t="n">
-        <v>167733.055962085</v>
+        <v>167733.0511344148</v>
       </c>
       <c r="P271" t="n">
         <v>2000</v>
@@ -12591,22 +12591,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M276" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N276" t="n">
         <v>6232.24</v>
       </c>
       <c r="O276" t="n">
-        <v>149573.76</v>
+        <v>43625.68</v>
       </c>
       <c r="P276" t="n">
         <v>7900</v>
       </c>
       <c r="Q276" t="n">
-        <v>189600</v>
+        <v>55300</v>
       </c>
     </row>
     <row r="277">
@@ -13247,10 +13247,10 @@
         <v>81</v>
       </c>
       <c r="N290" t="n">
-        <v>5218.1705412054</v>
+        <v>5218.1705479452</v>
       </c>
       <c r="O290" t="n">
-        <v>422671.8138376374</v>
+        <v>422671.8143835612</v>
       </c>
       <c r="P290" t="n">
         <v>8500</v>
@@ -13293,10 +13293,10 @@
         <v>1</v>
       </c>
       <c r="N291" t="n">
-        <v>1595.0093958665</v>
+        <v>1595.0093800979</v>
       </c>
       <c r="O291" t="n">
-        <v>1595.0093958665</v>
+        <v>1595.0093800979</v>
       </c>
       <c r="P291" t="n">
         <v>2600</v>
@@ -14035,10 +14035,10 @@
         <v>824</v>
       </c>
       <c r="N307" t="n">
-        <v>1778.4725978277</v>
+        <v>1778.4726172988</v>
       </c>
       <c r="O307" t="n">
-        <v>1465461.420610025</v>
+        <v>1465461.436654211</v>
       </c>
       <c r="P307" t="n">
         <v>4900</v>
@@ -16019,10 +16019,10 @@
         <v>5</v>
       </c>
       <c r="N350" t="n">
-        <v>2252.2966541823</v>
+        <v>2252.2966708385</v>
       </c>
       <c r="O350" t="n">
-        <v>11261.4832709115</v>
+        <v>11261.4833541925</v>
       </c>
       <c r="P350" t="n">
         <v>3900</v>
@@ -16345,10 +16345,10 @@
         <v>324</v>
       </c>
       <c r="N357" t="n">
-        <v>2328.1187258454</v>
+        <v>2328.1187254606</v>
       </c>
       <c r="O357" t="n">
-        <v>754310.4671739097</v>
+        <v>754310.4670492344</v>
       </c>
       <c r="P357" t="n">
         <v>4500</v>
@@ -17121,22 +17121,22 @@
         <v>0</v>
       </c>
       <c r="L374" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M374" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N374" t="n">
         <v>76839</v>
       </c>
       <c r="O374" t="n">
-        <v>614712</v>
+        <v>153678</v>
       </c>
       <c r="P374" t="n">
         <v>122900</v>
       </c>
       <c r="Q374" t="n">
-        <v>983200</v>
+        <v>245800</v>
       </c>
     </row>
     <row r="375">
@@ -17219,10 +17219,10 @@
         <v>289</v>
       </c>
       <c r="N376" t="n">
-        <v>3903.7364457831</v>
+        <v>3903.7364581763</v>
       </c>
       <c r="O376" t="n">
-        <v>1128179.832831316</v>
+        <v>1128179.836412951</v>
       </c>
       <c r="P376" t="n">
         <v>7500</v>
@@ -17444,10 +17444,10 @@
         <v>48</v>
       </c>
       <c r="N381" t="n">
-        <v>5869.1726950355</v>
+        <v>5869.172680203</v>
       </c>
       <c r="O381" t="n">
-        <v>281720.289361704</v>
+        <v>281720.288649744</v>
       </c>
       <c r="P381" t="n">
         <v>9500</v>
@@ -17628,10 +17628,10 @@
         <v>44</v>
       </c>
       <c r="N385" t="n">
-        <v>6645</v>
+        <v>6666.7987971569</v>
       </c>
       <c r="O385" t="n">
-        <v>292380</v>
+        <v>293339.1470749036</v>
       </c>
       <c r="P385" t="n">
         <v>10900</v>
@@ -19558,10 +19558,10 @@
         <v>120</v>
       </c>
       <c r="N427" t="n">
-        <v>2458.5132504039</v>
+        <v>2477.7391560769</v>
       </c>
       <c r="O427" t="n">
-        <v>295021.590048468</v>
+        <v>297328.698729228</v>
       </c>
       <c r="P427" t="n">
         <v>3500</v>
@@ -19604,10 +19604,10 @@
         <v>192</v>
       </c>
       <c r="N428" t="n">
-        <v>1771.0905981795</v>
+        <v>1799.166010568</v>
       </c>
       <c r="O428" t="n">
-        <v>340049.394850464</v>
+        <v>345439.874029056</v>
       </c>
       <c r="P428" t="n">
         <v>2500</v>
@@ -19650,10 +19650,10 @@
         <v>264</v>
       </c>
       <c r="N429" t="n">
-        <v>2079.3840473807</v>
+        <v>2079.3840374332</v>
       </c>
       <c r="O429" t="n">
-        <v>548957.3885085048</v>
+        <v>548957.3858823648</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
@@ -19696,10 +19696,10 @@
         <v>72</v>
       </c>
       <c r="N430" t="n">
-        <v>1803.0155591997</v>
+        <v>1817.3204760331</v>
       </c>
       <c r="O430" t="n">
-        <v>129817.1202623784</v>
+        <v>130847.0742743832</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -19742,10 +19742,10 @@
         <v>216</v>
       </c>
       <c r="N431" t="n">
-        <v>3306.5951935915</v>
+        <v>3306.5951807229</v>
       </c>
       <c r="O431" t="n">
-        <v>714224.5618157641</v>
+        <v>714224.5590361464</v>
       </c>
       <c r="P431" t="n">
         <v>4900</v>
@@ -19788,10 +19788,10 @@
         <v>192</v>
       </c>
       <c r="N432" t="n">
-        <v>2122.1639198011</v>
+        <v>2138.1701634192</v>
       </c>
       <c r="O432" t="n">
-        <v>407455.4726018112</v>
+        <v>410528.6713764864</v>
       </c>
       <c r="P432" t="n">
         <v>2900</v>
@@ -19834,10 +19834,10 @@
         <v>120</v>
       </c>
       <c r="N433" t="n">
-        <v>2108.7914267016</v>
+        <v>2142.8043145161</v>
       </c>
       <c r="O433" t="n">
-        <v>253054.971204192</v>
+        <v>257136.517741932</v>
       </c>
       <c r="P433" t="n">
         <v>2900</v>
@@ -19880,10 +19880,10 @@
         <v>144</v>
       </c>
       <c r="N434" t="n">
-        <v>2056.0834183673</v>
+        <v>2056.0833654773</v>
       </c>
       <c r="O434" t="n">
-        <v>296076.0122448912</v>
+        <v>296076.0046287312</v>
       </c>
       <c r="P434" t="n">
         <v>2900</v>
@@ -19926,10 +19926,10 @@
         <v>216</v>
       </c>
       <c r="N435" t="n">
-        <v>3224.5685238095</v>
+        <v>3224.5685400763</v>
       </c>
       <c r="O435" t="n">
-        <v>696506.8011428521</v>
+        <v>696506.8046564808</v>
       </c>
       <c r="P435" t="n">
         <v>4500</v>
@@ -19972,10 +19972,10 @@
         <v>360</v>
       </c>
       <c r="N436" t="n">
-        <v>1655.9309666884</v>
+        <v>1669.0127123107</v>
       </c>
       <c r="O436" t="n">
-        <v>596135.1480078241</v>
+        <v>600844.576431852</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -20012,22 +20012,22 @@
         <v>0</v>
       </c>
       <c r="L437" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M437" t="n">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="N437" t="n">
         <v>1871</v>
       </c>
       <c r="O437" t="n">
-        <v>538848</v>
+        <v>493944</v>
       </c>
       <c r="P437" t="n">
         <v>3900</v>
       </c>
       <c r="Q437" t="n">
-        <v>1123200</v>
+        <v>1029600</v>
       </c>
     </row>
     <row r="438">
@@ -20104,22 +20104,22 @@
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M439" t="n">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="N439" t="n">
         <v>2003</v>
       </c>
       <c r="O439" t="n">
-        <v>897344</v>
+        <v>833248</v>
       </c>
       <c r="P439" t="n">
         <v>3900</v>
       </c>
       <c r="Q439" t="n">
-        <v>1747200</v>
+        <v>1622400</v>
       </c>
     </row>
     <row r="440">
@@ -20196,22 +20196,22 @@
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M441" t="n">
-        <v>384</v>
+        <v>304</v>
       </c>
       <c r="N441" t="n">
-        <v>1592.2773416667</v>
+        <v>1592.2776475694</v>
       </c>
       <c r="O441" t="n">
-        <v>611434.4992000128</v>
+        <v>484052.4048610976</v>
       </c>
       <c r="P441" t="n">
         <v>2500</v>
       </c>
       <c r="Q441" t="n">
-        <v>960000</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="442">
@@ -20373,22 +20373,22 @@
         <v>0</v>
       </c>
       <c r="L445" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M445" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N445" t="n">
-        <v>1668.628045977</v>
+        <v>1668.6281268012</v>
       </c>
       <c r="O445" t="n">
-        <v>40047.073103448</v>
+        <v>0</v>
       </c>
       <c r="P445" t="n">
         <v>2500</v>
       </c>
       <c r="Q445" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -20425,10 +20425,10 @@
         <v>24</v>
       </c>
       <c r="N446" t="n">
-        <v>2546.9843873518</v>
+        <v>2609.1059349593</v>
       </c>
       <c r="O446" t="n">
-        <v>61127.62529644319</v>
+        <v>62618.54243902321</v>
       </c>
       <c r="P446" t="n">
         <v>3900</v>
@@ -20471,10 +20471,10 @@
         <v>800</v>
       </c>
       <c r="N447" t="n">
-        <v>1259.2745258911</v>
+        <v>1264.6608869878</v>
       </c>
       <c r="O447" t="n">
-        <v>1007419.62071288</v>
+        <v>1011728.70959024</v>
       </c>
       <c r="P447" t="n">
         <v>1900</v>
@@ -20598,22 +20598,22 @@
         <v>0</v>
       </c>
       <c r="L450" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M450" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="N450" t="n">
         <v>2556.7459385666</v>
       </c>
       <c r="O450" t="n">
-        <v>184085.7075767952</v>
+        <v>122723.8050511968</v>
       </c>
       <c r="P450" t="n">
         <v>3900</v>
       </c>
       <c r="Q450" t="n">
-        <v>280800</v>
+        <v>187200</v>
       </c>
     </row>
     <row r="451">
@@ -21850,10 +21850,10 @@
         <v>306</v>
       </c>
       <c r="N477" t="n">
-        <v>1690.8700090909</v>
+        <v>1690.870009095</v>
       </c>
       <c r="O477" t="n">
-        <v>517406.2227818154</v>
+        <v>517406.2227830699</v>
       </c>
       <c r="P477" t="n">
         <v>3000</v>
@@ -22183,10 +22183,10 @@
         <v>140</v>
       </c>
       <c r="N484" t="n">
-        <v>3907.5003292181</v>
+        <v>3907.5003305785</v>
       </c>
       <c r="O484" t="n">
-        <v>547050.046090534</v>
+        <v>547050.04628099</v>
       </c>
       <c r="P484" t="n">
         <v>3900</v>
@@ -22693,10 +22693,10 @@
         <v>461</v>
       </c>
       <c r="N495" t="n">
-        <v>517.28908220781</v>
+        <v>517.28922545101</v>
       </c>
       <c r="O495" t="n">
-        <v>238470.2668978004</v>
+        <v>238470.3329329156</v>
       </c>
       <c r="P495" t="n">
         <v>900</v>
@@ -23061,22 +23061,22 @@
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M503" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N503" t="n">
         <v>3259.1342692308</v>
       </c>
       <c r="O503" t="n">
-        <v>107551.4308846164</v>
+        <v>84737.49100000079</v>
       </c>
       <c r="P503" t="n">
         <v>3600</v>
       </c>
       <c r="Q503" t="n">
-        <v>118800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="504">
@@ -23116,10 +23116,10 @@
         <v>757</v>
       </c>
       <c r="N504" t="n">
-        <v>3110.842321894</v>
+        <v>3110.8421999117</v>
       </c>
       <c r="O504" t="n">
-        <v>2354907.637673758</v>
+        <v>2354907.545333157</v>
       </c>
       <c r="P504" t="n">
         <v>4500</v>
@@ -23567,10 +23567,10 @@
         <v>19802</v>
       </c>
       <c r="N514" t="n">
-        <v>703.79521051815</v>
+        <v>703.79520622865</v>
       </c>
       <c r="O514" t="n">
-        <v>13936552.75868041</v>
+        <v>13936552.67373973</v>
       </c>
       <c r="P514" t="n">
         <v>900</v>
@@ -23708,10 +23708,10 @@
         <v>78</v>
       </c>
       <c r="N517" t="n">
-        <v>2501.385</v>
+        <v>2501.3849767442</v>
       </c>
       <c r="O517" t="n">
-        <v>195108.03</v>
+        <v>195108.0281860476</v>
       </c>
       <c r="P517" t="n">
         <v>4100</v>
@@ -23838,22 +23838,22 @@
         <v>0</v>
       </c>
       <c r="L520" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M520" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="N520" t="n">
         <v>2400</v>
       </c>
       <c r="O520" t="n">
-        <v>112800</v>
+        <v>84000</v>
       </c>
       <c r="P520" t="n">
         <v>3000</v>
       </c>
       <c r="Q520" t="n">
-        <v>141000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="521">
@@ -24074,10 +24074,10 @@
         <v>47</v>
       </c>
       <c r="N525" t="n">
-        <v>1595.513125523</v>
+        <v>1595.5130117944</v>
       </c>
       <c r="O525" t="n">
-        <v>74989.116899581</v>
+        <v>74989.11155433679</v>
       </c>
       <c r="P525" t="n">
         <v>2500</v>
@@ -24463,10 +24463,10 @@
         <v>159</v>
       </c>
       <c r="N533" t="n">
-        <v>2098.4049570201</v>
+        <v>2098.4049712644</v>
       </c>
       <c r="O533" t="n">
-        <v>333646.3881661959</v>
+        <v>333646.3904310396</v>
       </c>
       <c r="P533" t="n">
         <v>9500</v>
@@ -25233,10 +25233,10 @@
         <v>18</v>
       </c>
       <c r="N549" t="n">
-        <v>23475.658</v>
+        <v>23475.657857143</v>
       </c>
       <c r="O549" t="n">
-        <v>422561.844</v>
+        <v>422561.841428574</v>
       </c>
       <c r="P549" t="n">
         <v>31900</v>
@@ -25472,22 +25472,22 @@
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M554" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N554" t="n">
         <v>4795.69</v>
       </c>
       <c r="O554" t="n">
-        <v>1184535.43</v>
+        <v>1160556.98</v>
       </c>
       <c r="P554" t="n">
         <v>10200</v>
       </c>
       <c r="Q554" t="n">
-        <v>2519400</v>
+        <v>2468400</v>
       </c>
     </row>
     <row r="555">
@@ -25622,10 +25622,10 @@
         <v>165</v>
       </c>
       <c r="N557" t="n">
-        <v>875.69016</v>
+        <v>875.69016806723</v>
       </c>
       <c r="O557" t="n">
-        <v>144488.8764</v>
+        <v>144488.8777310929</v>
       </c>
       <c r="P557" t="n">
         <v>4500</v>
@@ -25949,10 +25949,10 @@
         <v>312</v>
       </c>
       <c r="N564" t="n">
-        <v>3414.5660775194</v>
+        <v>3414.5660744763</v>
       </c>
       <c r="O564" t="n">
-        <v>1065344.616186053</v>
+        <v>1065344.615236606</v>
       </c>
       <c r="P564" t="n">
         <v>3500</v>
@@ -29222,22 +29222,22 @@
         <v>0</v>
       </c>
       <c r="L634" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M634" t="n">
-        <v>1346</v>
+        <v>1298</v>
       </c>
       <c r="N634" t="n">
-        <v>1176.57</v>
+        <v>1179.3131202642</v>
       </c>
       <c r="O634" t="n">
-        <v>1583663.22</v>
+        <v>1530748.430102932</v>
       </c>
       <c r="P634" t="n">
         <v>1900</v>
       </c>
       <c r="Q634" t="n">
-        <v>2557400</v>
+        <v>2466200</v>
       </c>
     </row>
     <row r="635">
@@ -29762,10 +29762,10 @@
         <v>352</v>
       </c>
       <c r="N646" t="n">
-        <v>22951.704904943</v>
+        <v>22951.7048659</v>
       </c>
       <c r="O646" t="n">
-        <v>8079000.126539935</v>
+        <v>8079000.1127968</v>
       </c>
       <c r="P646" t="n">
         <v>37900</v>
@@ -29808,10 +29808,10 @@
         <v>172</v>
       </c>
       <c r="N647" t="n">
-        <v>705.52800453515</v>
+        <v>705.5279984837</v>
       </c>
       <c r="O647" t="n">
-        <v>121350.8167800458</v>
+        <v>121350.8157391964</v>
       </c>
       <c r="P647" t="n">
         <v>1500</v>
@@ -31249,10 +31249,10 @@
         <v>95</v>
       </c>
       <c r="N678" t="n">
-        <v>3306.00983</v>
+        <v>3306.00915</v>
       </c>
       <c r="O678" t="n">
-        <v>314070.93385</v>
+        <v>314070.86925</v>
       </c>
       <c r="P678" t="n">
         <v>4200</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q691"/>
+  <dimension ref="A1:Q693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3062015504</v>
+        <v>1811.3067953668</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3062015504</v>
+        <v>1811.3067953668</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1429,10 +1429,10 @@
         <v>120</v>
       </c>
       <c r="N26" t="n">
-        <v>3716.3301935484</v>
+        <v>3716.3301938611</v>
       </c>
       <c r="O26" t="n">
-        <v>445959.623225808</v>
+        <v>445959.623263332</v>
       </c>
       <c r="P26" t="n">
         <v>9500</v>
@@ -2211,22 +2211,22 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
         <v>200072.20057377</v>
       </c>
       <c r="O45" t="n">
-        <v>1400505.40401639</v>
+        <v>1000361.00286885</v>
       </c>
       <c r="P45" t="n">
         <v>312000</v>
       </c>
       <c r="Q45" t="n">
-        <v>2184000</v>
+        <v>1560000</v>
       </c>
     </row>
     <row r="46">
@@ -3349,10 +3349,10 @@
         <v>1295</v>
       </c>
       <c r="N71" t="n">
-        <v>1098.0583408184</v>
+        <v>1098.0591631908</v>
       </c>
       <c r="O71" t="n">
-        <v>1421985.551359828</v>
+        <v>1421986.616332086</v>
       </c>
       <c r="P71" t="n">
         <v>1500</v>
@@ -4230,22 +4230,22 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M91" t="n">
-        <v>1968</v>
+        <v>1964</v>
       </c>
       <c r="N91" t="n">
         <v>3247</v>
       </c>
       <c r="O91" t="n">
-        <v>6390096</v>
+        <v>6377108</v>
       </c>
       <c r="P91" t="n">
         <v>5200</v>
       </c>
       <c r="Q91" t="n">
-        <v>10233600</v>
+        <v>10212800</v>
       </c>
     </row>
     <row r="92">
@@ -4282,10 +4282,10 @@
         <v>741</v>
       </c>
       <c r="N92" t="n">
-        <v>2582.2558256496</v>
+        <v>2582.2557662062</v>
       </c>
       <c r="O92" t="n">
-        <v>1913451.566806354</v>
+        <v>1913451.522758794</v>
       </c>
       <c r="P92" t="n">
         <v>4500</v>
@@ -4374,10 +4374,10 @@
         <v>720</v>
       </c>
       <c r="N94" t="n">
-        <v>5216.8961603854</v>
+        <v>5216.8961467368</v>
       </c>
       <c r="O94" t="n">
-        <v>3756165.235477488</v>
+        <v>3756165.225650496</v>
       </c>
       <c r="P94" t="n">
         <v>8500</v>
@@ -4741,10 +4741,10 @@
         <v>156</v>
       </c>
       <c r="N102" t="n">
-        <v>3230.0673863636</v>
+        <v>3230.0673814042</v>
       </c>
       <c r="O102" t="n">
-        <v>503890.5122727216</v>
+        <v>503890.5114990553</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -5425,10 +5425,10 @@
         <v>312</v>
       </c>
       <c r="N117" t="n">
-        <v>4890.9300483676</v>
+        <v>4890.9300485437</v>
       </c>
       <c r="O117" t="n">
-        <v>1525970.175090691</v>
+        <v>1525970.175145634</v>
       </c>
       <c r="P117" t="n">
         <v>8200</v>
@@ -5465,22 +5465,22 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M118" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N118" t="n">
         <v>5613.75</v>
       </c>
       <c r="O118" t="n">
-        <v>342438.75</v>
+        <v>308756.25</v>
       </c>
       <c r="P118" t="n">
         <v>7900</v>
       </c>
       <c r="Q118" t="n">
-        <v>481900</v>
+        <v>434500</v>
       </c>
     </row>
     <row r="119">
@@ -5644,22 +5644,22 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M122" t="n">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="N122" t="n">
         <v>7041</v>
       </c>
       <c r="O122" t="n">
-        <v>4323174</v>
+        <v>4309092</v>
       </c>
       <c r="P122" t="n">
         <v>11500</v>
       </c>
       <c r="Q122" t="n">
-        <v>7061000</v>
+        <v>7038000</v>
       </c>
     </row>
     <row r="123">
@@ -5690,22 +5690,22 @@
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="N123" t="n">
         <v>5667.94</v>
       </c>
       <c r="O123" t="n">
-        <v>5480897.98</v>
+        <v>5469562.1</v>
       </c>
       <c r="P123" t="n">
         <v>9500</v>
       </c>
       <c r="Q123" t="n">
-        <v>9186500</v>
+        <v>9167500</v>
       </c>
     </row>
     <row r="124">
@@ -5736,22 +5736,22 @@
         <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M124" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N124" t="n">
         <v>8012</v>
       </c>
       <c r="O124" t="n">
-        <v>1970952</v>
+        <v>1954928</v>
       </c>
       <c r="P124" t="n">
         <v>13200</v>
       </c>
       <c r="Q124" t="n">
-        <v>3247200</v>
+        <v>3220800</v>
       </c>
     </row>
     <row r="125">
@@ -5924,10 +5924,10 @@
         <v>288</v>
       </c>
       <c r="N128" t="n">
-        <v>3594.2540520446</v>
+        <v>3594.2540372671</v>
       </c>
       <c r="O128" t="n">
-        <v>1035145.166988845</v>
+        <v>1035145.162732925</v>
       </c>
       <c r="P128" t="n">
         <v>6500</v>
@@ -5965,10 +5965,10 @@
         <v>108</v>
       </c>
       <c r="N129" t="n">
-        <v>3240.8500314961</v>
+        <v>3240.850031746</v>
       </c>
       <c r="O129" t="n">
-        <v>350011.8034015788</v>
+        <v>350011.803428568</v>
       </c>
       <c r="P129" t="n">
         <v>5200</v>
@@ -6051,22 +6051,22 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M131" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N131" t="n">
         <v>4891</v>
       </c>
       <c r="O131" t="n">
-        <v>601593</v>
+        <v>591811</v>
       </c>
       <c r="P131" t="n">
         <v>8200</v>
       </c>
       <c r="Q131" t="n">
-        <v>1008600</v>
+        <v>992200</v>
       </c>
     </row>
     <row r="132">
@@ -6149,10 +6149,10 @@
         <v>305</v>
       </c>
       <c r="N133" t="n">
-        <v>14822.378854415</v>
+        <v>14822.378852361</v>
       </c>
       <c r="O133" t="n">
-        <v>4520825.550596574</v>
+        <v>4520825.549970105</v>
       </c>
       <c r="P133" t="n">
         <v>24900</v>
@@ -6558,10 +6558,10 @@
         <v>32</v>
       </c>
       <c r="N142" t="n">
-        <v>12267.649642857</v>
+        <v>12267.648987342</v>
       </c>
       <c r="O142" t="n">
-        <v>392564.788571424</v>
+        <v>392564.767594944</v>
       </c>
       <c r="P142" t="n">
         <v>19900</v>
@@ -6778,22 +6778,22 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M147" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N147" t="n">
         <v>4242.5421445221</v>
       </c>
       <c r="O147" t="n">
-        <v>93335.9271794862</v>
+        <v>67880.6743123536</v>
       </c>
       <c r="P147" t="n">
         <v>5900</v>
       </c>
       <c r="Q147" t="n">
-        <v>129800</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="148">
@@ -6874,10 +6874,10 @@
         <v>210</v>
       </c>
       <c r="N149" t="n">
-        <v>3041.6600129786</v>
+        <v>3041.6600130804</v>
       </c>
       <c r="O149" t="n">
-        <v>638748.6027255061</v>
+        <v>638748.602746884</v>
       </c>
       <c r="P149" t="n">
         <v>5500</v>
@@ -7002,10 +7002,10 @@
         <v>1945</v>
       </c>
       <c r="N152" t="n">
-        <v>4372.2107892862</v>
+        <v>4372.2107896237</v>
       </c>
       <c r="O152" t="n">
-        <v>8503949.98516166</v>
+        <v>8503949.985818097</v>
       </c>
       <c r="P152" t="n">
         <v>7500</v>
@@ -7092,10 +7092,10 @@
         <v>306</v>
       </c>
       <c r="N154" t="n">
-        <v>1592.5669555035</v>
+        <v>1592.5668955224</v>
       </c>
       <c r="O154" t="n">
-        <v>487325.488384071</v>
+        <v>487325.4700298544</v>
       </c>
       <c r="P154" t="n">
         <v>3900</v>
@@ -8457,22 +8457,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M184" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="N184" t="n">
         <v>1520</v>
       </c>
       <c r="O184" t="n">
-        <v>592800</v>
+        <v>547200</v>
       </c>
       <c r="P184" t="n">
         <v>1900</v>
       </c>
       <c r="Q184" t="n">
-        <v>741000</v>
+        <v>684000</v>
       </c>
     </row>
     <row r="185">
@@ -8831,22 +8831,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M192" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="N192" t="n">
         <v>9903</v>
       </c>
       <c r="O192" t="n">
-        <v>1980600</v>
+        <v>1940988</v>
       </c>
       <c r="P192" t="n">
         <v>15900</v>
       </c>
       <c r="Q192" t="n">
-        <v>3180000</v>
+        <v>3116400</v>
       </c>
     </row>
     <row r="193">
@@ -8883,10 +8883,10 @@
         <v>760</v>
       </c>
       <c r="N193" t="n">
-        <v>1630.9234875283</v>
+        <v>1630.9235527836</v>
       </c>
       <c r="O193" t="n">
-        <v>1239501.850521508</v>
+        <v>1239501.900115536</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -8975,10 +8975,10 @@
         <v>288</v>
       </c>
       <c r="N195" t="n">
-        <v>1690.5983498584</v>
+        <v>1690.5981330472</v>
       </c>
       <c r="O195" t="n">
-        <v>486892.3247592192</v>
+        <v>486892.2623175936</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9021,10 +9021,10 @@
         <v>1942</v>
       </c>
       <c r="N196" t="n">
-        <v>1550.1935332762</v>
+        <v>1550.1935823921</v>
       </c>
       <c r="O196" t="n">
-        <v>3010475.841622381</v>
+        <v>3010475.937005458</v>
       </c>
       <c r="P196" t="n">
         <v>2500</v>
@@ -9067,10 +9067,10 @@
         <v>22</v>
       </c>
       <c r="N197" t="n">
-        <v>1579.3907235142</v>
+        <v>1579.3906753247</v>
       </c>
       <c r="O197" t="n">
-        <v>34746.5959173124</v>
+        <v>34746.5948571434</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9113,10 +9113,10 @@
         <v>418</v>
       </c>
       <c r="N198" t="n">
-        <v>2403.5115510508</v>
+        <v>2403.5116616598</v>
       </c>
       <c r="O198" t="n">
-        <v>1004667.828339234</v>
+        <v>1004667.874573797</v>
       </c>
       <c r="P198" t="n">
         <v>3500</v>
@@ -9154,10 +9154,10 @@
         <v>65</v>
       </c>
       <c r="N199" t="n">
-        <v>1232.8075688073</v>
+        <v>1232.8074537037</v>
       </c>
       <c r="O199" t="n">
-        <v>80132.4919724745</v>
+        <v>80132.48449074051</v>
       </c>
       <c r="P199" t="n">
         <v>2400</v>
@@ -10524,22 +10524,22 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M230" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
         <v>1958.73</v>
       </c>
       <c r="O230" t="n">
-        <v>58761.9</v>
+        <v>0</v>
       </c>
       <c r="P230" t="n">
         <v>3400</v>
       </c>
       <c r="Q230" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -10962,22 +10962,22 @@
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M240" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N240" t="n">
         <v>30611</v>
       </c>
       <c r="O240" t="n">
-        <v>1775438</v>
+        <v>1714216</v>
       </c>
       <c r="P240" t="n">
         <v>38900</v>
       </c>
       <c r="Q240" t="n">
-        <v>2256200</v>
+        <v>2178400</v>
       </c>
     </row>
     <row r="241">
@@ -11196,10 +11196,10 @@
         <v>125</v>
       </c>
       <c r="N245" t="n">
-        <v>4285.1954682454</v>
+        <v>4285.1954741379</v>
       </c>
       <c r="O245" t="n">
-        <v>535649.433530675</v>
+        <v>535649.4342672375</v>
       </c>
       <c r="P245" t="n">
         <v>6900</v>
@@ -11455,10 +11455,10 @@
         <v>563</v>
       </c>
       <c r="N251" t="n">
-        <v>4605.2147185741</v>
+        <v>4605.2147274436</v>
       </c>
       <c r="O251" t="n">
-        <v>2592735.886557218</v>
+        <v>2592735.891550747</v>
       </c>
       <c r="P251" t="n">
         <v>7600</v>
@@ -11542,10 +11542,10 @@
         <v>32</v>
       </c>
       <c r="N253" t="n">
-        <v>11562.038518519</v>
+        <v>11562.038494624</v>
       </c>
       <c r="O253" t="n">
-        <v>369985.232592608</v>
+        <v>369985.231827968</v>
       </c>
       <c r="P253" t="n">
         <v>18500</v>
@@ -11946,10 +11946,10 @@
         <v>72</v>
       </c>
       <c r="N262" t="n">
-        <v>8332.7796240601</v>
+        <v>8332.779622166199</v>
       </c>
       <c r="O262" t="n">
-        <v>599960.1329323272</v>
+        <v>599960.1327959663</v>
       </c>
       <c r="P262" t="n">
         <v>14900</v>
@@ -12038,10 +12038,10 @@
         <v>599</v>
       </c>
       <c r="N264" t="n">
-        <v>1561.000152391</v>
+        <v>1561.0001684211</v>
       </c>
       <c r="O264" t="n">
-        <v>935039.091282209</v>
+        <v>935039.1008842388</v>
       </c>
       <c r="P264" t="n">
         <v>2900</v>
@@ -12124,22 +12124,22 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M266" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N266" t="n">
         <v>26854</v>
       </c>
       <c r="O266" t="n">
-        <v>859328</v>
+        <v>725058</v>
       </c>
       <c r="P266" t="n">
         <v>43900</v>
       </c>
       <c r="Q266" t="n">
-        <v>1404800</v>
+        <v>1185300</v>
       </c>
     </row>
     <row r="267">
@@ -12361,10 +12361,10 @@
         <v>306</v>
       </c>
       <c r="N271" t="n">
-        <v>548.14722592946</v>
+        <v>548.14720461095</v>
       </c>
       <c r="O271" t="n">
-        <v>167733.0511344148</v>
+        <v>167733.0446109507</v>
       </c>
       <c r="P271" t="n">
         <v>2000</v>
@@ -13247,10 +13247,10 @@
         <v>81</v>
       </c>
       <c r="N290" t="n">
-        <v>5218.1705479452</v>
+        <v>5218.1705520703</v>
       </c>
       <c r="O290" t="n">
-        <v>422671.8143835612</v>
+        <v>422671.8147176943</v>
       </c>
       <c r="P290" t="n">
         <v>8500</v>
@@ -13293,10 +13293,10 @@
         <v>1</v>
       </c>
       <c r="N291" t="n">
-        <v>1595.0093800979</v>
+        <v>1595.0093780687</v>
       </c>
       <c r="O291" t="n">
-        <v>1595.0093800979</v>
+        <v>1595.0093780687</v>
       </c>
       <c r="P291" t="n">
         <v>2600</v>
@@ -13339,10 +13339,10 @@
         <v>123</v>
       </c>
       <c r="N292" t="n">
-        <v>3610.650025641</v>
+        <v>3610.65002574</v>
       </c>
       <c r="O292" t="n">
-        <v>444109.953153843</v>
+        <v>444109.95316602</v>
       </c>
       <c r="P292" t="n">
         <v>5800</v>
@@ -13474,22 +13474,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N295" t="n">
         <v>3920</v>
       </c>
       <c r="O295" t="n">
-        <v>1877680</v>
+        <v>1873760</v>
       </c>
       <c r="P295" t="n">
         <v>4900</v>
       </c>
       <c r="Q295" t="n">
-        <v>2347100</v>
+        <v>2342200</v>
       </c>
     </row>
     <row r="296">
@@ -15412,22 +15412,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M337" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="N337" t="n">
         <v>4917</v>
       </c>
       <c r="O337" t="n">
-        <v>324522</v>
+        <v>290103</v>
       </c>
       <c r="P337" t="n">
         <v>8600</v>
       </c>
       <c r="Q337" t="n">
-        <v>567600</v>
+        <v>507400</v>
       </c>
     </row>
     <row r="338">
@@ -15691,22 +15691,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M343" t="n">
-        <v>649</v>
+        <v>615</v>
       </c>
       <c r="N343" t="n">
         <v>3938.66</v>
       </c>
       <c r="O343" t="n">
-        <v>2556190.34</v>
+        <v>2422275.9</v>
       </c>
       <c r="P343" t="n">
         <v>4500</v>
       </c>
       <c r="Q343" t="n">
-        <v>2920500</v>
+        <v>2767500</v>
       </c>
     </row>
     <row r="344">
@@ -16019,10 +16019,10 @@
         <v>5</v>
       </c>
       <c r="N350" t="n">
-        <v>2252.2966708385</v>
+        <v>2252.2968774194</v>
       </c>
       <c r="O350" t="n">
-        <v>11261.4833541925</v>
+        <v>11261.484387097</v>
       </c>
       <c r="P350" t="n">
         <v>3900</v>
@@ -16345,10 +16345,10 @@
         <v>324</v>
       </c>
       <c r="N357" t="n">
-        <v>2328.1187254606</v>
+        <v>2328.1187184938</v>
       </c>
       <c r="O357" t="n">
-        <v>754310.4670492344</v>
+        <v>754310.4647919912</v>
       </c>
       <c r="P357" t="n">
         <v>4500</v>
@@ -16983,22 +16983,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M371" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="N371" t="n">
-        <v>4907.8220583468</v>
+        <v>4907.8220751634</v>
       </c>
       <c r="O371" t="n">
-        <v>731265.4866936732</v>
+        <v>672371.6242973858</v>
       </c>
       <c r="P371" t="n">
         <v>8200</v>
       </c>
       <c r="Q371" t="n">
-        <v>1221800</v>
+        <v>1123400</v>
       </c>
     </row>
     <row r="372">
@@ -17444,10 +17444,10 @@
         <v>48</v>
       </c>
       <c r="N381" t="n">
-        <v>5869.172680203</v>
+        <v>5869.1726653103</v>
       </c>
       <c r="O381" t="n">
-        <v>281720.288649744</v>
+        <v>281720.2879348944</v>
       </c>
       <c r="P381" t="n">
         <v>9500</v>
@@ -17760,22 +17760,22 @@
         <v>0</v>
       </c>
       <c r="L388" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M388" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N388" t="n">
         <v>13565</v>
       </c>
       <c r="O388" t="n">
-        <v>2048315</v>
+        <v>1980490</v>
       </c>
       <c r="P388" t="n">
         <v>22500</v>
       </c>
       <c r="Q388" t="n">
-        <v>3397500</v>
+        <v>3285000</v>
       </c>
     </row>
     <row r="389">
@@ -17806,22 +17806,22 @@
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M389" t="n">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="N389" t="n">
         <v>7635</v>
       </c>
       <c r="O389" t="n">
-        <v>4038915</v>
+        <v>4023645</v>
       </c>
       <c r="P389" t="n">
         <v>13900</v>
       </c>
       <c r="Q389" t="n">
-        <v>7353100</v>
+        <v>7325300</v>
       </c>
     </row>
     <row r="390">
@@ -18494,22 +18494,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M404" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="N404" t="n">
         <v>10755</v>
       </c>
       <c r="O404" t="n">
-        <v>1817595</v>
+        <v>1731555</v>
       </c>
       <c r="P404" t="n">
         <v>17900</v>
       </c>
       <c r="Q404" t="n">
-        <v>3025100</v>
+        <v>2881900</v>
       </c>
     </row>
     <row r="405">
@@ -18816,22 +18816,22 @@
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M411" t="n">
-        <v>2381</v>
+        <v>2341</v>
       </c>
       <c r="N411" t="n">
         <v>1326</v>
       </c>
       <c r="O411" t="n">
-        <v>3157206</v>
+        <v>3104166</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
       </c>
       <c r="Q411" t="n">
-        <v>5952500</v>
+        <v>5852500</v>
       </c>
     </row>
     <row r="412">
@@ -19322,22 +19322,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M422" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N422" t="n">
         <v>15223.06</v>
       </c>
       <c r="O422" t="n">
-        <v>806822.1799999999</v>
+        <v>776376.0599999999</v>
       </c>
       <c r="P422" t="n">
         <v>17500</v>
       </c>
       <c r="Q422" t="n">
-        <v>927500</v>
+        <v>892500</v>
       </c>
     </row>
     <row r="423">
@@ -19420,10 +19420,10 @@
         <v>1320</v>
       </c>
       <c r="N424" t="n">
-        <v>1516.0388018299</v>
+        <v>1516.038799961</v>
       </c>
       <c r="O424" t="n">
-        <v>2001171.218415468</v>
+        <v>2001171.21594852</v>
       </c>
       <c r="P424" t="n">
         <v>2300</v>
@@ -19512,10 +19512,10 @@
         <v>8</v>
       </c>
       <c r="N426" t="n">
-        <v>4248.6728</v>
+        <v>4248.6814925373</v>
       </c>
       <c r="O426" t="n">
-        <v>33989.3824</v>
+        <v>33989.4519402984</v>
       </c>
       <c r="P426" t="n">
         <v>5900</v>
@@ -19558,10 +19558,10 @@
         <v>120</v>
       </c>
       <c r="N427" t="n">
-        <v>2458.5131932225</v>
+        <v>2458.5131821149</v>
       </c>
       <c r="O427" t="n">
-        <v>295021.5831867</v>
+        <v>295021.581853788</v>
       </c>
       <c r="P427" t="n">
         <v>3500</v>
@@ -19696,10 +19696,10 @@
         <v>72</v>
       </c>
       <c r="N430" t="n">
-        <v>1803.0156033058</v>
+        <v>1803.0156051587</v>
       </c>
       <c r="O430" t="n">
-        <v>129817.1234380176</v>
+        <v>129817.1235714264</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -19742,10 +19742,10 @@
         <v>216</v>
       </c>
       <c r="N431" t="n">
-        <v>3306.5951807229</v>
+        <v>3306.5951742627</v>
       </c>
       <c r="O431" t="n">
-        <v>714224.5590361464</v>
+        <v>714224.5576407432</v>
       </c>
       <c r="P431" t="n">
         <v>4900</v>
@@ -19834,10 +19834,10 @@
         <v>120</v>
       </c>
       <c r="N433" t="n">
-        <v>2108.791733871</v>
+        <v>2108.7917654987</v>
       </c>
       <c r="O433" t="n">
-        <v>253055.00806452</v>
+        <v>253055.011859844</v>
       </c>
       <c r="P433" t="n">
         <v>2900</v>
@@ -19880,10 +19880,10 @@
         <v>144</v>
       </c>
       <c r="N434" t="n">
-        <v>2056.0833654773</v>
+        <v>2056.0833612094</v>
       </c>
       <c r="O434" t="n">
-        <v>296076.0046287312</v>
+        <v>296076.0040141536</v>
       </c>
       <c r="P434" t="n">
         <v>2900</v>
@@ -19926,10 +19926,10 @@
         <v>216</v>
       </c>
       <c r="N435" t="n">
-        <v>3224.5685400763</v>
+        <v>3224.5685727969</v>
       </c>
       <c r="O435" t="n">
-        <v>696506.8046564808</v>
+        <v>696506.8117241304</v>
       </c>
       <c r="P435" t="n">
         <v>4500</v>
@@ -19972,10 +19972,10 @@
         <v>360</v>
       </c>
       <c r="N436" t="n">
-        <v>1655.9308953259</v>
+        <v>1655.9308833223</v>
       </c>
       <c r="O436" t="n">
-        <v>596135.122317324</v>
+        <v>596135.1179960279</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -20202,10 +20202,10 @@
         <v>304</v>
       </c>
       <c r="N441" t="n">
-        <v>1592.2776475694</v>
+        <v>1592.2780825688</v>
       </c>
       <c r="O441" t="n">
-        <v>484052.4048610976</v>
+        <v>484052.5371009152</v>
       </c>
       <c r="P441" t="n">
         <v>2500</v>
@@ -20333,10 +20333,10 @@
         <v>408</v>
       </c>
       <c r="N444" t="n">
-        <v>2060.1601200686</v>
+        <v>2060.1601030928</v>
       </c>
       <c r="O444" t="n">
-        <v>840545.3289879888</v>
+        <v>840545.3220618624</v>
       </c>
       <c r="P444" t="n">
         <v>2900</v>
@@ -20379,10 +20379,10 @@
         <v>24</v>
       </c>
       <c r="N445" t="n">
-        <v>2546.9842276423</v>
+        <v>2546.9839957717</v>
       </c>
       <c r="O445" t="n">
-        <v>61127.6214634152</v>
+        <v>61127.6158985208</v>
       </c>
       <c r="P445" t="n">
         <v>3900</v>
@@ -20743,10 +20743,10 @@
         <v>2800</v>
       </c>
       <c r="N453" t="n">
-        <v>1955.2371159315</v>
+        <v>1955.2371140003</v>
       </c>
       <c r="O453" t="n">
-        <v>5474663.9246082</v>
+        <v>5474663.919200839</v>
       </c>
       <c r="P453" t="n">
         <v>3000</v>
@@ -22230,10 +22230,10 @@
         <v>5817</v>
       </c>
       <c r="N485" t="n">
-        <v>711.3366499515799</v>
+        <v>711.33664971986</v>
       </c>
       <c r="O485" t="n">
-        <v>4137845.292768341</v>
+        <v>4137845.291420426</v>
       </c>
       <c r="P485" t="n">
         <v>900</v>
@@ -22647,10 +22647,10 @@
         <v>461</v>
       </c>
       <c r="N494" t="n">
-        <v>517.28922545101</v>
+        <v>517.2892916984</v>
       </c>
       <c r="O494" t="n">
-        <v>238470.3329329156</v>
+        <v>238470.3634729624</v>
       </c>
       <c r="P494" t="n">
         <v>900</v>
@@ -23070,10 +23070,10 @@
         <v>757</v>
       </c>
       <c r="N503" t="n">
-        <v>3110.8421999117</v>
+        <v>3110.8418772978</v>
       </c>
       <c r="O503" t="n">
-        <v>2354907.545333157</v>
+        <v>2354907.301114434</v>
       </c>
       <c r="P503" t="n">
         <v>4500</v>
@@ -23477,10 +23477,10 @@
         <v>120</v>
       </c>
       <c r="N512" t="n">
-        <v>2973.0437950139</v>
+        <v>2973.0438002774</v>
       </c>
       <c r="O512" t="n">
-        <v>356765.255401668</v>
+        <v>356765.256033288</v>
       </c>
       <c r="P512" t="n">
         <v>4500</v>
@@ -23521,10 +23521,10 @@
         <v>19802</v>
       </c>
       <c r="N513" t="n">
-        <v>703.79520622865</v>
+        <v>703.79518726322</v>
       </c>
       <c r="O513" t="n">
-        <v>13936552.67373973</v>
+        <v>13936552.29818628</v>
       </c>
       <c r="P513" t="n">
         <v>900</v>
@@ -24028,10 +24028,10 @@
         <v>47</v>
       </c>
       <c r="N524" t="n">
-        <v>1595.5130117944</v>
+        <v>1595.5128965225</v>
       </c>
       <c r="O524" t="n">
-        <v>74989.11155433679</v>
+        <v>74989.1061365575</v>
       </c>
       <c r="P524" t="n">
         <v>2500</v>
@@ -25230,22 +25230,22 @@
         <v>0</v>
       </c>
       <c r="L549" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M549" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N549" t="n">
         <v>17208.63</v>
       </c>
       <c r="O549" t="n">
-        <v>103251.78</v>
+        <v>68834.52</v>
       </c>
       <c r="P549" t="n">
         <v>69900</v>
       </c>
       <c r="Q549" t="n">
-        <v>419400</v>
+        <v>279600</v>
       </c>
     </row>
     <row r="550">
@@ -25619,22 +25619,22 @@
         <v>0</v>
       </c>
       <c r="L557" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M557" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N557" t="n">
         <v>5430.86</v>
       </c>
       <c r="O557" t="n">
-        <v>92324.62</v>
+        <v>54308.6</v>
       </c>
       <c r="P557" t="n">
         <v>13900</v>
       </c>
       <c r="Q557" t="n">
-        <v>236300</v>
+        <v>139000</v>
       </c>
     </row>
     <row r="558">
@@ -25717,22 +25717,22 @@
         <v>0</v>
       </c>
       <c r="L559" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M559" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N559" t="n">
         <v>4568.55</v>
       </c>
       <c r="O559" t="n">
-        <v>292387.2</v>
+        <v>278681.55</v>
       </c>
       <c r="P559" t="n">
         <v>6900</v>
       </c>
       <c r="Q559" t="n">
-        <v>441600</v>
+        <v>420900</v>
       </c>
     </row>
     <row r="560">
@@ -25903,10 +25903,10 @@
         <v>312</v>
       </c>
       <c r="N563" t="n">
-        <v>3414.5660744763</v>
+        <v>3414.566049961</v>
       </c>
       <c r="O563" t="n">
-        <v>1065344.615236606</v>
+        <v>1065344.607587832</v>
       </c>
       <c r="P563" t="n">
         <v>3500</v>
@@ -26996,22 +26996,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M586" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N586" t="n">
         <v>14751.82031746</v>
       </c>
       <c r="O586" t="n">
-        <v>221277.3047619</v>
+        <v>206525.48444444</v>
       </c>
       <c r="P586" t="n">
         <v>37100</v>
       </c>
       <c r="Q586" t="n">
-        <v>556500</v>
+        <v>519400</v>
       </c>
     </row>
     <row r="587">
@@ -28232,10 +28232,10 @@
         <v>648</v>
       </c>
       <c r="N612" t="n">
-        <v>665.32352410996</v>
+        <v>665.32358222629</v>
       </c>
       <c r="O612" t="n">
-        <v>431129.6436232541</v>
+        <v>431129.6812826359</v>
       </c>
       <c r="P612" t="n">
         <v>2900</v>
@@ -29536,10 +29536,10 @@
         <v>48</v>
       </c>
       <c r="N641" t="n">
-        <v>8922.215</v>
+        <v>8922.2151190476</v>
       </c>
       <c r="O641" t="n">
-        <v>428266.32</v>
+        <v>428266.3257142848</v>
       </c>
       <c r="P641" t="n">
         <v>8200</v>
@@ -29716,10 +29716,10 @@
         <v>352</v>
       </c>
       <c r="N645" t="n">
-        <v>22951.7048659</v>
+        <v>22951.704852753</v>
       </c>
       <c r="O645" t="n">
-        <v>8079000.1127968</v>
+        <v>8079000.108169056</v>
       </c>
       <c r="P645" t="n">
         <v>37900</v>
@@ -29905,10 +29905,10 @@
         <v>306</v>
       </c>
       <c r="N649" t="n">
-        <v>1757.3205591398</v>
+        <v>1757.3205603448</v>
       </c>
       <c r="O649" t="n">
-        <v>537740.0910967789</v>
+        <v>537740.0914655088</v>
       </c>
       <c r="P649" t="n">
         <v>2000</v>
@@ -30564,12 +30564,12 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>J-582</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -30583,39 +30583,39 @@
         </is>
       </c>
       <c r="J664" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="K664" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="L664" t="n">
         <v>0</v>
       </c>
       <c r="M664" t="n">
-        <v>480</v>
+        <v>94</v>
       </c>
       <c r="N664" t="n">
-        <v>9240</v>
+        <v>5280</v>
       </c>
       <c r="O664" t="n">
-        <v>4435200</v>
+        <v>496320</v>
       </c>
       <c r="P664" t="n">
-        <v>11500</v>
+        <v>6900</v>
       </c>
       <c r="Q664" t="n">
-        <v>5520000</v>
+        <v>648600</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -30629,39 +30629,39 @@
         </is>
       </c>
       <c r="J665" t="n">
-        <v>31</v>
+        <v>480</v>
       </c>
       <c r="K665" t="n">
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M665" t="n">
-        <v>31</v>
+        <v>440</v>
       </c>
       <c r="N665" t="n">
-        <v>415.07</v>
+        <v>9240</v>
       </c>
       <c r="O665" t="n">
-        <v>12867.17</v>
+        <v>4065600</v>
       </c>
       <c r="P665" t="n">
-        <v>2900</v>
+        <v>11500</v>
       </c>
       <c r="Q665" t="n">
-        <v>89900</v>
+        <v>5060000</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -30675,44 +30675,44 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K666" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="N666" t="n">
-        <v>46491.75</v>
+        <v>5280</v>
       </c>
       <c r="O666" t="n">
-        <v>2743013.25</v>
+        <v>739200</v>
       </c>
       <c r="P666" t="n">
-        <v>52900</v>
+        <v>6900</v>
       </c>
       <c r="Q666" t="n">
-        <v>3121100</v>
+        <v>966000</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -30721,7 +30721,7 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K667" t="n">
         <v>0</v>
@@ -30730,35 +30730,35 @@
         <v>0</v>
       </c>
       <c r="M667" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N667" t="n">
-        <v>910.85</v>
+        <v>415.07</v>
       </c>
       <c r="O667" t="n">
-        <v>32790.6</v>
+        <v>12867.17</v>
       </c>
       <c r="P667" t="n">
-        <v>7900</v>
+        <v>2900</v>
       </c>
       <c r="Q667" t="n">
-        <v>284400</v>
+        <v>89900</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -30767,7 +30767,7 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="K668" t="n">
         <v>0</v>
@@ -30776,30 +30776,30 @@
         <v>0</v>
       </c>
       <c r="M668" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="N668" t="n">
-        <v>1129.14</v>
+        <v>46491.75</v>
       </c>
       <c r="O668" t="n">
-        <v>13549.68</v>
+        <v>2743013.25</v>
       </c>
       <c r="P668" t="n">
-        <v>6900</v>
+        <v>52900</v>
       </c>
       <c r="Q668" t="n">
-        <v>82800</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -30813,7 +30813,7 @@
         </is>
       </c>
       <c r="J669" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="K669" t="n">
         <v>0</v>
@@ -30822,40 +30822,35 @@
         <v>0</v>
       </c>
       <c r="M669" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="N669" t="n">
-        <v>11433.53</v>
+        <v>910.85</v>
       </c>
       <c r="O669" t="n">
-        <v>125768.83</v>
+        <v>32790.6</v>
       </c>
       <c r="P669" t="n">
-        <v>15000</v>
+        <v>7900</v>
       </c>
       <c r="Q669" t="n">
-        <v>165000</v>
+        <v>284400</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -30864,7 +30859,7 @@
         </is>
       </c>
       <c r="J670" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K670" t="n">
         <v>0</v>
@@ -30873,35 +30868,35 @@
         <v>0</v>
       </c>
       <c r="M670" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N670" t="n">
-        <v>15452.21</v>
+        <v>1129.14</v>
       </c>
       <c r="O670" t="n">
-        <v>61808.84</v>
+        <v>13549.68</v>
       </c>
       <c r="P670" t="n">
-        <v>36500</v>
+        <v>6900</v>
       </c>
       <c r="Q670" t="n">
-        <v>146000</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -30910,7 +30905,7 @@
         </is>
       </c>
       <c r="J671" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="K671" t="n">
         <v>0</v>
@@ -30919,40 +30914,40 @@
         <v>0</v>
       </c>
       <c r="M671" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="N671" t="n">
-        <v>1319.3608823529</v>
+        <v>11433.53</v>
       </c>
       <c r="O671" t="n">
-        <v>263872.17647058</v>
+        <v>125768.83</v>
       </c>
       <c r="P671" t="n">
-        <v>3500</v>
+        <v>15000</v>
       </c>
       <c r="Q671" t="n">
-        <v>700000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>MG33219</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>MG33219</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -30961,7 +30956,7 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
@@ -30970,35 +30965,35 @@
         <v>0</v>
       </c>
       <c r="M672" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="N672" t="n">
-        <v>751.45</v>
+        <v>15452.21</v>
       </c>
       <c r="O672" t="n">
-        <v>50347.15</v>
+        <v>61808.84</v>
       </c>
       <c r="P672" t="n">
-        <v>2500</v>
+        <v>36500</v>
       </c>
       <c r="Q672" t="n">
-        <v>167500</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -31007,44 +31002,49 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="K673" t="n">
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M673" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="N673" t="n">
-        <v>571.87</v>
+        <v>1319.3608823529</v>
       </c>
       <c r="O673" t="n">
-        <v>81777.41</v>
+        <v>232207.5152941104</v>
       </c>
       <c r="P673" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="Q673" t="n">
-        <v>357500</v>
+        <v>616000</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -31053,7 +31053,7 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>686</v>
+        <v>67</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
@@ -31062,40 +31062,35 @@
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>686</v>
+        <v>67</v>
       </c>
       <c r="N674" t="n">
-        <v>227.41601620029</v>
+        <v>751.45</v>
       </c>
       <c r="O674" t="n">
-        <v>156007.3871133989</v>
+        <v>50347.15</v>
       </c>
       <c r="P674" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="Q674" t="n">
-        <v>823200</v>
+        <v>167500</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -31104,7 +31099,7 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -31113,39 +31108,44 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="N675" t="n">
-        <v>9917.040000000001</v>
+        <v>571.87</v>
       </c>
       <c r="O675" t="n">
-        <v>218174.88</v>
+        <v>81777.41</v>
       </c>
       <c r="P675" t="n">
-        <v>15900</v>
+        <v>2500</v>
       </c>
       <c r="Q675" t="n">
-        <v>349800</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>MT4004</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J676" t="n">
-        <v>158</v>
+        <v>686</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
@@ -31154,35 +31154,40 @@
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>158</v>
+        <v>686</v>
       </c>
       <c r="N676" t="n">
-        <v>2058.92</v>
+        <v>227.41601620029</v>
       </c>
       <c r="O676" t="n">
-        <v>325309.36</v>
+        <v>156007.3871133989</v>
       </c>
       <c r="P676" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="Q676" t="n">
-        <v>395000</v>
+        <v>823200</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -31191,53 +31196,56 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M677" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="N677" t="n">
-        <v>3306.00915</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O677" t="n">
-        <v>314070.86925</v>
+        <v>208257.84</v>
       </c>
       <c r="P677" t="n">
-        <v>4200</v>
+        <v>15900</v>
       </c>
       <c r="Q677" t="n">
-        <v>399000</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>SEB010</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J678" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="K678" t="n">
         <v>0</v>
@@ -31246,35 +31254,35 @@
         <v>0</v>
       </c>
       <c r="M678" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="N678" t="n">
-        <v>7600</v>
+        <v>2297.5912635379</v>
       </c>
       <c r="O678" t="n">
-        <v>364800</v>
+        <v>363019.4196389882</v>
       </c>
       <c r="P678" t="n">
-        <v>9500</v>
+        <v>3500</v>
       </c>
       <c r="Q678" t="n">
-        <v>456000</v>
+        <v>553000</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -31295,32 +31303,32 @@
         <v>95</v>
       </c>
       <c r="N679" t="n">
-        <v>5520</v>
+        <v>4140.7522875</v>
       </c>
       <c r="O679" t="n">
-        <v>524400</v>
+        <v>393371.4673125001</v>
       </c>
       <c r="P679" t="n">
-        <v>6900</v>
+        <v>5500</v>
       </c>
       <c r="Q679" t="n">
-        <v>655500</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>SEB09</t>
+          <t>SEB010</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -31329,7 +31337,7 @@
         </is>
       </c>
       <c r="J680" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="K680" t="n">
         <v>0</v>
@@ -31338,30 +31346,30 @@
         <v>0</v>
       </c>
       <c r="M680" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="N680" t="n">
-        <v>1600</v>
+        <v>7600</v>
       </c>
       <c r="O680" t="n">
-        <v>132800</v>
+        <v>364800</v>
       </c>
       <c r="P680" t="n">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="Q680" t="n">
-        <v>166000</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -31375,7 +31383,7 @@
         </is>
       </c>
       <c r="J681" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="K681" t="n">
         <v>0</v>
@@ -31384,30 +31392,30 @@
         <v>0</v>
       </c>
       <c r="M681" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="N681" t="n">
-        <v>4091.4</v>
+        <v>5520</v>
       </c>
       <c r="O681" t="n">
-        <v>4091.4</v>
+        <v>524400</v>
       </c>
       <c r="P681" t="n">
-        <v>10000</v>
+        <v>6900</v>
       </c>
       <c r="Q681" t="n">
-        <v>10000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>SLT027</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>JUGUETE  DRAGON   AB-02 / 082</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -31421,7 +31429,7 @@
         </is>
       </c>
       <c r="J682" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="K682" t="n">
         <v>0</v>
@@ -31430,35 +31438,35 @@
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="N682" t="n">
-        <v>3732.8773611111</v>
+        <v>1600</v>
       </c>
       <c r="O682" t="n">
-        <v>37328.773611111</v>
+        <v>132800</v>
       </c>
       <c r="P682" t="n">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="Q682" t="n">
-        <v>45000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -31467,7 +31475,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -31476,35 +31484,35 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N683" t="n">
-        <v>3661.88</v>
+        <v>4091.4</v>
       </c>
       <c r="O683" t="n">
-        <v>10985.64</v>
+        <v>4091.4</v>
       </c>
       <c r="P683" t="n">
-        <v>38900</v>
+        <v>10000</v>
       </c>
       <c r="Q683" t="n">
-        <v>116700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>SLT027</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>JUGUETE  DRAGON   AB-02 / 082</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -31513,7 +31521,7 @@
         </is>
       </c>
       <c r="J684" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K684" t="n">
         <v>0</v>
@@ -31522,30 +31530,30 @@
         <v>0</v>
       </c>
       <c r="M684" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N684" t="n">
-        <v>2797.08</v>
+        <v>3732.8773611111</v>
       </c>
       <c r="O684" t="n">
-        <v>13985.4</v>
+        <v>37328.773611111</v>
       </c>
       <c r="P684" t="n">
-        <v>30900</v>
+        <v>4500</v>
       </c>
       <c r="Q684" t="n">
-        <v>154500</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T040-LJ</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -31559,7 +31567,7 @@
         </is>
       </c>
       <c r="J685" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K685" t="n">
         <v>0</v>
@@ -31568,30 +31576,30 @@
         <v>0</v>
       </c>
       <c r="M685" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N685" t="n">
-        <v>3462.255</v>
+        <v>3661.88</v>
       </c>
       <c r="O685" t="n">
-        <v>38084.805</v>
+        <v>10985.64</v>
       </c>
       <c r="P685" t="n">
-        <v>42000</v>
+        <v>38900</v>
       </c>
       <c r="Q685" t="n">
-        <v>462000</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T041-LJ</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -31605,7 +31613,7 @@
         </is>
       </c>
       <c r="J686" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K686" t="n">
         <v>0</v>
@@ -31614,30 +31622,30 @@
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="N686" t="n">
-        <v>24882.58</v>
+        <v>2797.08</v>
       </c>
       <c r="O686" t="n">
-        <v>696712.24</v>
+        <v>13985.4</v>
       </c>
       <c r="P686" t="n">
-        <v>31500</v>
+        <v>30900</v>
       </c>
       <c r="Q686" t="n">
-        <v>882000</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -31651,7 +31659,7 @@
         </is>
       </c>
       <c r="J687" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K687" t="n">
         <v>0</v>
@@ -31660,35 +31668,35 @@
         <v>0</v>
       </c>
       <c r="M687" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N687" t="n">
-        <v>0.8</v>
+        <v>3462.255</v>
       </c>
       <c r="O687" t="n">
-        <v>15.2</v>
+        <v>38084.805</v>
       </c>
       <c r="P687" t="n">
-        <v>22900</v>
+        <v>42000</v>
       </c>
       <c r="Q687" t="n">
-        <v>435100</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -31697,7 +31705,7 @@
         </is>
       </c>
       <c r="J688" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K688" t="n">
         <v>0</v>
@@ -31706,35 +31714,35 @@
         <v>0</v>
       </c>
       <c r="M688" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N688" t="n">
-        <v>5186.45</v>
+        <v>24882.58</v>
       </c>
       <c r="O688" t="n">
-        <v>82983.2</v>
+        <v>696712.24</v>
       </c>
       <c r="P688" t="n">
-        <v>7200</v>
+        <v>31500</v>
       </c>
       <c r="Q688" t="n">
-        <v>115200</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>T119-LJ</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -31743,7 +31751,7 @@
         </is>
       </c>
       <c r="J689" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K689" t="n">
         <v>0</v>
@@ -31752,30 +31760,30 @@
         <v>0</v>
       </c>
       <c r="M689" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N689" t="n">
-        <v>47796.1625</v>
+        <v>0.8</v>
       </c>
       <c r="O689" t="n">
-        <v>95592.325</v>
+        <v>15.2</v>
       </c>
       <c r="P689" t="n">
-        <v>54000</v>
+        <v>22900</v>
       </c>
       <c r="Q689" t="n">
-        <v>108000</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>TB115</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -31789,7 +31797,7 @@
         </is>
       </c>
       <c r="J690" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K690" t="n">
         <v>0</v>
@@ -31798,64 +31806,156 @@
         <v>0</v>
       </c>
       <c r="M690" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="N690" t="n">
-        <v>8006.3731111111</v>
+        <v>5186.45</v>
       </c>
       <c r="O690" t="n">
-        <v>344274.0437777773</v>
+        <v>82983.2</v>
       </c>
       <c r="P690" t="n">
-        <v>10000</v>
+        <v>7200</v>
       </c>
       <c r="Q690" t="n">
-        <v>430000</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
+          <t>TB028</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J691" t="n">
+        <v>2</v>
+      </c>
+      <c r="K691" t="n">
+        <v>0</v>
+      </c>
+      <c r="L691" t="n">
+        <v>0</v>
+      </c>
+      <c r="M691" t="n">
+        <v>2</v>
+      </c>
+      <c r="N691" t="n">
+        <v>47796.1625</v>
+      </c>
+      <c r="O691" t="n">
+        <v>95592.325</v>
+      </c>
+      <c r="P691" t="n">
+        <v>54000</v>
+      </c>
+      <c r="Q691" t="n">
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>TB115</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J692" t="n">
+        <v>43</v>
+      </c>
+      <c r="K692" t="n">
+        <v>0</v>
+      </c>
+      <c r="L692" t="n">
+        <v>0</v>
+      </c>
+      <c r="M692" t="n">
+        <v>43</v>
+      </c>
+      <c r="N692" t="n">
+        <v>8006.3731111111</v>
+      </c>
+      <c r="O692" t="n">
+        <v>344274.0437777773</v>
+      </c>
+      <c r="P692" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q692" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
           <t>TB122</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
-      <c r="E691" t="inlineStr">
+      <c r="E693" t="inlineStr">
         <is>
           <t>PELUCHES</t>
         </is>
       </c>
-      <c r="I691" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J691" t="n">
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J693" t="n">
         <v>4</v>
       </c>
-      <c r="K691" t="n">
-        <v>0</v>
-      </c>
-      <c r="L691" t="n">
-        <v>0</v>
-      </c>
-      <c r="M691" t="n">
+      <c r="K693" t="n">
+        <v>0</v>
+      </c>
+      <c r="L693" t="n">
+        <v>0</v>
+      </c>
+      <c r="M693" t="n">
         <v>4</v>
       </c>
-      <c r="N691" t="n">
+      <c r="N693" t="n">
         <v>47920</v>
       </c>
-      <c r="O691" t="n">
+      <c r="O693" t="n">
         <v>191680</v>
       </c>
-      <c r="P691" t="n">
+      <c r="P693" t="n">
         <v>59900</v>
       </c>
-      <c r="Q691" t="n">
+      <c r="Q693" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464699454</v>
+        <v>3376.7464660832</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.879431733</v>
+        <v>2985043.876017549</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -3308,10 +3308,10 @@
         <v>1295</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0593600211</v>
+        <v>1098.059452236</v>
       </c>
       <c r="O70" t="n">
-        <v>1421986.871227324</v>
+        <v>1421986.99064562</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4241,10 +4241,10 @@
         <v>741</v>
       </c>
       <c r="N91" t="n">
-        <v>2582.2557508532</v>
+        <v>2582.2557353886</v>
       </c>
       <c r="O91" t="n">
-        <v>1913451.511382221</v>
+        <v>1913451.499922953</v>
       </c>
       <c r="P91" t="n">
         <v>4500</v>
@@ -4333,10 +4333,10 @@
         <v>720</v>
       </c>
       <c r="N93" t="n">
-        <v>5216.8961296772</v>
+        <v>5216.8961258041</v>
       </c>
       <c r="O93" t="n">
-        <v>3756165.213367584</v>
+        <v>3756165.210578952</v>
       </c>
       <c r="P93" t="n">
         <v>8500</v>
@@ -4700,10 +4700,10 @@
         <v>156</v>
       </c>
       <c r="N101" t="n">
-        <v>3230.0672564612</v>
+        <v>3230.067250996</v>
       </c>
       <c r="O101" t="n">
-        <v>503890.4920079472</v>
+        <v>503890.491155376</v>
       </c>
       <c r="P101" t="n">
         <v>6200</v>
@@ -5159,10 +5159,10 @@
         <v>581</v>
       </c>
       <c r="N111" t="n">
-        <v>3795.7100075514</v>
+        <v>3795.7100075529</v>
       </c>
       <c r="O111" t="n">
-        <v>2205307.514387364</v>
+        <v>2205307.514388235</v>
       </c>
       <c r="P111" t="n">
         <v>6200</v>
@@ -5384,10 +5384,10 @@
         <v>312</v>
       </c>
       <c r="N116" t="n">
-        <v>4890.9300486322</v>
+        <v>4890.9300487805</v>
       </c>
       <c r="O116" t="n">
-        <v>1525970.175173246</v>
+        <v>1525970.175219516</v>
       </c>
       <c r="P116" t="n">
         <v>8200</v>
@@ -5563,10 +5563,10 @@
         <v>309</v>
       </c>
       <c r="N120" t="n">
-        <v>2267.0481451951</v>
+        <v>2267.0481436371</v>
       </c>
       <c r="O120" t="n">
-        <v>700517.8768652859</v>
+        <v>700517.876383864</v>
       </c>
       <c r="P120" t="n">
         <v>3900</v>
@@ -5924,10 +5924,10 @@
         <v>108</v>
       </c>
       <c r="N128" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.8500369004</v>
       </c>
       <c r="O128" t="n">
-        <v>350011.8035179164</v>
+        <v>350011.8039852432</v>
       </c>
       <c r="P128" t="n">
         <v>5200</v>
@@ -6108,10 +6108,10 @@
         <v>305</v>
       </c>
       <c r="N132" t="n">
-        <v>14822.378850987</v>
+        <v>14822.378849611</v>
       </c>
       <c r="O132" t="n">
-        <v>4520825.549551034</v>
+        <v>4520825.549131354</v>
       </c>
       <c r="P132" t="n">
         <v>24900</v>
@@ -6699,10 +6699,10 @@
         <v>16</v>
       </c>
       <c r="N145" t="n">
-        <v>4242.5421445221</v>
+        <v>4242.5421749409</v>
       </c>
       <c r="O145" t="n">
-        <v>67880.6743123536</v>
+        <v>67880.6747990544</v>
       </c>
       <c r="P145" t="n">
         <v>5900</v>
@@ -6789,10 +6789,10 @@
         <v>210</v>
       </c>
       <c r="N147" t="n">
-        <v>3041.6600131579</v>
+        <v>3041.660013245</v>
       </c>
       <c r="O147" t="n">
-        <v>638748.602763159</v>
+        <v>638748.6027814499</v>
       </c>
       <c r="P147" t="n">
         <v>5500</v>
@@ -6917,10 +6917,10 @@
         <v>1945</v>
       </c>
       <c r="N150" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O150" t="n">
-        <v>8503949.985818097</v>
+        <v>8503949.986803822</v>
       </c>
       <c r="P150" t="n">
         <v>7500</v>
@@ -7007,10 +7007,10 @@
         <v>306</v>
       </c>
       <c r="N152" t="n">
-        <v>1592.5668693558</v>
+        <v>1592.5667761934</v>
       </c>
       <c r="O152" t="n">
-        <v>487325.4620228748</v>
+        <v>487325.4335151804</v>
       </c>
       <c r="P152" t="n">
         <v>3900</v>
@@ -8798,10 +8798,10 @@
         <v>760</v>
       </c>
       <c r="N191" t="n">
-        <v>1630.9235742505</v>
+        <v>1630.9236077879</v>
       </c>
       <c r="O191" t="n">
-        <v>1239501.91643038</v>
+        <v>1239501.941918804</v>
       </c>
       <c r="P191" t="n">
         <v>2500</v>
@@ -8890,10 +8890,10 @@
         <v>288</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.5974723655</v>
+        <v>1690.5973219585</v>
       </c>
       <c r="O193" t="n">
-        <v>486892.072041264</v>
+        <v>486892.028724048</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8936,10 +8936,10 @@
         <v>1942</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O194" t="n">
-        <v>3010476.039224182</v>
+        <v>3010476.116114371</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8982,10 +8982,10 @@
         <v>22</v>
       </c>
       <c r="N195" t="n">
-        <v>1579.3906753247</v>
+        <v>1579.3905526316</v>
       </c>
       <c r="O195" t="n">
-        <v>34746.5948571434</v>
+        <v>34746.5921578952</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9028,10 +9028,10 @@
         <v>418</v>
       </c>
       <c r="N196" t="n">
-        <v>2403.5118666412</v>
+        <v>2403.5119649393</v>
       </c>
       <c r="O196" t="n">
-        <v>1004667.960256022</v>
+        <v>1004668.001344627</v>
       </c>
       <c r="P196" t="n">
         <v>3500</v>
@@ -10663,10 +10663,10 @@
         <v>159</v>
       </c>
       <c r="N233" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O233" t="n">
-        <v>426237.6122317572</v>
+        <v>426237.612173118</v>
       </c>
       <c r="P233" t="n">
         <v>4900</v>
@@ -11070,10 +11070,10 @@
         <v>113</v>
       </c>
       <c r="N242" t="n">
-        <v>4285.1954859611</v>
+        <v>4285.1954978355</v>
       </c>
       <c r="O242" t="n">
-        <v>484227.0899136043</v>
+        <v>484227.0912554114</v>
       </c>
       <c r="P242" t="n">
         <v>6900</v>
@@ -11329,10 +11329,10 @@
         <v>563</v>
       </c>
       <c r="N248" t="n">
-        <v>4605.2147274436</v>
+        <v>4605.2147318909</v>
       </c>
       <c r="O248" t="n">
-        <v>2592735.891550747</v>
+        <v>2592735.894054577</v>
       </c>
       <c r="P248" t="n">
         <v>7600</v>
@@ -11416,10 +11416,10 @@
         <v>32</v>
       </c>
       <c r="N250" t="n">
-        <v>11562.038478261</v>
+        <v>11562.038474114</v>
       </c>
       <c r="O250" t="n">
-        <v>369985.231304352</v>
+        <v>369985.231171648</v>
       </c>
       <c r="P250" t="n">
         <v>18500</v>
@@ -11462,10 +11462,10 @@
         <v>19</v>
       </c>
       <c r="N251" t="n">
-        <v>13513.643014706</v>
+        <v>13513.643059701</v>
       </c>
       <c r="O251" t="n">
-        <v>256759.217279414</v>
+        <v>256759.218134319</v>
       </c>
       <c r="P251" t="n">
         <v>21900</v>
@@ -11646,10 +11646,10 @@
         <v>94</v>
       </c>
       <c r="N255" t="n">
-        <v>27123.765223881</v>
+        <v>27123.765205993</v>
       </c>
       <c r="O255" t="n">
-        <v>2549633.931044814</v>
+        <v>2549633.929363342</v>
       </c>
       <c r="P255" t="n">
         <v>44500</v>
@@ -11912,10 +11912,10 @@
         <v>599</v>
       </c>
       <c r="N261" t="n">
-        <v>1561.0002330508</v>
+        <v>1561.0003094984</v>
       </c>
       <c r="O261" t="n">
-        <v>935039.1395974292</v>
+        <v>935039.1853895416</v>
       </c>
       <c r="P261" t="n">
         <v>2900</v>
@@ -12050,10 +12050,10 @@
         <v>188</v>
       </c>
       <c r="N264" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O264" t="n">
-        <v>1498350.631380885</v>
+        <v>1498350.63142858</v>
       </c>
       <c r="P264" t="n">
         <v>12900</v>
@@ -13121,10 +13121,10 @@
         <v>81</v>
       </c>
       <c r="N287" t="n">
-        <v>5218.1705520703</v>
+        <v>5218.1705541562</v>
       </c>
       <c r="O287" t="n">
-        <v>422671.8147176943</v>
+        <v>422671.8148866522</v>
       </c>
       <c r="P287" t="n">
         <v>8500</v>
@@ -13167,10 +13167,10 @@
         <v>1</v>
       </c>
       <c r="N288" t="n">
-        <v>1595.009375</v>
+        <v>1595.0093687708</v>
       </c>
       <c r="O288" t="n">
-        <v>1595.009375</v>
+        <v>1595.0093687708</v>
       </c>
       <c r="P288" t="n">
         <v>2600</v>
@@ -13213,10 +13213,10 @@
         <v>123</v>
       </c>
       <c r="N289" t="n">
-        <v>3610.6500258065</v>
+        <v>3610.6500258732</v>
       </c>
       <c r="O289" t="n">
-        <v>444109.9531741995</v>
+        <v>444109.9531824036</v>
       </c>
       <c r="P289" t="n">
         <v>5800</v>
@@ -13811,22 +13811,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M302" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="N302" t="n">
         <v>3646</v>
       </c>
       <c r="O302" t="n">
-        <v>875040</v>
+        <v>849518</v>
       </c>
       <c r="P302" t="n">
         <v>6900</v>
       </c>
       <c r="Q302" t="n">
-        <v>1656000</v>
+        <v>1607700</v>
       </c>
     </row>
     <row r="303">
@@ -13909,10 +13909,10 @@
         <v>824</v>
       </c>
       <c r="N304" t="n">
-        <v>1778.4726251691</v>
+        <v>1778.4726394558</v>
       </c>
       <c r="O304" t="n">
-        <v>1465461.443139338</v>
+        <v>1465461.454911579</v>
       </c>
       <c r="P304" t="n">
         <v>4900</v>
@@ -15893,10 +15893,10 @@
         <v>5</v>
       </c>
       <c r="N347" t="n">
-        <v>2252.2968774194</v>
+        <v>2252.2969855832</v>
       </c>
       <c r="O347" t="n">
-        <v>11261.484387097</v>
+        <v>11261.484927916</v>
       </c>
       <c r="P347" t="n">
         <v>3900</v>
@@ -16219,10 +16219,10 @@
         <v>324</v>
       </c>
       <c r="N354" t="n">
-        <v>2328.1187161545</v>
+        <v>2328.1187114504</v>
       </c>
       <c r="O354" t="n">
-        <v>754310.4640340579</v>
+        <v>754310.4625099297</v>
       </c>
       <c r="P354" t="n">
         <v>4500</v>
@@ -17093,10 +17093,10 @@
         <v>288</v>
       </c>
       <c r="N373" t="n">
-        <v>3903.7365705615</v>
+        <v>3903.736684492</v>
       </c>
       <c r="O373" t="n">
-        <v>1124276.132321712</v>
+        <v>1124276.165133696</v>
       </c>
       <c r="P373" t="n">
         <v>7500</v>
@@ -18100,10 +18100,10 @@
         <v>292</v>
       </c>
       <c r="N395" t="n">
-        <v>17075.989523481</v>
+        <v>17075.989523151</v>
       </c>
       <c r="O395" t="n">
-        <v>4986188.940856452</v>
+        <v>4986188.940760093</v>
       </c>
       <c r="P395" t="n">
         <v>27500</v>
@@ -19248,10 +19248,10 @@
         <v>1320</v>
       </c>
       <c r="N420" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O420" t="n">
-        <v>2001171.214248096</v>
+        <v>2001171.209903184</v>
       </c>
       <c r="P420" t="n">
         <v>2300</v>
@@ -19386,10 +19386,10 @@
         <v>120</v>
       </c>
       <c r="N423" t="n">
-        <v>2458.5131821149</v>
+        <v>2458.5130781975</v>
       </c>
       <c r="O423" t="n">
-        <v>295021.581853788</v>
+        <v>295021.5693837</v>
       </c>
       <c r="P423" t="n">
         <v>3500</v>
@@ -19432,10 +19432,10 @@
         <v>192</v>
       </c>
       <c r="N424" t="n">
-        <v>1771.0904491413</v>
+        <v>1771.0904111406</v>
       </c>
       <c r="O424" t="n">
-        <v>340049.3662351296</v>
+        <v>340049.3589389952</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
@@ -19478,10 +19478,10 @@
         <v>264</v>
       </c>
       <c r="N425" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839770425</v>
       </c>
       <c r="O425" t="n">
-        <v>548957.3827193545</v>
+        <v>548957.36993922</v>
       </c>
       <c r="P425" t="n">
         <v>2900</v>
@@ -19570,10 +19570,10 @@
         <v>216</v>
       </c>
       <c r="N427" t="n">
-        <v>3306.5951351351</v>
+        <v>3306.5946902655</v>
       </c>
       <c r="O427" t="n">
-        <v>714224.5491891816</v>
+        <v>714224.453097348</v>
       </c>
       <c r="P427" t="n">
         <v>4900</v>
@@ -19662,10 +19662,10 @@
         <v>120</v>
       </c>
       <c r="N429" t="n">
-        <v>2108.7918292683</v>
+        <v>2108.7920330806</v>
       </c>
       <c r="O429" t="n">
-        <v>253055.019512196</v>
+        <v>253055.043969672</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
@@ -19708,10 +19708,10 @@
         <v>144</v>
       </c>
       <c r="N430" t="n">
-        <v>2056.0833612094</v>
+        <v>2056.0831903662</v>
       </c>
       <c r="O430" t="n">
-        <v>296076.0040141536</v>
+        <v>296075.9794127328</v>
       </c>
       <c r="P430" t="n">
         <v>2900</v>
@@ -19800,10 +19800,10 @@
         <v>360</v>
       </c>
       <c r="N432" t="n">
-        <v>1655.9308652576</v>
+        <v>1655.9308592201</v>
       </c>
       <c r="O432" t="n">
-        <v>596135.111492736</v>
+        <v>596135.109319236</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
@@ -20030,10 +20030,10 @@
         <v>304</v>
       </c>
       <c r="N437" t="n">
-        <v>1592.278225957</v>
+        <v>1592.2785867446</v>
       </c>
       <c r="O437" t="n">
-        <v>484052.580690928</v>
+        <v>484052.6903703584</v>
       </c>
       <c r="P437" t="n">
         <v>2500</v>
@@ -20253,10 +20253,10 @@
         <v>800</v>
       </c>
       <c r="N442" t="n">
-        <v>1259.2745452499</v>
+        <v>1259.2745472973</v>
       </c>
       <c r="O442" t="n">
-        <v>1007419.63619992</v>
+        <v>1007419.63783784</v>
       </c>
       <c r="P442" t="n">
         <v>1900</v>
@@ -20476,10 +20476,10 @@
         <v>540</v>
       </c>
       <c r="N447" t="n">
-        <v>692.15222061657</v>
+        <v>692.15222920696</v>
       </c>
       <c r="O447" t="n">
-        <v>373762.1991329478</v>
+        <v>373762.2037717584</v>
       </c>
       <c r="P447" t="n">
         <v>1200</v>
@@ -21357,10 +21357,10 @@
         <v>2</v>
       </c>
       <c r="N466" t="n">
-        <v>527.91977777778</v>
+        <v>527.92037313433</v>
       </c>
       <c r="O466" t="n">
-        <v>1055.83955555556</v>
+        <v>1055.84074626866</v>
       </c>
       <c r="P466" t="n">
         <v>1300</v>
@@ -22475,10 +22475,10 @@
         <v>461</v>
       </c>
       <c r="N490" t="n">
-        <v>517.28943177426</v>
+        <v>517.28978235968</v>
       </c>
       <c r="O490" t="n">
-        <v>238470.4280479339</v>
+        <v>238470.5896678125</v>
       </c>
       <c r="P490" t="n">
         <v>900</v>
@@ -22898,10 +22898,10 @@
         <v>757</v>
       </c>
       <c r="N499" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O499" t="n">
-        <v>2354907.163894786</v>
+        <v>2354907.055746737</v>
       </c>
       <c r="P499" t="n">
         <v>4500</v>
@@ -23349,10 +23349,10 @@
         <v>19802</v>
       </c>
       <c r="N509" t="n">
-        <v>703.79518287415</v>
+        <v>703.79517569581</v>
       </c>
       <c r="O509" t="n">
-        <v>13936552.21127392</v>
+        <v>13936552.06912843</v>
       </c>
       <c r="P509" t="n">
         <v>900</v>
@@ -23856,10 +23856,10 @@
         <v>47</v>
       </c>
       <c r="N520" t="n">
-        <v>1595.5127943686</v>
+        <v>1595.5120596085</v>
       </c>
       <c r="O520" t="n">
-        <v>74989.1013353242</v>
+        <v>74989.0668015995</v>
       </c>
       <c r="P520" t="n">
         <v>2500</v>
@@ -24245,10 +24245,10 @@
         <v>159</v>
       </c>
       <c r="N528" t="n">
-        <v>2098.4049712644</v>
+        <v>2098.405</v>
       </c>
       <c r="O528" t="n">
-        <v>333646.3904310396</v>
+        <v>333646.395</v>
       </c>
       <c r="P528" t="n">
         <v>9500</v>
@@ -24343,10 +24343,10 @@
         <v>29</v>
       </c>
       <c r="N530" t="n">
-        <v>2832.1949275362</v>
+        <v>2832.195</v>
       </c>
       <c r="O530" t="n">
-        <v>82133.6528985498</v>
+        <v>82133.655</v>
       </c>
       <c r="P530" t="n">
         <v>12900</v>
@@ -28060,10 +28060,10 @@
         <v>648</v>
       </c>
       <c r="N608" t="n">
-        <v>665.32358222629</v>
+        <v>665.32359209922</v>
       </c>
       <c r="O608" t="n">
-        <v>431129.6812826359</v>
+        <v>431129.6876802946</v>
       </c>
       <c r="P608" t="n">
         <v>2900</v>
@@ -29095,10 +29095,10 @@
         <v>4</v>
       </c>
       <c r="N631" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O631" t="n">
-        <v>4854.728477842</v>
+        <v>4854.7285436892</v>
       </c>
       <c r="P631" t="n">
         <v>1500</v>
@@ -29364,10 +29364,10 @@
         <v>48</v>
       </c>
       <c r="N637" t="n">
-        <v>8922.2151190476</v>
+        <v>8922.2151807229</v>
       </c>
       <c r="O637" t="n">
-        <v>428266.3257142848</v>
+        <v>428266.3286746992</v>
       </c>
       <c r="P637" t="n">
         <v>8200</v>
@@ -29544,10 +29544,10 @@
         <v>346</v>
       </c>
       <c r="N641" t="n">
-        <v>22951.704839538</v>
+        <v>22951.704819588</v>
       </c>
       <c r="O641" t="n">
-        <v>7941289.874480148</v>
+        <v>7941289.867577448</v>
       </c>
       <c r="P641" t="n">
         <v>37900</v>
@@ -29682,10 +29682,10 @@
         <v>8</v>
       </c>
       <c r="N644" t="n">
-        <v>1547.8825373134</v>
+        <v>1547.8826153846</v>
       </c>
       <c r="O644" t="n">
-        <v>12383.0602985072</v>
+        <v>12383.0609230768</v>
       </c>
       <c r="P644" t="n">
         <v>5500</v>
@@ -29871,10 +29871,10 @@
         <v>3200</v>
       </c>
       <c r="N648" t="n">
-        <v>220.00534867624</v>
+        <v>220.00509068498</v>
       </c>
       <c r="O648" t="n">
-        <v>704017.115763968</v>
+        <v>704016.290191936</v>
       </c>
       <c r="P648" t="n">
         <v>260</v>
@@ -30842,10 +30842,10 @@
         <v>176</v>
       </c>
       <c r="N669" t="n">
-        <v>1319.3608823529</v>
+        <v>1319.360887574</v>
       </c>
       <c r="O669" t="n">
-        <v>232207.5152941104</v>
+        <v>232207.516213024</v>
       </c>
       <c r="P669" t="n">
         <v>3500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.307219032</v>
+        <v>1811.307345576</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.307219032</v>
+        <v>1811.307345576</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464660832</v>
+        <v>3376.7464651163</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.876017549</v>
+        <v>2985043.875162809</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -2175,10 +2175,10 @@
         <v>46</v>
       </c>
       <c r="N44" t="n">
-        <v>141416.88456026</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O44" t="n">
-        <v>6505176.68977196</v>
+        <v>6505176.690457359</v>
       </c>
       <c r="P44" t="n">
         <v>251900</v>
@@ -3087,10 +3087,10 @@
         <v>228</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O65" t="n">
-        <v>1125706.717293686</v>
+        <v>1125706.717321434</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3308,10 +3308,10 @@
         <v>1295</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0595661432</v>
+        <v>1098.0597873486</v>
       </c>
       <c r="O70" t="n">
-        <v>1421987.138155444</v>
+        <v>1421987.424616437</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4241,10 +4241,10 @@
         <v>741</v>
       </c>
       <c r="N91" t="n">
-        <v>2582.2557353886</v>
+        <v>2582.2557142857</v>
       </c>
       <c r="O91" t="n">
-        <v>1913451.499922953</v>
+        <v>1913451.484285704</v>
       </c>
       <c r="P91" t="n">
         <v>4500</v>
@@ -4333,10 +4333,10 @@
         <v>720</v>
       </c>
       <c r="N93" t="n">
-        <v>5216.8961202577</v>
+        <v>5216.8961124659</v>
       </c>
       <c r="O93" t="n">
-        <v>3756165.206585544</v>
+        <v>3756165.200975448</v>
       </c>
       <c r="P93" t="n">
         <v>8500</v>
@@ -4564,10 +4564,10 @@
         <v>3199</v>
       </c>
       <c r="N98" t="n">
-        <v>3158.8608260699</v>
+        <v>3158.8608262318</v>
       </c>
       <c r="O98" t="n">
-        <v>10105195.78259761</v>
+        <v>10105195.78311553</v>
       </c>
       <c r="P98" t="n">
         <v>5600</v>
@@ -4610,10 +4610,10 @@
         <v>80</v>
       </c>
       <c r="N99" t="n">
-        <v>3841.6247928994</v>
+        <v>3841.6248214286</v>
       </c>
       <c r="O99" t="n">
-        <v>307329.983431952</v>
+        <v>307329.985714288</v>
       </c>
       <c r="P99" t="n">
         <v>6900</v>
@@ -4694,22 +4694,22 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M101" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="N101" t="n">
         <v>3230.0672177419</v>
       </c>
       <c r="O101" t="n">
-        <v>503890.4859677364</v>
+        <v>465129.6793548336</v>
       </c>
       <c r="P101" t="n">
         <v>6200</v>
       </c>
       <c r="Q101" t="n">
-        <v>967200</v>
+        <v>892800</v>
       </c>
     </row>
     <row r="102">
@@ -5286,22 +5286,22 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M114" t="n">
-        <v>167</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
         <v>4357.55</v>
       </c>
       <c r="O114" t="n">
-        <v>727710.85</v>
+        <v>13072.65</v>
       </c>
       <c r="P114" t="n">
         <v>7500</v>
       </c>
       <c r="Q114" t="n">
-        <v>1252500</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="115">
@@ -5384,10 +5384,10 @@
         <v>312</v>
       </c>
       <c r="N116" t="n">
-        <v>4890.9300487805</v>
+        <v>4890.93004884</v>
       </c>
       <c r="O116" t="n">
-        <v>1525970.175219516</v>
+        <v>1525970.17523808</v>
       </c>
       <c r="P116" t="n">
         <v>8200</v>
@@ -5883,10 +5883,10 @@
         <v>288</v>
       </c>
       <c r="N127" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="O127" t="n">
-        <v>1035145.157383181</v>
+        <v>1035145.152</v>
       </c>
       <c r="P127" t="n">
         <v>6500</v>
@@ -5924,10 +5924,10 @@
         <v>108</v>
       </c>
       <c r="N128" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.850037037</v>
       </c>
       <c r="O128" t="n">
-        <v>350011.8035179164</v>
+        <v>350011.803999996</v>
       </c>
       <c r="P128" t="n">
         <v>5200</v>
@@ -6789,10 +6789,10 @@
         <v>210</v>
       </c>
       <c r="N147" t="n">
-        <v>3041.660013245</v>
+        <v>3041.6600132802</v>
       </c>
       <c r="O147" t="n">
-        <v>638748.6027814499</v>
+        <v>638748.6027888421</v>
       </c>
       <c r="P147" t="n">
         <v>5500</v>
@@ -7001,22 +7001,22 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M152" t="n">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="N152" t="n">
-        <v>1592.566762142</v>
+        <v>1592.5667254408</v>
       </c>
       <c r="O152" t="n">
-        <v>487325.429215452</v>
+        <v>383808.5808312328</v>
       </c>
       <c r="P152" t="n">
         <v>3900</v>
       </c>
       <c r="Q152" t="n">
-        <v>1193400</v>
+        <v>939900</v>
       </c>
     </row>
     <row r="153">
@@ -7401,22 +7401,22 @@
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M161" t="n">
-        <v>1622</v>
+        <v>1612</v>
       </c>
       <c r="N161" t="n">
         <v>4648.6</v>
       </c>
       <c r="O161" t="n">
-        <v>7540029.2</v>
+        <v>7493543.2</v>
       </c>
       <c r="P161" t="n">
         <v>8900</v>
       </c>
       <c r="Q161" t="n">
-        <v>14435800</v>
+        <v>14346800</v>
       </c>
     </row>
     <row r="162">
@@ -8084,22 +8084,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M176" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N176" t="n">
         <v>16897</v>
       </c>
       <c r="O176" t="n">
-        <v>1774185</v>
+        <v>1571421</v>
       </c>
       <c r="P176" t="n">
         <v>27900</v>
       </c>
       <c r="Q176" t="n">
-        <v>2929500</v>
+        <v>2594700</v>
       </c>
     </row>
     <row r="177">
@@ -8792,22 +8792,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M191" t="n">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="N191" t="n">
-        <v>1630.9235901027</v>
+        <v>1630.9236367936</v>
       </c>
       <c r="O191" t="n">
-        <v>1239501.928478052</v>
+        <v>1213407.185774439</v>
       </c>
       <c r="P191" t="n">
         <v>2500</v>
       </c>
       <c r="Q191" t="n">
-        <v>1900000</v>
+        <v>1860000</v>
       </c>
     </row>
     <row r="192">
@@ -8884,22 +8884,22 @@
         <v>0</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M193" t="n">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.5972035794</v>
+        <v>1690.5971524664</v>
       </c>
       <c r="O193" t="n">
-        <v>486891.9946308672</v>
+        <v>459842.4254708608</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
       </c>
       <c r="Q193" t="n">
-        <v>835200</v>
+        <v>788800</v>
       </c>
     </row>
     <row r="194">
@@ -8930,22 +8930,22 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M194" t="n">
-        <v>1942</v>
+        <v>1906</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O194" t="n">
-        <v>3010476.117527952</v>
+        <v>2954669.187091729</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
       </c>
       <c r="Q194" t="n">
-        <v>4855000</v>
+        <v>4765000</v>
       </c>
     </row>
     <row r="195">
@@ -8982,10 +8982,10 @@
         <v>22</v>
       </c>
       <c r="N195" t="n">
-        <v>1579.3905526316</v>
+        <v>1579.3904266667</v>
       </c>
       <c r="O195" t="n">
-        <v>34746.5921578952</v>
+        <v>34746.5893866674</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9028,10 +9028,10 @@
         <v>418</v>
       </c>
       <c r="N196" t="n">
-        <v>2403.5119996136</v>
+        <v>2403.5120742613</v>
       </c>
       <c r="O196" t="n">
-        <v>1004668.015838485</v>
+        <v>1004668.047041223</v>
       </c>
       <c r="P196" t="n">
         <v>3500</v>
@@ -10112,10 +10112,10 @@
         <v>361</v>
       </c>
       <c r="N220" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O220" t="n">
-        <v>1515070.983011634</v>
+        <v>1515070.983264911</v>
       </c>
       <c r="P220" t="n">
         <v>5900</v>
@@ -10240,10 +10240,10 @@
         <v>19</v>
       </c>
       <c r="N223" t="n">
-        <v>7537.4721969697</v>
+        <v>7537.4722307692</v>
       </c>
       <c r="O223" t="n">
-        <v>143211.9717424243</v>
+        <v>143211.9723846148</v>
       </c>
       <c r="P223" t="n">
         <v>8900</v>
@@ -11070,10 +11070,10 @@
         <v>113</v>
       </c>
       <c r="N242" t="n">
-        <v>4285.1955097614</v>
+        <v>4285.1955337691</v>
       </c>
       <c r="O242" t="n">
-        <v>484227.0926030382</v>
+        <v>484227.0953159083</v>
       </c>
       <c r="P242" t="n">
         <v>6900</v>
@@ -11329,10 +11329,10 @@
         <v>563</v>
       </c>
       <c r="N248" t="n">
-        <v>4605.2147318909</v>
+        <v>4605.2147408106</v>
       </c>
       <c r="O248" t="n">
-        <v>2592735.894054577</v>
+        <v>2592735.899076368</v>
       </c>
       <c r="P248" t="n">
         <v>7600</v>
@@ -11912,10 +11912,10 @@
         <v>599</v>
       </c>
       <c r="N261" t="n">
-        <v>1561.0003205128</v>
+        <v>1561.0009152542</v>
       </c>
       <c r="O261" t="n">
-        <v>935039.1919871672</v>
+        <v>935039.5482372658</v>
       </c>
       <c r="P261" t="n">
         <v>2900</v>
@@ -12235,10 +12235,10 @@
         <v>256</v>
       </c>
       <c r="N268" t="n">
-        <v>548.14720461095</v>
+        <v>548.1471884058</v>
       </c>
       <c r="O268" t="n">
-        <v>140325.6843804032</v>
+        <v>140325.6802318848</v>
       </c>
       <c r="P268" t="n">
         <v>2000</v>
@@ -13909,10 +13909,10 @@
         <v>824</v>
       </c>
       <c r="N304" t="n">
-        <v>1778.4726299141</v>
+        <v>1778.4726458554</v>
       </c>
       <c r="O304" t="n">
-        <v>1465461.447049218</v>
+        <v>1465461.46018485</v>
       </c>
       <c r="P304" t="n">
         <v>4900</v>
@@ -14179,22 +14179,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M310" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N310" t="n">
         <v>16058</v>
       </c>
       <c r="O310" t="n">
-        <v>2296294</v>
+        <v>2216004</v>
       </c>
       <c r="P310" t="n">
         <v>25900</v>
       </c>
       <c r="Q310" t="n">
-        <v>3703700</v>
+        <v>3574200</v>
       </c>
     </row>
     <row r="311">
@@ -16219,10 +16219,10 @@
         <v>324</v>
       </c>
       <c r="N354" t="n">
-        <v>2328.1187114504</v>
+        <v>2328.1187098747</v>
       </c>
       <c r="O354" t="n">
-        <v>754310.4625099297</v>
+        <v>754310.4619994028</v>
       </c>
       <c r="P354" t="n">
         <v>4500</v>
@@ -17087,22 +17087,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M373" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N373" t="n">
         <v>3903.7366972477</v>
       </c>
       <c r="O373" t="n">
-        <v>1124276.168807338</v>
+        <v>1077431.328440365</v>
       </c>
       <c r="P373" t="n">
         <v>7500</v>
       </c>
       <c r="Q373" t="n">
-        <v>2160000</v>
+        <v>2070000</v>
       </c>
     </row>
     <row r="374">
@@ -17266,22 +17266,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M377" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="N377" t="n">
         <v>5869.1726202661</v>
       </c>
       <c r="O377" t="n">
-        <v>281720.2857727728</v>
+        <v>140860.1428863864</v>
       </c>
       <c r="P377" t="n">
         <v>9500</v>
       </c>
       <c r="Q377" t="n">
-        <v>456000</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="378">
@@ -18054,10 +18054,10 @@
         <v>292</v>
       </c>
       <c r="N394" t="n">
-        <v>17075.989523151</v>
+        <v>17075.989522822</v>
       </c>
       <c r="O394" t="n">
-        <v>4986188.940760093</v>
+        <v>4986188.940664024</v>
       </c>
       <c r="P394" t="n">
         <v>27500</v>
@@ -19202,10 +19202,10 @@
         <v>1320</v>
       </c>
       <c r="N419" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O419" t="n">
-        <v>2001171.213628884</v>
+        <v>2001171.209591796</v>
       </c>
       <c r="P419" t="n">
         <v>2300</v>
@@ -19334,22 +19334,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M422" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="N422" t="n">
-        <v>2458.5131328074</v>
+        <v>2458.5130759032</v>
       </c>
       <c r="O422" t="n">
-        <v>295021.575936888</v>
+        <v>118008.6276433536</v>
       </c>
       <c r="P422" t="n">
         <v>3500</v>
       </c>
       <c r="Q422" t="n">
-        <v>420000</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="423">
@@ -19380,22 +19380,22 @@
         <v>0</v>
       </c>
       <c r="L423" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M423" t="n">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="N423" t="n">
         <v>1771.0904111406</v>
       </c>
       <c r="O423" t="n">
-        <v>340049.3589389952</v>
+        <v>85012.33973474881</v>
       </c>
       <c r="P423" t="n">
         <v>2500</v>
       </c>
       <c r="Q423" t="n">
-        <v>480000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="424">
@@ -19426,22 +19426,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M424" t="n">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="N424" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839709361</v>
       </c>
       <c r="O424" t="n">
-        <v>548957.3827193545</v>
+        <v>349336.5071172648</v>
       </c>
       <c r="P424" t="n">
         <v>2900</v>
       </c>
       <c r="Q424" t="n">
-        <v>765600</v>
+        <v>487200</v>
       </c>
     </row>
     <row r="425">
@@ -19478,10 +19478,10 @@
         <v>72</v>
       </c>
       <c r="N425" t="n">
-        <v>1803.0156051587</v>
+        <v>1803.0156237558</v>
       </c>
       <c r="O425" t="n">
-        <v>129817.1235714264</v>
+        <v>129817.1249104176</v>
       </c>
       <c r="P425" t="n">
         <v>2500</v>
@@ -19518,22 +19518,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M426" t="n">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="N426" t="n">
-        <v>3306.5951153324</v>
+        <v>3306.5946745562</v>
       </c>
       <c r="O426" t="n">
-        <v>714224.5449117984</v>
+        <v>515828.7692307672</v>
       </c>
       <c r="P426" t="n">
         <v>4900</v>
       </c>
       <c r="Q426" t="n">
-        <v>1058400</v>
+        <v>764400</v>
       </c>
     </row>
     <row r="427">
@@ -19564,22 +19564,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M427" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="N427" t="n">
-        <v>2122.1638529227</v>
+        <v>2122.1638509903</v>
       </c>
       <c r="O427" t="n">
-        <v>407455.4597611583</v>
+        <v>0</v>
       </c>
       <c r="P427" t="n">
         <v>2900</v>
       </c>
       <c r="Q427" t="n">
-        <v>556800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -19616,10 +19616,10 @@
         <v>120</v>
       </c>
       <c r="N428" t="n">
-        <v>2108.7920330806</v>
+        <v>2108.792083045</v>
       </c>
       <c r="O428" t="n">
-        <v>253055.043969672</v>
+        <v>253055.0499654</v>
       </c>
       <c r="P428" t="n">
         <v>2900</v>
@@ -19662,10 +19662,10 @@
         <v>144</v>
       </c>
       <c r="N429" t="n">
-        <v>2056.0831723454</v>
+        <v>2056.0829891304</v>
       </c>
       <c r="O429" t="n">
-        <v>296075.9768177376</v>
+        <v>296075.9504347777</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
@@ -19702,22 +19702,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M430" t="n">
-        <v>216</v>
+        <v>90</v>
       </c>
       <c r="N430" t="n">
-        <v>3224.5688003933</v>
+        <v>3224.5688090551</v>
       </c>
       <c r="O430" t="n">
-        <v>696506.8608849528</v>
+        <v>290211.192814959</v>
       </c>
       <c r="P430" t="n">
         <v>4500</v>
       </c>
       <c r="Q430" t="n">
-        <v>972000</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="431">
@@ -19754,10 +19754,10 @@
         <v>360</v>
       </c>
       <c r="N431" t="n">
-        <v>1655.9308592201</v>
+        <v>1655.9308045213</v>
       </c>
       <c r="O431" t="n">
-        <v>596135.109319236</v>
+        <v>596135.089627668</v>
       </c>
       <c r="P431" t="n">
         <v>2500</v>
@@ -19984,10 +19984,10 @@
         <v>304</v>
       </c>
       <c r="N436" t="n">
-        <v>1592.2786119257</v>
+        <v>1592.2787749004</v>
       </c>
       <c r="O436" t="n">
-        <v>484052.6980254128</v>
+        <v>484052.7475697217</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -20161,10 +20161,10 @@
         <v>24</v>
       </c>
       <c r="N440" t="n">
-        <v>2546.9839186296</v>
+        <v>2546.9838660907</v>
       </c>
       <c r="O440" t="n">
-        <v>61127.6140471104</v>
+        <v>61127.6127861768</v>
       </c>
       <c r="P440" t="n">
         <v>3900</v>
@@ -20207,10 +20207,10 @@
         <v>800</v>
       </c>
       <c r="N441" t="n">
-        <v>1259.2745472973</v>
+        <v>1259.274561681</v>
       </c>
       <c r="O441" t="n">
-        <v>1007419.63783784</v>
+        <v>1007419.6493448</v>
       </c>
       <c r="P441" t="n">
         <v>1900</v>
@@ -20340,10 +20340,10 @@
         <v>48</v>
       </c>
       <c r="N444" t="n">
-        <v>2556.7459385666</v>
+        <v>2556.7460207612</v>
       </c>
       <c r="O444" t="n">
-        <v>122723.8050511968</v>
+        <v>122723.8089965376</v>
       </c>
       <c r="P444" t="n">
         <v>3900</v>
@@ -20424,22 +20424,22 @@
         <v>0</v>
       </c>
       <c r="L446" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M446" t="n">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="N446" t="n">
         <v>692.15222920696</v>
       </c>
       <c r="O446" t="n">
-        <v>373762.2037717584</v>
+        <v>357150.5502707913</v>
       </c>
       <c r="P446" t="n">
         <v>1200</v>
       </c>
       <c r="Q446" t="n">
-        <v>648000</v>
+        <v>619200</v>
       </c>
     </row>
     <row r="447">
@@ -20473,22 +20473,22 @@
         <v>0</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M447" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="N447" t="n">
         <v>18491</v>
       </c>
       <c r="O447" t="n">
-        <v>1608717</v>
+        <v>1405316</v>
       </c>
       <c r="P447" t="n">
         <v>13500</v>
       </c>
       <c r="Q447" t="n">
-        <v>1174500</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="448">
@@ -22423,22 +22423,22 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="M489" t="n">
-        <v>461</v>
+        <v>149</v>
       </c>
       <c r="N489" t="n">
-        <v>517.2898138359</v>
+        <v>517.28990087531</v>
       </c>
       <c r="O489" t="n">
-        <v>238470.6041783499</v>
+        <v>77076.19523042119</v>
       </c>
       <c r="P489" t="n">
         <v>900</v>
       </c>
       <c r="Q489" t="n">
-        <v>414900</v>
+        <v>134100</v>
       </c>
     </row>
     <row r="490">
@@ -22852,10 +22852,10 @@
         <v>757</v>
       </c>
       <c r="N498" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O498" t="n">
-        <v>2354907.032745823</v>
+        <v>2354906.942230046</v>
       </c>
       <c r="P498" t="n">
         <v>4500</v>
@@ -22895,22 +22895,22 @@
         <v>0</v>
       </c>
       <c r="L499" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M499" t="n">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="N499" t="n">
         <v>9131.92</v>
       </c>
       <c r="O499" t="n">
-        <v>1862911.68</v>
+        <v>1424579.52</v>
       </c>
       <c r="P499" t="n">
         <v>14000</v>
       </c>
       <c r="Q499" t="n">
-        <v>2856000</v>
+        <v>2184000</v>
       </c>
     </row>
     <row r="500">
@@ -23303,10 +23303,10 @@
         <v>19802</v>
       </c>
       <c r="N508" t="n">
-        <v>703.795175</v>
+        <v>703.79516919374</v>
       </c>
       <c r="O508" t="n">
-        <v>13936552.05535</v>
+        <v>13936551.94037444</v>
       </c>
       <c r="P508" t="n">
         <v>900</v>
@@ -23810,10 +23810,10 @@
         <v>47</v>
       </c>
       <c r="N519" t="n">
-        <v>1595.5123423818</v>
+        <v>1595.5119633274</v>
       </c>
       <c r="O519" t="n">
-        <v>74989.0800919446</v>
+        <v>74989.06227638781</v>
       </c>
       <c r="P519" t="n">
         <v>2500</v>
@@ -26593,22 +26593,22 @@
         <v>0</v>
       </c>
       <c r="L577" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M577" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N577" t="n">
         <v>10737.526170213</v>
       </c>
       <c r="O577" t="n">
-        <v>257700.628085112</v>
+        <v>225488.049574473</v>
       </c>
       <c r="P577" t="n">
         <v>18900</v>
       </c>
       <c r="Q577" t="n">
-        <v>453600</v>
+        <v>396900</v>
       </c>
     </row>
     <row r="578">
@@ -27824,10 +27824,10 @@
         <v>1105</v>
       </c>
       <c r="N603" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O603" t="n">
-        <v>7786868.510096689</v>
+        <v>7786868.5098516</v>
       </c>
       <c r="P603" t="n">
         <v>9900</v>
@@ -29498,10 +29498,10 @@
         <v>346</v>
       </c>
       <c r="N640" t="n">
-        <v>22951.704812903</v>
+        <v>22951.704799483</v>
       </c>
       <c r="O640" t="n">
-        <v>7941289.865264438</v>
+        <v>7941289.860621118</v>
       </c>
       <c r="P640" t="n">
         <v>37900</v>
@@ -29585,10 +29585,10 @@
         <v>43</v>
       </c>
       <c r="N642" t="n">
-        <v>4985.4053097345</v>
+        <v>4985.4053571429</v>
       </c>
       <c r="O642" t="n">
-        <v>214372.4283185835</v>
+        <v>214372.4303571447</v>
       </c>
       <c r="P642" t="n">
         <v>7900</v>
@@ -30049,22 +30049,22 @@
         <v>0</v>
       </c>
       <c r="L652" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M652" t="n">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="N652" t="n">
         <v>1952.66</v>
       </c>
       <c r="O652" t="n">
-        <v>757632.0800000001</v>
+        <v>728342.1800000001</v>
       </c>
       <c r="P652" t="n">
         <v>3500</v>
       </c>
       <c r="Q652" t="n">
-        <v>1358000</v>
+        <v>1305500</v>
       </c>
     </row>
     <row r="653">
@@ -31085,10 +31085,10 @@
         <v>95</v>
       </c>
       <c r="N674" t="n">
-        <v>4171.6687</v>
+        <v>4171.6686912752</v>
       </c>
       <c r="O674" t="n">
-        <v>396308.5265</v>
+        <v>396308.525671144</v>
       </c>
       <c r="P674" t="n">
         <v>5500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1234,10 +1234,10 @@
         <v>194</v>
       </c>
       <c r="N21" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O21" t="n">
-        <v>761806.3968066316</v>
+        <v>761806.3965145259</v>
       </c>
       <c r="P21" t="n">
         <v>4800</v>
@@ -1878,10 +1878,10 @@
         <v>18</v>
       </c>
       <c r="N37" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O37" t="n">
-        <v>282815.386609446</v>
+        <v>282815.386293096</v>
       </c>
       <c r="P37" t="n">
         <v>28500</v>
@@ -3308,10 +3308,10 @@
         <v>1295</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0597873486</v>
+        <v>1098.0598890693</v>
       </c>
       <c r="O70" t="n">
-        <v>1421987.424616437</v>
+        <v>1421987.556344743</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4564,10 +4564,10 @@
         <v>3199</v>
       </c>
       <c r="N98" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O98" t="n">
-        <v>10105195.78311553</v>
+        <v>10109651.99175118</v>
       </c>
       <c r="P98" t="n">
         <v>5600</v>
@@ -4610,10 +4610,10 @@
         <v>80</v>
       </c>
       <c r="N99" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O99" t="n">
-        <v>307329.985714288</v>
+        <v>308554.407968128</v>
       </c>
       <c r="P99" t="n">
         <v>6900</v>
@@ -5883,10 +5883,10 @@
         <v>288</v>
       </c>
       <c r="N127" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O127" t="n">
-        <v>1035145.152</v>
+        <v>1035145.150919338</v>
       </c>
       <c r="P127" t="n">
         <v>6500</v>
@@ -6201,10 +6201,10 @@
         <v>1746</v>
       </c>
       <c r="N134" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O134" t="n">
-        <v>3650624.1</v>
+        <v>3651114.445748842</v>
       </c>
       <c r="P134" t="n">
         <v>2900</v>
@@ -6917,10 +6917,10 @@
         <v>1938</v>
       </c>
       <c r="N150" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O150" t="n">
-        <v>8473344.511709735</v>
+        <v>8473344.511819039</v>
       </c>
       <c r="P150" t="n">
         <v>7500</v>
@@ -7007,10 +7007,10 @@
         <v>241</v>
       </c>
       <c r="N152" t="n">
-        <v>1592.5667254408</v>
+        <v>1600.6713740458</v>
       </c>
       <c r="O152" t="n">
-        <v>383808.5808312328</v>
+        <v>385761.8011450378</v>
       </c>
       <c r="P152" t="n">
         <v>3900</v>
@@ -8281,10 +8281,10 @@
         <v>61</v>
       </c>
       <c r="N180" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O180" t="n">
-        <v>229457.6</v>
+        <v>230298.1040293068</v>
       </c>
       <c r="P180" t="n">
         <v>6900</v>
@@ -8798,10 +8798,10 @@
         <v>744</v>
       </c>
       <c r="N191" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O191" t="n">
-        <v>1213407.19347402</v>
+        <v>1213407.20057059</v>
       </c>
       <c r="P191" t="n">
         <v>2500</v>
@@ -8890,10 +8890,10 @@
         <v>272</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.5969977427</v>
+        <v>1690.5969630746</v>
       </c>
       <c r="O193" t="n">
-        <v>459842.3833860144</v>
+        <v>459842.3739562912</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8936,10 +8936,10 @@
         <v>1906</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O194" t="n">
-        <v>2954669.191307039</v>
+        <v>2954669.201867042</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8982,10 +8982,10 @@
         <v>22</v>
       </c>
       <c r="N195" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="O195" t="n">
-        <v>34746.5893866674</v>
+        <v>34746.5882573722</v>
       </c>
       <c r="P195" t="n">
         <v>2900</v>
@@ -9028,10 +9028,10 @@
         <v>418</v>
       </c>
       <c r="N196" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O196" t="n">
-        <v>1004668.057857015</v>
+        <v>1004668.064763964</v>
       </c>
       <c r="P196" t="n">
         <v>3500</v>
@@ -10663,10 +10663,10 @@
         <v>159</v>
       </c>
       <c r="N233" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O233" t="n">
-        <v>426237.611518356</v>
+        <v>426237.6114881619</v>
       </c>
       <c r="P233" t="n">
         <v>4900</v>
@@ -11912,10 +11912,10 @@
         <v>599</v>
       </c>
       <c r="N261" t="n">
-        <v>1561.0009337861</v>
+        <v>1561.000952381</v>
       </c>
       <c r="O261" t="n">
-        <v>935039.5593378738</v>
+        <v>935039.5704762189</v>
       </c>
       <c r="P261" t="n">
         <v>2900</v>
@@ -12799,10 +12799,10 @@
         <v>122</v>
       </c>
       <c r="N280" t="n">
-        <v>3113.8900274725</v>
+        <v>3113.8900276243</v>
       </c>
       <c r="O280" t="n">
-        <v>379894.583351645</v>
+        <v>379894.5833701646</v>
       </c>
       <c r="P280" t="n">
         <v>5000</v>
@@ -13213,10 +13213,10 @@
         <v>123</v>
       </c>
       <c r="N289" t="n">
-        <v>3610.6500258732</v>
+        <v>3610.6500261438</v>
       </c>
       <c r="O289" t="n">
-        <v>444109.9531824036</v>
+        <v>444109.9532156874</v>
       </c>
       <c r="P289" t="n">
         <v>5800</v>
@@ -16863,10 +16863,10 @@
         <v>137</v>
       </c>
       <c r="N368" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O368" t="n">
-        <v>672371.626639209</v>
+        <v>679084.1553577431</v>
       </c>
       <c r="P368" t="n">
         <v>8200</v>
@@ -19478,10 +19478,10 @@
         <v>72</v>
       </c>
       <c r="N425" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O425" t="n">
-        <v>129817.1249104176</v>
+        <v>129817.1258530128</v>
       </c>
       <c r="P425" t="n">
         <v>2500</v>
@@ -19524,10 +19524,10 @@
         <v>156</v>
       </c>
       <c r="N426" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O426" t="n">
-        <v>515828.7692307672</v>
+        <v>515828.7680000052</v>
       </c>
       <c r="P426" t="n">
         <v>4900</v>
@@ -19616,10 +19616,10 @@
         <v>144</v>
       </c>
       <c r="N428" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O428" t="n">
-        <v>296075.9497484736</v>
+        <v>296075.9494049616</v>
       </c>
       <c r="P428" t="n">
         <v>2900</v>
@@ -19708,10 +19708,10 @@
         <v>360</v>
       </c>
       <c r="N430" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O430" t="n">
-        <v>596135.089627668</v>
+        <v>596135.083011336</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -19938,10 +19938,10 @@
         <v>304</v>
       </c>
       <c r="N435" t="n">
-        <v>1592.27881</v>
+        <v>1592.2788188188</v>
       </c>
       <c r="O435" t="n">
-        <v>484052.75824</v>
+        <v>484052.7609209152</v>
       </c>
       <c r="P435" t="n">
         <v>2500</v>
@@ -21173,10 +21173,10 @@
         <v>272</v>
       </c>
       <c r="N462" t="n">
-        <v>3629.36</v>
+        <v>3642.7032352941</v>
       </c>
       <c r="O462" t="n">
-        <v>987185.92</v>
+        <v>990815.2799999953</v>
       </c>
       <c r="P462" t="n">
         <v>3900</v>
@@ -21638,10 +21638,10 @@
         <v>60</v>
       </c>
       <c r="N472" t="n">
-        <v>6090.22</v>
+        <v>6160.2225287356</v>
       </c>
       <c r="O472" t="n">
-        <v>365413.2</v>
+        <v>369613.351724136</v>
       </c>
       <c r="P472" t="n">
         <v>8500</v>
@@ -22383,10 +22383,10 @@
         <v>149</v>
       </c>
       <c r="N488" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O488" t="n">
-        <v>77076.20141335351</v>
+        <v>77076.20565090455</v>
       </c>
       <c r="P488" t="n">
         <v>900</v>
@@ -22806,10 +22806,10 @@
         <v>757</v>
       </c>
       <c r="N497" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O497" t="n">
-        <v>2354906.926365218</v>
+        <v>2354906.918403698</v>
       </c>
       <c r="P497" t="n">
         <v>4500</v>
@@ -23257,10 +23257,10 @@
         <v>19802</v>
       </c>
       <c r="N507" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O507" t="n">
-        <v>13936551.87701992</v>
+        <v>13936551.83781335</v>
       </c>
       <c r="P507" t="n">
         <v>900</v>
@@ -23398,10 +23398,10 @@
         <v>78</v>
       </c>
       <c r="N510" t="n">
-        <v>2501.3849767442</v>
+        <v>2501.384953271</v>
       </c>
       <c r="O510" t="n">
-        <v>195108.0281860476</v>
+        <v>195108.026355138</v>
       </c>
       <c r="P510" t="n">
         <v>4100</v>
@@ -24153,10 +24153,10 @@
         <v>159</v>
       </c>
       <c r="N526" t="n">
-        <v>2098.4050144928</v>
+        <v>2110.6406122449</v>
       </c>
       <c r="O526" t="n">
-        <v>333646.3973043552</v>
+        <v>335591.857346939</v>
       </c>
       <c r="P526" t="n">
         <v>9500</v>
@@ -25266,10 +25266,10 @@
         <v>33</v>
       </c>
       <c r="N549" t="n">
-        <v>2992.5689285714</v>
+        <v>3065.5584146341</v>
       </c>
       <c r="O549" t="n">
-        <v>98754.77464285621</v>
+        <v>101163.4276829253</v>
       </c>
       <c r="P549" t="n">
         <v>6000</v>
@@ -25312,10 +25312,10 @@
         <v>165</v>
       </c>
       <c r="N550" t="n">
-        <v>875.69016806723</v>
+        <v>883.11127118644</v>
       </c>
       <c r="O550" t="n">
-        <v>144488.8777310929</v>
+        <v>145713.3597457626</v>
       </c>
       <c r="P550" t="n">
         <v>4500</v>
@@ -27968,10 +27968,10 @@
         <v>648</v>
       </c>
       <c r="N606" t="n">
-        <v>665.32359209922</v>
+        <v>665.32360534809</v>
       </c>
       <c r="O606" t="n">
-        <v>431129.6876802946</v>
+        <v>431129.6962655623</v>
       </c>
       <c r="P606" t="n">
         <v>2900</v>
@@ -30331,10 +30331,10 @@
         <v>94</v>
       </c>
       <c r="N658" t="n">
-        <v>5280</v>
+        <v>5305.2631578947</v>
       </c>
       <c r="O658" t="n">
-        <v>496320</v>
+        <v>498694.7368421018</v>
       </c>
       <c r="P658" t="n">
         <v>6900</v>
@@ -30750,10 +30750,10 @@
         <v>176</v>
       </c>
       <c r="N667" t="n">
-        <v>1319.360887574</v>
+        <v>1327.2142261905</v>
       </c>
       <c r="O667" t="n">
-        <v>232207.516213024</v>
+        <v>233589.703809528</v>
       </c>
       <c r="P667" t="n">
         <v>3500</v>
@@ -30993,10 +30993,10 @@
         <v>158</v>
       </c>
       <c r="N672" t="n">
-        <v>2539.5715559441</v>
+        <v>2539.5715696649</v>
       </c>
       <c r="O672" t="n">
-        <v>401252.3058391678</v>
+        <v>401252.3080070542</v>
       </c>
       <c r="P672" t="n">
         <v>3500</v>
@@ -31039,10 +31039,10 @@
         <v>95</v>
       </c>
       <c r="N673" t="n">
-        <v>4171.6686912752</v>
+        <v>4171.6686824324</v>
       </c>
       <c r="O673" t="n">
-        <v>396308.525671144</v>
+        <v>396308.524831078</v>
       </c>
       <c r="P673" t="n">
         <v>5500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -16817,10 +16817,10 @@
         <v>137</v>
       </c>
       <c r="N367" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O367" t="n">
-        <v>679084.1553577431</v>
+        <v>672371.6295008375</v>
       </c>
       <c r="P367" t="n">
         <v>8200</v>
@@ -21127,10 +21127,10 @@
         <v>272</v>
       </c>
       <c r="N461" t="n">
-        <v>3642.7032352941</v>
+        <v>3629.36</v>
       </c>
       <c r="O461" t="n">
-        <v>990815.2799999953</v>
+        <v>987185.92</v>
       </c>
       <c r="P461" t="n">
         <v>3900</v>
@@ -21592,10 +21592,10 @@
         <v>60</v>
       </c>
       <c r="N471" t="n">
-        <v>6160.2225287356</v>
+        <v>6090.22</v>
       </c>
       <c r="O471" t="n">
-        <v>369613.351724136</v>
+        <v>365413.2</v>
       </c>
       <c r="P471" t="n">
         <v>8500</v>
@@ -25266,10 +25266,10 @@
         <v>165</v>
       </c>
       <c r="N549" t="n">
-        <v>883.11127118644</v>
+        <v>875.69016949153</v>
       </c>
       <c r="O549" t="n">
-        <v>145713.3597457626</v>
+        <v>144488.8779661024</v>
       </c>
       <c r="P549" t="n">
         <v>4500</v>
@@ -30704,10 +30704,10 @@
         <v>176</v>
       </c>
       <c r="N666" t="n">
-        <v>1327.2142261905</v>
+        <v>1319.3608928571</v>
       </c>
       <c r="O666" t="n">
-        <v>233589.703809528</v>
+        <v>232207.5171428496</v>
       </c>
       <c r="P666" t="n">
         <v>3500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q686"/>
+  <dimension ref="A1:Q687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3076124567</v>
+        <v>1811.3076256499</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3076124567</v>
+        <v>1811.3076256499</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1351,10 +1351,10 @@
         <v>102</v>
       </c>
       <c r="N24" t="n">
-        <v>2474.7041355932</v>
+        <v>2474.7040753425</v>
       </c>
       <c r="O24" t="n">
-        <v>252419.8218305064</v>
+        <v>252419.815684935</v>
       </c>
       <c r="P24" t="n">
         <v>4500</v>
@@ -1836,10 +1836,10 @@
         <v>24</v>
       </c>
       <c r="N36" t="n">
-        <v>16486.40875</v>
+        <v>16486.408661417</v>
       </c>
       <c r="O36" t="n">
-        <v>395673.8099999999</v>
+        <v>395673.807874008</v>
       </c>
       <c r="P36" t="n">
         <v>30500</v>
@@ -2901,22 +2901,22 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M61" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N61" t="n">
         <v>2563.34</v>
       </c>
       <c r="O61" t="n">
-        <v>107660.28</v>
+        <v>66646.84</v>
       </c>
       <c r="P61" t="n">
         <v>4700</v>
       </c>
       <c r="Q61" t="n">
-        <v>197400</v>
+        <v>122200</v>
       </c>
     </row>
     <row r="62">
@@ -3308,10 +3308,10 @@
         <v>1295</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0599864057</v>
+        <v>1098.0603685231</v>
       </c>
       <c r="O70" t="n">
-        <v>1421987.682395382</v>
+        <v>1421988.177237414</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -3348,22 +3348,22 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M71" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N71" t="n">
         <v>6295.2</v>
       </c>
       <c r="O71" t="n">
-        <v>358826.4</v>
+        <v>321055.2</v>
       </c>
       <c r="P71" t="n">
         <v>10500</v>
       </c>
       <c r="Q71" t="n">
-        <v>598500</v>
+        <v>535500</v>
       </c>
     </row>
     <row r="72">
@@ -3707,22 +3707,22 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M79" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N79" t="n">
         <v>17207.41</v>
       </c>
       <c r="O79" t="n">
-        <v>1015237.19</v>
+        <v>825955.6799999999</v>
       </c>
       <c r="P79" t="n">
         <v>20000</v>
       </c>
       <c r="Q79" t="n">
-        <v>1180000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="80">
@@ -4241,10 +4241,10 @@
         <v>741</v>
       </c>
       <c r="N91" t="n">
-        <v>2582.2556363636</v>
+        <v>2582.2556074972</v>
       </c>
       <c r="O91" t="n">
-        <v>1913451.426545428</v>
+        <v>1913451.405155425</v>
       </c>
       <c r="P91" t="n">
         <v>4500</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="N93" t="n">
-        <v>5216.8960979122</v>
+        <v>5216.8960939752</v>
       </c>
       <c r="O93" t="n">
-        <v>3651827.26853854</v>
+        <v>3630959.681406739</v>
       </c>
       <c r="P93" t="n">
         <v>8500</v>
       </c>
       <c r="Q93" t="n">
-        <v>5950000</v>
+        <v>5916000</v>
       </c>
     </row>
     <row r="94">
@@ -5384,10 +5384,10 @@
         <v>312</v>
       </c>
       <c r="N116" t="n">
-        <v>4890.9300489297</v>
+        <v>4890.9300489596</v>
       </c>
       <c r="O116" t="n">
-        <v>1525970.175266067</v>
+        <v>1525970.175275395</v>
       </c>
       <c r="P116" t="n">
         <v>8200</v>
@@ -5470,22 +5470,22 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M118" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="N118" t="n">
         <v>5888</v>
       </c>
       <c r="O118" t="n">
-        <v>830208</v>
+        <v>794880</v>
       </c>
       <c r="P118" t="n">
         <v>9500</v>
       </c>
       <c r="Q118" t="n">
-        <v>1339500</v>
+        <v>1282500</v>
       </c>
     </row>
     <row r="119">
@@ -5883,10 +5883,10 @@
         <v>288</v>
       </c>
       <c r="N127" t="n">
-        <v>3594.2539736347</v>
+        <v>3594.2539698492</v>
       </c>
       <c r="O127" t="n">
-        <v>1035145.144406794</v>
+        <v>1035145.14331657</v>
       </c>
       <c r="P127" t="n">
         <v>6500</v>
@@ -5924,10 +5924,10 @@
         <v>108</v>
       </c>
       <c r="N128" t="n">
-        <v>3240.8500374532</v>
+        <v>3240.850037594</v>
       </c>
       <c r="O128" t="n">
-        <v>350011.8040449456</v>
+        <v>350011.804060152</v>
       </c>
       <c r="P128" t="n">
         <v>5200</v>
@@ -6056,22 +6056,22 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M131" t="n">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="N131" t="n">
         <v>8154</v>
       </c>
       <c r="O131" t="n">
-        <v>3302370</v>
+        <v>3220830</v>
       </c>
       <c r="P131" t="n">
         <v>13500</v>
       </c>
       <c r="Q131" t="n">
-        <v>5467500</v>
+        <v>5332500</v>
       </c>
     </row>
     <row r="132">
@@ -6789,10 +6789,10 @@
         <v>210</v>
       </c>
       <c r="N147" t="n">
-        <v>3041.6600134228</v>
+        <v>3041.660013459</v>
       </c>
       <c r="O147" t="n">
-        <v>638748.602818788</v>
+        <v>638748.6028263899</v>
       </c>
       <c r="P147" t="n">
         <v>5500</v>
@@ -6917,10 +6917,10 @@
         <v>1938</v>
       </c>
       <c r="N150" t="n">
-        <v>4372.2107907508</v>
+        <v>4372.2107910895</v>
       </c>
       <c r="O150" t="n">
-        <v>8473344.512475049</v>
+        <v>8473344.513131451</v>
       </c>
       <c r="P150" t="n">
         <v>7500</v>
@@ -6955,22 +6955,22 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M151" t="n">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c r="N151" t="n">
         <v>6441.03</v>
       </c>
       <c r="O151" t="n">
-        <v>5429788.29</v>
+        <v>5300967.689999999</v>
       </c>
       <c r="P151" t="n">
         <v>10500</v>
       </c>
       <c r="Q151" t="n">
-        <v>8851500</v>
+        <v>8641500</v>
       </c>
     </row>
     <row r="152">
@@ -7007,10 +7007,10 @@
         <v>241</v>
       </c>
       <c r="N152" t="n">
-        <v>1592.5665147453</v>
+        <v>1592.566460177</v>
       </c>
       <c r="O152" t="n">
-        <v>383808.5300536173</v>
+        <v>383808.516902657</v>
       </c>
       <c r="P152" t="n">
         <v>3900</v>
@@ -8798,10 +8798,10 @@
         <v>744</v>
       </c>
       <c r="N191" t="n">
-        <v>1630.923733916</v>
+        <v>1630.9237493905</v>
       </c>
       <c r="O191" t="n">
-        <v>1213407.258033504</v>
+        <v>1213407.269546532</v>
       </c>
       <c r="P191" t="n">
         <v>2500</v>
@@ -8890,10 +8890,10 @@
         <v>272</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.5964846154</v>
+        <v>1690.5964302236</v>
       </c>
       <c r="O193" t="n">
-        <v>459842.2438153888</v>
+        <v>459842.2290208192</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8936,10 +8936,10 @@
         <v>1906</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.1937906027</v>
+        <v>1550.1937917646</v>
       </c>
       <c r="O194" t="n">
-        <v>2954669.364888746</v>
+        <v>2954669.367103328</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9028,10 +9028,10 @@
         <v>418</v>
       </c>
       <c r="N196" t="n">
-        <v>2403.5124244849</v>
+        <v>2403.5125045299</v>
       </c>
       <c r="O196" t="n">
-        <v>1004668.193434688</v>
+        <v>1004668.226893498</v>
       </c>
       <c r="P196" t="n">
         <v>3500</v>
@@ -10152,22 +10152,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M221" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N221" t="n">
         <v>4485.03</v>
       </c>
       <c r="O221" t="n">
-        <v>192856.29</v>
+        <v>121095.81</v>
       </c>
       <c r="P221" t="n">
         <v>9900</v>
       </c>
       <c r="Q221" t="n">
-        <v>425700</v>
+        <v>267300</v>
       </c>
     </row>
     <row r="222">
@@ -10882,22 +10882,22 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M238" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
         <v>56503</v>
       </c>
       <c r="O238" t="n">
-        <v>621533</v>
+        <v>0</v>
       </c>
       <c r="P238" t="n">
         <v>90500</v>
       </c>
       <c r="Q238" t="n">
-        <v>995500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -11070,10 +11070,10 @@
         <v>113</v>
       </c>
       <c r="N242" t="n">
-        <v>4285.1956570156</v>
+        <v>4285.195701459</v>
       </c>
       <c r="O242" t="n">
-        <v>484227.1092427628</v>
+        <v>484227.114264867</v>
       </c>
       <c r="P242" t="n">
         <v>6900</v>
@@ -11814,22 +11814,22 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M259" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="N259" t="n">
         <v>8332.779621212099</v>
       </c>
       <c r="O259" t="n">
-        <v>599960.1327272712</v>
+        <v>533297.8957575744</v>
       </c>
       <c r="P259" t="n">
         <v>14900</v>
       </c>
       <c r="Q259" t="n">
-        <v>1072800</v>
+        <v>953600</v>
       </c>
     </row>
     <row r="260">
@@ -11866,10 +11866,10 @@
         <v>599</v>
       </c>
       <c r="N260" t="n">
-        <v>1561.0010652921</v>
+        <v>1561.0013915094</v>
       </c>
       <c r="O260" t="n">
-        <v>935039.6381099679</v>
+        <v>935039.8335141307</v>
       </c>
       <c r="P260" t="n">
         <v>2900</v>
@@ -12753,10 +12753,10 @@
         <v>122</v>
       </c>
       <c r="N279" t="n">
-        <v>3113.8900276243</v>
+        <v>3113.8900280899</v>
       </c>
       <c r="O279" t="n">
-        <v>379894.5833701646</v>
+        <v>379894.5834269678</v>
       </c>
       <c r="P279" t="n">
         <v>5000</v>
@@ -13765,22 +13765,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M301" t="n">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="N301" t="n">
         <v>3646</v>
       </c>
       <c r="O301" t="n">
-        <v>849518</v>
+        <v>732846</v>
       </c>
       <c r="P301" t="n">
         <v>6900</v>
       </c>
       <c r="Q301" t="n">
-        <v>1607700</v>
+        <v>1386900</v>
       </c>
     </row>
     <row r="302">
@@ -13811,22 +13811,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M302" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N302" t="n">
         <v>23521.624067797</v>
       </c>
       <c r="O302" t="n">
-        <v>305781.112881361</v>
+        <v>0</v>
       </c>
       <c r="P302" t="n">
         <v>39000</v>
       </c>
       <c r="Q302" t="n">
-        <v>507000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -13857,22 +13857,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M303" t="n">
-        <v>824</v>
+        <v>784</v>
       </c>
       <c r="N303" t="n">
         <v>1778.4726494689</v>
       </c>
       <c r="O303" t="n">
-        <v>1465461.463162374</v>
+        <v>1394322.557183618</v>
       </c>
       <c r="P303" t="n">
         <v>4900</v>
       </c>
       <c r="Q303" t="n">
-        <v>4037600</v>
+        <v>3841600</v>
       </c>
     </row>
     <row r="304">
@@ -13903,22 +13903,22 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M304" t="n">
-        <v>688</v>
+        <v>624</v>
       </c>
       <c r="N304" t="n">
         <v>1548</v>
       </c>
       <c r="O304" t="n">
-        <v>1065024</v>
+        <v>965952</v>
       </c>
       <c r="P304" t="n">
         <v>3900</v>
       </c>
       <c r="Q304" t="n">
-        <v>2683200</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="305">
@@ -13949,22 +13949,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M305" t="n">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="N305" t="n">
         <v>2325</v>
       </c>
       <c r="O305" t="n">
-        <v>455700</v>
+        <v>372000</v>
       </c>
       <c r="P305" t="n">
         <v>4900</v>
       </c>
       <c r="Q305" t="n">
-        <v>960400</v>
+        <v>784000</v>
       </c>
     </row>
     <row r="306">
@@ -15565,22 +15565,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M340" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N340" t="n">
         <v>28116</v>
       </c>
       <c r="O340" t="n">
-        <v>843480</v>
+        <v>674784</v>
       </c>
       <c r="P340" t="n">
         <v>45900</v>
       </c>
       <c r="Q340" t="n">
-        <v>1377000</v>
+        <v>1101600</v>
       </c>
     </row>
     <row r="341">
@@ -15847,10 +15847,10 @@
         <v>5</v>
       </c>
       <c r="N346" t="n">
-        <v>2252.2972418478</v>
+        <v>2252.2973618785</v>
       </c>
       <c r="O346" t="n">
-        <v>11261.486209239</v>
+        <v>11261.4868093925</v>
       </c>
       <c r="P346" t="n">
         <v>3900</v>
@@ -16173,10 +16173,10 @@
         <v>324</v>
       </c>
       <c r="N353" t="n">
-        <v>2328.1187082951</v>
+        <v>2328.1186987357</v>
       </c>
       <c r="O353" t="n">
-        <v>754310.4614876125</v>
+        <v>754310.4583903669</v>
       </c>
       <c r="P353" t="n">
         <v>4500</v>
@@ -16817,10 +16817,10 @@
         <v>137</v>
       </c>
       <c r="N367" t="n">
-        <v>4907.8221131448</v>
+        <v>4907.8221561969</v>
       </c>
       <c r="O367" t="n">
-        <v>672371.6295008375</v>
+        <v>672371.6353989753</v>
       </c>
       <c r="P367" t="n">
         <v>8200</v>
@@ -16903,22 +16903,22 @@
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M369" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="N369" t="n">
         <v>13210</v>
       </c>
       <c r="O369" t="n">
-        <v>739760</v>
+        <v>581240</v>
       </c>
       <c r="P369" t="n">
         <v>23900</v>
       </c>
       <c r="Q369" t="n">
-        <v>1338400</v>
+        <v>1051600</v>
       </c>
     </row>
     <row r="370">
@@ -16949,22 +16949,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N370" t="n">
         <v>76839</v>
       </c>
       <c r="O370" t="n">
-        <v>153678</v>
+        <v>0</v>
       </c>
       <c r="P370" t="n">
         <v>122900</v>
       </c>
       <c r="Q370" t="n">
-        <v>245800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -18690,22 +18690,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M408" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N408" t="n">
         <v>10817</v>
       </c>
       <c r="O408" t="n">
-        <v>346144</v>
+        <v>324510</v>
       </c>
       <c r="P408" t="n">
         <v>17900</v>
       </c>
       <c r="Q408" t="n">
-        <v>572800</v>
+        <v>537000</v>
       </c>
     </row>
     <row r="409">
@@ -19104,22 +19104,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M417" t="n">
-        <v>270</v>
+        <v>174</v>
       </c>
       <c r="N417" t="n">
         <v>1803</v>
       </c>
       <c r="O417" t="n">
-        <v>486810</v>
+        <v>313722</v>
       </c>
       <c r="P417" t="n">
         <v>3900</v>
       </c>
       <c r="Q417" t="n">
-        <v>1053000</v>
+        <v>678600</v>
       </c>
     </row>
     <row r="418">
@@ -19294,10 +19294,10 @@
         <v>48</v>
       </c>
       <c r="N421" t="n">
-        <v>2458.5130528766</v>
+        <v>2458.5130063609</v>
       </c>
       <c r="O421" t="n">
-        <v>118008.6265380768</v>
+        <v>118008.6243053232</v>
       </c>
       <c r="P421" t="n">
         <v>3500</v>
@@ -19340,10 +19340,10 @@
         <v>48</v>
       </c>
       <c r="N422" t="n">
-        <v>1771.0904111406</v>
+        <v>1771.0903664224</v>
       </c>
       <c r="O422" t="n">
-        <v>85012.33973474881</v>
+        <v>85012.3375882752</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
@@ -19432,10 +19432,10 @@
         <v>72</v>
       </c>
       <c r="N424" t="n">
-        <v>1803.0156556557</v>
+        <v>1803.0157013118</v>
       </c>
       <c r="O424" t="n">
-        <v>129817.1272072104</v>
+        <v>129817.1304944496</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
@@ -19570,10 +19570,10 @@
         <v>144</v>
       </c>
       <c r="N427" t="n">
-        <v>2056.0829556314</v>
+        <v>2056.0829120879</v>
       </c>
       <c r="O427" t="n">
-        <v>296075.9456109216</v>
+        <v>296075.9393406576</v>
       </c>
       <c r="P427" t="n">
         <v>2900</v>
@@ -19892,10 +19892,10 @@
         <v>304</v>
       </c>
       <c r="N434" t="n">
-        <v>1592.279767184</v>
+        <v>1592.2798435754</v>
       </c>
       <c r="O434" t="n">
-        <v>484053.049223936</v>
+        <v>484053.0724469216</v>
       </c>
       <c r="P434" t="n">
         <v>2500</v>
@@ -21494,10 +21494,10 @@
         <v>306</v>
       </c>
       <c r="N469" t="n">
-        <v>1690.8700091449</v>
+        <v>1690.8700091701</v>
       </c>
       <c r="O469" t="n">
-        <v>517406.2227983394</v>
+        <v>517406.2228060506</v>
       </c>
       <c r="P469" t="n">
         <v>3000</v>
@@ -22337,10 +22337,10 @@
         <v>149</v>
       </c>
       <c r="N487" t="n">
-        <v>517.29010591089</v>
+        <v>517.2904197169401</v>
       </c>
       <c r="O487" t="n">
-        <v>77076.22578072261</v>
+        <v>77076.27253782407</v>
       </c>
       <c r="P487" t="n">
         <v>900</v>
@@ -22711,10 +22711,10 @@
         <v>26</v>
       </c>
       <c r="N495" t="n">
-        <v>3259.1342692308</v>
+        <v>3259.1343023256</v>
       </c>
       <c r="O495" t="n">
-        <v>84737.49100000079</v>
+        <v>84737.4918604656</v>
       </c>
       <c r="P495" t="n">
         <v>3600</v>
@@ -22760,10 +22760,10 @@
         <v>757</v>
       </c>
       <c r="N496" t="n">
-        <v>3110.8411757364</v>
+        <v>3110.8406506215</v>
       </c>
       <c r="O496" t="n">
-        <v>2354906.770032455</v>
+        <v>2354906.372520476</v>
       </c>
       <c r="P496" t="n">
         <v>4500</v>
@@ -23205,22 +23205,22 @@
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="M506" t="n">
-        <v>19802</v>
+        <v>18650</v>
       </c>
       <c r="N506" t="n">
-        <v>703.79514130448</v>
+        <v>703.79512253205</v>
       </c>
       <c r="O506" t="n">
-        <v>13936551.38811131</v>
+        <v>13125779.03522273</v>
       </c>
       <c r="P506" t="n">
         <v>900</v>
       </c>
       <c r="Q506" t="n">
-        <v>17821800</v>
+        <v>16785000</v>
       </c>
     </row>
     <row r="507">
@@ -24482,22 +24482,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M533" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N533" t="n">
         <v>10348.08</v>
       </c>
       <c r="O533" t="n">
-        <v>641580.96</v>
+        <v>579492.48</v>
       </c>
       <c r="P533" t="n">
         <v>16900</v>
       </c>
       <c r="Q533" t="n">
-        <v>1047800</v>
+        <v>946400</v>
       </c>
     </row>
     <row r="534">
@@ -26357,22 +26357,22 @@
         <v>0</v>
       </c>
       <c r="L572" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M572" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N572" t="n">
         <v>5876.81</v>
       </c>
       <c r="O572" t="n">
-        <v>205688.35</v>
+        <v>152797.06</v>
       </c>
       <c r="P572" t="n">
         <v>22900</v>
       </c>
       <c r="Q572" t="n">
-        <v>801500</v>
+        <v>595400</v>
       </c>
     </row>
     <row r="573">
@@ -26591,22 +26591,22 @@
         <v>0</v>
       </c>
       <c r="L577" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M577" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N577" t="n">
         <v>36004.28</v>
       </c>
       <c r="O577" t="n">
-        <v>504059.92</v>
+        <v>396047.08</v>
       </c>
       <c r="P577" t="n">
         <v>83500</v>
       </c>
       <c r="Q577" t="n">
-        <v>1169000</v>
+        <v>918500</v>
       </c>
     </row>
     <row r="578">
@@ -26732,22 +26732,22 @@
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M580" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N580" t="n">
         <v>9372</v>
       </c>
       <c r="O580" t="n">
-        <v>168696</v>
+        <v>112464</v>
       </c>
       <c r="P580" t="n">
         <v>17900</v>
       </c>
       <c r="Q580" t="n">
-        <v>322200</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="581">
@@ -27437,22 +27437,22 @@
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M595" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N595" t="n">
         <v>8671.389999999999</v>
       </c>
       <c r="O595" t="n">
-        <v>69371.12</v>
+        <v>0</v>
       </c>
       <c r="P595" t="n">
         <v>20500</v>
       </c>
       <c r="Q595" t="n">
-        <v>164000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596">
@@ -28910,22 +28910,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M627" t="n">
-        <v>791</v>
+        <v>731</v>
       </c>
       <c r="N627" t="n">
         <v>3181.9</v>
       </c>
       <c r="O627" t="n">
-        <v>2516882.9</v>
+        <v>2325968.9</v>
       </c>
       <c r="P627" t="n">
         <v>5100</v>
       </c>
       <c r="Q627" t="n">
-        <v>4034100</v>
+        <v>3728100</v>
       </c>
     </row>
     <row r="628">
@@ -28957,10 +28957,10 @@
         <v>4</v>
       </c>
       <c r="N628" t="n">
-        <v>1213.6821359223</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O628" t="n">
-        <v>4854.7285436892</v>
+        <v>4854.7285603112</v>
       </c>
       <c r="P628" t="n">
         <v>1500</v>
@@ -29400,22 +29400,22 @@
         <v>0</v>
       </c>
       <c r="L638" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M638" t="n">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="N638" t="n">
         <v>22951.704799483</v>
       </c>
       <c r="O638" t="n">
-        <v>7941289.860621118</v>
+        <v>7826531.336623703</v>
       </c>
       <c r="P638" t="n">
         <v>37900</v>
       </c>
       <c r="Q638" t="n">
-        <v>13113400</v>
+        <v>12923900</v>
       </c>
     </row>
     <row r="639">
@@ -30346,12 +30346,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -30365,39 +30365,39 @@
         </is>
       </c>
       <c r="J659" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="K659" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="L659" t="n">
         <v>0</v>
       </c>
       <c r="M659" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N659" t="n">
-        <v>5280</v>
+        <v>4576</v>
       </c>
       <c r="O659" t="n">
-        <v>739200</v>
+        <v>677248</v>
       </c>
       <c r="P659" t="n">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="Q659" t="n">
-        <v>966000</v>
+        <v>873200</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -30411,7 +30411,7 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
@@ -30420,30 +30420,30 @@
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="N660" t="n">
-        <v>415.07</v>
+        <v>5280</v>
       </c>
       <c r="O660" t="n">
-        <v>12867.17</v>
+        <v>739200</v>
       </c>
       <c r="P660" t="n">
-        <v>2900</v>
+        <v>6900</v>
       </c>
       <c r="Q660" t="n">
-        <v>89900</v>
+        <v>966000</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>MG09</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>COCINA CAJA MED MG20233</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -30457,7 +30457,7 @@
         </is>
       </c>
       <c r="J661" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="K661" t="n">
         <v>0</v>
@@ -30466,35 +30466,35 @@
         <v>0</v>
       </c>
       <c r="M661" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="N661" t="n">
-        <v>46491.75</v>
+        <v>415.07</v>
       </c>
       <c r="O661" t="n">
-        <v>2743013.25</v>
+        <v>12867.17</v>
       </c>
       <c r="P661" t="n">
-        <v>52900</v>
+        <v>2900</v>
       </c>
       <c r="Q661" t="n">
-        <v>3121100</v>
+        <v>89900</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>MG09</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>COCINA CAJA MED MG20233</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -30503,7 +30503,7 @@
         </is>
       </c>
       <c r="J662" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K662" t="n">
         <v>0</v>
@@ -30512,35 +30512,35 @@
         <v>0</v>
       </c>
       <c r="M662" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N662" t="n">
-        <v>910.85</v>
+        <v>46491.75</v>
       </c>
       <c r="O662" t="n">
-        <v>32790.6</v>
+        <v>2743013.25</v>
       </c>
       <c r="P662" t="n">
-        <v>7900</v>
+        <v>52900</v>
       </c>
       <c r="Q662" t="n">
-        <v>284400</v>
+        <v>3121100</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -30549,7 +30549,7 @@
         </is>
       </c>
       <c r="J663" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K663" t="n">
         <v>0</v>
@@ -30558,35 +30558,35 @@
         <v>0</v>
       </c>
       <c r="M663" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="N663" t="n">
-        <v>1129.14</v>
+        <v>910.85</v>
       </c>
       <c r="O663" t="n">
-        <v>13549.68</v>
+        <v>32790.6</v>
       </c>
       <c r="P663" t="n">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="Q663" t="n">
-        <v>82800</v>
+        <v>284400</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="J664" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K664" t="n">
         <v>0</v>
@@ -30604,40 +30604,35 @@
         <v>0</v>
       </c>
       <c r="M664" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N664" t="n">
-        <v>11433.53</v>
+        <v>1129.14</v>
       </c>
       <c r="O664" t="n">
-        <v>125768.83</v>
+        <v>13549.68</v>
       </c>
       <c r="P664" t="n">
-        <v>15000</v>
+        <v>6900</v>
       </c>
       <c r="Q664" t="n">
-        <v>165000</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -30646,7 +30641,7 @@
         </is>
       </c>
       <c r="J665" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K665" t="n">
         <v>0</v>
@@ -30655,35 +30650,40 @@
         <v>0</v>
       </c>
       <c r="M665" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N665" t="n">
-        <v>15452.21</v>
+        <v>11433.53</v>
       </c>
       <c r="O665" t="n">
-        <v>61808.84</v>
+        <v>125768.83</v>
       </c>
       <c r="P665" t="n">
-        <v>36500</v>
+        <v>15000</v>
       </c>
       <c r="Q665" t="n">
-        <v>146000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -30692,7 +30692,7 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>176</v>
+        <v>4</v>
       </c>
       <c r="K666" t="n">
         <v>0</v>
@@ -30701,40 +30701,35 @@
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>176</v>
+        <v>4</v>
       </c>
       <c r="N666" t="n">
-        <v>1319.3608928571</v>
+        <v>15452.21</v>
       </c>
       <c r="O666" t="n">
-        <v>232207.5171428496</v>
+        <v>61808.84</v>
       </c>
       <c r="P666" t="n">
-        <v>3500</v>
+        <v>36500</v>
       </c>
       <c r="Q666" t="n">
-        <v>616000</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -30743,7 +30738,7 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="K667" t="n">
         <v>0</v>
@@ -30752,35 +30747,40 @@
         <v>0</v>
       </c>
       <c r="M667" t="n">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="N667" t="n">
-        <v>751.45</v>
+        <v>1319.3608928571</v>
       </c>
       <c r="O667" t="n">
-        <v>50347.15</v>
+        <v>232207.5171428496</v>
       </c>
       <c r="P667" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="Q667" t="n">
-        <v>167500</v>
+        <v>616000</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -30789,7 +30789,7 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="K668" t="n">
         <v>0</v>
@@ -30798,35 +30798,35 @@
         <v>0</v>
       </c>
       <c r="M668" t="n">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="N668" t="n">
-        <v>571.87</v>
+        <v>751.45</v>
       </c>
       <c r="O668" t="n">
-        <v>81777.41</v>
+        <v>50347.15</v>
       </c>
       <c r="P668" t="n">
         <v>2500</v>
       </c>
       <c r="Q668" t="n">
-        <v>357500</v>
+        <v>167500</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -30835,7 +30835,7 @@
         </is>
       </c>
       <c r="J669" t="n">
-        <v>686</v>
+        <v>143</v>
       </c>
       <c r="K669" t="n">
         <v>0</v>
@@ -30844,40 +30844,35 @@
         <v>0</v>
       </c>
       <c r="M669" t="n">
-        <v>686</v>
+        <v>143</v>
       </c>
       <c r="N669" t="n">
-        <v>227.41613363363</v>
+        <v>571.87</v>
       </c>
       <c r="O669" t="n">
-        <v>156007.4676726702</v>
+        <v>81777.41</v>
       </c>
       <c r="P669" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="Q669" t="n">
-        <v>823200</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -30886,7 +30881,7 @@
         </is>
       </c>
       <c r="J670" t="n">
-        <v>21</v>
+        <v>686</v>
       </c>
       <c r="K670" t="n">
         <v>0</v>
@@ -30895,47 +30890,49 @@
         <v>0</v>
       </c>
       <c r="M670" t="n">
-        <v>21</v>
+        <v>686</v>
       </c>
       <c r="N670" t="n">
-        <v>9917.040000000001</v>
+        <v>227.41613363363</v>
       </c>
       <c r="O670" t="n">
-        <v>208257.84</v>
+        <v>156007.4676726702</v>
       </c>
       <c r="P670" t="n">
-        <v>15900</v>
+        <v>1200</v>
       </c>
       <c r="Q670" t="n">
-        <v>333900</v>
+        <v>823200</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B671" t="n">
-        <v>7700154271143</v>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>MG40720</t>
+        </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J671" t="n">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="K671" t="n">
         <v>0</v>
@@ -30944,30 +30941,33 @@
         <v>0</v>
       </c>
       <c r="M671" t="n">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="N671" t="n">
-        <v>2539.5715696649</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O671" t="n">
-        <v>401252.3080070542</v>
+        <v>208257.84</v>
       </c>
       <c r="P671" t="n">
-        <v>3500</v>
+        <v>15900</v>
       </c>
       <c r="Q671" t="n">
-        <v>553000</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>MT4691</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -30977,11 +30977,11 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J672" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
@@ -30990,35 +30990,35 @@
         <v>0</v>
       </c>
       <c r="M672" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="N672" t="n">
-        <v>4171.6686824324</v>
+        <v>2539.5715696649</v>
       </c>
       <c r="O672" t="n">
-        <v>396308.524831078</v>
+        <v>401252.3080070542</v>
       </c>
       <c r="P672" t="n">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="Q672" t="n">
-        <v>522500</v>
+        <v>553000</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -31027,7 +31027,7 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="K673" t="n">
         <v>0</v>
@@ -31036,35 +31036,35 @@
         <v>0</v>
       </c>
       <c r="M673" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="N673" t="n">
-        <v>7600</v>
+        <v>4171.6686824324</v>
       </c>
       <c r="O673" t="n">
-        <v>364800</v>
+        <v>396308.524831078</v>
       </c>
       <c r="P673" t="n">
-        <v>9500</v>
+        <v>5500</v>
       </c>
       <c r="Q673" t="n">
-        <v>456000</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>SEB010</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
@@ -31082,30 +31082,30 @@
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="N674" t="n">
-        <v>5520</v>
+        <v>7600</v>
       </c>
       <c r="O674" t="n">
-        <v>524400</v>
+        <v>364800</v>
       </c>
       <c r="P674" t="n">
-        <v>6900</v>
+        <v>9500</v>
       </c>
       <c r="Q674" t="n">
-        <v>655500</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>SEB09</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -31119,7 +31119,7 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -31128,30 +31128,30 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="N675" t="n">
-        <v>1600</v>
+        <v>5520</v>
       </c>
       <c r="O675" t="n">
-        <v>132800</v>
+        <v>524400</v>
       </c>
       <c r="P675" t="n">
-        <v>2000</v>
+        <v>6900</v>
       </c>
       <c r="Q675" t="n">
-        <v>166000</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -31165,7 +31165,7 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
@@ -31174,30 +31174,30 @@
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="N676" t="n">
-        <v>4091.4</v>
+        <v>1600</v>
       </c>
       <c r="O676" t="n">
-        <v>4091.4</v>
+        <v>132800</v>
       </c>
       <c r="P676" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="Q676" t="n">
-        <v>10000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>SLT027</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>JUGUETE  DRAGON   AB-02 / 082</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -31211,7 +31211,7 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
@@ -31220,35 +31220,35 @@
         <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N677" t="n">
-        <v>3732.8768115942</v>
+        <v>4091.4</v>
       </c>
       <c r="O677" t="n">
-        <v>37328.768115942</v>
+        <v>4091.4</v>
       </c>
       <c r="P677" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="Q677" t="n">
-        <v>45000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>SLT027</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>JUGUETE  DRAGON   AB-02 / 082</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -31257,7 +31257,7 @@
         </is>
       </c>
       <c r="J678" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K678" t="n">
         <v>0</v>
@@ -31266,30 +31266,30 @@
         <v>0</v>
       </c>
       <c r="M678" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N678" t="n">
-        <v>3661.88</v>
+        <v>3732.8768115942</v>
       </c>
       <c r="O678" t="n">
-        <v>10985.64</v>
+        <v>37328.768115942</v>
       </c>
       <c r="P678" t="n">
-        <v>38900</v>
+        <v>4500</v>
       </c>
       <c r="Q678" t="n">
-        <v>116700</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>T040-LJ</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -31303,7 +31303,7 @@
         </is>
       </c>
       <c r="J679" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K679" t="n">
         <v>0</v>
@@ -31312,30 +31312,30 @@
         <v>0</v>
       </c>
       <c r="M679" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N679" t="n">
-        <v>2797.08</v>
+        <v>3661.88</v>
       </c>
       <c r="O679" t="n">
-        <v>13985.4</v>
+        <v>10985.64</v>
       </c>
       <c r="P679" t="n">
-        <v>30900</v>
+        <v>38900</v>
       </c>
       <c r="Q679" t="n">
-        <v>154500</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T041-LJ</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="J680" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K680" t="n">
         <v>0</v>
@@ -31358,30 +31358,30 @@
         <v>0</v>
       </c>
       <c r="M680" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N680" t="n">
-        <v>3462.255</v>
+        <v>2797.08</v>
       </c>
       <c r="O680" t="n">
-        <v>38084.805</v>
+        <v>13985.4</v>
       </c>
       <c r="P680" t="n">
-        <v>42000</v>
+        <v>30900</v>
       </c>
       <c r="Q680" t="n">
-        <v>462000</v>
+        <v>154500</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -31395,7 +31395,7 @@
         </is>
       </c>
       <c r="J681" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K681" t="n">
         <v>0</v>
@@ -31404,30 +31404,30 @@
         <v>0</v>
       </c>
       <c r="M681" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="N681" t="n">
-        <v>24882.58</v>
+        <v>3462.255</v>
       </c>
       <c r="O681" t="n">
-        <v>696712.24</v>
+        <v>38084.805</v>
       </c>
       <c r="P681" t="n">
-        <v>31500</v>
+        <v>42000</v>
       </c>
       <c r="Q681" t="n">
-        <v>882000</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>T119-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -31441,7 +31441,7 @@
         </is>
       </c>
       <c r="J682" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K682" t="n">
         <v>0</v>
@@ -31450,35 +31450,35 @@
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="N682" t="n">
-        <v>0.8</v>
+        <v>24882.58</v>
       </c>
       <c r="O682" t="n">
-        <v>15.2</v>
+        <v>696712.24</v>
       </c>
       <c r="P682" t="n">
-        <v>22900</v>
+        <v>31500</v>
       </c>
       <c r="Q682" t="n">
-        <v>435100</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T119-LJ</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>COBIJA ROLLO PQÑ TZ-PEQ</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -31487,7 +31487,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -31496,30 +31496,30 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N683" t="n">
-        <v>5186.45</v>
+        <v>0.8</v>
       </c>
       <c r="O683" t="n">
-        <v>82983.2</v>
+        <v>15.2</v>
       </c>
       <c r="P683" t="n">
-        <v>7200</v>
+        <v>22900</v>
       </c>
       <c r="Q683" t="n">
-        <v>115200</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -31533,7 +31533,7 @@
         </is>
       </c>
       <c r="J684" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K684" t="n">
         <v>0</v>
@@ -31542,30 +31542,30 @@
         <v>0</v>
       </c>
       <c r="M684" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N684" t="n">
-        <v>47796.1625</v>
+        <v>5186.45</v>
       </c>
       <c r="O684" t="n">
-        <v>95592.325</v>
+        <v>82983.2</v>
       </c>
       <c r="P684" t="n">
-        <v>54000</v>
+        <v>7200</v>
       </c>
       <c r="Q684" t="n">
-        <v>108000</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>TB115</t>
+          <t>TB028</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -31579,7 +31579,7 @@
         </is>
       </c>
       <c r="J685" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="K685" t="n">
         <v>0</v>
@@ -31588,64 +31588,110 @@
         <v>0</v>
       </c>
       <c r="M685" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="N685" t="n">
-        <v>8006.3731111111</v>
+        <v>47796.1625</v>
       </c>
       <c r="O685" t="n">
-        <v>344274.0437777773</v>
+        <v>95592.325</v>
       </c>
       <c r="P685" t="n">
-        <v>10000</v>
+        <v>54000</v>
       </c>
       <c r="Q685" t="n">
-        <v>430000</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
+          <t>TB115</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J686" t="n">
+        <v>43</v>
+      </c>
+      <c r="K686" t="n">
+        <v>0</v>
+      </c>
+      <c r="L686" t="n">
+        <v>0</v>
+      </c>
+      <c r="M686" t="n">
+        <v>43</v>
+      </c>
+      <c r="N686" t="n">
+        <v>8006.3731111111</v>
+      </c>
+      <c r="O686" t="n">
+        <v>344274.0437777773</v>
+      </c>
+      <c r="P686" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q686" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
           <t>TB122</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
-      <c r="E686" t="inlineStr">
+      <c r="E687" t="inlineStr">
         <is>
           <t>PELUCHES</t>
         </is>
       </c>
-      <c r="I686" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J686" t="n">
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J687" t="n">
         <v>4</v>
       </c>
-      <c r="K686" t="n">
-        <v>0</v>
-      </c>
-      <c r="L686" t="n">
-        <v>0</v>
-      </c>
-      <c r="M686" t="n">
+      <c r="K687" t="n">
+        <v>0</v>
+      </c>
+      <c r="L687" t="n">
+        <v>0</v>
+      </c>
+      <c r="M687" t="n">
         <v>4</v>
       </c>
-      <c r="N686" t="n">
+      <c r="N687" t="n">
         <v>47920</v>
       </c>
-      <c r="O686" t="n">
+      <c r="O687" t="n">
         <v>191680</v>
       </c>
-      <c r="P686" t="n">
+      <c r="P687" t="n">
         <v>59900</v>
       </c>
-      <c r="Q686" t="n">
+      <c r="Q687" t="n">
         <v>239600</v>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -1878,10 +1878,10 @@
         <v>18</v>
       </c>
       <c r="N37" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O37" t="n">
-        <v>282815.38565217</v>
+        <v>282815.385327504</v>
       </c>
       <c r="P37" t="n">
         <v>28500</v>
@@ -4517,10 +4517,10 @@
         <v>3199</v>
       </c>
       <c r="N97" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O97" t="n">
-        <v>10105195.78609604</v>
+        <v>10105195.78622592</v>
       </c>
       <c r="P97" t="n">
         <v>5600</v>
@@ -5836,10 +5836,10 @@
         <v>288</v>
       </c>
       <c r="N126" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O126" t="n">
-        <v>1035145.14113209</v>
+        <v>1035145.138942051</v>
       </c>
       <c r="P126" t="n">
         <v>6500</v>
@@ -5877,10 +5877,10 @@
         <v>108</v>
       </c>
       <c r="N127" t="n">
-        <v>3240.850037594</v>
+        <v>3240.8500375235</v>
       </c>
       <c r="O127" t="n">
-        <v>350011.804060152</v>
+        <v>350011.804052538</v>
       </c>
       <c r="P127" t="n">
         <v>5200</v>
@@ -9151,10 +9151,10 @@
         <v>2825</v>
       </c>
       <c r="N199" t="n">
-        <v>893.67886945501</v>
+        <v>893.67886888156</v>
       </c>
       <c r="O199" t="n">
-        <v>2524642.806210403</v>
+        <v>2524642.804590407</v>
       </c>
       <c r="P199" t="n">
         <v>1200</v>
@@ -19247,10 +19247,10 @@
         <v>72</v>
       </c>
       <c r="N420" t="n">
-        <v>1803.0157013118</v>
+        <v>1803.0157128413</v>
       </c>
       <c r="O420" t="n">
-        <v>129817.1304944496</v>
+        <v>129817.1313245736</v>
       </c>
       <c r="P420" t="n">
         <v>2500</v>
@@ -19339,10 +19339,10 @@
         <v>120</v>
       </c>
       <c r="N422" t="n">
-        <v>2108.7924270463</v>
+        <v>2108.7924803431</v>
       </c>
       <c r="O422" t="n">
-        <v>253055.091245556</v>
+        <v>253055.097641172</v>
       </c>
       <c r="P422" t="n">
         <v>2900</v>
@@ -19385,10 +19385,10 @@
         <v>144</v>
       </c>
       <c r="N423" t="n">
-        <v>2056.0829120879</v>
+        <v>2056.0828974535</v>
       </c>
       <c r="O423" t="n">
-        <v>296075.9393406576</v>
+        <v>296075.937233304</v>
       </c>
       <c r="P423" t="n">
         <v>2900</v>
@@ -19707,10 +19707,10 @@
         <v>304</v>
       </c>
       <c r="N430" t="n">
-        <v>1592.2799548023</v>
+        <v>1592.2799660633</v>
       </c>
       <c r="O430" t="n">
-        <v>484053.1062598992</v>
+        <v>484053.1096832432</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -23026,10 +23026,10 @@
         <v>18650</v>
       </c>
       <c r="N502" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O502" t="n">
-        <v>13125778.94339722</v>
+        <v>13125778.93010574</v>
       </c>
       <c r="P502" t="n">
         <v>900</v>
@@ -29175,10 +29175,10 @@
         <v>341</v>
       </c>
       <c r="N633" t="n">
-        <v>22951.704792746</v>
+        <v>22951.704785992</v>
       </c>
       <c r="O633" t="n">
-        <v>7826531.334326386</v>
+        <v>7826531.332023271</v>
       </c>
       <c r="P633" t="n">
         <v>37900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -1836,10 +1836,10 @@
         <v>24</v>
       </c>
       <c r="N36" t="n">
-        <v>16486.408661417</v>
+        <v>16486.408571429</v>
       </c>
       <c r="O36" t="n">
-        <v>395673.807874008</v>
+        <v>395673.8057142961</v>
       </c>
       <c r="P36" t="n">
         <v>30500</v>
@@ -1878,10 +1878,10 @@
         <v>18</v>
       </c>
       <c r="N37" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O37" t="n">
-        <v>282815.384669604</v>
+        <v>282815.38433628</v>
       </c>
       <c r="P37" t="n">
         <v>28500</v>
@@ -4194,10 +4194,10 @@
         <v>741</v>
       </c>
       <c r="N90" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O90" t="n">
-        <v>1913451.3666667</v>
+        <v>1913451.365196407</v>
       </c>
       <c r="P90" t="n">
         <v>4500</v>
@@ -19477,10 +19477,10 @@
         <v>360</v>
       </c>
       <c r="N425" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O425" t="n">
-        <v>596135.056279392</v>
+        <v>596135.0517821281</v>
       </c>
       <c r="P425" t="n">
         <v>2500</v>
@@ -19707,10 +19707,10 @@
         <v>304</v>
       </c>
       <c r="N430" t="n">
-        <v>1592.2805889423</v>
+        <v>1592.2806787879</v>
       </c>
       <c r="O430" t="n">
-        <v>484053.2990384592</v>
+        <v>484053.3263515215</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -19884,10 +19884,10 @@
         <v>800</v>
       </c>
       <c r="N434" t="n">
-        <v>1259.2746360505</v>
+        <v>1259.2746413793</v>
       </c>
       <c r="O434" t="n">
-        <v>1007419.7088404</v>
+        <v>1007419.71310344</v>
       </c>
       <c r="P434" t="n">
         <v>1900</v>
@@ -22529,10 +22529,10 @@
         <v>757</v>
       </c>
       <c r="N491" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O491" t="n">
-        <v>2354906.201909557</v>
+        <v>2354906.194048263</v>
       </c>
       <c r="P491" t="n">
         <v>4500</v>
@@ -23487,10 +23487,10 @@
         <v>47</v>
       </c>
       <c r="N512" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O512" t="n">
-        <v>74989.04762056579</v>
+        <v>74989.04526003779</v>
       </c>
       <c r="P512" t="n">
         <v>2500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -4194,10 +4194,10 @@
         <v>681</v>
       </c>
       <c r="N90" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O90" t="n">
-        <v>1758516.027243453</v>
+        <v>1758516.02520808</v>
       </c>
       <c r="P90" t="n">
         <v>4500</v>
@@ -6148,22 +6148,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M133" t="n">
-        <v>1746</v>
+        <v>1650</v>
       </c>
       <c r="N133" t="n">
         <v>2090.85</v>
       </c>
       <c r="O133" t="n">
-        <v>3650624.1</v>
+        <v>3449902.5</v>
       </c>
       <c r="P133" t="n">
         <v>2900</v>
       </c>
       <c r="Q133" t="n">
-        <v>5063400</v>
+        <v>4785000</v>
       </c>
     </row>
     <row r="134">
@@ -8889,10 +8889,10 @@
         <v>1882</v>
       </c>
       <c r="N193" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O193" t="n">
-        <v>2917464.904700526</v>
+        <v>2917464.907774584</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -11727,10 +11727,10 @@
         <v>64</v>
       </c>
       <c r="N257" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="O257" t="n">
-        <v>533297.8957575744</v>
+        <v>533297.8956962049</v>
       </c>
       <c r="P257" t="n">
         <v>14900</v>
@@ -17731,10 +17731,10 @@
         <v>292</v>
       </c>
       <c r="N387" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O387" t="n">
-        <v>4986188.940567372</v>
+        <v>4986188.940471011</v>
       </c>
       <c r="P387" t="n">
         <v>27500</v>
@@ -19615,10 +19615,10 @@
         <v>304</v>
       </c>
       <c r="N428" t="n">
-        <v>1592.2810401003</v>
+        <v>1592.2811378003</v>
       </c>
       <c r="O428" t="n">
-        <v>484053.4361904912</v>
+        <v>484053.4658912912</v>
       </c>
       <c r="P428" t="n">
         <v>2500</v>
@@ -22014,10 +22014,10 @@
         <v>149</v>
       </c>
       <c r="N480" t="n">
-        <v>517.29096206919</v>
+        <v>517.29097263266</v>
       </c>
       <c r="O480" t="n">
-        <v>77076.35334830931</v>
+        <v>77076.35492226634</v>
       </c>
       <c r="P480" t="n">
         <v>900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -4653,10 +4653,10 @@
         <v>144</v>
       </c>
       <c r="N100" t="n">
-        <v>3230.0670575693</v>
+        <v>3230.0670386266</v>
       </c>
       <c r="O100" t="n">
-        <v>465129.6562899792</v>
+        <v>465129.6535622304</v>
       </c>
       <c r="P100" t="n">
         <v>6200</v>
@@ -4979,10 +4979,10 @@
         <v>120</v>
       </c>
       <c r="N107" t="n">
-        <v>5002</v>
+        <v>5013.3940774487</v>
       </c>
       <c r="O107" t="n">
-        <v>600240</v>
+        <v>601607.289293844</v>
       </c>
       <c r="P107" t="n">
         <v>8400</v>
@@ -5337,10 +5337,10 @@
         <v>312</v>
       </c>
       <c r="N115" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O115" t="n">
-        <v>1525970.175388402</v>
+        <v>1525970.175407402</v>
       </c>
       <c r="P115" t="n">
         <v>8200</v>
@@ -6154,10 +6154,10 @@
         <v>1650</v>
       </c>
       <c r="N133" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O133" t="n">
-        <v>3449902.5</v>
+        <v>3452862.5193051</v>
       </c>
       <c r="P133" t="n">
         <v>2900</v>
@@ -6870,10 +6870,10 @@
         <v>1938</v>
       </c>
       <c r="N149" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O149" t="n">
-        <v>8473344.514446191</v>
+        <v>8473344.514665572</v>
       </c>
       <c r="P149" t="n">
         <v>7500</v>
@@ -6960,10 +6960,10 @@
         <v>241</v>
       </c>
       <c r="N151" t="n">
-        <v>1592.5662209302</v>
+        <v>1617.3578206079</v>
       </c>
       <c r="O151" t="n">
-        <v>383808.4592441782</v>
+        <v>389783.2347665039</v>
       </c>
       <c r="P151" t="n">
         <v>3900</v>
@@ -8751,10 +8751,10 @@
         <v>720</v>
       </c>
       <c r="N190" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O190" t="n">
-        <v>1174265.190725832</v>
+        <v>1174265.198483688</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8889,10 +8889,10 @@
         <v>1882</v>
       </c>
       <c r="N193" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O193" t="n">
-        <v>2917464.931686336</v>
+        <v>2917464.944865605</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -8981,10 +8981,10 @@
         <v>418</v>
       </c>
       <c r="N195" t="n">
-        <v>2403.5134379057</v>
+        <v>2403.513461205</v>
       </c>
       <c r="O195" t="n">
-        <v>1004668.617044583</v>
+        <v>1004668.62678369</v>
       </c>
       <c r="P195" t="n">
         <v>3500</v>
@@ -12982,10 +12982,10 @@
         <v>81</v>
       </c>
       <c r="N284" t="n">
-        <v>5218.1705692109</v>
+        <v>5218.1705706874</v>
       </c>
       <c r="O284" t="n">
-        <v>422671.8161060829</v>
+        <v>422671.8162256794</v>
       </c>
       <c r="P284" t="n">
         <v>8500</v>
@@ -13028,10 +13028,10 @@
         <v>1</v>
       </c>
       <c r="N285" t="n">
-        <v>1595.0093202147</v>
+        <v>1595.0093078324</v>
       </c>
       <c r="O285" t="n">
-        <v>1595.0093202147</v>
+        <v>1595.0093078324</v>
       </c>
       <c r="P285" t="n">
         <v>2600</v>
@@ -18833,10 +18833,10 @@
         <v>1320</v>
       </c>
       <c r="N411" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O411" t="n">
-        <v>2001171.201613188</v>
+        <v>2003536.186291068</v>
       </c>
       <c r="P411" t="n">
         <v>2300</v>
@@ -19109,10 +19109,10 @@
         <v>48</v>
       </c>
       <c r="N417" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O417" t="n">
-        <v>86544.7625981232</v>
+        <v>86544.76289290561</v>
       </c>
       <c r="P417" t="n">
         <v>2500</v>
@@ -19569,10 +19569,10 @@
         <v>304</v>
       </c>
       <c r="N427" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="O427" t="n">
-        <v>484053.5855497344</v>
+        <v>484053.6226455168</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
@@ -21968,10 +21968,10 @@
         <v>149</v>
       </c>
       <c r="N479" t="n">
-        <v>517.29128286432</v>
+        <v>518.11303680169</v>
       </c>
       <c r="O479" t="n">
-        <v>77076.40114678368</v>
+        <v>77198.84248345181</v>
       </c>
       <c r="P479" t="n">
         <v>900</v>
@@ -22842,10 +22842,10 @@
         <v>18602</v>
       </c>
       <c r="N498" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O498" t="n">
-        <v>13091994.99714439</v>
+        <v>13091994.93394279</v>
       </c>
       <c r="P498" t="n">
         <v>900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -4152,10 +4152,10 @@
         <v>681</v>
       </c>
       <c r="N89" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O89" t="n">
-        <v>1758516.005390708</v>
+        <v>1758516.001258196</v>
       </c>
       <c r="P89" t="n">
         <v>4500</v>
@@ -4521,10 +4521,10 @@
         <v>80</v>
       </c>
       <c r="N97" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O97" t="n">
-        <v>307329.9888</v>
+        <v>307329.989969912</v>
       </c>
       <c r="P97" t="n">
         <v>6900</v>
@@ -8709,10 +8709,10 @@
         <v>720</v>
       </c>
       <c r="N189" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O189" t="n">
-        <v>1174265.214844968</v>
+        <v>1174265.219144592</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
@@ -8939,10 +8939,10 @@
         <v>418</v>
       </c>
       <c r="N194" t="n">
-        <v>2403.5136926808</v>
+        <v>2403.513738111</v>
       </c>
       <c r="O194" t="n">
-        <v>1004668.723540574</v>
+        <v>1004668.742530398</v>
       </c>
       <c r="P194" t="n">
         <v>3500</v>
@@ -19200,10 +19200,10 @@
         <v>304</v>
       </c>
       <c r="N419" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="O419" t="n">
-        <v>484053.6509866768</v>
+        <v>484053.665327968</v>
       </c>
       <c r="P419" t="n">
         <v>2500</v>
@@ -22473,10 +22473,10 @@
         <v>18602</v>
       </c>
       <c r="N490" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O490" t="n">
-        <v>13091994.74959251</v>
+        <v>13091994.73689144</v>
       </c>
       <c r="P490" t="n">
         <v>900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -595,10 +595,10 @@
         <v>109</v>
       </c>
       <c r="N5" t="n">
-        <v>27000</v>
+        <v>27035.809018568</v>
       </c>
       <c r="O5" t="n">
-        <v>2943000</v>
+        <v>2946903.183023912</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3079710145</v>
+        <v>1811.3080365297</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3079710145</v>
+        <v>1811.3080365297</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464515243</v>
+        <v>3376.746444689</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.863147481</v>
+        <v>2985043.857105076</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -2128,10 +2128,10 @@
         <v>46</v>
       </c>
       <c r="N43" t="n">
-        <v>141416.88457516</v>
+        <v>141416.88459016</v>
       </c>
       <c r="O43" t="n">
-        <v>6505176.690457359</v>
+        <v>6505176.691147361</v>
       </c>
       <c r="P43" t="n">
         <v>251900</v>
@@ -2434,10 +2434,10 @@
         <v>144</v>
       </c>
       <c r="N50" t="n">
-        <v>580.36596205962</v>
+        <v>580.3659400545</v>
       </c>
       <c r="O50" t="n">
-        <v>83572.69853658527</v>
+        <v>83572.69536784801</v>
       </c>
       <c r="P50" t="n">
         <v>6800</v>
@@ -2480,10 +2480,10 @@
         <v>98</v>
       </c>
       <c r="N51" t="n">
-        <v>538.40045627376</v>
+        <v>538.40049618321</v>
       </c>
       <c r="O51" t="n">
-        <v>52763.24471482848</v>
+        <v>52763.24862595458</v>
       </c>
       <c r="P51" t="n">
         <v>6800</v>
@@ -2908,10 +2908,10 @@
         <v>41</v>
       </c>
       <c r="N61" t="n">
-        <v>732.63425531915</v>
+        <v>732.63427046263</v>
       </c>
       <c r="O61" t="n">
-        <v>30038.00446808515</v>
+        <v>30038.00508896783</v>
       </c>
       <c r="P61" t="n">
         <v>6200</v>
@@ -2998,10 +2998,10 @@
         <v>228</v>
       </c>
       <c r="N63" t="n">
-        <v>4937.3101649175</v>
+        <v>4937.3101654135</v>
       </c>
       <c r="O63" t="n">
-        <v>1125706.71760119</v>
+        <v>1125706.717714278</v>
       </c>
       <c r="P63" t="n">
         <v>7500</v>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3172,19 +3172,19 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N67" t="n">
         <v>14233.54</v>
       </c>
       <c r="O67" t="n">
-        <v>1651090.64</v>
+        <v>1594156.48</v>
       </c>
       <c r="P67" t="n">
         <v>10000</v>
       </c>
       <c r="Q67" t="n">
-        <v>1160000</v>
+        <v>1120000</v>
       </c>
     </row>
     <row r="68">
@@ -3219,10 +3219,10 @@
         <v>1271</v>
       </c>
       <c r="N68" t="n">
-        <v>1098.0622084592</v>
+        <v>1098.0624184202</v>
       </c>
       <c r="O68" t="n">
-        <v>1395637.066951643</v>
+        <v>1395637.333812074</v>
       </c>
       <c r="P68" t="n">
         <v>1500</v>
@@ -3624,10 +3624,10 @@
         <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>17207.41</v>
+        <v>17234.854035088</v>
       </c>
       <c r="O77" t="n">
-        <v>825955.6799999999</v>
+        <v>827272.993684224</v>
       </c>
       <c r="P77" t="n">
         <v>20000</v>
@@ -4152,10 +4152,10 @@
         <v>681</v>
       </c>
       <c r="N89" t="n">
-        <v>2582.2555084555</v>
+        <v>2582.2554768392</v>
       </c>
       <c r="O89" t="n">
-        <v>1758516.001258196</v>
+        <v>1758515.979727495</v>
       </c>
       <c r="P89" t="n">
         <v>4500</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>696</v>
+        <v>666</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4241,19 +4241,19 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>696</v>
+        <v>666</v>
       </c>
       <c r="N91" t="n">
-        <v>5216.8960524399</v>
+        <v>5216.8960380117</v>
       </c>
       <c r="O91" t="n">
-        <v>3630959.65249817</v>
+        <v>3474452.761315792</v>
       </c>
       <c r="P91" t="n">
         <v>8500</v>
       </c>
       <c r="Q91" t="n">
-        <v>5916000</v>
+        <v>5661000</v>
       </c>
     </row>
     <row r="92">
@@ -4475,10 +4475,10 @@
         <v>3167</v>
       </c>
       <c r="N96" t="n">
-        <v>3158.8608305026</v>
+        <v>3158.860831485</v>
       </c>
       <c r="O96" t="n">
-        <v>10004112.25020173</v>
+        <v>10004112.25331299</v>
       </c>
       <c r="P96" t="n">
         <v>5600</v>
@@ -4750,10 +4750,10 @@
         <v>259</v>
       </c>
       <c r="N102" t="n">
-        <v>2694.8231638418</v>
+        <v>2694.8231444759</v>
       </c>
       <c r="O102" t="n">
-        <v>697959.1994350263</v>
+        <v>697959.194419258</v>
       </c>
       <c r="P102" t="n">
         <v>4900</v>
@@ -4891,10 +4891,10 @@
         <v>47</v>
       </c>
       <c r="N105" t="n">
-        <v>8796</v>
+        <v>8807.6968085106</v>
       </c>
       <c r="O105" t="n">
-        <v>413412</v>
+        <v>413961.7499999982</v>
       </c>
       <c r="P105" t="n">
         <v>14900</v>
@@ -5070,10 +5070,10 @@
         <v>581</v>
       </c>
       <c r="N109" t="n">
-        <v>3795.7100075887</v>
+        <v>3795.7100075916</v>
       </c>
       <c r="O109" t="n">
-        <v>2205307.514409035</v>
+        <v>2205307.51441072</v>
       </c>
       <c r="P109" t="n">
         <v>6200</v>
@@ -5295,10 +5295,10 @@
         <v>312</v>
       </c>
       <c r="N114" t="n">
-        <v>4890.9300493827</v>
+        <v>4890.930049597</v>
       </c>
       <c r="O114" t="n">
-        <v>1525970.175407402</v>
+        <v>1525970.175474264</v>
       </c>
       <c r="P114" t="n">
         <v>8200</v>
@@ -5387,10 +5387,10 @@
         <v>135</v>
       </c>
       <c r="N116" t="n">
-        <v>5888</v>
+        <v>5946.1052631579</v>
       </c>
       <c r="O116" t="n">
-        <v>794880</v>
+        <v>802724.2105263164</v>
       </c>
       <c r="P116" t="n">
         <v>9500</v>
@@ -5794,10 +5794,10 @@
         <v>252</v>
       </c>
       <c r="N125" t="n">
-        <v>3594.2536883629</v>
+        <v>3594.253608522</v>
       </c>
       <c r="O125" t="n">
-        <v>905751.9294674508</v>
+        <v>905751.909347544</v>
       </c>
       <c r="P125" t="n">
         <v>6500</v>
@@ -5835,10 +5835,10 @@
         <v>108</v>
       </c>
       <c r="N126" t="n">
-        <v>3240.8500375235</v>
+        <v>3240.8500395257</v>
       </c>
       <c r="O126" t="n">
-        <v>350011.804052538</v>
+        <v>350011.8042687756</v>
       </c>
       <c r="P126" t="n">
         <v>5200</v>
@@ -6019,10 +6019,10 @@
         <v>305</v>
       </c>
       <c r="N130" t="n">
-        <v>14822.378847539</v>
+        <v>14822.378837068</v>
       </c>
       <c r="O130" t="n">
-        <v>4520825.548499395</v>
+        <v>4520825.54530574</v>
       </c>
       <c r="P130" t="n">
         <v>24900</v>
@@ -6292,10 +6292,10 @@
         <v>708</v>
       </c>
       <c r="N136" t="n">
-        <v>2665.4</v>
+        <v>2667.0463248919</v>
       </c>
       <c r="O136" t="n">
-        <v>1887103.2</v>
+        <v>1888268.798023465</v>
       </c>
       <c r="P136" t="n">
         <v>20900</v>
@@ -6700,10 +6700,10 @@
         <v>210</v>
       </c>
       <c r="N145" t="n">
-        <v>3041.6600136054</v>
+        <v>3041.6600136893</v>
       </c>
       <c r="O145" t="n">
-        <v>638748.602857134</v>
+        <v>638748.6028747529</v>
       </c>
       <c r="P145" t="n">
         <v>5500</v>
@@ -6828,10 +6828,10 @@
         <v>1938</v>
       </c>
       <c r="N148" t="n">
-        <v>4372.2107921642</v>
+        <v>4372.5234503719</v>
       </c>
       <c r="O148" t="n">
-        <v>8473344.51521422</v>
+        <v>8473950.446820743</v>
       </c>
       <c r="P148" t="n">
         <v>7500</v>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -6869,19 +6869,19 @@
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="N149" t="n">
         <v>6441.03</v>
       </c>
       <c r="O149" t="n">
-        <v>5300967.689999999</v>
+        <v>5223675.33</v>
       </c>
       <c r="P149" t="n">
         <v>10500</v>
       </c>
       <c r="Q149" t="n">
-        <v>8641500</v>
+        <v>8515500</v>
       </c>
     </row>
     <row r="150">
@@ -6918,10 +6918,10 @@
         <v>241</v>
       </c>
       <c r="N150" t="n">
-        <v>1592.5661309524</v>
+        <v>1592.5660665658</v>
       </c>
       <c r="O150" t="n">
-        <v>383808.4375595284</v>
+        <v>383808.4220423578</v>
       </c>
       <c r="P150" t="n">
         <v>3900</v>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -7130,19 +7130,19 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="N155" t="n">
         <v>4717</v>
       </c>
       <c r="O155" t="n">
-        <v>924532</v>
+        <v>688682</v>
       </c>
       <c r="P155" t="n">
         <v>7900</v>
       </c>
       <c r="Q155" t="n">
-        <v>1548400</v>
+        <v>1153400</v>
       </c>
     </row>
     <row r="156">
@@ -7544,10 +7544,10 @@
         <v>2732</v>
       </c>
       <c r="N164" t="n">
-        <v>17472.91</v>
+        <v>17473.953844316</v>
       </c>
       <c r="O164" t="n">
-        <v>47735990.12</v>
+        <v>47738841.90267131</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -7632,10 +7632,10 @@
         <v>2781</v>
       </c>
       <c r="N166" t="n">
-        <v>1530.63</v>
+        <v>1530.7162764218</v>
       </c>
       <c r="O166" t="n">
-        <v>4256682.03</v>
+        <v>4256921.964729026</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -8189,19 +8189,19 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N178" t="n">
         <v>3761.6</v>
       </c>
       <c r="O178" t="n">
-        <v>214411.2</v>
+        <v>180556.8</v>
       </c>
       <c r="P178" t="n">
         <v>6900</v>
       </c>
       <c r="Q178" t="n">
-        <v>393300</v>
+        <v>331200</v>
       </c>
     </row>
     <row r="179">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -8611,19 +8611,19 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="N187" t="n">
         <v>3751</v>
       </c>
       <c r="O187" t="n">
-        <v>1980528</v>
+        <v>1920512</v>
       </c>
       <c r="P187" t="n">
         <v>6400</v>
       </c>
       <c r="Q187" t="n">
-        <v>3379200</v>
+        <v>3276800</v>
       </c>
     </row>
     <row r="188">
@@ -8709,10 +8709,10 @@
         <v>720</v>
       </c>
       <c r="N189" t="n">
-        <v>1630.9239154786</v>
+        <v>1630.9239476386</v>
       </c>
       <c r="O189" t="n">
-        <v>1174265.219144592</v>
+        <v>1174265.242299792</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
@@ -8755,10 +8755,10 @@
         <v>5</v>
       </c>
       <c r="N190" t="n">
-        <v>1467.3144171779</v>
+        <v>1467.3135220126</v>
       </c>
       <c r="O190" t="n">
-        <v>7336.5720858895</v>
+        <v>7336.567610063001</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8801,10 +8801,10 @@
         <v>272</v>
       </c>
       <c r="N191" t="n">
-        <v>1690.5944611529</v>
+        <v>1690.5922846782</v>
       </c>
       <c r="O191" t="n">
-        <v>459841.6934335888</v>
+        <v>459841.1014324704</v>
       </c>
       <c r="P191" t="n">
         <v>2900</v>
@@ -8847,10 +8847,10 @@
         <v>1882</v>
       </c>
       <c r="N192" t="n">
-        <v>1550.1939407455</v>
+        <v>1550.1940319426</v>
       </c>
       <c r="O192" t="n">
-        <v>2917464.996483031</v>
+        <v>2917465.168115973</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8893,10 +8893,10 @@
         <v>22</v>
       </c>
       <c r="N193" t="n">
-        <v>1579.388566879</v>
+        <v>1579.3884193548</v>
       </c>
       <c r="O193" t="n">
-        <v>34746.548471338</v>
+        <v>34746.5452258056</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8939,10 +8939,10 @@
         <v>418</v>
       </c>
       <c r="N194" t="n">
-        <v>2403.513738111</v>
+        <v>2403.5140171519</v>
       </c>
       <c r="O194" t="n">
-        <v>1004668.742530398</v>
+        <v>1004668.859169494</v>
       </c>
       <c r="P194" t="n">
         <v>3500</v>
@@ -10023,10 +10023,10 @@
         <v>361</v>
       </c>
       <c r="N218" t="n">
-        <v>4196.8725326298</v>
+        <v>4196.8725382689</v>
       </c>
       <c r="O218" t="n">
-        <v>1515070.984279358</v>
+        <v>1515070.986315073</v>
       </c>
       <c r="P218" t="n">
         <v>5900</v>
@@ -10402,10 +10402,10 @@
         <v>84</v>
       </c>
       <c r="N227" t="n">
-        <v>2567</v>
+        <v>2569.7269830028</v>
       </c>
       <c r="O227" t="n">
-        <v>215628</v>
+        <v>215857.0665722352</v>
       </c>
       <c r="P227" t="n">
         <v>4500</v>
@@ -10794,10 +10794,10 @@
         <v>12</v>
       </c>
       <c r="N236" t="n">
-        <v>3731.0243521595</v>
+        <v>3731.0243959732</v>
       </c>
       <c r="O236" t="n">
-        <v>44772.292225914</v>
+        <v>44772.2927516784</v>
       </c>
       <c r="P236" t="n">
         <v>5200</v>
@@ -10935,10 +10935,10 @@
         <v>113</v>
       </c>
       <c r="N239" t="n">
-        <v>4285.1957990868</v>
+        <v>4285.1958525346</v>
       </c>
       <c r="O239" t="n">
-        <v>484227.1252968084</v>
+        <v>484227.1313364098</v>
       </c>
       <c r="P239" t="n">
         <v>6900</v>
@@ -11194,10 +11194,10 @@
         <v>563</v>
       </c>
       <c r="N245" t="n">
-        <v>4605.2147677725</v>
+        <v>4605.2147813688</v>
       </c>
       <c r="O245" t="n">
-        <v>2592735.914255918</v>
+        <v>2592735.921910634</v>
       </c>
       <c r="P245" t="n">
         <v>7600</v>
@@ -11327,10 +11327,10 @@
         <v>19</v>
       </c>
       <c r="N248" t="n">
-        <v>13513.643203125</v>
+        <v>13513.643253968</v>
       </c>
       <c r="O248" t="n">
-        <v>256759.220859375</v>
+        <v>256759.221825392</v>
       </c>
       <c r="P248" t="n">
         <v>21900</v>
@@ -11511,10 +11511,10 @@
         <v>94</v>
       </c>
       <c r="N252" t="n">
-        <v>27123.765142315</v>
+        <v>27123.765105163</v>
       </c>
       <c r="O252" t="n">
-        <v>2549633.92337761</v>
+        <v>2549633.919885322</v>
       </c>
       <c r="P252" t="n">
         <v>44500</v>
@@ -11685,10 +11685,10 @@
         <v>64</v>
       </c>
       <c r="N256" t="n">
-        <v>8332.7796143959</v>
+        <v>8332.779613402099</v>
       </c>
       <c r="O256" t="n">
-        <v>533297.8953213376</v>
+        <v>533297.8952577343</v>
       </c>
       <c r="P256" t="n">
         <v>14900</v>
@@ -11731,10 +11731,10 @@
         <v>599</v>
       </c>
       <c r="N257" t="n">
-        <v>1561.0027356625</v>
+        <v>1561.0028372093</v>
       </c>
       <c r="O257" t="n">
-        <v>935040.6386618376</v>
+        <v>935040.6994883707</v>
       </c>
       <c r="P257" t="n">
         <v>2900</v>
@@ -11869,10 +11869,10 @@
         <v>188</v>
       </c>
       <c r="N260" t="n">
-        <v>7969.9501675552</v>
+        <v>7982.1180305344</v>
       </c>
       <c r="O260" t="n">
-        <v>1498350.631500378</v>
+        <v>1500638.189740467</v>
       </c>
       <c r="P260" t="n">
         <v>12900</v>
@@ -12940,10 +12940,10 @@
         <v>81</v>
       </c>
       <c r="N283" t="n">
-        <v>5218.1705736636</v>
+        <v>5218.1705744125</v>
       </c>
       <c r="O283" t="n">
-        <v>422671.8164667516</v>
+        <v>422671.8165274125</v>
       </c>
       <c r="P283" t="n">
         <v>8500</v>
@@ -13449,10 +13449,10 @@
         <v>76</v>
       </c>
       <c r="N294" t="n">
-        <v>14380</v>
+        <v>14447.670588235</v>
       </c>
       <c r="O294" t="n">
-        <v>1092880</v>
+        <v>1098022.96470586</v>
       </c>
       <c r="P294" t="n">
         <v>23000</v>
@@ -13682,10 +13682,10 @@
         <v>784</v>
       </c>
       <c r="N299" t="n">
-        <v>1778.4726787358</v>
+        <v>1778.4726973583</v>
       </c>
       <c r="O299" t="n">
-        <v>1394322.580128867</v>
+        <v>1394322.594728907</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
@@ -15573,10 +15573,10 @@
         <v>324</v>
       </c>
       <c r="N340" t="n">
-        <v>2328.1186963238</v>
+        <v>2328.1186869944</v>
       </c>
       <c r="O340" t="n">
-        <v>754310.4576089112</v>
+        <v>754310.4545861856</v>
       </c>
       <c r="P340" t="n">
         <v>4500</v>
@@ -16217,10 +16217,10 @@
         <v>137</v>
       </c>
       <c r="N354" t="n">
-        <v>4907.8222048611</v>
+        <v>4907.8223782772</v>
       </c>
       <c r="O354" t="n">
-        <v>672371.6420659707</v>
+        <v>672371.6658239764</v>
       </c>
       <c r="P354" t="n">
         <v>8200</v>
@@ -16401,10 +16401,10 @@
         <v>276</v>
       </c>
       <c r="N358" t="n">
-        <v>3903.7370093458</v>
+        <v>3903.7373747017</v>
       </c>
       <c r="O358" t="n">
-        <v>1077431.414579441</v>
+        <v>1077431.515417669</v>
       </c>
       <c r="P358" t="n">
         <v>7500</v>
@@ -17362,10 +17362,10 @@
         <v>292</v>
       </c>
       <c r="N379" t="n">
-        <v>17075.989522161</v>
+        <v>17075.98952183</v>
       </c>
       <c r="O379" t="n">
-        <v>4986188.940471011</v>
+        <v>4986188.94037436</v>
       </c>
       <c r="P379" t="n">
         <v>27500</v>
@@ -18234,10 +18234,10 @@
         <v>1126</v>
       </c>
       <c r="N398" t="n">
-        <v>3821</v>
+        <v>3821.6520477816</v>
       </c>
       <c r="O398" t="n">
-        <v>4302446</v>
+        <v>4303180.205802081</v>
       </c>
       <c r="P398" t="n">
         <v>5900</v>
@@ -18280,10 +18280,10 @@
         <v>14</v>
       </c>
       <c r="N399" t="n">
-        <v>15472</v>
+        <v>15512.291666667</v>
       </c>
       <c r="O399" t="n">
-        <v>216608</v>
+        <v>217172.083333338</v>
       </c>
       <c r="P399" t="n">
         <v>25900</v>
@@ -18510,10 +18510,10 @@
         <v>1320</v>
       </c>
       <c r="N404" t="n">
-        <v>1516.0387847976</v>
+        <v>1516.0387762203</v>
       </c>
       <c r="O404" t="n">
-        <v>2001171.195932832</v>
+        <v>2001171.184610796</v>
       </c>
       <c r="P404" t="n">
         <v>2300</v>
@@ -18602,10 +18602,10 @@
         <v>48</v>
       </c>
       <c r="N406" t="n">
-        <v>2458.5128483396</v>
+        <v>2458.5128385327</v>
       </c>
       <c r="O406" t="n">
-        <v>118008.6167203008</v>
+        <v>118008.6162495696</v>
       </c>
       <c r="P406" t="n">
         <v>3500</v>
@@ -18648,10 +18648,10 @@
         <v>48</v>
       </c>
       <c r="N407" t="n">
-        <v>1771.090242915</v>
+        <v>1771.0901699524</v>
       </c>
       <c r="O407" t="n">
-        <v>85012.33165992</v>
+        <v>85012.32815771519</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
@@ -18694,10 +18694,10 @@
         <v>168</v>
       </c>
       <c r="N408" t="n">
-        <v>2079.3838525155</v>
+        <v>2079.3837839721</v>
       </c>
       <c r="O408" t="n">
-        <v>349336.487222604</v>
+        <v>349336.4757073128</v>
       </c>
       <c r="P408" t="n">
         <v>2900</v>
@@ -18740,10 +18740,10 @@
         <v>48</v>
       </c>
       <c r="N409" t="n">
-        <v>1803.0158997564</v>
+        <v>1803.0159162304</v>
       </c>
       <c r="O409" t="n">
-        <v>86544.7631883072</v>
+        <v>86544.76397905921</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
@@ -18786,10 +18786,10 @@
         <v>156</v>
       </c>
       <c r="N410" t="n">
-        <v>3306.5945945946</v>
+        <v>3306.5945783133</v>
       </c>
       <c r="O410" t="n">
-        <v>515828.7567567576</v>
+        <v>515828.7542168748</v>
       </c>
       <c r="P410" t="n">
         <v>4900</v>
@@ -18832,10 +18832,10 @@
         <v>96</v>
       </c>
       <c r="N411" t="n">
-        <v>2108.7936087295</v>
+        <v>2108.7939012739</v>
       </c>
       <c r="O411" t="n">
-        <v>202444.186438032</v>
+        <v>202444.2145222944</v>
       </c>
       <c r="P411" t="n">
         <v>2900</v>
@@ -18878,10 +18878,10 @@
         <v>144</v>
       </c>
       <c r="N412" t="n">
-        <v>2056.0827629734</v>
+        <v>2056.082714437</v>
       </c>
       <c r="O412" t="n">
-        <v>296075.9178681696</v>
+        <v>296075.910878928</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18924,10 +18924,10 @@
         <v>90</v>
       </c>
       <c r="N413" t="n">
-        <v>3224.56895</v>
+        <v>3224.5689724311</v>
       </c>
       <c r="O413" t="n">
-        <v>290211.2055</v>
+        <v>290211.207518799</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18970,10 +18970,10 @@
         <v>360</v>
       </c>
       <c r="N414" t="n">
-        <v>1655.9303958333</v>
+        <v>1655.9303421788</v>
       </c>
       <c r="O414" t="n">
-        <v>596134.942499988</v>
+        <v>596134.9231843679</v>
       </c>
       <c r="P414" t="n">
         <v>2500</v>
@@ -19200,10 +19200,10 @@
         <v>304</v>
       </c>
       <c r="N419" t="n">
-        <v>1592.281793842</v>
+        <v>1592.2820519836</v>
       </c>
       <c r="O419" t="n">
-        <v>484053.665327968</v>
+        <v>484053.7438030144</v>
       </c>
       <c r="P419" t="n">
         <v>2500</v>
@@ -19285,10 +19285,10 @@
         <v>8</v>
       </c>
       <c r="N421" t="n">
-        <v>5347.73</v>
+        <v>5372.836713615</v>
       </c>
       <c r="O421" t="n">
-        <v>42781.84</v>
+        <v>42982.69370892</v>
       </c>
       <c r="P421" t="n">
         <v>9500</v>
@@ -19331,10 +19331,10 @@
         <v>408</v>
       </c>
       <c r="N422" t="n">
-        <v>2060.1594311927</v>
+        <v>2060.1591932458</v>
       </c>
       <c r="O422" t="n">
-        <v>840545.0479266216</v>
+        <v>840544.9508442864</v>
       </c>
       <c r="P422" t="n">
         <v>2900</v>
@@ -19377,10 +19377,10 @@
         <v>800</v>
       </c>
       <c r="N423" t="n">
-        <v>1259.2746638947</v>
+        <v>1259.2746779425</v>
       </c>
       <c r="O423" t="n">
-        <v>1007419.73111576</v>
+        <v>1007419.742354</v>
       </c>
       <c r="P423" t="n">
         <v>1900</v>
@@ -19464,10 +19464,10 @@
         <v>97</v>
       </c>
       <c r="N425" t="n">
-        <v>2842.2744460028</v>
+        <v>2842.2744382022</v>
       </c>
       <c r="O425" t="n">
-        <v>275700.6212622716</v>
+        <v>275700.6205056134</v>
       </c>
       <c r="P425" t="n">
         <v>4900</v>
@@ -19600,10 +19600,10 @@
         <v>516</v>
       </c>
       <c r="N428" t="n">
-        <v>692.15226424361</v>
+        <v>692.15226870079</v>
       </c>
       <c r="O428" t="n">
-        <v>357150.5683497027</v>
+        <v>357150.5706496077</v>
       </c>
       <c r="P428" t="n">
         <v>1200</v>
@@ -19649,10 +19649,10 @@
         <v>76</v>
       </c>
       <c r="N429" t="n">
-        <v>18491</v>
+        <v>18654.637168142</v>
       </c>
       <c r="O429" t="n">
-        <v>1405316</v>
+        <v>1417752.424778792</v>
       </c>
       <c r="P429" t="n">
         <v>13500</v>
@@ -20666,10 +20666,10 @@
         <v>20</v>
       </c>
       <c r="N451" t="n">
-        <v>2357.74</v>
+        <v>2407.2030769231</v>
       </c>
       <c r="O451" t="n">
-        <v>47154.8</v>
+        <v>48144.061538462</v>
       </c>
       <c r="P451" t="n">
         <v>3000</v>
@@ -21365,10 +21365,10 @@
         <v>99</v>
       </c>
       <c r="N466" t="n">
-        <v>1283.6532462687</v>
+        <v>1283.6530916031</v>
       </c>
       <c r="O466" t="n">
-        <v>127081.6713806013</v>
+        <v>127081.6560687069</v>
       </c>
       <c r="P466" t="n">
         <v>1900</v>
@@ -21501,10 +21501,10 @@
         <v>52</v>
       </c>
       <c r="N469" t="n">
-        <v>4032.3968051948</v>
+        <v>4032.396796875</v>
       </c>
       <c r="O469" t="n">
-        <v>209684.6338701296</v>
+        <v>209684.6334375</v>
       </c>
       <c r="P469" t="n">
         <v>4200</v>
@@ -21599,10 +21599,10 @@
         <v>149</v>
       </c>
       <c r="N471" t="n">
-        <v>517.29151641831</v>
+        <v>517.2923857868</v>
       </c>
       <c r="O471" t="n">
-        <v>77076.4359463282</v>
+        <v>77076.5654822332</v>
       </c>
       <c r="P471" t="n">
         <v>900</v>
@@ -22022,10 +22022,10 @@
         <v>757</v>
       </c>
       <c r="N480" t="n">
-        <v>3110.8401559454</v>
+        <v>3110.8400113026</v>
       </c>
       <c r="O480" t="n">
-        <v>2354905.998050668</v>
+        <v>2354905.888556068</v>
       </c>
       <c r="P480" t="n">
         <v>4500</v>
@@ -22473,10 +22473,10 @@
         <v>18602</v>
       </c>
       <c r="N490" t="n">
-        <v>703.79500789654</v>
+        <v>703.7949766627</v>
       </c>
       <c r="O490" t="n">
-        <v>13091994.73689144</v>
+        <v>13091994.15587955</v>
       </c>
       <c r="P490" t="n">
         <v>900</v>
@@ -22614,10 +22614,10 @@
         <v>66</v>
       </c>
       <c r="N493" t="n">
-        <v>2501.3848325359</v>
+        <v>2501.3847317073</v>
       </c>
       <c r="O493" t="n">
-        <v>165091.3989473694</v>
+        <v>165091.3922926818</v>
       </c>
       <c r="P493" t="n">
         <v>4100</v>
@@ -22980,10 +22980,10 @@
         <v>47</v>
       </c>
       <c r="N501" t="n">
-        <v>1595.5001480385</v>
+        <v>1595.4999702159</v>
       </c>
       <c r="O501" t="n">
-        <v>74988.5069578095</v>
+        <v>74988.4986001473</v>
       </c>
       <c r="P501" t="n">
         <v>2500</v>
@@ -24470,7 +24470,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24479,19 +24479,19 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="N532" t="n">
         <v>2992.5702739726</v>
       </c>
       <c r="O532" t="n">
-        <v>77806.8271232876</v>
+        <v>32918.2730136986</v>
       </c>
       <c r="P532" t="n">
         <v>6000</v>
       </c>
       <c r="Q532" t="n">
-        <v>156000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="533">
@@ -24528,10 +24528,10 @@
         <v>164</v>
       </c>
       <c r="N533" t="n">
-        <v>875.69017316017</v>
+        <v>875.6901754386</v>
       </c>
       <c r="O533" t="n">
-        <v>143613.1883982679</v>
+        <v>143613.1887719304</v>
       </c>
       <c r="P533" t="n">
         <v>4500</v>
@@ -24904,10 +24904,10 @@
         <v>100</v>
       </c>
       <c r="N541" t="n">
-        <v>3067.0905844156</v>
+        <v>3067.0906</v>
       </c>
       <c r="O541" t="n">
-        <v>306709.05844156</v>
+        <v>306709.06</v>
       </c>
       <c r="P541" t="n">
         <v>7200</v>
@@ -25769,10 +25769,10 @@
         <v>21</v>
       </c>
       <c r="N559" t="n">
-        <v>10737.526170213</v>
+        <v>10737.525909091</v>
       </c>
       <c r="O559" t="n">
-        <v>225488.049574473</v>
+        <v>225488.044090911</v>
       </c>
       <c r="P559" t="n">
         <v>18900</v>
@@ -26659,10 +26659,10 @@
         <v>75</v>
       </c>
       <c r="N578" t="n">
-        <v>5216.9</v>
+        <v>5235.0773519164</v>
       </c>
       <c r="O578" t="n">
-        <v>391267.5</v>
+        <v>392630.80139373</v>
       </c>
       <c r="P578" t="n">
         <v>20500</v>
@@ -26948,10 +26948,10 @@
         <v>1105</v>
       </c>
       <c r="N584" t="n">
-        <v>7046.9398275119</v>
+        <v>7049.9805782093</v>
       </c>
       <c r="O584" t="n">
-        <v>7786868.50940065</v>
+        <v>7790228.538921276</v>
       </c>
       <c r="P584" t="n">
         <v>9900</v>
@@ -27043,10 +27043,10 @@
         <v>1</v>
       </c>
       <c r="N586" t="n">
-        <v>16146.4984</v>
+        <v>16146.498333333</v>
       </c>
       <c r="O586" t="n">
-        <v>16146.4984</v>
+        <v>16146.498333333</v>
       </c>
       <c r="P586" t="n">
         <v>26900</v>
@@ -27138,10 +27138,10 @@
         <v>648</v>
       </c>
       <c r="N588" t="n">
-        <v>665.32371673004</v>
+        <v>665.32374700527</v>
       </c>
       <c r="O588" t="n">
-        <v>431129.7684410659</v>
+        <v>431129.7880594149</v>
       </c>
       <c r="P588" t="n">
         <v>2900</v>
@@ -27576,10 +27576,10 @@
         <v>95</v>
       </c>
       <c r="N597" t="n">
-        <v>315.02705797101</v>
+        <v>315.02716176471</v>
       </c>
       <c r="O597" t="n">
-        <v>29927.57050724595</v>
+        <v>29927.58036764745</v>
       </c>
       <c r="P597" t="n">
         <v>2200</v>
@@ -28120,7 +28120,7 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
@@ -28129,19 +28129,19 @@
         <v>0</v>
       </c>
       <c r="M610" t="n">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="N610" t="n">
         <v>3181.9</v>
       </c>
       <c r="O610" t="n">
-        <v>2325968.9</v>
+        <v>2275058.5</v>
       </c>
       <c r="P610" t="n">
         <v>5100</v>
       </c>
       <c r="Q610" t="n">
-        <v>3728100</v>
+        <v>3646500</v>
       </c>
     </row>
     <row r="611">
@@ -28622,10 +28622,10 @@
         <v>341</v>
       </c>
       <c r="N621" t="n">
-        <v>22951.704779221</v>
+        <v>22951.704751958</v>
       </c>
       <c r="O621" t="n">
-        <v>7826531.329714361</v>
+        <v>7826531.320417678</v>
       </c>
       <c r="P621" t="n">
         <v>37900</v>
@@ -28709,10 +28709,10 @@
         <v>43</v>
       </c>
       <c r="N623" t="n">
-        <v>4985.40591133</v>
+        <v>4985.4060913706</v>
       </c>
       <c r="O623" t="n">
-        <v>214372.45418719</v>
+        <v>214372.4619289358</v>
       </c>
       <c r="P623" t="n">
         <v>7900</v>
@@ -28811,10 +28811,10 @@
         <v>294</v>
       </c>
       <c r="N625" t="n">
-        <v>1757.3205652174</v>
+        <v>1757.3205676856</v>
       </c>
       <c r="O625" t="n">
-        <v>516652.2461739156</v>
+        <v>516652.2468995664</v>
       </c>
       <c r="P625" t="n">
         <v>2000</v>
@@ -28949,10 +28949,10 @@
         <v>2800</v>
       </c>
       <c r="N628" t="n">
-        <v>220.00454362906</v>
+        <v>220.00364812669</v>
       </c>
       <c r="O628" t="n">
-        <v>616012.722161368</v>
+        <v>616010.214754732</v>
       </c>
       <c r="P628" t="n">
         <v>260</v>
@@ -29041,10 +29041,10 @@
         <v>82</v>
       </c>
       <c r="N630" t="n">
-        <v>13493.858308157</v>
+        <v>13493.858297872</v>
       </c>
       <c r="O630" t="n">
-        <v>1106496.381268874</v>
+        <v>1106496.380425504</v>
       </c>
       <c r="P630" t="n">
         <v>16900</v>
@@ -29213,7 +29213,7 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
@@ -29222,19 +29222,19 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N634" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O634" t="n">
-        <v>155331.04</v>
+        <v>116498.28</v>
       </c>
       <c r="P634" t="n">
         <v>10200</v>
       </c>
       <c r="Q634" t="n">
-        <v>163200</v>
+        <v>122400</v>
       </c>
     </row>
     <row r="635">
@@ -29581,7 +29581,7 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
@@ -29590,19 +29590,19 @@
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="N642" t="n">
         <v>9240</v>
       </c>
       <c r="O642" t="n">
-        <v>3954720</v>
+        <v>3769920</v>
       </c>
       <c r="P642" t="n">
         <v>11500</v>
       </c>
       <c r="Q642" t="n">
-        <v>4922000</v>
+        <v>4692000</v>
       </c>
     </row>
     <row r="643">
@@ -29627,7 +29627,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -29636,19 +29636,19 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="N643" t="n">
         <v>4576</v>
       </c>
       <c r="O643" t="n">
-        <v>658944</v>
+        <v>617760</v>
       </c>
       <c r="P643" t="n">
         <v>5900</v>
       </c>
       <c r="Q643" t="n">
-        <v>849600</v>
+        <v>796500</v>
       </c>
     </row>
     <row r="644">
@@ -30012,10 +30012,10 @@
         <v>173</v>
       </c>
       <c r="N651" t="n">
-        <v>1319.3609009009</v>
+        <v>1319.3609036145</v>
       </c>
       <c r="O651" t="n">
-        <v>228249.4358558557</v>
+        <v>228249.4363253085</v>
       </c>
       <c r="P651" t="n">
         <v>3500</v>
@@ -30255,10 +30255,10 @@
         <v>158</v>
       </c>
       <c r="N656" t="n">
-        <v>2539.5715978456</v>
+        <v>2539.5716527391</v>
       </c>
       <c r="O656" t="n">
-        <v>401252.3124596048</v>
+        <v>401252.3211327778</v>
       </c>
       <c r="P656" t="n">
         <v>3500</v>
@@ -30301,10 +30301,10 @@
         <v>95</v>
       </c>
       <c r="N657" t="n">
-        <v>4171.6686597938</v>
+        <v>4171.6686473988</v>
       </c>
       <c r="O657" t="n">
-        <v>396308.5226804109</v>
+        <v>396308.521502886</v>
       </c>
       <c r="P657" t="n">
         <v>5500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -595,10 +595,10 @@
         <v>109</v>
       </c>
       <c r="N5" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>2946903.183023912</v>
+        <v>2943000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -3624,10 +3624,10 @@
         <v>48</v>
       </c>
       <c r="N77" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O77" t="n">
-        <v>827272.993684224</v>
+        <v>825955.6799999999</v>
       </c>
       <c r="P77" t="n">
         <v>20000</v>
@@ -4891,10 +4891,10 @@
         <v>47</v>
       </c>
       <c r="N105" t="n">
-        <v>8807.6968085106</v>
+        <v>8796</v>
       </c>
       <c r="O105" t="n">
-        <v>413961.7499999982</v>
+        <v>413412</v>
       </c>
       <c r="P105" t="n">
         <v>14900</v>
@@ -5387,10 +5387,10 @@
         <v>135</v>
       </c>
       <c r="N116" t="n">
-        <v>5946.1052631579</v>
+        <v>5888</v>
       </c>
       <c r="O116" t="n">
-        <v>802724.2105263164</v>
+        <v>794880</v>
       </c>
       <c r="P116" t="n">
         <v>9500</v>
@@ -6292,10 +6292,10 @@
         <v>708</v>
       </c>
       <c r="N136" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O136" t="n">
-        <v>1888268.798023465</v>
+        <v>1887103.2</v>
       </c>
       <c r="P136" t="n">
         <v>20900</v>
@@ -6828,10 +6828,10 @@
         <v>1938</v>
       </c>
       <c r="N148" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O148" t="n">
-        <v>8473950.446820743</v>
+        <v>8473344.515543485</v>
       </c>
       <c r="P148" t="n">
         <v>7500</v>
@@ -7544,10 +7544,10 @@
         <v>2732</v>
       </c>
       <c r="N164" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O164" t="n">
-        <v>47738841.90267131</v>
+        <v>47735990.12</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -7632,10 +7632,10 @@
         <v>2781</v>
       </c>
       <c r="N166" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O166" t="n">
-        <v>4256921.964729026</v>
+        <v>4256682.03</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -10402,10 +10402,10 @@
         <v>84</v>
       </c>
       <c r="N227" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O227" t="n">
-        <v>215857.0665722352</v>
+        <v>215628</v>
       </c>
       <c r="P227" t="n">
         <v>4500</v>
@@ -11869,10 +11869,10 @@
         <v>188</v>
       </c>
       <c r="N260" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O260" t="n">
-        <v>1500638.189740467</v>
+        <v>1498350.631572513</v>
       </c>
       <c r="P260" t="n">
         <v>12900</v>
@@ -13449,10 +13449,10 @@
         <v>76</v>
       </c>
       <c r="N294" t="n">
-        <v>14447.670588235</v>
+        <v>14380</v>
       </c>
       <c r="O294" t="n">
-        <v>1098022.96470586</v>
+        <v>1092880</v>
       </c>
       <c r="P294" t="n">
         <v>23000</v>
@@ -18234,10 +18234,10 @@
         <v>1126</v>
       </c>
       <c r="N398" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O398" t="n">
-        <v>4303180.205802081</v>
+        <v>4302446</v>
       </c>
       <c r="P398" t="n">
         <v>5900</v>
@@ -18280,10 +18280,10 @@
         <v>14</v>
       </c>
       <c r="N399" t="n">
-        <v>15512.291666667</v>
+        <v>15472</v>
       </c>
       <c r="O399" t="n">
-        <v>217172.083333338</v>
+        <v>216608</v>
       </c>
       <c r="P399" t="n">
         <v>25900</v>
@@ -19285,10 +19285,10 @@
         <v>8</v>
       </c>
       <c r="N421" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O421" t="n">
-        <v>42982.69370892</v>
+        <v>42781.84</v>
       </c>
       <c r="P421" t="n">
         <v>9500</v>
@@ -19649,10 +19649,10 @@
         <v>76</v>
       </c>
       <c r="N429" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="O429" t="n">
-        <v>1417752.424778792</v>
+        <v>1405316</v>
       </c>
       <c r="P429" t="n">
         <v>13500</v>
@@ -20666,10 +20666,10 @@
         <v>20</v>
       </c>
       <c r="N451" t="n">
-        <v>2407.2030769231</v>
+        <v>2357.74</v>
       </c>
       <c r="O451" t="n">
-        <v>48144.061538462</v>
+        <v>47154.8</v>
       </c>
       <c r="P451" t="n">
         <v>3000</v>
@@ -26659,10 +26659,10 @@
         <v>75</v>
       </c>
       <c r="N578" t="n">
-        <v>5235.0773519164</v>
+        <v>5216.9</v>
       </c>
       <c r="O578" t="n">
-        <v>392630.80139373</v>
+        <v>391267.5</v>
       </c>
       <c r="P578" t="n">
         <v>20500</v>
@@ -26948,10 +26948,10 @@
         <v>1105</v>
       </c>
       <c r="N584" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O584" t="n">
-        <v>7790228.538921276</v>
+        <v>7786868.509277221</v>
       </c>
       <c r="P584" t="n">
         <v>9900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -1794,10 +1794,10 @@
         <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>10994.361818182</v>
+        <v>10994.362222222</v>
       </c>
       <c r="O35" t="n">
-        <v>65966.170909092</v>
+        <v>65966.173333332</v>
       </c>
       <c r="P35" t="n">
         <v>16900</v>
@@ -1872,22 +1872,22 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N37" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O37" t="n">
-        <v>282815.38119816</v>
+        <v>188543.586728976</v>
       </c>
       <c r="P37" t="n">
         <v>28500</v>
       </c>
       <c r="Q37" t="n">
-        <v>513000</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="38">
@@ -2128,10 +2128,10 @@
         <v>46</v>
       </c>
       <c r="N43" t="n">
-        <v>141416.88459016</v>
+        <v>141416.88460526</v>
       </c>
       <c r="O43" t="n">
-        <v>6505176.691147361</v>
+        <v>6505176.691841961</v>
       </c>
       <c r="P43" t="n">
         <v>251900</v>
@@ -2175,10 +2175,10 @@
         <v>11</v>
       </c>
       <c r="N44" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O44" t="n">
-        <v>3790590.96361704</v>
+        <v>3790590.96288884</v>
       </c>
       <c r="P44" t="n">
         <v>532900</v>
@@ -3219,10 +3219,10 @@
         <v>1271</v>
       </c>
       <c r="N68" t="n">
-        <v>1098.0624184202</v>
+        <v>1098.0625007652</v>
       </c>
       <c r="O68" t="n">
-        <v>1395637.333812074</v>
+        <v>1395637.438472569</v>
       </c>
       <c r="P68" t="n">
         <v>1500</v>
@@ -4152,10 +4152,10 @@
         <v>681</v>
       </c>
       <c r="N89" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O89" t="n">
-        <v>1758515.979727495</v>
+        <v>1758515.976927291</v>
       </c>
       <c r="P89" t="n">
         <v>4500</v>
@@ -5794,10 +5794,10 @@
         <v>252</v>
       </c>
       <c r="N125" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O125" t="n">
-        <v>905751.909347544</v>
+        <v>905751.9072</v>
       </c>
       <c r="P125" t="n">
         <v>6500</v>
@@ -6019,10 +6019,10 @@
         <v>305</v>
       </c>
       <c r="N130" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O130" t="n">
-        <v>4520825.54530574</v>
+        <v>4520825.54509102</v>
       </c>
       <c r="P130" t="n">
         <v>24900</v>
@@ -6918,10 +6918,10 @@
         <v>241</v>
       </c>
       <c r="N150" t="n">
-        <v>1592.5660665658</v>
+        <v>1592.5660516325</v>
       </c>
       <c r="O150" t="n">
-        <v>383808.4220423578</v>
+        <v>383808.4184434325</v>
       </c>
       <c r="P150" t="n">
         <v>3900</v>
@@ -8801,10 +8801,10 @@
         <v>272</v>
       </c>
       <c r="N191" t="n">
-        <v>1690.5922846782</v>
+        <v>1690.591979835</v>
       </c>
       <c r="O191" t="n">
-        <v>459841.1014324704</v>
+        <v>459841.01851512</v>
       </c>
       <c r="P191" t="n">
         <v>2900</v>
@@ -8847,10 +8847,10 @@
         <v>1882</v>
       </c>
       <c r="N192" t="n">
-        <v>1550.1940319426</v>
+        <v>1550.1940372063</v>
       </c>
       <c r="O192" t="n">
-        <v>2917465.168115973</v>
+        <v>2917465.178022257</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8939,10 +8939,10 @@
         <v>418</v>
       </c>
       <c r="N194" t="n">
-        <v>2403.5140171519</v>
+        <v>2403.5141965714</v>
       </c>
       <c r="O194" t="n">
-        <v>1004668.859169494</v>
+        <v>1004668.934166845</v>
       </c>
       <c r="P194" t="n">
         <v>3500</v>
@@ -10935,10 +10935,10 @@
         <v>113</v>
       </c>
       <c r="N239" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="O239" t="n">
-        <v>484227.1313364098</v>
+        <v>484227.1320991936</v>
       </c>
       <c r="P239" t="n">
         <v>6900</v>
@@ -13682,10 +13682,10 @@
         <v>784</v>
       </c>
       <c r="N299" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O299" t="n">
-        <v>1394322.594728907</v>
+        <v>1394322.5950556</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
@@ -16217,10 +16217,10 @@
         <v>137</v>
       </c>
       <c r="N354" t="n">
-        <v>4907.8223782772</v>
+        <v>4907.8223917137</v>
       </c>
       <c r="O354" t="n">
-        <v>672371.6658239764</v>
+        <v>672371.6676647769</v>
       </c>
       <c r="P354" t="n">
         <v>8200</v>
@@ -17362,10 +17362,10 @@
         <v>292</v>
       </c>
       <c r="N379" t="n">
-        <v>17075.98952183</v>
+        <v>17075.989521166</v>
       </c>
       <c r="O379" t="n">
-        <v>4986188.94037436</v>
+        <v>4986188.940180472</v>
       </c>
       <c r="P379" t="n">
         <v>27500</v>
@@ -18878,10 +18878,10 @@
         <v>144</v>
       </c>
       <c r="N412" t="n">
-        <v>2056.082714437</v>
+        <v>2056.08270929</v>
       </c>
       <c r="O412" t="n">
-        <v>296075.910878928</v>
+        <v>296075.91013776</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18924,10 +18924,10 @@
         <v>90</v>
       </c>
       <c r="N413" t="n">
-        <v>3224.5689724311</v>
+        <v>3224.568981435</v>
       </c>
       <c r="O413" t="n">
-        <v>290211.207518799</v>
+        <v>290211.20832915</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -19200,10 +19200,10 @@
         <v>304</v>
       </c>
       <c r="N419" t="n">
-        <v>1592.2820519836</v>
+        <v>1592.2820684932</v>
       </c>
       <c r="O419" t="n">
-        <v>484053.7438030144</v>
+        <v>484053.7488219328</v>
       </c>
       <c r="P419" t="n">
         <v>2500</v>
@@ -21599,10 +21599,10 @@
         <v>149</v>
       </c>
       <c r="N471" t="n">
-        <v>517.2923857868</v>
+        <v>517.29240467717</v>
       </c>
       <c r="O471" t="n">
-        <v>77076.5654822332</v>
+        <v>77076.56829689833</v>
       </c>
       <c r="P471" t="n">
         <v>900</v>
@@ -22022,10 +22022,10 @@
         <v>757</v>
       </c>
       <c r="N480" t="n">
-        <v>3110.8400113026</v>
+        <v>3110.8399744753</v>
       </c>
       <c r="O480" t="n">
-        <v>2354905.888556068</v>
+        <v>2354905.860677802</v>
       </c>
       <c r="P480" t="n">
         <v>4500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -4029,10 +4029,10 @@
         <v>681</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O86" t="n">
-        <v>1758515.973419801</v>
+        <v>1758515.969200257</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4719,10 +4719,10 @@
         <v>290</v>
       </c>
       <c r="N101" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O101" t="n">
-        <v>2177143.1</v>
+        <v>2180277.935277191</v>
       </c>
       <c r="P101" t="n">
         <v>13500</v>
@@ -4768,10 +4768,10 @@
         <v>47</v>
       </c>
       <c r="N102" t="n">
-        <v>8796</v>
+        <v>8831.230974632799</v>
       </c>
       <c r="O102" t="n">
-        <v>413412</v>
+        <v>415067.8558077416</v>
       </c>
       <c r="P102" t="n">
         <v>14900</v>
@@ -8724,10 +8724,10 @@
         <v>1882</v>
       </c>
       <c r="N189" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O189" t="n">
-        <v>2917465.23716693</v>
+        <v>2917465.240526488</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
@@ -8816,10 +8816,10 @@
         <v>418</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.5142945915</v>
+        <v>2403.514304468</v>
       </c>
       <c r="O191" t="n">
-        <v>1004668.975139247</v>
+        <v>1004668.979267624</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -13559,10 +13559,10 @@
         <v>768</v>
       </c>
       <c r="N296" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O296" t="n">
-        <v>1365867.034134605</v>
+        <v>1365867.034455475</v>
       </c>
       <c r="P296" t="n">
         <v>4900</v>
@@ -14853,10 +14853,10 @@
         <v>24</v>
       </c>
       <c r="N324" t="n">
-        <v>28116</v>
+        <v>28613.628318584</v>
       </c>
       <c r="O324" t="n">
-        <v>674784</v>
+        <v>686727.079646016</v>
       </c>
       <c r="P324" t="n">
         <v>45900</v>
@@ -16646,10 +16646,10 @@
         <v>14</v>
       </c>
       <c r="N363" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O363" t="n">
-        <v>380604</v>
+        <v>382334.018181822</v>
       </c>
       <c r="P363" t="n">
         <v>43900</v>
@@ -17472,10 +17472,10 @@
         <v>161</v>
       </c>
       <c r="N381" t="n">
-        <v>10755</v>
+        <v>10792.803163445</v>
       </c>
       <c r="O381" t="n">
-        <v>1731555</v>
+        <v>1737641.309314645</v>
       </c>
       <c r="P381" t="n">
         <v>17900</v>
@@ -18576,10 +18576,10 @@
         <v>48</v>
       </c>
       <c r="N405" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O405" t="n">
-        <v>86544.76457502719</v>
+        <v>86544.7647742368</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -22260,10 +22260,10 @@
         <v>18602</v>
       </c>
       <c r="N485" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O485" t="n">
-        <v>13091994.04114818</v>
+        <v>13091994.03059749</v>
       </c>
       <c r="P485" t="n">
         <v>900</v>
@@ -29242,10 +29242,10 @@
         <v>84</v>
       </c>
       <c r="N634" t="n">
-        <v>7480</v>
+        <v>7524.8351648352</v>
       </c>
       <c r="O634" t="n">
-        <v>628320</v>
+        <v>632086.1538461568</v>
       </c>
       <c r="P634" t="n">
         <v>9500</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -3096,10 +3096,10 @@
         <v>1271</v>
       </c>
       <c r="N65" t="n">
-        <v>1098.0627514701</v>
+        <v>1098.0628221049</v>
       </c>
       <c r="O65" t="n">
-        <v>1395637.757118497</v>
+        <v>1395637.846895328</v>
       </c>
       <c r="P65" t="n">
         <v>1500</v>
@@ -3460,10 +3460,10 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O73" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="P73" t="n">
         <v>25500</v>
@@ -3765,10 +3765,10 @@
         <v>363</v>
       </c>
       <c r="N80" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O80" t="n">
-        <v>1019414.357486999</v>
+        <v>1017971.79</v>
       </c>
       <c r="P80" t="n">
         <v>4900</v>
@@ -4029,10 +4029,10 @@
         <v>681</v>
       </c>
       <c r="N86" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O86" t="n">
-        <v>1759731.779903201</v>
+        <v>1758515.933583752</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.743450076</v>
+        <v>3474452.742276517</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -4352,10 +4352,10 @@
         <v>3167</v>
       </c>
       <c r="N93" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O93" t="n">
-        <v>10012008.93826408</v>
+        <v>10004112.25578135</v>
       </c>
       <c r="P93" t="n">
         <v>5600</v>
@@ -4768,10 +4768,10 @@
         <v>47</v>
       </c>
       <c r="N102" t="n">
-        <v>8807.775100401601</v>
+        <v>8796</v>
       </c>
       <c r="O102" t="n">
-        <v>413965.4297188753</v>
+        <v>413412</v>
       </c>
       <c r="P102" t="n">
         <v>14900</v>
@@ -5034,10 +5034,10 @@
         <v>115</v>
       </c>
       <c r="N108" t="n">
-        <v>2619.5155335628</v>
+        <v>2612.77</v>
       </c>
       <c r="O108" t="n">
-        <v>301244.286359722</v>
+        <v>300468.55</v>
       </c>
       <c r="P108" t="n">
         <v>4900</v>
@@ -5080,10 +5080,10 @@
         <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O109" t="n">
-        <v>13088.1695686584</v>
+        <v>13072.65</v>
       </c>
       <c r="P109" t="n">
         <v>7500</v>
@@ -5172,10 +5172,10 @@
         <v>309</v>
       </c>
       <c r="N111" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O111" t="n">
-        <v>1511297.385344507</v>
+        <v>1511297.385363573</v>
       </c>
       <c r="P111" t="n">
         <v>8200</v>
@@ -5535,10 +5535,10 @@
         <v>281</v>
       </c>
       <c r="N119" t="n">
-        <v>8670.9576008273</v>
+        <v>8662</v>
       </c>
       <c r="O119" t="n">
-        <v>2436539.085832471</v>
+        <v>2434022</v>
       </c>
       <c r="P119" t="n">
         <v>14200</v>
@@ -5671,10 +5671,10 @@
         <v>252</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O122" t="n">
-        <v>905751.9018060156</v>
+        <v>905751.9007228944</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -5896,10 +5896,10 @@
         <v>305</v>
       </c>
       <c r="N127" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O127" t="n">
-        <v>4529060.19999999</v>
+        <v>4520825.54444442</v>
       </c>
       <c r="P127" t="n">
         <v>24900</v>
@@ -6169,10 +6169,10 @@
         <v>708</v>
       </c>
       <c r="N133" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="O133" t="n">
-        <v>1891780.035687721</v>
+        <v>1887103.2</v>
       </c>
       <c r="P133" t="n">
         <v>20900</v>
@@ -6261,10 +6261,10 @@
         <v>32</v>
       </c>
       <c r="N135" t="n">
-        <v>12618.152142857</v>
+        <v>12267.647571429</v>
       </c>
       <c r="O135" t="n">
-        <v>403780.868571424</v>
+        <v>392564.722285728</v>
       </c>
       <c r="P135" t="n">
         <v>19900</v>
@@ -6577,10 +6577,10 @@
         <v>210</v>
       </c>
       <c r="N142" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O142" t="n">
-        <v>638748.602882628</v>
+        <v>638748.602890566</v>
       </c>
       <c r="P142" t="n">
         <v>5500</v>
@@ -6699,22 +6699,22 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M145" t="n">
-        <v>1938</v>
+        <v>1930</v>
       </c>
       <c r="N145" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O145" t="n">
-        <v>8473344.516202601</v>
+        <v>8443199.108647186</v>
       </c>
       <c r="P145" t="n">
         <v>7500</v>
       </c>
       <c r="Q145" t="n">
-        <v>14535000</v>
+        <v>14475000</v>
       </c>
     </row>
     <row r="146">
@@ -7553,10 +7553,10 @@
         <v>149</v>
       </c>
       <c r="N164" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O164" t="n">
-        <v>1403970.259011479</v>
+        <v>1402732.19</v>
       </c>
       <c r="P164" t="n">
         <v>16900</v>
@@ -7741,10 +7741,10 @@
         <v>109</v>
       </c>
       <c r="N168" t="n">
-        <v>4673.2793206522</v>
+        <v>4635.49</v>
       </c>
       <c r="O168" t="n">
-        <v>509387.4459510898</v>
+        <v>505268.41</v>
       </c>
       <c r="P168" t="n">
         <v>7500</v>
@@ -7878,10 +7878,10 @@
         <v>91</v>
       </c>
       <c r="N171" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O171" t="n">
-        <v>1543375.13831774</v>
+        <v>1537627</v>
       </c>
       <c r="P171" t="n">
         <v>27900</v>
@@ -8120,10 +8120,10 @@
         <v>120</v>
       </c>
       <c r="N176" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O176" t="n">
-        <v>1432765.49308752</v>
+        <v>1430568</v>
       </c>
       <c r="P176" t="n">
         <v>19900</v>
@@ -8540,10 +8540,10 @@
         <v>193</v>
       </c>
       <c r="N185" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O185" t="n">
-        <v>1915730.736801238</v>
+        <v>1911279</v>
       </c>
       <c r="P185" t="n">
         <v>15900</v>
@@ -8672,22 +8672,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M188" t="n">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="N188" t="n">
-        <v>1690.5907183908</v>
+        <v>1830.8887033195</v>
       </c>
       <c r="O188" t="n">
-        <v>459840.6754022976</v>
+        <v>351530.631037344</v>
       </c>
       <c r="P188" t="n">
         <v>2900</v>
       </c>
       <c r="Q188" t="n">
-        <v>788800</v>
+        <v>556800</v>
       </c>
     </row>
     <row r="189">
@@ -8718,22 +8718,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="M189" t="n">
-        <v>1882</v>
+        <v>1542</v>
       </c>
       <c r="N189" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O189" t="n">
-        <v>2917465.31604569</v>
+        <v>2390399.570305227</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
       </c>
       <c r="Q189" t="n">
-        <v>4705000</v>
+        <v>3855000</v>
       </c>
     </row>
     <row r="190">
@@ -8810,22 +8810,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="M191" t="n">
-        <v>418</v>
+        <v>174</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.5145969448</v>
+        <v>2549.7269035153</v>
       </c>
       <c r="O191" t="n">
-        <v>1004669.101522926</v>
+        <v>443652.4812116622</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
       </c>
       <c r="Q191" t="n">
-        <v>1463000</v>
+        <v>609000</v>
       </c>
     </row>
     <row r="192">
@@ -9856,10 +9856,10 @@
         <v>8</v>
       </c>
       <c r="N214" t="n">
-        <v>9396.9148264984</v>
+        <v>9338</v>
       </c>
       <c r="O214" t="n">
-        <v>75175.3186119872</v>
+        <v>74704</v>
       </c>
       <c r="P214" t="n">
         <v>15500</v>
@@ -10233,10 +10233,10 @@
         <v>148</v>
       </c>
       <c r="N223" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O223" t="n">
-        <v>1302317.567674943</v>
+        <v>1301583.04</v>
       </c>
       <c r="P223" t="n">
         <v>14500</v>
@@ -10543,10 +10543,10 @@
         <v>13</v>
       </c>
       <c r="N230" t="n">
-        <v>14161.073142857</v>
+        <v>14060.64</v>
       </c>
       <c r="O230" t="n">
-        <v>184093.950857141</v>
+        <v>182788.32</v>
       </c>
       <c r="P230" t="n">
         <v>22900</v>
@@ -10812,10 +10812,10 @@
         <v>113</v>
       </c>
       <c r="N236" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O236" t="n">
-        <v>484227.1328637404</v>
+        <v>484227.1445475901</v>
       </c>
       <c r="P236" t="n">
         <v>6900</v>
@@ -11158,10 +11158,10 @@
         <v>32</v>
       </c>
       <c r="N244" t="n">
-        <v>11594.607549296</v>
+        <v>11562.038422535</v>
       </c>
       <c r="O244" t="n">
-        <v>371027.441577472</v>
+        <v>369985.22952112</v>
       </c>
       <c r="P244" t="n">
         <v>18500</v>
@@ -11204,10 +11204,10 @@
         <v>17</v>
       </c>
       <c r="N245" t="n">
-        <v>13621.7524</v>
+        <v>13513.64328</v>
       </c>
       <c r="O245" t="n">
-        <v>231569.7908</v>
+        <v>229731.93576</v>
       </c>
       <c r="P245" t="n">
         <v>21900</v>
@@ -11388,10 +11388,10 @@
         <v>92</v>
       </c>
       <c r="N249" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O249" t="n">
-        <v>2564156.879842532</v>
+        <v>2495386.37637796</v>
       </c>
       <c r="P249" t="n">
         <v>44500</v>
@@ -11475,10 +11475,10 @@
         <v>52</v>
       </c>
       <c r="N251" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O251" t="n">
-        <v>887656.7469295759</v>
+        <v>882683.8799999999</v>
       </c>
       <c r="P251" t="n">
         <v>26900</v>
@@ -11516,10 +11516,10 @@
         <v>1330</v>
       </c>
       <c r="N252" t="n">
-        <v>4110.4025485437</v>
+        <v>4100.45</v>
       </c>
       <c r="O252" t="n">
-        <v>5466835.389563121</v>
+        <v>5453598.5</v>
       </c>
       <c r="P252" t="n">
         <v>26900</v>
@@ -11792,10 +11792,10 @@
         <v>77</v>
       </c>
       <c r="N258" t="n">
-        <v>9681.731751412401</v>
+        <v>9627.34</v>
       </c>
       <c r="O258" t="n">
-        <v>745493.3448587549</v>
+        <v>741305.1800000001</v>
       </c>
       <c r="P258" t="n">
         <v>15900</v>
@@ -13513,10 +13513,10 @@
         <v>768</v>
       </c>
       <c r="N295" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O295" t="n">
-        <v>1365867.05062679</v>
+        <v>1365867.051605069</v>
       </c>
       <c r="P295" t="n">
         <v>4900</v>
@@ -14899,10 +14899,10 @@
         <v>419</v>
       </c>
       <c r="N325" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O325" t="n">
-        <v>3717510.719359659</v>
+        <v>3711569.04</v>
       </c>
       <c r="P325" t="n">
         <v>15500</v>
@@ -15363,10 +15363,10 @@
         <v>324</v>
       </c>
       <c r="N335" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O335" t="n">
-        <v>757139.1185250001</v>
+        <v>754310.452725</v>
       </c>
       <c r="P335" t="n">
         <v>4500</v>
@@ -15449,22 +15449,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M337" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="N337" t="n">
-        <v>9384</v>
+        <v>9686.7096774194</v>
       </c>
       <c r="O337" t="n">
-        <v>900864</v>
+        <v>833057.0322580683</v>
       </c>
       <c r="P337" t="n">
         <v>15900</v>
       </c>
       <c r="Q337" t="n">
-        <v>1526400</v>
+        <v>1367400</v>
       </c>
     </row>
     <row r="338">
@@ -16191,10 +16191,10 @@
         <v>276</v>
       </c>
       <c r="N353" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O353" t="n">
-        <v>1082739.189753685</v>
+        <v>1077431.668965522</v>
       </c>
       <c r="P353" t="n">
         <v>7500</v>
@@ -16278,10 +16278,10 @@
         <v>23</v>
       </c>
       <c r="N355" t="n">
-        <v>33317.307692308</v>
+        <v>33000</v>
       </c>
       <c r="O355" t="n">
-        <v>766298.076923084</v>
+        <v>759000</v>
       </c>
       <c r="P355" t="n">
         <v>52900</v>
@@ -16646,10 +16646,10 @@
         <v>157</v>
       </c>
       <c r="N363" t="n">
-        <v>3901.1562753036</v>
+        <v>3898</v>
       </c>
       <c r="O363" t="n">
-        <v>612481.5352226652</v>
+        <v>611986</v>
       </c>
       <c r="P363" t="n">
         <v>6900</v>
@@ -16692,10 +16692,10 @@
         <v>146</v>
       </c>
       <c r="N364" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O364" t="n">
-        <v>1986555.819295584</v>
+        <v>1980490</v>
       </c>
       <c r="P364" t="n">
         <v>22500</v>
@@ -16738,10 +16738,10 @@
         <v>527</v>
       </c>
       <c r="N365" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O365" t="n">
-        <v>4030388.539106159</v>
+        <v>4023645</v>
       </c>
       <c r="P365" t="n">
         <v>13900</v>
@@ -16784,10 +16784,10 @@
         <v>21</v>
       </c>
       <c r="N366" t="n">
-        <v>5465.19</v>
+        <v>5438</v>
       </c>
       <c r="O366" t="n">
-        <v>114768.99</v>
+        <v>114198</v>
       </c>
       <c r="P366" t="n">
         <v>8900</v>
@@ -17656,10 +17656,10 @@
         <v>51</v>
       </c>
       <c r="N385" t="n">
-        <v>8721.0653753027</v>
+        <v>8700</v>
       </c>
       <c r="O385" t="n">
-        <v>444774.3341404377</v>
+        <v>443700</v>
       </c>
       <c r="P385" t="n">
         <v>14900</v>
@@ -17978,10 +17978,10 @@
         <v>16</v>
       </c>
       <c r="N392" t="n">
-        <v>21822.282548476</v>
+        <v>21762</v>
       </c>
       <c r="O392" t="n">
-        <v>349156.520775616</v>
+        <v>348192</v>
       </c>
       <c r="P392" t="n">
         <v>35900</v>
@@ -18070,10 +18070,10 @@
         <v>14</v>
       </c>
       <c r="N394" t="n">
-        <v>15512.396866841</v>
+        <v>15472</v>
       </c>
       <c r="O394" t="n">
-        <v>217173.556135774</v>
+        <v>216608</v>
       </c>
       <c r="P394" t="n">
         <v>25900</v>
@@ -18984,22 +18984,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M414" t="n">
-        <v>304</v>
+        <v>224</v>
       </c>
       <c r="N414" t="n">
-        <v>1592.2821517241</v>
+        <v>1789.7745116279</v>
       </c>
       <c r="O414" t="n">
-        <v>484053.7741241264</v>
+        <v>400909.4906046496</v>
       </c>
       <c r="P414" t="n">
         <v>2500</v>
       </c>
       <c r="Q414" t="n">
-        <v>760000</v>
+        <v>560000</v>
       </c>
     </row>
     <row r="415">
@@ -19665,10 +19665,10 @@
         <v>46</v>
       </c>
       <c r="N429" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="O429" t="n">
-        <v>723759.282684544</v>
+        <v>709474.5600000001</v>
       </c>
       <c r="P429" t="n">
         <v>24900</v>
@@ -21763,10 +21763,10 @@
         <v>757</v>
       </c>
       <c r="N474" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O474" t="n">
-        <v>2354905.760359178</v>
+        <v>2354905.727070709</v>
       </c>
       <c r="P474" t="n">
         <v>4500</v>
@@ -22966,10 +22966,10 @@
         <v>9</v>
       </c>
       <c r="N500" t="n">
-        <v>18621.814408602</v>
+        <v>18423.71</v>
       </c>
       <c r="O500" t="n">
-        <v>167596.329677418</v>
+        <v>165813.39</v>
       </c>
       <c r="P500" t="n">
         <v>10000</v>
@@ -24645,10 +24645,10 @@
         <v>96</v>
       </c>
       <c r="N535" t="n">
-        <v>3098.3874489796</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O535" t="n">
-        <v>297445.1951020416</v>
+        <v>294440.6987755104</v>
       </c>
       <c r="P535" t="n">
         <v>7200</v>
@@ -25510,10 +25510,10 @@
         <v>17</v>
       </c>
       <c r="N553" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="O553" t="n">
-        <v>186884.080238092</v>
+        <v>182537.937142862</v>
       </c>
       <c r="P553" t="n">
         <v>18900</v>
@@ -26735,10 +26735,10 @@
         <v>127</v>
       </c>
       <c r="N579" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="O579" t="n">
-        <v>3110244.167819264</v>
+        <v>3090985.69</v>
       </c>
       <c r="P579" t="n">
         <v>27900</v>
@@ -29380,10 +29380,10 @@
         <v>135</v>
       </c>
       <c r="N637" t="n">
-        <v>4598.7284768212</v>
+        <v>4576</v>
       </c>
       <c r="O637" t="n">
-        <v>620828.344370862</v>
+        <v>617760</v>
       </c>
       <c r="P637" t="n">
         <v>5900</v>
@@ -30266,22 +30266,22 @@
         <v>0</v>
       </c>
       <c r="L656" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M656" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N656" t="n">
-        <v>3732.8768115942</v>
+        <v>4365.5677966102</v>
       </c>
       <c r="O656" t="n">
-        <v>37328.768115942</v>
+        <v>0</v>
       </c>
       <c r="P656" t="n">
         <v>4500</v>
       </c>
       <c r="Q656" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="657">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -4029,10 +4029,10 @@
         <v>681</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O86" t="n">
-        <v>1758515.929254567</v>
+        <v>1758515.927085446</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4488,10 +4488,10 @@
         <v>144</v>
       </c>
       <c r="N96" t="n">
-        <v>3230.0666176471</v>
+        <v>3230.0665925926</v>
       </c>
       <c r="O96" t="n">
-        <v>465129.5929411824</v>
+        <v>465129.5893333344</v>
       </c>
       <c r="P96" t="n">
         <v>6200</v>
@@ -8114,22 +8114,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M176" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N176" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O176" t="n">
-        <v>1430568</v>
+        <v>1398067.771450896</v>
       </c>
       <c r="P176" t="n">
         <v>19900</v>
       </c>
       <c r="Q176" t="n">
-        <v>2388000</v>
+        <v>2328300</v>
       </c>
     </row>
     <row r="177">
@@ -8586,10 +8586,10 @@
         <v>640</v>
       </c>
       <c r="N186" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O186" t="n">
-        <v>1043791.404710272</v>
+        <v>1043791.406089472</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8724,10 +8724,10 @@
         <v>1542</v>
       </c>
       <c r="N189" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O189" t="n">
-        <v>2390399.401683364</v>
+        <v>2390399.405288559</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
@@ -8816,10 +8816,10 @@
         <v>174</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.5147075539</v>
+        <v>2403.51472848</v>
       </c>
       <c r="O191" t="n">
-        <v>418211.5591143786</v>
+        <v>418211.56275552</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -11556,22 +11556,22 @@
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M253" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N253" t="n">
-        <v>8332.779613402099</v>
+        <v>8397.710363636401</v>
       </c>
       <c r="O253" t="n">
-        <v>483301.2175773217</v>
+        <v>461874.070000002</v>
       </c>
       <c r="P253" t="n">
         <v>14900</v>
       </c>
       <c r="Q253" t="n">
-        <v>864200</v>
+        <v>819500</v>
       </c>
     </row>
     <row r="254">
@@ -13878,22 +13878,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N303" t="n">
-        <v>26956</v>
+        <v>28079.166666667</v>
       </c>
       <c r="O303" t="n">
-        <v>161736</v>
+        <v>140395.833333335</v>
       </c>
       <c r="P303" t="n">
         <v>44900</v>
       </c>
       <c r="Q303" t="n">
-        <v>269400</v>
+        <v>224500</v>
       </c>
     </row>
     <row r="304">
@@ -16145,10 +16145,10 @@
         <v>276</v>
       </c>
       <c r="N352" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O352" t="n">
-        <v>1077431.77267393</v>
+        <v>1077431.785411771</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
@@ -18944,10 +18944,10 @@
         <v>224</v>
       </c>
       <c r="N413" t="n">
-        <v>1592.2821517241</v>
+        <v>1592.2821853389</v>
       </c>
       <c r="O413" t="n">
-        <v>356671.2019861984</v>
+        <v>356671.2095159136</v>
       </c>
       <c r="P413" t="n">
         <v>2500</v>
@@ -21671,10 +21671,10 @@
         <v>757</v>
       </c>
       <c r="N472" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O472" t="n">
-        <v>2354905.655083037</v>
+        <v>2354905.641435689</v>
       </c>
       <c r="P472" t="n">
         <v>4500</v>
@@ -24125,22 +24125,22 @@
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M524" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N524" t="n">
         <v>2992.5708695652</v>
       </c>
       <c r="O524" t="n">
-        <v>32918.2795652172</v>
+        <v>17955.4252173912</v>
       </c>
       <c r="P524" t="n">
         <v>6000</v>
       </c>
       <c r="Q524" t="n">
-        <v>66000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="525">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -592,19 +592,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="N5" t="n">
         <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>2943000</v>
+        <v>2862000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2180000</v>
+        <v>2120000</v>
       </c>
     </row>
     <row r="6">
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3082551595</v>
+        <v>1811.3085686465</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3082551595</v>
+        <v>1811.3085686465</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -714,10 +714,10 @@
         <v>884</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464407714</v>
+        <v>3376.7464397906</v>
       </c>
       <c r="O8" t="n">
-        <v>2985043.853641917</v>
+        <v>2985043.852774891</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -792,10 +792,10 @@
         <v>55</v>
       </c>
       <c r="N10" t="n">
-        <v>5758.9597777778</v>
+        <v>5758.9597772829</v>
       </c>
       <c r="O10" t="n">
-        <v>316742.787777779</v>
+        <v>316742.7877505595</v>
       </c>
       <c r="P10" t="n">
         <v>16900</v>
@@ -870,10 +870,10 @@
         <v>12</v>
       </c>
       <c r="N12" t="n">
-        <v>15970.739113924</v>
+        <v>15970.739066667</v>
       </c>
       <c r="O12" t="n">
-        <v>191648.869367088</v>
+        <v>191648.868800004</v>
       </c>
       <c r="P12" t="n">
         <v>26900</v>
@@ -1195,10 +1195,10 @@
         <v>194</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370909091</v>
+        <v>3926.8370787689</v>
       </c>
       <c r="O20" t="n">
-        <v>761806.3956363654</v>
+        <v>761806.3932811666</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1312,10 +1312,10 @@
         <v>66</v>
       </c>
       <c r="N23" t="n">
-        <v>2474.7039930556</v>
+        <v>2474.7039826087</v>
       </c>
       <c r="O23" t="n">
-        <v>163330.4635416696</v>
+        <v>163330.4628521742</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -1802,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>13712.843448276</v>
+        <v>13712.841538462</v>
       </c>
       <c r="O35" t="n">
-        <v>13712.843448276</v>
+        <v>13712.841538462</v>
       </c>
       <c r="P35" t="n">
         <v>22600</v>
@@ -2785,10 +2785,10 @@
         <v>41</v>
       </c>
       <c r="N58" t="n">
-        <v>732.63427046263</v>
+        <v>732.6342857142899</v>
       </c>
       <c r="O58" t="n">
-        <v>30038.00508896783</v>
+        <v>30038.00571428589</v>
       </c>
       <c r="P58" t="n">
         <v>6200</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3049,19 +3049,19 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="N64" t="n">
         <v>14233.54</v>
       </c>
       <c r="O64" t="n">
-        <v>1594156.48</v>
+        <v>1537222.32</v>
       </c>
       <c r="P64" t="n">
         <v>10000</v>
       </c>
       <c r="Q64" t="n">
-        <v>1120000</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="65">
@@ -3096,10 +3096,10 @@
         <v>1271</v>
       </c>
       <c r="N65" t="n">
-        <v>1098.062979056</v>
+        <v>1098.0630078247</v>
       </c>
       <c r="O65" t="n">
-        <v>1395638.046380176</v>
+        <v>1395638.082945194</v>
       </c>
       <c r="P65" t="n">
         <v>1500</v>
@@ -4029,10 +4029,10 @@
         <v>681</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2553995381</v>
+        <v>2582.2552</v>
       </c>
       <c r="O86" t="n">
-        <v>1758515.927085446</v>
+        <v>1758515.7912</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.8960047177</v>
+        <v>5216.8959994095</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.739141988</v>
+        <v>3474452.735606727</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -4352,10 +4352,10 @@
         <v>3167</v>
       </c>
       <c r="N93" t="n">
-        <v>3158.8608345701</v>
+        <v>3158.8608346114</v>
       </c>
       <c r="O93" t="n">
-        <v>10004112.26308351</v>
+        <v>10004112.26321431</v>
       </c>
       <c r="P93" t="n">
         <v>5600</v>
@@ -4488,10 +4488,10 @@
         <v>144</v>
       </c>
       <c r="N96" t="n">
-        <v>3230.0665925926</v>
+        <v>3230.0665756824</v>
       </c>
       <c r="O96" t="n">
-        <v>465129.5893333344</v>
+        <v>465129.5868982656</v>
       </c>
       <c r="P96" t="n">
         <v>6200</v>
@@ -4627,10 +4627,10 @@
         <v>259</v>
       </c>
       <c r="N99" t="n">
-        <v>2694.8231379962</v>
+        <v>2694.8231282537</v>
       </c>
       <c r="O99" t="n">
-        <v>697959.1927410158</v>
+        <v>697959.1902177082</v>
       </c>
       <c r="P99" t="n">
         <v>4900</v>
@@ -4947,10 +4947,10 @@
         <v>581</v>
       </c>
       <c r="N106" t="n">
-        <v>3795.7100075916</v>
+        <v>3795.7100076089</v>
       </c>
       <c r="O106" t="n">
-        <v>2205307.51441072</v>
+        <v>2205307.514420771</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N113" t="n">
         <v>5888</v>
       </c>
       <c r="O113" t="n">
-        <v>794880</v>
+        <v>783104</v>
       </c>
       <c r="P113" t="n">
         <v>9500</v>
       </c>
       <c r="Q113" t="n">
-        <v>1282500</v>
+        <v>1263500</v>
       </c>
     </row>
     <row r="114">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -5394,19 +5394,19 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="N116" t="n">
         <v>7041</v>
       </c>
       <c r="O116" t="n">
-        <v>4309092</v>
+        <v>4287969</v>
       </c>
       <c r="P116" t="n">
         <v>11500</v>
       </c>
       <c r="Q116" t="n">
-        <v>7038000</v>
+        <v>7003500</v>
       </c>
     </row>
     <row r="117">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5619,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N121" t="n">
         <v>10716.34</v>
       </c>
       <c r="O121" t="n">
-        <v>375071.9</v>
+        <v>353639.22</v>
       </c>
       <c r="P121" t="n">
         <v>39000</v>
       </c>
       <c r="Q121" t="n">
-        <v>1365000</v>
+        <v>1287000</v>
       </c>
     </row>
     <row r="122">
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5668,19 +5668,19 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2535483871</v>
+        <v>3594.2535397039</v>
       </c>
       <c r="O122" t="n">
-        <v>905751.8941935493</v>
+        <v>862620.849528936</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
       </c>
       <c r="Q122" t="n">
-        <v>1638000</v>
+        <v>1560000</v>
       </c>
     </row>
     <row r="123">
@@ -5712,10 +5712,10 @@
         <v>108</v>
       </c>
       <c r="N123" t="n">
-        <v>3240.8500449438</v>
+        <v>3240.8500464037</v>
       </c>
       <c r="O123" t="n">
-        <v>350011.8048539304</v>
+        <v>350011.8050115996</v>
       </c>
       <c r="P123" t="n">
         <v>5200</v>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5755,19 +5755,19 @@
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N124" t="n">
         <v>7120</v>
       </c>
       <c r="O124" t="n">
-        <v>199360</v>
+        <v>192240</v>
       </c>
       <c r="P124" t="n">
         <v>8900</v>
       </c>
       <c r="Q124" t="n">
-        <v>249200</v>
+        <v>240300</v>
       </c>
     </row>
     <row r="125">
@@ -5896,10 +5896,10 @@
         <v>305</v>
       </c>
       <c r="N127" t="n">
-        <v>14822.378831406</v>
+        <v>14822.378830694</v>
       </c>
       <c r="O127" t="n">
-        <v>4520825.54357883</v>
+        <v>4520825.54336167</v>
       </c>
       <c r="P127" t="n">
         <v>24900</v>
@@ -6261,10 +6261,10 @@
         <v>32</v>
       </c>
       <c r="N135" t="n">
-        <v>12267.647205882</v>
+        <v>12422.024238382</v>
       </c>
       <c r="O135" t="n">
-        <v>392564.710588224</v>
+        <v>397504.775628224</v>
       </c>
       <c r="P135" t="n">
         <v>19900</v>
@@ -6577,10 +6577,10 @@
         <v>210</v>
       </c>
       <c r="N142" t="n">
-        <v>3041.6600137931</v>
+        <v>3041.66001386</v>
       </c>
       <c r="O142" t="n">
-        <v>638748.602896551</v>
+        <v>638748.6029106</v>
       </c>
       <c r="P142" t="n">
         <v>5500</v>
@@ -6705,16 +6705,16 @@
         <v>1930</v>
       </c>
       <c r="N145" t="n">
-        <v>4372.2107930714</v>
+        <v>4371.1712607216</v>
       </c>
       <c r="O145" t="n">
-        <v>8438366.830627803</v>
+        <v>8436360.533192689</v>
       </c>
       <c r="P145" t="n">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="Q145" t="n">
-        <v>14475000</v>
+        <v>17177000</v>
       </c>
     </row>
     <row r="146">
@@ -6795,10 +6795,10 @@
         <v>181</v>
       </c>
       <c r="N147" t="n">
-        <v>1592.565713108</v>
+        <v>1592.5656339211</v>
       </c>
       <c r="O147" t="n">
-        <v>288254.394072548</v>
+        <v>288254.3797397191</v>
       </c>
       <c r="P147" t="n">
         <v>3900</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7875,19 +7875,19 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N171" t="n">
         <v>16897</v>
       </c>
       <c r="O171" t="n">
-        <v>1537627</v>
+        <v>1470039</v>
       </c>
       <c r="P171" t="n">
         <v>27900</v>
       </c>
       <c r="Q171" t="n">
-        <v>2538900</v>
+        <v>2427300</v>
       </c>
     </row>
     <row r="172">
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -8066,19 +8066,19 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N175" t="n">
         <v>3761.6</v>
       </c>
       <c r="O175" t="n">
-        <v>180556.8</v>
+        <v>161748.8</v>
       </c>
       <c r="P175" t="n">
         <v>6900</v>
       </c>
       <c r="Q175" t="n">
-        <v>331200</v>
+        <v>296700</v>
       </c>
     </row>
     <row r="176">
@@ -8108,22 +8108,22 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
         <v>117</v>
       </c>
       <c r="N176" t="n">
-        <v>11949.297191888</v>
+        <v>11921.4</v>
       </c>
       <c r="O176" t="n">
-        <v>1398067.771450896</v>
+        <v>1394803.8</v>
       </c>
       <c r="P176" t="n">
         <v>19900</v>
@@ -8586,10 +8586,10 @@
         <v>640</v>
       </c>
       <c r="N186" t="n">
-        <v>1630.9240720148</v>
+        <v>1630.924143319</v>
       </c>
       <c r="O186" t="n">
-        <v>1043791.406089472</v>
+        <v>1043791.45172416</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8632,10 +8632,10 @@
         <v>5</v>
       </c>
       <c r="N187" t="n">
-        <v>1467.3135220126</v>
+        <v>1467.3132911392</v>
       </c>
       <c r="O187" t="n">
-        <v>7336.567610063001</v>
+        <v>7336.566455696</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8678,10 +8678,10 @@
         <v>192</v>
       </c>
       <c r="N188" t="n">
-        <v>1690.5903203883</v>
+        <v>1690.5869155844</v>
       </c>
       <c r="O188" t="n">
-        <v>324593.3415145536</v>
+        <v>324592.6877922048</v>
       </c>
       <c r="P188" t="n">
         <v>2900</v>
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>1542</v>
+        <v>1482</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -8721,19 +8721,19 @@
         <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>1542</v>
+        <v>1482</v>
       </c>
       <c r="N189" t="n">
-        <v>1550.1941668538</v>
+        <v>1550.1943181289</v>
       </c>
       <c r="O189" t="n">
-        <v>2390399.405288559</v>
+        <v>2297387.97946703</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
       </c>
       <c r="Q189" t="n">
-        <v>3855000</v>
+        <v>3705000</v>
       </c>
     </row>
     <row r="190">
@@ -8816,10 +8816,10 @@
         <v>174</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.51472848</v>
+        <v>2403.515543043</v>
       </c>
       <c r="O191" t="n">
-        <v>418211.56275552</v>
+        <v>418211.704489482</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -9348,10 +9348,10 @@
         <v>15</v>
       </c>
       <c r="N203" t="n">
-        <v>10836.973589744</v>
+        <v>10836.973612903</v>
       </c>
       <c r="O203" t="n">
-        <v>162554.60384616</v>
+        <v>162554.604193545</v>
       </c>
       <c r="P203" t="n">
         <v>19900</v>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9573,19 +9573,19 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="N208" t="n">
         <v>19120</v>
       </c>
       <c r="O208" t="n">
-        <v>1491360</v>
+        <v>1281040</v>
       </c>
       <c r="P208" t="n">
         <v>23900</v>
       </c>
       <c r="Q208" t="n">
-        <v>1864200</v>
+        <v>1601300</v>
       </c>
     </row>
     <row r="209">
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9853,19 +9853,19 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N214" t="n">
         <v>9338</v>
       </c>
       <c r="O214" t="n">
-        <v>74704</v>
+        <v>56028</v>
       </c>
       <c r="P214" t="n">
         <v>15500</v>
       </c>
       <c r="Q214" t="n">
-        <v>124000</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="215">
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -10107,19 +10107,19 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N220" t="n">
         <v>2610</v>
       </c>
       <c r="O220" t="n">
-        <v>245340</v>
+        <v>234900</v>
       </c>
       <c r="P220" t="n">
         <v>3200</v>
       </c>
       <c r="Q220" t="n">
-        <v>300800</v>
+        <v>288000</v>
       </c>
     </row>
     <row r="221">
@@ -10451,10 +10451,10 @@
         <v>159</v>
       </c>
       <c r="N228" t="n">
-        <v>2680.739694704</v>
+        <v>2680.7396945137</v>
       </c>
       <c r="O228" t="n">
-        <v>426237.611457936</v>
+        <v>426237.6114276783</v>
       </c>
       <c r="P228" t="n">
         <v>4900</v>
@@ -10531,7 +10531,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10540,19 +10540,19 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N230" t="n">
         <v>14060.64</v>
       </c>
       <c r="O230" t="n">
-        <v>182788.32</v>
+        <v>154667.04</v>
       </c>
       <c r="P230" t="n">
         <v>22900</v>
       </c>
       <c r="Q230" t="n">
-        <v>297700</v>
+        <v>251900</v>
       </c>
     </row>
     <row r="231">
@@ -11071,16 +11071,16 @@
         <v>560</v>
       </c>
       <c r="N242" t="n">
-        <v>4605.2147904762</v>
+        <v>4813.4669326076</v>
       </c>
       <c r="O242" t="n">
-        <v>2578920.282666672</v>
+        <v>2695541.482260256</v>
       </c>
       <c r="P242" t="n">
-        <v>7600</v>
+        <v>9900</v>
       </c>
       <c r="Q242" t="n">
-        <v>4256000</v>
+        <v>5544000</v>
       </c>
     </row>
     <row r="243">
@@ -11204,10 +11204,10 @@
         <v>17</v>
       </c>
       <c r="N245" t="n">
-        <v>13513.643306452</v>
+        <v>13513.643333333</v>
       </c>
       <c r="O245" t="n">
-        <v>229731.936209684</v>
+        <v>229731.936666661</v>
       </c>
       <c r="P245" t="n">
         <v>21900</v>
@@ -11388,10 +11388,10 @@
         <v>92</v>
       </c>
       <c r="N249" t="n">
-        <v>27123.76496063</v>
+        <v>27123.764900398</v>
       </c>
       <c r="O249" t="n">
-        <v>2495386.37637796</v>
+        <v>2495386.370836616</v>
       </c>
       <c r="P249" t="n">
         <v>44500</v>
@@ -11504,7 +11504,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11513,19 +11513,19 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="N252" t="n">
         <v>4100.45</v>
       </c>
       <c r="O252" t="n">
-        <v>5453598.5</v>
+        <v>5445397.6</v>
       </c>
       <c r="P252" t="n">
         <v>26900</v>
       </c>
       <c r="Q252" t="n">
-        <v>35777000</v>
+        <v>35723200</v>
       </c>
     </row>
     <row r="253">
@@ -11550,22 +11550,22 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
         <v>55</v>
       </c>
       <c r="N253" t="n">
-        <v>8397.710363636401</v>
+        <v>8332.779613402099</v>
       </c>
       <c r="O253" t="n">
-        <v>461874.070000002</v>
+        <v>458302.8787371155</v>
       </c>
       <c r="P253" t="n">
         <v>14900</v>
@@ -11608,10 +11608,10 @@
         <v>549</v>
       </c>
       <c r="N254" t="n">
-        <v>1561.003125</v>
+        <v>1561.0032692308</v>
       </c>
       <c r="O254" t="n">
-        <v>856990.715625</v>
+        <v>856990.7948077092</v>
       </c>
       <c r="P254" t="n">
         <v>2900</v>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11697,19 +11697,19 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N256" t="n">
         <v>26854</v>
       </c>
       <c r="O256" t="n">
-        <v>725058</v>
+        <v>644496</v>
       </c>
       <c r="P256" t="n">
         <v>43900</v>
       </c>
       <c r="Q256" t="n">
-        <v>1185300</v>
+        <v>1053600</v>
       </c>
     </row>
     <row r="257">
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12023,19 +12023,19 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N263" t="n">
         <v>12981.59</v>
       </c>
       <c r="O263" t="n">
-        <v>337521.34</v>
+        <v>246650.21</v>
       </c>
       <c r="P263" t="n">
         <v>21900</v>
       </c>
       <c r="Q263" t="n">
-        <v>569400</v>
+        <v>416100</v>
       </c>
     </row>
     <row r="264">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12115,19 +12115,19 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N265" t="n">
         <v>4720</v>
       </c>
       <c r="O265" t="n">
-        <v>896800</v>
+        <v>882640</v>
       </c>
       <c r="P265" t="n">
         <v>5900</v>
       </c>
       <c r="Q265" t="n">
-        <v>1121000</v>
+        <v>1103300</v>
       </c>
     </row>
     <row r="266">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12446,19 +12446,19 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="N272" t="n">
         <v>7700</v>
       </c>
       <c r="O272" t="n">
-        <v>2887500</v>
+        <v>2772000</v>
       </c>
       <c r="P272" t="n">
         <v>13900</v>
       </c>
       <c r="Q272" t="n">
-        <v>5212500</v>
+        <v>5004000</v>
       </c>
     </row>
     <row r="273">
@@ -13513,10 +13513,10 @@
         <v>768</v>
       </c>
       <c r="N295" t="n">
-        <v>1778.4727448514</v>
+        <v>1778.4727414037</v>
       </c>
       <c r="O295" t="n">
-        <v>1365867.068045875</v>
+        <v>1365867.065398042</v>
       </c>
       <c r="P295" t="n">
         <v>4900</v>
@@ -13872,22 +13872,22 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
         <v>5</v>
       </c>
       <c r="N303" t="n">
-        <v>28079.166666667</v>
+        <v>26956</v>
       </c>
       <c r="O303" t="n">
-        <v>140395.833333335</v>
+        <v>134780</v>
       </c>
       <c r="P303" t="n">
         <v>44900</v>
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14620,19 +14620,19 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="N319" t="n">
         <v>11857</v>
       </c>
       <c r="O319" t="n">
-        <v>379424</v>
+        <v>82999</v>
       </c>
       <c r="P319" t="n">
         <v>19900</v>
       </c>
       <c r="Q319" t="n">
-        <v>636800</v>
+        <v>139300</v>
       </c>
     </row>
     <row r="320">
@@ -14795,7 +14795,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14804,19 +14804,19 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N323" t="n">
         <v>28116</v>
       </c>
       <c r="O323" t="n">
-        <v>674784</v>
+        <v>618552</v>
       </c>
       <c r="P323" t="n">
         <v>45900</v>
       </c>
       <c r="Q323" t="n">
-        <v>1101600</v>
+        <v>1009800</v>
       </c>
     </row>
     <row r="324">
@@ -14991,10 +14991,10 @@
         <v>5</v>
       </c>
       <c r="N327" t="n">
-        <v>2252.2976470588</v>
+        <v>2252.297658046</v>
       </c>
       <c r="O327" t="n">
-        <v>11261.488235294</v>
+        <v>11261.48829023</v>
       </c>
       <c r="P327" t="n">
         <v>3900</v>
@@ -15317,10 +15317,10 @@
         <v>324</v>
       </c>
       <c r="N334" t="n">
-        <v>2328.11868125</v>
+        <v>2328.1186779449</v>
       </c>
       <c r="O334" t="n">
-        <v>754310.452725</v>
+        <v>754310.4516541476</v>
       </c>
       <c r="P334" t="n">
         <v>4500</v>
@@ -15811,7 +15811,7 @@
         </is>
       </c>
       <c r="J345" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
@@ -15820,19 +15820,19 @@
         <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N345" t="n">
         <v>16285.911125</v>
       </c>
       <c r="O345" t="n">
-        <v>423433.68925</v>
+        <v>407147.778125</v>
       </c>
       <c r="P345" t="n">
         <v>29900</v>
       </c>
       <c r="Q345" t="n">
-        <v>777400</v>
+        <v>747500</v>
       </c>
     </row>
     <row r="346">
@@ -15857,7 +15857,7 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
@@ -15866,19 +15866,19 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N346" t="n">
         <v>17981</v>
       </c>
       <c r="O346" t="n">
-        <v>305677</v>
+        <v>287696</v>
       </c>
       <c r="P346" t="n">
         <v>29900</v>
       </c>
       <c r="Q346" t="n">
-        <v>508300</v>
+        <v>478400</v>
       </c>
     </row>
     <row r="347">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
@@ -15912,19 +15912,19 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N347" t="n">
         <v>3396.38</v>
       </c>
       <c r="O347" t="n">
-        <v>519646.14</v>
+        <v>506060.62</v>
       </c>
       <c r="P347" t="n">
         <v>6500</v>
       </c>
       <c r="Q347" t="n">
-        <v>994500</v>
+        <v>968500</v>
       </c>
     </row>
     <row r="348">
@@ -16145,10 +16145,10 @@
         <v>276</v>
       </c>
       <c r="N352" t="n">
-        <v>3903.7383529412</v>
+        <v>3903.7383683768</v>
       </c>
       <c r="O352" t="n">
-        <v>1077431.785411771</v>
+        <v>1077431.789671997</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
@@ -16680,7 +16680,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -16689,19 +16689,19 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="N364" t="n">
         <v>7635</v>
       </c>
       <c r="O364" t="n">
-        <v>4023645</v>
+        <v>4000740</v>
       </c>
       <c r="P364" t="n">
         <v>13900</v>
       </c>
       <c r="Q364" t="n">
-        <v>7325300</v>
+        <v>7283600</v>
       </c>
     </row>
     <row r="365">
@@ -16818,7 +16818,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -16827,19 +16827,19 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N367" t="n">
         <v>8806</v>
       </c>
       <c r="O367" t="n">
-        <v>1400154</v>
+        <v>1382542</v>
       </c>
       <c r="P367" t="n">
         <v>14900</v>
       </c>
       <c r="Q367" t="n">
-        <v>2369100</v>
+        <v>2339300</v>
       </c>
     </row>
     <row r="368">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16873,19 +16873,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N368" t="n">
         <v>23439</v>
       </c>
       <c r="O368" t="n">
-        <v>375024</v>
+        <v>281268</v>
       </c>
       <c r="P368" t="n">
         <v>37900</v>
       </c>
       <c r="Q368" t="n">
-        <v>606400</v>
+        <v>454800</v>
       </c>
     </row>
     <row r="369">
@@ -17094,7 +17094,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
@@ -17103,19 +17103,19 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N373" t="n">
         <v>17075.989520833</v>
       </c>
       <c r="O373" t="n">
-        <v>4986188.940083236</v>
+        <v>4969112.950562404</v>
       </c>
       <c r="P373" t="n">
         <v>27500</v>
       </c>
       <c r="Q373" t="n">
-        <v>8030000</v>
+        <v>8002500</v>
       </c>
     </row>
     <row r="374">
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="J374" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K374" t="n">
         <v>0</v>
@@ -17149,19 +17149,19 @@
         <v>0</v>
       </c>
       <c r="M374" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N374" t="n">
         <v>10398</v>
       </c>
       <c r="O374" t="n">
-        <v>603084</v>
+        <v>540696</v>
       </c>
       <c r="P374" t="n">
         <v>16900</v>
       </c>
       <c r="Q374" t="n">
-        <v>980200</v>
+        <v>878800</v>
       </c>
     </row>
     <row r="375">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -17837,19 +17837,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N389" t="n">
         <v>2458</v>
       </c>
       <c r="O389" t="n">
-        <v>159770</v>
+        <v>152396</v>
       </c>
       <c r="P389" t="n">
         <v>3500</v>
       </c>
       <c r="Q389" t="n">
-        <v>227500</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="390">
@@ -18254,10 +18254,10 @@
         <v>1248</v>
       </c>
       <c r="N398" t="n">
-        <v>1516.0387635597</v>
+        <v>1516.0387603223</v>
       </c>
       <c r="O398" t="n">
-        <v>1892016.376922506</v>
+        <v>1892016.37288223</v>
       </c>
       <c r="P398" t="n">
         <v>2300</v>
@@ -18346,10 +18346,10 @@
         <v>48</v>
       </c>
       <c r="N400" t="n">
-        <v>2458.5127187173</v>
+        <v>2458.5126727464</v>
       </c>
       <c r="O400" t="n">
-        <v>118008.6104984304</v>
+        <v>118008.6082918272</v>
       </c>
       <c r="P400" t="n">
         <v>3500</v>
@@ -18392,10 +18392,10 @@
         <v>48</v>
       </c>
       <c r="N401" t="n">
-        <v>1771.0901026694</v>
+        <v>1771.0896492484</v>
       </c>
       <c r="O401" t="n">
-        <v>85012.3249281312</v>
+        <v>85012.30316392321</v>
       </c>
       <c r="P401" t="n">
         <v>2500</v>
@@ -18438,10 +18438,10 @@
         <v>168</v>
       </c>
       <c r="N402" t="n">
-        <v>2079.3836916549</v>
+        <v>2079.383486674</v>
       </c>
       <c r="O402" t="n">
-        <v>349336.4601980232</v>
+        <v>349336.425761232</v>
       </c>
       <c r="P402" t="n">
         <v>2900</v>
@@ -18484,10 +18484,10 @@
         <v>48</v>
       </c>
       <c r="N403" t="n">
-        <v>1803.0161346363</v>
+        <v>1803.0162754535</v>
       </c>
       <c r="O403" t="n">
-        <v>86544.77446254239</v>
+        <v>86544.781221768</v>
       </c>
       <c r="P403" t="n">
         <v>2500</v>
@@ -18576,10 +18576,10 @@
         <v>96</v>
       </c>
       <c r="N405" t="n">
-        <v>2108.7945137157</v>
+        <v>2108.7953562005</v>
       </c>
       <c r="O405" t="n">
-        <v>202444.2733167072</v>
+        <v>202444.354195248</v>
       </c>
       <c r="P405" t="n">
         <v>2900</v>
@@ -18622,10 +18622,10 @@
         <v>144</v>
       </c>
       <c r="N406" t="n">
-        <v>2056.0824863487</v>
+        <v>2056.0823949889</v>
       </c>
       <c r="O406" t="n">
-        <v>296075.8780342128</v>
+        <v>296075.8648784016</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
@@ -18714,10 +18714,10 @@
         <v>360</v>
       </c>
       <c r="N408" t="n">
-        <v>1655.9298420859</v>
+        <v>1655.9297971228</v>
       </c>
       <c r="O408" t="n">
-        <v>596134.743150924</v>
+        <v>596134.7269642079</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18944,10 +18944,10 @@
         <v>224</v>
       </c>
       <c r="N413" t="n">
-        <v>1592.2821853389</v>
+        <v>1592.2823909986</v>
       </c>
       <c r="O413" t="n">
-        <v>356671.2095159136</v>
+        <v>356671.2555836864</v>
       </c>
       <c r="P413" t="n">
         <v>2500</v>
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="J416" t="n">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="K416" t="n">
         <v>0</v>
@@ -19072,19 +19072,19 @@
         <v>0</v>
       </c>
       <c r="M416" t="n">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="N416" t="n">
         <v>2060.1589866157</v>
       </c>
       <c r="O416" t="n">
-        <v>840544.8665392057</v>
+        <v>766379.1430210405</v>
       </c>
       <c r="P416" t="n">
         <v>2900</v>
       </c>
       <c r="Q416" t="n">
-        <v>1183200</v>
+        <v>1078800</v>
       </c>
     </row>
     <row r="417">
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="J417" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="K417" t="n">
         <v>0</v>
@@ -19118,19 +19118,19 @@
         <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N417" t="n">
-        <v>1259.2747051969</v>
+        <v>1259.2747084888</v>
       </c>
       <c r="O417" t="n">
-        <v>881492.2936378299</v>
+        <v>629637.3542443999</v>
       </c>
       <c r="P417" t="n">
         <v>1900</v>
       </c>
       <c r="Q417" t="n">
-        <v>1330000</v>
+        <v>950000</v>
       </c>
     </row>
     <row r="418">
@@ -19298,10 +19298,10 @@
         <v>516</v>
       </c>
       <c r="N421" t="n">
-        <v>692.15231697102</v>
+        <v>692.1523548442</v>
       </c>
       <c r="O421" t="n">
-        <v>357150.5955570464</v>
+        <v>357150.6150996072</v>
       </c>
       <c r="P421" t="n">
         <v>1200</v>
@@ -19335,7 +19335,7 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
@@ -19344,19 +19344,19 @@
         <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N422" t="n">
         <v>18491</v>
       </c>
       <c r="O422" t="n">
-        <v>1405316</v>
+        <v>1349843</v>
       </c>
       <c r="P422" t="n">
         <v>13500</v>
       </c>
       <c r="Q422" t="n">
-        <v>1026000</v>
+        <v>985500</v>
       </c>
     </row>
     <row r="423">
@@ -19439,10 +19439,10 @@
         <v>2800</v>
       </c>
       <c r="N424" t="n">
-        <v>1185.3195703545</v>
+        <v>1185.3195700703</v>
       </c>
       <c r="O424" t="n">
-        <v>3318894.7969926</v>
+        <v>3318894.79619684</v>
       </c>
       <c r="P424" t="n">
         <v>1900</v>
@@ -20601,10 +20601,10 @@
         <v>3</v>
       </c>
       <c r="N449" t="n">
-        <v>2270.3212987013</v>
+        <v>2270.3213157895</v>
       </c>
       <c r="O449" t="n">
-        <v>6810.9638961039</v>
+        <v>6810.9639473685</v>
       </c>
       <c r="P449" t="n">
         <v>3900</v>
@@ -21671,10 +21671,10 @@
         <v>757</v>
       </c>
       <c r="N472" t="n">
-        <v>3110.8396848556</v>
+        <v>3110.8396334311</v>
       </c>
       <c r="O472" t="n">
-        <v>2354905.641435689</v>
+        <v>2354905.602507343</v>
       </c>
       <c r="P472" t="n">
         <v>4500</v>
@@ -21837,7 +21837,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -21846,19 +21846,19 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="N476" t="n">
         <v>2030.02</v>
       </c>
       <c r="O476" t="n">
-        <v>245632.42</v>
+        <v>36540.36</v>
       </c>
       <c r="P476" t="n">
         <v>3600</v>
       </c>
       <c r="Q476" t="n">
-        <v>435600</v>
+        <v>64800</v>
       </c>
     </row>
     <row r="477">
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -21892,19 +21892,19 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N477" t="n">
         <v>7120</v>
       </c>
       <c r="O477" t="n">
-        <v>78320</v>
+        <v>49840</v>
       </c>
       <c r="P477" t="n">
         <v>8900</v>
       </c>
       <c r="Q477" t="n">
-        <v>97900</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="478">
@@ -22122,10 +22122,10 @@
         <v>18602</v>
       </c>
       <c r="N482" t="n">
-        <v>703.79492130965</v>
+        <v>703.79488487659</v>
       </c>
       <c r="O482" t="n">
-        <v>13091993.12620211</v>
+        <v>13091992.44847433</v>
       </c>
       <c r="P482" t="n">
         <v>900</v>
@@ -22251,7 +22251,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -22260,19 +22260,19 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N485" t="n">
         <v>2501.3846268657</v>
       </c>
       <c r="O485" t="n">
-        <v>165091.3853731362</v>
+        <v>150083.077611942</v>
       </c>
       <c r="P485" t="n">
         <v>4100</v>
       </c>
       <c r="Q485" t="n">
-        <v>270600</v>
+        <v>246000</v>
       </c>
     </row>
     <row r="486">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -22309,19 +22309,19 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N486" t="n">
         <v>14260.14</v>
       </c>
       <c r="O486" t="n">
-        <v>442064.34</v>
+        <v>370763.64</v>
       </c>
       <c r="P486" t="n">
         <v>15900</v>
       </c>
       <c r="Q486" t="n">
-        <v>492900</v>
+        <v>413400</v>
       </c>
     </row>
     <row r="487">
@@ -22629,10 +22629,10 @@
         <v>47</v>
       </c>
       <c r="N493" t="n">
-        <v>1595.4998805078</v>
+        <v>1595.4997449362</v>
       </c>
       <c r="O493" t="n">
-        <v>74988.49438386661</v>
+        <v>74988.4880120014</v>
       </c>
       <c r="P493" t="n">
         <v>2500</v>
@@ -23485,7 +23485,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23494,19 +23494,19 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N511" t="n">
         <v>12156.79</v>
       </c>
       <c r="O511" t="n">
-        <v>729407.4</v>
+        <v>717250.6100000001</v>
       </c>
       <c r="P511" t="n">
         <v>12000</v>
       </c>
       <c r="Q511" t="n">
-        <v>720000</v>
+        <v>708000</v>
       </c>
     </row>
     <row r="512">
@@ -23534,7 +23534,7 @@
         </is>
       </c>
       <c r="J512" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -23543,19 +23543,19 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N512" t="n">
         <v>12837.03</v>
       </c>
       <c r="O512" t="n">
-        <v>243903.57</v>
+        <v>192555.45</v>
       </c>
       <c r="P512" t="n">
         <v>15500</v>
       </c>
       <c r="Q512" t="n">
-        <v>294500</v>
+        <v>232500</v>
       </c>
     </row>
     <row r="513">
@@ -23681,7 +23681,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23690,19 +23690,19 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N515" t="n">
         <v>10084.09</v>
       </c>
       <c r="O515" t="n">
-        <v>131093.17</v>
+        <v>110924.99</v>
       </c>
       <c r="P515" t="n">
         <v>17900</v>
       </c>
       <c r="Q515" t="n">
-        <v>232700</v>
+        <v>196900</v>
       </c>
     </row>
     <row r="516">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -23785,19 +23785,19 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N517" t="n">
-        <v>23475.6576</v>
+        <v>23475.657391304</v>
       </c>
       <c r="O517" t="n">
-        <v>352134.864</v>
+        <v>305183.546086952</v>
       </c>
       <c r="P517" t="n">
         <v>31900</v>
       </c>
       <c r="Q517" t="n">
-        <v>478500</v>
+        <v>414700</v>
       </c>
     </row>
     <row r="518">
@@ -23886,10 +23886,10 @@
         <v>15</v>
       </c>
       <c r="N519" t="n">
-        <v>9746.8801960784</v>
+        <v>9746.8801980198</v>
       </c>
       <c r="O519" t="n">
-        <v>146203.202941176</v>
+        <v>146203.202970297</v>
       </c>
       <c r="P519" t="n">
         <v>18500</v>
@@ -24119,13 +24119,13 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M524" t="n">
         <v>6</v>
@@ -24541,7 +24541,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24550,19 +24550,19 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N533" t="n">
         <v>3067.0906122449</v>
       </c>
       <c r="O533" t="n">
-        <v>294440.6987755104</v>
+        <v>288306.5175510206</v>
       </c>
       <c r="P533" t="n">
         <v>7200</v>
       </c>
       <c r="Q533" t="n">
-        <v>691200</v>
+        <v>676800</v>
       </c>
     </row>
     <row r="534">
@@ -24590,7 +24590,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24599,19 +24599,19 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="N534" t="n">
         <v>507.37</v>
       </c>
       <c r="O534" t="n">
-        <v>24353.76</v>
+        <v>12176.88</v>
       </c>
       <c r="P534" t="n">
         <v>2500</v>
       </c>
       <c r="Q534" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="535">
@@ -26536,7 +26536,7 @@
         </is>
       </c>
       <c r="J575" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="K575" t="n">
         <v>0</v>
@@ -26545,19 +26545,19 @@
         <v>0</v>
       </c>
       <c r="M575" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N575" t="n">
         <v>1934.77</v>
       </c>
       <c r="O575" t="n">
-        <v>653952.26</v>
+        <v>646213.1800000001</v>
       </c>
       <c r="P575" t="n">
         <v>8900</v>
       </c>
       <c r="Q575" t="n">
-        <v>3008200</v>
+        <v>2972600</v>
       </c>
     </row>
     <row r="576">
@@ -26787,10 +26787,10 @@
         <v>648</v>
       </c>
       <c r="N580" t="n">
-        <v>665.3237979601701</v>
+        <v>665.32380350195</v>
       </c>
       <c r="O580" t="n">
-        <v>431129.8210781902</v>
+        <v>431129.8246692636</v>
       </c>
       <c r="P580" t="n">
         <v>2900</v>
@@ -28317,10 +28317,10 @@
         <v>172</v>
       </c>
       <c r="N614" t="n">
-        <v>705.5279984837</v>
+        <v>705.52797546012</v>
       </c>
       <c r="O614" t="n">
-        <v>121350.8157391964</v>
+        <v>121350.8117791407</v>
       </c>
       <c r="P614" t="n">
         <v>1500</v>
@@ -28358,10 +28358,10 @@
         <v>43</v>
       </c>
       <c r="N615" t="n">
-        <v>4985.4063157895</v>
+        <v>4985.4064864865</v>
       </c>
       <c r="O615" t="n">
-        <v>214372.4715789485</v>
+        <v>214372.4789189195</v>
       </c>
       <c r="P615" t="n">
         <v>7900</v>
@@ -28460,10 +28460,10 @@
         <v>294</v>
       </c>
       <c r="N617" t="n">
-        <v>1757.3205829596</v>
+        <v>1757.3206175772</v>
       </c>
       <c r="O617" t="n">
-        <v>516652.2513901224</v>
+        <v>516652.2615676968</v>
       </c>
       <c r="P617" t="n">
         <v>2000</v>
@@ -28690,10 +28690,10 @@
         <v>82</v>
       </c>
       <c r="N622" t="n">
-        <v>13493.858297872</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O622" t="n">
-        <v>1106496.380425504</v>
+        <v>1106496.380000006</v>
       </c>
       <c r="P622" t="n">
         <v>16900</v>
@@ -29046,7 +29046,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -29055,19 +29055,19 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N630" t="n">
         <v>17986.24</v>
       </c>
       <c r="O630" t="n">
-        <v>1528830.4</v>
+        <v>1510844.16</v>
       </c>
       <c r="P630" t="n">
         <v>18500</v>
       </c>
       <c r="Q630" t="n">
-        <v>1572500</v>
+        <v>1554000</v>
       </c>
     </row>
     <row r="631">
@@ -29092,7 +29092,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -29101,19 +29101,19 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="N631" t="n">
         <v>7480</v>
       </c>
       <c r="O631" t="n">
-        <v>628320</v>
+        <v>538560</v>
       </c>
       <c r="P631" t="n">
         <v>9500</v>
       </c>
       <c r="Q631" t="n">
-        <v>798000</v>
+        <v>684000</v>
       </c>
     </row>
     <row r="632">
@@ -29138,7 +29138,7 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -29147,19 +29147,19 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N632" t="n">
         <v>5280</v>
       </c>
       <c r="O632" t="n">
-        <v>369600</v>
+        <v>337920</v>
       </c>
       <c r="P632" t="n">
         <v>6900</v>
       </c>
       <c r="Q632" t="n">
-        <v>483000</v>
+        <v>441600</v>
       </c>
     </row>
     <row r="633">
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
@@ -29239,19 +29239,19 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="N634" t="n">
         <v>9240</v>
       </c>
       <c r="O634" t="n">
-        <v>3585120</v>
+        <v>3400320</v>
       </c>
       <c r="P634" t="n">
         <v>11500</v>
       </c>
       <c r="Q634" t="n">
-        <v>4462000</v>
+        <v>4232000</v>
       </c>
     </row>
     <row r="635">
@@ -29276,7 +29276,7 @@
         </is>
       </c>
       <c r="J635" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K635" t="n">
         <v>0</v>
@@ -29285,19 +29285,19 @@
         <v>0</v>
       </c>
       <c r="M635" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="N635" t="n">
         <v>4576</v>
       </c>
       <c r="O635" t="n">
-        <v>617760</v>
+        <v>594880</v>
       </c>
       <c r="P635" t="n">
         <v>5900</v>
       </c>
       <c r="Q635" t="n">
-        <v>796500</v>
+        <v>767000</v>
       </c>
     </row>
     <row r="636">
@@ -29460,7 +29460,7 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -29469,19 +29469,19 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N639" t="n">
         <v>910.85</v>
       </c>
       <c r="O639" t="n">
-        <v>32790.6</v>
+        <v>30968.9</v>
       </c>
       <c r="P639" t="n">
         <v>7900</v>
       </c>
       <c r="Q639" t="n">
-        <v>284400</v>
+        <v>268600</v>
       </c>
     </row>
     <row r="640">
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -29658,19 +29658,19 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N643" t="n">
-        <v>1319.3609146341</v>
+        <v>1319.3609259259</v>
       </c>
       <c r="O643" t="n">
-        <v>228249.4382316993</v>
+        <v>221652.6355555512</v>
       </c>
       <c r="P643" t="n">
         <v>3500</v>
       </c>
       <c r="Q643" t="n">
-        <v>605500</v>
+        <v>588000</v>
       </c>
     </row>
     <row r="644">
@@ -29904,16 +29904,16 @@
         <v>158</v>
       </c>
       <c r="N648" t="n">
-        <v>2539.5716527391</v>
+        <v>2539.5716573557</v>
       </c>
       <c r="O648" t="n">
-        <v>401252.3211327778</v>
+        <v>401252.3218622006</v>
       </c>
       <c r="P648" t="n">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="Q648" t="n">
-        <v>553000</v>
+        <v>458200</v>
       </c>
     </row>
     <row r="649">
@@ -29950,16 +29950,16 @@
         <v>95</v>
       </c>
       <c r="N649" t="n">
-        <v>4171.6686251469</v>
+        <v>4171.668620283</v>
       </c>
       <c r="O649" t="n">
-        <v>396308.5193889555</v>
+        <v>396308.518926885</v>
       </c>
       <c r="P649" t="n">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="Q649" t="n">
-        <v>522500</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="650">

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -8816,10 +8816,10 @@
         <v>174</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.515543043</v>
+        <v>2403.5155820371</v>
       </c>
       <c r="O191" t="n">
-        <v>418211.704489482</v>
+        <v>418211.7112744554</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -21671,10 +21671,10 @@
         <v>757</v>
       </c>
       <c r="N472" t="n">
-        <v>3110.8396334311</v>
+        <v>3110.8396273474</v>
       </c>
       <c r="O472" t="n">
-        <v>2354905.602507343</v>
+        <v>2354905.597901982</v>
       </c>
       <c r="P472" t="n">
         <v>4500</v>
@@ -22122,10 +22122,10 @@
         <v>18602</v>
       </c>
       <c r="N482" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O482" t="n">
-        <v>13091992.44847433</v>
+        <v>13091992.42421992</v>
       </c>
       <c r="P482" t="n">
         <v>900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -595,10 +595,10 @@
         <v>106</v>
       </c>
       <c r="N5" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>2873463.284379136</v>
+        <v>2862000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -675,10 +675,10 @@
         <v>51</v>
       </c>
       <c r="N7" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O7" t="n">
-        <v>1382986.956521748</v>
+        <v>1377000</v>
       </c>
       <c r="P7" t="n">
         <v>30000</v>
@@ -2099,10 +2099,10 @@
         <v>82</v>
       </c>
       <c r="N42" t="n">
-        <v>27229.787234043</v>
+        <v>27000</v>
       </c>
       <c r="O42" t="n">
-        <v>2232842.553191526</v>
+        <v>2214000</v>
       </c>
       <c r="P42" t="n">
         <v>20000</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O88" t="n">
-        <v>3479589.419130711</v>
+        <v>3474452.73166767</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -5172,10 +5172,10 @@
         <v>309</v>
       </c>
       <c r="N111" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O111" t="n">
-        <v>1515135.601238108</v>
+        <v>1511297.385695253</v>
       </c>
       <c r="P111" t="n">
         <v>8200</v>
@@ -5264,10 +5264,10 @@
         <v>133</v>
       </c>
       <c r="N113" t="n">
-        <v>5928.7474048443</v>
+        <v>5888</v>
       </c>
       <c r="O113" t="n">
-        <v>788523.4048442919</v>
+        <v>783104</v>
       </c>
       <c r="P113" t="n">
         <v>9500</v>
@@ -5850,10 +5850,10 @@
         <v>395</v>
       </c>
       <c r="N126" t="n">
-        <v>8184.2747524752</v>
+        <v>8154</v>
       </c>
       <c r="O126" t="n">
-        <v>3232788.527227704</v>
+        <v>3220830</v>
       </c>
       <c r="P126" t="n">
         <v>13500</v>
@@ -5896,10 +5896,10 @@
         <v>305</v>
       </c>
       <c r="N127" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O127" t="n">
-        <v>4523580.464472735</v>
+        <v>4520825.54314451</v>
       </c>
       <c r="P127" t="n">
         <v>24900</v>
@@ -6482,10 +6482,10 @@
         <v>31</v>
       </c>
       <c r="N140" t="n">
-        <v>15071.76</v>
+        <v>14386.68</v>
       </c>
       <c r="O140" t="n">
-        <v>467224.56</v>
+        <v>445987.08</v>
       </c>
       <c r="P140" t="n">
         <v>21900</v>
@@ -8166,10 +8166,10 @@
         <v>117</v>
       </c>
       <c r="N177" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O177" t="n">
-        <v>1399210.763033187</v>
+        <v>1394803.8</v>
       </c>
       <c r="P177" t="n">
         <v>19900</v>
@@ -9394,10 +9394,10 @@
         <v>15</v>
       </c>
       <c r="N204" t="n">
-        <v>10907.343571429</v>
+        <v>10836.973636364</v>
       </c>
       <c r="O204" t="n">
-        <v>163610.153571435</v>
+        <v>162554.60454546</v>
       </c>
       <c r="P204" t="n">
         <v>19900</v>
@@ -9902,10 +9902,10 @@
         <v>6</v>
       </c>
       <c r="N215" t="n">
-        <v>9460.065359477099</v>
+        <v>9338</v>
       </c>
       <c r="O215" t="n">
-        <v>56760.3921568626</v>
+        <v>56028</v>
       </c>
       <c r="P215" t="n">
         <v>15500</v>
@@ -10456,10 +10456,10 @@
         <v>129</v>
       </c>
       <c r="N228" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O228" t="n">
-        <v>3170032.364473734</v>
+        <v>3165404.58</v>
       </c>
       <c r="P228" t="n">
         <v>52900</v>
@@ -11250,10 +11250,10 @@
         <v>32</v>
       </c>
       <c r="N246" t="n">
-        <v>11594.699548023</v>
+        <v>11562.038418079</v>
       </c>
       <c r="O246" t="n">
-        <v>371030.385536736</v>
+        <v>369985.229378528</v>
       </c>
       <c r="P246" t="n">
         <v>18500</v>
@@ -11480,10 +11480,10 @@
         <v>92</v>
       </c>
       <c r="N251" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O251" t="n">
-        <v>2505367.91632</v>
+        <v>2495386.36896</v>
       </c>
       <c r="P251" t="n">
         <v>44500</v>
@@ -11792,10 +11792,10 @@
         <v>24</v>
       </c>
       <c r="N258" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O258" t="n">
-        <v>648264.9824561521</v>
+        <v>644496</v>
       </c>
       <c r="P258" t="n">
         <v>43900</v>
@@ -12118,10 +12118,10 @@
         <v>19</v>
       </c>
       <c r="N265" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O265" t="n">
-        <v>248511.721018869</v>
+        <v>246650.21</v>
       </c>
       <c r="P265" t="n">
         <v>21900</v>
@@ -15037,10 +15037,10 @@
         <v>6</v>
       </c>
       <c r="N328" t="n">
-        <v>27408.335664336</v>
+        <v>27218</v>
       </c>
       <c r="O328" t="n">
-        <v>164450.013986016</v>
+        <v>163308</v>
       </c>
       <c r="P328" t="n">
         <v>43900</v>
@@ -15083,10 +15083,10 @@
         <v>8</v>
       </c>
       <c r="N329" t="n">
-        <v>21456.861702128</v>
+        <v>21231</v>
       </c>
       <c r="O329" t="n">
-        <v>171654.893617024</v>
+        <v>169848</v>
       </c>
       <c r="P329" t="n">
         <v>34500</v>
@@ -15590,10 +15590,10 @@
         <v>172</v>
       </c>
       <c r="N340" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O340" t="n">
-        <v>1582112.380952386</v>
+        <v>1578616</v>
       </c>
       <c r="P340" t="n">
         <v>14900</v>
@@ -15636,10 +15636,10 @@
         <v>3</v>
       </c>
       <c r="N341" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O341" t="n">
-        <v>13703.6844872919</v>
+        <v>13632</v>
       </c>
       <c r="P341" t="n">
         <v>7900</v>
@@ -15728,10 +15728,10 @@
         <v>39</v>
       </c>
       <c r="N343" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O343" t="n">
-        <v>543990.239543712</v>
+        <v>542958</v>
       </c>
       <c r="P343" t="n">
         <v>22900</v>
@@ -17057,10 +17057,10 @@
         <v>291</v>
       </c>
       <c r="N372" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O372" t="n">
-        <v>4982973.795418518</v>
+        <v>4969112.949978948</v>
       </c>
       <c r="P372" t="n">
         <v>27500</v>
@@ -17377,10 +17377,10 @@
         <v>36</v>
       </c>
       <c r="N379" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O379" t="n">
-        <v>623735.5582821959</v>
+        <v>618048</v>
       </c>
       <c r="P379" t="n">
         <v>27900</v>
@@ -17423,10 +17423,10 @@
         <v>12</v>
       </c>
       <c r="N380" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O380" t="n">
-        <v>327468.911196912</v>
+        <v>327048</v>
       </c>
       <c r="P380" t="n">
         <v>43900</v>
@@ -17515,10 +17515,10 @@
         <v>51</v>
       </c>
       <c r="N382" t="n">
-        <v>8721.297429620599</v>
+        <v>8700</v>
       </c>
       <c r="O382" t="n">
-        <v>444786.1689106506</v>
+        <v>443700</v>
       </c>
       <c r="P382" t="n">
         <v>14900</v>
@@ -24232,10 +24232,10 @@
         <v>1</v>
       </c>
       <c r="N526" t="n">
-        <v>7184.3863636364</v>
+        <v>6773.85</v>
       </c>
       <c r="O526" t="n">
-        <v>7184.3863636364</v>
+        <v>6773.85</v>
       </c>
       <c r="P526" t="n">
         <v>9500</v>
@@ -26793,10 +26793,10 @@
         <v>127</v>
       </c>
       <c r="N580" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="O580" t="n">
-        <v>3110548.890569609</v>
+        <v>3090985.69</v>
       </c>
       <c r="P580" t="n">
         <v>27900</v>

--- a/bodegas/LJ-100.xlsx
+++ b/bodegas/LJ-100.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -636,10 +636,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1811.3087042532</v>
+        <v>1811.3087824351</v>
       </c>
       <c r="O6" t="n">
-        <v>1811.3087042532</v>
+        <v>1811.3087824351</v>
       </c>
       <c r="P6" t="n">
         <v>2600</v>
@@ -1312,10 +1312,10 @@
         <v>66</v>
       </c>
       <c r="N23" t="n">
-        <v>2474.703951049</v>
+        <v>2474.7036162362</v>
       </c>
       <c r="O23" t="n">
-        <v>163330.460769234</v>
+        <v>163330.4386715892</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -3096,10 +3096,10 @@
         <v>1271</v>
       </c>
       <c r="N65" t="n">
-        <v>1098.0630438871</v>
+        <v>1098.0630728186</v>
       </c>
       <c r="O65" t="n">
-        <v>1395638.128780504</v>
+        <v>1395638.165552441</v>
       </c>
       <c r="P65" t="n">
         <v>1500</v>
@@ -4029,10 +4029,10 @@
         <v>666</v>
       </c>
       <c r="N86" t="n">
-        <v>2582.2551814224</v>
+        <v>2582.2551438323</v>
       </c>
       <c r="O86" t="n">
-        <v>1719781.950827318</v>
+        <v>1719781.925792312</v>
       </c>
       <c r="P86" t="n">
         <v>4500</v>
@@ -4121,10 +4121,10 @@
         <v>666</v>
       </c>
       <c r="N88" t="n">
-        <v>5216.895993495</v>
+        <v>5216.8959816133</v>
       </c>
       <c r="O88" t="n">
-        <v>3474452.73166767</v>
+        <v>3474452.723754458</v>
       </c>
       <c r="P88" t="n">
         <v>8500</v>
@@ -4352,10 +4352,10 @@
         <v>3167</v>
       </c>
       <c r="N93" t="n">
-        <v>3158.8608347353</v>
+        <v>3158.8608348592</v>
       </c>
       <c r="O93" t="n">
-        <v>10004112.2636067</v>
+        <v>10004112.26399909</v>
       </c>
       <c r="P93" t="n">
         <v>5600</v>
@@ -4627,10 +4627,10 @@
         <v>259</v>
       </c>
       <c r="N99" t="n">
-        <v>2694.8231282537</v>
+        <v>2694.823125</v>
       </c>
       <c r="O99" t="n">
-        <v>697959.1902177082</v>
+        <v>697959.189375</v>
       </c>
       <c r="P99" t="n">
         <v>4900</v>
@@ -4947,10 +4947,10 @@
         <v>581</v>
       </c>
       <c r="N106" t="n">
-        <v>3795.7100076132</v>
+        <v>3795.7100076147</v>
       </c>
       <c r="O106" t="n">
-        <v>2205307.514423269</v>
+        <v>2205307.514424141</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -5172,10 +5172,10 @@
         <v>309</v>
       </c>
       <c r="N111" t="n">
-        <v>4890.9300507937</v>
+        <v>4890.9300509879</v>
       </c>
       <c r="O111" t="n">
-        <v>1511297.385695253</v>
+        <v>1511297.385755261</v>
       </c>
       <c r="P111" t="n">
         <v>8200</v>
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5619,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N121" t="n">
         <v>10716.34</v>
       </c>
       <c r="O121" t="n">
-        <v>267908.5</v>
+        <v>160745.1</v>
       </c>
       <c r="P121" t="n">
         <v>39000</v>
       </c>
       <c r="Q121" t="n">
-        <v>975000</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="122">
@@ -5671,10 +5671,10 @@
         <v>240</v>
       </c>
       <c r="N122" t="n">
-        <v>3594.2534111187</v>
+        <v>3594.2533147632</v>
       </c>
       <c r="O122" t="n">
-        <v>862620.8186684881</v>
+        <v>862620.795543168</v>
       </c>
       <c r="P122" t="n">
         <v>6500</v>
@@ -5712,10 +5712,10 @@
         <v>108</v>
       </c>
       <c r="N123" t="n">
-        <v>3240.8500479616</v>
+        <v>3240.8500492611</v>
       </c>
       <c r="O123" t="n">
-        <v>350011.8051798528</v>
+        <v>350011.8053201988</v>
       </c>
       <c r="P123" t="n">
         <v>5200</v>
@@ -5896,10 +5896,10 @@
         <v>305</v>
       </c>
       <c r="N127" t="n">
-        <v>14822.378829982</v>
+        <v>14822.378829268</v>
       </c>
       <c r="O127" t="n">
-        <v>4520825.54314451</v>
+        <v>4520825.54292674</v>
       </c>
       <c r="P127" t="n">
         <v>24900</v>
@@ -6623,10 +6623,10 @@
         <v>210</v>
       </c>
       <c r="N143" t="n">
-        <v>3041.66001386</v>
+        <v>3041.6600138793</v>
       </c>
       <c r="O143" t="n">
-        <v>638748.6029106</v>
+        <v>638748.602914653</v>
       </c>
       <c r="P143" t="n">
         <v>5500</v>
@@ -6751,10 +6751,10 @@
         <v>1930</v>
       </c>
       <c r="N146" t="n">
-        <v>4371.171261065</v>
+        <v>4371.1712612367</v>
       </c>
       <c r="O146" t="n">
-        <v>8436360.533855451</v>
+        <v>8436360.534186831</v>
       </c>
       <c r="P146" t="n">
         <v>8900</v>
@@ -6841,10 +6841,10 @@
         <v>181</v>
       </c>
       <c r="N148" t="n">
-        <v>1592.5656302521</v>
+        <v>1592.5655172414</v>
       </c>
       <c r="O148" t="n">
-        <v>288254.3790756301</v>
+        <v>288254.3586206934</v>
       </c>
       <c r="P148" t="n">
         <v>3900</v>
@@ -8632,10 +8632,10 @@
         <v>556</v>
       </c>
       <c r="N187" t="n">
-        <v>1630.9241816204</v>
+        <v>1630.9242252747</v>
       </c>
       <c r="O187" t="n">
-        <v>906793.8449809424</v>
+        <v>906793.8692527332</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8724,10 +8724,10 @@
         <v>192</v>
       </c>
       <c r="N189" t="n">
-        <v>1690.5861086474</v>
+        <v>1690.5858435754</v>
       </c>
       <c r="O189" t="n">
-        <v>324592.5328603008</v>
+        <v>324592.4819664768</v>
       </c>
       <c r="P189" t="n">
         <v>2900</v>
@@ -8770,10 +8770,10 @@
         <v>1422</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.1943423824</v>
+        <v>1550.1943880809</v>
       </c>
       <c r="O190" t="n">
-        <v>2204376.354867773</v>
+        <v>2204376.41985104</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8816,10 +8816,10 @@
         <v>22</v>
       </c>
       <c r="N191" t="n">
-        <v>1579.3866044776</v>
+        <v>1579.3858102767</v>
       </c>
       <c r="O191" t="n">
-        <v>34746.5052985072</v>
+        <v>34746.4878260874</v>
       </c>
       <c r="P191" t="n">
         <v>2900</v>
@@ -8862,10 +8862,10 @@
         <v>174</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5162209454</v>
+        <v>2403.5165803524</v>
       </c>
       <c r="O192" t="n">
-        <v>418211.8224444996</v>
+        <v>418211.8849813176</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -8903,10 +8903,10 @@
         <v>59</v>
       </c>
       <c r="N193" t="n">
-        <v>1232.8061025641</v>
+        <v>1232.8060309278</v>
       </c>
       <c r="O193" t="n">
-        <v>72735.56005128191</v>
+        <v>72735.55582474021</v>
       </c>
       <c r="P193" t="n">
         <v>2400</v>
@@ -9946,10 +9946,10 @@
         <v>361</v>
       </c>
       <c r="N216" t="n">
-        <v>4196.8725410978</v>
+        <v>4196.872541806</v>
       </c>
       <c r="O216" t="n">
-        <v>1515070.987336306</v>
+        <v>1515070.987591966</v>
       </c>
       <c r="P216" t="n">
         <v>5900</v>
@@ -10763,10 +10763,10 @@
         <v>900</v>
       </c>
       <c r="N235" t="n">
-        <v>998.76126091703</v>
+        <v>998.76126229508</v>
       </c>
       <c r="O235" t="n">
-        <v>898885.134825327</v>
+        <v>898885.1360655719</v>
       </c>
       <c r="P235" t="n">
         <v>1600</v>
@@ -10904,10 +10904,10 @@
         <v>113</v>
       </c>
       <c r="N238" t="n">
-        <v>4285.1960620525</v>
+        <v>4285.1961426844</v>
       </c>
       <c r="O238" t="n">
-        <v>484227.1550119325</v>
+        <v>484227.1641233372</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
@@ -11163,10 +11163,10 @@
         <v>1280</v>
       </c>
       <c r="N244" t="n">
-        <v>4814.2679276196</v>
+        <v>4814.2679275122</v>
       </c>
       <c r="O244" t="n">
-        <v>6162262.947353088</v>
+        <v>6162262.947215616</v>
       </c>
       <c r="P244" t="n">
         <v>9900</v>
@@ -11480,10 +11480,10 @@
         <v>92</v>
       </c>
       <c r="N251" t="n">
-        <v>27123.76488</v>
+        <v>27123.764869739</v>
       </c>
       <c r="O251" t="n">
-        <v>2495386.36896</v>
+        <v>2495386.368015988</v>
       </c>
       <c r="P251" t="n">
         <v>44500</v>
@@ -11700,10 +11700,10 @@
         <v>522</v>
       </c>
       <c r="N256" t="n">
-        <v>1561.0033241379</v>
+        <v>1561.0035960591</v>
       </c>
       <c r="O256" t="n">
-        <v>814843.7351999838</v>
+        <v>814843.8771428502</v>
       </c>
       <c r="P256" t="n">
         <v>2900</v>
@@ -11838,10 +11838,10 @@
         <v>188</v>
       </c>
       <c r="N259" t="n">
-        <v>7969.9501692308</v>
+        <v>7969.950169361</v>
       </c>
       <c r="O259" t="n">
-        <v>1498350.63181539</v>
+        <v>1498350.631839868</v>
       </c>
       <c r="P259" t="n">
         <v>12900</v>
@@ -12860,10 +12860,10 @@
         <v>81</v>
       </c>
       <c r="N281" t="n">
-        <v>5218.1705789474</v>
+        <v>5218.1705812417</v>
       </c>
       <c r="O281" t="n">
-        <v>422671.8168947394</v>
+        <v>422671.8170805777</v>
       </c>
       <c r="P281" t="n">
         <v>8500</v>
@@ -13556,10 +13556,10 @@
         <v>768</v>
       </c>
       <c r="N296" t="n">
-        <v>1778.4727487406</v>
+        <v>1778.4727855775</v>
       </c>
       <c r="O296" t="n">
-        <v>1365867.071032781</v>
+        <v>1365867.09932352</v>
       </c>
       <c r="P296" t="n">
         <v>4900</v>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13737,19 +13737,19 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N300" t="n">
         <v>22739</v>
       </c>
       <c r="O300" t="n">
-        <v>3433589</v>
+        <v>3319894</v>
       </c>
       <c r="P300" t="n">
         <v>36900</v>
       </c>
       <c r="Q300" t="n">
-        <v>5571900</v>
+        <v>5387400</v>
       </c>
     </row>
     <row r="301">
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13783,19 +13783,19 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="N301" t="n">
         <v>18016</v>
       </c>
       <c r="O301" t="n">
-        <v>5314720</v>
+        <v>5206624</v>
       </c>
       <c r="P301" t="n">
         <v>29900</v>
       </c>
       <c r="Q301" t="n">
-        <v>8820500</v>
+        <v>8641100</v>
       </c>
     </row>
     <row r="302">
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13829,19 +13829,19 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N302" t="n">
         <v>16058</v>
       </c>
       <c r="O302" t="n">
-        <v>2216004</v>
+        <v>2119656</v>
       </c>
       <c r="P302" t="n">
         <v>25900</v>
       </c>
       <c r="Q302" t="n">
-        <v>3574200</v>
+        <v>3418800</v>
       </c>
     </row>
     <row r="303">
@@ -14942,10 +14942,10 @@
         <v>5</v>
       </c>
       <c r="N326" t="n">
-        <v>2252.2977023121</v>
+        <v>2252.2978962963</v>
       </c>
       <c r="O326" t="n">
-        <v>11261.4885115605</v>
+        <v>11261.4894814815</v>
       </c>
       <c r="P326" t="n">
         <v>3900</v>
@@ -15268,10 +15268,10 @@
         <v>324</v>
       </c>
       <c r="N333" t="n">
-        <v>2328.1186779449</v>
+        <v>2328.1186767012</v>
       </c>
       <c r="O333" t="n">
-        <v>754310.4516541476</v>
+        <v>754310.4512511888</v>
       </c>
       <c r="P333" t="n">
         <v>4500</v>
@@ -15912,10 +15912,10 @@
         <v>137</v>
       </c>
       <c r="N347" t="n">
-        <v>4907.8225098814</v>
+        <v>4907.8225298805</v>
       </c>
       <c r="O347" t="n">
-        <v>672371.6838537517</v>
+        <v>672371.6865936285</v>
       </c>
       <c r="P347" t="n">
         <v>8200</v>
@@ -16096,10 +16096,10 @@
         <v>276</v>
       </c>
       <c r="N351" t="n">
-        <v>3903.7386507259</v>
+        <v>3903.7388113695</v>
       </c>
       <c r="O351" t="n">
-        <v>1077431.867600348</v>
+        <v>1077431.911937982</v>
       </c>
       <c r="P351" t="n">
         <v>7500</v>
@@ -18159,10 +18159,10 @@
         <v>1248</v>
       </c>
       <c r="N396" t="n">
-        <v>1516.0387603223</v>
+        <v>1516.0387548048</v>
       </c>
       <c r="O396" t="n">
-        <v>1892016.37288223</v>
+        <v>1892016.36599639</v>
       </c>
       <c r="P396" t="n">
         <v>2300</v>
@@ -18251,10 +18251,10 @@
         <v>48</v>
       </c>
       <c r="N398" t="n">
-        <v>2458.5126727464</v>
+        <v>2458.5126365879</v>
       </c>
       <c r="O398" t="n">
-        <v>118008.6082918272</v>
+        <v>118008.6065562192</v>
       </c>
       <c r="P398" t="n">
         <v>3500</v>
@@ -18297,10 +18297,10 @@
         <v>48</v>
       </c>
       <c r="N399" t="n">
-        <v>1771.0894683176</v>
+        <v>1771.0894375457</v>
       </c>
       <c r="O399" t="n">
-        <v>85012.2944792448</v>
+        <v>85012.2930021936</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
@@ -18343,10 +18343,10 @@
         <v>168</v>
       </c>
       <c r="N400" t="n">
-        <v>2079.383486674</v>
+        <v>2079.3834819145</v>
       </c>
       <c r="O400" t="n">
-        <v>349336.425761232</v>
+        <v>349336.424961636</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -18389,10 +18389,10 @@
         <v>48</v>
       </c>
       <c r="N401" t="n">
-        <v>1803.0162940958</v>
+        <v>1803.0163011152</v>
       </c>
       <c r="O401" t="n">
-        <v>86544.78211659841</v>
+        <v>86544.78245352959</v>
       </c>
       <c r="P401" t="n">
         <v>2500</v>
@@ -18435,10 +18435,10 @@
         <v>156</v>
       </c>
       <c r="N402" t="n">
-        <v>3306.5944785276</v>
+        <v>3306.5944700461</v>
       </c>
       <c r="O402" t="n">
-        <v>515828.7386503056</v>
+        <v>515828.7373271916</v>
       </c>
       <c r="P402" t="n">
         <v>4900</v>
@@ -18481,10 +18481,10 @@
         <v>96</v>
       </c>
       <c r="N403" t="n">
-        <v>2108.7954376658</v>
+        <v>2108.7956032172</v>
       </c>
       <c r="O403" t="n">
-        <v>202444.3620159168</v>
+        <v>202444.3779088512</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>
@@ -18527,10 +18527,10 @@
         <v>144</v>
       </c>
       <c r="N404" t="n">
-        <v>2056.0823949889</v>
+        <v>2056.0823271375</v>
       </c>
       <c r="O404" t="n">
-        <v>296075.8648784016</v>
+        <v>296075.8551078</v>
       </c>
       <c r="P404" t="n">
         <v>2900</v>
@@ -18573,10 +18573,10 @@
         <v>90</v>
       </c>
       <c r="N405" t="n">
-        <v>3224.5693375065</v>
+        <v>3224.5693668237</v>
       </c>
       <c r="O405" t="n">
-        <v>290211.240375585</v>
+        <v>290211.243014133</v>
       </c>
       <c r="P405" t="n">
         <v>4500</v>
@@ -18619,10 +18619,10 @@
         <v>360</v>
       </c>
       <c r="N406" t="n">
-        <v>1655.9297403561</v>
+        <v>1655.9297327394</v>
       </c>
       <c r="O406" t="n">
-        <v>596134.706528196</v>
+        <v>596134.703786184</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -18980,10 +18980,10 @@
         <v>372</v>
       </c>
       <c r="N414" t="n">
-        <v>2060.1589866157</v>
+        <v>2060.1589443378</v>
       </c>
       <c r="O414" t="n">
-        <v>766379.1430210405</v>
+        <v>766379.1272936617</v>
       </c>
       <c r="P414" t="n">
         <v>2900</v>
@@ -19026,10 +19026,10 @@
         <v>400</v>
       </c>
       <c r="N415" t="n">
-        <v>1259.2747095871</v>
+        <v>1259.2747272302</v>
       </c>
       <c r="O415" t="n">
-        <v>503709.88383484</v>
+        <v>503709.89089208</v>
       </c>
       <c r="P415" t="n">
         <v>1900</v>
@@ -19113,10 +19113,10 @@
         <v>97</v>
       </c>
       <c r="N417" t="n">
-        <v>2842.2744146685</v>
+        <v>2842.2744067797</v>
       </c>
       <c r="O417" t="n">
-        <v>275700.6182228445</v>
+        <v>275700.6174576309</v>
       </c>
       <c r="P417" t="n">
         <v>4900</v>
@@ -19203,10 +19203,10 @@
         <v>516</v>
       </c>
       <c r="N419" t="n">
-        <v>692.15238407171</v>
+        <v>692.1524039631501</v>
       </c>
       <c r="O419" t="n">
-        <v>357150.6301810024</v>
+        <v>357150.6404449854</v>
       </c>
       <c r="P419" t="n">
         <v>1200</v>
@@ -19344,10 +19344,10 @@
         <v>2800</v>
       </c>
       <c r="N422" t="n">
-        <v>1185.3195700703</v>
+        <v>1185.319565762</v>
       </c>
       <c r="O422" t="n">
-        <v>3318894.79619684</v>
+        <v>3318894.7841336</v>
       </c>
       <c r="P422" t="n">
         <v>1900</v>
@@ -19577,7 +19577,7 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
@@ -19586,19 +19586,19 @@
         <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="N427" t="n">
         <v>5215</v>
       </c>
       <c r="O427" t="n">
-        <v>5006400</v>
+        <v>4928175</v>
       </c>
       <c r="P427" t="n">
         <v>8900</v>
       </c>
       <c r="Q427" t="n">
-        <v>8544000</v>
+        <v>8410500</v>
       </c>
     </row>
     <row r="428">
@@ -21821,10 +21821,10 @@
         <v>757</v>
       </c>
       <c r="N475" t="n">
-        <v>3110.8392324094</v>
+        <v>3110.8390217391</v>
       </c>
       <c r="O475" t="n">
-        <v>2354905.298933916</v>
+        <v>2354905.139456499</v>
       </c>
       <c r="P475" t="n">
         <v>4500</v>
@@ -22272,10 +22272,10 @@
         <v>18602</v>
       </c>
       <c r="N485" t="n">
-        <v>703.79485280542</v>
+        <v>703.79483731577</v>
       </c>
       <c r="O485" t="n">
-        <v>13091991.85188642</v>
+        <v>13091991.56374795</v>
       </c>
       <c r="P485" t="n">
         <v>900</v>
@@ -22321,10 +22321,10 @@
         <v>55</v>
       </c>
       <c r="N486" t="n">
-        <v>3182.251119403</v>
+        <v>3182.2511257036</v>
       </c>
       <c r="O486" t="n">
-        <v>175023.811567165</v>
+        <v>175023.811913698</v>
       </c>
       <c r="P486" t="n">
         <v>6900</v>
@@ -22413,10 +22413,10 @@
         <v>60</v>
       </c>
       <c r="N488" t="n">
-        <v>2501.3845728643</v>
+        <v>2501.3845177665</v>
       </c>
       <c r="O488" t="n">
-        <v>150083.074371858</v>
+        <v>150083.07106599</v>
       </c>
       <c r="P488" t="n">
         <v>4100</v>
@@ -22779,10 +22779,10 @@
         <v>47</v>
       </c>
       <c r="N496" t="n">
-        <v>1595.4997222222</v>
+        <v>1595.4994469697</v>
       </c>
       <c r="O496" t="n">
-        <v>74988.4869444434</v>
+        <v>74988.4740075759</v>
       </c>
       <c r="P496" t="n">
         <v>2500</v>
@@ -24036,10 +24036,10 @@
         <v>15</v>
       </c>
       <c r="N522" t="n">
-        <v>9746.8801980198</v>
+        <v>9746.8802</v>
       </c>
       <c r="O522" t="n">
-        <v>146203.202970297</v>
+        <v>146203.203</v>
       </c>
       <c r="P522" t="n">
         <v>18500</v>
@@ -24281,10 +24281,10 @@
         <v>6</v>
       </c>
       <c r="N527" t="n">
-        <v>2992.5708695652</v>
+        <v>2992.5720967742</v>
       </c>
       <c r="O527" t="n">
-        <v>17955.4252173912</v>
+        <v>17955.4325806452</v>
       </c>
       <c r="P527" t="n">
         <v>6000</v>
@@ -24327,10 +24327,10 @@
         <v>164</v>
       </c>
       <c r="N528" t="n">
-        <v>875.69017777778</v>
+        <v>875.6901793722</v>
       </c>
       <c r="O528" t="n">
-        <v>143613.1891555559</v>
+        <v>143613.1894170408</v>
       </c>
       <c r="P528" t="n">
         <v>4500</v>
@@ -25334,10 +25334,10 @@
         <v>8</v>
       </c>
       <c r="N549" t="n">
-        <v>4697.3812903226</v>
+        <v>4697.3813793103</v>
       </c>
       <c r="O549" t="n">
-        <v>37579.0503225808</v>
+        <v>37579.0510344824</v>
       </c>
       <c r="P549" t="n">
         <v>10900</v>
@@ -26937,10 +26937,10 @@
         <v>648</v>
       </c>
       <c r="N583" t="n">
-        <v>665.32380905991</v>
+        <v>665.3238408644399</v>
       </c>
       <c r="O583" t="n">
-        <v>431129.8282708217</v>
+        <v>431129.8488801571</v>
       </c>
       <c r="P583" t="n">
         <v>2900</v>
@@ -28375,10 +28375,10 @@
         <v>100</v>
       </c>
       <c r="N615" t="n">
-        <v>3683.6327400468</v>
+        <v>3683.6327464789</v>
       </c>
       <c r="O615" t="n">
-        <v>368363.27400468</v>
+        <v>368363.27464789</v>
       </c>
       <c r="P615" t="n">
         <v>3600</v>
@@ -28421,10 +28421,10 @@
         <v>337</v>
       </c>
       <c r="N616" t="n">
-        <v>22951.70473822</v>
+        <v>22951.704717477</v>
       </c>
       <c r="O616" t="n">
-        <v>7734724.49678014</v>
+        <v>7734724.489789749</v>
       </c>
       <c r="P616" t="n">
         <v>37900</v>
@@ -28508,10 +28508,10 @@
         <v>43</v>
       </c>
       <c r="N618" t="n">
-        <v>4985.4064864865</v>
+        <v>4985.4066666667</v>
       </c>
       <c r="O618" t="n">
-        <v>214372.4789189195</v>
+        <v>214372.4866666681</v>
       </c>
       <c r="P618" t="n">
         <v>7900</v>
@@ -28610,10 +28610,10 @@
         <v>289</v>
       </c>
       <c r="N620" t="n">
-        <v>1757.3206175772</v>
+        <v>1757.3206205251</v>
       </c>
       <c r="O620" t="n">
-        <v>507865.6584798108</v>
+        <v>507865.6593317538</v>
       </c>
       <c r="P620" t="n">
         <v>2000</v>
@@ -28736,7 +28736,7 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>2800</v>
+        <v>2200</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
@@ -28745,19 +28745,19 @@
         <v>0</v>
       </c>
       <c r="M623" t="n">
-        <v>2800</v>
+        <v>2200</v>
       </c>
       <c r="N623" t="n">
-        <v>220.00299116111</v>
+        <v>220.00227919632</v>
       </c>
       <c r="O623" t="n">
-        <v>616008.375251108</v>
+        <v>484005.014231904</v>
       </c>
       <c r="P623" t="n">
         <v>260</v>
       </c>
       <c r="Q623" t="n">
-        <v>728000</v>
+        <v>572000</v>
       </c>
     </row>
     <row r="624">
@@ -29811,10 +29811,10 @@
         <v>168</v>
       </c>
       <c r="N646" t="n">
-        <v>1319.3609259259</v>
+        <v>1319.3609287926</v>
       </c>
       <c r="O646" t="n">
-        <v>221652.6355555512</v>
+        <v>221652.6360371568</v>
       </c>
       <c r="P646" t="n">
         <v>3500</v>
@@ -30054,10 +30054,10 @@
         <v>158</v>
       </c>
       <c r="N651" t="n">
-        <v>2539.5716651076</v>
+        <v>2539.5716920152</v>
       </c>
       <c r="O651" t="n">
-        <v>401252.3230870008</v>
+        <v>401252.3273384016</v>
       </c>
       <c r="P651" t="n">
         <v>2900</v>
@@ -30100,10 +30100,10 @@
         <v>95</v>
       </c>
       <c r="N652" t="n">
-        <v>4171.6686137441</v>
+        <v>4171.6685988024</v>
       </c>
       <c r="O652" t="n">
-        <v>396308.5183056895</v>
+        <v>396308.516886228</v>
       </c>
       <c r="P652" t="n">
         <v>5000</v>
